--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nchaku/Documents/GitHub/pubertybrain/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6F57F1-411C-594C-8E26-89B79748C104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A063C0BF-9634-0944-BC9A-5DF77A458D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2040" yWindow="500" windowWidth="26380" windowHeight="16460" activeTab="1" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
+    <workbookView xWindow="2040" yWindow="500" windowWidth="26380" windowHeight="16460" activeTab="4" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptive table" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="97">
   <si>
     <t>16.10 (2.98)</t>
   </si>
@@ -376,6 +376,21 @@
       </rPr>
       <t>)</t>
     </r>
+  </si>
+  <si>
+    <t>Model 1</t>
+  </si>
+  <si>
+    <t>Model 2</t>
+  </si>
+  <si>
+    <t>Model 3</t>
+  </si>
+  <si>
+    <t>Model 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 2. </t>
   </si>
 </sst>
 </file>
@@ -1695,9 +1710,29 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA86F85-A8D4-F648-84C3-730F1A42C846}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="C2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nchaku/Documents/GitHub/pubertybrain/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nchaku\Documents\GitHub\pubertybrain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A063C0BF-9634-0944-BC9A-5DF77A458D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9548B466-316A-40C6-8CA5-F307D8B9796E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2040" yWindow="500" windowWidth="26380" windowHeight="16460" activeTab="4" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
+    <workbookView xWindow="1725" yWindow="15" windowWidth="28860" windowHeight="15135" activeTab="4" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptive table" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="127">
   <si>
     <t>16.10 (2.98)</t>
   </si>
@@ -387,17 +387,303 @@
     <t>Model 3</t>
   </si>
   <si>
-    <t>Model 4</t>
-  </si>
-  <si>
     <t xml:space="preserve">Table 2. </t>
+  </si>
+  <si>
+    <t>Means</t>
+  </si>
+  <si>
+    <t>Variances</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Timing</t>
+  </si>
+  <si>
+    <t>Latent variables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Covariances </t>
+  </si>
+  <si>
+    <t>Path coefficients</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Timing      with Tempo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Tempo</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ELA</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>95%</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>CI</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   Intercept</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   Slope</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   Intercept</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> with Slope</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   Intercept</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> with Timing</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   Intercept</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> with Tempo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   Slope</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">      with Tempo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   Timing on Slope</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   ELA    on Intercept</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   ELA    on Slope</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   WM    on Intercept</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   WM    on Slope</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">   ELA    on Timing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ELA    on Tempo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   WM    on Tempo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   WM    on Timing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   WM    on ELA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   WM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -453,13 +739,45 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -492,7 +810,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -513,6 +831,34 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1094,20 +1440,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39987BE7-3659-524A-81AE-D479F97EF698}">
   <dimension ref="A1:F34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="9"/>
       <c r="B2" s="10" t="s">
         <v>75</v>
@@ -1125,7 +1471,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="11" t="s">
         <v>81</v>
@@ -1139,7 +1485,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>72</v>
       </c>
@@ -1149,7 +1495,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>73</v>
       </c>
@@ -1169,7 +1515,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>74</v>
       </c>
@@ -1189,7 +1535,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>70</v>
       </c>
@@ -1209,7 +1555,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>71</v>
       </c>
@@ -1219,7 +1565,7 @@
       <c r="E8" s="12"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>73</v>
       </c>
@@ -1239,7 +1585,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>78</v>
       </c>
@@ -1259,7 +1605,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>79</v>
       </c>
@@ -1279,7 +1625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>74</v>
       </c>
@@ -1299,7 +1645,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>80</v>
       </c>
@@ -1309,7 +1655,7 @@
       <c r="E13" s="12"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>86</v>
       </c>
@@ -1329,7 +1675,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>87</v>
       </c>
@@ -1349,7 +1695,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>88</v>
       </c>
@@ -1369,7 +1715,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>89</v>
       </c>
@@ -1387,7 +1733,7 @@
       </c>
       <c r="F17" s="1"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>83</v>
       </c>
@@ -1397,7 +1743,7 @@
       <c r="E18" s="12"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>73</v>
       </c>
@@ -1417,7 +1763,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>78</v>
       </c>
@@ -1437,7 +1783,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>79</v>
       </c>
@@ -1457,7 +1803,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>74</v>
       </c>
@@ -1477,7 +1823,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>84</v>
       </c>
@@ -1487,7 +1833,7 @@
       <c r="E23" s="12"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>73</v>
       </c>
@@ -1507,7 +1853,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>78</v>
       </c>
@@ -1527,7 +1873,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>79</v>
       </c>
@@ -1547,7 +1893,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>74</v>
       </c>
@@ -1567,7 +1913,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>85</v>
       </c>
@@ -1577,7 +1923,7 @@
       <c r="E28" s="12"/>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>73</v>
       </c>
@@ -1597,7 +1943,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>78</v>
       </c>
@@ -1617,7 +1963,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>79</v>
       </c>
@@ -1637,7 +1983,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>74</v>
       </c>
@@ -1657,7 +2003,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1665,7 +2011,7 @@
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
     </row>
-    <row r="34" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1681,7 +2027,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A749072B-F938-0F49-BE23-243603B2B3D0}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1691,7 +2037,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45875D41-9C56-AA4E-A18A-2D3A4CE169B3}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1701,7 +2047,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A5153E-6E5C-054A-8ACA-5118463B96C5}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1710,29 +2056,1192 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA86F85-A8D4-F648-84C3-730F1A42C846}">
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:R36"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="5.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="11" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="15"/>
+      <c r="B2" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="17"/>
+      <c r="B3" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="19"/>
+      <c r="B4" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="M4" s="20" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="20" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="19">
+        <v>576.59</v>
+      </c>
+      <c r="C6" s="19">
+        <v>1.07</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19">
+        <v>583.54999999999995</v>
+      </c>
+      <c r="G6" s="19">
+        <v>1.51</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" s="19"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="B7" s="19">
+        <v>-93.95</v>
+      </c>
+      <c r="C7" s="19">
+        <v>4.51</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19">
+        <v>-94.05</v>
+      </c>
+      <c r="G7" s="19">
+        <v>4.62</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" s="19"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B9" s="19">
+        <v>-143.01</v>
+      </c>
+      <c r="C9" s="19">
+        <v>19.41</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19">
+        <v>-143.01</v>
+      </c>
+      <c r="G9" s="19">
+        <v>19.260000000000002</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19">
+        <v>-143.02000000000001</v>
+      </c>
+      <c r="K9" s="19">
+        <v>19.260000000000002</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" s="19"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="B10" s="19">
+        <v>6.87</v>
+      </c>
+      <c r="C10" s="19">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19">
+        <v>5.48</v>
+      </c>
+      <c r="G10" s="19">
+        <v>1.05</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19">
+        <v>5.48</v>
+      </c>
+      <c r="K10" s="19">
+        <v>1.05</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M10" s="19"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="22">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="C11" s="22">
+        <v>0.16</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22">
+        <v>0.93</v>
+      </c>
+      <c r="G11" s="22">
+        <v>0.15</v>
+      </c>
+      <c r="H11" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22">
+        <v>0.93</v>
+      </c>
+      <c r="K11" s="22">
+        <v>0.15</v>
+      </c>
+      <c r="L11" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="M11" s="22"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" s="19">
+        <v>-0.08</v>
+      </c>
+      <c r="C12" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="D12" s="21">
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19">
+        <v>-0.08</v>
+      </c>
+      <c r="G12" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="H12" s="21">
+        <v>0.15</v>
+      </c>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19">
+        <v>-0.08</v>
+      </c>
+      <c r="K12" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="L12" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" s="19"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="C13" s="19">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="G13" s="19">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="K13" s="19">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M13" s="19"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="19"/>
+      <c r="M14" s="19"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="B15" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="C15" s="19">
+        <v>0.37</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="19">
+        <v>3.21</v>
+      </c>
+      <c r="G15" s="19">
+        <v>0.38</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19">
+        <v>3.2</v>
+      </c>
+      <c r="K15" s="19">
+        <v>0.38</v>
+      </c>
+      <c r="L15" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M15" s="19"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="F16" s="19">
+        <v>-3.81</v>
+      </c>
+      <c r="G16" s="19">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19">
+        <v>-3.82</v>
+      </c>
+      <c r="K16" s="19">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="L16" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" s="19"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="F17" s="19">
+        <v>0.02</v>
+      </c>
+      <c r="G17" s="19">
+        <v>0.22</v>
+      </c>
+      <c r="H17" s="19">
+        <v>0.94</v>
+      </c>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19">
+        <v>0.01</v>
+      </c>
+      <c r="K17" s="19">
+        <v>0.22</v>
+      </c>
+      <c r="L17" s="21">
+        <v>0.65</v>
+      </c>
+      <c r="M17" s="19"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="F18" s="19">
+        <v>-0.11</v>
+      </c>
+      <c r="G18" s="19">
+        <v>0.01</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="19"/>
+      <c r="J18" s="23">
+        <v>-0.11</v>
+      </c>
+      <c r="K18" s="23">
+        <v>0.01</v>
+      </c>
+      <c r="L18" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M18" s="19"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>108</v>
+      </c>
+      <c r="E19" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="F19" s="19">
+        <v>-0.02</v>
+      </c>
+      <c r="G19" s="19">
+        <v>2E-3</v>
+      </c>
+      <c r="H19" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19">
+        <v>-0.02</v>
+      </c>
+      <c r="K19" s="19">
+        <v>2E-3</v>
+      </c>
+      <c r="L19" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M19" s="19"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="G20" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="I20" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="J20" s="19">
+        <v>0.01</v>
+      </c>
+      <c r="K20" s="19">
+        <v>2E-3</v>
+      </c>
+      <c r="L20" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M20" s="19"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="E21" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="G21" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="H21" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="I21" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="J21" s="19">
+        <v>-2E-3</v>
+      </c>
+      <c r="K21" s="19">
+        <v>0.01</v>
+      </c>
+      <c r="L21" s="21">
+        <v>0.84</v>
+      </c>
+      <c r="M21" s="19"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="H22" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="I22" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="J22" s="19">
+        <v>0.11</v>
+      </c>
+      <c r="K22" s="19">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L22" s="21">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M22" s="19"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="E23" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="H23" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="I23" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="J23" s="19">
+        <v>1.84</v>
+      </c>
+      <c r="K23" s="19">
+        <v>0.41</v>
+      </c>
+      <c r="L23" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M23" s="19"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="E24" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="G24" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="H24" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="I24" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="J24" s="19">
+        <v>-0.17</v>
+      </c>
+      <c r="K24" s="19">
+        <v>0.04</v>
+      </c>
+      <c r="L24" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M24" s="19"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="20" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="C2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I2" t="s">
-        <v>95</v>
-      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="23">
+        <v>12.02</v>
+      </c>
+      <c r="C26" s="23">
+        <v>0.02</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19">
+        <v>12.23</v>
+      </c>
+      <c r="G26" s="19">
+        <v>0.04</v>
+      </c>
+      <c r="H26" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19">
+        <v>12.23</v>
+      </c>
+      <c r="K26" s="19">
+        <v>0.04</v>
+      </c>
+      <c r="L26" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M26" s="19"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" s="19">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="C27" s="19">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19">
+        <v>0.59</v>
+      </c>
+      <c r="G27" s="19">
+        <v>0.01</v>
+      </c>
+      <c r="H27" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19">
+        <v>0.59</v>
+      </c>
+      <c r="K27" s="19">
+        <v>0.01</v>
+      </c>
+      <c r="L27" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M27" s="19"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="F28" s="24">
+        <v>1.83</v>
+      </c>
+      <c r="G28" s="24">
+        <v>0.04</v>
+      </c>
+      <c r="H28" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19">
+        <v>1.83</v>
+      </c>
+      <c r="K28" s="19">
+        <v>0.04</v>
+      </c>
+      <c r="L28" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M28" s="19"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="I29" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="J29" s="19">
+        <v>10.97</v>
+      </c>
+      <c r="K29" s="19">
+        <v>1.21</v>
+      </c>
+      <c r="L29" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" s="19"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="23"/>
+      <c r="J30" s="23"/>
+      <c r="K30" s="23"/>
+      <c r="L30" s="23"/>
+      <c r="M30" s="23"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="B31" s="19">
+        <v>2247.4699999999998</v>
+      </c>
+      <c r="C31" s="19">
+        <v>76.02</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23">
+        <v>2200.12</v>
+      </c>
+      <c r="G31" s="23">
+        <v>14.08</v>
+      </c>
+      <c r="H31" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23">
+        <v>2199.7800000000002</v>
+      </c>
+      <c r="K31" s="23">
+        <v>74.569999999999993</v>
+      </c>
+      <c r="L31" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M31" s="23"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" s="27">
+        <v>93.62</v>
+      </c>
+      <c r="C32" s="27">
+        <v>14.08</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23">
+        <v>93.66</v>
+      </c>
+      <c r="G32" s="23">
+        <v>14.08</v>
+      </c>
+      <c r="H32" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="23"/>
+      <c r="J32" s="23">
+        <v>93.71</v>
+      </c>
+      <c r="K32" s="23">
+        <v>14.08</v>
+      </c>
+      <c r="L32" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M32" s="23"/>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="C33" s="19">
+        <v>0.04</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="G33" s="23">
+        <v>0.03</v>
+      </c>
+      <c r="H33" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I33" s="23"/>
+      <c r="J33" s="23">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="K33" s="23">
+        <v>0.03</v>
+      </c>
+      <c r="L33" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M33" s="23"/>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" s="19">
+        <v>0.02</v>
+      </c>
+      <c r="C34" s="19">
+        <v>1E-3</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23">
+        <v>0.02</v>
+      </c>
+      <c r="G34" s="23">
+        <v>1E-3</v>
+      </c>
+      <c r="H34" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34" s="24"/>
+      <c r="J34" s="24">
+        <v>0.02</v>
+      </c>
+      <c r="K34" s="24">
+        <v>1E-3</v>
+      </c>
+      <c r="L34" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M34" s="24"/>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="B35" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="D35" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="E35" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="F35" s="23">
+        <v>3.26</v>
+      </c>
+      <c r="G35" s="23">
+        <v>0.13</v>
+      </c>
+      <c r="H35" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35" s="24"/>
+      <c r="J35" s="23">
+        <v>3.26</v>
+      </c>
+      <c r="K35" s="23">
+        <v>0.13</v>
+      </c>
+      <c r="L35" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="M35" s="24"/>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="E36" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="F36" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="G36" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="H36" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="I36" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="J36" s="25">
+        <v>7.64</v>
+      </c>
+      <c r="K36" s="25">
+        <v>0.3</v>
+      </c>
+      <c r="L36" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
+      <c r="Q36" s="6"/>
+      <c r="R36" s="6"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="J3:M3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nchaku\Documents\GitHub\pubertybrain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9548B466-316A-40C6-8CA5-F307D8B9796E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C843E2-79B8-4EF8-9093-C52971641E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1725" yWindow="15" windowWidth="28860" windowHeight="15135" activeTab="4" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
+    <workbookView xWindow="-30" yWindow="90" windowWidth="28860" windowHeight="15135" activeTab="4" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptive table" sheetId="1" r:id="rId1"/>
     <sheet name="Correlation table" sheetId="2" r:id="rId2"/>
     <sheet name="Fig1 (Pub)" sheetId="3" r:id="rId3"/>
     <sheet name="Fig2 (Brain)" sheetId="4" r:id="rId4"/>
-    <sheet name="Models" sheetId="6" r:id="rId5"/>
+    <sheet name="CortModels" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="117">
   <si>
     <t>16.10 (2.98)</t>
   </si>
@@ -142,42 +142,6 @@
   </si>
   <si>
     <t>0.47 (0.12)</t>
-  </si>
-  <si>
-    <t>659,950.29 (59,297.14)</t>
-  </si>
-  <si>
-    <t>634,688.69 (50,908.75)</t>
-  </si>
-  <si>
-    <t>682,791.39 (57,045.49)</t>
-  </si>
-  <si>
-    <t>650,855.29 (60,522.18)</t>
-  </si>
-  <si>
-    <t>622,982.82 (52,137.99)</t>
-  </si>
-  <si>
-    <t>674,914.90 (56,831.41)</t>
-  </si>
-  <si>
-    <t>632,872.52 (63,638.18)</t>
-  </si>
-  <si>
-    <t>597,940.65 (51,585.63)</t>
-  </si>
-  <si>
-    <t>663,521.47 (57,091.37)</t>
-  </si>
-  <si>
-    <t>614,766.27 (62,186.19)</t>
-  </si>
-  <si>
-    <t>579,783.70 (49,676.72)</t>
-  </si>
-  <si>
-    <t>646,390.78 (55,013.48)</t>
   </si>
   <si>
     <t>599,882.78 (55,480.87)</t>
@@ -312,9 +276,6 @@
     </r>
   </si>
   <si>
-    <t>Total gray matter volume</t>
-  </si>
-  <si>
     <t>Cortical volume</t>
   </si>
   <si>
@@ -387,9 +348,6 @@
     <t>Model 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Table 2. </t>
-  </si>
-  <si>
     <t>Means</t>
   </si>
   <si>
@@ -677,6 +635,18 @@
   </si>
   <si>
     <t xml:space="preserve">   WM</t>
+  </si>
+  <si>
+    <t>Take out total gray volume</t>
+  </si>
+  <si>
+    <t>Girls</t>
+  </si>
+  <si>
+    <t>Boys</t>
+  </si>
+  <si>
+    <t>Table 2. Cortical volume by sex</t>
   </si>
 </sst>
 </file>
@@ -810,7 +780,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -833,32 +803,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1078,15 +1042,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>85724</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>660400</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:colOff>698500</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>101599</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1101,16 +1065,17 @@
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
-      <xdr:blipFill>
+      <xdr:blipFill rotWithShape="1">
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect t="34238"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="6438900" cy="8674100"/>
+          <a:off x="38100" y="85724"/>
+          <a:ext cx="6527800" cy="5616575"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1439,7 +1404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39987BE7-3659-524A-81AE-D479F97EF698}">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.875" bestFit="1" customWidth="1"/>
@@ -1450,44 +1415,44 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="9"/>
       <c r="B2" s="10" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="11" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E3" s="11"/>
       <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1497,7 +1462,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>0</v>
@@ -1517,7 +1482,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>3</v>
@@ -1537,7 +1502,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>6</v>
@@ -1557,7 +1522,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1567,7 +1532,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>9</v>
@@ -1587,7 +1552,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>12</v>
@@ -1607,7 +1572,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>15</v>
@@ -1627,7 +1592,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>18</v>
@@ -1647,7 +1612,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1657,7 +1622,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>21</v>
@@ -1677,7 +1642,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>25</v>
@@ -1697,7 +1662,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>28</v>
@@ -1717,7 +1682,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>31</v>
@@ -1731,11 +1696,11 @@
       <c r="E17" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="1"/>
+      <c r="F17" s="23"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1745,7 +1710,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>34</v>
@@ -1760,12 +1725,12 @@
         <v>24</v>
       </c>
       <c r="F19" s="1">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>37</v>
@@ -1780,12 +1745,12 @@
         <v>24</v>
       </c>
       <c r="F20" s="1">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>40</v>
@@ -1800,12 +1765,12 @@
         <v>24</v>
       </c>
       <c r="F21" s="1">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>43</v>
@@ -1820,12 +1785,12 @@
         <v>24</v>
       </c>
       <c r="F22" s="1">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -1835,7 +1800,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>46</v>
@@ -1850,12 +1815,12 @@
         <v>24</v>
       </c>
       <c r="F24" s="1">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>49</v>
@@ -1870,12 +1835,12 @@
         <v>24</v>
       </c>
       <c r="F25" s="1">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>52</v>
@@ -1890,134 +1855,44 @@
         <v>24</v>
       </c>
       <c r="F26" s="1">
-        <v>1.18</v>
+        <v>1.1299999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B27" s="3" t="s">
+      <c r="A27" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E27" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F27" s="1">
-        <v>1.24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="12"/>
+      <c r="E27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" s="6">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E29" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29" s="1">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F30" s="1">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E31" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F31" s="1">
-        <v>1.1299999999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="F32" s="6">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-    </row>
-    <row r="34" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
+    <row r="29" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="4"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2026,9 +1901,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A749072B-F938-0F49-BE23-243603B2B3D0}">
-  <dimension ref="A1"/>
+  <dimension ref="M2"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="2" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2056,1191 +1937,1644 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA86F85-A8D4-F648-84C3-730F1A42C846}">
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:Z36"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.75" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="5.875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="4.625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="4.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.75" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="5.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="11" style="1"/>
+    <col min="14" max="14" width="2.875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="14"/>
+      <c r="B2" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="22"/>
+      <c r="O2" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="22"/>
+      <c r="U2" s="22"/>
+      <c r="V2" s="22"/>
+      <c r="W2" s="22"/>
+      <c r="X2" s="22"/>
+      <c r="Y2" s="22"/>
+      <c r="Z2" s="22"/>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="15"/>
+      <c r="B3" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="O3" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="P3" s="21"/>
+      <c r="Q3" s="21"/>
+      <c r="R3" s="21"/>
+      <c r="S3" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="T3" s="21"/>
+      <c r="U3" s="21"/>
+      <c r="V3" s="21"/>
+      <c r="W3" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="X3" s="21"/>
+      <c r="Y3" s="21"/>
+      <c r="Z3" s="21"/>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="16"/>
+      <c r="B4" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="15"/>
-      <c r="B2" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="18" t="s">
+      <c r="F4" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="H4" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="19"/>
-      <c r="B4" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="F4" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="I4" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="J4" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="K4" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="L4" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="M4" s="20" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="B6" s="19">
+      <c r="I4" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="M4" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="O4" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="P4" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q4" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="R4" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="S4" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="T4" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="U4" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="V4" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="W4" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="X4" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y4" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z4" s="17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="16"/>
+      <c r="V5" s="16"/>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="16"/>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="16">
         <v>576.59</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="16">
         <v>1.07</v>
       </c>
-      <c r="D6" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19">
+      <c r="D6" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16">
         <v>583.54999999999995</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="16">
         <v>1.51</v>
       </c>
-      <c r="H6" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="19"/>
+      <c r="H6" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="16"/>
       <c r="J6" s="19"/>
       <c r="K6" s="19"/>
-      <c r="L6" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" s="19"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="B7" s="19">
+      <c r="L6" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="16"/>
+      <c r="S6" s="16"/>
+      <c r="T6" s="16"/>
+      <c r="U6" s="18"/>
+      <c r="V6" s="16"/>
+      <c r="W6" s="19"/>
+      <c r="X6" s="19"/>
+      <c r="Y6" s="18"/>
+      <c r="Z6" s="16"/>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="16">
         <v>-93.95</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="16">
         <v>4.51</v>
       </c>
-      <c r="D7" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19">
+      <c r="D7" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16">
         <v>-94.05</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="16">
         <v>4.62</v>
       </c>
-      <c r="H7" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="19"/>
+      <c r="H7" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="16"/>
       <c r="J7" s="19"/>
       <c r="K7" s="19"/>
-      <c r="L7" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M7" s="19"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
+      <c r="L7" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" s="16"/>
+      <c r="O7" s="16"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="18"/>
+      <c r="R7" s="16"/>
+      <c r="S7" s="16"/>
+      <c r="T7" s="16"/>
+      <c r="U7" s="18"/>
+      <c r="V7" s="16"/>
+      <c r="W7" s="19"/>
+      <c r="X7" s="19"/>
+      <c r="Y7" s="18"/>
+      <c r="Z7" s="16"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="16"/>
+      <c r="S8" s="16"/>
+      <c r="T8" s="16"/>
+      <c r="U8" s="16"/>
+      <c r="V8" s="16"/>
+      <c r="W8" s="16"/>
+      <c r="X8" s="16"/>
+      <c r="Y8" s="16"/>
+      <c r="Z8" s="16"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" s="16">
+        <v>-143.01</v>
+      </c>
+      <c r="C9" s="16">
+        <v>19.41</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16">
+        <v>-143.01</v>
+      </c>
+      <c r="G9" s="16">
+        <v>19.260000000000002</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16">
+        <v>-143.02000000000001</v>
+      </c>
+      <c r="K9" s="16">
+        <v>19.260000000000002</v>
+      </c>
+      <c r="L9" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="18"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="16"/>
+      <c r="U9" s="18"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="16"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="18"/>
+      <c r="Z9" s="16"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" s="16">
+        <v>6.87</v>
+      </c>
+      <c r="C10" s="16">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16">
+        <v>5.48</v>
+      </c>
+      <c r="G10" s="16">
+        <v>1.05</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16">
+        <v>5.48</v>
+      </c>
+      <c r="K10" s="16">
+        <v>1.05</v>
+      </c>
+      <c r="L10" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="18"/>
+      <c r="R10" s="16"/>
+      <c r="S10" s="16"/>
+      <c r="T10" s="16"/>
+      <c r="U10" s="18"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="16"/>
+      <c r="X10" s="16"/>
+      <c r="Y10" s="18"/>
+      <c r="Z10" s="16"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="B11" s="24">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="C11" s="24">
+        <v>0.16</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24">
+        <v>0.93</v>
+      </c>
+      <c r="G11" s="24">
+        <v>0.15</v>
+      </c>
+      <c r="H11" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24">
+        <v>0.93</v>
+      </c>
+      <c r="K11" s="24">
+        <v>0.15</v>
+      </c>
+      <c r="L11" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="M11" s="24"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="24"/>
+      <c r="S11" s="24"/>
+      <c r="T11" s="24"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="24"/>
+      <c r="W11" s="24"/>
+      <c r="X11" s="24"/>
+      <c r="Y11" s="25"/>
+      <c r="Z11" s="24"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B12" s="16">
+        <v>-0.08</v>
+      </c>
+      <c r="C12" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="D12" s="18">
+        <v>0.15</v>
+      </c>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16">
+        <v>-0.08</v>
+      </c>
+      <c r="G12" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="H12" s="18">
+        <v>0.15</v>
+      </c>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16">
+        <v>-0.08</v>
+      </c>
+      <c r="K12" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="L12" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="18"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="18"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="16"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="18"/>
+      <c r="Z12" s="16"/>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="C13" s="16">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="G13" s="16">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="K13" s="16">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="L13" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M13" s="16"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="18"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="16"/>
+      <c r="T13" s="16"/>
+      <c r="U13" s="18"/>
+      <c r="V13" s="16"/>
+      <c r="W13" s="16"/>
+      <c r="X13" s="16"/>
+      <c r="Y13" s="18"/>
+      <c r="Z13" s="16"/>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+      <c r="T14" s="16"/>
+      <c r="U14" s="16"/>
+      <c r="V14" s="16"/>
+      <c r="W14" s="16"/>
+      <c r="X14" s="16"/>
+      <c r="Y14" s="16"/>
+      <c r="Z14" s="16"/>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="16">
+        <v>3.2</v>
+      </c>
+      <c r="C15" s="16">
+        <v>0.37</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="18"/>
+      <c r="F15" s="16">
+        <v>3.21</v>
+      </c>
+      <c r="G15" s="16">
+        <v>0.38</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16">
+        <v>3.2</v>
+      </c>
+      <c r="K15" s="16">
+        <v>0.38</v>
+      </c>
+      <c r="L15" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="18"/>
+      <c r="R15" s="18"/>
+      <c r="S15" s="16"/>
+      <c r="T15" s="16"/>
+      <c r="U15" s="18"/>
+      <c r="V15" s="16"/>
+      <c r="W15" s="16"/>
+      <c r="X15" s="16"/>
+      <c r="Y15" s="18"/>
+      <c r="Z15" s="16"/>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F16" s="16">
+        <v>-3.81</v>
+      </c>
+      <c r="G16" s="16">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16">
+        <v>-3.82</v>
+      </c>
+      <c r="K16" s="16">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="L16" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" s="16"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="16"/>
+      <c r="T16" s="16"/>
+      <c r="U16" s="18"/>
+      <c r="V16" s="16"/>
+      <c r="W16" s="16"/>
+      <c r="X16" s="16"/>
+      <c r="Y16" s="18"/>
+      <c r="Z16" s="16"/>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F17" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="G17" s="16">
+        <v>0.22</v>
+      </c>
+      <c r="H17" s="16">
+        <v>0.94</v>
+      </c>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="K17" s="16">
+        <v>0.22</v>
+      </c>
+      <c r="L17" s="18">
+        <v>0.65</v>
+      </c>
+      <c r="M17" s="16"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="16"/>
+      <c r="S17" s="16"/>
+      <c r="T17" s="16"/>
+      <c r="U17" s="16"/>
+      <c r="V17" s="16"/>
+      <c r="W17" s="16"/>
+      <c r="X17" s="16"/>
+      <c r="Y17" s="18"/>
+      <c r="Z17" s="16"/>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F18" s="16">
+        <v>-0.11</v>
+      </c>
+      <c r="G18" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="H18" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16">
+        <v>-0.11</v>
+      </c>
+      <c r="K18" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="L18" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M18" s="16"/>
+      <c r="O18" s="16"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="16"/>
+      <c r="S18" s="16"/>
+      <c r="T18" s="16"/>
+      <c r="U18" s="18"/>
+      <c r="V18" s="16"/>
+      <c r="W18" s="16"/>
+      <c r="X18" s="16"/>
+      <c r="Y18" s="18"/>
+      <c r="Z18" s="16"/>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A19" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="16">
+        <v>-0.02</v>
+      </c>
+      <c r="G19" s="16">
+        <v>2E-3</v>
+      </c>
+      <c r="H19" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16">
+        <v>-0.02</v>
+      </c>
+      <c r="K19" s="16">
+        <v>2E-3</v>
+      </c>
+      <c r="L19" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="16"/>
+      <c r="S19" s="16"/>
+      <c r="T19" s="16"/>
+      <c r="U19" s="18"/>
+      <c r="V19" s="16"/>
+      <c r="W19" s="16"/>
+      <c r="X19" s="16"/>
+      <c r="Y19" s="18"/>
+      <c r="Z19" s="16"/>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A20" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J20" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="K20" s="16">
+        <v>2E-3</v>
+      </c>
+      <c r="L20" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M20" s="16"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="16"/>
+      <c r="S20" s="16"/>
+      <c r="T20" s="16"/>
+      <c r="U20" s="16"/>
+      <c r="V20" s="16"/>
+      <c r="W20" s="16"/>
+      <c r="X20" s="16"/>
+      <c r="Y20" s="18"/>
+      <c r="Z20" s="16"/>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J21" s="16">
+        <v>-2E-3</v>
+      </c>
+      <c r="K21" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="L21" s="18">
+        <v>0.84</v>
+      </c>
+      <c r="M21" s="16"/>
+      <c r="O21" s="16"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="16"/>
+      <c r="R21" s="16"/>
+      <c r="S21" s="16"/>
+      <c r="T21" s="16"/>
+      <c r="U21" s="16"/>
+      <c r="V21" s="16"/>
+      <c r="W21" s="16"/>
+      <c r="X21" s="16"/>
+      <c r="Y21" s="18"/>
+      <c r="Z21" s="16"/>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J22" s="16">
+        <v>0.11</v>
+      </c>
+      <c r="K22" s="16">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="L22" s="18">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="M22" s="16"/>
+      <c r="O22" s="16"/>
+      <c r="P22" s="16"/>
+      <c r="Q22" s="16"/>
+      <c r="R22" s="16"/>
+      <c r="S22" s="16"/>
+      <c r="T22" s="16"/>
+      <c r="U22" s="16"/>
+      <c r="V22" s="16"/>
+      <c r="W22" s="16"/>
+      <c r="X22" s="16"/>
+      <c r="Y22" s="18"/>
+      <c r="Z22" s="16"/>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A23" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J23" s="16">
+        <v>1.84</v>
+      </c>
+      <c r="K23" s="16">
+        <v>0.41</v>
+      </c>
+      <c r="L23" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M23" s="16"/>
+      <c r="O23" s="16"/>
+      <c r="P23" s="16"/>
+      <c r="Q23" s="16"/>
+      <c r="R23" s="16"/>
+      <c r="S23" s="16"/>
+      <c r="T23" s="16"/>
+      <c r="U23" s="16"/>
+      <c r="V23" s="16"/>
+      <c r="W23" s="16"/>
+      <c r="X23" s="16"/>
+      <c r="Y23" s="18"/>
+      <c r="Z23" s="16"/>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A24" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J24" s="16">
+        <v>-0.17</v>
+      </c>
+      <c r="K24" s="16">
+        <v>0.04</v>
+      </c>
+      <c r="L24" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M24" s="16"/>
+      <c r="O24" s="16"/>
+      <c r="P24" s="16"/>
+      <c r="Q24" s="16"/>
+      <c r="R24" s="16"/>
+      <c r="S24" s="16"/>
+      <c r="T24" s="16"/>
+      <c r="U24" s="16"/>
+      <c r="V24" s="16"/>
+      <c r="W24" s="16"/>
+      <c r="X24" s="16"/>
+      <c r="Y24" s="18"/>
+      <c r="Z24" s="16"/>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
+      <c r="M25" s="16"/>
+      <c r="O25" s="16"/>
+      <c r="P25" s="16"/>
+      <c r="Q25" s="16"/>
+      <c r="R25" s="16"/>
+      <c r="S25" s="16"/>
+      <c r="T25" s="16"/>
+      <c r="U25" s="16"/>
+      <c r="V25" s="16"/>
+      <c r="W25" s="16"/>
+      <c r="X25" s="16"/>
+      <c r="Y25" s="16"/>
+      <c r="Z25" s="16"/>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="16">
+        <v>12.02</v>
+      </c>
+      <c r="C26" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16">
+        <v>12.23</v>
+      </c>
+      <c r="G26" s="16">
+        <v>0.04</v>
+      </c>
+      <c r="H26" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16">
+        <v>12.23</v>
+      </c>
+      <c r="K26" s="16">
+        <v>0.04</v>
+      </c>
+      <c r="L26" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M26" s="16"/>
+      <c r="O26" s="16"/>
+      <c r="P26" s="16"/>
+      <c r="Q26" s="18"/>
+      <c r="R26" s="16"/>
+      <c r="S26" s="16"/>
+      <c r="T26" s="16"/>
+      <c r="U26" s="18"/>
+      <c r="V26" s="16"/>
+      <c r="W26" s="16"/>
+      <c r="X26" s="16"/>
+      <c r="Y26" s="18"/>
+      <c r="Z26" s="16"/>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A27" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" s="16">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="C27" s="16">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16">
+        <v>0.59</v>
+      </c>
+      <c r="G27" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="H27" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16">
+        <v>0.59</v>
+      </c>
+      <c r="K27" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="L27" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M27" s="16"/>
+      <c r="O27" s="16"/>
+      <c r="P27" s="16"/>
+      <c r="Q27" s="18"/>
+      <c r="R27" s="16"/>
+      <c r="S27" s="16"/>
+      <c r="T27" s="16"/>
+      <c r="U27" s="18"/>
+      <c r="V27" s="16"/>
+      <c r="W27" s="16"/>
+      <c r="X27" s="16"/>
+      <c r="Y27" s="18"/>
+      <c r="Z27" s="16"/>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A28" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F28" s="16">
+        <v>1.83</v>
+      </c>
+      <c r="G28" s="16">
+        <v>0.04</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16">
+        <v>1.83</v>
+      </c>
+      <c r="K28" s="16">
+        <v>0.04</v>
+      </c>
+      <c r="L28" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M28" s="16"/>
+      <c r="O28" s="16"/>
+      <c r="P28" s="16"/>
+      <c r="Q28" s="16"/>
+      <c r="R28" s="16"/>
+      <c r="S28" s="16"/>
+      <c r="T28" s="16"/>
+      <c r="U28" s="18"/>
+      <c r="V28" s="16"/>
+      <c r="W28" s="16"/>
+      <c r="X28" s="16"/>
+      <c r="Y28" s="18"/>
+      <c r="Z28" s="16"/>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A29" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="B9" s="19">
-        <v>-143.01</v>
-      </c>
-      <c r="C9" s="19">
-        <v>19.41</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19">
-        <v>-143.01</v>
-      </c>
-      <c r="G9" s="19">
-        <v>19.260000000000002</v>
-      </c>
-      <c r="H9" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19">
-        <v>-143.02000000000001</v>
-      </c>
-      <c r="K9" s="19">
-        <v>19.260000000000002</v>
-      </c>
-      <c r="L9" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M9" s="19"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="B10" s="19">
-        <v>6.87</v>
-      </c>
-      <c r="C10" s="19">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19">
-        <v>5.48</v>
-      </c>
-      <c r="G10" s="19">
-        <v>1.05</v>
-      </c>
-      <c r="H10" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19">
-        <v>5.48</v>
-      </c>
-      <c r="K10" s="19">
-        <v>1.05</v>
-      </c>
-      <c r="L10" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M10" s="19"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="B11" s="22">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="C11" s="22">
-        <v>0.16</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22">
-        <v>0.93</v>
-      </c>
-      <c r="G11" s="22">
-        <v>0.15</v>
-      </c>
-      <c r="H11" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22">
-        <v>0.93</v>
-      </c>
-      <c r="K11" s="22">
-        <v>0.15</v>
-      </c>
-      <c r="L11" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="M11" s="22"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>115</v>
-      </c>
-      <c r="B12" s="19">
-        <v>-0.08</v>
-      </c>
-      <c r="C12" s="19">
-        <v>0.05</v>
-      </c>
-      <c r="D12" s="21">
-        <v>0.15</v>
-      </c>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19">
-        <v>-0.08</v>
-      </c>
-      <c r="G12" s="19">
-        <v>0.05</v>
-      </c>
-      <c r="H12" s="21">
-        <v>0.15</v>
-      </c>
-      <c r="I12" s="19"/>
-      <c r="J12" s="19">
-        <v>-0.08</v>
-      </c>
-      <c r="K12" s="19">
-        <v>0.05</v>
-      </c>
-      <c r="L12" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M12" s="19"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="B13" s="19">
-        <v>0.05</v>
-      </c>
-      <c r="C13" s="19">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19">
-        <v>0.05</v>
-      </c>
-      <c r="G13" s="19">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="H13" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19">
-        <v>0.05</v>
-      </c>
-      <c r="K13" s="19">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="L13" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M13" s="19"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="B15" s="19">
-        <v>3.2</v>
-      </c>
-      <c r="C15" s="19">
-        <v>0.37</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="21"/>
-      <c r="F15" s="19">
-        <v>3.21</v>
-      </c>
-      <c r="G15" s="19">
-        <v>0.38</v>
-      </c>
-      <c r="H15" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I15" s="19"/>
-      <c r="J15" s="19">
-        <v>3.2</v>
-      </c>
-      <c r="K15" s="19">
-        <v>0.38</v>
-      </c>
-      <c r="L15" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M15" s="19"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="F16" s="19">
-        <v>-3.81</v>
-      </c>
-      <c r="G16" s="19">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="H16" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19">
-        <v>-3.82</v>
-      </c>
-      <c r="K16" s="19">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="L16" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M16" s="19"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="E17" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="F17" s="19">
+      <c r="B29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J29" s="16">
+        <v>10.97</v>
+      </c>
+      <c r="K29" s="16">
+        <v>1.21</v>
+      </c>
+      <c r="L29" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" s="16"/>
+      <c r="O29" s="16"/>
+      <c r="P29" s="16"/>
+      <c r="Q29" s="16"/>
+      <c r="R29" s="16"/>
+      <c r="S29" s="16"/>
+      <c r="T29" s="16"/>
+      <c r="U29" s="16"/>
+      <c r="V29" s="16"/>
+      <c r="W29" s="16"/>
+      <c r="X29" s="16"/>
+      <c r="Y29" s="18"/>
+      <c r="Z29" s="16"/>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+      <c r="M30" s="16"/>
+      <c r="O30" s="16"/>
+      <c r="P30" s="16"/>
+      <c r="Q30" s="16"/>
+      <c r="R30" s="16"/>
+      <c r="S30" s="16"/>
+      <c r="T30" s="16"/>
+      <c r="U30" s="16"/>
+      <c r="V30" s="16"/>
+      <c r="W30" s="16"/>
+      <c r="X30" s="16"/>
+      <c r="Y30" s="16"/>
+      <c r="Z30" s="16"/>
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A31" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="16">
+        <v>2247.4699999999998</v>
+      </c>
+      <c r="C31" s="16">
+        <v>76.02</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16">
+        <v>2200.12</v>
+      </c>
+      <c r="G31" s="16">
+        <v>14.08</v>
+      </c>
+      <c r="H31" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" s="16"/>
+      <c r="J31" s="16">
+        <v>2199.7800000000002</v>
+      </c>
+      <c r="K31" s="16">
+        <v>74.569999999999993</v>
+      </c>
+      <c r="L31" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M31" s="16"/>
+      <c r="O31" s="16"/>
+      <c r="P31" s="16"/>
+      <c r="Q31" s="18"/>
+      <c r="R31" s="16"/>
+      <c r="S31" s="16"/>
+      <c r="T31" s="16"/>
+      <c r="U31" s="18"/>
+      <c r="V31" s="16"/>
+      <c r="W31" s="16"/>
+      <c r="X31" s="16"/>
+      <c r="Y31" s="18"/>
+      <c r="Z31" s="16"/>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A32" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B32" s="16">
+        <v>93.62</v>
+      </c>
+      <c r="C32" s="16">
+        <v>14.08</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16">
+        <v>93.66</v>
+      </c>
+      <c r="G32" s="16">
+        <v>14.08</v>
+      </c>
+      <c r="H32" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16">
+        <v>93.71</v>
+      </c>
+      <c r="K32" s="16">
+        <v>14.08</v>
+      </c>
+      <c r="L32" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M32" s="16"/>
+      <c r="O32" s="16"/>
+      <c r="P32" s="16"/>
+      <c r="Q32" s="18"/>
+      <c r="R32" s="16"/>
+      <c r="S32" s="16"/>
+      <c r="T32" s="16"/>
+      <c r="U32" s="18"/>
+      <c r="V32" s="16"/>
+      <c r="W32" s="16"/>
+      <c r="X32" s="16"/>
+      <c r="Y32" s="18"/>
+      <c r="Z32" s="16"/>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A33" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B33" s="16">
+        <v>1.2</v>
+      </c>
+      <c r="C33" s="16">
+        <v>0.04</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="G33" s="16">
+        <v>0.03</v>
+      </c>
+      <c r="H33" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I33" s="16"/>
+      <c r="J33" s="16">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="K33" s="16">
+        <v>0.03</v>
+      </c>
+      <c r="L33" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M33" s="16"/>
+      <c r="O33" s="16"/>
+      <c r="P33" s="16"/>
+      <c r="Q33" s="18"/>
+      <c r="R33" s="16"/>
+      <c r="S33" s="16"/>
+      <c r="T33" s="16"/>
+      <c r="U33" s="18"/>
+      <c r="V33" s="16"/>
+      <c r="W33" s="16"/>
+      <c r="X33" s="16"/>
+      <c r="Y33" s="18"/>
+      <c r="Z33" s="16"/>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A34" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" s="16">
         <v>0.02</v>
       </c>
-      <c r="G17" s="19">
-        <v>0.22</v>
-      </c>
-      <c r="H17" s="19">
-        <v>0.94</v>
-      </c>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19">
-        <v>0.01</v>
-      </c>
-      <c r="K17" s="19">
-        <v>0.22</v>
-      </c>
-      <c r="L17" s="21">
-        <v>0.65</v>
-      </c>
-      <c r="M17" s="19"/>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="D18" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="F18" s="19">
-        <v>-0.11</v>
-      </c>
-      <c r="G18" s="19">
-        <v>0.01</v>
-      </c>
-      <c r="H18" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I18" s="19"/>
-      <c r="J18" s="23">
-        <v>-0.11</v>
-      </c>
-      <c r="K18" s="23">
-        <v>0.01</v>
-      </c>
-      <c r="L18" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M18" s="19"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="D19" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="F19" s="19">
-        <v>-0.02</v>
-      </c>
-      <c r="G19" s="19">
-        <v>2E-3</v>
-      </c>
-      <c r="H19" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19">
-        <v>-0.02</v>
-      </c>
-      <c r="K19" s="19">
-        <v>2E-3</v>
-      </c>
-      <c r="L19" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M19" s="19"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="F20" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="G20" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="H20" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="I20" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="J20" s="19">
-        <v>0.01</v>
-      </c>
-      <c r="K20" s="19">
-        <v>2E-3</v>
-      </c>
-      <c r="L20" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M20" s="19"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="E21" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="G21" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="H21" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="I21" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="J21" s="19">
-        <v>-2E-3</v>
-      </c>
-      <c r="K21" s="19">
-        <v>0.01</v>
-      </c>
-      <c r="L21" s="21">
-        <v>0.84</v>
-      </c>
-      <c r="M21" s="19"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="G22" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="H22" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="I22" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="J22" s="19">
-        <v>0.11</v>
-      </c>
-      <c r="K22" s="19">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="L22" s="21">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="M22" s="19"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="E23" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="H23" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="I23" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="J23" s="19">
-        <v>1.84</v>
-      </c>
-      <c r="K23" s="19">
-        <v>0.41</v>
-      </c>
-      <c r="L23" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M23" s="19"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="D24" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="E24" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="F24" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="G24" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="H24" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="I24" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="J24" s="19">
-        <v>-0.17</v>
-      </c>
-      <c r="K24" s="19">
-        <v>0.04</v>
-      </c>
-      <c r="L24" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M24" s="19"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="19"/>
-      <c r="M25" s="19"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="B26" s="23">
-        <v>12.02</v>
-      </c>
-      <c r="C26" s="23">
+      <c r="C34" s="16">
+        <v>1E-3</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16">
         <v>0.02</v>
       </c>
-      <c r="D26" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19">
-        <v>12.23</v>
-      </c>
-      <c r="G26" s="19">
-        <v>0.04</v>
-      </c>
-      <c r="H26" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I26" s="19"/>
-      <c r="J26" s="19">
-        <v>12.23</v>
-      </c>
-      <c r="K26" s="19">
-        <v>0.04</v>
-      </c>
-      <c r="L26" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M26" s="19"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="B27" s="19">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="C27" s="19">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19">
-        <v>0.59</v>
-      </c>
-      <c r="G27" s="19">
-        <v>0.01</v>
-      </c>
-      <c r="H27" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19">
-        <v>0.59</v>
-      </c>
-      <c r="K27" s="19">
-        <v>0.01</v>
-      </c>
-      <c r="L27" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M27" s="19"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="D28" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="E28" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="F28" s="24">
-        <v>1.83</v>
-      </c>
-      <c r="G28" s="24">
-        <v>0.04</v>
-      </c>
-      <c r="H28" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19">
-        <v>1.83</v>
-      </c>
-      <c r="K28" s="19">
-        <v>0.04</v>
-      </c>
-      <c r="L28" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M28" s="19"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="C29" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="D29" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="E29" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="G29" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="H29" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="I29" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="J29" s="19">
-        <v>10.97</v>
-      </c>
-      <c r="K29" s="19">
-        <v>1.21</v>
-      </c>
-      <c r="L29" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M29" s="19"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A30" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="23"/>
-      <c r="J30" s="23"/>
-      <c r="K30" s="23"/>
-      <c r="L30" s="23"/>
-      <c r="M30" s="23"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="B31" s="19">
-        <v>2247.4699999999998</v>
-      </c>
-      <c r="C31" s="19">
-        <v>76.02</v>
-      </c>
-      <c r="D31" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23">
-        <v>2200.12</v>
-      </c>
-      <c r="G31" s="23">
-        <v>14.08</v>
-      </c>
-      <c r="H31" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I31" s="23"/>
-      <c r="J31" s="23">
-        <v>2199.7800000000002</v>
-      </c>
-      <c r="K31" s="23">
-        <v>74.569999999999993</v>
-      </c>
-      <c r="L31" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M31" s="23"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="B32" s="27">
-        <v>93.62</v>
-      </c>
-      <c r="C32" s="27">
-        <v>14.08</v>
-      </c>
-      <c r="D32" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23">
-        <v>93.66</v>
-      </c>
-      <c r="G32" s="23">
-        <v>14.08</v>
-      </c>
-      <c r="H32" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I32" s="23"/>
-      <c r="J32" s="23">
-        <v>93.71</v>
-      </c>
-      <c r="K32" s="23">
-        <v>14.08</v>
-      </c>
-      <c r="L32" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M32" s="23"/>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="B33" s="19">
-        <v>1.2</v>
-      </c>
-      <c r="C33" s="19">
-        <v>0.04</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="G33" s="23">
-        <v>0.03</v>
-      </c>
-      <c r="H33" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I33" s="23"/>
-      <c r="J33" s="23">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="K33" s="23">
-        <v>0.03</v>
-      </c>
-      <c r="L33" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M33" s="23"/>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="B34" s="19">
+      <c r="G34" s="16">
+        <v>1E-3</v>
+      </c>
+      <c r="H34" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34" s="16"/>
+      <c r="J34" s="16">
         <v>0.02</v>
       </c>
-      <c r="C34" s="19">
+      <c r="K34" s="16">
         <v>1E-3</v>
       </c>
-      <c r="D34" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="23"/>
-      <c r="F34" s="23">
-        <v>0.02</v>
-      </c>
-      <c r="G34" s="23">
-        <v>1E-3</v>
-      </c>
-      <c r="H34" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I34" s="24"/>
-      <c r="J34" s="24">
-        <v>0.02</v>
-      </c>
-      <c r="K34" s="24">
-        <v>1E-3</v>
-      </c>
-      <c r="L34" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M34" s="24"/>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A35" s="24" t="s">
-        <v>107</v>
-      </c>
-      <c r="B35" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="C35" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="D35" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="E35" s="24" t="s">
-        <v>108</v>
-      </c>
-      <c r="F35" s="23">
+      <c r="L34" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M34" s="16"/>
+      <c r="O34" s="16"/>
+      <c r="P34" s="16"/>
+      <c r="Q34" s="18"/>
+      <c r="R34" s="16"/>
+      <c r="S34" s="16"/>
+      <c r="T34" s="16"/>
+      <c r="U34" s="18"/>
+      <c r="V34" s="16"/>
+      <c r="W34" s="16"/>
+      <c r="X34" s="16"/>
+      <c r="Y34" s="18"/>
+      <c r="Z34" s="16"/>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A35" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F35" s="16">
         <v>3.26</v>
       </c>
-      <c r="G35" s="23">
+      <c r="G35" s="16">
         <v>0.13</v>
       </c>
-      <c r="H35" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="I35" s="24"/>
-      <c r="J35" s="23">
+      <c r="H35" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35" s="16"/>
+      <c r="J35" s="16">
         <v>3.26</v>
       </c>
-      <c r="K35" s="23">
+      <c r="K35" s="16">
         <v>0.13</v>
       </c>
-      <c r="L35" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="M35" s="24"/>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A36" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="B36" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="C36" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="D36" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="E36" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="F36" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="G36" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="H36" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="I36" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="J36" s="25">
+      <c r="L35" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M35" s="16"/>
+      <c r="O35" s="16"/>
+      <c r="P35" s="16"/>
+      <c r="Q35" s="16"/>
+      <c r="R35" s="16"/>
+      <c r="S35" s="16"/>
+      <c r="T35" s="16"/>
+      <c r="U35" s="18"/>
+      <c r="V35" s="16"/>
+      <c r="W35" s="16"/>
+      <c r="X35" s="16"/>
+      <c r="Y35" s="18"/>
+      <c r="Z35" s="16"/>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A36" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="H36" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="I36" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="J36" s="15">
         <v>7.64</v>
       </c>
-      <c r="K36" s="25">
+      <c r="K36" s="15">
         <v>0.3</v>
       </c>
-      <c r="L36" s="29" t="s">
+      <c r="L36" s="20" t="s">
         <v>24</v>
       </c>
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="6"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="6"/>
+      <c r="O36" s="15"/>
+      <c r="P36" s="15"/>
+      <c r="Q36" s="15"/>
+      <c r="R36" s="15"/>
+      <c r="S36" s="15"/>
+      <c r="T36" s="15"/>
+      <c r="U36" s="15"/>
+      <c r="V36" s="15"/>
+      <c r="W36" s="15"/>
+      <c r="X36" s="15"/>
+      <c r="Y36" s="20"/>
+      <c r="Z36" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="F3:I3"/>
     <mergeCell ref="J3:M3"/>
+    <mergeCell ref="O2:Z2"/>
+    <mergeCell ref="O3:R3"/>
+    <mergeCell ref="S3:V3"/>
+    <mergeCell ref="W3:Z3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nchaku\Documents\GitHub\pubertybrain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3C843E2-79B8-4EF8-9093-C52971641E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C85D9B2-5526-4A3F-887C-73776185B9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30" yWindow="90" windowWidth="28860" windowHeight="15135" activeTab="4" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
+    <workbookView xWindow="-60" yWindow="90" windowWidth="28860" windowHeight="15135" activeTab="4" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptive table" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="121">
   <si>
     <t>16.10 (2.98)</t>
   </si>
@@ -647,6 +647,30 @@
   </si>
   <si>
     <t>Table 2. Cortical volume by sex</t>
+  </si>
+  <si>
+    <t>Fit statistics</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   sa</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>BIC</t>
+    </r>
+  </si>
+  <si>
+    <t>2.58, 3.81</t>
+  </si>
+  <si>
+    <t>-174.94, -111.08</t>
   </si>
 </sst>
 </file>
@@ -780,7 +804,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -811,20 +835,26 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="11" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1696,7 +1726,7 @@
       <c r="E17" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="23"/>
+      <c r="F17" s="20"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
@@ -1937,14 +1967,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA86F85-A8D4-F648-84C3-730F1A42C846}">
-  <dimension ref="A1:Z36"/>
+  <dimension ref="A1:AC38"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="5.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.875" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="4.625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.875" style="1" bestFit="1" customWidth="1"/>
@@ -2125,7 +2156,7 @@
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
+      <c r="E5" s="28"/>
       <c r="F5" s="16"/>
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
@@ -2160,7 +2191,7 @@
       <c r="D6" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="16"/>
+      <c r="E6" s="28"/>
       <c r="F6" s="16">
         <v>583.54999999999995</v>
       </c>
@@ -2185,8 +2216,8 @@
       <c r="T6" s="16"/>
       <c r="U6" s="18"/>
       <c r="V6" s="16"/>
-      <c r="W6" s="19"/>
-      <c r="X6" s="19"/>
+      <c r="W6" s="23"/>
+      <c r="X6" s="23"/>
       <c r="Y6" s="18"/>
       <c r="Z6" s="16"/>
     </row>
@@ -2203,7 +2234,7 @@
       <c r="D7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="16"/>
+      <c r="E7" s="28"/>
       <c r="F7" s="16">
         <v>-94.05</v>
       </c>
@@ -2228,8 +2259,8 @@
       <c r="T7" s="16"/>
       <c r="U7" s="18"/>
       <c r="V7" s="16"/>
-      <c r="W7" s="19"/>
-      <c r="X7" s="19"/>
+      <c r="W7" s="23"/>
+      <c r="X7" s="23"/>
       <c r="Y7" s="18"/>
       <c r="Z7" s="16"/>
     </row>
@@ -2240,7 +2271,7 @@
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
       <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
+      <c r="E8" s="28"/>
       <c r="F8" s="16"/>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
@@ -2275,7 +2306,9 @@
       <c r="D9" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="16"/>
+      <c r="E9" s="31" t="s">
+        <v>120</v>
+      </c>
       <c r="F9" s="16">
         <v>-143.01</v>
       </c>
@@ -2322,7 +2355,7 @@
       <c r="D10" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="16"/>
+      <c r="E10" s="28"/>
       <c r="F10" s="16">
         <v>5.48</v>
       </c>
@@ -2357,51 +2390,51 @@
       <c r="Z10" s="16"/>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="16">
         <v>1.1499999999999999</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="16">
         <v>0.16</v>
       </c>
-      <c r="D11" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24">
+      <c r="D11" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="28"/>
+      <c r="F11" s="16">
         <v>0.93</v>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="16">
         <v>0.15</v>
       </c>
-      <c r="H11" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24">
+      <c r="H11" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16">
         <v>0.93</v>
       </c>
-      <c r="K11" s="24">
+      <c r="K11" s="16">
         <v>0.15</v>
       </c>
-      <c r="L11" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="M11" s="24"/>
-      <c r="O11" s="24"/>
-      <c r="P11" s="24"/>
-      <c r="Q11" s="25"/>
-      <c r="R11" s="24"/>
-      <c r="S11" s="24"/>
-      <c r="T11" s="24"/>
-      <c r="U11" s="25"/>
-      <c r="V11" s="24"/>
-      <c r="W11" s="24"/>
-      <c r="X11" s="24"/>
-      <c r="Y11" s="25"/>
-      <c r="Z11" s="24"/>
+      <c r="L11" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="M11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="16"/>
+      <c r="T11" s="16"/>
+      <c r="U11" s="18"/>
+      <c r="V11" s="16"/>
+      <c r="W11" s="16"/>
+      <c r="X11" s="16"/>
+      <c r="Y11" s="18"/>
+      <c r="Z11" s="16"/>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
@@ -2416,7 +2449,7 @@
       <c r="D12" s="18">
         <v>0.15</v>
       </c>
-      <c r="E12" s="16"/>
+      <c r="E12" s="28"/>
       <c r="F12" s="16">
         <v>-0.08</v>
       </c>
@@ -2463,7 +2496,7 @@
       <c r="D13" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="16"/>
+      <c r="E13" s="28"/>
       <c r="F13" s="16">
         <v>0.05</v>
       </c>
@@ -2504,7 +2537,7 @@
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
+      <c r="E14" s="28"/>
       <c r="F14" s="16"/>
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
@@ -2539,7 +2572,9 @@
       <c r="D15" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="18"/>
+      <c r="E15" s="29" t="s">
+        <v>119</v>
+      </c>
       <c r="F15" s="16">
         <v>3.21</v>
       </c>
@@ -2586,7 +2621,7 @@
       <c r="D16" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="28" t="s">
         <v>94</v>
       </c>
       <c r="F16" s="16">
@@ -2635,7 +2670,7 @@
       <c r="D17" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="28" t="s">
         <v>94</v>
       </c>
       <c r="F17" s="16">
@@ -2684,7 +2719,7 @@
       <c r="D18" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="28" t="s">
         <v>94</v>
       </c>
       <c r="F18" s="16">
@@ -2733,7 +2768,7 @@
       <c r="D19" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="28" t="s">
         <v>94</v>
       </c>
       <c r="F19" s="16">
@@ -2782,7 +2817,7 @@
       <c r="D20" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="28" t="s">
         <v>94</v>
       </c>
       <c r="F20" s="16" t="s">
@@ -2833,7 +2868,7 @@
       <c r="D21" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="E21" s="28" t="s">
         <v>94</v>
       </c>
       <c r="F21" s="16" t="s">
@@ -2884,7 +2919,7 @@
       <c r="D22" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="28" t="s">
         <v>94</v>
       </c>
       <c r="F22" s="16" t="s">
@@ -2935,7 +2970,7 @@
       <c r="D23" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E23" s="16" t="s">
+      <c r="E23" s="28" t="s">
         <v>94</v>
       </c>
       <c r="F23" s="16" t="s">
@@ -2986,7 +3021,7 @@
       <c r="D24" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="28" t="s">
         <v>94</v>
       </c>
       <c r="F24" s="16" t="s">
@@ -3031,7 +3066,7 @@
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
+      <c r="E25" s="28"/>
       <c r="F25" s="16"/>
       <c r="G25" s="16"/>
       <c r="H25" s="16"/>
@@ -3066,7 +3101,7 @@
       <c r="D26" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E26" s="16"/>
+      <c r="E26" s="28"/>
       <c r="F26" s="16">
         <v>12.23</v>
       </c>
@@ -3113,7 +3148,7 @@
       <c r="D27" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="16"/>
+      <c r="E27" s="28"/>
       <c r="F27" s="16">
         <v>0.59</v>
       </c>
@@ -3160,7 +3195,7 @@
       <c r="D28" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="28" t="s">
         <v>94</v>
       </c>
       <c r="F28" s="16">
@@ -3209,7 +3244,7 @@
       <c r="D29" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E29" s="16" t="s">
+      <c r="E29" s="28" t="s">
         <v>94</v>
       </c>
       <c r="F29" s="16" t="s">
@@ -3254,7 +3289,7 @@
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
+      <c r="E30" s="28"/>
       <c r="F30" s="16"/>
       <c r="G30" s="16"/>
       <c r="H30" s="16"/>
@@ -3289,7 +3324,7 @@
       <c r="D31" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E31" s="16"/>
+      <c r="E31" s="28"/>
       <c r="F31" s="16">
         <v>2200.12</v>
       </c>
@@ -3336,7 +3371,7 @@
       <c r="D32" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E32" s="16"/>
+      <c r="E32" s="28"/>
       <c r="F32" s="16">
         <v>93.66</v>
       </c>
@@ -3370,7 +3405,7 @@
       <c r="Y32" s="18"/>
       <c r="Z32" s="16"/>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
         <v>84</v>
       </c>
@@ -3383,7 +3418,7 @@
       <c r="D33" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E33" s="16"/>
+      <c r="E33" s="28"/>
       <c r="F33" s="16">
         <v>1.1599999999999999</v>
       </c>
@@ -3417,7 +3452,7 @@
       <c r="Y33" s="18"/>
       <c r="Z33" s="16"/>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
         <v>89</v>
       </c>
@@ -3430,7 +3465,7 @@
       <c r="D34" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E34" s="16"/>
+      <c r="E34" s="28"/>
       <c r="F34" s="16">
         <v>0.02</v>
       </c>
@@ -3464,7 +3499,7 @@
       <c r="Y34" s="18"/>
       <c r="Z34" s="16"/>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
         <v>93</v>
       </c>
@@ -3477,7 +3512,7 @@
       <c r="D35" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E35" s="16" t="s">
+      <c r="E35" s="28" t="s">
         <v>94</v>
       </c>
       <c r="F35" s="16">
@@ -3513,57 +3548,122 @@
       <c r="Y35" s="18"/>
       <c r="Z35" s="16"/>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
+    <row r="36" spans="1:29" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="B36" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="E36" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="F36" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="G36" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="H36" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="I36" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="J36" s="15">
+      <c r="B36" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D36" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="E36" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="F36" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="G36" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="H36" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="I36" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="J36" s="24">
         <v>7.64</v>
       </c>
-      <c r="K36" s="15">
+      <c r="K36" s="24">
         <v>0.3</v>
       </c>
-      <c r="L36" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="M36" s="6"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="15"/>
-      <c r="P36" s="15"/>
-      <c r="Q36" s="15"/>
-      <c r="R36" s="15"/>
-      <c r="S36" s="15"/>
-      <c r="T36" s="15"/>
-      <c r="U36" s="15"/>
-      <c r="V36" s="15"/>
-      <c r="W36" s="15"/>
-      <c r="X36" s="15"/>
-      <c r="Y36" s="20"/>
-      <c r="Z36" s="6"/>
+      <c r="L36" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="O36" s="24"/>
+      <c r="P36" s="24"/>
+      <c r="Q36" s="24"/>
+      <c r="R36" s="24"/>
+      <c r="S36" s="24"/>
+      <c r="T36" s="24"/>
+      <c r="U36" s="24"/>
+      <c r="V36" s="24"/>
+      <c r="W36" s="24"/>
+      <c r="X36" s="24"/>
+      <c r="Y36" s="25"/>
+    </row>
+    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A37" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="14"/>
+      <c r="O37" s="14"/>
+      <c r="P37" s="14"/>
+      <c r="Q37" s="14"/>
+      <c r="R37" s="14"/>
+      <c r="S37" s="14"/>
+      <c r="T37" s="14"/>
+      <c r="U37" s="14"/>
+      <c r="V37" s="14"/>
+      <c r="W37" s="14"/>
+      <c r="X37" s="14"/>
+      <c r="Y37" s="14"/>
+      <c r="Z37" s="14"/>
+      <c r="AA37" s="14"/>
+      <c r="AB37" s="16"/>
+      <c r="AC37" s="16"/>
+    </row>
+    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A38" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B38" s="15">
+        <v>74058</v>
+      </c>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="15"/>
+      <c r="N38" s="15"/>
+      <c r="O38" s="15"/>
+      <c r="P38" s="15"/>
+      <c r="Q38" s="15"/>
+      <c r="R38" s="15"/>
+      <c r="S38" s="15"/>
+      <c r="T38" s="15"/>
+      <c r="U38" s="15"/>
+      <c r="V38" s="15"/>
+      <c r="W38" s="15"/>
+      <c r="X38" s="15"/>
+      <c r="Y38" s="15"/>
+      <c r="Z38" s="15"/>
+      <c r="AA38" s="15"/>
+      <c r="AB38" s="16"/>
+      <c r="AC38" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nchaku\Documents\GitHub\pubertybrain\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmoffice-my.sharepoint.com/personal/abrieant_uvm_edu/Documents/OneDrive/Manuscripts/reg report DCN/pubertybrain/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C85D9B2-5526-4A3F-887C-73776185B9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{1C85D9B2-5526-4A3F-887C-73776185B9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2AA9C4B-FAB2-AB49-B4FB-20A7516B6A3B}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="90" windowWidth="28860" windowHeight="15135" activeTab="4" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
+    <workbookView xWindow="0" yWindow="2140" windowWidth="28800" windowHeight="15140" activeTab="5" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptive table" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Fig1 (Pub)" sheetId="3" r:id="rId3"/>
     <sheet name="Fig2 (Brain)" sheetId="4" r:id="rId4"/>
     <sheet name="CortModels" sheetId="6" r:id="rId5"/>
+    <sheet name="Indirect effects" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="136">
   <si>
     <t>16.10 (2.98)</t>
   </si>
@@ -672,12 +673,57 @@
   <si>
     <t>-174.94, -111.08</t>
   </si>
+  <si>
+    <t xml:space="preserve"> wm6 ind intercept ela_plus;</t>
+  </si>
+  <si>
+    <t>ELA --&gt; GMV intercept --&gt; working memory</t>
+  </si>
+  <si>
+    <t>EXPLORATORY</t>
+  </si>
+  <si>
+    <t>*pubertal timing not associated with working memory, thus did not test indirect effects</t>
+  </si>
+  <si>
+    <t>hypothesis not supported</t>
+  </si>
+  <si>
+    <t>HYPOTHESIS 4a: earlier pubertal timing will mediate associations between adversity and working memory (path a1*b1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYPOTHESIS 4B: more advanced brain maturation will mediate associations between adversity and working memory (path a2*b2) </t>
+  </si>
+  <si>
+    <t>FEMALE- cortical</t>
+  </si>
+  <si>
+    <t>MALE - cortical</t>
+  </si>
+  <si>
+    <t>FEMALE - subcortical</t>
+  </si>
+  <si>
+    <t>Lower 2.5%</t>
+  </si>
+  <si>
+    <t>Upper 2.5%</t>
+  </si>
+  <si>
+    <t>wm6 ind pfPDStempo ela_plus;</t>
+  </si>
+  <si>
+    <t>*All estimates STDYX</t>
+  </si>
+  <si>
+    <t>MALE - subcortical</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -759,6 +805,19 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -804,7 +863,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -836,25 +895,20 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="11" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="11" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="11" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1435,20 +1489,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39987BE7-3659-524A-81AE-D479F97EF698}">
   <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="20.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="9"/>
       <c r="B2" s="10" t="s">
         <v>63</v>
@@ -1466,7 +1520,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="6"/>
       <c r="B3" s="11" t="s">
         <v>69</v>
@@ -1480,7 +1534,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>60</v>
       </c>
@@ -1490,7 +1544,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>61</v>
       </c>
@@ -1510,7 +1564,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>62</v>
       </c>
@@ -1530,7 +1584,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>58</v>
       </c>
@@ -1550,7 +1604,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>59</v>
       </c>
@@ -1560,7 +1614,7 @@
       <c r="E8" s="12"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>61</v>
       </c>
@@ -1580,7 +1634,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>66</v>
       </c>
@@ -1600,7 +1654,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>67</v>
       </c>
@@ -1620,7 +1674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>62</v>
       </c>
@@ -1640,7 +1694,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>68</v>
       </c>
@@ -1650,7 +1704,7 @@
       <c r="E13" s="12"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>73</v>
       </c>
@@ -1670,7 +1724,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>74</v>
       </c>
@@ -1690,7 +1744,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>75</v>
       </c>
@@ -1710,7 +1764,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>76</v>
       </c>
@@ -1728,7 +1782,7 @@
       </c>
       <c r="F17" s="20"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>71</v>
       </c>
@@ -1738,7 +1792,7 @@
       <c r="E18" s="12"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>61</v>
       </c>
@@ -1758,7 +1812,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>66</v>
       </c>
@@ -1778,7 +1832,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>67</v>
       </c>
@@ -1798,7 +1852,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>62</v>
       </c>
@@ -1818,7 +1872,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>72</v>
       </c>
@@ -1828,7 +1882,7 @@
       <c r="E23" s="12"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>61</v>
       </c>
@@ -1848,7 +1902,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>66</v>
       </c>
@@ -1868,7 +1922,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>67</v>
       </c>
@@ -1888,7 +1942,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>62</v>
       </c>
@@ -1908,7 +1962,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1916,7 +1970,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1932,9 +1986,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A749072B-F938-0F49-BE23-243603B2B3D0}">
   <dimension ref="M2"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M2" t="s">
         <v>113</v>
       </c>
@@ -1948,7 +2002,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45875D41-9C56-AA4E-A18A-2D3A4CE169B3}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1958,7 +2012,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A5153E-6E5C-054A-8ACA-5118463B96C5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -1968,113 +2022,113 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA86F85-A8D4-F648-84C3-730F1A42C846}">
   <dimension ref="A1:AC38"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="2.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="2.83203125" style="1" customWidth="1"/>
     <col min="15" max="15" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="O2" s="22" t="s">
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="O2" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="22"/>
-      <c r="W2" s="22"/>
-      <c r="X2" s="22"/>
-      <c r="Y2" s="22"/>
-      <c r="Z2" s="22"/>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="26"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="26"/>
+      <c r="Z2" s="26"/>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" s="15"/>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21" t="s">
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21" t="s">
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="K3" s="21"/>
-      <c r="L3" s="21"/>
-      <c r="M3" s="21"/>
-      <c r="O3" s="21" t="s">
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="O3" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="P3" s="21"/>
-      <c r="Q3" s="21"/>
-      <c r="R3" s="21"/>
-      <c r="S3" s="21" t="s">
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="T3" s="21"/>
-      <c r="U3" s="21"/>
-      <c r="V3" s="21"/>
-      <c r="W3" s="21" t="s">
+      <c r="T3" s="25"/>
+      <c r="U3" s="25"/>
+      <c r="V3" s="25"/>
+      <c r="W3" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="X3" s="21"/>
-      <c r="Y3" s="21"/>
-      <c r="Z3" s="21"/>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="X3" s="25"/>
+      <c r="Y3" s="25"/>
+      <c r="Z3" s="25"/>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="16"/>
       <c r="B4" s="17" t="s">
         <v>90</v>
@@ -2149,14 +2203,14 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
         <v>85</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
-      <c r="E5" s="28"/>
+      <c r="E5" s="22"/>
       <c r="F5" s="16"/>
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
@@ -2178,7 +2232,7 @@
       <c r="Y5" s="16"/>
       <c r="Z5" s="16"/>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>96</v>
       </c>
@@ -2191,7 +2245,7 @@
       <c r="D6" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="28"/>
+      <c r="E6" s="22"/>
       <c r="F6" s="16">
         <v>583.54999999999995</v>
       </c>
@@ -2216,12 +2270,12 @@
       <c r="T6" s="16"/>
       <c r="U6" s="18"/>
       <c r="V6" s="16"/>
-      <c r="W6" s="23"/>
-      <c r="X6" s="23"/>
+      <c r="W6" s="16"/>
+      <c r="X6" s="16"/>
       <c r="Y6" s="18"/>
       <c r="Z6" s="16"/>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>97</v>
       </c>
@@ -2234,7 +2288,7 @@
       <c r="D7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="28"/>
+      <c r="E7" s="22"/>
       <c r="F7" s="16">
         <v>-94.05</v>
       </c>
@@ -2259,19 +2313,19 @@
       <c r="T7" s="16"/>
       <c r="U7" s="18"/>
       <c r="V7" s="16"/>
-      <c r="W7" s="23"/>
-      <c r="X7" s="23"/>
+      <c r="W7" s="16"/>
+      <c r="X7" s="16"/>
       <c r="Y7" s="18"/>
       <c r="Z7" s="16"/>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
         <v>86</v>
       </c>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
       <c r="D8" s="16"/>
-      <c r="E8" s="28"/>
+      <c r="E8" s="22"/>
       <c r="F8" s="16"/>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
@@ -2293,7 +2347,7 @@
       <c r="Y8" s="16"/>
       <c r="Z8" s="16"/>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>98</v>
       </c>
@@ -2306,7 +2360,7 @@
       <c r="D9" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="E9" s="24" t="s">
         <v>120</v>
       </c>
       <c r="F9" s="16">
@@ -2342,7 +2396,7 @@
       <c r="Y9" s="18"/>
       <c r="Z9" s="16"/>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>99</v>
       </c>
@@ -2355,7 +2409,7 @@
       <c r="D10" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="28"/>
+      <c r="E10" s="22"/>
       <c r="F10" s="16">
         <v>5.48</v>
       </c>
@@ -2389,7 +2443,7 @@
       <c r="Y10" s="18"/>
       <c r="Z10" s="16"/>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>100</v>
       </c>
@@ -2402,7 +2456,7 @@
       <c r="D11" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="28"/>
+      <c r="E11" s="22"/>
       <c r="F11" s="16">
         <v>0.93</v>
       </c>
@@ -2436,7 +2490,7 @@
       <c r="Y11" s="18"/>
       <c r="Z11" s="16"/>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>101</v>
       </c>
@@ -2449,7 +2503,7 @@
       <c r="D12" s="18">
         <v>0.15</v>
       </c>
-      <c r="E12" s="28"/>
+      <c r="E12" s="22"/>
       <c r="F12" s="16">
         <v>-0.08</v>
       </c>
@@ -2483,7 +2537,7 @@
       <c r="Y12" s="18"/>
       <c r="Z12" s="16"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A13" s="16" t="s">
         <v>88</v>
       </c>
@@ -2496,7 +2550,7 @@
       <c r="D13" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="28"/>
+      <c r="E13" s="22"/>
       <c r="F13" s="16">
         <v>0.05</v>
       </c>
@@ -2530,14 +2584,14 @@
       <c r="Y13" s="18"/>
       <c r="Z13" s="16"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
         <v>87</v>
       </c>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
-      <c r="E14" s="28"/>
+      <c r="E14" s="22"/>
       <c r="F14" s="16"/>
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
@@ -2559,7 +2613,7 @@
       <c r="Y14" s="16"/>
       <c r="Z14" s="16"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>102</v>
       </c>
@@ -2572,7 +2626,7 @@
       <c r="D15" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="29" t="s">
+      <c r="E15" s="23" t="s">
         <v>119</v>
       </c>
       <c r="F15" s="16">
@@ -2608,7 +2662,7 @@
       <c r="Y15" s="18"/>
       <c r="Z15" s="16"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>103</v>
       </c>
@@ -2621,7 +2675,7 @@
       <c r="D16" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="28" t="s">
+      <c r="E16" s="22" t="s">
         <v>94</v>
       </c>
       <c r="F16" s="16">
@@ -2657,7 +2711,7 @@
       <c r="Y16" s="18"/>
       <c r="Z16" s="16"/>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>104</v>
       </c>
@@ -2670,7 +2724,7 @@
       <c r="D17" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E17" s="28" t="s">
+      <c r="E17" s="22" t="s">
         <v>94</v>
       </c>
       <c r="F17" s="16">
@@ -2706,7 +2760,7 @@
       <c r="Y17" s="18"/>
       <c r="Z17" s="16"/>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
         <v>107</v>
       </c>
@@ -2719,7 +2773,7 @@
       <c r="D18" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E18" s="28" t="s">
+      <c r="E18" s="22" t="s">
         <v>94</v>
       </c>
       <c r="F18" s="16">
@@ -2755,7 +2809,7 @@
       <c r="Y18" s="18"/>
       <c r="Z18" s="16"/>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
         <v>108</v>
       </c>
@@ -2768,7 +2822,7 @@
       <c r="D19" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E19" s="28" t="s">
+      <c r="E19" s="22" t="s">
         <v>94</v>
       </c>
       <c r="F19" s="16">
@@ -2804,7 +2858,7 @@
       <c r="Y19" s="18"/>
       <c r="Z19" s="16"/>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>105</v>
       </c>
@@ -2817,7 +2871,7 @@
       <c r="D20" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E20" s="28" t="s">
+      <c r="E20" s="22" t="s">
         <v>94</v>
       </c>
       <c r="F20" s="16" t="s">
@@ -2855,7 +2909,7 @@
       <c r="Y20" s="18"/>
       <c r="Z20" s="16"/>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>106</v>
       </c>
@@ -2868,7 +2922,7 @@
       <c r="D21" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E21" s="28" t="s">
+      <c r="E21" s="22" t="s">
         <v>94</v>
       </c>
       <c r="F21" s="16" t="s">
@@ -2906,7 +2960,7 @@
       <c r="Y21" s="18"/>
       <c r="Z21" s="16"/>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
         <v>110</v>
       </c>
@@ -2919,7 +2973,7 @@
       <c r="D22" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E22" s="28" t="s">
+      <c r="E22" s="22" t="s">
         <v>94</v>
       </c>
       <c r="F22" s="16" t="s">
@@ -2957,7 +3011,7 @@
       <c r="Y22" s="18"/>
       <c r="Z22" s="16"/>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A23" s="16" t="s">
         <v>109</v>
       </c>
@@ -2970,7 +3024,7 @@
       <c r="D23" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E23" s="28" t="s">
+      <c r="E23" s="22" t="s">
         <v>94</v>
       </c>
       <c r="F23" s="16" t="s">
@@ -3008,7 +3062,7 @@
       <c r="Y23" s="18"/>
       <c r="Z23" s="16"/>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
         <v>111</v>
       </c>
@@ -3021,7 +3075,7 @@
       <c r="D24" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E24" s="28" t="s">
+      <c r="E24" s="22" t="s">
         <v>94</v>
       </c>
       <c r="F24" s="16" t="s">
@@ -3059,14 +3113,14 @@
       <c r="Y24" s="18"/>
       <c r="Z24" s="16"/>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A25" s="17" t="s">
         <v>82</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
-      <c r="E25" s="28"/>
+      <c r="E25" s="22"/>
       <c r="F25" s="16"/>
       <c r="G25" s="16"/>
       <c r="H25" s="16"/>
@@ -3088,7 +3142,7 @@
       <c r="Y25" s="16"/>
       <c r="Z25" s="16"/>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
         <v>84</v>
       </c>
@@ -3101,7 +3155,7 @@
       <c r="D26" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E26" s="28"/>
+      <c r="E26" s="22"/>
       <c r="F26" s="16">
         <v>12.23</v>
       </c>
@@ -3135,7 +3189,7 @@
       <c r="Y26" s="18"/>
       <c r="Z26" s="16"/>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
         <v>89</v>
       </c>
@@ -3148,7 +3202,7 @@
       <c r="D27" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="28"/>
+      <c r="E27" s="22"/>
       <c r="F27" s="16">
         <v>0.59</v>
       </c>
@@ -3182,7 +3236,7 @@
       <c r="Y27" s="18"/>
       <c r="Z27" s="16"/>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A28" s="16" t="s">
         <v>93</v>
       </c>
@@ -3195,7 +3249,7 @@
       <c r="D28" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E28" s="28" t="s">
+      <c r="E28" s="22" t="s">
         <v>94</v>
       </c>
       <c r="F28" s="16">
@@ -3231,7 +3285,7 @@
       <c r="Y28" s="18"/>
       <c r="Z28" s="16"/>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A29" s="16" t="s">
         <v>112</v>
       </c>
@@ -3244,7 +3298,7 @@
       <c r="D29" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E29" s="28" t="s">
+      <c r="E29" s="22" t="s">
         <v>94</v>
       </c>
       <c r="F29" s="16" t="s">
@@ -3282,14 +3336,14 @@
       <c r="Y29" s="18"/>
       <c r="Z29" s="16"/>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A30" s="17" t="s">
         <v>83</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
-      <c r="E30" s="28"/>
+      <c r="E30" s="22"/>
       <c r="F30" s="16"/>
       <c r="G30" s="16"/>
       <c r="H30" s="16"/>
@@ -3311,7 +3365,7 @@
       <c r="Y30" s="16"/>
       <c r="Z30" s="16"/>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>96</v>
       </c>
@@ -3324,7 +3378,7 @@
       <c r="D31" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E31" s="28"/>
+      <c r="E31" s="22"/>
       <c r="F31" s="16">
         <v>2200.12</v>
       </c>
@@ -3358,7 +3412,7 @@
       <c r="Y31" s="18"/>
       <c r="Z31" s="16"/>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
         <v>97</v>
       </c>
@@ -3371,7 +3425,7 @@
       <c r="D32" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E32" s="28"/>
+      <c r="E32" s="22"/>
       <c r="F32" s="16">
         <v>93.66</v>
       </c>
@@ -3405,7 +3459,7 @@
       <c r="Y32" s="18"/>
       <c r="Z32" s="16"/>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A33" s="16" t="s">
         <v>84</v>
       </c>
@@ -3418,7 +3472,7 @@
       <c r="D33" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E33" s="28"/>
+      <c r="E33" s="22"/>
       <c r="F33" s="16">
         <v>1.1599999999999999</v>
       </c>
@@ -3452,7 +3506,7 @@
       <c r="Y33" s="18"/>
       <c r="Z33" s="16"/>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A34" s="16" t="s">
         <v>89</v>
       </c>
@@ -3465,7 +3519,7 @@
       <c r="D34" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E34" s="28"/>
+      <c r="E34" s="22"/>
       <c r="F34" s="16">
         <v>0.02</v>
       </c>
@@ -3499,7 +3553,7 @@
       <c r="Y34" s="18"/>
       <c r="Z34" s="16"/>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A35" s="16" t="s">
         <v>93</v>
       </c>
@@ -3512,7 +3566,7 @@
       <c r="D35" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E35" s="28" t="s">
+      <c r="E35" s="22" t="s">
         <v>94</v>
       </c>
       <c r="F35" s="16">
@@ -3548,57 +3602,57 @@
       <c r="Y35" s="18"/>
       <c r="Z35" s="16"/>
     </row>
-    <row r="36" spans="1:29" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="24" t="s">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A36" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="B36" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D36" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="E36" s="30" t="s">
-        <v>94</v>
-      </c>
-      <c r="F36" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="G36" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="H36" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="I36" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="J36" s="24">
+      <c r="B36" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I36" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J36" s="16">
         <v>7.64</v>
       </c>
-      <c r="K36" s="24">
+      <c r="K36" s="16">
         <v>0.3</v>
       </c>
-      <c r="L36" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="O36" s="24"/>
-      <c r="P36" s="24"/>
-      <c r="Q36" s="24"/>
-      <c r="R36" s="24"/>
-      <c r="S36" s="24"/>
-      <c r="T36" s="24"/>
-      <c r="U36" s="24"/>
-      <c r="V36" s="24"/>
-      <c r="W36" s="24"/>
-      <c r="X36" s="24"/>
-      <c r="Y36" s="25"/>
-    </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A37" s="27" t="s">
+      <c r="L36" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="O36" s="16"/>
+      <c r="P36" s="16"/>
+      <c r="Q36" s="16"/>
+      <c r="R36" s="16"/>
+      <c r="S36" s="16"/>
+      <c r="T36" s="16"/>
+      <c r="U36" s="16"/>
+      <c r="V36" s="16"/>
+      <c r="W36" s="16"/>
+      <c r="X36" s="16"/>
+      <c r="Y36" s="18"/>
+    </row>
+    <row r="37" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A37" s="21" t="s">
         <v>117</v>
       </c>
       <c r="B37" s="14"/>
@@ -3630,7 +3684,7 @@
       <c r="AB37" s="16"/>
       <c r="AC37" s="16"/>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A38" s="15" t="s">
         <v>118</v>
       </c>
@@ -3678,4 +3732,166 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{540507A6-720C-0B43-804E-087FEE710926}">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="27" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="28"/>
+    </row>
+    <row r="3" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="28" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="28" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="28"/>
+    </row>
+    <row r="6" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="28"/>
+    </row>
+    <row r="7" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="27" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="28" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="28" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B11" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B12">
+        <v>-3.4000000000000002E-2</v>
+      </c>
+      <c r="C12">
+        <v>-1.4E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>129</v>
+      </c>
+      <c r="B13">
+        <v>-2.4E-2</v>
+      </c>
+      <c r="C13">
+        <v>-8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>130</v>
+      </c>
+      <c r="B14">
+        <v>-2.3E-2</v>
+      </c>
+      <c r="C14">
+        <v>-7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="27" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="28" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B19" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>128</v>
+      </c>
+      <c r="B20">
+        <v>-3.1E-2</v>
+      </c>
+      <c r="C20">
+        <v>-1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>129</v>
+      </c>
+      <c r="B21">
+        <v>-0.03</v>
+      </c>
+      <c r="C21">
+        <v>-1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22">
+        <v>-0.113</v>
+      </c>
+      <c r="C22">
+        <v>9.7000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E25" s="27" t="s">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmoffice-my.sharepoint.com/personal/abrieant_uvm_edu/Documents/OneDrive/Manuscripts/reg report DCN/pubertybrain/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nchaku/Documents/GitHub/pubertybrain/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{1C85D9B2-5526-4A3F-887C-73776185B9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2AA9C4B-FAB2-AB49-B4FB-20A7516B6A3B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B817228C-EF8E-0F4D-9C4C-0E5F3A6B8D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2140" windowWidth="28800" windowHeight="15140" activeTab="5" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
+    <workbookView xWindow="10140" yWindow="500" windowWidth="32680" windowHeight="16500" activeTab="4" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptive table" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="179">
   <si>
     <t>16.10 (2.98)</t>
   </si>
@@ -650,24 +650,6 @@
     <t>Table 2. Cortical volume by sex</t>
   </si>
   <si>
-    <t>Fit statistics</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">   sa</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>BIC</t>
-    </r>
-  </si>
-  <si>
     <t>2.58, 3.81</t>
   </si>
   <si>
@@ -717,6 +699,141 @@
   </si>
   <si>
     <t>MALE - subcortical</t>
+  </si>
+  <si>
+    <t>5.08, 8.99</t>
+  </si>
+  <si>
+    <t>.89, 1.41</t>
+  </si>
+  <si>
+    <t>-.17, .01</t>
+  </si>
+  <si>
+    <t>574.81, 578.34</t>
+  </si>
+  <si>
+    <t>-101.37, -86.53</t>
+  </si>
+  <si>
+    <t>.02, .02</t>
+  </si>
+  <si>
+    <t>2122.33, 2372.47</t>
+  </si>
+  <si>
+    <t>70.45, 116.79</t>
+  </si>
+  <si>
+    <t>1.14, 1.26</t>
+  </si>
+  <si>
+    <t>.02., .02</t>
+  </si>
+  <si>
+    <t>11.98, 12.06</t>
+  </si>
+  <si>
+    <t>.55, .56</t>
+  </si>
+  <si>
+    <t>581.07, 586.03</t>
+  </si>
+  <si>
+    <t>-101.65, -86.46</t>
+  </si>
+  <si>
+    <t>-174.70, -111.33</t>
+  </si>
+  <si>
+    <t>3.74, 7.22</t>
+  </si>
+  <si>
+    <t>.68, 1.17</t>
+  </si>
+  <si>
+    <t>.04, .05</t>
+  </si>
+  <si>
+    <t>2.58, 3.83</t>
+  </si>
+  <si>
+    <t>-.35, .38</t>
+  </si>
+  <si>
+    <t>-4.75, -2.86</t>
+  </si>
+  <si>
+    <t>-.13, -.09</t>
+  </si>
+  <si>
+    <t>-.02, -.02</t>
+  </si>
+  <si>
+    <t>12.17, 12.28</t>
+  </si>
+  <si>
+    <t>.58, .59</t>
+  </si>
+  <si>
+    <t>1.76, 1.90</t>
+  </si>
+  <si>
+    <t>2077.37, 2322.86</t>
+  </si>
+  <si>
+    <t>70.50, 116.82</t>
+  </si>
+  <si>
+    <t>1.10, 1.22</t>
+  </si>
+  <si>
+    <t>3.05, 3.48</t>
+  </si>
+  <si>
+    <t>581.10, 586.06</t>
+  </si>
+  <si>
+    <t>-101.64, -86.44</t>
+  </si>
+  <si>
+    <t>-174, 70, -111.34</t>
+  </si>
+  <si>
+    <t>3.74, 7.21</t>
+  </si>
+  <si>
+    <t>.68, 1.71</t>
+  </si>
+  <si>
+    <t>-4.76, -2.88</t>
+  </si>
+  <si>
+    <t>.01, .01</t>
+  </si>
+  <si>
+    <t>-.02, .02</t>
+  </si>
+  <si>
+    <t>-.01, .22</t>
+  </si>
+  <si>
+    <t>1.52, 2.53</t>
+  </si>
+  <si>
+    <t>-.23, -.11</t>
+  </si>
+  <si>
+    <t>8.98, 12.96</t>
+  </si>
+  <si>
+    <t>2077.10, 2322.46</t>
+  </si>
+  <si>
+    <t>70.55, 116.86</t>
+  </si>
+  <si>
+    <t>7.15, 8.14</t>
   </si>
 </sst>
 </file>
@@ -863,7 +980,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -893,22 +1010,30 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="11" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1780,7 +1905,7 @@
       <c r="E17" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="20"/>
+      <c r="F17" s="19"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
@@ -2021,22 +2146,21 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA86F85-A8D4-F648-84C3-730F1A42C846}">
-  <dimension ref="A1:AC38"/>
+  <dimension ref="A1:Z36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.83203125" style="25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.6640625" style="25" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="2.83203125" style="1" customWidth="1"/>
     <col min="15" max="15" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
@@ -2060,73 +2184,73 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="O2" s="26" t="s">
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="O2" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="26"/>
-      <c r="Y2" s="26"/>
-      <c r="Z2" s="26"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="24"/>
+      <c r="U2" s="24"/>
+      <c r="V2" s="24"/>
+      <c r="W2" s="24"/>
+      <c r="X2" s="24"/>
+      <c r="Y2" s="24"/>
+      <c r="Z2" s="24"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3" s="15"/>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25" t="s">
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25" t="s">
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="O3" s="25" t="s">
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="O3" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25" t="s">
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25" t="s">
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="23"/>
+      <c r="W3" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="X3" s="25"/>
-      <c r="Y3" s="25"/>
-      <c r="Z3" s="25"/>
+      <c r="X3" s="23"/>
+      <c r="Y3" s="23"/>
+      <c r="Z3" s="23"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4" s="16"/>
@@ -2139,7 +2263,7 @@
       <c r="D4" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="26" t="s">
         <v>95</v>
       </c>
       <c r="F4" s="17" t="s">
@@ -2151,7 +2275,7 @@
       <c r="H4" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="I4" s="26" t="s">
         <v>95</v>
       </c>
       <c r="J4" s="17" t="s">
@@ -2163,43 +2287,43 @@
       <c r="L4" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="M4" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="O4" s="17" t="s">
+      <c r="O4" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="P4" s="17" t="s">
+      <c r="P4" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="Q4" s="17" t="s">
+      <c r="Q4" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="R4" s="17" t="s">
+      <c r="R4" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="S4" s="17" t="s">
+      <c r="S4" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="T4" s="17" t="s">
+      <c r="T4" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="U4" s="17" t="s">
+      <c r="U4" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="V4" s="17" t="s">
+      <c r="V4" s="26" t="s">
         <v>95</v>
       </c>
-      <c r="W4" s="17" t="s">
+      <c r="W4" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="X4" s="17" t="s">
+      <c r="X4" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="Y4" s="17" t="s">
+      <c r="Y4" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="Z4" s="17" t="s">
+      <c r="Z4" s="26" t="s">
         <v>95</v>
       </c>
     </row>
@@ -2210,34 +2334,34 @@
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
-      <c r="E5" s="22"/>
+      <c r="E5" s="20"/>
       <c r="F5" s="16"/>
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
+      <c r="I5" s="20"/>
       <c r="J5" s="16"/>
       <c r="K5" s="16"/>
       <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
-      <c r="S5" s="16"/>
-      <c r="T5" s="16"/>
-      <c r="U5" s="16"/>
-      <c r="V5" s="16"/>
-      <c r="W5" s="16"/>
-      <c r="X5" s="16"/>
-      <c r="Y5" s="16"/>
-      <c r="Z5" s="16"/>
+      <c r="M5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="20"/>
+      <c r="Y5" s="20"/>
+      <c r="Z5" s="20"/>
     </row>
     <row r="6" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>96</v>
       </c>
       <c r="B6" s="16">
-        <v>576.59</v>
+        <v>576.58000000000004</v>
       </c>
       <c r="C6" s="16">
         <v>1.07</v>
@@ -2245,7 +2369,9 @@
       <c r="D6" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="20" t="s">
+        <v>137</v>
+      </c>
       <c r="F6" s="16">
         <v>583.54999999999995</v>
       </c>
@@ -2255,25 +2381,33 @@
       <c r="H6" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="16"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
+      <c r="I6" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="J6" s="29">
+        <v>583.58000000000004</v>
+      </c>
+      <c r="K6" s="29">
+        <v>1.51</v>
+      </c>
       <c r="L6" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="16"/>
-      <c r="U6" s="18"/>
-      <c r="V6" s="16"/>
-      <c r="W6" s="16"/>
-      <c r="X6" s="16"/>
-      <c r="Y6" s="18"/>
-      <c r="Z6" s="16"/>
+      <c r="M6" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="20"/>
+      <c r="U6" s="27"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="20"/>
+      <c r="X6" s="20"/>
+      <c r="Y6" s="27"/>
+      <c r="Z6" s="20"/>
     </row>
     <row r="7" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
@@ -2288,7 +2422,9 @@
       <c r="D7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="22"/>
+      <c r="E7" s="20" t="s">
+        <v>138</v>
+      </c>
       <c r="F7" s="16">
         <v>-94.05</v>
       </c>
@@ -2298,25 +2434,33 @@
       <c r="H7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="16"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
+      <c r="I7" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="J7" s="29">
+        <v>-94.04</v>
+      </c>
+      <c r="K7" s="29">
+        <v>4.62</v>
+      </c>
       <c r="L7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M7" s="16"/>
-      <c r="O7" s="16"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="18"/>
-      <c r="R7" s="16"/>
-      <c r="S7" s="16"/>
-      <c r="T7" s="16"/>
-      <c r="U7" s="18"/>
-      <c r="V7" s="16"/>
-      <c r="W7" s="16"/>
-      <c r="X7" s="16"/>
-      <c r="Y7" s="18"/>
-      <c r="Z7" s="16"/>
+      <c r="M7" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="27"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="27"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20"/>
+      <c r="X7" s="20"/>
+      <c r="Y7" s="27"/>
+      <c r="Z7" s="20"/>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
@@ -2325,27 +2469,27 @@
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
       <c r="D8" s="16"/>
-      <c r="E8" s="22"/>
+      <c r="E8" s="20"/>
       <c r="F8" s="16"/>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
+      <c r="I8" s="20"/>
       <c r="J8" s="16"/>
       <c r="K8" s="16"/>
       <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="16"/>
-      <c r="S8" s="16"/>
-      <c r="T8" s="16"/>
-      <c r="U8" s="16"/>
-      <c r="V8" s="16"/>
-      <c r="W8" s="16"/>
-      <c r="X8" s="16"/>
-      <c r="Y8" s="16"/>
-      <c r="Z8" s="16"/>
+      <c r="M8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="20"/>
+      <c r="T8" s="20"/>
+      <c r="U8" s="20"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="20"/>
+      <c r="X8" s="20"/>
+      <c r="Y8" s="20"/>
+      <c r="Z8" s="20"/>
     </row>
     <row r="9" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
@@ -2360,8 +2504,8 @@
       <c r="D9" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="24" t="s">
-        <v>120</v>
+      <c r="E9" s="20" t="s">
+        <v>118</v>
       </c>
       <c r="F9" s="16">
         <v>-143.01</v>
@@ -2372,7 +2516,9 @@
       <c r="H9" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="16"/>
+      <c r="I9" s="20" t="s">
+        <v>148</v>
+      </c>
       <c r="J9" s="16">
         <v>-143.02000000000001</v>
       </c>
@@ -2382,19 +2528,21 @@
       <c r="L9" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="16"/>
-      <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="18"/>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="18"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="16"/>
-      <c r="Y9" s="18"/>
-      <c r="Z9" s="16"/>
+      <c r="M9" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="27"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="20"/>
+      <c r="U9" s="27"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="27"/>
+      <c r="Z9" s="20"/>
     </row>
     <row r="10" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
@@ -2409,7 +2557,9 @@
       <c r="D10" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="22"/>
+      <c r="E10" s="20" t="s">
+        <v>134</v>
+      </c>
       <c r="F10" s="16">
         <v>5.48</v>
       </c>
@@ -2419,7 +2569,9 @@
       <c r="H10" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I10" s="16"/>
+      <c r="I10" s="20" t="s">
+        <v>149</v>
+      </c>
       <c r="J10" s="16">
         <v>5.48</v>
       </c>
@@ -2429,19 +2581,21 @@
       <c r="L10" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M10" s="16"/>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="18"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="18"/>
-      <c r="V10" s="16"/>
-      <c r="W10" s="16"/>
-      <c r="X10" s="16"/>
-      <c r="Y10" s="18"/>
-      <c r="Z10" s="16"/>
+      <c r="M10" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="27"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="20"/>
+      <c r="U10" s="27"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="27"/>
+      <c r="Z10" s="20"/>
     </row>
     <row r="11" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
@@ -2456,7 +2610,9 @@
       <c r="D11" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="22"/>
+      <c r="E11" s="20" t="s">
+        <v>135</v>
+      </c>
       <c r="F11" s="16">
         <v>0.93</v>
       </c>
@@ -2466,7 +2622,9 @@
       <c r="H11" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I11" s="16"/>
+      <c r="I11" s="20" t="s">
+        <v>150</v>
+      </c>
       <c r="J11" s="16">
         <v>0.93</v>
       </c>
@@ -2476,19 +2634,21 @@
       <c r="L11" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M11" s="16"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="18"/>
-      <c r="R11" s="16"/>
-      <c r="S11" s="16"/>
-      <c r="T11" s="16"/>
-      <c r="U11" s="18"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="16"/>
-      <c r="X11" s="16"/>
-      <c r="Y11" s="18"/>
-      <c r="Z11" s="16"/>
+      <c r="M11" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="27"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="27"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="20"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="27"/>
+      <c r="Z11" s="20"/>
     </row>
     <row r="12" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
@@ -2503,7 +2663,9 @@
       <c r="D12" s="18">
         <v>0.15</v>
       </c>
-      <c r="E12" s="22"/>
+      <c r="E12" s="27" t="s">
+        <v>117</v>
+      </c>
       <c r="F12" s="16">
         <v>-0.08</v>
       </c>
@@ -2513,7 +2675,9 @@
       <c r="H12" s="18">
         <v>0.15</v>
       </c>
-      <c r="I12" s="16"/>
+      <c r="I12" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="J12" s="16">
         <v>-0.08</v>
       </c>
@@ -2523,19 +2687,21 @@
       <c r="L12" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="18"/>
-      <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
-      <c r="T12" s="16"/>
-      <c r="U12" s="18"/>
-      <c r="V12" s="16"/>
-      <c r="W12" s="16"/>
-      <c r="X12" s="16"/>
-      <c r="Y12" s="18"/>
-      <c r="Z12" s="16"/>
+      <c r="M12" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="27"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="20"/>
+      <c r="U12" s="27"/>
+      <c r="V12" s="20"/>
+      <c r="W12" s="20"/>
+      <c r="X12" s="20"/>
+      <c r="Y12" s="27"/>
+      <c r="Z12" s="20"/>
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A13" s="16" t="s">
@@ -2550,7 +2716,9 @@
       <c r="D13" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="22"/>
+      <c r="E13" s="20" t="s">
+        <v>136</v>
+      </c>
       <c r="F13" s="16">
         <v>0.05</v>
       </c>
@@ -2560,7 +2728,9 @@
       <c r="H13" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I13" s="16"/>
+      <c r="I13" s="20" t="s">
+        <v>151</v>
+      </c>
       <c r="J13" s="16">
         <v>0.05</v>
       </c>
@@ -2570,19 +2740,21 @@
       <c r="L13" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M13" s="16"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="18"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="16"/>
-      <c r="T13" s="16"/>
-      <c r="U13" s="18"/>
-      <c r="V13" s="16"/>
-      <c r="W13" s="16"/>
-      <c r="X13" s="16"/>
-      <c r="Y13" s="18"/>
-      <c r="Z13" s="16"/>
+      <c r="M13" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="27"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="27"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="20"/>
+      <c r="X13" s="20"/>
+      <c r="Y13" s="27"/>
+      <c r="Z13" s="20"/>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
@@ -2591,27 +2763,27 @@
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
-      <c r="E14" s="22"/>
+      <c r="E14" s="20"/>
       <c r="F14" s="16"/>
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
+      <c r="I14" s="20"/>
       <c r="J14" s="16"/>
       <c r="K14" s="16"/>
       <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="16"/>
-      <c r="U14" s="16"/>
-      <c r="V14" s="16"/>
-      <c r="W14" s="16"/>
-      <c r="X14" s="16"/>
-      <c r="Y14" s="16"/>
-      <c r="Z14" s="16"/>
+      <c r="M14" s="20"/>
+      <c r="O14" s="20"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="20"/>
+      <c r="T14" s="20"/>
+      <c r="U14" s="20"/>
+      <c r="V14" s="20"/>
+      <c r="W14" s="20"/>
+      <c r="X14" s="20"/>
+      <c r="Y14" s="20"/>
+      <c r="Z14" s="20"/>
     </row>
     <row r="15" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
@@ -2626,8 +2798,8 @@
       <c r="D15" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="23" t="s">
-        <v>119</v>
+      <c r="E15" s="20" t="s">
+        <v>117</v>
       </c>
       <c r="F15" s="16">
         <v>3.21</v>
@@ -2638,7 +2810,9 @@
       <c r="H15" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I15" s="16"/>
+      <c r="I15" s="20" t="s">
+        <v>152</v>
+      </c>
       <c r="J15" s="16">
         <v>3.2</v>
       </c>
@@ -2648,19 +2822,21 @@
       <c r="L15" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="18"/>
-      <c r="R15" s="18"/>
-      <c r="S15" s="16"/>
-      <c r="T15" s="16"/>
-      <c r="U15" s="18"/>
-      <c r="V15" s="16"/>
-      <c r="W15" s="16"/>
-      <c r="X15" s="16"/>
-      <c r="Y15" s="18"/>
-      <c r="Z15" s="16"/>
+      <c r="M15" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="27"/>
+      <c r="R15" s="27"/>
+      <c r="S15" s="20"/>
+      <c r="T15" s="20"/>
+      <c r="U15" s="27"/>
+      <c r="V15" s="20"/>
+      <c r="W15" s="20"/>
+      <c r="X15" s="20"/>
+      <c r="Y15" s="27"/>
+      <c r="Z15" s="20"/>
     </row>
     <row r="16" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
@@ -2675,7 +2851,7 @@
       <c r="D16" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="20" t="s">
         <v>94</v>
       </c>
       <c r="F16" s="16">
@@ -2687,7 +2863,9 @@
       <c r="H16" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="16"/>
+      <c r="I16" s="20" t="s">
+        <v>154</v>
+      </c>
       <c r="J16" s="16">
         <v>-3.82</v>
       </c>
@@ -2697,19 +2875,29 @@
       <c r="L16" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="18"/>
-      <c r="V16" s="16"/>
-      <c r="W16" s="16"/>
-      <c r="X16" s="16"/>
-      <c r="Y16" s="18"/>
-      <c r="Z16" s="16"/>
+      <c r="M16" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="O16" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="P16" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q16" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R16" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="S16" s="20"/>
+      <c r="T16" s="20"/>
+      <c r="U16" s="27"/>
+      <c r="V16" s="20"/>
+      <c r="W16" s="20"/>
+      <c r="X16" s="20"/>
+      <c r="Y16" s="27"/>
+      <c r="Z16" s="20"/>
     </row>
     <row r="17" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
@@ -2724,7 +2912,7 @@
       <c r="D17" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E17" s="22" t="s">
+      <c r="E17" s="20" t="s">
         <v>94</v>
       </c>
       <c r="F17" s="16">
@@ -2736,7 +2924,9 @@
       <c r="H17" s="16">
         <v>0.94</v>
       </c>
-      <c r="I17" s="16"/>
+      <c r="I17" s="20" t="s">
+        <v>153</v>
+      </c>
       <c r="J17" s="16">
         <v>0.01</v>
       </c>
@@ -2746,19 +2936,29 @@
       <c r="L17" s="18">
         <v>0.65</v>
       </c>
-      <c r="M17" s="16"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="16"/>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="16"/>
-      <c r="S17" s="16"/>
-      <c r="T17" s="16"/>
-      <c r="U17" s="16"/>
-      <c r="V17" s="16"/>
-      <c r="W17" s="16"/>
-      <c r="X17" s="16"/>
-      <c r="Y17" s="18"/>
-      <c r="Z17" s="16"/>
+      <c r="M17" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="O17" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="P17" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q17" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R17" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="S17" s="20"/>
+      <c r="T17" s="20"/>
+      <c r="U17" s="20"/>
+      <c r="V17" s="20"/>
+      <c r="W17" s="20"/>
+      <c r="X17" s="20"/>
+      <c r="Y17" s="27"/>
+      <c r="Z17" s="20"/>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
@@ -2773,7 +2973,7 @@
       <c r="D18" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="20" t="s">
         <v>94</v>
       </c>
       <c r="F18" s="16">
@@ -2785,7 +2985,9 @@
       <c r="H18" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I18" s="16"/>
+      <c r="I18" s="20" t="s">
+        <v>155</v>
+      </c>
       <c r="J18" s="16">
         <v>-0.11</v>
       </c>
@@ -2795,19 +2997,29 @@
       <c r="L18" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="16"/>
-      <c r="S18" s="16"/>
-      <c r="T18" s="16"/>
-      <c r="U18" s="18"/>
-      <c r="V18" s="16"/>
-      <c r="W18" s="16"/>
-      <c r="X18" s="16"/>
-      <c r="Y18" s="18"/>
-      <c r="Z18" s="16"/>
+      <c r="M18" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="O18" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="P18" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q18" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R18" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="S18" s="20"/>
+      <c r="T18" s="20"/>
+      <c r="U18" s="27"/>
+      <c r="V18" s="20"/>
+      <c r="W18" s="20"/>
+      <c r="X18" s="20"/>
+      <c r="Y18" s="27"/>
+      <c r="Z18" s="20"/>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
@@ -2822,7 +3034,7 @@
       <c r="D19" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E19" s="20" t="s">
         <v>94</v>
       </c>
       <c r="F19" s="16">
@@ -2834,7 +3046,9 @@
       <c r="H19" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I19" s="16"/>
+      <c r="I19" s="20" t="s">
+        <v>156</v>
+      </c>
       <c r="J19" s="16">
         <v>-0.02</v>
       </c>
@@ -2844,19 +3058,29 @@
       <c r="L19" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M19" s="16"/>
-      <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="16"/>
-      <c r="S19" s="16"/>
-      <c r="T19" s="16"/>
-      <c r="U19" s="18"/>
-      <c r="V19" s="16"/>
-      <c r="W19" s="16"/>
-      <c r="X19" s="16"/>
-      <c r="Y19" s="18"/>
-      <c r="Z19" s="16"/>
+      <c r="M19" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="O19" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="P19" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q19" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R19" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="S19" s="20"/>
+      <c r="T19" s="20"/>
+      <c r="U19" s="27"/>
+      <c r="V19" s="20"/>
+      <c r="W19" s="20"/>
+      <c r="X19" s="20"/>
+      <c r="Y19" s="27"/>
+      <c r="Z19" s="20"/>
     </row>
     <row r="20" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
@@ -2871,7 +3095,7 @@
       <c r="D20" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="20" t="s">
         <v>94</v>
       </c>
       <c r="F20" s="16" t="s">
@@ -2883,7 +3107,7 @@
       <c r="H20" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="I20" s="16" t="s">
+      <c r="I20" s="20" t="s">
         <v>94</v>
       </c>
       <c r="J20" s="16">
@@ -2895,19 +3119,37 @@
       <c r="L20" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M20" s="16"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="16"/>
-      <c r="Q20" s="16"/>
-      <c r="R20" s="16"/>
-      <c r="S20" s="16"/>
-      <c r="T20" s="16"/>
-      <c r="U20" s="16"/>
-      <c r="V20" s="16"/>
-      <c r="W20" s="16"/>
-      <c r="X20" s="16"/>
-      <c r="Y20" s="18"/>
-      <c r="Z20" s="16"/>
+      <c r="M20" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="O20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="P20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R20" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="S20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="T20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V20" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="W20" s="20"/>
+      <c r="X20" s="20"/>
+      <c r="Y20" s="27"/>
+      <c r="Z20" s="20"/>
     </row>
     <row r="21" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
@@ -2922,7 +3164,7 @@
       <c r="D21" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E21" s="22" t="s">
+      <c r="E21" s="20" t="s">
         <v>94</v>
       </c>
       <c r="F21" s="16" t="s">
@@ -2934,7 +3176,7 @@
       <c r="H21" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="I21" s="16" t="s">
+      <c r="I21" s="20" t="s">
         <v>94</v>
       </c>
       <c r="J21" s="16">
@@ -2946,19 +3188,37 @@
       <c r="L21" s="18">
         <v>0.84</v>
       </c>
-      <c r="M21" s="16"/>
-      <c r="O21" s="16"/>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="16"/>
-      <c r="S21" s="16"/>
-      <c r="T21" s="16"/>
-      <c r="U21" s="16"/>
-      <c r="V21" s="16"/>
-      <c r="W21" s="16"/>
-      <c r="X21" s="16"/>
-      <c r="Y21" s="18"/>
-      <c r="Z21" s="16"/>
+      <c r="M21" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="O21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="P21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R21" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="S21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="T21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V21" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="W21" s="20"/>
+      <c r="X21" s="20"/>
+      <c r="Y21" s="27"/>
+      <c r="Z21" s="20"/>
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
@@ -2973,7 +3233,7 @@
       <c r="D22" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="20" t="s">
         <v>94</v>
       </c>
       <c r="F22" s="16" t="s">
@@ -2985,7 +3245,7 @@
       <c r="H22" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="I22" s="16" t="s">
+      <c r="I22" s="20" t="s">
         <v>94</v>
       </c>
       <c r="J22" s="16">
@@ -2997,19 +3257,37 @@
       <c r="L22" s="18">
         <v>0.14000000000000001</v>
       </c>
-      <c r="M22" s="16"/>
-      <c r="O22" s="16"/>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="16"/>
-      <c r="R22" s="16"/>
-      <c r="S22" s="16"/>
-      <c r="T22" s="16"/>
-      <c r="U22" s="16"/>
-      <c r="V22" s="16"/>
-      <c r="W22" s="16"/>
-      <c r="X22" s="16"/>
-      <c r="Y22" s="18"/>
-      <c r="Z22" s="16"/>
+      <c r="M22" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="O22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="P22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R22" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="S22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="T22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V22" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="W22" s="20"/>
+      <c r="X22" s="20"/>
+      <c r="Y22" s="27"/>
+      <c r="Z22" s="20"/>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A23" s="16" t="s">
@@ -3024,7 +3302,7 @@
       <c r="D23" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E23" s="22" t="s">
+      <c r="E23" s="20" t="s">
         <v>94</v>
       </c>
       <c r="F23" s="16" t="s">
@@ -3036,7 +3314,7 @@
       <c r="H23" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="I23" s="16" t="s">
+      <c r="I23" s="20" t="s">
         <v>94</v>
       </c>
       <c r="J23" s="16">
@@ -3048,19 +3326,37 @@
       <c r="L23" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M23" s="16"/>
-      <c r="O23" s="16"/>
-      <c r="P23" s="16"/>
-      <c r="Q23" s="16"/>
-      <c r="R23" s="16"/>
-      <c r="S23" s="16"/>
-      <c r="T23" s="16"/>
-      <c r="U23" s="16"/>
-      <c r="V23" s="16"/>
-      <c r="W23" s="16"/>
-      <c r="X23" s="16"/>
-      <c r="Y23" s="18"/>
-      <c r="Z23" s="16"/>
+      <c r="M23" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="O23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="P23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R23" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="S23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="T23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V23" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="W23" s="20"/>
+      <c r="X23" s="20"/>
+      <c r="Y23" s="27"/>
+      <c r="Z23" s="20"/>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
@@ -3075,7 +3371,7 @@
       <c r="D24" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E24" s="22" t="s">
+      <c r="E24" s="20" t="s">
         <v>94</v>
       </c>
       <c r="F24" s="16" t="s">
@@ -3087,7 +3383,7 @@
       <c r="H24" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="I24" s="16" t="s">
+      <c r="I24" s="20" t="s">
         <v>94</v>
       </c>
       <c r="J24" s="16">
@@ -3099,19 +3395,37 @@
       <c r="L24" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="16"/>
-      <c r="O24" s="16"/>
-      <c r="P24" s="16"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="16"/>
-      <c r="S24" s="16"/>
-      <c r="T24" s="16"/>
-      <c r="U24" s="16"/>
-      <c r="V24" s="16"/>
-      <c r="W24" s="16"/>
-      <c r="X24" s="16"/>
-      <c r="Y24" s="18"/>
-      <c r="Z24" s="16"/>
+      <c r="M24" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="O24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="P24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R24" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="S24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="T24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V24" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="W24" s="20"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="27"/>
+      <c r="Z24" s="20"/>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A25" s="17" t="s">
@@ -3120,27 +3434,27 @@
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
-      <c r="E25" s="22"/>
+      <c r="E25" s="20"/>
       <c r="F25" s="16"/>
       <c r="G25" s="16"/>
       <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
+      <c r="I25" s="20"/>
       <c r="J25" s="16"/>
       <c r="K25" s="16"/>
       <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="O25" s="16"/>
-      <c r="P25" s="16"/>
-      <c r="Q25" s="16"/>
-      <c r="R25" s="16"/>
-      <c r="S25" s="16"/>
-      <c r="T25" s="16"/>
-      <c r="U25" s="16"/>
-      <c r="V25" s="16"/>
-      <c r="W25" s="16"/>
-      <c r="X25" s="16"/>
-      <c r="Y25" s="16"/>
-      <c r="Z25" s="16"/>
+      <c r="M25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="20"/>
+      <c r="R25" s="20"/>
+      <c r="S25" s="20"/>
+      <c r="T25" s="20"/>
+      <c r="U25" s="20"/>
+      <c r="V25" s="20"/>
+      <c r="W25" s="20"/>
+      <c r="X25" s="20"/>
+      <c r="Y25" s="20"/>
+      <c r="Z25" s="20"/>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
@@ -3155,7 +3469,9 @@
       <c r="D26" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E26" s="22"/>
+      <c r="E26" s="20" t="s">
+        <v>144</v>
+      </c>
       <c r="F26" s="16">
         <v>12.23</v>
       </c>
@@ -3165,7 +3481,9 @@
       <c r="H26" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I26" s="16"/>
+      <c r="I26" s="20" t="s">
+        <v>157</v>
+      </c>
       <c r="J26" s="16">
         <v>12.23</v>
       </c>
@@ -3175,19 +3493,21 @@
       <c r="L26" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M26" s="16"/>
-      <c r="O26" s="16"/>
-      <c r="P26" s="16"/>
-      <c r="Q26" s="18"/>
-      <c r="R26" s="16"/>
-      <c r="S26" s="16"/>
-      <c r="T26" s="16"/>
-      <c r="U26" s="18"/>
-      <c r="V26" s="16"/>
-      <c r="W26" s="16"/>
-      <c r="X26" s="16"/>
-      <c r="Y26" s="18"/>
-      <c r="Z26" s="16"/>
+      <c r="M26" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="O26" s="20"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="27"/>
+      <c r="R26" s="20"/>
+      <c r="S26" s="20"/>
+      <c r="T26" s="20"/>
+      <c r="U26" s="27"/>
+      <c r="V26" s="20"/>
+      <c r="W26" s="20"/>
+      <c r="X26" s="20"/>
+      <c r="Y26" s="27"/>
+      <c r="Z26" s="20"/>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
@@ -3202,7 +3522,9 @@
       <c r="D27" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="22"/>
+      <c r="E27" s="20" t="s">
+        <v>145</v>
+      </c>
       <c r="F27" s="16">
         <v>0.59</v>
       </c>
@@ -3212,7 +3534,9 @@
       <c r="H27" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I27" s="16"/>
+      <c r="I27" s="20" t="s">
+        <v>158</v>
+      </c>
       <c r="J27" s="16">
         <v>0.59</v>
       </c>
@@ -3222,19 +3546,21 @@
       <c r="L27" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M27" s="16"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="16"/>
-      <c r="Q27" s="18"/>
-      <c r="R27" s="16"/>
-      <c r="S27" s="16"/>
-      <c r="T27" s="16"/>
-      <c r="U27" s="18"/>
-      <c r="V27" s="16"/>
-      <c r="W27" s="16"/>
-      <c r="X27" s="16"/>
-      <c r="Y27" s="18"/>
-      <c r="Z27" s="16"/>
+      <c r="M27" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="O27" s="20"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="27"/>
+      <c r="R27" s="20"/>
+      <c r="S27" s="20"/>
+      <c r="T27" s="20"/>
+      <c r="U27" s="27"/>
+      <c r="V27" s="20"/>
+      <c r="W27" s="20"/>
+      <c r="X27" s="20"/>
+      <c r="Y27" s="27"/>
+      <c r="Z27" s="20"/>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A28" s="16" t="s">
@@ -3249,7 +3575,7 @@
       <c r="D28" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E28" s="22" t="s">
+      <c r="E28" s="20" t="s">
         <v>94</v>
       </c>
       <c r="F28" s="16">
@@ -3261,7 +3587,9 @@
       <c r="H28" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I28" s="16"/>
+      <c r="I28" s="20" t="s">
+        <v>159</v>
+      </c>
       <c r="J28" s="16">
         <v>1.83</v>
       </c>
@@ -3271,19 +3599,29 @@
       <c r="L28" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M28" s="16"/>
-      <c r="O28" s="16"/>
-      <c r="P28" s="16"/>
-      <c r="Q28" s="16"/>
-      <c r="R28" s="16"/>
-      <c r="S28" s="16"/>
-      <c r="T28" s="16"/>
-      <c r="U28" s="18"/>
-      <c r="V28" s="16"/>
-      <c r="W28" s="16"/>
-      <c r="X28" s="16"/>
-      <c r="Y28" s="18"/>
-      <c r="Z28" s="16"/>
+      <c r="M28" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="O28" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="P28" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q28" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R28" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="S28" s="20"/>
+      <c r="T28" s="20"/>
+      <c r="U28" s="27"/>
+      <c r="V28" s="20"/>
+      <c r="W28" s="20"/>
+      <c r="X28" s="20"/>
+      <c r="Y28" s="27"/>
+      <c r="Z28" s="20"/>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A29" s="16" t="s">
@@ -3298,7 +3636,7 @@
       <c r="D29" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E29" s="22" t="s">
+      <c r="E29" s="20" t="s">
         <v>94</v>
       </c>
       <c r="F29" s="16" t="s">
@@ -3310,7 +3648,7 @@
       <c r="H29" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="I29" s="16" t="s">
+      <c r="I29" s="20" t="s">
         <v>94</v>
       </c>
       <c r="J29" s="16">
@@ -3322,19 +3660,37 @@
       <c r="L29" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M29" s="16"/>
-      <c r="O29" s="16"/>
-      <c r="P29" s="16"/>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="16"/>
-      <c r="S29" s="16"/>
-      <c r="T29" s="16"/>
-      <c r="U29" s="16"/>
-      <c r="V29" s="16"/>
-      <c r="W29" s="16"/>
-      <c r="X29" s="16"/>
-      <c r="Y29" s="18"/>
-      <c r="Z29" s="16"/>
+      <c r="M29" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="O29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="P29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R29" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="S29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="T29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V29" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="W29" s="20"/>
+      <c r="X29" s="20"/>
+      <c r="Y29" s="27"/>
+      <c r="Z29" s="20"/>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A30" s="17" t="s">
@@ -3343,27 +3699,27 @@
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
-      <c r="E30" s="22"/>
+      <c r="E30" s="20"/>
       <c r="F30" s="16"/>
       <c r="G30" s="16"/>
       <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
+      <c r="I30" s="20"/>
       <c r="J30" s="16"/>
       <c r="K30" s="16"/>
       <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="O30" s="16"/>
-      <c r="P30" s="16"/>
-      <c r="Q30" s="16"/>
-      <c r="R30" s="16"/>
-      <c r="S30" s="16"/>
-      <c r="T30" s="16"/>
-      <c r="U30" s="16"/>
-      <c r="V30" s="16"/>
-      <c r="W30" s="16"/>
-      <c r="X30" s="16"/>
-      <c r="Y30" s="16"/>
-      <c r="Z30" s="16"/>
+      <c r="M30" s="20"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20"/>
+      <c r="R30" s="20"/>
+      <c r="S30" s="20"/>
+      <c r="T30" s="20"/>
+      <c r="U30" s="20"/>
+      <c r="V30" s="20"/>
+      <c r="W30" s="20"/>
+      <c r="X30" s="20"/>
+      <c r="Y30" s="20"/>
+      <c r="Z30" s="20"/>
     </row>
     <row r="31" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
@@ -3378,7 +3734,9 @@
       <c r="D31" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E31" s="22"/>
+      <c r="E31" s="20" t="s">
+        <v>140</v>
+      </c>
       <c r="F31" s="16">
         <v>2200.12</v>
       </c>
@@ -3388,7 +3746,9 @@
       <c r="H31" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I31" s="16"/>
+      <c r="I31" s="20" t="s">
+        <v>160</v>
+      </c>
       <c r="J31" s="16">
         <v>2199.7800000000002</v>
       </c>
@@ -3398,19 +3758,21 @@
       <c r="L31" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M31" s="16"/>
-      <c r="O31" s="16"/>
-      <c r="P31" s="16"/>
-      <c r="Q31" s="18"/>
-      <c r="R31" s="16"/>
-      <c r="S31" s="16"/>
-      <c r="T31" s="16"/>
-      <c r="U31" s="18"/>
-      <c r="V31" s="16"/>
-      <c r="W31" s="16"/>
-      <c r="X31" s="16"/>
-      <c r="Y31" s="18"/>
-      <c r="Z31" s="16"/>
+      <c r="M31" s="20" t="s">
+        <v>176</v>
+      </c>
+      <c r="O31" s="20"/>
+      <c r="P31" s="20"/>
+      <c r="Q31" s="27"/>
+      <c r="R31" s="20"/>
+      <c r="S31" s="20"/>
+      <c r="T31" s="20"/>
+      <c r="U31" s="27"/>
+      <c r="V31" s="20"/>
+      <c r="W31" s="20"/>
+      <c r="X31" s="20"/>
+      <c r="Y31" s="27"/>
+      <c r="Z31" s="20"/>
     </row>
     <row r="32" spans="1:26" ht="17" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
@@ -3425,7 +3787,9 @@
       <c r="D32" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E32" s="22"/>
+      <c r="E32" s="20" t="s">
+        <v>141</v>
+      </c>
       <c r="F32" s="16">
         <v>93.66</v>
       </c>
@@ -3435,7 +3799,9 @@
       <c r="H32" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I32" s="16"/>
+      <c r="I32" s="20" t="s">
+        <v>161</v>
+      </c>
       <c r="J32" s="16">
         <v>93.71</v>
       </c>
@@ -3445,21 +3811,23 @@
       <c r="L32" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M32" s="16"/>
-      <c r="O32" s="16"/>
-      <c r="P32" s="16"/>
-      <c r="Q32" s="18"/>
-      <c r="R32" s="16"/>
-      <c r="S32" s="16"/>
-      <c r="T32" s="16"/>
-      <c r="U32" s="18"/>
-      <c r="V32" s="16"/>
-      <c r="W32" s="16"/>
-      <c r="X32" s="16"/>
-      <c r="Y32" s="18"/>
-      <c r="Z32" s="16"/>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="M32" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="27"/>
+      <c r="R32" s="20"/>
+      <c r="S32" s="20"/>
+      <c r="T32" s="20"/>
+      <c r="U32" s="27"/>
+      <c r="V32" s="20"/>
+      <c r="W32" s="20"/>
+      <c r="X32" s="20"/>
+      <c r="Y32" s="27"/>
+      <c r="Z32" s="20"/>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A33" s="16" t="s">
         <v>84</v>
       </c>
@@ -3472,7 +3840,9 @@
       <c r="D33" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E33" s="22"/>
+      <c r="E33" s="20" t="s">
+        <v>142</v>
+      </c>
       <c r="F33" s="16">
         <v>1.1599999999999999</v>
       </c>
@@ -3482,7 +3852,9 @@
       <c r="H33" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I33" s="16"/>
+      <c r="I33" s="20" t="s">
+        <v>162</v>
+      </c>
       <c r="J33" s="16">
         <v>1.1599999999999999</v>
       </c>
@@ -3492,21 +3864,23 @@
       <c r="L33" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M33" s="16"/>
-      <c r="O33" s="16"/>
-      <c r="P33" s="16"/>
-      <c r="Q33" s="18"/>
-      <c r="R33" s="16"/>
-      <c r="S33" s="16"/>
-      <c r="T33" s="16"/>
-      <c r="U33" s="18"/>
-      <c r="V33" s="16"/>
-      <c r="W33" s="16"/>
-      <c r="X33" s="16"/>
-      <c r="Y33" s="18"/>
-      <c r="Z33" s="16"/>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="M33" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="27"/>
+      <c r="R33" s="20"/>
+      <c r="S33" s="20"/>
+      <c r="T33" s="20"/>
+      <c r="U33" s="27"/>
+      <c r="V33" s="20"/>
+      <c r="W33" s="20"/>
+      <c r="X33" s="20"/>
+      <c r="Y33" s="27"/>
+      <c r="Z33" s="20"/>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A34" s="16" t="s">
         <v>89</v>
       </c>
@@ -3519,7 +3893,9 @@
       <c r="D34" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E34" s="22"/>
+      <c r="E34" s="20" t="s">
+        <v>143</v>
+      </c>
       <c r="F34" s="16">
         <v>0.02</v>
       </c>
@@ -3529,7 +3905,9 @@
       <c r="H34" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I34" s="16"/>
+      <c r="I34" s="20" t="s">
+        <v>139</v>
+      </c>
       <c r="J34" s="16">
         <v>0.02</v>
       </c>
@@ -3539,21 +3917,23 @@
       <c r="L34" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M34" s="16"/>
-      <c r="O34" s="16"/>
-      <c r="P34" s="16"/>
-      <c r="Q34" s="18"/>
-      <c r="R34" s="16"/>
-      <c r="S34" s="16"/>
-      <c r="T34" s="16"/>
-      <c r="U34" s="18"/>
-      <c r="V34" s="16"/>
-      <c r="W34" s="16"/>
-      <c r="X34" s="16"/>
-      <c r="Y34" s="18"/>
-      <c r="Z34" s="16"/>
-    </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="M34" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="O34" s="20"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="27"/>
+      <c r="R34" s="20"/>
+      <c r="S34" s="20"/>
+      <c r="T34" s="20"/>
+      <c r="U34" s="27"/>
+      <c r="V34" s="20"/>
+      <c r="W34" s="20"/>
+      <c r="X34" s="20"/>
+      <c r="Y34" s="27"/>
+      <c r="Z34" s="20"/>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A35" s="16" t="s">
         <v>93</v>
       </c>
@@ -3566,7 +3946,7 @@
       <c r="D35" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E35" s="22" t="s">
+      <c r="E35" s="20" t="s">
         <v>94</v>
       </c>
       <c r="F35" s="16">
@@ -3578,7 +3958,9 @@
       <c r="H35" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="I35" s="16"/>
+      <c r="I35" s="20" t="s">
+        <v>163</v>
+      </c>
       <c r="J35" s="16">
         <v>3.26</v>
       </c>
@@ -3588,136 +3970,98 @@
       <c r="L35" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M35" s="16"/>
-      <c r="O35" s="16"/>
-      <c r="P35" s="16"/>
-      <c r="Q35" s="16"/>
-      <c r="R35" s="16"/>
-      <c r="S35" s="16"/>
-      <c r="T35" s="16"/>
-      <c r="U35" s="18"/>
-      <c r="V35" s="16"/>
-      <c r="W35" s="16"/>
-      <c r="X35" s="16"/>
-      <c r="Y35" s="18"/>
-      <c r="Z35" s="16"/>
-    </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A36" s="16" t="s">
+      <c r="M35" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="O35" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="P35" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q35" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R35" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="S35" s="20"/>
+      <c r="T35" s="20"/>
+      <c r="U35" s="27"/>
+      <c r="V35" s="20"/>
+      <c r="W35" s="20"/>
+      <c r="X35" s="20"/>
+      <c r="Y35" s="27"/>
+      <c r="Z35" s="20"/>
+    </row>
+    <row r="36" spans="1:26" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="B36" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D36" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F36" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="G36" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="H36" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I36" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="J36" s="16">
+      <c r="B36" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E36" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="H36" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="I36" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="J36" s="15">
         <v>7.64</v>
       </c>
-      <c r="K36" s="16">
+      <c r="K36" s="15">
         <v>0.3</v>
       </c>
-      <c r="L36" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="O36" s="16"/>
-      <c r="P36" s="16"/>
-      <c r="Q36" s="16"/>
-      <c r="R36" s="16"/>
-      <c r="S36" s="16"/>
-      <c r="T36" s="16"/>
-      <c r="U36" s="16"/>
-      <c r="V36" s="16"/>
-      <c r="W36" s="16"/>
-      <c r="X36" s="16"/>
-      <c r="Y36" s="18"/>
-    </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A37" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="14"/>
-      <c r="N37" s="14"/>
-      <c r="O37" s="14"/>
-      <c r="P37" s="14"/>
-      <c r="Q37" s="14"/>
-      <c r="R37" s="14"/>
-      <c r="S37" s="14"/>
-      <c r="T37" s="14"/>
-      <c r="U37" s="14"/>
-      <c r="V37" s="14"/>
-      <c r="W37" s="14"/>
-      <c r="X37" s="14"/>
-      <c r="Y37" s="14"/>
-      <c r="Z37" s="14"/>
-      <c r="AA37" s="14"/>
-      <c r="AB37" s="16"/>
-      <c r="AC37" s="16"/>
-    </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A38" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B38" s="15">
-        <v>74058</v>
-      </c>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
-      <c r="N38" s="15"/>
-      <c r="O38" s="15"/>
-      <c r="P38" s="15"/>
-      <c r="Q38" s="15"/>
-      <c r="R38" s="15"/>
-      <c r="S38" s="15"/>
-      <c r="T38" s="15"/>
-      <c r="U38" s="15"/>
-      <c r="V38" s="15"/>
-      <c r="W38" s="15"/>
-      <c r="X38" s="15"/>
-      <c r="Y38" s="15"/>
-      <c r="Z38" s="15"/>
-      <c r="AA38" s="15"/>
-      <c r="AB38" s="16"/>
-      <c r="AC38" s="16"/>
+      <c r="L36" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="M36" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="O36" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="P36" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q36" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="R36" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="S36" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="T36" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="U36" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="V36" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="W36" s="28"/>
+      <c r="X36" s="28"/>
+      <c r="Y36" s="31"/>
+      <c r="Z36" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -3744,57 +4088,57 @@
     <col min="3" max="3" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28"/>
-    </row>
-    <row r="3" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
+    <row r="1" spans="1:3" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="21" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28" t="s">
+    <row r="2" spans="1:3" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="22"/>
+    </row>
+    <row r="3" spans="1:3" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="22" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="22"/>
+    </row>
+    <row r="6" spans="1:3" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="22"/>
+    </row>
+    <row r="7" spans="1:3" s="21" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:3" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="21" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="28"/>
-    </row>
-    <row r="6" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="28"/>
-    </row>
-    <row r="7" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="27" t="s">
-        <v>127</v>
-      </c>
-    </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="28" t="s">
-        <v>122</v>
+      <c r="A9" s="22" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="28" t="s">
-        <v>121</v>
+      <c r="A10" s="22" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B11" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>132</v>
+      <c r="B11" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B12">
         <v>-3.4000000000000002E-2</v>
@@ -3805,7 +4149,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B13">
         <v>-2.4E-2</v>
@@ -3816,7 +4160,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B14">
         <v>-2.3E-2</v>
@@ -3827,30 +4171,30 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="27" t="s">
-        <v>123</v>
+      <c r="A17" s="21" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="28" t="s">
-        <v>133</v>
+      <c r="A18" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B19" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>132</v>
+      <c r="B19" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B20">
         <v>-3.1E-2</v>
@@ -3861,7 +4205,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B21">
         <v>-0.03</v>
@@ -3872,7 +4216,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B22">
         <v>-0.113</v>
@@ -3883,12 +4227,12 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E25" s="27" t="s">
-        <v>134</v>
+      <c r="E25" s="21" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmoffice-my.sharepoint.com/personal/abrieant_uvm_edu/Documents/OneDrive/Manuscripts/reg report DCN/pubertybrain/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{1C85D9B2-5526-4A3F-887C-73776185B9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2AA9C4B-FAB2-AB49-B4FB-20A7516B6A3B}"/>
+  <xr:revisionPtr revIDLastSave="154" documentId="13_ncr:1_{1C85D9B2-5526-4A3F-887C-73776185B9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94A72430-9BB9-324F-A298-FFA3802015BD}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="2140" windowWidth="28800" windowHeight="15140" activeTab="5" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
@@ -18,7 +18,9 @@
     <sheet name="Fig1 (Pub)" sheetId="3" r:id="rId3"/>
     <sheet name="Fig2 (Brain)" sheetId="4" r:id="rId4"/>
     <sheet name="CortModels" sheetId="6" r:id="rId5"/>
-    <sheet name="Indirect effects" sheetId="7" r:id="rId6"/>
+    <sheet name="Youth report PDS" sheetId="9" r:id="rId6"/>
+    <sheet name="Indirect effects" sheetId="7" r:id="rId7"/>
+    <sheet name="Corrected ps" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="141">
   <si>
     <t>16.10 (2.98)</t>
   </si>
@@ -718,12 +720,59 @@
   <si>
     <t>MALE - subcortical</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">p </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>value</t>
+    </r>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">corrected </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">p </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>value</t>
+    </r>
+  </si>
+  <si>
+    <t>Corrected p value</t>
+  </si>
+  <si>
+    <t>Cortical volume by sex - YOUTH REPORT PDS</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -818,8 +867,21 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -832,8 +894,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -859,11 +933,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -901,14 +986,29 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2021,7 +2121,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA86F85-A8D4-F648-84C3-730F1A42C846}">
-  <dimension ref="A1:AC38"/>
+  <dimension ref="A1:AE38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -2036,99 +2136,105 @@
     <col min="10" max="10" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="2.83203125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="11" style="1"/>
+    <col min="13" max="13" width="12.5" style="1" customWidth="1"/>
+    <col min="14" max="14" width="14.1640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="2.83203125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="O2" s="26" t="s">
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="Q2" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="26"/>
-      <c r="Y2" s="26"/>
-      <c r="Z2" s="26"/>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="31"/>
+      <c r="Z2" s="31"/>
+      <c r="AA2" s="31"/>
+      <c r="AB2" s="31"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="15"/>
-      <c r="B3" s="25" t="s">
+      <c r="B3" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25" t="s">
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25" t="s">
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="O3" s="25" t="s">
+      <c r="K3" s="30"/>
+      <c r="L3" s="30"/>
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
+      <c r="Q3" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25" t="s">
+      <c r="R3" s="30"/>
+      <c r="S3" s="30"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
-      <c r="W3" s="25" t="s">
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="30"/>
+      <c r="Y3" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="X3" s="25"/>
-      <c r="Y3" s="25"/>
-      <c r="Z3" s="25"/>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="Z3" s="30"/>
+      <c r="AA3" s="30"/>
+      <c r="AB3" s="30"/>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" s="16"/>
       <c r="B4" s="17" t="s">
         <v>90</v>
@@ -2163,47 +2269,53 @@
       <c r="L4" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="M4" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="N4" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="O4" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="O4" s="17" t="s">
+      <c r="Q4" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="P4" s="17" t="s">
+      <c r="R4" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="Q4" s="17" t="s">
+      <c r="S4" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="R4" s="17" t="s">
+      <c r="T4" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="S4" s="17" t="s">
+      <c r="U4" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="T4" s="17" t="s">
+      <c r="V4" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="U4" s="17" t="s">
+      <c r="W4" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="V4" s="17" t="s">
+      <c r="X4" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="W4" s="17" t="s">
+      <c r="Y4" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="X4" s="17" t="s">
+      <c r="Z4" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="Y4" s="17" t="s">
+      <c r="AA4" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="Z4" s="17" t="s">
+      <c r="AB4" s="17" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
         <v>85</v>
       </c>
@@ -2219,8 +2331,8 @@
       <c r="K5" s="16"/>
       <c r="L5" s="16"/>
       <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
       <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
       <c r="Q5" s="16"/>
       <c r="R5" s="16"/>
       <c r="S5" s="16"/>
@@ -2231,8 +2343,10 @@
       <c r="X5" s="16"/>
       <c r="Y5" s="16"/>
       <c r="Z5" s="16"/>
-    </row>
-    <row r="6" spans="1:26" ht="17" x14ac:dyDescent="0.25">
+      <c r="AA5" s="16"/>
+      <c r="AB5" s="16"/>
+    </row>
+    <row r="6" spans="1:28" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>96</v>
       </c>
@@ -2261,21 +2375,23 @@
       <c r="L6" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M6" s="16"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
       <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="18"/>
+      <c r="Q6" s="16"/>
       <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
+      <c r="S6" s="18"/>
       <c r="T6" s="16"/>
-      <c r="U6" s="18"/>
+      <c r="U6" s="16"/>
       <c r="V6" s="16"/>
-      <c r="W6" s="16"/>
+      <c r="W6" s="18"/>
       <c r="X6" s="16"/>
-      <c r="Y6" s="18"/>
+      <c r="Y6" s="16"/>
       <c r="Z6" s="16"/>
-    </row>
-    <row r="7" spans="1:26" ht="17" x14ac:dyDescent="0.25">
+      <c r="AA6" s="18"/>
+      <c r="AB6" s="16"/>
+    </row>
+    <row r="7" spans="1:28" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>97</v>
       </c>
@@ -2304,21 +2420,23 @@
       <c r="L7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M7" s="16"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18"/>
       <c r="O7" s="16"/>
-      <c r="P7" s="16"/>
-      <c r="Q7" s="18"/>
+      <c r="Q7" s="16"/>
       <c r="R7" s="16"/>
-      <c r="S7" s="16"/>
+      <c r="S7" s="18"/>
       <c r="T7" s="16"/>
-      <c r="U7" s="18"/>
+      <c r="U7" s="16"/>
       <c r="V7" s="16"/>
-      <c r="W7" s="16"/>
+      <c r="W7" s="18"/>
       <c r="X7" s="16"/>
-      <c r="Y7" s="18"/>
+      <c r="Y7" s="16"/>
       <c r="Z7" s="16"/>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="18"/>
+      <c r="AB7" s="16"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
         <v>86</v>
       </c>
@@ -2334,8 +2452,8 @@
       <c r="K8" s="16"/>
       <c r="L8" s="16"/>
       <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
       <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
       <c r="Q8" s="16"/>
       <c r="R8" s="16"/>
       <c r="S8" s="16"/>
@@ -2346,8 +2464,10 @@
       <c r="X8" s="16"/>
       <c r="Y8" s="16"/>
       <c r="Z8" s="16"/>
-    </row>
-    <row r="9" spans="1:26" ht="17" x14ac:dyDescent="0.25">
+      <c r="AA8" s="16"/>
+      <c r="AB8" s="16"/>
+    </row>
+    <row r="9" spans="1:28" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>98</v>
       </c>
@@ -2382,21 +2502,23 @@
       <c r="L9" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="16"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
       <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="18"/>
+      <c r="Q9" s="16"/>
       <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
+      <c r="S9" s="18"/>
       <c r="T9" s="16"/>
-      <c r="U9" s="18"/>
+      <c r="U9" s="16"/>
       <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
+      <c r="W9" s="18"/>
       <c r="X9" s="16"/>
-      <c r="Y9" s="18"/>
+      <c r="Y9" s="16"/>
       <c r="Z9" s="16"/>
-    </row>
-    <row r="10" spans="1:26" ht="17" x14ac:dyDescent="0.25">
+      <c r="AA9" s="18"/>
+      <c r="AB9" s="16"/>
+    </row>
+    <row r="10" spans="1:28" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>99</v>
       </c>
@@ -2429,21 +2551,23 @@
       <c r="L10" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M10" s="16"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18"/>
       <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="18"/>
+      <c r="Q10" s="16"/>
       <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
+      <c r="S10" s="18"/>
       <c r="T10" s="16"/>
-      <c r="U10" s="18"/>
+      <c r="U10" s="16"/>
       <c r="V10" s="16"/>
-      <c r="W10" s="16"/>
+      <c r="W10" s="18"/>
       <c r="X10" s="16"/>
-      <c r="Y10" s="18"/>
+      <c r="Y10" s="16"/>
       <c r="Z10" s="16"/>
-    </row>
-    <row r="11" spans="1:26" ht="17" x14ac:dyDescent="0.25">
+      <c r="AA10" s="18"/>
+      <c r="AB10" s="16"/>
+    </row>
+    <row r="11" spans="1:28" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>100</v>
       </c>
@@ -2476,21 +2600,23 @@
       <c r="L11" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M11" s="16"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
       <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="18"/>
+      <c r="Q11" s="16"/>
       <c r="R11" s="16"/>
-      <c r="S11" s="16"/>
+      <c r="S11" s="18"/>
       <c r="T11" s="16"/>
-      <c r="U11" s="18"/>
+      <c r="U11" s="16"/>
       <c r="V11" s="16"/>
-      <c r="W11" s="16"/>
+      <c r="W11" s="18"/>
       <c r="X11" s="16"/>
-      <c r="Y11" s="18"/>
+      <c r="Y11" s="16"/>
       <c r="Z11" s="16"/>
-    </row>
-    <row r="12" spans="1:26" ht="17" x14ac:dyDescent="0.25">
+      <c r="AA11" s="18"/>
+      <c r="AB11" s="16"/>
+    </row>
+    <row r="12" spans="1:28" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>101</v>
       </c>
@@ -2523,21 +2649,23 @@
       <c r="L12" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="16"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18"/>
       <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="18"/>
+      <c r="Q12" s="16"/>
       <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
+      <c r="S12" s="18"/>
       <c r="T12" s="16"/>
-      <c r="U12" s="18"/>
+      <c r="U12" s="16"/>
       <c r="V12" s="16"/>
-      <c r="W12" s="16"/>
+      <c r="W12" s="18"/>
       <c r="X12" s="16"/>
-      <c r="Y12" s="18"/>
+      <c r="Y12" s="16"/>
       <c r="Z12" s="16"/>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="18"/>
+      <c r="AB12" s="16"/>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A13" s="16" t="s">
         <v>88</v>
       </c>
@@ -2570,21 +2698,23 @@
       <c r="L13" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M13" s="16"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18"/>
       <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="18"/>
+      <c r="Q13" s="16"/>
       <c r="R13" s="16"/>
-      <c r="S13" s="16"/>
+      <c r="S13" s="18"/>
       <c r="T13" s="16"/>
-      <c r="U13" s="18"/>
+      <c r="U13" s="16"/>
       <c r="V13" s="16"/>
-      <c r="W13" s="16"/>
+      <c r="W13" s="18"/>
       <c r="X13" s="16"/>
-      <c r="Y13" s="18"/>
+      <c r="Y13" s="16"/>
       <c r="Z13" s="16"/>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="18"/>
+      <c r="AB13" s="16"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
         <v>87</v>
       </c>
@@ -2600,8 +2730,8 @@
       <c r="K14" s="16"/>
       <c r="L14" s="16"/>
       <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
       <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
       <c r="Q14" s="16"/>
       <c r="R14" s="16"/>
       <c r="S14" s="16"/>
@@ -2612,8 +2742,10 @@
       <c r="X14" s="16"/>
       <c r="Y14" s="16"/>
       <c r="Z14" s="16"/>
-    </row>
-    <row r="15" spans="1:26" ht="17" x14ac:dyDescent="0.25">
+      <c r="AA14" s="16"/>
+      <c r="AB14" s="16"/>
+    </row>
+    <row r="15" spans="1:28" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>102</v>
       </c>
@@ -2648,21 +2780,23 @@
       <c r="L15" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M15" s="16"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="18"/>
       <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="18"/>
-      <c r="R15" s="18"/>
-      <c r="S15" s="16"/>
-      <c r="T15" s="16"/>
-      <c r="U15" s="18"/>
+      <c r="Q15" s="16"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="18"/>
+      <c r="T15" s="18"/>
+      <c r="U15" s="16"/>
       <c r="V15" s="16"/>
-      <c r="W15" s="16"/>
+      <c r="W15" s="18"/>
       <c r="X15" s="16"/>
-      <c r="Y15" s="18"/>
+      <c r="Y15" s="16"/>
       <c r="Z15" s="16"/>
-    </row>
-    <row r="16" spans="1:26" ht="17" x14ac:dyDescent="0.25">
+      <c r="AA15" s="18"/>
+      <c r="AB15" s="16"/>
+    </row>
+    <row r="16" spans="1:28" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>103</v>
       </c>
@@ -2697,21 +2831,23 @@
       <c r="L16" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M16" s="16"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
       <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
       <c r="Q16" s="16"/>
       <c r="R16" s="16"/>
       <c r="S16" s="16"/>
       <c r="T16" s="16"/>
-      <c r="U16" s="18"/>
+      <c r="U16" s="16"/>
       <c r="V16" s="16"/>
-      <c r="W16" s="16"/>
+      <c r="W16" s="18"/>
       <c r="X16" s="16"/>
-      <c r="Y16" s="18"/>
+      <c r="Y16" s="16"/>
       <c r="Z16" s="16"/>
-    </row>
-    <row r="17" spans="1:26" ht="17" x14ac:dyDescent="0.25">
+      <c r="AA16" s="18"/>
+      <c r="AB16" s="16"/>
+    </row>
+    <row r="17" spans="1:28" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>104</v>
       </c>
@@ -2746,9 +2882,9 @@
       <c r="L17" s="18">
         <v>0.65</v>
       </c>
-      <c r="M17" s="16"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18"/>
       <c r="O17" s="16"/>
-      <c r="P17" s="16"/>
       <c r="Q17" s="16"/>
       <c r="R17" s="16"/>
       <c r="S17" s="16"/>
@@ -2757,10 +2893,12 @@
       <c r="V17" s="16"/>
       <c r="W17" s="16"/>
       <c r="X17" s="16"/>
-      <c r="Y17" s="18"/>
+      <c r="Y17" s="16"/>
       <c r="Z17" s="16"/>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="18"/>
+      <c r="AB17" s="16"/>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
         <v>107</v>
       </c>
@@ -2795,21 +2933,23 @@
       <c r="L18" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M18" s="16"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
       <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
       <c r="Q18" s="16"/>
       <c r="R18" s="16"/>
       <c r="S18" s="16"/>
       <c r="T18" s="16"/>
-      <c r="U18" s="18"/>
+      <c r="U18" s="16"/>
       <c r="V18" s="16"/>
-      <c r="W18" s="16"/>
+      <c r="W18" s="18"/>
       <c r="X18" s="16"/>
-      <c r="Y18" s="18"/>
+      <c r="Y18" s="16"/>
       <c r="Z18" s="16"/>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="18"/>
+      <c r="AB18" s="16"/>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
         <v>108</v>
       </c>
@@ -2844,21 +2984,23 @@
       <c r="L19" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M19" s="16"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
       <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
       <c r="Q19" s="16"/>
       <c r="R19" s="16"/>
       <c r="S19" s="16"/>
       <c r="T19" s="16"/>
-      <c r="U19" s="18"/>
+      <c r="U19" s="16"/>
       <c r="V19" s="16"/>
-      <c r="W19" s="16"/>
+      <c r="W19" s="18"/>
       <c r="X19" s="16"/>
-      <c r="Y19" s="18"/>
+      <c r="Y19" s="16"/>
       <c r="Z19" s="16"/>
-    </row>
-    <row r="20" spans="1:26" ht="17" x14ac:dyDescent="0.25">
+      <c r="AA19" s="18"/>
+      <c r="AB19" s="16"/>
+    </row>
+    <row r="20" spans="1:28" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>105</v>
       </c>
@@ -2895,9 +3037,9 @@
       <c r="L20" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M20" s="16"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18"/>
       <c r="O20" s="16"/>
-      <c r="P20" s="16"/>
       <c r="Q20" s="16"/>
       <c r="R20" s="16"/>
       <c r="S20" s="16"/>
@@ -2906,10 +3048,12 @@
       <c r="V20" s="16"/>
       <c r="W20" s="16"/>
       <c r="X20" s="16"/>
-      <c r="Y20" s="18"/>
+      <c r="Y20" s="16"/>
       <c r="Z20" s="16"/>
-    </row>
-    <row r="21" spans="1:26" ht="17" x14ac:dyDescent="0.25">
+      <c r="AA20" s="18"/>
+      <c r="AB20" s="16"/>
+    </row>
+    <row r="21" spans="1:28" ht="17" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>106</v>
       </c>
@@ -2946,9 +3090,9 @@
       <c r="L21" s="18">
         <v>0.84</v>
       </c>
-      <c r="M21" s="16"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
       <c r="O21" s="16"/>
-      <c r="P21" s="16"/>
       <c r="Q21" s="16"/>
       <c r="R21" s="16"/>
       <c r="S21" s="16"/>
@@ -2957,10 +3101,12 @@
       <c r="V21" s="16"/>
       <c r="W21" s="16"/>
       <c r="X21" s="16"/>
-      <c r="Y21" s="18"/>
+      <c r="Y21" s="16"/>
       <c r="Z21" s="16"/>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="18"/>
+      <c r="AB21" s="16"/>
+    </row>
+    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
         <v>110</v>
       </c>
@@ -2997,9 +3143,9 @@
       <c r="L22" s="18">
         <v>0.14000000000000001</v>
       </c>
-      <c r="M22" s="16"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18"/>
       <c r="O22" s="16"/>
-      <c r="P22" s="16"/>
       <c r="Q22" s="16"/>
       <c r="R22" s="16"/>
       <c r="S22" s="16"/>
@@ -3008,10 +3154,12 @@
       <c r="V22" s="16"/>
       <c r="W22" s="16"/>
       <c r="X22" s="16"/>
-      <c r="Y22" s="18"/>
+      <c r="Y22" s="16"/>
       <c r="Z22" s="16"/>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="18"/>
+      <c r="AB22" s="16"/>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A23" s="16" t="s">
         <v>109</v>
       </c>
@@ -3048,9 +3196,9 @@
       <c r="L23" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M23" s="16"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18"/>
       <c r="O23" s="16"/>
-      <c r="P23" s="16"/>
       <c r="Q23" s="16"/>
       <c r="R23" s="16"/>
       <c r="S23" s="16"/>
@@ -3059,10 +3207,12 @@
       <c r="V23" s="16"/>
       <c r="W23" s="16"/>
       <c r="X23" s="16"/>
-      <c r="Y23" s="18"/>
+      <c r="Y23" s="16"/>
       <c r="Z23" s="16"/>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="18"/>
+      <c r="AB23" s="16"/>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
         <v>111</v>
       </c>
@@ -3099,9 +3249,9 @@
       <c r="L24" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M24" s="16"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18"/>
       <c r="O24" s="16"/>
-      <c r="P24" s="16"/>
       <c r="Q24" s="16"/>
       <c r="R24" s="16"/>
       <c r="S24" s="16"/>
@@ -3110,10 +3260,12 @@
       <c r="V24" s="16"/>
       <c r="W24" s="16"/>
       <c r="X24" s="16"/>
-      <c r="Y24" s="18"/>
+      <c r="Y24" s="16"/>
       <c r="Z24" s="16"/>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="18"/>
+      <c r="AB24" s="16"/>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A25" s="17" t="s">
         <v>82</v>
       </c>
@@ -3129,8 +3281,8 @@
       <c r="K25" s="16"/>
       <c r="L25" s="16"/>
       <c r="M25" s="16"/>
+      <c r="N25" s="16"/>
       <c r="O25" s="16"/>
-      <c r="P25" s="16"/>
       <c r="Q25" s="16"/>
       <c r="R25" s="16"/>
       <c r="S25" s="16"/>
@@ -3141,8 +3293,10 @@
       <c r="X25" s="16"/>
       <c r="Y25" s="16"/>
       <c r="Z25" s="16"/>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="16"/>
+      <c r="AB25" s="16"/>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
         <v>84</v>
       </c>
@@ -3175,21 +3329,23 @@
       <c r="L26" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M26" s="16"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
       <c r="O26" s="16"/>
-      <c r="P26" s="16"/>
-      <c r="Q26" s="18"/>
+      <c r="Q26" s="16"/>
       <c r="R26" s="16"/>
-      <c r="S26" s="16"/>
+      <c r="S26" s="18"/>
       <c r="T26" s="16"/>
-      <c r="U26" s="18"/>
+      <c r="U26" s="16"/>
       <c r="V26" s="16"/>
-      <c r="W26" s="16"/>
+      <c r="W26" s="18"/>
       <c r="X26" s="16"/>
-      <c r="Y26" s="18"/>
+      <c r="Y26" s="16"/>
       <c r="Z26" s="16"/>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="18"/>
+      <c r="AB26" s="16"/>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
         <v>89</v>
       </c>
@@ -3222,21 +3378,23 @@
       <c r="L27" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M27" s="16"/>
+      <c r="M27" s="18"/>
+      <c r="N27" s="18"/>
       <c r="O27" s="16"/>
-      <c r="P27" s="16"/>
-      <c r="Q27" s="18"/>
+      <c r="Q27" s="16"/>
       <c r="R27" s="16"/>
-      <c r="S27" s="16"/>
+      <c r="S27" s="18"/>
       <c r="T27" s="16"/>
-      <c r="U27" s="18"/>
+      <c r="U27" s="16"/>
       <c r="V27" s="16"/>
-      <c r="W27" s="16"/>
+      <c r="W27" s="18"/>
       <c r="X27" s="16"/>
-      <c r="Y27" s="18"/>
+      <c r="Y27" s="16"/>
       <c r="Z27" s="16"/>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="18"/>
+      <c r="AB27" s="16"/>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A28" s="16" t="s">
         <v>93</v>
       </c>
@@ -3271,21 +3429,23 @@
       <c r="L28" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M28" s="16"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18"/>
       <c r="O28" s="16"/>
-      <c r="P28" s="16"/>
       <c r="Q28" s="16"/>
       <c r="R28" s="16"/>
       <c r="S28" s="16"/>
       <c r="T28" s="16"/>
-      <c r="U28" s="18"/>
+      <c r="U28" s="16"/>
       <c r="V28" s="16"/>
-      <c r="W28" s="16"/>
+      <c r="W28" s="18"/>
       <c r="X28" s="16"/>
-      <c r="Y28" s="18"/>
+      <c r="Y28" s="16"/>
       <c r="Z28" s="16"/>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="18"/>
+      <c r="AB28" s="16"/>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A29" s="16" t="s">
         <v>112</v>
       </c>
@@ -3322,9 +3482,9 @@
       <c r="L29" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M29" s="16"/>
+      <c r="M29" s="18"/>
+      <c r="N29" s="18"/>
       <c r="O29" s="16"/>
-      <c r="P29" s="16"/>
       <c r="Q29" s="16"/>
       <c r="R29" s="16"/>
       <c r="S29" s="16"/>
@@ -3333,10 +3493,12 @@
       <c r="V29" s="16"/>
       <c r="W29" s="16"/>
       <c r="X29" s="16"/>
-      <c r="Y29" s="18"/>
+      <c r="Y29" s="16"/>
       <c r="Z29" s="16"/>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="18"/>
+      <c r="AB29" s="16"/>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A30" s="17" t="s">
         <v>83</v>
       </c>
@@ -3352,8 +3514,8 @@
       <c r="K30" s="16"/>
       <c r="L30" s="16"/>
       <c r="M30" s="16"/>
+      <c r="N30" s="16"/>
       <c r="O30" s="16"/>
-      <c r="P30" s="16"/>
       <c r="Q30" s="16"/>
       <c r="R30" s="16"/>
       <c r="S30" s="16"/>
@@ -3364,8 +3526,10 @@
       <c r="X30" s="16"/>
       <c r="Y30" s="16"/>
       <c r="Z30" s="16"/>
-    </row>
-    <row r="31" spans="1:26" ht="17" x14ac:dyDescent="0.25">
+      <c r="AA30" s="16"/>
+      <c r="AB30" s="16"/>
+    </row>
+    <row r="31" spans="1:28" ht="17" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>96</v>
       </c>
@@ -3398,21 +3562,23 @@
       <c r="L31" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M31" s="16"/>
+      <c r="M31" s="18"/>
+      <c r="N31" s="18"/>
       <c r="O31" s="16"/>
-      <c r="P31" s="16"/>
-      <c r="Q31" s="18"/>
+      <c r="Q31" s="16"/>
       <c r="R31" s="16"/>
-      <c r="S31" s="16"/>
+      <c r="S31" s="18"/>
       <c r="T31" s="16"/>
-      <c r="U31" s="18"/>
+      <c r="U31" s="16"/>
       <c r="V31" s="16"/>
-      <c r="W31" s="16"/>
+      <c r="W31" s="18"/>
       <c r="X31" s="16"/>
-      <c r="Y31" s="18"/>
+      <c r="Y31" s="16"/>
       <c r="Z31" s="16"/>
-    </row>
-    <row r="32" spans="1:26" ht="17" x14ac:dyDescent="0.25">
+      <c r="AA31" s="18"/>
+      <c r="AB31" s="16"/>
+    </row>
+    <row r="32" spans="1:28" ht="17" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
         <v>97</v>
       </c>
@@ -3445,21 +3611,23 @@
       <c r="L32" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M32" s="16"/>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18"/>
       <c r="O32" s="16"/>
-      <c r="P32" s="16"/>
-      <c r="Q32" s="18"/>
+      <c r="Q32" s="16"/>
       <c r="R32" s="16"/>
-      <c r="S32" s="16"/>
+      <c r="S32" s="18"/>
       <c r="T32" s="16"/>
-      <c r="U32" s="18"/>
+      <c r="U32" s="16"/>
       <c r="V32" s="16"/>
-      <c r="W32" s="16"/>
+      <c r="W32" s="18"/>
       <c r="X32" s="16"/>
-      <c r="Y32" s="18"/>
+      <c r="Y32" s="16"/>
       <c r="Z32" s="16"/>
-    </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AA32" s="18"/>
+      <c r="AB32" s="16"/>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A33" s="16" t="s">
         <v>84</v>
       </c>
@@ -3492,21 +3660,23 @@
       <c r="L33" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M33" s="16"/>
+      <c r="M33" s="18"/>
+      <c r="N33" s="18"/>
       <c r="O33" s="16"/>
-      <c r="P33" s="16"/>
-      <c r="Q33" s="18"/>
+      <c r="Q33" s="16"/>
       <c r="R33" s="16"/>
-      <c r="S33" s="16"/>
+      <c r="S33" s="18"/>
       <c r="T33" s="16"/>
-      <c r="U33" s="18"/>
+      <c r="U33" s="16"/>
       <c r="V33" s="16"/>
-      <c r="W33" s="16"/>
+      <c r="W33" s="18"/>
       <c r="X33" s="16"/>
-      <c r="Y33" s="18"/>
+      <c r="Y33" s="16"/>
       <c r="Z33" s="16"/>
-    </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AA33" s="18"/>
+      <c r="AB33" s="16"/>
+    </row>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A34" s="16" t="s">
         <v>89</v>
       </c>
@@ -3539,21 +3709,23 @@
       <c r="L34" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M34" s="16"/>
+      <c r="M34" s="18"/>
+      <c r="N34" s="18"/>
       <c r="O34" s="16"/>
-      <c r="P34" s="16"/>
-      <c r="Q34" s="18"/>
+      <c r="Q34" s="16"/>
       <c r="R34" s="16"/>
-      <c r="S34" s="16"/>
+      <c r="S34" s="18"/>
       <c r="T34" s="16"/>
-      <c r="U34" s="18"/>
+      <c r="U34" s="16"/>
       <c r="V34" s="16"/>
-      <c r="W34" s="16"/>
+      <c r="W34" s="18"/>
       <c r="X34" s="16"/>
-      <c r="Y34" s="18"/>
+      <c r="Y34" s="16"/>
       <c r="Z34" s="16"/>
-    </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AA34" s="18"/>
+      <c r="AB34" s="16"/>
+    </row>
+    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A35" s="16" t="s">
         <v>93</v>
       </c>
@@ -3588,21 +3760,23 @@
       <c r="L35" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="M35" s="16"/>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18"/>
       <c r="O35" s="16"/>
-      <c r="P35" s="16"/>
       <c r="Q35" s="16"/>
       <c r="R35" s="16"/>
       <c r="S35" s="16"/>
       <c r="T35" s="16"/>
-      <c r="U35" s="18"/>
+      <c r="U35" s="16"/>
       <c r="V35" s="16"/>
-      <c r="W35" s="16"/>
+      <c r="W35" s="18"/>
       <c r="X35" s="16"/>
-      <c r="Y35" s="18"/>
+      <c r="Y35" s="16"/>
       <c r="Z35" s="16"/>
-    </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AA35" s="18"/>
+      <c r="AB35" s="16"/>
+    </row>
+    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A36" s="16" t="s">
         <v>112</v>
       </c>
@@ -3639,8 +3813,8 @@
       <c r="L36" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="O36" s="16"/>
-      <c r="P36" s="16"/>
+      <c r="M36" s="18"/>
+      <c r="N36" s="18"/>
       <c r="Q36" s="16"/>
       <c r="R36" s="16"/>
       <c r="S36" s="16"/>
@@ -3649,9 +3823,11 @@
       <c r="V36" s="16"/>
       <c r="W36" s="16"/>
       <c r="X36" s="16"/>
-      <c r="Y36" s="18"/>
-    </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="Y36" s="16"/>
+      <c r="Z36" s="16"/>
+      <c r="AA36" s="18"/>
+    </row>
+    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A37" s="21" t="s">
         <v>117</v>
       </c>
@@ -3681,10 +3857,12 @@
       <c r="Y37" s="14"/>
       <c r="Z37" s="14"/>
       <c r="AA37" s="14"/>
-      <c r="AB37" s="16"/>
-      <c r="AC37" s="16"/>
-    </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AB37" s="14"/>
+      <c r="AC37" s="14"/>
+      <c r="AD37" s="16"/>
+      <c r="AE37" s="16"/>
+    </row>
+    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A38" s="15" t="s">
         <v>118</v>
       </c>
@@ -3716,25 +3894,632 @@
       <c r="Y38" s="15"/>
       <c r="Z38" s="15"/>
       <c r="AA38" s="15"/>
-      <c r="AB38" s="16"/>
-      <c r="AC38" s="16"/>
+      <c r="AB38" s="15"/>
+      <c r="AC38" s="15"/>
+      <c r="AD38" s="16"/>
+      <c r="AE38" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B2:O2"/>
     <mergeCell ref="F3:I3"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="O2:Z2"/>
-    <mergeCell ref="O3:R3"/>
-    <mergeCell ref="S3:V3"/>
-    <mergeCell ref="W3:Z3"/>
+    <mergeCell ref="J3:O3"/>
+    <mergeCell ref="Q2:AB2"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="U3:X3"/>
+    <mergeCell ref="Y3:AB3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57A86273-0E84-8246-B3ED-A023C6721217}">
+  <dimension ref="A1:M38"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="11" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="14"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="15"/>
+      <c r="B3" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="G3" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="16"/>
+      <c r="B4" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+    </row>
+    <row r="6" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="16"/>
+    </row>
+    <row r="7" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="33"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="16"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+    </row>
+    <row r="9" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="16"/>
+    </row>
+    <row r="10" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" s="16">
+        <v>2.3919999999999999</v>
+      </c>
+      <c r="C10" s="16"/>
+      <c r="D10" s="18">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="E10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="16"/>
+    </row>
+    <row r="11" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" s="16">
+        <v>0.76400000000000001</v>
+      </c>
+      <c r="C11" s="16"/>
+      <c r="D11" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="16"/>
+    </row>
+    <row r="12" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+      <c r="A12" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="B12" s="34">
+        <v>-4.1000000000000002E-2</v>
+      </c>
+      <c r="C12" s="34"/>
+      <c r="D12" s="35">
+        <v>0.40300000000000002</v>
+      </c>
+      <c r="E12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="16"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="16">
+        <v>0.03</v>
+      </c>
+      <c r="C13" s="16"/>
+      <c r="D13" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="16"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+    </row>
+    <row r="15" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" s="16">
+        <v>3.1</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="16"/>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="16"/>
+    </row>
+    <row r="16" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="16"/>
+    </row>
+    <row r="17" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="16"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" s="16">
+        <v>-7.8E-2</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="16"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" s="16">
+        <v>-1.2E-2</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="16"/>
+    </row>
+    <row r="20" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+      <c r="A20" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="16"/>
+    </row>
+    <row r="21" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="16"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22" s="16">
+        <v>4.7E-2</v>
+      </c>
+      <c r="C22" s="16"/>
+      <c r="D22" s="18">
+        <v>0.51400000000000001</v>
+      </c>
+      <c r="E22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="16"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="16">
+        <v>1.41</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="D23" s="18">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="E23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="16"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="16"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B26" s="16">
+        <v>12.433</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="D26" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="16"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" s="16">
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="C27" s="16"/>
+      <c r="D27" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="16"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B28" s="16">
+        <v>1.83</v>
+      </c>
+      <c r="C28" s="16">
+        <v>0.04</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="16"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="16"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+    </row>
+    <row r="31" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+      <c r="A31" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="16">
+        <v>2199.7800000000002</v>
+      </c>
+      <c r="C31" s="16">
+        <v>74.569999999999993</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="16"/>
+      <c r="G31" s="16"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="18"/>
+      <c r="J31" s="16"/>
+    </row>
+    <row r="32" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+      <c r="A32" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B32" s="16">
+        <v>93.71</v>
+      </c>
+      <c r="C32" s="16">
+        <v>14.08</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="16"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A33" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B33" s="16">
+        <v>0.93400000000000005</v>
+      </c>
+      <c r="C33" s="16"/>
+      <c r="D33" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="16"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A34" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" s="16">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="C34" s="16"/>
+      <c r="D34" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="16"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A35" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="16"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A36" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="18"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="18"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A37" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="16"/>
+      <c r="M37" s="16"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A38" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B38" s="15"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+      <c r="K38" s="15"/>
+      <c r="L38" s="16"/>
+      <c r="M38" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="G3:J3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{540507A6-720C-0B43-804E-087FEE710926}">
   <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -3744,51 +4529,51 @@
     <col min="3" max="3" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:3" s="25" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="25" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="28"/>
-    </row>
-    <row r="3" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
+    <row r="2" spans="1:3" s="25" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="26"/>
+    </row>
+    <row r="3" spans="1:3" s="25" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="26" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28" t="s">
+    <row r="4" spans="1:3" s="25" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="26" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="28"/>
-    </row>
-    <row r="6" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="28"/>
-    </row>
-    <row r="7" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:3" s="27" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="27" t="s">
+    <row r="5" spans="1:3" s="25" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="26"/>
+    </row>
+    <row r="6" spans="1:3" s="25" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="26"/>
+    </row>
+    <row r="7" spans="1:3" s="25" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:3" s="25" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="25" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="28" t="s">
+      <c r="A9" s="26" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="26" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="25" t="s">
         <v>132</v>
       </c>
     </row>
@@ -3829,22 +4614,28 @@
       <c r="A15" t="s">
         <v>135</v>
       </c>
+      <c r="B15">
+        <v>-2.5999999999999999E-2</v>
+      </c>
+      <c r="C15">
+        <v>-8.0000000000000002E-3</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="25" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="26" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="C19" s="25" t="s">
         <v>132</v>
       </c>
     </row>
@@ -3885,10 +4676,42 @@
       <c r="A23" t="s">
         <v>135</v>
       </c>
+      <c r="B23">
+        <v>-3.3000000000000002E-2</v>
+      </c>
+      <c r="C23">
+        <v>-1.4999999999999999E-2</v>
+      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E25" s="27" t="s">
+      <c r="E25" s="25" t="s">
         <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C308E17-D64A-5B49-AF88-4F6C5A914899}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21.5" customWidth="1"/>
+    <col min="2" max="2" width="20.33203125" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="28" x14ac:dyDescent="0.2">
+      <c r="A1" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmoffice-my.sharepoint.com/personal/abrieant_uvm_edu/Documents/OneDrive/Manuscripts/reg report DCN/pubertybrain/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nchaku/Documents/GitHub/pubertybrain/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="154" documentId="13_ncr:1_{1C85D9B2-5526-4A3F-887C-73776185B9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94A72430-9BB9-324F-A298-FFA3802015BD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4204D339-1036-BB4F-81E1-92D258D9859C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2140" windowWidth="28800" windowHeight="15140" activeTab="5" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
+    <workbookView xWindow="320" yWindow="600" windowWidth="28800" windowHeight="15140" activeTab="4" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptive table" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,6 @@
     <sheet name="CortModels" sheetId="6" r:id="rId5"/>
     <sheet name="Youth report PDS" sheetId="9" r:id="rId6"/>
     <sheet name="Indirect effects" sheetId="7" r:id="rId7"/>
-    <sheet name="Corrected ps" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="137">
   <si>
     <t>16.10 (2.98)</t>
   </si>
@@ -670,12 +669,6 @@
     </r>
   </si>
   <si>
-    <t>2.58, 3.81</t>
-  </si>
-  <si>
-    <t>-174.94, -111.08</t>
-  </si>
-  <si>
     <t xml:space="preserve"> wm6 ind intercept ela_plus;</t>
   </si>
   <si>
@@ -721,45 +714,7 @@
     <t>MALE - subcortical</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">p </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>value</t>
-    </r>
-  </si>
-  <si>
     <t>Rank</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">corrected </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">p </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>value</t>
-    </r>
   </si>
   <si>
     <t>Corrected p value</t>
@@ -772,7 +727,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -867,19 +822,6 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -907,7 +849,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -933,22 +875,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -988,26 +919,16 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2125,9 +2046,9 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -2162,77 +2083,77 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="Q2" s="31" t="s">
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="Q2" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="R2" s="31"/>
-      <c r="S2" s="31"/>
-      <c r="T2" s="31"/>
-      <c r="U2" s="31"/>
-      <c r="V2" s="31"/>
-      <c r="W2" s="31"/>
-      <c r="X2" s="31"/>
-      <c r="Y2" s="31"/>
-      <c r="Z2" s="31"/>
-      <c r="AA2" s="31"/>
-      <c r="AB2" s="31"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
+      <c r="U2" s="30"/>
+      <c r="V2" s="30"/>
+      <c r="W2" s="30"/>
+      <c r="X2" s="30"/>
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="30"/>
+      <c r="AA2" s="30"/>
+      <c r="AB2" s="30"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="15"/>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30" t="s">
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30" t="s">
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="K3" s="30"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="30"/>
-      <c r="Q3" s="30" t="s">
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31"/>
+      <c r="Q3" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="R3" s="30"/>
-      <c r="S3" s="30"/>
-      <c r="T3" s="30"/>
-      <c r="U3" s="30" t="s">
+      <c r="R3" s="31"/>
+      <c r="S3" s="31"/>
+      <c r="T3" s="31"/>
+      <c r="U3" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="V3" s="30"/>
-      <c r="W3" s="30"/>
-      <c r="X3" s="30"/>
-      <c r="Y3" s="30" t="s">
+      <c r="V3" s="31"/>
+      <c r="W3" s="31"/>
+      <c r="X3" s="31"/>
+      <c r="Y3" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="Z3" s="30"/>
-      <c r="AA3" s="30"/>
-      <c r="AB3" s="30"/>
+      <c r="Z3" s="31"/>
+      <c r="AA3" s="31"/>
+      <c r="AB3" s="31"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A4" s="16"/>
@@ -2269,11 +2190,11 @@
       <c r="L4" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="M4" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="N4" s="32" t="s">
-        <v>139</v>
+      <c r="M4" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="N4" s="27" t="s">
+        <v>135</v>
       </c>
       <c r="O4" s="17" t="s">
         <v>95</v>
@@ -2351,21 +2272,17 @@
         <v>96</v>
       </c>
       <c r="B6" s="16">
-        <v>576.59</v>
+        <v>12.162000000000001</v>
       </c>
       <c r="C6" s="16">
-        <v>1.07</v>
+        <v>0.20399999999999999</v>
       </c>
       <c r="D6" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E6" s="22"/>
-      <c r="F6" s="16">
-        <v>583.54999999999995</v>
-      </c>
-      <c r="G6" s="16">
-        <v>1.51</v>
-      </c>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
       <c r="H6" s="18" t="s">
         <v>24</v>
       </c>
@@ -2396,21 +2313,17 @@
         <v>97</v>
       </c>
       <c r="B7" s="16">
-        <v>-93.95</v>
+        <v>-9.1289999999999996</v>
       </c>
       <c r="C7" s="16">
-        <v>4.51</v>
+        <v>0.70699999999999996</v>
       </c>
       <c r="D7" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E7" s="22"/>
-      <c r="F7" s="16">
-        <v>-94.05</v>
-      </c>
-      <c r="G7" s="16">
-        <v>4.62</v>
-      </c>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
       <c r="H7" s="18" t="s">
         <v>24</v>
       </c>
@@ -2472,33 +2385,23 @@
         <v>98</v>
       </c>
       <c r="B9" s="16">
-        <v>-143.01</v>
+        <v>-0.312</v>
       </c>
       <c r="C9" s="16">
-        <v>19.41</v>
+        <v>3.9E-2</v>
       </c>
       <c r="D9" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="F9" s="16">
-        <v>-143.01</v>
-      </c>
-      <c r="G9" s="16">
-        <v>19.260000000000002</v>
-      </c>
+      <c r="E9" s="24"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
       <c r="H9" s="18" t="s">
         <v>24</v>
       </c>
       <c r="I9" s="16"/>
-      <c r="J9" s="16">
-        <v>-143.02000000000001</v>
-      </c>
-      <c r="K9" s="16">
-        <v>19.260000000000002</v>
-      </c>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
       <c r="L9" s="18" t="s">
         <v>24</v>
       </c>
@@ -2523,31 +2426,23 @@
         <v>99</v>
       </c>
       <c r="B10" s="16">
-        <v>6.87</v>
+        <v>0.13200000000000001</v>
       </c>
       <c r="C10" s="16">
-        <v>1.0900000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="D10" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E10" s="22"/>
-      <c r="F10" s="16">
-        <v>5.48</v>
-      </c>
-      <c r="G10" s="16">
-        <v>1.05</v>
-      </c>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
       <c r="H10" s="18" t="s">
         <v>24</v>
       </c>
       <c r="I10" s="16"/>
-      <c r="J10" s="16">
-        <v>5.48</v>
-      </c>
-      <c r="K10" s="16">
-        <v>1.05</v>
-      </c>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
       <c r="L10" s="18" t="s">
         <v>24</v>
       </c>
@@ -2572,31 +2467,23 @@
         <v>100</v>
       </c>
       <c r="B11" s="16">
-        <v>1.1499999999999999</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="C11" s="16">
-        <v>0.16</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="D11" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E11" s="22"/>
-      <c r="F11" s="16">
-        <v>0.93</v>
-      </c>
-      <c r="G11" s="16">
-        <v>0.15</v>
-      </c>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
       <c r="H11" s="18" t="s">
         <v>24</v>
       </c>
       <c r="I11" s="16"/>
-      <c r="J11" s="16">
-        <v>0.93</v>
-      </c>
-      <c r="K11" s="16">
-        <v>0.15</v>
-      </c>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
       <c r="L11" s="18" t="s">
         <v>24</v>
       </c>
@@ -2621,31 +2508,23 @@
         <v>101</v>
       </c>
       <c r="B12" s="16">
-        <v>-0.08</v>
+        <v>-5.5E-2</v>
       </c>
       <c r="C12" s="16">
-        <v>0.05</v>
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="D12" s="18">
         <v>0.15</v>
       </c>
       <c r="E12" s="22"/>
-      <c r="F12" s="16">
-        <v>-0.08</v>
-      </c>
-      <c r="G12" s="16">
-        <v>0.05</v>
-      </c>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
       <c r="H12" s="18">
         <v>0.15</v>
       </c>
       <c r="I12" s="16"/>
-      <c r="J12" s="16">
-        <v>-0.08</v>
-      </c>
-      <c r="K12" s="16">
-        <v>0.05</v>
-      </c>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
       <c r="L12" s="18" t="s">
         <v>24</v>
       </c>
@@ -2670,31 +2549,23 @@
         <v>88</v>
       </c>
       <c r="B13" s="16">
-        <v>0.05</v>
+        <v>0.318</v>
       </c>
       <c r="C13" s="16">
-        <v>4.0000000000000001E-3</v>
+        <v>0.02</v>
       </c>
       <c r="D13" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E13" s="22"/>
-      <c r="F13" s="16">
-        <v>0.05</v>
-      </c>
-      <c r="G13" s="16">
-        <v>3.0000000000000001E-3</v>
-      </c>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
       <c r="H13" s="18" t="s">
         <v>24</v>
       </c>
       <c r="I13" s="16"/>
-      <c r="J13" s="16">
-        <v>0.05</v>
-      </c>
-      <c r="K13" s="16">
-        <v>3.0000000000000001E-3</v>
-      </c>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
       <c r="L13" s="18" t="s">
         <v>24</v>
       </c>
@@ -2750,33 +2621,23 @@
         <v>102</v>
       </c>
       <c r="B15" s="16">
-        <v>3.2</v>
+        <v>0.34100000000000003</v>
       </c>
       <c r="C15" s="16">
-        <v>0.37</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="F15" s="16">
-        <v>3.21</v>
-      </c>
-      <c r="G15" s="16">
-        <v>0.38</v>
-      </c>
+      <c r="E15" s="23"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
       <c r="H15" s="18" t="s">
         <v>24</v>
       </c>
       <c r="I15" s="16"/>
-      <c r="J15" s="16">
-        <v>3.2</v>
-      </c>
-      <c r="K15" s="16">
-        <v>0.38</v>
-      </c>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
       <c r="L15" s="18" t="s">
         <v>24</v>
       </c>
@@ -2809,35 +2670,31 @@
       <c r="D16" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F16" s="16">
-        <v>-3.81</v>
-      </c>
-      <c r="G16" s="16">
-        <v>0.56999999999999995</v>
-      </c>
+      <c r="E16" s="22"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
       <c r="H16" s="18" t="s">
         <v>24</v>
       </c>
       <c r="I16" s="16"/>
-      <c r="J16" s="16">
-        <v>-3.82</v>
-      </c>
-      <c r="K16" s="16">
-        <v>0.56999999999999995</v>
-      </c>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
       <c r="L16" s="18" t="s">
         <v>24</v>
       </c>
       <c r="M16" s="18"/>
       <c r="N16" s="18"/>
       <c r="O16" s="16"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
-      <c r="T16" s="16"/>
+      <c r="Q16" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R16" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="S16" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="T16" s="22"/>
       <c r="U16" s="16"/>
       <c r="V16" s="16"/>
       <c r="W16" s="18"/>
@@ -2863,32 +2720,32 @@
       <c r="E17" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="F17" s="16">
-        <v>0.02</v>
-      </c>
-      <c r="G17" s="16">
-        <v>0.22</v>
-      </c>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
       <c r="H17" s="16">
         <v>0.94</v>
       </c>
       <c r="I17" s="16"/>
-      <c r="J17" s="16">
-        <v>0.01</v>
-      </c>
-      <c r="K17" s="16">
-        <v>0.22</v>
-      </c>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
       <c r="L17" s="18">
         <v>0.65</v>
       </c>
       <c r="M17" s="18"/>
       <c r="N17" s="18"/>
       <c r="O17" s="16"/>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="16"/>
-      <c r="S17" s="16"/>
-      <c r="T17" s="16"/>
+      <c r="Q17" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R17" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="S17" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="T17" s="22" t="s">
+        <v>94</v>
+      </c>
       <c r="U17" s="16"/>
       <c r="V17" s="16"/>
       <c r="W17" s="16"/>
@@ -2914,32 +2771,32 @@
       <c r="E18" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="F18" s="16">
-        <v>-0.11</v>
-      </c>
-      <c r="G18" s="16">
-        <v>0.01</v>
-      </c>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
       <c r="H18" s="18" t="s">
         <v>24</v>
       </c>
       <c r="I18" s="16"/>
-      <c r="J18" s="16">
-        <v>-0.11</v>
-      </c>
-      <c r="K18" s="16">
-        <v>0.01</v>
-      </c>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
       <c r="L18" s="18" t="s">
         <v>24</v>
       </c>
       <c r="M18" s="18"/>
       <c r="N18" s="18"/>
       <c r="O18" s="16"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="16"/>
-      <c r="S18" s="16"/>
-      <c r="T18" s="16"/>
+      <c r="Q18" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R18" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="S18" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="T18" s="22" t="s">
+        <v>94</v>
+      </c>
       <c r="U18" s="16"/>
       <c r="V18" s="16"/>
       <c r="W18" s="18"/>
@@ -2965,32 +2822,32 @@
       <c r="E19" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="F19" s="16">
-        <v>-0.02</v>
-      </c>
-      <c r="G19" s="16">
-        <v>2E-3</v>
-      </c>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
       <c r="H19" s="18" t="s">
         <v>24</v>
       </c>
       <c r="I19" s="16"/>
-      <c r="J19" s="16">
-        <v>-0.02</v>
-      </c>
-      <c r="K19" s="16">
-        <v>2E-3</v>
-      </c>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
       <c r="L19" s="18" t="s">
         <v>24</v>
       </c>
       <c r="M19" s="18"/>
       <c r="N19" s="18"/>
       <c r="O19" s="16"/>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="16"/>
-      <c r="S19" s="16"/>
-      <c r="T19" s="16"/>
+      <c r="Q19" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R19" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="S19" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="T19" s="22" t="s">
+        <v>94</v>
+      </c>
       <c r="U19" s="16"/>
       <c r="V19" s="16"/>
       <c r="W19" s="18"/>
@@ -3028,26 +2885,38 @@
       <c r="I20" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="J20" s="16">
-        <v>0.01</v>
-      </c>
-      <c r="K20" s="16">
-        <v>2E-3</v>
-      </c>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
       <c r="L20" s="18" t="s">
         <v>24</v>
       </c>
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
       <c r="O20" s="16"/>
-      <c r="Q20" s="16"/>
-      <c r="R20" s="16"/>
-      <c r="S20" s="16"/>
-      <c r="T20" s="16"/>
-      <c r="U20" s="16"/>
-      <c r="V20" s="16"/>
-      <c r="W20" s="16"/>
-      <c r="X20" s="16"/>
+      <c r="Q20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="S20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="T20" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="U20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="X20" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="Y20" s="16"/>
       <c r="Z20" s="16"/>
       <c r="AA20" s="18"/>
@@ -3081,26 +2950,38 @@
       <c r="I21" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="J21" s="16">
-        <v>-2E-3</v>
-      </c>
-      <c r="K21" s="16">
-        <v>0.01</v>
-      </c>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16"/>
       <c r="L21" s="18">
         <v>0.84</v>
       </c>
       <c r="M21" s="18"/>
       <c r="N21" s="18"/>
       <c r="O21" s="16"/>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="16"/>
-      <c r="S21" s="16"/>
-      <c r="T21" s="16"/>
-      <c r="U21" s="16"/>
-      <c r="V21" s="16"/>
-      <c r="W21" s="16"/>
-      <c r="X21" s="16"/>
+      <c r="Q21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="S21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="T21" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="U21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="X21" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="Y21" s="16"/>
       <c r="Z21" s="16"/>
       <c r="AA21" s="18"/>
@@ -3134,26 +3015,38 @@
       <c r="I22" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="J22" s="16">
-        <v>0.11</v>
-      </c>
-      <c r="K22" s="16">
-        <v>7.0000000000000007E-2</v>
-      </c>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
       <c r="L22" s="18">
         <v>0.14000000000000001</v>
       </c>
       <c r="M22" s="18"/>
       <c r="N22" s="18"/>
       <c r="O22" s="16"/>
-      <c r="Q22" s="16"/>
-      <c r="R22" s="16"/>
-      <c r="S22" s="16"/>
-      <c r="T22" s="16"/>
-      <c r="U22" s="16"/>
-      <c r="V22" s="16"/>
-      <c r="W22" s="16"/>
-      <c r="X22" s="16"/>
+      <c r="Q22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="S22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="T22" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="U22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="X22" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="Y22" s="16"/>
       <c r="Z22" s="16"/>
       <c r="AA22" s="18"/>
@@ -3187,26 +3080,38 @@
       <c r="I23" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="J23" s="16">
-        <v>1.84</v>
-      </c>
-      <c r="K23" s="16">
-        <v>0.41</v>
-      </c>
+      <c r="J23" s="16"/>
+      <c r="K23" s="16"/>
       <c r="L23" s="18" t="s">
         <v>24</v>
       </c>
       <c r="M23" s="18"/>
       <c r="N23" s="18"/>
       <c r="O23" s="16"/>
-      <c r="Q23" s="16"/>
-      <c r="R23" s="16"/>
-      <c r="S23" s="16"/>
-      <c r="T23" s="16"/>
-      <c r="U23" s="16"/>
-      <c r="V23" s="16"/>
-      <c r="W23" s="16"/>
-      <c r="X23" s="16"/>
+      <c r="Q23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="S23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="T23" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="U23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="X23" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="Y23" s="16"/>
       <c r="Z23" s="16"/>
       <c r="AA23" s="18"/>
@@ -3240,26 +3145,38 @@
       <c r="I24" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="J24" s="16">
-        <v>-0.17</v>
-      </c>
-      <c r="K24" s="16">
-        <v>0.04</v>
-      </c>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
       <c r="L24" s="18" t="s">
         <v>24</v>
       </c>
       <c r="M24" s="18"/>
       <c r="N24" s="18"/>
       <c r="O24" s="16"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="16"/>
-      <c r="S24" s="16"/>
-      <c r="T24" s="16"/>
-      <c r="U24" s="16"/>
-      <c r="V24" s="16"/>
-      <c r="W24" s="16"/>
-      <c r="X24" s="16"/>
+      <c r="Q24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="S24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="T24" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="U24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="X24" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="Y24" s="16"/>
       <c r="Z24" s="16"/>
       <c r="AA24" s="18"/>
@@ -3301,31 +3218,23 @@
         <v>84</v>
       </c>
       <c r="B26" s="16">
-        <v>12.02</v>
+        <v>3.7069999999999999</v>
       </c>
       <c r="C26" s="16">
-        <v>0.02</v>
+        <v>6.3E-2</v>
       </c>
       <c r="D26" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E26" s="22"/>
-      <c r="F26" s="16">
-        <v>12.23</v>
-      </c>
-      <c r="G26" s="16">
-        <v>0.04</v>
-      </c>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
       <c r="H26" s="18" t="s">
         <v>24</v>
       </c>
       <c r="I26" s="16"/>
-      <c r="J26" s="16">
-        <v>12.23</v>
-      </c>
-      <c r="K26" s="16">
-        <v>0.04</v>
-      </c>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
       <c r="L26" s="18" t="s">
         <v>24</v>
       </c>
@@ -3350,31 +3259,23 @@
         <v>89</v>
       </c>
       <c r="B27" s="16">
-        <v>0.55000000000000004</v>
+        <v>10.965999999999999</v>
       </c>
       <c r="C27" s="16">
-        <v>3.0000000000000001E-3</v>
+        <v>0.158</v>
       </c>
       <c r="D27" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E27" s="22"/>
-      <c r="F27" s="16">
-        <v>0.59</v>
-      </c>
-      <c r="G27" s="16">
-        <v>0.01</v>
-      </c>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
       <c r="H27" s="18" t="s">
         <v>24</v>
       </c>
       <c r="I27" s="16"/>
-      <c r="J27" s="16">
-        <v>0.59</v>
-      </c>
-      <c r="K27" s="16">
-        <v>0.01</v>
-      </c>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
       <c r="L27" s="18" t="s">
         <v>24</v>
       </c>
@@ -3410,32 +3311,32 @@
       <c r="E28" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="F28" s="16">
-        <v>1.83</v>
-      </c>
-      <c r="G28" s="16">
-        <v>0.04</v>
-      </c>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
       <c r="H28" s="18" t="s">
         <v>24</v>
       </c>
       <c r="I28" s="16"/>
-      <c r="J28" s="16">
-        <v>1.83</v>
-      </c>
-      <c r="K28" s="16">
-        <v>0.04</v>
-      </c>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
       <c r="L28" s="18" t="s">
         <v>24</v>
       </c>
       <c r="M28" s="18"/>
       <c r="N28" s="18"/>
       <c r="O28" s="16"/>
-      <c r="Q28" s="16"/>
-      <c r="R28" s="16"/>
-      <c r="S28" s="16"/>
-      <c r="T28" s="16"/>
+      <c r="Q28" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R28" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="S28" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="T28" s="22" t="s">
+        <v>94</v>
+      </c>
       <c r="U28" s="16"/>
       <c r="V28" s="16"/>
       <c r="W28" s="18"/>
@@ -3473,26 +3374,38 @@
       <c r="I29" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="J29" s="16">
-        <v>10.97</v>
-      </c>
-      <c r="K29" s="16">
-        <v>1.21</v>
-      </c>
+      <c r="J29" s="16"/>
+      <c r="K29" s="16"/>
       <c r="L29" s="18" t="s">
         <v>24</v>
       </c>
       <c r="M29" s="18"/>
       <c r="N29" s="18"/>
       <c r="O29" s="16"/>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="16"/>
-      <c r="S29" s="16"/>
-      <c r="T29" s="16"/>
-      <c r="U29" s="16"/>
-      <c r="V29" s="16"/>
-      <c r="W29" s="16"/>
-      <c r="X29" s="16"/>
+      <c r="Q29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="S29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="T29" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="U29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="X29" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="Y29" s="16"/>
       <c r="Z29" s="16"/>
       <c r="AA29" s="18"/>
@@ -3534,31 +3447,23 @@
         <v>96</v>
       </c>
       <c r="B31" s="16">
-        <v>2247.4699999999998</v>
+        <v>1</v>
       </c>
       <c r="C31" s="16">
-        <v>76.02</v>
+        <v>0</v>
       </c>
       <c r="D31" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E31" s="22"/>
-      <c r="F31" s="16">
-        <v>2200.12</v>
-      </c>
-      <c r="G31" s="16">
-        <v>14.08</v>
-      </c>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
       <c r="H31" s="18" t="s">
         <v>24</v>
       </c>
       <c r="I31" s="16"/>
-      <c r="J31" s="16">
-        <v>2199.7800000000002</v>
-      </c>
-      <c r="K31" s="16">
-        <v>74.569999999999993</v>
-      </c>
+      <c r="J31" s="16"/>
+      <c r="K31" s="16"/>
       <c r="L31" s="18" t="s">
         <v>24</v>
       </c>
@@ -3583,31 +3488,23 @@
         <v>97</v>
       </c>
       <c r="B32" s="16">
-        <v>93.62</v>
+        <v>1</v>
       </c>
       <c r="C32" s="16">
-        <v>14.08</v>
+        <v>0</v>
       </c>
       <c r="D32" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E32" s="22"/>
-      <c r="F32" s="16">
-        <v>93.66</v>
-      </c>
-      <c r="G32" s="16">
-        <v>14.08</v>
-      </c>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
       <c r="H32" s="18" t="s">
         <v>24</v>
       </c>
       <c r="I32" s="16"/>
-      <c r="J32" s="16">
-        <v>93.71</v>
-      </c>
-      <c r="K32" s="16">
-        <v>14.08</v>
-      </c>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16"/>
       <c r="L32" s="18" t="s">
         <v>24</v>
       </c>
@@ -3632,31 +3529,23 @@
         <v>84</v>
       </c>
       <c r="B33" s="16">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="C33" s="16">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="D33" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E33" s="22"/>
-      <c r="F33" s="16">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="G33" s="16">
-        <v>0.03</v>
-      </c>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
       <c r="H33" s="18" t="s">
         <v>24</v>
       </c>
       <c r="I33" s="16"/>
-      <c r="J33" s="16">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="K33" s="16">
-        <v>0.03</v>
-      </c>
+      <c r="J33" s="16"/>
+      <c r="K33" s="16"/>
       <c r="L33" s="18" t="s">
         <v>24</v>
       </c>
@@ -3681,31 +3570,23 @@
         <v>89</v>
       </c>
       <c r="B34" s="16">
-        <v>0.02</v>
+        <v>0.88400000000000001</v>
       </c>
       <c r="C34" s="16">
-        <v>1E-3</v>
+        <v>0.03</v>
       </c>
       <c r="D34" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E34" s="22"/>
-      <c r="F34" s="16">
-        <v>0.02</v>
-      </c>
-      <c r="G34" s="16">
-        <v>1E-3</v>
-      </c>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
       <c r="H34" s="18" t="s">
         <v>24</v>
       </c>
       <c r="I34" s="16"/>
-      <c r="J34" s="16">
-        <v>0.02</v>
-      </c>
-      <c r="K34" s="16">
-        <v>1E-3</v>
-      </c>
+      <c r="J34" s="16"/>
+      <c r="K34" s="16"/>
       <c r="L34" s="18" t="s">
         <v>24</v>
       </c>
@@ -3741,22 +3622,14 @@
       <c r="E35" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="F35" s="16">
-        <v>3.26</v>
-      </c>
-      <c r="G35" s="16">
-        <v>0.13</v>
-      </c>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
       <c r="H35" s="18" t="s">
         <v>24</v>
       </c>
       <c r="I35" s="16"/>
-      <c r="J35" s="16">
-        <v>3.26</v>
-      </c>
-      <c r="K35" s="16">
-        <v>0.13</v>
-      </c>
+      <c r="J35" s="16"/>
+      <c r="K35" s="16"/>
       <c r="L35" s="18" t="s">
         <v>24</v>
       </c>
@@ -3804,12 +3677,8 @@
       <c r="I36" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="J36" s="16">
-        <v>7.64</v>
-      </c>
-      <c r="K36" s="16">
-        <v>0.3</v>
-      </c>
+      <c r="J36" s="16"/>
+      <c r="K36" s="16"/>
       <c r="L36" s="18" t="s">
         <v>24</v>
       </c>
@@ -3934,34 +3803,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="15"/>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="G3" s="30" t="s">
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="G3" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="16"/>
@@ -4007,8 +3876,8 @@
       <c r="A6" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
       <c r="D6" s="18"/>
       <c r="E6" s="16"/>
       <c r="G6" s="16"/>
@@ -4020,8 +3889,8 @@
       <c r="A7" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
       <c r="D7" s="18"/>
       <c r="E7" s="16"/>
       <c r="G7" s="16"/>
@@ -4090,14 +3959,14 @@
       <c r="J11" s="16"/>
     </row>
     <row r="12" spans="1:10" ht="17" x14ac:dyDescent="0.25">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="B12" s="34">
+      <c r="B12" s="28">
         <v>-4.1000000000000002E-2</v>
       </c>
-      <c r="C12" s="34"/>
-      <c r="D12" s="35">
+      <c r="C12" s="28"/>
+      <c r="D12" s="29">
         <v>0.40300000000000002</v>
       </c>
       <c r="E12" s="16"/>
@@ -4531,7 +4400,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="25" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="25" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="25" customFormat="1" x14ac:dyDescent="0.2">
@@ -4539,12 +4408,12 @@
     </row>
     <row r="3" spans="1:3" s="25" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="25" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="26" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="25" customFormat="1" x14ac:dyDescent="0.2">
@@ -4556,30 +4425,30 @@
     <row r="7" spans="1:3" s="25" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:3" s="25" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="25" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="26" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="26" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B11" s="25" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B12">
         <v>-3.4000000000000002E-2</v>
@@ -4590,7 +4459,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B13">
         <v>-2.4E-2</v>
@@ -4601,7 +4470,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B14">
         <v>-2.3E-2</v>
@@ -4612,7 +4481,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B15">
         <v>-2.5999999999999999E-2</v>
@@ -4623,25 +4492,25 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="25" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="26" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B19" s="25" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B20">
         <v>-3.1E-2</v>
@@ -4652,7 +4521,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B21">
         <v>-0.03</v>
@@ -4663,7 +4532,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B22">
         <v>-0.113</v>
@@ -4674,7 +4543,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B23">
         <v>-3.3000000000000002E-2</v>
@@ -4685,33 +4554,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E25" s="25" t="s">
-        <v>134</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C308E17-D64A-5B49-AF88-4F6C5A914899}">
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="21.5" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="28" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="B1" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nchaku/Documents/GitHub/pubertybrain/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nchaku\Documents\GitHub\pubertybrain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4204D339-1036-BB4F-81E1-92D258D9859C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3049B952-14D7-4B8A-9371-24029F884A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="320" yWindow="600" windowWidth="28800" windowHeight="15140" activeTab="4" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptive table" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="137">
   <si>
     <t>16.10 (2.98)</t>
   </si>
@@ -714,13 +714,13 @@
     <t>MALE - subcortical</t>
   </si>
   <si>
-    <t>Rank</t>
-  </si>
-  <si>
-    <t>Corrected p value</t>
-  </si>
-  <si>
     <t>Cortical volume by sex - YOUTH REPORT PDS</t>
+  </si>
+  <si>
+    <t>LLCI</t>
+  </si>
+  <si>
+    <t>ULCI</t>
   </si>
 </sst>
 </file>
@@ -823,7 +823,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -838,18 +838,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -875,11 +869,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -909,27 +914,45 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="11" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="11" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1510,20 +1533,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39987BE7-3659-524A-81AE-D479F97EF698}">
   <dimension ref="A1:F29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="9"/>
       <c r="B2" s="10" t="s">
         <v>63</v>
@@ -1541,7 +1564,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="11" t="s">
         <v>69</v>
@@ -1555,7 +1578,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>60</v>
       </c>
@@ -1565,7 +1588,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>61</v>
       </c>
@@ -1585,7 +1608,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>62</v>
       </c>
@@ -1605,7 +1628,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>58</v>
       </c>
@@ -1625,7 +1648,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>59</v>
       </c>
@@ -1635,7 +1658,7 @@
       <c r="E8" s="12"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>61</v>
       </c>
@@ -1655,7 +1678,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>66</v>
       </c>
@@ -1675,7 +1698,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>67</v>
       </c>
@@ -1695,7 +1718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>62</v>
       </c>
@@ -1715,7 +1738,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>68</v>
       </c>
@@ -1725,7 +1748,7 @@
       <c r="E13" s="12"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>73</v>
       </c>
@@ -1745,7 +1768,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>74</v>
       </c>
@@ -1765,7 +1788,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>75</v>
       </c>
@@ -1785,7 +1808,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>76</v>
       </c>
@@ -1801,9 +1824,9 @@
       <c r="E17" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="20"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F17" s="19"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>71</v>
       </c>
@@ -1813,7 +1836,7 @@
       <c r="E18" s="12"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>61</v>
       </c>
@@ -1833,7 +1856,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>66</v>
       </c>
@@ -1853,7 +1876,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>67</v>
       </c>
@@ -1873,7 +1896,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>62</v>
       </c>
@@ -1893,7 +1916,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>72</v>
       </c>
@@ -1903,7 +1926,7 @@
       <c r="E23" s="12"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>61</v>
       </c>
@@ -1923,7 +1946,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>66</v>
       </c>
@@ -1943,7 +1966,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>67</v>
       </c>
@@ -1963,7 +1986,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>62</v>
       </c>
@@ -1983,7 +2006,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1991,7 +2014,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2007,9 +2030,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A749072B-F938-0F49-BE23-243603B2B3D0}">
   <dimension ref="M2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="13:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M2" t="s">
         <v>113</v>
       </c>
@@ -2023,7 +2046,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45875D41-9C56-AA4E-A18A-2D3A4CE169B3}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2033,7 +2056,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A5153E-6E5C-054A-8ACA-5118463B96C5}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2042,210 +2065,251 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA86F85-A8D4-F648-84C3-730F1A42C846}">
-  <dimension ref="A1:AE38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AM34"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="14.1640625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="2.83203125" style="1" customWidth="1"/>
-    <col min="17" max="17" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="11" style="1"/>
+    <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="6.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="1.125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="0.875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="5.625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="6.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="1" style="33" customWidth="1"/>
+    <col min="26" max="26" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.625" style="1" customWidth="1"/>
+    <col min="29" max="30" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="1.125" style="33" customWidth="1"/>
+    <col min="32" max="32" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="5.625" style="1" customWidth="1"/>
+    <col min="36" max="36" width="6.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="Q2" s="30" t="s">
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="35" t="s">
         <v>115</v>
       </c>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="30"/>
-      <c r="AB2" s="30"/>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A3" s="15"/>
-      <c r="B3" s="31" t="s">
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
+      <c r="AA2" s="35"/>
+      <c r="AB2" s="35"/>
+      <c r="AC2" s="35"/>
+      <c r="AD2" s="35"/>
+      <c r="AE2" s="35"/>
+      <c r="AF2" s="35"/>
+      <c r="AG2" s="35"/>
+      <c r="AH2" s="35"/>
+      <c r="AI2" s="35"/>
+      <c r="AJ2" s="35"/>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A3" s="31"/>
+      <c r="B3" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31" t="s">
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31" t="s">
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="31"/>
-      <c r="N3" s="31"/>
-      <c r="O3" s="31"/>
-      <c r="Q3" s="31" t="s">
+      <c r="O3" s="35"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="35"/>
+      <c r="S3" s="33"/>
+      <c r="T3" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="R3" s="31"/>
-      <c r="S3" s="31"/>
-      <c r="T3" s="31"/>
-      <c r="U3" s="31" t="s">
+      <c r="U3" s="32"/>
+      <c r="V3" s="32"/>
+      <c r="W3" s="32"/>
+      <c r="X3" s="32"/>
+      <c r="Y3" s="37"/>
+      <c r="Z3" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="V3" s="31"/>
-      <c r="W3" s="31"/>
-      <c r="X3" s="31"/>
-      <c r="Y3" s="31" t="s">
+      <c r="AA3" s="35"/>
+      <c r="AB3" s="35"/>
+      <c r="AC3" s="35"/>
+      <c r="AD3" s="35"/>
+      <c r="AE3" s="37"/>
+      <c r="AF3" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="Z3" s="31"/>
-      <c r="AA3" s="31"/>
-      <c r="AB3" s="31"/>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A4" s="16"/>
-      <c r="B4" s="17" t="s">
+      <c r="AG3" s="35"/>
+      <c r="AH3" s="35"/>
+      <c r="AI3" s="35"/>
+      <c r="AJ3" s="35"/>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A4" s="15"/>
+      <c r="B4" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="E4" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="F4" s="17" t="s">
+      <c r="E4" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="I4" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="J4" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="I4" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="J4" s="17" t="s">
+      <c r="K4" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="L4" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="K4" s="17" t="s">
+      <c r="O4" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="L4" s="17" t="s">
+      <c r="P4" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="M4" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="N4" s="27" t="s">
+      <c r="Q4" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="O4" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q4" s="17" t="s">
+      <c r="R4" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="S4" s="6"/>
+      <c r="T4" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="R4" s="17" t="s">
+      <c r="U4" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="S4" s="17" t="s">
+      <c r="V4" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="T4" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="U4" s="17" t="s">
+      <c r="W4" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="X4" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y4" s="34"/>
+      <c r="Z4" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="V4" s="17" t="s">
+      <c r="AA4" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="W4" s="17" t="s">
+      <c r="AB4" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="X4" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="Y4" s="17" t="s">
+      <c r="AC4" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="AD4" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="AE4" s="34"/>
+      <c r="AF4" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="Z4" s="17" t="s">
+      <c r="AG4" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="AA4" s="17" t="s">
+      <c r="AH4" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="AB4" s="17" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AI4" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="AJ4" s="36" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>85</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
       <c r="D5" s="16"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
       <c r="H5" s="16"/>
       <c r="I5" s="16"/>
       <c r="J5" s="16"/>
@@ -2254,20 +2318,28 @@
       <c r="M5" s="16"/>
       <c r="N5" s="16"/>
       <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
       <c r="Q5" s="16"/>
       <c r="R5" s="16"/>
-      <c r="S5" s="16"/>
       <c r="T5" s="16"/>
       <c r="U5" s="16"/>
       <c r="V5" s="16"/>
       <c r="W5" s="16"/>
       <c r="X5" s="16"/>
-      <c r="Y5" s="16"/>
+      <c r="Y5" s="31"/>
       <c r="Z5" s="16"/>
       <c r="AA5" s="16"/>
       <c r="AB5" s="16"/>
-    </row>
-    <row r="6" spans="1:28" ht="17" x14ac:dyDescent="0.25">
+      <c r="AC5" s="16"/>
+      <c r="AD5" s="16"/>
+      <c r="AE5" s="31"/>
+      <c r="AF5" s="16"/>
+      <c r="AG5" s="16"/>
+      <c r="AH5" s="16"/>
+      <c r="AI5" s="16"/>
+      <c r="AJ5" s="16"/>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>96</v>
       </c>
@@ -2280,35 +2352,93 @@
       <c r="D6" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="22"/>
-      <c r="F6" s="16"/>
+      <c r="E6" s="16">
+        <v>11.826000000000001</v>
+      </c>
+      <c r="F6" s="16">
+        <v>12.497999999999999</v>
+      </c>
       <c r="G6" s="16"/>
-      <c r="H6" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="I6" s="16"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="16"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="18"/>
-      <c r="T6" s="16"/>
-      <c r="U6" s="16"/>
-      <c r="V6" s="16"/>
-      <c r="W6" s="18"/>
-      <c r="X6" s="16"/>
-      <c r="Y6" s="16"/>
-      <c r="Z6" s="16"/>
-      <c r="AA6" s="18"/>
-      <c r="AB6" s="16"/>
-    </row>
-    <row r="7" spans="1:28" ht="17" x14ac:dyDescent="0.25">
+      <c r="H6" s="16">
+        <v>12.31</v>
+      </c>
+      <c r="I6" s="16">
+        <v>0.20399999999999999</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="16">
+        <v>11.975</v>
+      </c>
+      <c r="L6" s="16">
+        <v>12.644</v>
+      </c>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16">
+        <v>12.31</v>
+      </c>
+      <c r="O6" s="16">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="P6" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>11.975</v>
+      </c>
+      <c r="R6" s="16">
+        <v>12.645</v>
+      </c>
+      <c r="T6" s="16">
+        <v>11.789</v>
+      </c>
+      <c r="U6" s="16">
+        <v>0.186</v>
+      </c>
+      <c r="V6" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="W6" s="16">
+        <v>11.481999999999999</v>
+      </c>
+      <c r="X6" s="16">
+        <v>12.095000000000001</v>
+      </c>
+      <c r="Y6" s="31"/>
+      <c r="Z6" s="16">
+        <v>11.930999999999999</v>
+      </c>
+      <c r="AA6" s="16">
+        <v>0.185</v>
+      </c>
+      <c r="AB6" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC6" s="16">
+        <v>11.627000000000001</v>
+      </c>
+      <c r="AD6" s="16">
+        <v>12.236000000000001</v>
+      </c>
+      <c r="AE6" s="31"/>
+      <c r="AF6" s="16">
+        <v>11.930999999999999</v>
+      </c>
+      <c r="AG6" s="16">
+        <v>0.185</v>
+      </c>
+      <c r="AH6" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI6" s="16">
+        <v>11.625999999999999</v>
+      </c>
+      <c r="AJ6" s="16">
+        <v>12.236000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>97</v>
       </c>
@@ -2321,1518 +2451,2361 @@
       <c r="D7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="22"/>
-      <c r="F7" s="16"/>
+      <c r="E7" s="16">
+        <v>-10.292</v>
+      </c>
+      <c r="F7" s="16">
+        <v>-7.9649999999999999</v>
+      </c>
       <c r="G7" s="16"/>
-      <c r="H7" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="16"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M7" s="18"/>
-      <c r="N7" s="18"/>
-      <c r="O7" s="16"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="16"/>
-      <c r="S7" s="18"/>
-      <c r="T7" s="16"/>
-      <c r="U7" s="16"/>
-      <c r="V7" s="16"/>
-      <c r="W7" s="18"/>
-      <c r="X7" s="16"/>
-      <c r="Y7" s="16"/>
-      <c r="Z7" s="16"/>
-      <c r="AA7" s="18"/>
-      <c r="AB7" s="16"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A8" s="17" t="s">
-        <v>86</v>
-      </c>
+      <c r="H7" s="16">
+        <v>-9.1370000000000005</v>
+      </c>
+      <c r="I7" s="16">
+        <v>0.71099999999999997</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="16">
+        <v>-10.305999999999999</v>
+      </c>
+      <c r="L7" s="16">
+        <v>-7.968</v>
+      </c>
+      <c r="M7" s="16"/>
+      <c r="N7" s="16">
+        <v>-9.1329999999999991</v>
+      </c>
+      <c r="O7" s="16">
+        <v>0.71</v>
+      </c>
+      <c r="P7" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q7" s="16">
+        <v>-10.301</v>
+      </c>
+      <c r="R7" s="16">
+        <v>-7.9660000000000002</v>
+      </c>
+      <c r="T7" s="16">
+        <v>-8.7789999999999999</v>
+      </c>
+      <c r="U7" s="16">
+        <v>0.63</v>
+      </c>
+      <c r="V7" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="W7" s="16">
+        <v>-9.8160000000000007</v>
+      </c>
+      <c r="X7" s="16">
+        <v>-7.7430000000000003</v>
+      </c>
+      <c r="Y7" s="31"/>
+      <c r="Z7" s="16">
+        <v>-8.8079999999999998</v>
+      </c>
+      <c r="AA7" s="16">
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="AB7" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC7" s="16">
+        <v>-9.8539999999999992</v>
+      </c>
+      <c r="AD7" s="16">
+        <v>-7.7619999999999996</v>
+      </c>
+      <c r="AE7" s="31"/>
+      <c r="AF7" s="16">
+        <v>-8.8030000000000008</v>
+      </c>
+      <c r="AG7" s="16">
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="AH7" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI7" s="16">
+        <v>-9.8490000000000002</v>
+      </c>
+      <c r="AJ7" s="16">
+        <v>-7.7560000000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A8" s="16"/>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
       <c r="H8" s="16"/>
       <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
       <c r="L8" s="16"/>
       <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="Q8" s="16"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="18"/>
       <c r="R8" s="16"/>
-      <c r="S8" s="16"/>
       <c r="T8" s="16"/>
       <c r="U8" s="16"/>
-      <c r="V8" s="16"/>
-      <c r="W8" s="16"/>
-      <c r="X8" s="16"/>
-      <c r="Y8" s="16"/>
+      <c r="V8" s="18"/>
+      <c r="W8" s="18"/>
+      <c r="X8" s="21"/>
+      <c r="Y8" s="39"/>
       <c r="Z8" s="16"/>
       <c r="AA8" s="16"/>
-      <c r="AB8" s="16"/>
-    </row>
-    <row r="9" spans="1:28" ht="17" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B9" s="16">
-        <v>-0.312</v>
-      </c>
-      <c r="C9" s="16">
-        <v>3.9E-2</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" s="24"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="18" t="s">
-        <v>24</v>
-      </c>
+      <c r="AB8" s="18"/>
+      <c r="AC8" s="18"/>
+      <c r="AD8" s="16"/>
+      <c r="AE8" s="31"/>
+      <c r="AF8" s="16"/>
+      <c r="AG8" s="16"/>
+      <c r="AH8" s="18"/>
+      <c r="AI8" s="18"/>
+      <c r="AJ8" s="16"/>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="16"/>
       <c r="I9" s="16"/>
       <c r="J9" s="16"/>
       <c r="K9" s="16"/>
-      <c r="L9" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
       <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
       <c r="Q9" s="16"/>
       <c r="R9" s="16"/>
-      <c r="S9" s="18"/>
       <c r="T9" s="16"/>
       <c r="U9" s="16"/>
       <c r="V9" s="16"/>
-      <c r="W9" s="18"/>
-      <c r="X9" s="16"/>
-      <c r="Y9" s="16"/>
+      <c r="W9" s="16"/>
+      <c r="X9" s="21"/>
+      <c r="Y9" s="39"/>
       <c r="Z9" s="16"/>
-      <c r="AA9" s="18"/>
+      <c r="AA9" s="16"/>
       <c r="AB9" s="16"/>
-    </row>
-    <row r="10" spans="1:28" ht="17" x14ac:dyDescent="0.25">
+      <c r="AC9" s="16"/>
+      <c r="AD9" s="16"/>
+      <c r="AE9" s="31"/>
+      <c r="AF9" s="16"/>
+      <c r="AG9" s="16"/>
+      <c r="AH9" s="16"/>
+      <c r="AI9" s="16"/>
+      <c r="AJ9" s="16"/>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" s="16">
+        <v>-0.312</v>
+      </c>
+      <c r="C10" s="16">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="16">
+        <v>-0.376</v>
+      </c>
+      <c r="F10" s="16">
+        <v>-0.248</v>
+      </c>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16">
+        <v>-0.315</v>
+      </c>
+      <c r="I10" s="16">
+        <v>3.9E-2</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="16">
+        <v>-0.38</v>
+      </c>
+      <c r="L10" s="16">
+        <v>-0.251</v>
+      </c>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16">
+        <v>-0.315</v>
+      </c>
+      <c r="O10" s="16">
+        <v>3.9E-2</v>
+      </c>
+      <c r="P10" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q10" s="16">
+        <v>-0.379</v>
+      </c>
+      <c r="R10" s="16">
+        <v>-0.251</v>
+      </c>
+      <c r="T10" s="16">
+        <v>-0.307</v>
+      </c>
+      <c r="U10" s="16">
+        <v>0.04</v>
+      </c>
+      <c r="V10" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="W10" s="16">
+        <v>-0.373</v>
+      </c>
+      <c r="X10" s="16">
+        <v>-0.24</v>
+      </c>
+      <c r="Y10" s="31"/>
+      <c r="Z10" s="16">
+        <v>-0.30599999999999999</v>
+      </c>
+      <c r="AA10" s="16">
+        <v>0.04</v>
+      </c>
+      <c r="AB10" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC10" s="16">
+        <v>-0.371</v>
+      </c>
+      <c r="AD10" s="16">
+        <v>-0.24099999999999999</v>
+      </c>
+      <c r="AE10" s="31"/>
+      <c r="AF10" s="16">
+        <v>-0.30599999999999999</v>
+      </c>
+      <c r="AG10" s="16">
+        <v>0.04</v>
+      </c>
+      <c r="AH10" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI10" s="16">
+        <v>-0.371</v>
+      </c>
+      <c r="AJ10" s="16">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B11" s="16">
         <v>0.13200000000000001</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C11" s="16">
         <v>0.02</v>
       </c>
-      <c r="D10" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="22"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
-      <c r="K10" s="16"/>
-      <c r="L10" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M10" s="18"/>
-      <c r="N10" s="18"/>
-      <c r="O10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="18"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="16"/>
-      <c r="V10" s="16"/>
-      <c r="W10" s="18"/>
-      <c r="X10" s="16"/>
-      <c r="Y10" s="16"/>
-      <c r="Z10" s="16"/>
-      <c r="AA10" s="18"/>
-      <c r="AB10" s="16"/>
-    </row>
-    <row r="11" spans="1:28" ht="17" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+      <c r="D11" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="16">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="F11" s="16">
+        <v>0.16500000000000001</v>
+      </c>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16">
+        <v>0.108</v>
+      </c>
+      <c r="I11" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" s="16">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="L11" s="16">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16">
+        <v>0.108</v>
+      </c>
+      <c r="O11" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="P11" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q11" s="16">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="R11" s="16">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="T11" s="16">
+        <v>5.5E-2</v>
+      </c>
+      <c r="U11" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="V11" s="18">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="W11" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="X11" s="16">
+        <v>0.09</v>
+      </c>
+      <c r="Y11" s="31"/>
+      <c r="Z11" s="16">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="AA11" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AB11" s="18">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="AC11" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AD11" s="16">
+        <v>0.09</v>
+      </c>
+      <c r="AE11" s="31"/>
+      <c r="AF11" s="16">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="AG11" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AH11" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI11" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AJ11" s="16">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B12" s="16">
         <v>0.16300000000000001</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C12" s="16">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="D11" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="22"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M11" s="18"/>
-      <c r="N11" s="18"/>
-      <c r="O11" s="16"/>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="16"/>
-      <c r="S11" s="18"/>
-      <c r="T11" s="16"/>
-      <c r="U11" s="16"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="18"/>
-      <c r="X11" s="16"/>
-      <c r="Y11" s="16"/>
-      <c r="Z11" s="16"/>
-      <c r="AA11" s="18"/>
-      <c r="AB11" s="16"/>
-    </row>
-    <row r="12" spans="1:28" ht="17" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="D12" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="16">
+        <v>0.128</v>
+      </c>
+      <c r="F12" s="16">
+        <v>0.19700000000000001</v>
+      </c>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="I12" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="16">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="L12" s="16">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16">
+        <v>0.13600000000000001</v>
+      </c>
+      <c r="O12" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="P12" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q12" s="16">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="R12" s="16">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="T12" s="16">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="U12" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="V12" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="W12" s="16">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="X12" s="16">
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="Y12" s="31"/>
+      <c r="Z12" s="16">
+        <v>0.114</v>
+      </c>
+      <c r="AA12" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AB12" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC12" s="16">
+        <v>0.08</v>
+      </c>
+      <c r="AD12" s="16">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="AE12" s="31"/>
+      <c r="AF12" s="16">
+        <v>0.115</v>
+      </c>
+      <c r="AG12" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AH12" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI12" s="16">
+        <v>8.1000000000000003E-2</v>
+      </c>
+      <c r="AJ12" s="16">
+        <v>0.14899999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="B12" s="16">
+      <c r="B13" s="16">
         <v>-5.5E-2</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C13" s="16">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="D12" s="18">
-        <v>0.15</v>
-      </c>
-      <c r="E12" s="22"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="18">
-        <v>0.15</v>
-      </c>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M12" s="18"/>
-      <c r="N12" s="18"/>
-      <c r="O12" s="16"/>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="16"/>
-      <c r="S12" s="18"/>
-      <c r="T12" s="16"/>
-      <c r="U12" s="16"/>
-      <c r="V12" s="16"/>
-      <c r="W12" s="18"/>
-      <c r="X12" s="16"/>
-      <c r="Y12" s="16"/>
-      <c r="Z12" s="16"/>
-      <c r="AA12" s="18"/>
-      <c r="AB12" s="16"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A13" s="16" t="s">
+      <c r="D13" s="16">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="E13" s="16">
+        <v>-0.11700000000000001</v>
+      </c>
+      <c r="F13" s="16">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16">
+        <v>-5.5E-2</v>
+      </c>
+      <c r="I13" s="16">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="J13" s="18">
+        <v>0.151</v>
+      </c>
+      <c r="K13" s="16">
+        <v>-0.11799999999999999</v>
+      </c>
+      <c r="L13" s="16">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16">
+        <v>-5.5E-2</v>
+      </c>
+      <c r="O13" s="16">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="P13" s="18">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="Q13" s="16">
+        <v>-0.11899999999999999</v>
+      </c>
+      <c r="R13" s="16">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="T13" s="16">
+        <v>-3.3000000000000002E-2</v>
+      </c>
+      <c r="U13" s="16">
+        <v>3.9E-2</v>
+      </c>
+      <c r="V13" s="18">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="W13" s="16">
+        <v>-9.8000000000000004E-2</v>
+      </c>
+      <c r="X13" s="16">
+        <v>3.1E-2</v>
+      </c>
+      <c r="Y13" s="31"/>
+      <c r="Z13" s="16">
+        <v>-2.8000000000000001E-2</v>
+      </c>
+      <c r="AA13" s="16">
+        <v>3.9E-2</v>
+      </c>
+      <c r="AB13" s="16">
+        <v>0.46300000000000002</v>
+      </c>
+      <c r="AC13" s="16">
+        <v>-9.1999999999999998E-2</v>
+      </c>
+      <c r="AD13" s="16">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AE13" s="31"/>
+      <c r="AF13" s="16">
+        <v>-2.8000000000000001E-2</v>
+      </c>
+      <c r="AG13" s="16">
+        <v>3.9E-2</v>
+      </c>
+      <c r="AH13" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI13" s="16">
+        <v>-9.1999999999999998E-2</v>
+      </c>
+      <c r="AJ13" s="16">
+        <v>3.5999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B14" s="16">
         <v>0.318</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C14" s="16">
         <v>0.02</v>
       </c>
-      <c r="D13" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="22"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M13" s="18"/>
-      <c r="N13" s="18"/>
-      <c r="O13" s="16"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="18"/>
-      <c r="T13" s="16"/>
-      <c r="U13" s="16"/>
-      <c r="V13" s="16"/>
-      <c r="W13" s="18"/>
-      <c r="X13" s="16"/>
-      <c r="Y13" s="16"/>
-      <c r="Z13" s="16"/>
-      <c r="AA13" s="18"/>
-      <c r="AB13" s="16"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A14" s="17" t="s">
+      <c r="D14" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="16">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="F14" s="16">
+        <v>0.35099999999999998</v>
+      </c>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16">
+        <v>0.28899999999999998</v>
+      </c>
+      <c r="I14" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" s="16">
+        <v>0.255</v>
+      </c>
+      <c r="L14" s="16">
+        <v>0.32300000000000001</v>
+      </c>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16">
+        <v>0.28899999999999998</v>
+      </c>
+      <c r="O14" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="P14" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q14" s="16">
+        <v>0.255</v>
+      </c>
+      <c r="R14" s="16">
+        <v>0.32300000000000001</v>
+      </c>
+      <c r="T14" s="16">
+        <v>0.248</v>
+      </c>
+      <c r="U14" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="V14" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="W14" s="16">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="X14" s="16">
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="Y14" s="31"/>
+      <c r="Z14" s="16">
+        <v>0.252</v>
+      </c>
+      <c r="AA14" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="AB14" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC14" s="16">
+        <v>0.216</v>
+      </c>
+      <c r="AD14" s="16">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="AE14" s="31"/>
+      <c r="AF14" s="16">
+        <v>0.252</v>
+      </c>
+      <c r="AG14" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="AH14" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI14" s="16">
+        <v>0.216</v>
+      </c>
+      <c r="AJ14" s="16">
+        <v>0.28799999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="18"/>
+      <c r="Q15" s="18"/>
+      <c r="R15" s="16"/>
+      <c r="T15" s="16"/>
+      <c r="U15" s="16"/>
+      <c r="V15" s="18"/>
+      <c r="W15" s="18"/>
+      <c r="X15" s="21"/>
+      <c r="Y15" s="39"/>
+      <c r="Z15" s="16"/>
+      <c r="AA15" s="16"/>
+      <c r="AB15" s="18"/>
+      <c r="AC15" s="18"/>
+      <c r="AD15" s="16"/>
+      <c r="AE15" s="31"/>
+      <c r="AF15" s="16"/>
+      <c r="AG15" s="16"/>
+      <c r="AH15" s="18"/>
+      <c r="AI15" s="18"/>
+      <c r="AJ15" s="16"/>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="16"/>
-      <c r="U14" s="16"/>
-      <c r="V14" s="16"/>
-      <c r="W14" s="16"/>
-      <c r="X14" s="16"/>
-      <c r="Y14" s="16"/>
-      <c r="Z14" s="16"/>
-      <c r="AA14" s="16"/>
-      <c r="AB14" s="16"/>
-    </row>
-    <row r="15" spans="1:28" ht="17" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="B15" s="16">
-        <v>0.34100000000000003</v>
-      </c>
-      <c r="C15" s="16">
-        <v>4.2999999999999997E-2</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="23"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-      <c r="K15" s="16"/>
-      <c r="L15" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M15" s="18"/>
-      <c r="N15" s="18"/>
-      <c r="O15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="16"/>
-      <c r="S15" s="18"/>
-      <c r="T15" s="18"/>
-      <c r="U15" s="16"/>
-      <c r="V15" s="16"/>
-      <c r="W15" s="18"/>
-      <c r="X15" s="16"/>
-      <c r="Y15" s="16"/>
-      <c r="Z15" s="16"/>
-      <c r="AA15" s="18"/>
-      <c r="AB15" s="16"/>
-    </row>
-    <row r="16" spans="1:28" ht="17" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E16" s="22"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="18" t="s">
-        <v>24</v>
-      </c>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="16"/>
       <c r="I16" s="16"/>
       <c r="J16" s="16"/>
       <c r="K16" s="16"/>
-      <c r="L16" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M16" s="18"/>
-      <c r="N16" s="18"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
       <c r="O16" s="16"/>
-      <c r="Q16" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="R16" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="S16" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="T16" s="22"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="T16" s="16"/>
       <c r="U16" s="16"/>
       <c r="V16" s="16"/>
-      <c r="W16" s="18"/>
-      <c r="X16" s="16"/>
-      <c r="Y16" s="16"/>
+      <c r="W16" s="16"/>
+      <c r="X16" s="21"/>
+      <c r="Y16" s="39"/>
       <c r="Z16" s="16"/>
-      <c r="AA16" s="18"/>
+      <c r="AA16" s="16"/>
       <c r="AB16" s="16"/>
-    </row>
-    <row r="17" spans="1:28" ht="17" x14ac:dyDescent="0.25">
+      <c r="AC16" s="16"/>
+      <c r="AD16" s="16"/>
+      <c r="AE16" s="31"/>
+      <c r="AF16" s="16"/>
+      <c r="AG16" s="16"/>
+      <c r="AH16" s="16"/>
+      <c r="AI16" s="16"/>
+      <c r="AJ16" s="16"/>
+    </row>
+    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F17" s="16"/>
+        <v>102</v>
+      </c>
+      <c r="B17" s="16">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="C17" s="16">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="16">
+        <v>0.26900000000000002</v>
+      </c>
+      <c r="F17" s="16">
+        <v>0.41199999999999998</v>
+      </c>
       <c r="G17" s="16"/>
       <c r="H17" s="16">
-        <v>0.94</v>
-      </c>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="18">
-        <v>0.65</v>
-      </c>
-      <c r="M17" s="18"/>
-      <c r="N17" s="18"/>
-      <c r="O17" s="16"/>
-      <c r="Q17" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="R17" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="S17" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="T17" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="U17" s="16"/>
-      <c r="V17" s="16"/>
-      <c r="W17" s="16"/>
-      <c r="X17" s="16"/>
-      <c r="Y17" s="16"/>
-      <c r="Z17" s="16"/>
-      <c r="AA17" s="18"/>
-      <c r="AB17" s="16"/>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="I17" s="16">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="J17" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="16">
+        <v>0.27</v>
+      </c>
+      <c r="L17" s="16">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16">
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="O17" s="16">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="P17" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q17" s="16">
+        <v>0.27</v>
+      </c>
+      <c r="R17" s="16">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="T17" s="16">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="U17" s="16">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="V17" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="W17" s="16">
+        <v>0.32300000000000001</v>
+      </c>
+      <c r="X17" s="16">
+        <v>0.443</v>
+      </c>
+      <c r="Y17" s="31"/>
+      <c r="Z17" s="16">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="AA17" s="16">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="AB17" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC17" s="16">
+        <v>0.32300000000000001</v>
+      </c>
+      <c r="AD17" s="16">
+        <v>0.443</v>
+      </c>
+      <c r="AE17" s="31"/>
+      <c r="AF17" s="16">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="AG17" s="16">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="AH17" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI17" s="16">
+        <v>0.32200000000000001</v>
+      </c>
+      <c r="AJ17" s="16">
+        <v>0.443</v>
+      </c>
+    </row>
+    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G18" s="21"/>
+      <c r="H18" s="16">
+        <v>-0.14499999999999999</v>
+      </c>
+      <c r="I18" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="J18" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="16">
+        <v>-0.18099999999999999</v>
+      </c>
+      <c r="L18" s="16">
+        <v>-0.11</v>
+      </c>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16">
+        <v>-0.14599999999999999</v>
+      </c>
+      <c r="O18" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="P18" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q18" s="16">
+        <v>-0.18099999999999999</v>
+      </c>
+      <c r="R18" s="16">
+        <v>-0.11</v>
+      </c>
+      <c r="T18" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U18" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V18" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W18" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X18" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y18" s="39"/>
+      <c r="Z18" s="16">
+        <v>-0.13900000000000001</v>
+      </c>
+      <c r="AA18" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AB18" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC18" s="16">
+        <v>-0.17399999999999999</v>
+      </c>
+      <c r="AD18" s="16">
+        <v>-0.104</v>
+      </c>
+      <c r="AE18" s="31"/>
+      <c r="AF18" s="16">
+        <v>-0.13900000000000001</v>
+      </c>
+      <c r="AG18" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AH18" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI18" s="16">
+        <v>-0.17399999999999999</v>
+      </c>
+      <c r="AJ18" s="16">
+        <v>-0.10299999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A19" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="21"/>
+      <c r="H19" s="22">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="I19" s="22">
+        <v>3.9E-2</v>
+      </c>
+      <c r="J19" s="16">
+        <v>0.93799999999999994</v>
+      </c>
+      <c r="K19" s="16">
+        <v>-6.0999999999999999E-2</v>
+      </c>
+      <c r="L19" s="16">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16">
+        <v>2E-3</v>
+      </c>
+      <c r="O19" s="16">
+        <v>3.9E-2</v>
+      </c>
+      <c r="P19" s="18">
+        <v>0.95199999999999996</v>
+      </c>
+      <c r="Q19" s="16">
+        <v>-6.2E-2</v>
+      </c>
+      <c r="R19" s="16">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="T19" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U19" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V19" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W19" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X19" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y19" s="39"/>
+      <c r="Z19" s="16">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AA19" s="16">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="AB19" s="16">
+        <v>0.54</v>
+      </c>
+      <c r="AC19" s="16">
+        <v>-4.2000000000000003E-2</v>
+      </c>
+      <c r="AD19" s="16">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="AE19" s="31"/>
+      <c r="AF19" s="16">
+        <v>2.4E-2</v>
+      </c>
+      <c r="AG19" s="16">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="AH19" s="16">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="AI19" s="16">
+        <v>-4.2999999999999997E-2</v>
+      </c>
+      <c r="AJ19" s="40">
+        <v>9.0999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A20" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="B18" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M18" s="18"/>
-      <c r="N18" s="18"/>
-      <c r="O18" s="16"/>
-      <c r="Q18" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="R18" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="S18" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="T18" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="U18" s="16"/>
-      <c r="V18" s="16"/>
-      <c r="W18" s="18"/>
-      <c r="X18" s="16"/>
-      <c r="Y18" s="16"/>
-      <c r="Z18" s="16"/>
-      <c r="AA18" s="18"/>
-      <c r="AB18" s="16"/>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A19" s="16" t="s">
+      <c r="B20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G20" s="21"/>
+      <c r="H20" s="16">
+        <v>-0.185</v>
+      </c>
+      <c r="I20" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="J20" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="16">
+        <v>-0.22</v>
+      </c>
+      <c r="L20" s="16">
+        <v>-0.15</v>
+      </c>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16">
+        <v>-0.185</v>
+      </c>
+      <c r="O20" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="P20" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q20" s="16">
+        <v>-0.22</v>
+      </c>
+      <c r="R20" s="16">
+        <v>-0.15</v>
+      </c>
+      <c r="T20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W20" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X20" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y20" s="39"/>
+      <c r="Z20" s="16">
+        <v>-0.17</v>
+      </c>
+      <c r="AA20" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AB20" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC20" s="16">
+        <v>-3.6999999999999998E-2</v>
+      </c>
+      <c r="AD20" s="16">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="AE20" s="31"/>
+      <c r="AF20" s="16">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="AG20" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AH20" s="16">
+        <v>0.879</v>
+      </c>
+      <c r="AI20" s="16">
+        <v>-3.7999999999999999E-2</v>
+      </c>
+      <c r="AJ20" s="16">
+        <v>3.1E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="B19" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
-      <c r="L19" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M19" s="18"/>
-      <c r="N19" s="18"/>
-      <c r="O19" s="16"/>
-      <c r="Q19" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="R19" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="S19" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="T19" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="U19" s="16"/>
-      <c r="V19" s="16"/>
-      <c r="W19" s="18"/>
-      <c r="X19" s="16"/>
-      <c r="Y19" s="16"/>
-      <c r="Z19" s="16"/>
-      <c r="AA19" s="18"/>
-      <c r="AB19" s="16"/>
-    </row>
-    <row r="20" spans="1:28" ht="17" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
+      <c r="B21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G21" s="21"/>
+      <c r="H21" s="16">
+        <v>-0.218</v>
+      </c>
+      <c r="I21" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K21" s="16">
+        <v>-0.255</v>
+      </c>
+      <c r="L21" s="16">
+        <v>-0.182</v>
+      </c>
+      <c r="M21" s="16"/>
+      <c r="N21" s="16">
+        <v>-0.219</v>
+      </c>
+      <c r="O21" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="P21" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q21" s="16">
+        <v>-0.255</v>
+      </c>
+      <c r="R21" s="16">
+        <v>-0.183</v>
+      </c>
+      <c r="T21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W21" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X21" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y21" s="39"/>
+      <c r="Z21" s="16">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="AA21" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AB21" s="16">
+        <v>0.9</v>
+      </c>
+      <c r="AC21" s="16">
+        <v>-0.20399999999999999</v>
+      </c>
+      <c r="AD21" s="16">
+        <v>-0.13600000000000001</v>
+      </c>
+      <c r="AE21" s="31"/>
+      <c r="AF21" s="16">
+        <v>-0.17100000000000001</v>
+      </c>
+      <c r="AG21" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AH21" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI21" s="16">
+        <v>-0.20499999999999999</v>
+      </c>
+      <c r="AJ21" s="16">
+        <v>-0.13600000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="G20" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="J20" s="16"/>
-      <c r="K20" s="16"/>
-      <c r="L20" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M20" s="18"/>
-      <c r="N20" s="18"/>
-      <c r="O20" s="16"/>
-      <c r="Q20" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="R20" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="S20" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="T20" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="U20" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="V20" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="W20" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="X20" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y20" s="16"/>
-      <c r="Z20" s="16"/>
-      <c r="AA20" s="18"/>
-      <c r="AB20" s="16"/>
-    </row>
-    <row r="21" spans="1:28" ht="17" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+      <c r="B22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G22" s="21"/>
+      <c r="H22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="M22" s="16"/>
+      <c r="N22" s="16">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="O22" s="16">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="P22" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q22" s="16">
+        <v>0.124</v>
+      </c>
+      <c r="R22" s="16">
+        <v>0.21099999999999999</v>
+      </c>
+      <c r="T22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W22" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X22" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y22" s="39"/>
+      <c r="Z22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC22" s="16"/>
+      <c r="AD22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE22" s="31"/>
+      <c r="AF22" s="16">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="AG22" s="16">
+        <v>2.3E-2</v>
+      </c>
+      <c r="AH22" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI22" s="16">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="AJ22" s="16">
+        <v>0.156</v>
+      </c>
+    </row>
+    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A23" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="G21" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I21" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="18">
-        <v>0.84</v>
-      </c>
-      <c r="M21" s="18"/>
-      <c r="N21" s="18"/>
-      <c r="O21" s="16"/>
-      <c r="Q21" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="R21" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="S21" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="T21" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="U21" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="V21" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="W21" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="X21" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y21" s="16"/>
-      <c r="Z21" s="16"/>
-      <c r="AA21" s="18"/>
-      <c r="AB21" s="16"/>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A22" s="16" t="s">
+      <c r="B23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G23" s="21"/>
+      <c r="H23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="M23" s="16"/>
+      <c r="N23" s="16">
+        <v>-8.9999999999999993E-3</v>
+      </c>
+      <c r="O23" s="16">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="P23" s="18">
+        <v>0.83899999999999997</v>
+      </c>
+      <c r="Q23" s="16">
+        <v>-8.1000000000000003E-2</v>
+      </c>
+      <c r="R23" s="16">
+        <v>6.3E-2</v>
+      </c>
+      <c r="T23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W23" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X23" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y23" s="39"/>
+      <c r="Z23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC23" s="16"/>
+      <c r="AD23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE23" s="31"/>
+      <c r="AF23" s="16">
+        <v>-8.8999999999999996E-2</v>
+      </c>
+      <c r="AG23" s="16">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="AH23" s="16">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="AI23" s="16">
+        <v>-0.16200000000000001</v>
+      </c>
+      <c r="AJ23" s="16">
+        <v>-1.6E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A24" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="B22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="G22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="H22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="J22" s="16"/>
-      <c r="K22" s="16"/>
-      <c r="L22" s="18">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="M22" s="18"/>
-      <c r="N22" s="18"/>
-      <c r="O22" s="16"/>
-      <c r="Q22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="R22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="S22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="T22" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="U22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="V22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="W22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="X22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y22" s="16"/>
-      <c r="Z22" s="16"/>
-      <c r="AA22" s="18"/>
-      <c r="AB22" s="16"/>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A23" s="16" t="s">
+      <c r="B24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G24" s="21"/>
+      <c r="H24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="M24" s="16"/>
+      <c r="N24" s="16">
+        <v>0.04</v>
+      </c>
+      <c r="O24" s="16">
+        <v>2.7E-2</v>
+      </c>
+      <c r="P24" s="18">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="Q24" s="16">
+        <v>-5.0000000000000001E-3</v>
+      </c>
+      <c r="R24" s="16">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="T24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W24" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X24" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y24" s="39"/>
+      <c r="Z24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC24" s="16"/>
+      <c r="AD24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE24" s="31"/>
+      <c r="AF24" s="16">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="AG24" s="16">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="AH24" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI24" s="16">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="AJ24" s="16">
+        <v>0.112</v>
+      </c>
+    </row>
+    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A25" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="B23" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="G23" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="H23" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I23" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="J23" s="16"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M23" s="18"/>
-      <c r="N23" s="18"/>
-      <c r="O23" s="16"/>
-      <c r="Q23" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="R23" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="S23" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="T23" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="U23" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="V23" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="W23" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="X23" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y23" s="16"/>
-      <c r="Z23" s="16"/>
-      <c r="AA23" s="18"/>
-      <c r="AB23" s="16"/>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A24" s="16" t="s">
+      <c r="B25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G25" s="21"/>
+      <c r="H25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="M25" s="16"/>
+      <c r="N25" s="16">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="O25" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="P25" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q25" s="16">
+        <v>0.06</v>
+      </c>
+      <c r="R25" s="16">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="T25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W25" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X25" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y25" s="39"/>
+      <c r="Z25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC25" s="16"/>
+      <c r="AD25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE25" s="31"/>
+      <c r="AF25" s="16">
+        <v>0.125</v>
+      </c>
+      <c r="AG25" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AH25" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="AI25" s="16">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="AJ25" s="16">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="B24" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="G24" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="H24" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I24" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M24" s="18"/>
-      <c r="N24" s="18"/>
-      <c r="O24" s="16"/>
-      <c r="Q24" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="R24" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="S24" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="T24" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="U24" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="V24" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="W24" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="X24" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y24" s="16"/>
-      <c r="Z24" s="16"/>
-      <c r="AA24" s="18"/>
-      <c r="AB24" s="16"/>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A25" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="16"/>
-      <c r="O25" s="16"/>
-      <c r="Q25" s="16"/>
-      <c r="R25" s="16"/>
-      <c r="S25" s="16"/>
-      <c r="T25" s="16"/>
-      <c r="U25" s="16"/>
-      <c r="V25" s="16"/>
-      <c r="W25" s="16"/>
-      <c r="X25" s="16"/>
-      <c r="Y25" s="16"/>
-      <c r="Z25" s="16"/>
-      <c r="AA25" s="16"/>
-      <c r="AB25" s="16"/>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A26" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B26" s="16">
-        <v>3.7069999999999999</v>
-      </c>
-      <c r="C26" s="16">
-        <v>6.3E-2</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="22"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M26" s="18"/>
-      <c r="N26" s="18"/>
-      <c r="O26" s="16"/>
-      <c r="Q26" s="16"/>
-      <c r="R26" s="16"/>
-      <c r="S26" s="18"/>
-      <c r="T26" s="16"/>
-      <c r="U26" s="16"/>
-      <c r="V26" s="16"/>
-      <c r="W26" s="18"/>
-      <c r="X26" s="16"/>
-      <c r="Y26" s="16"/>
-      <c r="Z26" s="16"/>
-      <c r="AA26" s="18"/>
-      <c r="AB26" s="16"/>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A27" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B27" s="16">
-        <v>10.965999999999999</v>
-      </c>
-      <c r="C27" s="16">
-        <v>0.158</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="22"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="18" t="s">
-        <v>24</v>
-      </c>
+      <c r="B26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G26" s="21"/>
+      <c r="H26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="M26" s="16"/>
+      <c r="N26" s="16">
+        <v>-0.108</v>
+      </c>
+      <c r="O26" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="P26" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q26" s="16">
+        <v>-0.14299999999999999</v>
+      </c>
+      <c r="R26" s="16">
+        <v>-7.1999999999999995E-2</v>
+      </c>
+      <c r="T26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W26" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X26" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y26" s="39"/>
+      <c r="Z26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC26" s="16"/>
+      <c r="AD26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE26" s="31"/>
+      <c r="AF26" s="16">
+        <v>-8.3000000000000004E-2</v>
+      </c>
+      <c r="AG26" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AH26" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI26" s="16">
+        <v>-0.11700000000000001</v>
+      </c>
+      <c r="AJ26" s="16">
+        <v>-4.9000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="16"/>
       <c r="I27" s="16"/>
       <c r="J27" s="16"/>
       <c r="K27" s="16"/>
-      <c r="L27" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M27" s="18"/>
-      <c r="N27" s="18"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
+      <c r="N27" s="16"/>
       <c r="O27" s="16"/>
-      <c r="Q27" s="16"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="18"/>
       <c r="R27" s="16"/>
-      <c r="S27" s="18"/>
       <c r="T27" s="16"/>
       <c r="U27" s="16"/>
       <c r="V27" s="16"/>
-      <c r="W27" s="18"/>
-      <c r="X27" s="16"/>
-      <c r="Y27" s="16"/>
+      <c r="W27" s="16"/>
+      <c r="X27" s="21"/>
+      <c r="Y27" s="39"/>
       <c r="Z27" s="16"/>
-      <c r="AA27" s="18"/>
+      <c r="AA27" s="16"/>
       <c r="AB27" s="16"/>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A28" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="18" t="s">
-        <v>24</v>
-      </c>
+      <c r="AC27" s="16"/>
+      <c r="AD27" s="16"/>
+      <c r="AE27" s="31"/>
+      <c r="AF27" s="16"/>
+      <c r="AG27" s="16"/>
+      <c r="AH27" s="18"/>
+      <c r="AI27" s="18"/>
+      <c r="AJ27" s="16"/>
+    </row>
+    <row r="28" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A28" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="16"/>
       <c r="I28" s="16"/>
       <c r="J28" s="16"/>
       <c r="K28" s="16"/>
-      <c r="L28" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M28" s="18"/>
-      <c r="N28" s="18"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
       <c r="O28" s="16"/>
-      <c r="Q28" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="R28" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="S28" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="T28" s="22" t="s">
-        <v>94</v>
-      </c>
+      <c r="P28" s="16"/>
+      <c r="Q28" s="16"/>
+      <c r="R28" s="16"/>
+      <c r="T28" s="16"/>
       <c r="U28" s="16"/>
       <c r="V28" s="16"/>
-      <c r="W28" s="18"/>
-      <c r="X28" s="16"/>
-      <c r="Y28" s="16"/>
+      <c r="W28" s="16"/>
+      <c r="X28" s="21"/>
+      <c r="Y28" s="39"/>
       <c r="Z28" s="16"/>
-      <c r="AA28" s="18"/>
+      <c r="AA28" s="16"/>
       <c r="AB28" s="16"/>
-    </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="16"/>
+      <c r="AD28" s="16"/>
+      <c r="AE28" s="31"/>
+      <c r="AF28" s="16"/>
+      <c r="AG28" s="16"/>
+      <c r="AH28" s="16"/>
+      <c r="AI28" s="16"/>
+      <c r="AJ28" s="16"/>
+    </row>
+    <row r="29" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="16">
+        <v>10.965999999999999</v>
+      </c>
+      <c r="C29" s="16">
+        <v>0.158</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="16">
+        <v>10.706</v>
+      </c>
+      <c r="F29" s="16">
+        <v>11.225</v>
+      </c>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16">
+        <v>11.154</v>
+      </c>
+      <c r="I29" s="16">
+        <v>0.158</v>
+      </c>
+      <c r="J29" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K29" s="16">
+        <v>10.895</v>
+      </c>
+      <c r="L29" s="16">
+        <v>11.413</v>
+      </c>
+      <c r="M29" s="16"/>
+      <c r="N29" s="16">
+        <v>11.154</v>
+      </c>
+      <c r="O29" s="16">
+        <v>0.158</v>
+      </c>
+      <c r="P29" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q29" s="16">
+        <v>10.895</v>
+      </c>
+      <c r="R29" s="16">
+        <v>11.413</v>
+      </c>
+      <c r="T29" s="16">
+        <v>13.83</v>
+      </c>
+      <c r="U29" s="16">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="V29" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="W29" s="16">
+        <v>13.499000000000001</v>
+      </c>
+      <c r="X29" s="16">
+        <v>14.16</v>
+      </c>
+      <c r="Y29" s="31"/>
+      <c r="Z29" s="16">
+        <v>13.832000000000001</v>
+      </c>
+      <c r="AA29" s="16">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="AB29" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC29" s="16">
+        <v>13.499000000000001</v>
+      </c>
+      <c r="AD29" s="16">
+        <v>14.164999999999999</v>
+      </c>
+      <c r="AE29" s="31"/>
+      <c r="AF29" s="16">
+        <v>13.832000000000001</v>
+      </c>
+      <c r="AG29" s="16">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="AH29" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI29" s="16">
+        <v>13.5</v>
+      </c>
+      <c r="AJ29" s="16">
+        <v>14.164999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A30" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" s="16">
+        <v>3.7069999999999999</v>
+      </c>
+      <c r="C30" s="16">
+        <v>6.3E-2</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="16">
+        <v>3.6030000000000002</v>
+      </c>
+      <c r="F30" s="16">
+        <v>3.81</v>
+      </c>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16">
+        <v>3.9260000000000002</v>
+      </c>
+      <c r="I30" s="16">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="J30" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K30" s="16">
+        <v>3.819</v>
+      </c>
+      <c r="L30" s="16">
+        <v>4.0330000000000004</v>
+      </c>
+      <c r="M30" s="16"/>
+      <c r="N30" s="16">
+        <v>3.927</v>
+      </c>
+      <c r="O30" s="16">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P30" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q30" s="16">
+        <v>3.82</v>
+      </c>
+      <c r="R30" s="16">
+        <v>4.0339999999999998</v>
+      </c>
+      <c r="T30" s="16">
+        <v>3.8879999999999999</v>
+      </c>
+      <c r="U30" s="16">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="V30" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="W30" s="16">
+        <v>3.7839999999999998</v>
+      </c>
+      <c r="X30" s="16">
+        <v>3.992</v>
+      </c>
+      <c r="Y30" s="31"/>
+      <c r="Z30" s="16">
+        <v>4.0620000000000003</v>
+      </c>
+      <c r="AA30" s="16">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="AB30" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC30" s="16">
+        <v>3.956</v>
+      </c>
+      <c r="AD30" s="16">
+        <v>4.1669999999999998</v>
+      </c>
+      <c r="AE30" s="31"/>
+      <c r="AF30" s="16">
+        <v>4.0609999999999999</v>
+      </c>
+      <c r="AG30" s="16">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="AH30" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI30" s="16">
+        <v>3.9550000000000001</v>
+      </c>
+      <c r="AJ30" s="16">
+        <v>4.1660000000000004</v>
+      </c>
+    </row>
+    <row r="31" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A31" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F31" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G31" s="21"/>
+      <c r="H31" s="16">
+        <v>1.014</v>
+      </c>
+      <c r="I31" s="16">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="J31" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K31" s="16">
+        <v>0.98499999999999999</v>
+      </c>
+      <c r="L31" s="16">
+        <v>1.044</v>
+      </c>
+      <c r="M31" s="16"/>
+      <c r="N31" s="16">
+        <v>1.014</v>
+      </c>
+      <c r="O31" s="16">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="P31" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q31" s="16">
+        <v>0.98499999999999999</v>
+      </c>
+      <c r="R31" s="16">
+        <v>1.0429999999999999</v>
+      </c>
+      <c r="T31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="X31" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y31" s="39"/>
+      <c r="Z31" s="16">
+        <v>1.026</v>
+      </c>
+      <c r="AA31" s="16">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="AB31" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC31" s="16">
+        <v>0.998</v>
+      </c>
+      <c r="AD31" s="16">
+        <v>1.0549999999999999</v>
+      </c>
+      <c r="AE31" s="31"/>
+      <c r="AF31" s="16">
+        <v>1.0269999999999999</v>
+      </c>
+      <c r="AG31" s="16">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="AH31" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI31" s="16">
+        <v>0.999</v>
+      </c>
+      <c r="AJ31" s="16">
+        <v>1.0549999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A32" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="B29" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E29" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F29" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="G29" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="H29" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I29" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="J29" s="16"/>
-      <c r="K29" s="16"/>
-      <c r="L29" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M29" s="18"/>
-      <c r="N29" s="18"/>
-      <c r="O29" s="16"/>
-      <c r="Q29" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="R29" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="S29" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="T29" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="U29" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="V29" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="W29" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="X29" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y29" s="16"/>
-      <c r="Z29" s="16"/>
-      <c r="AA29" s="18"/>
-      <c r="AB29" s="16"/>
-    </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A30" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="16"/>
-      <c r="O30" s="16"/>
-      <c r="Q30" s="16"/>
-      <c r="R30" s="16"/>
-      <c r="S30" s="16"/>
-      <c r="T30" s="16"/>
-      <c r="U30" s="16"/>
-      <c r="V30" s="16"/>
-      <c r="W30" s="16"/>
-      <c r="X30" s="16"/>
-      <c r="Y30" s="16"/>
-      <c r="Z30" s="16"/>
-      <c r="AA30" s="16"/>
-      <c r="AB30" s="16"/>
-    </row>
-    <row r="31" spans="1:28" ht="17" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B31" s="16">
-        <v>1</v>
-      </c>
-      <c r="C31" s="16">
-        <v>0</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="22"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M31" s="18"/>
-      <c r="N31" s="18"/>
-      <c r="O31" s="16"/>
-      <c r="Q31" s="16"/>
-      <c r="R31" s="16"/>
-      <c r="S31" s="18"/>
-      <c r="T31" s="16"/>
-      <c r="U31" s="16"/>
-      <c r="V31" s="16"/>
-      <c r="W31" s="18"/>
-      <c r="X31" s="16"/>
-      <c r="Y31" s="16"/>
-      <c r="Z31" s="16"/>
-      <c r="AA31" s="18"/>
-      <c r="AB31" s="16"/>
-    </row>
-    <row r="32" spans="1:28" ht="17" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B32" s="16">
-        <v>1</v>
-      </c>
-      <c r="C32" s="16">
-        <v>0</v>
-      </c>
-      <c r="D32" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="22"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
+      <c r="B32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G32" s="39"/>
+      <c r="H32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J32" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="K32" s="16"/>
-      <c r="L32" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M32" s="18"/>
-      <c r="N32" s="18"/>
-      <c r="O32" s="16"/>
-      <c r="Q32" s="16"/>
-      <c r="R32" s="16"/>
-      <c r="S32" s="18"/>
-      <c r="T32" s="16"/>
-      <c r="U32" s="16"/>
-      <c r="V32" s="16"/>
-      <c r="W32" s="18"/>
-      <c r="X32" s="16"/>
-      <c r="Y32" s="16"/>
-      <c r="Z32" s="16"/>
-      <c r="AA32" s="18"/>
-      <c r="AB32" s="16"/>
-    </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A33" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B33" s="16">
-        <v>1</v>
-      </c>
-      <c r="C33" s="16">
-        <v>0</v>
-      </c>
-      <c r="D33" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="22"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="I33" s="16"/>
-      <c r="J33" s="16"/>
-      <c r="K33" s="16"/>
-      <c r="L33" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M33" s="18"/>
-      <c r="N33" s="18"/>
-      <c r="O33" s="16"/>
-      <c r="Q33" s="16"/>
-      <c r="R33" s="16"/>
-      <c r="S33" s="18"/>
-      <c r="T33" s="16"/>
-      <c r="U33" s="16"/>
-      <c r="V33" s="16"/>
-      <c r="W33" s="18"/>
-      <c r="X33" s="16"/>
-      <c r="Y33" s="16"/>
-      <c r="Z33" s="16"/>
-      <c r="AA33" s="18"/>
-      <c r="AB33" s="16"/>
-    </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A34" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B34" s="16">
-        <v>0.88400000000000001</v>
-      </c>
-      <c r="C34" s="16">
-        <v>0.03</v>
-      </c>
-      <c r="D34" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="22"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="I34" s="16"/>
-      <c r="J34" s="16"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M34" s="18"/>
-      <c r="N34" s="18"/>
-      <c r="O34" s="16"/>
-      <c r="Q34" s="16"/>
-      <c r="R34" s="16"/>
-      <c r="S34" s="18"/>
-      <c r="T34" s="16"/>
-      <c r="U34" s="16"/>
-      <c r="V34" s="16"/>
-      <c r="W34" s="18"/>
-      <c r="X34" s="16"/>
-      <c r="Y34" s="16"/>
-      <c r="Z34" s="16"/>
-      <c r="AA34" s="18"/>
-      <c r="AB34" s="16"/>
-    </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A35" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D35" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E35" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="I35" s="16"/>
-      <c r="J35" s="16"/>
-      <c r="K35" s="16"/>
-      <c r="L35" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M35" s="18"/>
-      <c r="N35" s="18"/>
-      <c r="O35" s="16"/>
-      <c r="Q35" s="16"/>
-      <c r="R35" s="16"/>
-      <c r="S35" s="16"/>
-      <c r="T35" s="16"/>
-      <c r="U35" s="16"/>
-      <c r="V35" s="16"/>
-      <c r="W35" s="18"/>
-      <c r="X35" s="16"/>
-      <c r="Y35" s="16"/>
-      <c r="Z35" s="16"/>
-      <c r="AA35" s="18"/>
-      <c r="AB35" s="16"/>
-    </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A36" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D36" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>94</v>
-      </c>
-      <c r="F36" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="G36" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="H36" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I36" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="M36" s="18"/>
-      <c r="N36" s="18"/>
-      <c r="Q36" s="16"/>
-      <c r="R36" s="16"/>
-      <c r="S36" s="16"/>
-      <c r="T36" s="16"/>
-      <c r="U36" s="16"/>
-      <c r="V36" s="16"/>
-      <c r="W36" s="16"/>
-      <c r="X36" s="16"/>
-      <c r="Y36" s="16"/>
-      <c r="Z36" s="16"/>
-      <c r="AA36" s="18"/>
-    </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A37" s="21" t="s">
+      <c r="L32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="M32" s="31"/>
+      <c r="N32" s="16">
+        <v>3.8239999999999998</v>
+      </c>
+      <c r="O32" s="16">
+        <v>0.436</v>
+      </c>
+      <c r="P32" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q32" s="16">
+        <v>3.1070000000000002</v>
+      </c>
+      <c r="R32" s="16">
+        <v>4.5410000000000004</v>
+      </c>
+      <c r="S32" s="33"/>
+      <c r="T32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W32" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X32" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y32" s="39"/>
+      <c r="Z32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC32" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD32" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE32" s="31"/>
+      <c r="AF32" s="16">
+        <v>3.387</v>
+      </c>
+      <c r="AG32" s="16">
+        <v>0.495</v>
+      </c>
+      <c r="AH32" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI32" s="16">
+        <v>2.573</v>
+      </c>
+      <c r="AJ32" s="16">
+        <v>4.202</v>
+      </c>
+      <c r="AK32" s="33"/>
+    </row>
+    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A33" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="14"/>
-      <c r="N37" s="14"/>
-      <c r="O37" s="14"/>
-      <c r="P37" s="14"/>
-      <c r="Q37" s="14"/>
-      <c r="R37" s="14"/>
-      <c r="S37" s="14"/>
-      <c r="T37" s="14"/>
-      <c r="U37" s="14"/>
-      <c r="V37" s="14"/>
-      <c r="W37" s="14"/>
-      <c r="X37" s="14"/>
-      <c r="Y37" s="14"/>
-      <c r="Z37" s="14"/>
-      <c r="AA37" s="14"/>
-      <c r="AB37" s="14"/>
-      <c r="AC37" s="14"/>
-      <c r="AD37" s="16"/>
-      <c r="AE37" s="16"/>
-    </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A38" s="15" t="s">
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="14"/>
+      <c r="P33" s="14"/>
+      <c r="Q33" s="14"/>
+      <c r="R33" s="14"/>
+      <c r="S33" s="31"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="14"/>
+      <c r="V33" s="14"/>
+      <c r="W33" s="14"/>
+      <c r="X33" s="14"/>
+      <c r="Y33" s="31"/>
+      <c r="Z33" s="14"/>
+      <c r="AA33" s="14"/>
+      <c r="AB33" s="14"/>
+      <c r="AC33" s="14"/>
+      <c r="AD33" s="14"/>
+      <c r="AE33" s="31"/>
+      <c r="AF33" s="14"/>
+      <c r="AG33" s="14"/>
+      <c r="AH33" s="14"/>
+      <c r="AI33" s="14"/>
+      <c r="AJ33" s="14"/>
+      <c r="AK33" s="31"/>
+      <c r="AL33" s="16"/>
+      <c r="AM33" s="16"/>
+    </row>
+    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A34" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="B38" s="15">
-        <v>74058</v>
-      </c>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
-      <c r="N38" s="15"/>
-      <c r="O38" s="15"/>
-      <c r="P38" s="15"/>
-      <c r="Q38" s="15"/>
-      <c r="R38" s="15"/>
-      <c r="S38" s="15"/>
-      <c r="T38" s="15"/>
-      <c r="U38" s="15"/>
-      <c r="V38" s="15"/>
-      <c r="W38" s="15"/>
-      <c r="X38" s="15"/>
-      <c r="Y38" s="15"/>
-      <c r="Z38" s="15"/>
-      <c r="AA38" s="15"/>
-      <c r="AB38" s="15"/>
-      <c r="AC38" s="15"/>
-      <c r="AD38" s="16"/>
-      <c r="AE38" s="16"/>
+      <c r="B34" s="30">
+        <v>74058.118000000002</v>
+      </c>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="38"/>
+      <c r="H34" s="30">
+        <v>83016.937999999995</v>
+      </c>
+      <c r="I34" s="30"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
+      <c r="L34" s="30"/>
+      <c r="M34" s="38"/>
+      <c r="N34" s="30">
+        <v>94345.274999999994</v>
+      </c>
+      <c r="O34" s="30"/>
+      <c r="P34" s="30"/>
+      <c r="Q34" s="30"/>
+      <c r="R34" s="30"/>
+      <c r="S34" s="15"/>
+      <c r="T34" s="30">
+        <v>83167.763000000006</v>
+      </c>
+      <c r="U34" s="30"/>
+      <c r="V34" s="30"/>
+      <c r="W34" s="30"/>
+      <c r="X34" s="30"/>
+      <c r="Y34" s="38"/>
+      <c r="Z34" s="30">
+        <v>93083.505999999994</v>
+      </c>
+      <c r="AA34" s="30"/>
+      <c r="AB34" s="30"/>
+      <c r="AC34" s="30"/>
+      <c r="AD34" s="30"/>
+      <c r="AE34" s="38"/>
+      <c r="AF34" s="30">
+        <v>105770.462</v>
+      </c>
+      <c r="AG34" s="30"/>
+      <c r="AH34" s="30"/>
+      <c r="AI34" s="30"/>
+      <c r="AJ34" s="30"/>
+      <c r="AK34" s="41"/>
+      <c r="AL34" s="16"/>
+      <c r="AM34" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="J3:O3"/>
-    <mergeCell ref="Q2:AB2"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="U3:X3"/>
-    <mergeCell ref="Y3:AB3"/>
+  <mergeCells count="14">
+    <mergeCell ref="AF34:AJ34"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="H34:L34"/>
+    <mergeCell ref="T34:X34"/>
+    <mergeCell ref="N34:R34"/>
+    <mergeCell ref="Z34:AD34"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B2:R2"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="N3:R3"/>
+    <mergeCell ref="T2:AJ2"/>
+    <mergeCell ref="T3:X3"/>
+    <mergeCell ref="Z3:AD3"/>
+    <mergeCell ref="AF3:AJ3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57A86273-0E84-8246-B3ED-A023C6721217}">
   <dimension ref="A1:M38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.1640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="4.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="15"/>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="G3" s="31" t="s">
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="G3" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="16"/>
       <c r="B4" s="17" t="s">
         <v>90</v>
@@ -3859,7 +4832,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>85</v>
       </c>
@@ -3872,7 +4845,7 @@
       <c r="I5" s="16"/>
       <c r="J5" s="16"/>
     </row>
-    <row r="6" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>96</v>
       </c>
@@ -3885,7 +4858,7 @@
       <c r="I6" s="18"/>
       <c r="J6" s="16"/>
     </row>
-    <row r="7" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>97</v>
       </c>
@@ -3898,7 +4871,7 @@
       <c r="I7" s="18"/>
       <c r="J7" s="16"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>86</v>
       </c>
@@ -3911,7 +4884,7 @@
       <c r="I8" s="16"/>
       <c r="J8" s="16"/>
     </row>
-    <row r="9" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>98</v>
       </c>
@@ -3924,7 +4897,7 @@
       <c r="I9" s="18"/>
       <c r="J9" s="16"/>
     </row>
-    <row r="10" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>99</v>
       </c>
@@ -3941,7 +4914,7 @@
       <c r="I10" s="18"/>
       <c r="J10" s="16"/>
     </row>
-    <row r="11" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>100</v>
       </c>
@@ -3958,15 +4931,15 @@
       <c r="I11" s="18"/>
       <c r="J11" s="16"/>
     </row>
-    <row r="12" spans="1:10" ht="17" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="25">
         <v>-4.1000000000000002E-2</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="29">
+      <c r="C12" s="25"/>
+      <c r="D12" s="26">
         <v>0.40300000000000002</v>
       </c>
       <c r="E12" s="16"/>
@@ -3975,7 +4948,7 @@
       <c r="I12" s="18"/>
       <c r="J12" s="16"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>88</v>
       </c>
@@ -3992,7 +4965,7 @@
       <c r="I13" s="18"/>
       <c r="J13" s="16"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>87</v>
       </c>
@@ -4005,7 +4978,7 @@
       <c r="I14" s="16"/>
       <c r="J14" s="16"/>
     </row>
-    <row r="15" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>102</v>
       </c>
@@ -4022,7 +4995,7 @@
       <c r="I15" s="18"/>
       <c r="J15" s="16"/>
     </row>
-    <row r="16" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>103</v>
       </c>
@@ -4035,7 +5008,7 @@
       <c r="I16" s="18"/>
       <c r="J16" s="16"/>
     </row>
-    <row r="17" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>104</v>
       </c>
@@ -4048,7 +5021,7 @@
       <c r="I17" s="18"/>
       <c r="J17" s="16"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>107</v>
       </c>
@@ -4065,7 +5038,7 @@
       <c r="I18" s="18"/>
       <c r="J18" s="16"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>108</v>
       </c>
@@ -4082,7 +5055,7 @@
       <c r="I19" s="18"/>
       <c r="J19" s="16"/>
     </row>
-    <row r="20" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>105</v>
       </c>
@@ -4095,7 +5068,7 @@
       <c r="I20" s="18"/>
       <c r="J20" s="16"/>
     </row>
-    <row r="21" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>106</v>
       </c>
@@ -4108,7 +5081,7 @@
       <c r="I21" s="18"/>
       <c r="J21" s="16"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>110</v>
       </c>
@@ -4125,7 +5098,7 @@
       <c r="I22" s="18"/>
       <c r="J22" s="16"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>109</v>
       </c>
@@ -4142,7 +5115,7 @@
       <c r="I23" s="18"/>
       <c r="J23" s="16"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>111</v>
       </c>
@@ -4155,7 +5128,7 @@
       <c r="I24" s="18"/>
       <c r="J24" s="16"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>82</v>
       </c>
@@ -4168,7 +5141,7 @@
       <c r="I25" s="16"/>
       <c r="J25" s="16"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>84</v>
       </c>
@@ -4185,7 +5158,7 @@
       <c r="I26" s="18"/>
       <c r="J26" s="16"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
         <v>89</v>
       </c>
@@ -4202,7 +5175,7 @@
       <c r="I27" s="18"/>
       <c r="J27" s="16"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
         <v>93</v>
       </c>
@@ -4221,7 +5194,7 @@
       <c r="I28" s="18"/>
       <c r="J28" s="16"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>112</v>
       </c>
@@ -4234,7 +5207,7 @@
       <c r="I29" s="18"/>
       <c r="J29" s="16"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
         <v>83</v>
       </c>
@@ -4247,7 +5220,7 @@
       <c r="I30" s="16"/>
       <c r="J30" s="16"/>
     </row>
-    <row r="31" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>96</v>
       </c>
@@ -4266,7 +5239,7 @@
       <c r="I31" s="18"/>
       <c r="J31" s="16"/>
     </row>
-    <row r="32" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
         <v>97</v>
       </c>
@@ -4285,7 +5258,7 @@
       <c r="I32" s="18"/>
       <c r="J32" s="16"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
         <v>84</v>
       </c>
@@ -4302,7 +5275,7 @@
       <c r="I33" s="18"/>
       <c r="J33" s="16"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
         <v>89</v>
       </c>
@@ -4319,7 +5292,7 @@
       <c r="I34" s="18"/>
       <c r="J34" s="16"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
         <v>93</v>
       </c>
@@ -4332,7 +5305,7 @@
       <c r="I35" s="18"/>
       <c r="J35" s="16"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
         <v>112</v>
       </c>
@@ -4343,8 +5316,8 @@
       <c r="H36" s="16"/>
       <c r="I36" s="18"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A37" s="21" t="s">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="20" t="s">
         <v>117</v>
       </c>
       <c r="B37" s="14"/>
@@ -4360,7 +5333,7 @@
       <c r="L37" s="16"/>
       <c r="M37" s="16"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
         <v>118</v>
       </c>
@@ -4391,62 +5364,62 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{540507A6-720C-0B43-804E-087FEE710926}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" customWidth="1"/>
+    <col min="1" max="1" width="19.875" customWidth="1"/>
+    <col min="2" max="2" width="18.875" customWidth="1"/>
+    <col min="3" max="3" width="19.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="26"/>
-    </row>
-    <row r="3" spans="1:3" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="26" t="s">
+    <row r="2" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="24"/>
+    </row>
+    <row r="3" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="24" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="26" t="s">
+    <row r="4" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="26"/>
-    </row>
-    <row r="6" spans="1:3" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="26"/>
-    </row>
-    <row r="7" spans="1:3" s="25" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:3" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="25" t="s">
+    <row r="5" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="24"/>
+    </row>
+    <row r="6" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="24"/>
+    </row>
+    <row r="7" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="23" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="26" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="24" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="26" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="24" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B11" s="25" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="23" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>126</v>
       </c>
@@ -4457,7 +5430,7 @@
         <v>-1.4E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>127</v>
       </c>
@@ -4468,7 +5441,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>128</v>
       </c>
@@ -4479,7 +5452,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>133</v>
       </c>
@@ -4490,25 +5463,25 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="25" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="23" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="26" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="24" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B19" s="25" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B19" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="23" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>126</v>
       </c>
@@ -4519,7 +5492,7 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>127</v>
       </c>
@@ -4530,7 +5503,7 @@
         <v>-1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>128</v>
       </c>
@@ -4541,7 +5514,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>133</v>
       </c>
@@ -4552,8 +5525,8 @@
         <v>-1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E25" s="25" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E25" s="23" t="s">
         <v>132</v>
       </c>
     </row>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nchaku\Documents\GitHub\pubertybrain\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nchaku/Documents/GitHub/pubertybrain/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3049B952-14D7-4B8A-9371-24029F884A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF775CB-4F28-1742-9002-F940C250CB44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
+    <workbookView xWindow="13360" yWindow="500" windowWidth="15440" windowHeight="16400" firstSheet="1" activeTab="5" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptive table" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,9 @@
     <sheet name="Fig1 (Pub)" sheetId="3" r:id="rId3"/>
     <sheet name="Fig2 (Brain)" sheetId="4" r:id="rId4"/>
     <sheet name="CortModels" sheetId="6" r:id="rId5"/>
-    <sheet name="Youth report PDS" sheetId="9" r:id="rId6"/>
-    <sheet name="Indirect effects" sheetId="7" r:id="rId7"/>
+    <sheet name="SubCortModel" sheetId="10" r:id="rId6"/>
+    <sheet name="Youth report PDS" sheetId="9" r:id="rId7"/>
+    <sheet name="Indirect effects" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="137">
   <si>
     <t>16.10 (2.98)</t>
   </si>
@@ -884,7 +885,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -925,34 +926,31 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="11" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1533,20 +1531,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39987BE7-3659-524A-81AE-D479F97EF698}">
   <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="20.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="9"/>
       <c r="B2" s="10" t="s">
         <v>63</v>
@@ -1564,7 +1562,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="6"/>
       <c r="B3" s="11" t="s">
         <v>69</v>
@@ -1578,7 +1576,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>60</v>
       </c>
@@ -1588,7 +1586,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>61</v>
       </c>
@@ -1608,7 +1606,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>62</v>
       </c>
@@ -1628,7 +1626,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>58</v>
       </c>
@@ -1648,7 +1646,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>59</v>
       </c>
@@ -1658,7 +1656,7 @@
       <c r="E8" s="12"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>61</v>
       </c>
@@ -1678,7 +1676,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>66</v>
       </c>
@@ -1698,7 +1696,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>67</v>
       </c>
@@ -1718,7 +1716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>62</v>
       </c>
@@ -1738,7 +1736,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>68</v>
       </c>
@@ -1748,7 +1746,7 @@
       <c r="E13" s="12"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>73</v>
       </c>
@@ -1768,7 +1766,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>74</v>
       </c>
@@ -1788,7 +1786,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>75</v>
       </c>
@@ -1808,7 +1806,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>76</v>
       </c>
@@ -1826,7 +1824,7 @@
       </c>
       <c r="F17" s="19"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>71</v>
       </c>
@@ -1836,7 +1834,7 @@
       <c r="E18" s="12"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>61</v>
       </c>
@@ -1856,7 +1854,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>66</v>
       </c>
@@ -1876,7 +1874,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>67</v>
       </c>
@@ -1896,7 +1894,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>62</v>
       </c>
@@ -1916,7 +1914,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>72</v>
       </c>
@@ -1926,7 +1924,7 @@
       <c r="E23" s="12"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>61</v>
       </c>
@@ -1946,7 +1944,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>66</v>
       </c>
@@ -1966,7 +1964,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>67</v>
       </c>
@@ -1986,7 +1984,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>62</v>
       </c>
@@ -2006,7 +2004,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2014,7 +2012,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2030,9 +2028,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A749072B-F938-0F49-BE23-243603B2B3D0}">
   <dimension ref="M2"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M2" t="s">
         <v>113</v>
       </c>
@@ -2046,7 +2044,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45875D41-9C56-AA4E-A18A-2D3A4CE169B3}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2056,7 +2054,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A5153E-6E5C-054A-8ACA-5118463B96C5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2066,241 +2064,240 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA86F85-A8D4-F648-84C3-730F1A42C846}">
   <dimension ref="A1:AM34"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="1.1640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.6640625" style="1" customWidth="1"/>
     <col min="11" max="11" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="1.125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="1.1640625" style="1" customWidth="1"/>
     <col min="14" max="14" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.6640625" style="1" customWidth="1"/>
     <col min="17" max="17" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="0.875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="0.83203125" style="1" customWidth="1"/>
     <col min="20" max="20" width="8.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="5.625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="6.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="1" style="33" customWidth="1"/>
+    <col min="21" max="21" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="5.6640625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="1" style="1" customWidth="1"/>
     <col min="26" max="26" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.6640625" style="1" customWidth="1"/>
     <col min="29" max="30" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="1.125" style="33" customWidth="1"/>
+    <col min="31" max="31" width="1.1640625" style="1" customWidth="1"/>
     <col min="32" max="32" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="5.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="5.625" style="1" customWidth="1"/>
-    <col min="36" max="36" width="6.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="5.6640625" style="1" customWidth="1"/>
+    <col min="36" max="36" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
       <c r="S2" s="9"/>
-      <c r="T2" s="35" t="s">
+      <c r="T2" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="35"/>
-      <c r="AA2" s="35"/>
-      <c r="AB2" s="35"/>
-      <c r="AC2" s="35"/>
-      <c r="AD2" s="35"/>
-      <c r="AE2" s="35"/>
-      <c r="AF2" s="35"/>
-      <c r="AG2" s="35"/>
-      <c r="AH2" s="35"/>
-      <c r="AI2" s="35"/>
-      <c r="AJ2" s="35"/>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
-      <c r="A3" s="31"/>
-      <c r="B3" s="35" t="s">
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
+      <c r="X2" s="32"/>
+      <c r="Y2" s="32"/>
+      <c r="Z2" s="32"/>
+      <c r="AA2" s="32"/>
+      <c r="AB2" s="32"/>
+      <c r="AC2" s="32"/>
+      <c r="AD2" s="32"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
+      <c r="AJ2" s="32"/>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A3" s="16"/>
+      <c r="B3" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="35" t="s">
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="37"/>
-      <c r="N3" s="35" t="s">
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="O3" s="35"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="35"/>
-      <c r="R3" s="35"/>
-      <c r="S3" s="33"/>
-      <c r="T3" s="32" t="s">
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
+      <c r="R3" s="32"/>
+      <c r="T3" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="U3" s="32"/>
-      <c r="V3" s="32"/>
-      <c r="W3" s="32"/>
-      <c r="X3" s="32"/>
-      <c r="Y3" s="37"/>
-      <c r="Z3" s="35" t="s">
+      <c r="U3" s="33"/>
+      <c r="V3" s="33"/>
+      <c r="W3" s="33"/>
+      <c r="X3" s="33"/>
+      <c r="Y3" s="28"/>
+      <c r="Z3" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="AA3" s="35"/>
-      <c r="AB3" s="35"/>
-      <c r="AC3" s="35"/>
-      <c r="AD3" s="35"/>
-      <c r="AE3" s="37"/>
-      <c r="AF3" s="35" t="s">
+      <c r="AA3" s="32"/>
+      <c r="AB3" s="32"/>
+      <c r="AC3" s="32"/>
+      <c r="AD3" s="32"/>
+      <c r="AE3" s="28"/>
+      <c r="AF3" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="AG3" s="35"/>
-      <c r="AH3" s="35"/>
-      <c r="AI3" s="35"/>
-      <c r="AJ3" s="35"/>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AG3" s="32"/>
+      <c r="AH3" s="32"/>
+      <c r="AI3" s="32"/>
+      <c r="AJ3" s="32"/>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="D4" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="29" t="s">
         <v>136</v>
       </c>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36" t="s">
+      <c r="G4" s="29"/>
+      <c r="H4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="36" t="s">
+      <c r="I4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="36" t="s">
+      <c r="J4" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="L4" s="36" t="s">
+      <c r="L4" s="29" t="s">
         <v>136</v>
       </c>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36" t="s">
+      <c r="M4" s="29"/>
+      <c r="N4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="O4" s="36" t="s">
+      <c r="O4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="P4" s="36" t="s">
+      <c r="P4" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="Q4" s="36" t="s">
+      <c r="Q4" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="R4" s="36" t="s">
+      <c r="R4" s="29" t="s">
         <v>136</v>
       </c>
       <c r="S4" s="6"/>
-      <c r="T4" s="36" t="s">
+      <c r="T4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="U4" s="36" t="s">
+      <c r="U4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="V4" s="36" t="s">
+      <c r="V4" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="W4" s="36" t="s">
+      <c r="W4" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="X4" s="36" t="s">
+      <c r="X4" s="29" t="s">
         <v>136</v>
       </c>
-      <c r="Y4" s="34"/>
-      <c r="Z4" s="36" t="s">
+      <c r="Y4" s="17"/>
+      <c r="Z4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="AA4" s="36" t="s">
+      <c r="AA4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="AB4" s="36" t="s">
+      <c r="AB4" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="AC4" s="36" t="s">
+      <c r="AC4" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="AD4" s="36" t="s">
+      <c r="AD4" s="29" t="s">
         <v>136</v>
       </c>
-      <c r="AE4" s="34"/>
-      <c r="AF4" s="36" t="s">
+      <c r="AE4" s="17"/>
+      <c r="AF4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="AG4" s="36" t="s">
+      <c r="AG4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="AH4" s="36" t="s">
+      <c r="AH4" s="29" t="s">
         <v>92</v>
       </c>
-      <c r="AI4" s="36" t="s">
+      <c r="AI4" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="AJ4" s="36" t="s">
+      <c r="AJ4" s="29" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
         <v>85</v>
       </c>
@@ -2326,20 +2323,20 @@
       <c r="V5" s="16"/>
       <c r="W5" s="16"/>
       <c r="X5" s="16"/>
-      <c r="Y5" s="31"/>
+      <c r="Y5" s="16"/>
       <c r="Z5" s="16"/>
       <c r="AA5" s="16"/>
       <c r="AB5" s="16"/>
       <c r="AC5" s="16"/>
       <c r="AD5" s="16"/>
-      <c r="AE5" s="31"/>
+      <c r="AE5" s="16"/>
       <c r="AF5" s="16"/>
       <c r="AG5" s="16"/>
       <c r="AH5" s="16"/>
       <c r="AI5" s="16"/>
       <c r="AJ5" s="16"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>96</v>
       </c>
@@ -2405,7 +2402,7 @@
       <c r="X6" s="16">
         <v>12.095000000000001</v>
       </c>
-      <c r="Y6" s="31"/>
+      <c r="Y6" s="16"/>
       <c r="Z6" s="16">
         <v>11.930999999999999</v>
       </c>
@@ -2421,7 +2418,7 @@
       <c r="AD6" s="16">
         <v>12.236000000000001</v>
       </c>
-      <c r="AE6" s="31"/>
+      <c r="AE6" s="16"/>
       <c r="AF6" s="16">
         <v>11.930999999999999</v>
       </c>
@@ -2438,7 +2435,7 @@
         <v>12.236000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>97</v>
       </c>
@@ -2504,7 +2501,7 @@
       <c r="X7" s="16">
         <v>-7.7430000000000003</v>
       </c>
-      <c r="Y7" s="31"/>
+      <c r="Y7" s="16"/>
       <c r="Z7" s="16">
         <v>-8.8079999999999998</v>
       </c>
@@ -2520,7 +2517,7 @@
       <c r="AD7" s="16">
         <v>-7.7619999999999996</v>
       </c>
-      <c r="AE7" s="31"/>
+      <c r="AE7" s="16"/>
       <c r="AF7" s="16">
         <v>-8.8030000000000008</v>
       </c>
@@ -2537,7 +2534,7 @@
         <v>-7.7560000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A8" s="16"/>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -2551,8 +2548,8 @@
       <c r="K8" s="18"/>
       <c r="L8" s="16"/>
       <c r="M8" s="16"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="29"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
       <c r="P8" s="18"/>
       <c r="Q8" s="18"/>
       <c r="R8" s="16"/>
@@ -2561,20 +2558,20 @@
       <c r="V8" s="18"/>
       <c r="W8" s="18"/>
       <c r="X8" s="21"/>
-      <c r="Y8" s="39"/>
+      <c r="Y8" s="21"/>
       <c r="Z8" s="16"/>
       <c r="AA8" s="16"/>
       <c r="AB8" s="18"/>
       <c r="AC8" s="18"/>
       <c r="AD8" s="16"/>
-      <c r="AE8" s="31"/>
+      <c r="AE8" s="16"/>
       <c r="AF8" s="16"/>
       <c r="AG8" s="16"/>
       <c r="AH8" s="18"/>
       <c r="AI8" s="18"/>
       <c r="AJ8" s="16"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A9" s="17" t="s">
         <v>86</v>
       </c>
@@ -2600,20 +2597,20 @@
       <c r="V9" s="16"/>
       <c r="W9" s="16"/>
       <c r="X9" s="21"/>
-      <c r="Y9" s="39"/>
+      <c r="Y9" s="21"/>
       <c r="Z9" s="16"/>
       <c r="AA9" s="16"/>
       <c r="AB9" s="16"/>
       <c r="AC9" s="16"/>
       <c r="AD9" s="16"/>
-      <c r="AE9" s="31"/>
+      <c r="AE9" s="16"/>
       <c r="AF9" s="16"/>
       <c r="AG9" s="16"/>
       <c r="AH9" s="16"/>
       <c r="AI9" s="16"/>
       <c r="AJ9" s="16"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>98</v>
       </c>
@@ -2679,7 +2676,7 @@
       <c r="X10" s="16">
         <v>-0.24</v>
       </c>
-      <c r="Y10" s="31"/>
+      <c r="Y10" s="16"/>
       <c r="Z10" s="16">
         <v>-0.30599999999999999</v>
       </c>
@@ -2695,7 +2692,7 @@
       <c r="AD10" s="16">
         <v>-0.24099999999999999</v>
       </c>
-      <c r="AE10" s="31"/>
+      <c r="AE10" s="16"/>
       <c r="AF10" s="16">
         <v>-0.30599999999999999</v>
       </c>
@@ -2712,7 +2709,7 @@
         <v>-0.24</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>99</v>
       </c>
@@ -2778,7 +2775,7 @@
       <c r="X11" s="16">
         <v>0.09</v>
       </c>
-      <c r="Y11" s="31"/>
+      <c r="Y11" s="16"/>
       <c r="Z11" s="16">
         <v>5.6000000000000001E-2</v>
       </c>
@@ -2794,7 +2791,7 @@
       <c r="AD11" s="16">
         <v>0.09</v>
       </c>
-      <c r="AE11" s="31"/>
+      <c r="AE11" s="16"/>
       <c r="AF11" s="16">
         <v>5.6000000000000001E-2</v>
       </c>
@@ -2811,7 +2808,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>100</v>
       </c>
@@ -2877,7 +2874,7 @@
       <c r="X12" s="16">
         <v>0.16900000000000001</v>
       </c>
-      <c r="Y12" s="31"/>
+      <c r="Y12" s="16"/>
       <c r="Z12" s="16">
         <v>0.114</v>
       </c>
@@ -2893,7 +2890,7 @@
       <c r="AD12" s="16">
         <v>0.14799999999999999</v>
       </c>
-      <c r="AE12" s="31"/>
+      <c r="AE12" s="16"/>
       <c r="AF12" s="16">
         <v>0.115</v>
       </c>
@@ -2910,7 +2907,7 @@
         <v>0.14899999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>101</v>
       </c>
@@ -2976,7 +2973,7 @@
       <c r="X13" s="16">
         <v>3.1E-2</v>
       </c>
-      <c r="Y13" s="31"/>
+      <c r="Y13" s="16"/>
       <c r="Z13" s="16">
         <v>-2.8000000000000001E-2</v>
       </c>
@@ -2992,7 +2989,7 @@
       <c r="AD13" s="16">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="AE13" s="31"/>
+      <c r="AE13" s="16"/>
       <c r="AF13" s="16">
         <v>-2.8000000000000001E-2</v>
       </c>
@@ -3009,7 +3006,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A14" s="16" t="s">
         <v>88</v>
       </c>
@@ -3075,7 +3072,7 @@
       <c r="X14" s="16">
         <v>0.28399999999999997</v>
       </c>
-      <c r="Y14" s="31"/>
+      <c r="Y14" s="16"/>
       <c r="Z14" s="16">
         <v>0.252</v>
       </c>
@@ -3091,7 +3088,7 @@
       <c r="AD14" s="16">
         <v>0.28699999999999998</v>
       </c>
-      <c r="AE14" s="31"/>
+      <c r="AE14" s="16"/>
       <c r="AF14" s="16">
         <v>0.252</v>
       </c>
@@ -3108,7 +3105,7 @@
         <v>0.28799999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A15" s="16"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -3132,20 +3129,20 @@
       <c r="V15" s="18"/>
       <c r="W15" s="18"/>
       <c r="X15" s="21"/>
-      <c r="Y15" s="39"/>
+      <c r="Y15" s="21"/>
       <c r="Z15" s="16"/>
       <c r="AA15" s="16"/>
       <c r="AB15" s="18"/>
       <c r="AC15" s="18"/>
       <c r="AD15" s="16"/>
-      <c r="AE15" s="31"/>
+      <c r="AE15" s="16"/>
       <c r="AF15" s="16"/>
       <c r="AG15" s="16"/>
       <c r="AH15" s="18"/>
       <c r="AI15" s="18"/>
       <c r="AJ15" s="16"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
         <v>87</v>
       </c>
@@ -3171,20 +3168,20 @@
       <c r="V16" s="16"/>
       <c r="W16" s="16"/>
       <c r="X16" s="21"/>
-      <c r="Y16" s="39"/>
+      <c r="Y16" s="21"/>
       <c r="Z16" s="16"/>
       <c r="AA16" s="16"/>
       <c r="AB16" s="16"/>
       <c r="AC16" s="16"/>
       <c r="AD16" s="16"/>
-      <c r="AE16" s="31"/>
+      <c r="AE16" s="16"/>
       <c r="AF16" s="16"/>
       <c r="AG16" s="16"/>
       <c r="AH16" s="16"/>
       <c r="AI16" s="16"/>
       <c r="AJ16" s="16"/>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>102</v>
       </c>
@@ -3250,7 +3247,7 @@
       <c r="X17" s="16">
         <v>0.443</v>
       </c>
-      <c r="Y17" s="31"/>
+      <c r="Y17" s="16"/>
       <c r="Z17" s="16">
         <v>0.38300000000000001</v>
       </c>
@@ -3266,7 +3263,7 @@
       <c r="AD17" s="16">
         <v>0.443</v>
       </c>
-      <c r="AE17" s="31"/>
+      <c r="AE17" s="16"/>
       <c r="AF17" s="16">
         <v>0.38300000000000001</v>
       </c>
@@ -3283,7 +3280,7 @@
         <v>0.443</v>
       </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>103</v>
       </c>
@@ -3349,7 +3346,7 @@
       <c r="X18" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="Y18" s="39"/>
+      <c r="Y18" s="21"/>
       <c r="Z18" s="16">
         <v>-0.13900000000000001</v>
       </c>
@@ -3365,7 +3362,7 @@
       <c r="AD18" s="16">
         <v>-0.104</v>
       </c>
-      <c r="AE18" s="31"/>
+      <c r="AE18" s="16"/>
       <c r="AF18" s="16">
         <v>-0.13900000000000001</v>
       </c>
@@ -3382,7 +3379,7 @@
         <v>-0.10299999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>104</v>
       </c>
@@ -3448,7 +3445,7 @@
       <c r="X19" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="Y19" s="39"/>
+      <c r="Y19" s="21"/>
       <c r="Z19" s="16">
         <v>2.5000000000000001E-2</v>
       </c>
@@ -3464,7 +3461,7 @@
       <c r="AD19" s="16">
         <v>9.1999999999999998E-2</v>
       </c>
-      <c r="AE19" s="31"/>
+      <c r="AE19" s="16"/>
       <c r="AF19" s="16">
         <v>2.4E-2</v>
       </c>
@@ -3477,11 +3474,11 @@
       <c r="AI19" s="16">
         <v>-4.2999999999999997E-2</v>
       </c>
-      <c r="AJ19" s="40">
+      <c r="AJ19" s="30">
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
         <v>107</v>
       </c>
@@ -3547,7 +3544,7 @@
       <c r="X20" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="Y20" s="39"/>
+      <c r="Y20" s="21"/>
       <c r="Z20" s="16">
         <v>-0.17</v>
       </c>
@@ -3563,7 +3560,7 @@
       <c r="AD20" s="16">
         <v>3.2000000000000001E-2</v>
       </c>
-      <c r="AE20" s="31"/>
+      <c r="AE20" s="16"/>
       <c r="AF20" s="16">
         <v>-3.0000000000000001E-3</v>
       </c>
@@ -3580,7 +3577,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
         <v>108</v>
       </c>
@@ -3646,7 +3643,7 @@
       <c r="X21" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="Y21" s="39"/>
+      <c r="Y21" s="21"/>
       <c r="Z21" s="16">
         <v>-3.0000000000000001E-3</v>
       </c>
@@ -3662,7 +3659,7 @@
       <c r="AD21" s="16">
         <v>-0.13600000000000001</v>
       </c>
-      <c r="AE21" s="31"/>
+      <c r="AE21" s="16"/>
       <c r="AF21" s="16">
         <v>-0.17100000000000001</v>
       </c>
@@ -3679,7 +3676,7 @@
         <v>-0.13600000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>105</v>
       </c>
@@ -3745,7 +3742,7 @@
       <c r="X22" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="Y22" s="39"/>
+      <c r="Y22" s="21"/>
       <c r="Z22" s="16" t="s">
         <v>94</v>
       </c>
@@ -3759,7 +3756,7 @@
       <c r="AD22" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="AE22" s="31"/>
+      <c r="AE22" s="16"/>
       <c r="AF22" s="16">
         <v>0.11700000000000001</v>
       </c>
@@ -3776,7 +3773,7 @@
         <v>0.156</v>
       </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>106</v>
       </c>
@@ -3842,7 +3839,7 @@
       <c r="X23" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="Y23" s="39"/>
+      <c r="Y23" s="21"/>
       <c r="Z23" s="16" t="s">
         <v>94</v>
       </c>
@@ -3856,7 +3853,7 @@
       <c r="AD23" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="AE23" s="31"/>
+      <c r="AE23" s="16"/>
       <c r="AF23" s="16">
         <v>-8.8999999999999996E-2</v>
       </c>
@@ -3873,7 +3870,7 @@
         <v>-1.6E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
         <v>110</v>
       </c>
@@ -3939,7 +3936,7 @@
       <c r="X24" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="Y24" s="39"/>
+      <c r="Y24" s="21"/>
       <c r="Z24" s="16" t="s">
         <v>94</v>
       </c>
@@ -3953,7 +3950,7 @@
       <c r="AD24" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="AE24" s="31"/>
+      <c r="AE24" s="16"/>
       <c r="AF24" s="16">
         <v>6.8000000000000005E-2</v>
       </c>
@@ -3970,7 +3967,7 @@
         <v>0.112</v>
       </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A25" s="16" t="s">
         <v>109</v>
       </c>
@@ -4036,7 +4033,7 @@
       <c r="X25" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="Y25" s="39"/>
+      <c r="Y25" s="21"/>
       <c r="Z25" s="16" t="s">
         <v>94</v>
       </c>
@@ -4050,7 +4047,7 @@
       <c r="AD25" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="AE25" s="31"/>
+      <c r="AE25" s="16"/>
       <c r="AF25" s="16">
         <v>0.125</v>
       </c>
@@ -4067,7 +4064,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
         <v>111</v>
       </c>
@@ -4133,7 +4130,7 @@
       <c r="X26" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="Y26" s="39"/>
+      <c r="Y26" s="21"/>
       <c r="Z26" s="16" t="s">
         <v>94</v>
       </c>
@@ -4147,7 +4144,7 @@
       <c r="AD26" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="AE26" s="31"/>
+      <c r="AE26" s="16"/>
       <c r="AF26" s="16">
         <v>-8.3000000000000004E-2</v>
       </c>
@@ -4164,7 +4161,7 @@
         <v>-4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -4188,20 +4185,20 @@
       <c r="V27" s="16"/>
       <c r="W27" s="16"/>
       <c r="X27" s="21"/>
-      <c r="Y27" s="39"/>
+      <c r="Y27" s="21"/>
       <c r="Z27" s="16"/>
       <c r="AA27" s="16"/>
       <c r="AB27" s="16"/>
       <c r="AC27" s="16"/>
       <c r="AD27" s="16"/>
-      <c r="AE27" s="31"/>
+      <c r="AE27" s="16"/>
       <c r="AF27" s="16"/>
       <c r="AG27" s="16"/>
       <c r="AH27" s="18"/>
       <c r="AI27" s="18"/>
       <c r="AJ27" s="16"/>
     </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A28" s="17" t="s">
         <v>82</v>
       </c>
@@ -4227,20 +4224,20 @@
       <c r="V28" s="16"/>
       <c r="W28" s="16"/>
       <c r="X28" s="21"/>
-      <c r="Y28" s="39"/>
+      <c r="Y28" s="21"/>
       <c r="Z28" s="16"/>
       <c r="AA28" s="16"/>
       <c r="AB28" s="16"/>
       <c r="AC28" s="16"/>
       <c r="AD28" s="16"/>
-      <c r="AE28" s="31"/>
+      <c r="AE28" s="16"/>
       <c r="AF28" s="16"/>
       <c r="AG28" s="16"/>
       <c r="AH28" s="16"/>
       <c r="AI28" s="16"/>
       <c r="AJ28" s="16"/>
     </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A29" s="16" t="s">
         <v>84</v>
       </c>
@@ -4306,7 +4303,7 @@
       <c r="X29" s="16">
         <v>14.16</v>
       </c>
-      <c r="Y29" s="31"/>
+      <c r="Y29" s="16"/>
       <c r="Z29" s="16">
         <v>13.832000000000001</v>
       </c>
@@ -4322,7 +4319,7 @@
       <c r="AD29" s="16">
         <v>14.164999999999999</v>
       </c>
-      <c r="AE29" s="31"/>
+      <c r="AE29" s="16"/>
       <c r="AF29" s="16">
         <v>13.832000000000001</v>
       </c>
@@ -4339,7 +4336,7 @@
         <v>14.164999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A30" s="16" t="s">
         <v>89</v>
       </c>
@@ -4405,7 +4402,7 @@
       <c r="X30" s="16">
         <v>3.992</v>
       </c>
-      <c r="Y30" s="31"/>
+      <c r="Y30" s="16"/>
       <c r="Z30" s="16">
         <v>4.0620000000000003</v>
       </c>
@@ -4421,7 +4418,7 @@
       <c r="AD30" s="16">
         <v>4.1669999999999998</v>
       </c>
-      <c r="AE30" s="31"/>
+      <c r="AE30" s="16"/>
       <c r="AF30" s="16">
         <v>4.0609999999999999</v>
       </c>
@@ -4438,7 +4435,7 @@
         <v>4.1660000000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A31" s="16" t="s">
         <v>93</v>
       </c>
@@ -4504,7 +4501,7 @@
       <c r="X31" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="Y31" s="39"/>
+      <c r="Y31" s="21"/>
       <c r="Z31" s="16">
         <v>1.026</v>
       </c>
@@ -4520,7 +4517,7 @@
       <c r="AD31" s="16">
         <v>1.0549999999999999</v>
       </c>
-      <c r="AE31" s="31"/>
+      <c r="AE31" s="16"/>
       <c r="AF31" s="16">
         <v>1.0269999999999999</v>
       </c>
@@ -4537,7 +4534,7 @@
         <v>1.0549999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A32" s="16" t="s">
         <v>112</v>
       </c>
@@ -4556,7 +4553,7 @@
       <c r="F32" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="G32" s="39"/>
+      <c r="G32" s="21"/>
       <c r="H32" s="16" t="s">
         <v>94</v>
       </c>
@@ -4570,7 +4567,7 @@
       <c r="L32" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="M32" s="31"/>
+      <c r="M32" s="16"/>
       <c r="N32" s="16">
         <v>3.8239999999999998</v>
       </c>
@@ -4586,7 +4583,6 @@
       <c r="R32" s="16">
         <v>4.5410000000000004</v>
       </c>
-      <c r="S32" s="33"/>
       <c r="T32" s="16" t="s">
         <v>94</v>
       </c>
@@ -4602,7 +4598,7 @@
       <c r="X32" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="Y32" s="39"/>
+      <c r="Y32" s="21"/>
       <c r="Z32" s="16" t="s">
         <v>94</v>
       </c>
@@ -4618,7 +4614,7 @@
       <c r="AD32" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="AE32" s="31"/>
+      <c r="AE32" s="16"/>
       <c r="AF32" s="16">
         <v>3.387</v>
       </c>
@@ -4634,9 +4630,8 @@
       <c r="AJ32" s="16">
         <v>4.202</v>
       </c>
-      <c r="AK32" s="33"/>
-    </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A33" s="20" t="s">
         <v>117</v>
       </c>
@@ -4645,108 +4640,1935 @@
       <c r="D33" s="14"/>
       <c r="E33" s="14"/>
       <c r="F33" s="14"/>
-      <c r="G33" s="31"/>
+      <c r="G33" s="16"/>
       <c r="H33" s="14"/>
       <c r="I33" s="14"/>
       <c r="J33" s="14"/>
       <c r="K33" s="14"/>
       <c r="L33" s="14"/>
-      <c r="M33" s="31"/>
+      <c r="M33" s="16"/>
       <c r="N33" s="14"/>
       <c r="O33" s="14"/>
       <c r="P33" s="14"/>
       <c r="Q33" s="14"/>
       <c r="R33" s="14"/>
-      <c r="S33" s="31"/>
+      <c r="S33" s="16"/>
       <c r="T33" s="14"/>
       <c r="U33" s="14"/>
       <c r="V33" s="14"/>
       <c r="W33" s="14"/>
       <c r="X33" s="14"/>
-      <c r="Y33" s="31"/>
+      <c r="Y33" s="16"/>
       <c r="Z33" s="14"/>
       <c r="AA33" s="14"/>
       <c r="AB33" s="14"/>
       <c r="AC33" s="14"/>
       <c r="AD33" s="14"/>
-      <c r="AE33" s="31"/>
+      <c r="AE33" s="16"/>
       <c r="AF33" s="14"/>
       <c r="AG33" s="14"/>
       <c r="AH33" s="14"/>
       <c r="AI33" s="14"/>
       <c r="AJ33" s="14"/>
-      <c r="AK33" s="31"/>
+      <c r="AK33" s="16"/>
       <c r="AL33" s="16"/>
       <c r="AM33" s="16"/>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="B34" s="30">
+      <c r="B34" s="31">
         <v>74058.118000000002</v>
       </c>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="30">
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="31">
         <v>83016.937999999995</v>
       </c>
-      <c r="I34" s="30"/>
-      <c r="J34" s="30"/>
-      <c r="K34" s="30"/>
-      <c r="L34" s="30"/>
-      <c r="M34" s="38"/>
-      <c r="N34" s="30">
+      <c r="I34" s="31"/>
+      <c r="J34" s="31"/>
+      <c r="K34" s="31"/>
+      <c r="L34" s="31"/>
+      <c r="M34" s="27"/>
+      <c r="N34" s="31">
         <v>94345.274999999994</v>
       </c>
-      <c r="O34" s="30"/>
-      <c r="P34" s="30"/>
-      <c r="Q34" s="30"/>
-      <c r="R34" s="30"/>
+      <c r="O34" s="31"/>
+      <c r="P34" s="31"/>
+      <c r="Q34" s="31"/>
+      <c r="R34" s="31"/>
       <c r="S34" s="15"/>
-      <c r="T34" s="30">
+      <c r="T34" s="31">
         <v>83167.763000000006</v>
       </c>
-      <c r="U34" s="30"/>
-      <c r="V34" s="30"/>
-      <c r="W34" s="30"/>
-      <c r="X34" s="30"/>
-      <c r="Y34" s="38"/>
-      <c r="Z34" s="30">
+      <c r="U34" s="31"/>
+      <c r="V34" s="31"/>
+      <c r="W34" s="31"/>
+      <c r="X34" s="31"/>
+      <c r="Y34" s="27"/>
+      <c r="Z34" s="31">
         <v>93083.505999999994</v>
       </c>
-      <c r="AA34" s="30"/>
-      <c r="AB34" s="30"/>
-      <c r="AC34" s="30"/>
-      <c r="AD34" s="30"/>
-      <c r="AE34" s="38"/>
-      <c r="AF34" s="30">
+      <c r="AA34" s="31"/>
+      <c r="AB34" s="31"/>
+      <c r="AC34" s="31"/>
+      <c r="AD34" s="31"/>
+      <c r="AE34" s="27"/>
+      <c r="AF34" s="31">
         <v>105770.462</v>
       </c>
-      <c r="AG34" s="30"/>
-      <c r="AH34" s="30"/>
-      <c r="AI34" s="30"/>
-      <c r="AJ34" s="30"/>
-      <c r="AK34" s="41"/>
+      <c r="AG34" s="31"/>
+      <c r="AH34" s="31"/>
+      <c r="AI34" s="31"/>
+      <c r="AJ34" s="31"/>
+      <c r="AK34" s="16"/>
       <c r="AL34" s="16"/>
       <c r="AM34" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B2:R2"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="N3:R3"/>
+    <mergeCell ref="T2:AJ2"/>
+    <mergeCell ref="T3:X3"/>
+    <mergeCell ref="Z3:AD3"/>
+    <mergeCell ref="AF3:AJ3"/>
     <mergeCell ref="AF34:AJ34"/>
     <mergeCell ref="B34:F34"/>
     <mergeCell ref="H34:L34"/>
     <mergeCell ref="T34:X34"/>
     <mergeCell ref="N34:R34"/>
     <mergeCell ref="Z34:AD34"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CD5CF7F-81D6-D24D-8228-B4C578C35D65}">
+  <dimension ref="A1:AM34"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="6.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="1.1640625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.6640625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="0.83203125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.6640625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="1" style="1" customWidth="1"/>
+    <col min="26" max="26" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.6640625" style="1" customWidth="1"/>
+    <col min="29" max="30" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="1.1640625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="5.6640625" style="1" customWidth="1"/>
+    <col min="36" max="36" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="11" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A2" s="14"/>
+      <c r="B2" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
+      <c r="X2" s="32"/>
+      <c r="Y2" s="32"/>
+      <c r="Z2" s="32"/>
+      <c r="AA2" s="32"/>
+      <c r="AB2" s="32"/>
+      <c r="AC2" s="32"/>
+      <c r="AD2" s="32"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
+      <c r="AJ2" s="32"/>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A3" s="16"/>
+      <c r="B3" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
+      <c r="R3" s="32"/>
+      <c r="T3" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="U3" s="33"/>
+      <c r="V3" s="33"/>
+      <c r="W3" s="33"/>
+      <c r="X3" s="33"/>
+      <c r="Y3" s="28"/>
+      <c r="Z3" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="AA3" s="32"/>
+      <c r="AB3" s="32"/>
+      <c r="AC3" s="32"/>
+      <c r="AD3" s="32"/>
+      <c r="AE3" s="28"/>
+      <c r="AF3" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG3" s="32"/>
+      <c r="AH3" s="32"/>
+      <c r="AI3" s="32"/>
+      <c r="AJ3" s="32"/>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A4" s="15"/>
+      <c r="B4" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="I4" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="J4" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="K4" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="L4" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="M4" s="29"/>
+      <c r="N4" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="O4" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="P4" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q4" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="R4" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="S4" s="6"/>
+      <c r="T4" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="U4" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="V4" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="W4" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="X4" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y4" s="17"/>
+      <c r="Z4" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="AA4" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="AB4" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="AC4" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="AD4" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="AE4" s="17"/>
+      <c r="AF4" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="AG4" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="AH4" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="AI4" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="AJ4" s="29" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A5" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="16"/>
+      <c r="V5" s="16"/>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="16"/>
+      <c r="AA5" s="16"/>
+      <c r="AB5" s="16"/>
+      <c r="AC5" s="16"/>
+      <c r="AD5" s="16"/>
+      <c r="AE5" s="16"/>
+      <c r="AF5" s="16"/>
+      <c r="AG5" s="16"/>
+      <c r="AH5" s="16"/>
+      <c r="AI5" s="16"/>
+      <c r="AJ5" s="16"/>
+    </row>
+    <row r="6" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="16"/>
+      <c r="T6" s="16">
+        <v>13.391</v>
+      </c>
+      <c r="U6" s="16">
+        <v>0.215</v>
+      </c>
+      <c r="V6" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="W6" s="16"/>
+      <c r="X6" s="16"/>
+      <c r="Y6" s="16"/>
+      <c r="Z6" s="16"/>
+      <c r="AA6" s="16"/>
+      <c r="AB6" s="18"/>
+      <c r="AC6" s="16"/>
+      <c r="AD6" s="16"/>
+      <c r="AE6" s="16"/>
+      <c r="AF6" s="16"/>
+      <c r="AG6" s="16"/>
+      <c r="AH6" s="18"/>
+      <c r="AI6" s="16"/>
+      <c r="AJ6" s="16"/>
+    </row>
+    <row r="7" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="16"/>
+      <c r="P7" s="18"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="16"/>
+      <c r="T7" s="16">
+        <v>1.222</v>
+      </c>
+      <c r="U7" s="16">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="V7" s="18">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="W7" s="16"/>
+      <c r="X7" s="16"/>
+      <c r="Y7" s="16"/>
+      <c r="Z7" s="16"/>
+      <c r="AA7" s="16"/>
+      <c r="AB7" s="18"/>
+      <c r="AC7" s="16"/>
+      <c r="AD7" s="16"/>
+      <c r="AE7" s="16"/>
+      <c r="AF7" s="16"/>
+      <c r="AG7" s="16"/>
+      <c r="AH7" s="18"/>
+      <c r="AI7" s="16"/>
+      <c r="AJ7" s="16"/>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A8" s="16"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="18"/>
+      <c r="R8" s="16"/>
+      <c r="T8" s="16"/>
+      <c r="U8" s="16"/>
+      <c r="V8" s="18"/>
+      <c r="W8" s="18"/>
+      <c r="X8" s="21"/>
+      <c r="Y8" s="21"/>
+      <c r="Z8" s="16"/>
+      <c r="AA8" s="16"/>
+      <c r="AB8" s="18"/>
+      <c r="AC8" s="18"/>
+      <c r="AD8" s="16"/>
+      <c r="AE8" s="16"/>
+      <c r="AF8" s="16"/>
+      <c r="AG8" s="16"/>
+      <c r="AH8" s="18"/>
+      <c r="AI8" s="18"/>
+      <c r="AJ8" s="16"/>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A9" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
+      <c r="T9" s="16"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="16"/>
+      <c r="X9" s="21"/>
+      <c r="Y9" s="21"/>
+      <c r="Z9" s="16"/>
+      <c r="AA9" s="16"/>
+      <c r="AB9" s="16"/>
+      <c r="AC9" s="16"/>
+      <c r="AD9" s="16"/>
+      <c r="AE9" s="16"/>
+      <c r="AF9" s="16"/>
+      <c r="AG9" s="16"/>
+      <c r="AH9" s="16"/>
+      <c r="AI9" s="16"/>
+      <c r="AJ9" s="16"/>
+    </row>
+    <row r="10" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="18"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="16"/>
+      <c r="T10" s="16">
+        <v>0.318</v>
+      </c>
+      <c r="U10" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="V10" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="W10" s="16"/>
+      <c r="X10" s="16"/>
+      <c r="Y10" s="16"/>
+      <c r="Z10" s="16"/>
+      <c r="AA10" s="16"/>
+      <c r="AB10" s="18"/>
+      <c r="AC10" s="16"/>
+      <c r="AD10" s="16"/>
+      <c r="AE10" s="16"/>
+      <c r="AF10" s="16"/>
+      <c r="AG10" s="16"/>
+      <c r="AH10" s="18"/>
+      <c r="AI10" s="16"/>
+      <c r="AJ10" s="16"/>
+    </row>
+    <row r="11" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16"/>
+      <c r="H11" s="16"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
+      <c r="T11" s="16">
+        <v>-0.01</v>
+      </c>
+      <c r="U11" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="V11" s="18">
+        <v>0.63500000000000001</v>
+      </c>
+      <c r="W11" s="16"/>
+      <c r="X11" s="16"/>
+      <c r="Y11" s="16"/>
+      <c r="Z11" s="16"/>
+      <c r="AA11" s="16"/>
+      <c r="AB11" s="18"/>
+      <c r="AC11" s="16"/>
+      <c r="AD11" s="16"/>
+      <c r="AE11" s="16"/>
+      <c r="AF11" s="16"/>
+      <c r="AG11" s="16"/>
+      <c r="AH11" s="18"/>
+      <c r="AI11" s="16"/>
+      <c r="AJ11" s="16"/>
+    </row>
+    <row r="12" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="18"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="T12" s="16">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="U12" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="V12" s="18">
+        <v>1E-3</v>
+      </c>
+      <c r="W12" s="16"/>
+      <c r="X12" s="16"/>
+      <c r="Y12" s="16"/>
+      <c r="Z12" s="16"/>
+      <c r="AA12" s="16"/>
+      <c r="AB12" s="18"/>
+      <c r="AC12" s="16"/>
+      <c r="AD12" s="16"/>
+      <c r="AE12" s="16"/>
+      <c r="AF12" s="16"/>
+      <c r="AG12" s="16"/>
+      <c r="AH12" s="18"/>
+      <c r="AI12" s="16"/>
+      <c r="AJ12" s="16"/>
+    </row>
+    <row r="13" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="18"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="16"/>
+      <c r="T13" s="16">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="U13" s="16">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="V13" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="W13" s="16"/>
+      <c r="X13" s="16"/>
+      <c r="Y13" s="16"/>
+      <c r="Z13" s="16"/>
+      <c r="AA13" s="16"/>
+      <c r="AB13" s="16"/>
+      <c r="AC13" s="16"/>
+      <c r="AD13" s="16"/>
+      <c r="AE13" s="16"/>
+      <c r="AF13" s="16"/>
+      <c r="AG13" s="16"/>
+      <c r="AH13" s="18"/>
+      <c r="AI13" s="16"/>
+      <c r="AJ13" s="16"/>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A14" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="T14" s="16">
+        <v>0.248</v>
+      </c>
+      <c r="U14" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="V14" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="W14" s="16"/>
+      <c r="X14" s="16"/>
+      <c r="Y14" s="16"/>
+      <c r="Z14" s="16"/>
+      <c r="AA14" s="16"/>
+      <c r="AB14" s="18"/>
+      <c r="AC14" s="16"/>
+      <c r="AD14" s="16"/>
+      <c r="AE14" s="16"/>
+      <c r="AF14" s="16"/>
+      <c r="AG14" s="16"/>
+      <c r="AH14" s="18"/>
+      <c r="AI14" s="16"/>
+      <c r="AJ14" s="16"/>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="18"/>
+      <c r="Q15" s="18"/>
+      <c r="R15" s="16"/>
+      <c r="T15" s="16"/>
+      <c r="U15" s="16"/>
+      <c r="V15" s="18"/>
+      <c r="W15" s="18"/>
+      <c r="X15" s="21"/>
+      <c r="Y15" s="21"/>
+      <c r="Z15" s="16"/>
+      <c r="AA15" s="16"/>
+      <c r="AB15" s="18"/>
+      <c r="AC15" s="18"/>
+      <c r="AD15" s="16"/>
+      <c r="AE15" s="16"/>
+      <c r="AF15" s="16"/>
+      <c r="AG15" s="16"/>
+      <c r="AH15" s="18"/>
+      <c r="AI15" s="18"/>
+      <c r="AJ15" s="16"/>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A16" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="T16" s="16"/>
+      <c r="U16" s="16"/>
+      <c r="V16" s="16"/>
+      <c r="W16" s="16"/>
+      <c r="X16" s="21"/>
+      <c r="Y16" s="21"/>
+      <c r="Z16" s="16"/>
+      <c r="AA16" s="16"/>
+      <c r="AB16" s="16"/>
+      <c r="AC16" s="16"/>
+      <c r="AD16" s="16"/>
+      <c r="AE16" s="16"/>
+      <c r="AF16" s="16"/>
+      <c r="AG16" s="16"/>
+      <c r="AH16" s="16"/>
+      <c r="AI16" s="16"/>
+      <c r="AJ16" s="16"/>
+    </row>
+    <row r="17" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="18"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="16"/>
+      <c r="T17" s="16">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="U17" s="16">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="V17" s="18">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="W17" s="16"/>
+      <c r="X17" s="16"/>
+      <c r="Y17" s="16"/>
+      <c r="Z17" s="16"/>
+      <c r="AA17" s="16"/>
+      <c r="AB17" s="18"/>
+      <c r="AC17" s="16"/>
+      <c r="AD17" s="16"/>
+      <c r="AE17" s="16"/>
+      <c r="AF17" s="16"/>
+      <c r="AG17" s="16"/>
+      <c r="AH17" s="18"/>
+      <c r="AI17" s="16"/>
+      <c r="AJ17" s="16"/>
+    </row>
+    <row r="18" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G18" s="21"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16"/>
+      <c r="P18" s="18"/>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="16"/>
+      <c r="T18" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U18" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V18" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W18" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X18" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y18" s="21"/>
+      <c r="Z18" s="16"/>
+      <c r="AA18" s="16"/>
+      <c r="AB18" s="18"/>
+      <c r="AC18" s="16"/>
+      <c r="AD18" s="16"/>
+      <c r="AE18" s="16"/>
+      <c r="AF18" s="16"/>
+      <c r="AG18" s="16"/>
+      <c r="AH18" s="18"/>
+      <c r="AI18" s="16"/>
+      <c r="AJ18" s="16"/>
+    </row>
+    <row r="19" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+      <c r="A19" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G19" s="21"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="16"/>
+      <c r="T19" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U19" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V19" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W19" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X19" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y19" s="21"/>
+      <c r="Z19" s="16"/>
+      <c r="AA19" s="16"/>
+      <c r="AB19" s="16"/>
+      <c r="AC19" s="16"/>
+      <c r="AD19" s="16"/>
+      <c r="AE19" s="16"/>
+      <c r="AF19" s="16"/>
+      <c r="AG19" s="16"/>
+      <c r="AH19" s="16"/>
+      <c r="AI19" s="16"/>
+      <c r="AJ19" s="30"/>
+    </row>
+    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A20" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G20" s="21"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="18"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="16"/>
+      <c r="T20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V20" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W20" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X20" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y20" s="21"/>
+      <c r="Z20" s="16"/>
+      <c r="AA20" s="16"/>
+      <c r="AB20" s="18"/>
+      <c r="AC20" s="16"/>
+      <c r="AD20" s="16"/>
+      <c r="AE20" s="16"/>
+      <c r="AF20" s="16"/>
+      <c r="AG20" s="16"/>
+      <c r="AH20" s="16"/>
+      <c r="AI20" s="16"/>
+      <c r="AJ20" s="16"/>
+    </row>
+    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A21" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G21" s="21"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="16"/>
+      <c r="O21" s="16"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="16"/>
+      <c r="R21" s="16"/>
+      <c r="T21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W21" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X21" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y21" s="21"/>
+      <c r="Z21" s="16"/>
+      <c r="AA21" s="16"/>
+      <c r="AB21" s="16"/>
+      <c r="AC21" s="16"/>
+      <c r="AD21" s="16"/>
+      <c r="AE21" s="16"/>
+      <c r="AF21" s="16"/>
+      <c r="AG21" s="16"/>
+      <c r="AH21" s="18"/>
+      <c r="AI21" s="16"/>
+      <c r="AJ21" s="16"/>
+    </row>
+    <row r="22" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G22" s="21"/>
+      <c r="H22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="M22" s="16"/>
+      <c r="N22" s="16"/>
+      <c r="O22" s="16"/>
+      <c r="P22" s="18"/>
+      <c r="Q22" s="16"/>
+      <c r="R22" s="16"/>
+      <c r="T22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W22" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X22" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y22" s="21"/>
+      <c r="Z22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC22" s="16"/>
+      <c r="AD22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE22" s="16"/>
+      <c r="AF22" s="16"/>
+      <c r="AG22" s="16"/>
+      <c r="AH22" s="18"/>
+      <c r="AI22" s="16"/>
+      <c r="AJ22" s="16"/>
+    </row>
+    <row r="23" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+      <c r="A23" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G23" s="21"/>
+      <c r="H23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="M23" s="16"/>
+      <c r="N23" s="16"/>
+      <c r="O23" s="16"/>
+      <c r="P23" s="18"/>
+      <c r="Q23" s="16"/>
+      <c r="R23" s="16"/>
+      <c r="T23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W23" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X23" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y23" s="21"/>
+      <c r="Z23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC23" s="16"/>
+      <c r="AD23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE23" s="16"/>
+      <c r="AF23" s="16"/>
+      <c r="AG23" s="16"/>
+      <c r="AH23" s="16"/>
+      <c r="AI23" s="16"/>
+      <c r="AJ23" s="16"/>
+    </row>
+    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A24" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G24" s="21"/>
+      <c r="H24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="M24" s="16"/>
+      <c r="N24" s="16"/>
+      <c r="O24" s="16"/>
+      <c r="P24" s="18"/>
+      <c r="Q24" s="16"/>
+      <c r="R24" s="16"/>
+      <c r="T24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W24" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X24" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y24" s="21"/>
+      <c r="Z24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC24" s="16"/>
+      <c r="AD24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE24" s="16"/>
+      <c r="AF24" s="16"/>
+      <c r="AG24" s="16"/>
+      <c r="AH24" s="18"/>
+      <c r="AI24" s="16"/>
+      <c r="AJ24" s="16"/>
+    </row>
+    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A25" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G25" s="21"/>
+      <c r="H25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="M25" s="16"/>
+      <c r="N25" s="16"/>
+      <c r="O25" s="16"/>
+      <c r="P25" s="18"/>
+      <c r="Q25" s="16"/>
+      <c r="R25" s="16"/>
+      <c r="T25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W25" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X25" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y25" s="21"/>
+      <c r="Z25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC25" s="16"/>
+      <c r="AD25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE25" s="16"/>
+      <c r="AF25" s="16"/>
+      <c r="AG25" s="16"/>
+      <c r="AH25" s="16"/>
+      <c r="AI25" s="16"/>
+      <c r="AJ25" s="16"/>
+    </row>
+    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A26" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G26" s="21"/>
+      <c r="H26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="M26" s="16"/>
+      <c r="N26" s="16"/>
+      <c r="O26" s="16"/>
+      <c r="P26" s="18"/>
+      <c r="Q26" s="16"/>
+      <c r="R26" s="16"/>
+      <c r="T26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W26" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X26" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y26" s="21"/>
+      <c r="Z26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC26" s="16"/>
+      <c r="AD26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE26" s="16"/>
+      <c r="AF26" s="16"/>
+      <c r="AG26" s="16"/>
+      <c r="AH26" s="18"/>
+      <c r="AI26" s="16"/>
+      <c r="AJ26" s="16"/>
+    </row>
+    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
+      <c r="N27" s="16"/>
+      <c r="O27" s="16"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="18"/>
+      <c r="R27" s="16"/>
+      <c r="T27" s="16"/>
+      <c r="U27" s="16"/>
+      <c r="V27" s="16"/>
+      <c r="W27" s="16"/>
+      <c r="X27" s="21"/>
+      <c r="Y27" s="21"/>
+      <c r="Z27" s="16"/>
+      <c r="AA27" s="16"/>
+      <c r="AB27" s="16"/>
+      <c r="AC27" s="16"/>
+      <c r="AD27" s="16"/>
+      <c r="AE27" s="16"/>
+      <c r="AF27" s="16"/>
+      <c r="AG27" s="16"/>
+      <c r="AH27" s="18"/>
+      <c r="AI27" s="18"/>
+      <c r="AJ27" s="16"/>
+    </row>
+    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A28" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
+      <c r="O28" s="16"/>
+      <c r="P28" s="16"/>
+      <c r="Q28" s="16"/>
+      <c r="R28" s="16"/>
+      <c r="T28" s="16"/>
+      <c r="U28" s="16"/>
+      <c r="V28" s="16"/>
+      <c r="W28" s="16"/>
+      <c r="X28" s="21"/>
+      <c r="Y28" s="21"/>
+      <c r="Z28" s="16"/>
+      <c r="AA28" s="16"/>
+      <c r="AB28" s="16"/>
+      <c r="AC28" s="16"/>
+      <c r="AD28" s="16"/>
+      <c r="AE28" s="16"/>
+      <c r="AF28" s="16"/>
+      <c r="AG28" s="16"/>
+      <c r="AH28" s="16"/>
+      <c r="AI28" s="16"/>
+      <c r="AJ28" s="16"/>
+    </row>
+    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A29" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="16"/>
+      <c r="L29" s="16"/>
+      <c r="M29" s="16"/>
+      <c r="N29" s="16"/>
+      <c r="O29" s="16"/>
+      <c r="P29" s="18"/>
+      <c r="Q29" s="16"/>
+      <c r="R29" s="16"/>
+      <c r="T29" s="16">
+        <v>13.827</v>
+      </c>
+      <c r="U29" s="16">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="V29" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="W29" s="16"/>
+      <c r="X29" s="16"/>
+      <c r="Y29" s="16"/>
+      <c r="Z29" s="16"/>
+      <c r="AA29" s="16"/>
+      <c r="AB29" s="18"/>
+      <c r="AC29" s="16"/>
+      <c r="AD29" s="16"/>
+      <c r="AE29" s="16"/>
+      <c r="AF29" s="16"/>
+      <c r="AG29" s="16"/>
+      <c r="AH29" s="18"/>
+      <c r="AI29" s="16"/>
+      <c r="AJ29" s="16"/>
+    </row>
+    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A30" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+      <c r="M30" s="16"/>
+      <c r="N30" s="16"/>
+      <c r="O30" s="16"/>
+      <c r="P30" s="18"/>
+      <c r="Q30" s="16"/>
+      <c r="R30" s="16"/>
+      <c r="T30" s="16">
+        <v>3.8889999999999998</v>
+      </c>
+      <c r="U30" s="16">
+        <v>6.3E-2</v>
+      </c>
+      <c r="V30" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="W30" s="16"/>
+      <c r="X30" s="16"/>
+      <c r="Y30" s="16"/>
+      <c r="Z30" s="16"/>
+      <c r="AA30" s="16"/>
+      <c r="AB30" s="18"/>
+      <c r="AC30" s="16"/>
+      <c r="AD30" s="16"/>
+      <c r="AE30" s="16"/>
+      <c r="AF30" s="16"/>
+      <c r="AG30" s="16"/>
+      <c r="AH30" s="18"/>
+      <c r="AI30" s="16"/>
+      <c r="AJ30" s="16"/>
+    </row>
+    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A31" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F31" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G31" s="21"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="18"/>
+      <c r="K31" s="16"/>
+      <c r="L31" s="16"/>
+      <c r="M31" s="16"/>
+      <c r="N31" s="16"/>
+      <c r="O31" s="16"/>
+      <c r="P31" s="18"/>
+      <c r="Q31" s="16"/>
+      <c r="R31" s="16"/>
+      <c r="T31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="X31" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y31" s="21"/>
+      <c r="Z31" s="16"/>
+      <c r="AA31" s="16"/>
+      <c r="AB31" s="18"/>
+      <c r="AC31" s="16"/>
+      <c r="AD31" s="16"/>
+      <c r="AE31" s="16"/>
+      <c r="AF31" s="16"/>
+      <c r="AG31" s="16"/>
+      <c r="AH31" s="18"/>
+      <c r="AI31" s="16"/>
+      <c r="AJ31" s="16"/>
+    </row>
+    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="A32" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G32" s="21"/>
+      <c r="H32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K32" s="16"/>
+      <c r="L32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="M32" s="16"/>
+      <c r="N32" s="16"/>
+      <c r="O32" s="16"/>
+      <c r="P32" s="18"/>
+      <c r="Q32" s="16"/>
+      <c r="R32" s="16"/>
+      <c r="T32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W32" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X32" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y32" s="21"/>
+      <c r="Z32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC32" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD32" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE32" s="16"/>
+      <c r="AF32" s="16"/>
+      <c r="AG32" s="16"/>
+      <c r="AH32" s="18"/>
+      <c r="AI32" s="16"/>
+      <c r="AJ32" s="16"/>
+    </row>
+    <row r="33" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A33" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="16"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="14"/>
+      <c r="P33" s="14"/>
+      <c r="Q33" s="14"/>
+      <c r="R33" s="14"/>
+      <c r="S33" s="16"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="14"/>
+      <c r="V33" s="14"/>
+      <c r="W33" s="14"/>
+      <c r="X33" s="14"/>
+      <c r="Y33" s="16"/>
+      <c r="Z33" s="14"/>
+      <c r="AA33" s="14"/>
+      <c r="AB33" s="14"/>
+      <c r="AC33" s="14"/>
+      <c r="AD33" s="14"/>
+      <c r="AE33" s="16"/>
+      <c r="AF33" s="14"/>
+      <c r="AG33" s="14"/>
+      <c r="AH33" s="14"/>
+      <c r="AI33" s="14"/>
+      <c r="AJ33" s="14"/>
+      <c r="AK33" s="16"/>
+      <c r="AL33" s="16"/>
+      <c r="AM33" s="16"/>
+    </row>
+    <row r="34" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A34" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="B34" s="31">
+        <v>74058.118000000002</v>
+      </c>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="27"/>
+      <c r="H34" s="31">
+        <v>83016.937999999995</v>
+      </c>
+      <c r="I34" s="31"/>
+      <c r="J34" s="31"/>
+      <c r="K34" s="31"/>
+      <c r="L34" s="31"/>
+      <c r="M34" s="27"/>
+      <c r="N34" s="31">
+        <v>94345.274999999994</v>
+      </c>
+      <c r="O34" s="31"/>
+      <c r="P34" s="31"/>
+      <c r="Q34" s="31"/>
+      <c r="R34" s="31"/>
+      <c r="S34" s="15"/>
+      <c r="T34" s="36">
+        <v>37782.404000000002</v>
+      </c>
+      <c r="U34" s="36"/>
+      <c r="V34" s="36"/>
+      <c r="W34" s="36"/>
+      <c r="X34" s="36"/>
+      <c r="Y34" s="27"/>
+      <c r="Z34" s="31"/>
+      <c r="AA34" s="31"/>
+      <c r="AB34" s="31"/>
+      <c r="AC34" s="31"/>
+      <c r="AD34" s="31"/>
+      <c r="AE34" s="27"/>
+      <c r="AF34" s="31"/>
+      <c r="AG34" s="31"/>
+      <c r="AH34" s="31"/>
+      <c r="AI34" s="31"/>
+      <c r="AJ34" s="31"/>
+      <c r="AK34" s="16"/>
+      <c r="AL34" s="16"/>
+      <c r="AM34" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="H34:L34"/>
+    <mergeCell ref="N34:R34"/>
+    <mergeCell ref="T34:X34"/>
+    <mergeCell ref="Z34:AD34"/>
+    <mergeCell ref="AF34:AJ34"/>
+    <mergeCell ref="B2:R2"/>
+    <mergeCell ref="T2:AJ2"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B2:R2"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="N3:R3"/>
-    <mergeCell ref="T2:AJ2"/>
     <mergeCell ref="T3:X3"/>
     <mergeCell ref="Z3:AD3"/>
     <mergeCell ref="AF3:AJ3"/>
@@ -4756,56 +6578,56 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57A86273-0E84-8246-B3ED-A023C6721217}">
   <dimension ref="A1:M38"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="15"/>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="G3" s="27" t="s">
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="G3" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="16"/>
       <c r="B4" s="17" t="s">
         <v>90</v>
@@ -4832,7 +6654,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
         <v>85</v>
       </c>
@@ -4845,7 +6667,7 @@
       <c r="I5" s="16"/>
       <c r="J5" s="16"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>96</v>
       </c>
@@ -4858,7 +6680,7 @@
       <c r="I6" s="18"/>
       <c r="J6" s="16"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>97</v>
       </c>
@@ -4871,7 +6693,7 @@
       <c r="I7" s="18"/>
       <c r="J7" s="16"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
         <v>86</v>
       </c>
@@ -4884,7 +6706,7 @@
       <c r="I8" s="16"/>
       <c r="J8" s="16"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>98</v>
       </c>
@@ -4897,7 +6719,7 @@
       <c r="I9" s="18"/>
       <c r="J9" s="16"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>99</v>
       </c>
@@ -4914,7 +6736,7 @@
       <c r="I10" s="18"/>
       <c r="J10" s="16"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>100</v>
       </c>
@@ -4931,7 +6753,7 @@
       <c r="I11" s="18"/>
       <c r="J11" s="16"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
         <v>101</v>
       </c>
@@ -4948,7 +6770,7 @@
       <c r="I12" s="18"/>
       <c r="J12" s="16"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="16" t="s">
         <v>88</v>
       </c>
@@ -4965,7 +6787,7 @@
       <c r="I13" s="18"/>
       <c r="J13" s="16"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
         <v>87</v>
       </c>
@@ -4978,7 +6800,7 @@
       <c r="I14" s="16"/>
       <c r="J14" s="16"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>102</v>
       </c>
@@ -4995,7 +6817,7 @@
       <c r="I15" s="18"/>
       <c r="J15" s="16"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>103</v>
       </c>
@@ -5008,7 +6830,7 @@
       <c r="I16" s="18"/>
       <c r="J16" s="16"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>104</v>
       </c>
@@ -5021,7 +6843,7 @@
       <c r="I17" s="18"/>
       <c r="J17" s="16"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
         <v>107</v>
       </c>
@@ -5038,7 +6860,7 @@
       <c r="I18" s="18"/>
       <c r="J18" s="16"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
         <v>108</v>
       </c>
@@ -5055,7 +6877,7 @@
       <c r="I19" s="18"/>
       <c r="J19" s="16"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>105</v>
       </c>
@@ -5068,7 +6890,7 @@
       <c r="I20" s="18"/>
       <c r="J20" s="16"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="17" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>106</v>
       </c>
@@ -5081,7 +6903,7 @@
       <c r="I21" s="18"/>
       <c r="J21" s="16"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
         <v>110</v>
       </c>
@@ -5098,7 +6920,7 @@
       <c r="I22" s="18"/>
       <c r="J22" s="16"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="16" t="s">
         <v>109</v>
       </c>
@@ -5115,7 +6937,7 @@
       <c r="I23" s="18"/>
       <c r="J23" s="16"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
         <v>111</v>
       </c>
@@ -5128,7 +6950,7 @@
       <c r="I24" s="18"/>
       <c r="J24" s="16"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="17" t="s">
         <v>82</v>
       </c>
@@ -5141,7 +6963,7 @@
       <c r="I25" s="16"/>
       <c r="J25" s="16"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
         <v>84</v>
       </c>
@@ -5158,7 +6980,7 @@
       <c r="I26" s="18"/>
       <c r="J26" s="16"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
         <v>89</v>
       </c>
@@ -5175,7 +6997,7 @@
       <c r="I27" s="18"/>
       <c r="J27" s="16"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="16" t="s">
         <v>93</v>
       </c>
@@ -5194,7 +7016,7 @@
       <c r="I28" s="18"/>
       <c r="J28" s="16"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="16" t="s">
         <v>112</v>
       </c>
@@ -5207,7 +7029,7 @@
       <c r="I29" s="18"/>
       <c r="J29" s="16"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="17" t="s">
         <v>83</v>
       </c>
@@ -5220,7 +7042,7 @@
       <c r="I30" s="16"/>
       <c r="J30" s="16"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="17" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>96</v>
       </c>
@@ -5239,7 +7061,7 @@
       <c r="I31" s="18"/>
       <c r="J31" s="16"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="17" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
         <v>97</v>
       </c>
@@ -5258,7 +7080,7 @@
       <c r="I32" s="18"/>
       <c r="J32" s="16"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="16" t="s">
         <v>84</v>
       </c>
@@ -5275,7 +7097,7 @@
       <c r="I33" s="18"/>
       <c r="J33" s="16"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A34" s="16" t="s">
         <v>89</v>
       </c>
@@ -5292,7 +7114,7 @@
       <c r="I34" s="18"/>
       <c r="J34" s="16"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A35" s="16" t="s">
         <v>93</v>
       </c>
@@ -5305,7 +7127,7 @@
       <c r="I35" s="18"/>
       <c r="J35" s="16"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A36" s="16" t="s">
         <v>112</v>
       </c>
@@ -5316,7 +7138,7 @@
       <c r="H36" s="16"/>
       <c r="I36" s="18"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="20" t="s">
         <v>117</v>
       </c>
@@ -5333,7 +7155,7 @@
       <c r="L37" s="16"/>
       <c r="M37" s="16"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A38" s="15" t="s">
         <v>118</v>
       </c>
@@ -5361,57 +7183,57 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{540507A6-720C-0B43-804E-087FEE710926}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.875" customWidth="1"/>
-    <col min="2" max="2" width="18.875" customWidth="1"/>
-    <col min="3" max="3" width="19.125" customWidth="1"/>
+    <col min="1" max="1" width="19.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="23" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="24"/>
     </row>
-    <row r="3" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="24" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="24" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="24"/>
     </row>
-    <row r="6" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="24"/>
     </row>
-    <row r="7" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="23" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="24" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B11" s="23" t="s">
         <v>129</v>
       </c>
@@ -5419,7 +7241,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>126</v>
       </c>
@@ -5430,7 +7252,7 @@
         <v>-1.4E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>127</v>
       </c>
@@ -5441,7 +7263,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>128</v>
       </c>
@@ -5452,7 +7274,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>133</v>
       </c>
@@ -5463,17 +7285,17 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="23" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="24" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B19" s="23" t="s">
         <v>129</v>
       </c>
@@ -5481,7 +7303,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>126</v>
       </c>
@@ -5492,7 +7314,7 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>127</v>
       </c>
@@ -5503,7 +7325,7 @@
         <v>-1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>128</v>
       </c>
@@ -5514,7 +7336,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>133</v>
       </c>
@@ -5525,7 +7347,7 @@
         <v>-1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E25" s="23" t="s">
         <v>132</v>
       </c>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nchaku/Documents/GitHub/pubertybrain/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nchaku\Documents\GitHub\pubertybrain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DF775CB-4F28-1742-9002-F940C250CB44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0C5C2D-21F6-4142-814F-EFC173B4BD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13360" yWindow="500" windowWidth="15440" windowHeight="16400" firstSheet="1" activeTab="5" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptive table" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="143">
   <si>
     <t>16.10 (2.98)</t>
   </si>
@@ -722,6 +722,119 @@
   </si>
   <si>
     <t>ULCI</t>
+  </si>
+  <si>
+    <t>Table 3. Subcortical volume by sex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Timing on Quadratic Slope</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   Intercept</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> with Quadratic Slope</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   Quadratic Slope</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   Slope</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">      with Quadratic Slope</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   Quadratic Slope</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">b </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>with Tempo</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -885,7 +998,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -933,23 +1046,20 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1531,20 +1641,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39987BE7-3659-524A-81AE-D479F97EF698}">
   <dimension ref="A1:F29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="9"/>
       <c r="B2" s="10" t="s">
         <v>63</v>
@@ -1562,7 +1672,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="11" t="s">
         <v>69</v>
@@ -1576,7 +1686,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>60</v>
       </c>
@@ -1586,7 +1696,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>61</v>
       </c>
@@ -1606,7 +1716,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>62</v>
       </c>
@@ -1626,7 +1736,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>58</v>
       </c>
@@ -1646,7 +1756,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>59</v>
       </c>
@@ -1656,7 +1766,7 @@
       <c r="E8" s="12"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>61</v>
       </c>
@@ -1676,7 +1786,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>66</v>
       </c>
@@ -1696,7 +1806,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>67</v>
       </c>
@@ -1716,7 +1826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>62</v>
       </c>
@@ -1736,7 +1846,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>68</v>
       </c>
@@ -1746,7 +1856,7 @@
       <c r="E13" s="12"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>73</v>
       </c>
@@ -1766,7 +1876,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>74</v>
       </c>
@@ -1786,7 +1896,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>75</v>
       </c>
@@ -1806,7 +1916,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>76</v>
       </c>
@@ -1824,7 +1934,7 @@
       </c>
       <c r="F17" s="19"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>71</v>
       </c>
@@ -1834,7 +1944,7 @@
       <c r="E18" s="12"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>61</v>
       </c>
@@ -1854,7 +1964,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>66</v>
       </c>
@@ -1874,7 +1984,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>67</v>
       </c>
@@ -1894,7 +2004,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>62</v>
       </c>
@@ -1914,7 +2024,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>72</v>
       </c>
@@ -1924,7 +2034,7 @@
       <c r="E23" s="12"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>61</v>
       </c>
@@ -1944,7 +2054,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>66</v>
       </c>
@@ -1964,7 +2074,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>67</v>
       </c>
@@ -1984,7 +2094,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>62</v>
       </c>
@@ -2004,7 +2114,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2012,7 +2122,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2028,9 +2138,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A749072B-F938-0F49-BE23-243603B2B3D0}">
   <dimension ref="M2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="13:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M2" t="s">
         <v>113</v>
       </c>
@@ -2044,7 +2154,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45875D41-9C56-AA4E-A18A-2D3A4CE169B3}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2054,7 +2164,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A5153E-6E5C-054A-8ACA-5118463B96C5}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2064,142 +2174,142 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA86F85-A8D4-F648-84C3-730F1A42C846}">
   <dimension ref="A1:AM34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.1640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="1.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.625" style="1" customWidth="1"/>
     <col min="11" max="11" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="1.1640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="1.125" style="1" customWidth="1"/>
     <col min="14" max="14" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.6640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.625" style="1" customWidth="1"/>
     <col min="17" max="17" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="0.83203125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="0.875" style="1" customWidth="1"/>
     <col min="20" max="20" width="8.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="5.6640625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="5.625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="6.125" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="1" style="1" customWidth="1"/>
     <col min="26" max="26" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.6640625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.625" style="1" customWidth="1"/>
     <col min="29" max="30" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="1.1640625" style="1" customWidth="1"/>
+    <col min="31" max="31" width="1.125" style="1" customWidth="1"/>
     <col min="32" max="32" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="5.6640625" style="1" customWidth="1"/>
-    <col min="36" max="36" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="5.625" style="1" customWidth="1"/>
+    <col min="36" max="36" width="6.125" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
       <c r="S2" s="9"/>
-      <c r="T2" s="32" t="s">
+      <c r="T2" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="32"/>
-      <c r="X2" s="32"/>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="32"/>
-      <c r="AA2" s="32"/>
-      <c r="AB2" s="32"/>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="31"/>
+      <c r="Z2" s="31"/>
+      <c r="AA2" s="31"/>
+      <c r="AB2" s="31"/>
+      <c r="AC2" s="31"/>
+      <c r="AD2" s="31"/>
+      <c r="AE2" s="31"/>
+      <c r="AF2" s="31"/>
+      <c r="AG2" s="31"/>
+      <c r="AH2" s="31"/>
+      <c r="AI2" s="31"/>
+      <c r="AJ2" s="31"/>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="16"/>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
       <c r="G3" s="28"/>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
       <c r="M3" s="28"/>
-      <c r="N3" s="32" t="s">
+      <c r="N3" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="32"/>
-      <c r="T3" s="33" t="s">
+      <c r="O3" s="31"/>
+      <c r="P3" s="31"/>
+      <c r="Q3" s="31"/>
+      <c r="R3" s="31"/>
+      <c r="T3" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="U3" s="33"/>
-      <c r="V3" s="33"/>
-      <c r="W3" s="33"/>
-      <c r="X3" s="33"/>
+      <c r="U3" s="32"/>
+      <c r="V3" s="32"/>
+      <c r="W3" s="32"/>
+      <c r="X3" s="32"/>
       <c r="Y3" s="28"/>
-      <c r="Z3" s="32" t="s">
+      <c r="Z3" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="AA3" s="32"/>
-      <c r="AB3" s="32"/>
-      <c r="AC3" s="32"/>
-      <c r="AD3" s="32"/>
+      <c r="AA3" s="31"/>
+      <c r="AB3" s="31"/>
+      <c r="AC3" s="31"/>
+      <c r="AD3" s="31"/>
       <c r="AE3" s="28"/>
-      <c r="AF3" s="32" t="s">
+      <c r="AF3" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="AG3" s="32"/>
-      <c r="AH3" s="32"/>
-      <c r="AI3" s="32"/>
-      <c r="AJ3" s="32"/>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AG3" s="31"/>
+      <c r="AH3" s="31"/>
+      <c r="AI3" s="31"/>
+      <c r="AJ3" s="31"/>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="15"/>
       <c r="B4" s="29" t="s">
         <v>90</v>
@@ -2297,7 +2407,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>85</v>
       </c>
@@ -2336,7 +2446,7 @@
       <c r="AI5" s="16"/>
       <c r="AJ5" s="16"/>
     </row>
-    <row r="6" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>96</v>
       </c>
@@ -2435,7 +2545,7 @@
         <v>12.236000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>97</v>
       </c>
@@ -2534,7 +2644,7 @@
         <v>-7.7560000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -2571,7 +2681,7 @@
       <c r="AI8" s="18"/>
       <c r="AJ8" s="16"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>86</v>
       </c>
@@ -2610,7 +2720,7 @@
       <c r="AI9" s="16"/>
       <c r="AJ9" s="16"/>
     </row>
-    <row r="10" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>98</v>
       </c>
@@ -2709,7 +2819,7 @@
         <v>-0.24</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>99</v>
       </c>
@@ -2808,7 +2918,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>100</v>
       </c>
@@ -2907,7 +3017,7 @@
         <v>0.14899999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>101</v>
       </c>
@@ -3006,7 +3116,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>88</v>
       </c>
@@ -3105,7 +3215,7 @@
         <v>0.28799999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="16"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -3142,7 +3252,7 @@
       <c r="AI15" s="18"/>
       <c r="AJ15" s="16"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>87</v>
       </c>
@@ -3181,7 +3291,7 @@
       <c r="AI16" s="16"/>
       <c r="AJ16" s="16"/>
     </row>
-    <row r="17" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>102</v>
       </c>
@@ -3280,7 +3390,7 @@
         <v>0.443</v>
       </c>
     </row>
-    <row r="18" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>103</v>
       </c>
@@ -3379,7 +3489,7 @@
         <v>-0.10299999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>104</v>
       </c>
@@ -3478,7 +3588,7 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>107</v>
       </c>
@@ -3577,7 +3687,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>108</v>
       </c>
@@ -3676,7 +3786,7 @@
         <v>-0.13600000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>105</v>
       </c>
@@ -3773,7 +3883,7 @@
         <v>0.156</v>
       </c>
     </row>
-    <row r="23" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>106</v>
       </c>
@@ -3870,7 +3980,7 @@
         <v>-1.6E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>110</v>
       </c>
@@ -3967,7 +4077,7 @@
         <v>0.112</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>109</v>
       </c>
@@ -4064,7 +4174,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>111</v>
       </c>
@@ -4161,7 +4271,7 @@
         <v>-4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -4198,7 +4308,7 @@
       <c r="AI27" s="18"/>
       <c r="AJ27" s="16"/>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>82</v>
       </c>
@@ -4237,7 +4347,7 @@
       <c r="AI28" s="16"/>
       <c r="AJ28" s="16"/>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>84</v>
       </c>
@@ -4336,7 +4446,7 @@
         <v>14.164999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
         <v>89</v>
       </c>
@@ -4435,7 +4545,7 @@
         <v>4.1660000000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>93</v>
       </c>
@@ -4534,7 +4644,7 @@
         <v>1.0549999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
         <v>112</v>
       </c>
@@ -4631,7 +4741,7 @@
         <v>4.202</v>
       </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
         <v>117</v>
       </c>
@@ -4674,63 +4784,69 @@
       <c r="AL33" s="16"/>
       <c r="AM33" s="16"/>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="B34" s="31">
+      <c r="B34" s="33">
         <v>74058.118000000002</v>
       </c>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="33"/>
       <c r="G34" s="27"/>
-      <c r="H34" s="31">
+      <c r="H34" s="33">
         <v>83016.937999999995</v>
       </c>
-      <c r="I34" s="31"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="31"/>
-      <c r="L34" s="31"/>
+      <c r="I34" s="33"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="33"/>
+      <c r="L34" s="33"/>
       <c r="M34" s="27"/>
-      <c r="N34" s="31">
+      <c r="N34" s="33">
         <v>94345.274999999994</v>
       </c>
-      <c r="O34" s="31"/>
-      <c r="P34" s="31"/>
-      <c r="Q34" s="31"/>
-      <c r="R34" s="31"/>
+      <c r="O34" s="33"/>
+      <c r="P34" s="33"/>
+      <c r="Q34" s="33"/>
+      <c r="R34" s="33"/>
       <c r="S34" s="15"/>
-      <c r="T34" s="31">
+      <c r="T34" s="33">
         <v>83167.763000000006</v>
       </c>
-      <c r="U34" s="31"/>
-      <c r="V34" s="31"/>
-      <c r="W34" s="31"/>
-      <c r="X34" s="31"/>
+      <c r="U34" s="33"/>
+      <c r="V34" s="33"/>
+      <c r="W34" s="33"/>
+      <c r="X34" s="33"/>
       <c r="Y34" s="27"/>
-      <c r="Z34" s="31">
+      <c r="Z34" s="33">
         <v>93083.505999999994</v>
       </c>
-      <c r="AA34" s="31"/>
-      <c r="AB34" s="31"/>
-      <c r="AC34" s="31"/>
-      <c r="AD34" s="31"/>
+      <c r="AA34" s="33"/>
+      <c r="AB34" s="33"/>
+      <c r="AC34" s="33"/>
+      <c r="AD34" s="33"/>
       <c r="AE34" s="27"/>
-      <c r="AF34" s="31">
+      <c r="AF34" s="33">
         <v>105770.462</v>
       </c>
-      <c r="AG34" s="31"/>
-      <c r="AH34" s="31"/>
-      <c r="AI34" s="31"/>
-      <c r="AJ34" s="31"/>
+      <c r="AG34" s="33"/>
+      <c r="AH34" s="33"/>
+      <c r="AI34" s="33"/>
+      <c r="AJ34" s="33"/>
       <c r="AK34" s="16"/>
       <c r="AL34" s="16"/>
       <c r="AM34" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="AF34:AJ34"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="H34:L34"/>
+    <mergeCell ref="T34:X34"/>
+    <mergeCell ref="N34:R34"/>
+    <mergeCell ref="Z34:AD34"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="H3:L3"/>
@@ -4739,12 +4855,6 @@
     <mergeCell ref="T3:X3"/>
     <mergeCell ref="Z3:AD3"/>
     <mergeCell ref="AF3:AJ3"/>
-    <mergeCell ref="AF34:AJ34"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="H34:L34"/>
-    <mergeCell ref="T34:X34"/>
-    <mergeCell ref="N34:R34"/>
-    <mergeCell ref="Z34:AD34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -4753,144 +4863,142 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CD5CF7F-81D6-D24D-8228-B4C578C35D65}">
-  <dimension ref="A1:AM34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AM39"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24" style="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.625" style="1" customWidth="1"/>
     <col min="11" max="11" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="1.1640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="1.125" style="1" customWidth="1"/>
     <col min="14" max="14" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.6640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.625" style="1" customWidth="1"/>
     <col min="17" max="17" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="0.83203125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="6.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.6640625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="0.875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="1" style="1" customWidth="1"/>
     <col min="26" max="26" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.6640625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.625" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="30" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="1.1640625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="5.6640625" style="1" customWidth="1"/>
-    <col min="36" max="36" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="1.125" style="1" customWidth="1"/>
+    <col min="32" max="32" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.625" style="1" customWidth="1"/>
+    <col min="35" max="36" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
       <c r="S2" s="9"/>
-      <c r="T2" s="32" t="s">
+      <c r="T2" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="32"/>
-      <c r="X2" s="32"/>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="32"/>
-      <c r="AA2" s="32"/>
-      <c r="AB2" s="32"/>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="U2" s="31"/>
+      <c r="V2" s="31"/>
+      <c r="W2" s="31"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="31"/>
+      <c r="Z2" s="31"/>
+      <c r="AA2" s="31"/>
+      <c r="AB2" s="31"/>
+      <c r="AC2" s="31"/>
+      <c r="AD2" s="31"/>
+      <c r="AE2" s="31"/>
+      <c r="AF2" s="31"/>
+      <c r="AG2" s="31"/>
+      <c r="AH2" s="31"/>
+      <c r="AI2" s="31"/>
+      <c r="AJ2" s="31"/>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="16"/>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="31" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
       <c r="G3" s="28"/>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
       <c r="M3" s="28"/>
-      <c r="N3" s="32" t="s">
+      <c r="N3" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="32"/>
-      <c r="T3" s="33" t="s">
+      <c r="O3" s="31"/>
+      <c r="P3" s="31"/>
+      <c r="Q3" s="31"/>
+      <c r="R3" s="31"/>
+      <c r="T3" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="U3" s="33"/>
-      <c r="V3" s="33"/>
-      <c r="W3" s="33"/>
-      <c r="X3" s="33"/>
+      <c r="U3" s="32"/>
+      <c r="V3" s="32"/>
+      <c r="W3" s="32"/>
+      <c r="X3" s="32"/>
       <c r="Y3" s="28"/>
-      <c r="Z3" s="32" t="s">
+      <c r="Z3" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="AA3" s="32"/>
-      <c r="AB3" s="32"/>
-      <c r="AC3" s="32"/>
-      <c r="AD3" s="32"/>
+      <c r="AA3" s="31"/>
+      <c r="AB3" s="31"/>
+      <c r="AC3" s="31"/>
+      <c r="AD3" s="31"/>
       <c r="AE3" s="28"/>
-      <c r="AF3" s="32" t="s">
+      <c r="AF3" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="AG3" s="32"/>
-      <c r="AH3" s="32"/>
-      <c r="AI3" s="32"/>
-      <c r="AJ3" s="32"/>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AG3" s="31"/>
+      <c r="AH3" s="31"/>
+      <c r="AI3" s="31"/>
+      <c r="AJ3" s="31"/>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="15"/>
       <c r="B4" s="29" t="s">
         <v>90</v>
@@ -4988,7 +5096,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>85</v>
       </c>
@@ -5027,15 +5135,25 @@
       <c r="AI5" s="16"/>
       <c r="AJ5" s="16"/>
     </row>
-    <row r="6" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
+      <c r="B6" s="16">
+        <v>13.944000000000001</v>
+      </c>
+      <c r="C6" s="16">
+        <v>0.247</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="16">
+        <v>13.538</v>
+      </c>
+      <c r="F6" s="16">
+        <v>14.35</v>
+      </c>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
       <c r="I6" s="16"/>
@@ -5057,30 +5175,64 @@
       <c r="V6" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="W6" s="16"/>
-      <c r="X6" s="16"/>
+      <c r="W6" s="16">
+        <v>13.037000000000001</v>
+      </c>
+      <c r="X6" s="16">
+        <v>13.746</v>
+      </c>
       <c r="Y6" s="16"/>
-      <c r="Z6" s="16"/>
-      <c r="AA6" s="16"/>
-      <c r="AB6" s="18"/>
-      <c r="AC6" s="16"/>
-      <c r="AD6" s="16"/>
+      <c r="Z6" s="16">
+        <v>13.525</v>
+      </c>
+      <c r="AA6" s="16">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="AB6" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC6" s="16">
+        <v>13.173999999999999</v>
+      </c>
+      <c r="AD6" s="16">
+        <v>13.875999999999999</v>
+      </c>
       <c r="AE6" s="16"/>
-      <c r="AF6" s="16"/>
-      <c r="AG6" s="16"/>
-      <c r="AH6" s="18"/>
-      <c r="AI6" s="16"/>
-      <c r="AJ6" s="16"/>
-    </row>
-    <row r="7" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+      <c r="AF6" s="16">
+        <v>13.525</v>
+      </c>
+      <c r="AG6" s="16">
+        <v>0.21299999999999999</v>
+      </c>
+      <c r="AH6" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI6" s="16">
+        <v>13.173999999999999</v>
+      </c>
+      <c r="AJ6" s="16">
+        <v>13.875999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
+      <c r="B7" s="16">
+        <v>-7.5229999999999997</v>
+      </c>
+      <c r="C7" s="16">
+        <v>0.48599999999999999</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="16">
+        <v>-8.3209999999999997</v>
+      </c>
+      <c r="F7" s="16">
+        <v>-6.7240000000000002</v>
+      </c>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
       <c r="I7" s="16"/>
@@ -5102,196 +5254,288 @@
       <c r="V7" s="18">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="W7" s="16"/>
-      <c r="X7" s="16"/>
+      <c r="W7" s="16">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="X7" s="16">
+        <v>2.1</v>
+      </c>
       <c r="Y7" s="16"/>
-      <c r="Z7" s="16"/>
-      <c r="AA7" s="16"/>
-      <c r="AB7" s="18"/>
-      <c r="AC7" s="16"/>
-      <c r="AD7" s="16"/>
+      <c r="Z7" s="16">
+        <v>1.236</v>
+      </c>
+      <c r="AA7" s="16">
+        <v>0.53800000000000003</v>
+      </c>
+      <c r="AB7" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="AC7" s="16">
+        <v>0.35099999999999998</v>
+      </c>
+      <c r="AD7" s="16">
+        <v>2.121</v>
+      </c>
       <c r="AE7" s="16"/>
-      <c r="AF7" s="16"/>
-      <c r="AG7" s="16"/>
-      <c r="AH7" s="18"/>
-      <c r="AI7" s="16"/>
-      <c r="AJ7" s="16"/>
-    </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A8" s="16"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
+      <c r="AF7" s="16">
+        <v>1.2370000000000001</v>
+      </c>
+      <c r="AG7" s="16">
+        <v>0.53800000000000003</v>
+      </c>
+      <c r="AH7" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AI7" s="16">
+        <v>0.35199999999999998</v>
+      </c>
+      <c r="AJ7" s="16">
+        <v>2.1219999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="B8" s="16">
+        <v>-0.253</v>
+      </c>
+      <c r="C8" s="16">
+        <v>1.236</v>
+      </c>
+      <c r="D8" s="18">
+        <v>0.83699999999999997</v>
+      </c>
+      <c r="E8" s="16">
+        <v>-2.286</v>
+      </c>
+      <c r="F8" s="16">
+        <v>1.7789999999999999</v>
+      </c>
+      <c r="G8" s="16"/>
       <c r="H8" s="16"/>
       <c r="I8" s="16"/>
       <c r="J8" s="18"/>
-      <c r="K8" s="18"/>
+      <c r="K8" s="16"/>
       <c r="L8" s="16"/>
       <c r="M8" s="16"/>
       <c r="N8" s="16"/>
       <c r="O8" s="16"/>
       <c r="P8" s="18"/>
-      <c r="Q8" s="18"/>
+      <c r="Q8" s="16"/>
       <c r="R8" s="16"/>
       <c r="T8" s="16"/>
       <c r="U8" s="16"/>
       <c r="V8" s="18"/>
-      <c r="W8" s="18"/>
-      <c r="X8" s="21"/>
-      <c r="Y8" s="21"/>
+      <c r="W8" s="16"/>
+      <c r="X8" s="16"/>
+      <c r="Y8" s="16"/>
       <c r="Z8" s="16"/>
       <c r="AA8" s="16"/>
-      <c r="AB8" s="18"/>
-      <c r="AC8" s="18"/>
+      <c r="AB8" s="16"/>
+      <c r="AC8" s="16"/>
       <c r="AD8" s="16"/>
       <c r="AE8" s="16"/>
       <c r="AF8" s="16"/>
       <c r="AG8" s="16"/>
-      <c r="AH8" s="18"/>
-      <c r="AI8" s="18"/>
+      <c r="AH8" s="16"/>
+      <c r="AI8" s="16"/>
       <c r="AJ8" s="16"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A9" s="17" t="s">
-        <v>86</v>
-      </c>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A9" s="16"/>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
       <c r="F9" s="21"/>
       <c r="G9" s="21"/>
       <c r="H9" s="16"/>
       <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
-      <c r="K9" s="16"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
       <c r="L9" s="16"/>
       <c r="M9" s="16"/>
       <c r="N9" s="16"/>
       <c r="O9" s="16"/>
-      <c r="P9" s="16"/>
-      <c r="Q9" s="16"/>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="18"/>
       <c r="R9" s="16"/>
       <c r="T9" s="16"/>
       <c r="U9" s="16"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
+      <c r="V9" s="18"/>
+      <c r="W9" s="18"/>
       <c r="X9" s="21"/>
       <c r="Y9" s="21"/>
       <c r="Z9" s="16"/>
       <c r="AA9" s="16"/>
-      <c r="AB9" s="16"/>
-      <c r="AC9" s="16"/>
+      <c r="AB9" s="18"/>
+      <c r="AC9" s="18"/>
       <c r="AD9" s="16"/>
       <c r="AE9" s="16"/>
       <c r="AF9" s="16"/>
       <c r="AG9" s="16"/>
-      <c r="AH9" s="16"/>
-      <c r="AI9" s="16"/>
+      <c r="AH9" s="18"/>
+      <c r="AI9" s="18"/>
       <c r="AJ9" s="16"/>
     </row>
-    <row r="10" spans="1:36" ht="17" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
-        <v>98</v>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
+        <v>86</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
-      <c r="D10" s="18"/>
+      <c r="D10" s="16"/>
       <c r="E10" s="16"/>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
       <c r="H10" s="16"/>
       <c r="I10" s="16"/>
-      <c r="J10" s="18"/>
+      <c r="J10" s="16"/>
       <c r="K10" s="16"/>
       <c r="L10" s="16"/>
       <c r="M10" s="16"/>
       <c r="N10" s="16"/>
       <c r="O10" s="16"/>
-      <c r="P10" s="18"/>
+      <c r="P10" s="16"/>
       <c r="Q10" s="16"/>
       <c r="R10" s="16"/>
-      <c r="T10" s="16">
-        <v>0.318</v>
-      </c>
-      <c r="U10" s="16">
-        <v>0.05</v>
-      </c>
-      <c r="V10" s="18" t="s">
-        <v>24</v>
-      </c>
+      <c r="T10" s="16"/>
+      <c r="U10" s="16"/>
+      <c r="V10" s="16"/>
       <c r="W10" s="16"/>
-      <c r="X10" s="16"/>
-      <c r="Y10" s="16"/>
+      <c r="X10" s="21"/>
+      <c r="Y10" s="21"/>
       <c r="Z10" s="16"/>
       <c r="AA10" s="16"/>
-      <c r="AB10" s="18"/>
+      <c r="AB10" s="16"/>
       <c r="AC10" s="16"/>
       <c r="AD10" s="16"/>
       <c r="AE10" s="16"/>
       <c r="AF10" s="16"/>
       <c r="AG10" s="16"/>
-      <c r="AH10" s="18"/>
+      <c r="AH10" s="16"/>
       <c r="AI10" s="16"/>
       <c r="AJ10" s="16"/>
     </row>
-    <row r="11" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B11" s="16"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
+        <v>98</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
+      <c r="H11" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="L11" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="16"/>
+      <c r="N11" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="O11" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="P11" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q11" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="R11" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="T11" s="16">
-        <v>-0.01</v>
+        <v>0.318</v>
       </c>
       <c r="U11" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="V11" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="W11" s="16">
+        <v>0.23599999999999999</v>
+      </c>
+      <c r="X11" s="16">
+        <v>0.40100000000000002</v>
+      </c>
+      <c r="Y11" s="16"/>
+      <c r="Z11" s="16">
+        <v>0.32</v>
+      </c>
+      <c r="AA11" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="AB11" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC11" s="16">
+        <v>0.23699999999999999</v>
+      </c>
+      <c r="AD11" s="16">
+        <v>0.40300000000000002</v>
+      </c>
+      <c r="AE11" s="16"/>
+      <c r="AF11" s="16">
+        <v>0.32</v>
+      </c>
+      <c r="AG11" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="AH11" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI11" s="16">
+        <v>0.23699999999999999</v>
+      </c>
+      <c r="AJ11" s="16">
+        <v>0.40300000000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B12" s="16">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="C12" s="16">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="D12" s="16">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="E12" s="16">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="V11" s="18">
-        <v>0.63500000000000001</v>
-      </c>
-      <c r="W11" s="16"/>
-      <c r="X11" s="16"/>
-      <c r="Y11" s="16"/>
-      <c r="Z11" s="16"/>
-      <c r="AA11" s="16"/>
-      <c r="AB11" s="18"/>
-      <c r="AC11" s="16"/>
-      <c r="AD11" s="16"/>
-      <c r="AE11" s="16"/>
-      <c r="AF11" s="16"/>
-      <c r="AG11" s="16"/>
-      <c r="AH11" s="18"/>
-      <c r="AI11" s="16"/>
-      <c r="AJ11" s="16"/>
-    </row>
-    <row r="12" spans="1:36" ht="17" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
+      <c r="F12" s="16">
+        <v>0.21299999999999999</v>
+      </c>
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
       <c r="I12" s="16"/>
@@ -5304,15 +5548,9 @@
       <c r="P12" s="18"/>
       <c r="Q12" s="16"/>
       <c r="R12" s="16"/>
-      <c r="T12" s="16">
-        <v>7.0999999999999994E-2</v>
-      </c>
-      <c r="U12" s="16">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="V12" s="18">
-        <v>1E-3</v>
-      </c>
+      <c r="T12" s="16"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="18"/>
       <c r="W12" s="16"/>
       <c r="X12" s="16"/>
       <c r="Y12" s="16"/>
@@ -5328,15 +5566,25 @@
       <c r="AI12" s="16"/>
       <c r="AJ12" s="16"/>
     </row>
-    <row r="13" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
+        <v>99</v>
+      </c>
+      <c r="B13" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="C13" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="D13" s="16">
+        <v>0.35199999999999998</v>
+      </c>
+      <c r="E13" s="16">
+        <v>-1.4999999999999999E-2</v>
+      </c>
+      <c r="F13" s="16">
+        <v>5.6000000000000001E-2</v>
+      </c>
       <c r="G13" s="16"/>
       <c r="H13" s="16"/>
       <c r="I13" s="16"/>
@@ -5350,38 +5598,72 @@
       <c r="Q13" s="16"/>
       <c r="R13" s="16"/>
       <c r="T13" s="16">
-        <v>0.16800000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="U13" s="16">
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="V13" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="W13" s="16"/>
-      <c r="X13" s="16"/>
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="V13" s="18">
+        <v>0.63500000000000001</v>
+      </c>
+      <c r="W13" s="16">
+        <v>-4.4999999999999998E-2</v>
+      </c>
+      <c r="X13" s="16">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="Y13" s="16"/>
-      <c r="Z13" s="16"/>
-      <c r="AA13" s="16"/>
-      <c r="AB13" s="16"/>
-      <c r="AC13" s="16"/>
-      <c r="AD13" s="16"/>
+      <c r="Z13" s="16">
+        <v>-0.01</v>
+      </c>
+      <c r="AA13" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AB13" s="16">
+        <v>0.625</v>
+      </c>
+      <c r="AC13" s="16">
+        <v>-4.4999999999999998E-2</v>
+      </c>
+      <c r="AD13" s="16">
+        <v>2.4E-2</v>
+      </c>
       <c r="AE13" s="16"/>
-      <c r="AF13" s="16"/>
-      <c r="AG13" s="16"/>
-      <c r="AH13" s="18"/>
-      <c r="AI13" s="16"/>
-      <c r="AJ13" s="16"/>
-    </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AF13" s="16">
+        <v>-0.01</v>
+      </c>
+      <c r="AG13" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AH13" s="16">
+        <v>0.621</v>
+      </c>
+      <c r="AI13" s="16">
+        <v>-4.4999999999999998E-2</v>
+      </c>
+      <c r="AJ13" s="16">
+        <v>2.4E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
+        <v>100</v>
+      </c>
+      <c r="B14" s="16">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="C14" s="16">
+        <v>2.3E-2</v>
+      </c>
+      <c r="D14" s="16">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E14" s="16">
+        <v>3.1E-2</v>
+      </c>
+      <c r="F14" s="16">
+        <v>0.106</v>
+      </c>
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
       <c r="I14" s="16"/>
@@ -5395,114 +5677,220 @@
       <c r="Q14" s="16"/>
       <c r="R14" s="16"/>
       <c r="T14" s="16">
-        <v>0.248</v>
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="U14" s="16">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="V14" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="W14" s="16"/>
-      <c r="X14" s="16"/>
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="V14" s="18">
+        <v>1E-3</v>
+      </c>
+      <c r="W14" s="16">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="X14" s="16">
+        <v>0.106</v>
+      </c>
       <c r="Y14" s="16"/>
-      <c r="Z14" s="16"/>
-      <c r="AA14" s="16"/>
-      <c r="AB14" s="18"/>
-      <c r="AC14" s="16"/>
-      <c r="AD14" s="16"/>
+      <c r="Z14" s="16">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="AA14" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AB14" s="16">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="AC14" s="16">
+        <v>1.6E-2</v>
+      </c>
+      <c r="AD14" s="16">
+        <v>8.5999999999999993E-2</v>
+      </c>
       <c r="AE14" s="16"/>
-      <c r="AF14" s="16"/>
-      <c r="AG14" s="16"/>
-      <c r="AH14" s="18"/>
-      <c r="AI14" s="16"/>
-      <c r="AJ14" s="16"/>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A15" s="16"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="21"/>
+      <c r="AF14" s="16">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="AG14" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AH14" s="16">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="AI14" s="16">
+        <v>1.6E-2</v>
+      </c>
+      <c r="AJ14" s="16">
+        <v>8.5999999999999993E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="G15" s="21"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="16"/>
+      <c r="H15" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K15" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="L15" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="16"/>
-      <c r="P15" s="18"/>
-      <c r="Q15" s="18"/>
-      <c r="R15" s="16"/>
+      <c r="N15" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="O15" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="P15" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q15" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="R15" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="T15" s="16"/>
       <c r="U15" s="16"/>
       <c r="V15" s="18"/>
-      <c r="W15" s="18"/>
-      <c r="X15" s="21"/>
-      <c r="Y15" s="21"/>
+      <c r="W15" s="16"/>
+      <c r="X15" s="16"/>
+      <c r="Y15" s="16"/>
       <c r="Z15" s="16"/>
       <c r="AA15" s="16"/>
-      <c r="AB15" s="18"/>
-      <c r="AC15" s="18"/>
+      <c r="AB15" s="16"/>
+      <c r="AC15" s="16"/>
       <c r="AD15" s="16"/>
       <c r="AE15" s="16"/>
       <c r="AF15" s="16"/>
       <c r="AG15" s="16"/>
-      <c r="AH15" s="18"/>
-      <c r="AI15" s="18"/>
+      <c r="AH15" s="16"/>
+      <c r="AI15" s="16"/>
       <c r="AJ15" s="16"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A16" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G16" s="16"/>
       <c r="H16" s="16"/>
       <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
+      <c r="J16" s="18"/>
       <c r="K16" s="16"/>
       <c r="L16" s="16"/>
       <c r="M16" s="16"/>
       <c r="N16" s="16"/>
       <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
+      <c r="P16" s="18"/>
       <c r="Q16" s="16"/>
       <c r="R16" s="16"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="16"/>
-      <c r="V16" s="16"/>
-      <c r="W16" s="16"/>
-      <c r="X16" s="21"/>
-      <c r="Y16" s="21"/>
-      <c r="Z16" s="16"/>
-      <c r="AA16" s="16"/>
-      <c r="AB16" s="16"/>
-      <c r="AC16" s="16"/>
-      <c r="AD16" s="16"/>
+      <c r="T16" s="16">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="U16" s="16">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="V16" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="W16" s="16">
+        <v>0.108</v>
+      </c>
+      <c r="X16" s="16">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="Y16" s="16"/>
+      <c r="Z16" s="16">
+        <v>0.16800000000000001</v>
+      </c>
+      <c r="AA16" s="16">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="AB16" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC16" s="16">
+        <v>0.108</v>
+      </c>
+      <c r="AD16" s="16">
+        <v>0.22900000000000001</v>
+      </c>
       <c r="AE16" s="16"/>
-      <c r="AF16" s="16"/>
-      <c r="AG16" s="16"/>
-      <c r="AH16" s="16"/>
-      <c r="AI16" s="16"/>
-      <c r="AJ16" s="16"/>
-    </row>
-    <row r="17" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+      <c r="AF16" s="16">
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="AG16" s="16">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="AH16" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI16" s="16">
+        <v>0.109</v>
+      </c>
+      <c r="AJ16" s="16">
+        <v>0.22900000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
+        <v>142</v>
+      </c>
+      <c r="B17" s="16">
+        <v>-0.45300000000000001</v>
+      </c>
+      <c r="C17" s="16">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="D17" s="16">
+        <v>1E-3</v>
+      </c>
+      <c r="E17" s="16">
+        <v>-0.68100000000000005</v>
+      </c>
+      <c r="F17" s="16">
+        <v>-0.22500000000000001</v>
+      </c>
       <c r="G17" s="16"/>
       <c r="H17" s="16"/>
       <c r="I17" s="16"/>
@@ -5515,15 +5903,9 @@
       <c r="P17" s="18"/>
       <c r="Q17" s="16"/>
       <c r="R17" s="16"/>
-      <c r="T17" s="16">
-        <v>8.5000000000000006E-2</v>
-      </c>
-      <c r="U17" s="16">
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="V17" s="18">
-        <v>2.1000000000000001E-2</v>
-      </c>
+      <c r="T17" s="16"/>
+      <c r="U17" s="16"/>
+      <c r="V17" s="18"/>
       <c r="W17" s="16"/>
       <c r="X17" s="16"/>
       <c r="Y17" s="16"/>
@@ -5539,26 +5921,26 @@
       <c r="AI17" s="16"/>
       <c r="AJ17" s="16"/>
     </row>
-    <row r="18" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E18" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="F18" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="G18" s="21"/>
+        <v>88</v>
+      </c>
+      <c r="B18" s="16">
+        <v>0.318</v>
+      </c>
+      <c r="C18" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="16">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="F18" s="16">
+        <v>0.35099999999999998</v>
+      </c>
+      <c r="G18" s="16"/>
       <c r="H18" s="16"/>
       <c r="I18" s="16"/>
       <c r="J18" s="18"/>
@@ -5570,143 +5952,121 @@
       <c r="P18" s="18"/>
       <c r="Q18" s="16"/>
       <c r="R18" s="16"/>
-      <c r="T18" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="U18" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="V18" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="W18" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="X18" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y18" s="21"/>
-      <c r="Z18" s="16"/>
-      <c r="AA18" s="16"/>
-      <c r="AB18" s="18"/>
-      <c r="AC18" s="16"/>
-      <c r="AD18" s="16"/>
+      <c r="T18" s="16">
+        <v>0.248</v>
+      </c>
+      <c r="U18" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="V18" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="W18" s="16">
+        <v>0.21199999999999999</v>
+      </c>
+      <c r="X18" s="16">
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="Y18" s="16"/>
+      <c r="Z18" s="16">
+        <v>0.252</v>
+      </c>
+      <c r="AA18" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="AB18" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC18" s="16">
+        <v>0.216</v>
+      </c>
+      <c r="AD18" s="16">
+        <v>0.28799999999999998</v>
+      </c>
       <c r="AE18" s="16"/>
-      <c r="AF18" s="16"/>
-      <c r="AG18" s="16"/>
-      <c r="AH18" s="18"/>
-      <c r="AI18" s="16"/>
-      <c r="AJ18" s="16"/>
-    </row>
-    <row r="19" spans="1:36" ht="17" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E19" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>94</v>
-      </c>
+      <c r="AF18" s="16">
+        <v>0.252</v>
+      </c>
+      <c r="AG18" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="AH18" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI18" s="16">
+        <v>0.216</v>
+      </c>
+      <c r="AJ18" s="16">
+        <v>0.28799999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="21"/>
       <c r="G19" s="21"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="16"/>
-      <c r="K19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
       <c r="L19" s="16"/>
       <c r="M19" s="16"/>
       <c r="N19" s="16"/>
       <c r="O19" s="16"/>
       <c r="P19" s="18"/>
-      <c r="Q19" s="16"/>
+      <c r="Q19" s="18"/>
       <c r="R19" s="16"/>
-      <c r="T19" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="U19" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="V19" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="W19" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="X19" s="21" t="s">
-        <v>94</v>
-      </c>
+      <c r="T19" s="16"/>
+      <c r="U19" s="16"/>
+      <c r="V19" s="18"/>
+      <c r="W19" s="18"/>
+      <c r="X19" s="21"/>
       <c r="Y19" s="21"/>
       <c r="Z19" s="16"/>
       <c r="AA19" s="16"/>
-      <c r="AB19" s="16"/>
-      <c r="AC19" s="16"/>
+      <c r="AB19" s="18"/>
+      <c r="AC19" s="18"/>
       <c r="AD19" s="16"/>
       <c r="AE19" s="16"/>
       <c r="AF19" s="16"/>
       <c r="AG19" s="16"/>
-      <c r="AH19" s="16"/>
-      <c r="AI19" s="16"/>
-      <c r="AJ19" s="30"/>
-    </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A20" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E20" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>94</v>
-      </c>
+      <c r="AH19" s="18"/>
+      <c r="AI19" s="18"/>
+      <c r="AJ19" s="16"/>
+    </row>
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A20" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="21"/>
       <c r="G20" s="21"/>
       <c r="H20" s="16"/>
       <c r="I20" s="16"/>
-      <c r="J20" s="18"/>
+      <c r="J20" s="16"/>
       <c r="K20" s="16"/>
       <c r="L20" s="16"/>
       <c r="M20" s="16"/>
       <c r="N20" s="16"/>
       <c r="O20" s="16"/>
-      <c r="P20" s="18"/>
+      <c r="P20" s="16"/>
       <c r="Q20" s="16"/>
       <c r="R20" s="16"/>
-      <c r="T20" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="U20" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="V20" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="W20" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="X20" s="21" t="s">
-        <v>94</v>
-      </c>
+      <c r="T20" s="16"/>
+      <c r="U20" s="16"/>
+      <c r="V20" s="16"/>
+      <c r="W20" s="16"/>
+      <c r="X20" s="21"/>
       <c r="Y20" s="21"/>
       <c r="Z20" s="16"/>
       <c r="AA20" s="16"/>
-      <c r="AB20" s="18"/>
+      <c r="AB20" s="16"/>
       <c r="AC20" s="16"/>
       <c r="AD20" s="16"/>
       <c r="AE20" s="16"/>
@@ -5716,52 +6076,42 @@
       <c r="AI20" s="16"/>
       <c r="AJ20" s="16"/>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E21" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="F21" s="21" t="s">
-        <v>94</v>
+        <v>138</v>
+      </c>
+      <c r="B21" s="16">
+        <v>-0.29099999999999998</v>
+      </c>
+      <c r="C21" s="16">
+        <v>0.106</v>
+      </c>
+      <c r="D21" s="16">
+        <v>6.0000000000000001E-3</v>
+      </c>
+      <c r="E21" s="16">
+        <v>-0.46500000000000002</v>
+      </c>
+      <c r="F21" s="16">
+        <v>-0.11700000000000001</v>
       </c>
       <c r="G21" s="21"/>
       <c r="H21" s="16"/>
       <c r="I21" s="16"/>
-      <c r="J21" s="18"/>
+      <c r="J21" s="16"/>
       <c r="K21" s="16"/>
       <c r="L21" s="16"/>
       <c r="M21" s="16"/>
       <c r="N21" s="16"/>
       <c r="O21" s="16"/>
-      <c r="P21" s="18"/>
+      <c r="P21" s="16"/>
       <c r="Q21" s="16"/>
       <c r="R21" s="16"/>
-      <c r="T21" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="U21" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="V21" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="W21" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="X21" s="21" t="s">
-        <v>94</v>
-      </c>
+      <c r="T21" s="16"/>
+      <c r="U21" s="16"/>
+      <c r="V21" s="16"/>
+      <c r="W21" s="16"/>
+      <c r="X21" s="21"/>
       <c r="Y21" s="21"/>
       <c r="Z21" s="16"/>
       <c r="AA21" s="16"/>
@@ -5771,13 +6121,13 @@
       <c r="AE21" s="16"/>
       <c r="AF21" s="16"/>
       <c r="AG21" s="16"/>
-      <c r="AH21" s="18"/>
+      <c r="AH21" s="16"/>
       <c r="AI21" s="16"/>
       <c r="AJ21" s="16"/>
     </row>
-    <row r="22" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>94</v>
@@ -5794,7 +6144,7 @@
       <c r="F22" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="G22" s="21"/>
+      <c r="G22" s="16"/>
       <c r="H22" s="16" t="s">
         <v>94</v>
       </c>
@@ -5804,57 +6154,79 @@
       <c r="J22" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="K22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="L22" s="16" t="s">
+      <c r="K22" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="L22" s="21" t="s">
         <v>94</v>
       </c>
       <c r="M22" s="16"/>
-      <c r="N22" s="16"/>
-      <c r="O22" s="16"/>
-      <c r="P22" s="18"/>
-      <c r="Q22" s="16"/>
-      <c r="R22" s="16"/>
-      <c r="T22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="U22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="V22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="W22" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="X22" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y22" s="21"/>
-      <c r="Z22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AA22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AB22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC22" s="16"/>
-      <c r="AD22" s="16" t="s">
-        <v>94</v>
+      <c r="N22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="O22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="P22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q22" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="R22" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="T22" s="16">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="U22" s="16">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="V22" s="18">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="W22" s="16">
+        <v>2.4E-2</v>
+      </c>
+      <c r="X22" s="16">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="Y22" s="16"/>
+      <c r="Z22" s="16">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="AA22" s="16">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="AB22" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="AC22" s="16">
+        <v>2.4E-2</v>
+      </c>
+      <c r="AD22" s="16">
+        <v>0.14499999999999999</v>
       </c>
       <c r="AE22" s="16"/>
-      <c r="AF22" s="16"/>
-      <c r="AG22" s="16"/>
-      <c r="AH22" s="18"/>
-      <c r="AI22" s="16"/>
-      <c r="AJ22" s="16"/>
-    </row>
-    <row r="23" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+      <c r="AF22" s="16">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="AG22" s="16">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="AH22" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="AI22" s="16">
+        <v>2.4E-2</v>
+      </c>
+      <c r="AJ22" s="16">
+        <v>0.14499999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B23" s="16" t="s">
         <v>94</v>
@@ -5872,21 +6244,11 @@
         <v>94</v>
       </c>
       <c r="G23" s="21"/>
-      <c r="H23" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I23" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="J23" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="K23" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="L23" s="16" t="s">
-        <v>94</v>
-      </c>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
       <c r="M23" s="16"/>
       <c r="N23" s="16"/>
       <c r="O23" s="16"/>
@@ -5909,29 +6271,41 @@
         <v>94</v>
       </c>
       <c r="Y23" s="21"/>
-      <c r="Z23" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AA23" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AB23" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC23" s="16"/>
-      <c r="AD23" s="16" t="s">
-        <v>94</v>
+      <c r="Z23" s="16">
+        <v>-0.13100000000000001</v>
+      </c>
+      <c r="AA23" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="AB23" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC23" s="16">
+        <v>-0.16600000000000001</v>
+      </c>
+      <c r="AD23" s="16">
+        <v>-9.5000000000000001E-2</v>
       </c>
       <c r="AE23" s="16"/>
-      <c r="AF23" s="16"/>
-      <c r="AG23" s="16"/>
-      <c r="AH23" s="16"/>
-      <c r="AI23" s="16"/>
-      <c r="AJ23" s="16"/>
-    </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AF23" s="16">
+        <v>-0.13100000000000001</v>
+      </c>
+      <c r="AG23" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="AH23" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI23" s="16">
+        <v>-0.16600000000000001</v>
+      </c>
+      <c r="AJ23" s="16">
+        <v>-9.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B24" s="16" t="s">
         <v>94</v>
@@ -5949,21 +6323,11 @@
         <v>94</v>
       </c>
       <c r="G24" s="21"/>
-      <c r="H24" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I24" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="J24" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="K24" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="L24" s="16" t="s">
-        <v>94</v>
-      </c>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
       <c r="M24" s="16"/>
       <c r="N24" s="16"/>
       <c r="O24" s="16"/>
@@ -5986,29 +6350,41 @@
         <v>94</v>
       </c>
       <c r="Y24" s="21"/>
-      <c r="Z24" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AA24" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AB24" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC24" s="16"/>
-      <c r="AD24" s="16" t="s">
-        <v>94</v>
+      <c r="Z24" s="16">
+        <v>-8.9999999999999993E-3</v>
+      </c>
+      <c r="AA24" s="16">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="AB24" s="16">
+        <v>0.81399999999999995</v>
+      </c>
+      <c r="AC24" s="16">
+        <v>-6.9000000000000006E-2</v>
+      </c>
+      <c r="AD24" s="16">
+        <v>5.1999999999999998E-2</v>
       </c>
       <c r="AE24" s="16"/>
-      <c r="AF24" s="16"/>
-      <c r="AG24" s="16"/>
-      <c r="AH24" s="18"/>
-      <c r="AI24" s="16"/>
-      <c r="AJ24" s="16"/>
-    </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AF24" s="16">
+        <v>-0.01</v>
+      </c>
+      <c r="AG24" s="16">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="AH24" s="16">
+        <v>0.79300000000000004</v>
+      </c>
+      <c r="AI24" s="16">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="AJ24" s="16">
+        <v>5.0999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B25" s="16" t="s">
         <v>94</v>
@@ -6026,21 +6402,11 @@
         <v>94</v>
       </c>
       <c r="G25" s="21"/>
-      <c r="H25" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I25" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="J25" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="K25" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="L25" s="16" t="s">
-        <v>94</v>
-      </c>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="18"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
       <c r="M25" s="16"/>
       <c r="N25" s="16"/>
       <c r="O25" s="16"/>
@@ -6063,29 +6429,41 @@
         <v>94</v>
       </c>
       <c r="Y25" s="21"/>
-      <c r="Z25" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AA25" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AB25" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC25" s="16"/>
-      <c r="AD25" s="16" t="s">
-        <v>94</v>
+      <c r="Z25" s="16">
+        <v>-2E-3</v>
+      </c>
+      <c r="AA25" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AB25" s="16">
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="AC25" s="16">
+        <v>-3.5999999999999997E-2</v>
+      </c>
+      <c r="AD25" s="16">
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="AE25" s="16"/>
-      <c r="AF25" s="16"/>
-      <c r="AG25" s="16"/>
-      <c r="AH25" s="16"/>
-      <c r="AI25" s="16"/>
-      <c r="AJ25" s="16"/>
-    </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AF25" s="16">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="AG25" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AH25" s="16">
+        <v>0.90400000000000003</v>
+      </c>
+      <c r="AI25" s="16">
+        <v>-3.6999999999999998E-2</v>
+      </c>
+      <c r="AJ25" s="16">
+        <v>3.2000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>94</v>
@@ -6103,21 +6481,11 @@
         <v>94</v>
       </c>
       <c r="G26" s="21"/>
-      <c r="H26" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I26" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="J26" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="K26" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="L26" s="16" t="s">
-        <v>94</v>
-      </c>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
       <c r="M26" s="16"/>
       <c r="N26" s="16"/>
       <c r="O26" s="16"/>
@@ -6140,195 +6508,389 @@
         <v>94</v>
       </c>
       <c r="Y26" s="21"/>
-      <c r="Z26" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AA26" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AB26" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC26" s="16"/>
-      <c r="AD26" s="16" t="s">
-        <v>94</v>
+      <c r="Z26" s="16">
+        <v>-0.17</v>
+      </c>
+      <c r="AA26" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AB26" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC26" s="16">
+        <v>-0.20399999999999999</v>
+      </c>
+      <c r="AD26" s="16">
+        <v>-0.13500000000000001</v>
       </c>
       <c r="AE26" s="16"/>
-      <c r="AF26" s="16"/>
-      <c r="AG26" s="16"/>
-      <c r="AH26" s="18"/>
-      <c r="AI26" s="16"/>
-      <c r="AJ26" s="16"/>
-    </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="21"/>
+      <c r="AF26" s="16">
+        <v>-0.17</v>
+      </c>
+      <c r="AG26" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AH26" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI26" s="16">
+        <v>-0.20399999999999999</v>
+      </c>
+      <c r="AJ26" s="16">
+        <v>-0.13600000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A27" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="G27" s="21"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
+      <c r="H27" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I27" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J27" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="M27" s="16"/>
       <c r="N27" s="16"/>
       <c r="O27" s="16"/>
       <c r="P27" s="18"/>
-      <c r="Q27" s="18"/>
+      <c r="Q27" s="16"/>
       <c r="R27" s="16"/>
-      <c r="T27" s="16"/>
-      <c r="U27" s="16"/>
-      <c r="V27" s="16"/>
-      <c r="W27" s="16"/>
-      <c r="X27" s="21"/>
+      <c r="T27" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U27" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V27" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W27" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X27" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="Y27" s="21"/>
-      <c r="Z27" s="16"/>
-      <c r="AA27" s="16"/>
-      <c r="AB27" s="16"/>
+      <c r="Z27" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA27" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB27" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="AC27" s="16"/>
-      <c r="AD27" s="16"/>
+      <c r="AD27" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="AE27" s="16"/>
-      <c r="AF27" s="16"/>
-      <c r="AG27" s="16"/>
-      <c r="AH27" s="18"/>
-      <c r="AI27" s="18"/>
-      <c r="AJ27" s="16"/>
-    </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A28" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="21"/>
+      <c r="AF27" s="16">
+        <v>-3.7999999999999999E-2</v>
+      </c>
+      <c r="AG27" s="16">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="AH27" s="16">
+        <v>0.39900000000000002</v>
+      </c>
+      <c r="AI27" s="16">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="AJ27" s="16">
+        <v>0.17199999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A28" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="G28" s="21"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
+      <c r="H28" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I28" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J28" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="M28" s="16"/>
       <c r="N28" s="16"/>
       <c r="O28" s="16"/>
-      <c r="P28" s="16"/>
+      <c r="P28" s="18"/>
       <c r="Q28" s="16"/>
       <c r="R28" s="16"/>
-      <c r="T28" s="16"/>
-      <c r="U28" s="16"/>
-      <c r="V28" s="16"/>
-      <c r="W28" s="16"/>
-      <c r="X28" s="21"/>
+      <c r="T28" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U28" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V28" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W28" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X28" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="Y28" s="21"/>
-      <c r="Z28" s="16"/>
-      <c r="AA28" s="16"/>
-      <c r="AB28" s="16"/>
+      <c r="Z28" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA28" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB28" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="AC28" s="16"/>
-      <c r="AD28" s="16"/>
+      <c r="AD28" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="AE28" s="16"/>
-      <c r="AF28" s="16"/>
-      <c r="AG28" s="16"/>
-      <c r="AH28" s="16"/>
-      <c r="AI28" s="16"/>
-      <c r="AJ28" s="16"/>
-    </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AF28" s="16">
+        <v>0.129</v>
+      </c>
+      <c r="AG28" s="16">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="AH28" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI28" s="16">
+        <v>-0.111</v>
+      </c>
+      <c r="AJ28" s="16">
+        <v>3.5999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="18"/>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
+        <v>110</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G29" s="21"/>
+      <c r="H29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="M29" s="16"/>
       <c r="N29" s="16"/>
       <c r="O29" s="16"/>
       <c r="P29" s="18"/>
       <c r="Q29" s="16"/>
       <c r="R29" s="16"/>
-      <c r="T29" s="16">
-        <v>13.827</v>
-      </c>
-      <c r="U29" s="16">
-        <v>0.20100000000000001</v>
-      </c>
-      <c r="V29" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="W29" s="16"/>
-      <c r="X29" s="16"/>
-      <c r="Y29" s="16"/>
-      <c r="Z29" s="16"/>
-      <c r="AA29" s="16"/>
-      <c r="AB29" s="18"/>
+      <c r="T29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W29" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X29" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y29" s="21"/>
+      <c r="Z29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB29" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="AC29" s="16"/>
-      <c r="AD29" s="16"/>
+      <c r="AD29" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="AE29" s="16"/>
-      <c r="AF29" s="16"/>
-      <c r="AG29" s="16"/>
-      <c r="AH29" s="18"/>
-      <c r="AI29" s="16"/>
-      <c r="AJ29" s="16"/>
-    </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AF29" s="16">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="AG29" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="AH29" s="16">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="AI29" s="16">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="AJ29" s="16">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="18"/>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
+        <v>109</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G30" s="21"/>
+      <c r="H30" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J30" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="M30" s="16"/>
       <c r="N30" s="16"/>
       <c r="O30" s="16"/>
       <c r="P30" s="18"/>
       <c r="Q30" s="16"/>
       <c r="R30" s="16"/>
-      <c r="T30" s="16">
-        <v>3.8889999999999998</v>
-      </c>
-      <c r="U30" s="16">
-        <v>6.3E-2</v>
-      </c>
-      <c r="V30" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="W30" s="16"/>
-      <c r="X30" s="16"/>
-      <c r="Y30" s="16"/>
-      <c r="Z30" s="16"/>
-      <c r="AA30" s="16"/>
-      <c r="AB30" s="18"/>
+      <c r="T30" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U30" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V30" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W30" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X30" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y30" s="21"/>
+      <c r="Z30" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA30" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB30" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="AC30" s="16"/>
-      <c r="AD30" s="16"/>
+      <c r="AD30" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="AE30" s="16"/>
-      <c r="AF30" s="16"/>
-      <c r="AG30" s="16"/>
-      <c r="AH30" s="18"/>
-      <c r="AI30" s="16"/>
-      <c r="AJ30" s="16"/>
-    </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AF30" s="16">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AG30" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="AH30" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI30" s="16">
+        <v>0.104</v>
+      </c>
+      <c r="AJ30" s="16">
+        <v>0.17499999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="B31" s="16" t="s">
         <v>94</v>
@@ -6339,18 +6901,28 @@
       <c r="D31" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="E31" s="16" t="s">
+      <c r="E31" s="21" t="s">
         <v>94</v>
       </c>
       <c r="F31" s="21" t="s">
         <v>94</v>
       </c>
       <c r="G31" s="21"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="18"/>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
+      <c r="H31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="M31" s="16"/>
       <c r="N31" s="16"/>
       <c r="O31" s="16"/>
@@ -6366,204 +6938,540 @@
       <c r="V31" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="W31" s="16" t="s">
+      <c r="W31" s="21" t="s">
         <v>94</v>
       </c>
       <c r="X31" s="21" t="s">
         <v>94</v>
       </c>
       <c r="Y31" s="21"/>
-      <c r="Z31" s="16"/>
-      <c r="AA31" s="16"/>
-      <c r="AB31" s="18"/>
+      <c r="Z31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA31" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB31" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="AC31" s="16"/>
-      <c r="AD31" s="16"/>
+      <c r="AD31" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="AE31" s="16"/>
-      <c r="AF31" s="16"/>
-      <c r="AG31" s="16"/>
-      <c r="AH31" s="18"/>
-      <c r="AI31" s="16"/>
-      <c r="AJ31" s="16"/>
-    </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A32" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C32" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E32" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="F32" s="21" t="s">
-        <v>94</v>
-      </c>
+      <c r="AF31" s="16">
+        <v>-8.4000000000000005E-2</v>
+      </c>
+      <c r="AG31" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="AH31" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI31" s="16">
+        <v>-0.11700000000000001</v>
+      </c>
+      <c r="AJ31" s="16">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A32" s="16"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="21"/>
       <c r="G32" s="21"/>
-      <c r="H32" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I32" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="J32" s="16" t="s">
-        <v>94</v>
-      </c>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
       <c r="K32" s="16"/>
-      <c r="L32" s="16" t="s">
-        <v>94</v>
-      </c>
+      <c r="L32" s="16"/>
       <c r="M32" s="16"/>
       <c r="N32" s="16"/>
       <c r="O32" s="16"/>
       <c r="P32" s="18"/>
-      <c r="Q32" s="16"/>
+      <c r="Q32" s="18"/>
       <c r="R32" s="16"/>
-      <c r="T32" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="U32" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="V32" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="W32" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="X32" s="21" t="s">
-        <v>94</v>
-      </c>
+      <c r="T32" s="16"/>
+      <c r="U32" s="16"/>
+      <c r="V32" s="16"/>
+      <c r="W32" s="16"/>
+      <c r="X32" s="21"/>
       <c r="Y32" s="21"/>
-      <c r="Z32" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AA32" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AB32" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC32" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="AD32" s="21" t="s">
-        <v>94</v>
-      </c>
+      <c r="Z32" s="16"/>
+      <c r="AA32" s="16"/>
+      <c r="AB32" s="16"/>
+      <c r="AC32" s="16"/>
+      <c r="AD32" s="16"/>
       <c r="AE32" s="16"/>
       <c r="AF32" s="16"/>
       <c r="AG32" s="16"/>
       <c r="AH32" s="18"/>
-      <c r="AI32" s="16"/>
+      <c r="AI32" s="18"/>
       <c r="AJ32" s="16"/>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A33" s="20" t="s">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A33" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="16"/>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
+      <c r="M33" s="16"/>
+      <c r="N33" s="16"/>
+      <c r="O33" s="16"/>
+      <c r="P33" s="16"/>
+      <c r="Q33" s="16"/>
+      <c r="R33" s="16"/>
+      <c r="T33" s="16"/>
+      <c r="U33" s="16"/>
+      <c r="V33" s="16"/>
+      <c r="W33" s="16"/>
+      <c r="X33" s="21"/>
+      <c r="Y33" s="21"/>
+      <c r="Z33" s="16"/>
+      <c r="AA33" s="16"/>
+      <c r="AB33" s="16"/>
+      <c r="AC33" s="16"/>
+      <c r="AD33" s="16"/>
+      <c r="AE33" s="16"/>
+      <c r="AF33" s="16"/>
+      <c r="AG33" s="16"/>
+      <c r="AH33" s="16"/>
+      <c r="AI33" s="16"/>
+      <c r="AJ33" s="16"/>
+    </row>
+    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A34" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B34" s="16">
+        <v>10.965</v>
+      </c>
+      <c r="C34" s="16">
+        <v>0.158</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="16">
+        <v>10.706</v>
+      </c>
+      <c r="F34" s="16">
+        <v>11.225</v>
+      </c>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="16"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
+      <c r="M34" s="16"/>
+      <c r="N34" s="16"/>
+      <c r="O34" s="16"/>
+      <c r="P34" s="18"/>
+      <c r="Q34" s="16"/>
+      <c r="R34" s="16"/>
+      <c r="T34" s="16">
+        <v>13.827</v>
+      </c>
+      <c r="U34" s="16">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="V34" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="W34" s="16">
+        <v>13.496</v>
+      </c>
+      <c r="X34" s="16">
+        <v>14.157999999999999</v>
+      </c>
+      <c r="Y34" s="16"/>
+      <c r="Z34" s="16">
+        <v>13.829000000000001</v>
+      </c>
+      <c r="AA34" s="16">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="AB34" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC34" s="16">
+        <v>13.496</v>
+      </c>
+      <c r="AD34" s="16">
+        <v>14.161</v>
+      </c>
+      <c r="AE34" s="16"/>
+      <c r="AF34" s="16">
+        <v>13.829000000000001</v>
+      </c>
+      <c r="AG34" s="16">
+        <v>0.20200000000000001</v>
+      </c>
+      <c r="AH34" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI34" s="16">
+        <v>13.497</v>
+      </c>
+      <c r="AJ34" s="16">
+        <v>14.162000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A35" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B35" s="16">
+        <v>3.7109999999999999</v>
+      </c>
+      <c r="C35" s="16">
+        <v>6.3E-2</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="16">
+        <v>3.6070000000000002</v>
+      </c>
+      <c r="F35" s="16">
+        <v>3.8149999999999999</v>
+      </c>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
+      <c r="M35" s="16"/>
+      <c r="N35" s="16"/>
+      <c r="O35" s="16"/>
+      <c r="P35" s="18"/>
+      <c r="Q35" s="16"/>
+      <c r="R35" s="16"/>
+      <c r="T35" s="16">
+        <v>3.8889999999999998</v>
+      </c>
+      <c r="U35" s="16">
+        <v>6.3E-2</v>
+      </c>
+      <c r="V35" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="W35" s="16">
+        <v>3.7839999999999998</v>
+      </c>
+      <c r="X35" s="16">
+        <v>3.9929999999999999</v>
+      </c>
+      <c r="Y35" s="16"/>
+      <c r="Z35" s="16">
+        <v>4.0620000000000003</v>
+      </c>
+      <c r="AA35" s="16">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="AB35" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC35" s="16">
+        <v>3.9569999999999999</v>
+      </c>
+      <c r="AD35" s="16">
+        <v>4.1669999999999998</v>
+      </c>
+      <c r="AE35" s="16"/>
+      <c r="AF35" s="16">
+        <v>4.0609999999999999</v>
+      </c>
+      <c r="AG35" s="16">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="AH35" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI35" s="16">
+        <v>3.956</v>
+      </c>
+      <c r="AJ35" s="16">
+        <v>4.1660000000000004</v>
+      </c>
+    </row>
+    <row r="36" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A36" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F36" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G36" s="21"/>
+      <c r="H36" s="16"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="18"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="16"/>
+      <c r="N36" s="16"/>
+      <c r="O36" s="16"/>
+      <c r="P36" s="18"/>
+      <c r="Q36" s="16"/>
+      <c r="R36" s="16"/>
+      <c r="T36" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U36" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V36" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W36" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="X36" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y36" s="21"/>
+      <c r="Z36" s="16">
+        <v>1.026</v>
+      </c>
+      <c r="AA36" s="16">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="AB36" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC36" s="16">
+        <v>0.998</v>
+      </c>
+      <c r="AD36" s="16">
+        <v>1.054</v>
+      </c>
+      <c r="AE36" s="16"/>
+      <c r="AF36" s="16">
+        <v>1.0269999999999999</v>
+      </c>
+      <c r="AG36" s="16">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="AH36" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI36" s="16">
+        <v>0.999</v>
+      </c>
+      <c r="AJ36" s="16">
+        <v>1.0549999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A37" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G37" s="21"/>
+      <c r="H37" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I37" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J37" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="M37" s="16"/>
+      <c r="N37" s="16"/>
+      <c r="O37" s="16"/>
+      <c r="P37" s="18"/>
+      <c r="Q37" s="16"/>
+      <c r="R37" s="16"/>
+      <c r="T37" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U37" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V37" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W37" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X37" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y37" s="21"/>
+      <c r="Z37" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA37" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB37" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC37" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD37" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE37" s="16"/>
+      <c r="AF37" s="16">
+        <v>3.7440000000000002</v>
+      </c>
+      <c r="AG37" s="16">
+        <v>0.46500000000000002</v>
+      </c>
+      <c r="AH37" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI37" s="16">
+        <v>2.9790000000000001</v>
+      </c>
+      <c r="AJ37" s="16">
+        <v>4.5090000000000003</v>
+      </c>
+    </row>
+    <row r="38" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A38" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="14"/>
-      <c r="P33" s="14"/>
-      <c r="Q33" s="14"/>
-      <c r="R33" s="14"/>
-      <c r="S33" s="16"/>
-      <c r="T33" s="14"/>
-      <c r="U33" s="14"/>
-      <c r="V33" s="14"/>
-      <c r="W33" s="14"/>
-      <c r="X33" s="14"/>
-      <c r="Y33" s="16"/>
-      <c r="Z33" s="14"/>
-      <c r="AA33" s="14"/>
-      <c r="AB33" s="14"/>
-      <c r="AC33" s="14"/>
-      <c r="AD33" s="14"/>
-      <c r="AE33" s="16"/>
-      <c r="AF33" s="14"/>
-      <c r="AG33" s="14"/>
-      <c r="AH33" s="14"/>
-      <c r="AI33" s="14"/>
-      <c r="AJ33" s="14"/>
-      <c r="AK33" s="16"/>
-      <c r="AL33" s="16"/>
-      <c r="AM33" s="16"/>
-    </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A34" s="15" t="s">
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="14"/>
+      <c r="L38" s="14"/>
+      <c r="M38" s="16"/>
+      <c r="N38" s="14"/>
+      <c r="O38" s="14"/>
+      <c r="P38" s="14"/>
+      <c r="Q38" s="14"/>
+      <c r="R38" s="14"/>
+      <c r="S38" s="16"/>
+      <c r="T38" s="14"/>
+      <c r="U38" s="14"/>
+      <c r="V38" s="14"/>
+      <c r="W38" s="14"/>
+      <c r="X38" s="14"/>
+      <c r="Y38" s="16"/>
+      <c r="Z38" s="14"/>
+      <c r="AA38" s="14"/>
+      <c r="AB38" s="14"/>
+      <c r="AC38" s="14"/>
+      <c r="AD38" s="14"/>
+      <c r="AE38" s="16"/>
+      <c r="AF38" s="14"/>
+      <c r="AG38" s="14"/>
+      <c r="AH38" s="14"/>
+      <c r="AI38" s="14"/>
+      <c r="AJ38" s="14"/>
+      <c r="AK38" s="16"/>
+      <c r="AL38" s="16"/>
+      <c r="AM38" s="16"/>
+    </row>
+    <row r="39" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A39" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="B34" s="31">
-        <v>74058.118000000002</v>
-      </c>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="31">
-        <v>83016.937999999995</v>
-      </c>
-      <c r="I34" s="31"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="31"/>
-      <c r="L34" s="31"/>
-      <c r="M34" s="27"/>
-      <c r="N34" s="31">
-        <v>94345.274999999994</v>
-      </c>
-      <c r="O34" s="31"/>
-      <c r="P34" s="31"/>
-      <c r="Q34" s="31"/>
-      <c r="R34" s="31"/>
-      <c r="S34" s="15"/>
-      <c r="T34" s="36">
+      <c r="B39" s="33">
+        <v>34697.703999999998</v>
+      </c>
+      <c r="C39" s="33"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="27"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33"/>
+      <c r="L39" s="33"/>
+      <c r="M39" s="27"/>
+      <c r="N39" s="33"/>
+      <c r="O39" s="33"/>
+      <c r="P39" s="33"/>
+      <c r="Q39" s="33"/>
+      <c r="R39" s="33"/>
+      <c r="S39" s="15"/>
+      <c r="T39" s="33">
         <v>37782.404000000002</v>
       </c>
-      <c r="U34" s="36"/>
-      <c r="V34" s="36"/>
-      <c r="W34" s="36"/>
-      <c r="X34" s="36"/>
-      <c r="Y34" s="27"/>
-      <c r="Z34" s="31"/>
-      <c r="AA34" s="31"/>
-      <c r="AB34" s="31"/>
-      <c r="AC34" s="31"/>
-      <c r="AD34" s="31"/>
-      <c r="AE34" s="27"/>
-      <c r="AF34" s="31"/>
-      <c r="AG34" s="31"/>
-      <c r="AH34" s="31"/>
-      <c r="AI34" s="31"/>
-      <c r="AJ34" s="31"/>
-      <c r="AK34" s="16"/>
-      <c r="AL34" s="16"/>
-      <c r="AM34" s="16"/>
+      <c r="U39" s="33"/>
+      <c r="V39" s="33"/>
+      <c r="W39" s="33"/>
+      <c r="X39" s="33"/>
+      <c r="Y39" s="27"/>
+      <c r="Z39" s="33">
+        <v>47698.324999999997</v>
+      </c>
+      <c r="AA39" s="33"/>
+      <c r="AB39" s="33"/>
+      <c r="AC39" s="33"/>
+      <c r="AD39" s="33"/>
+      <c r="AE39" s="27"/>
+      <c r="AF39" s="33">
+        <v>60402.93</v>
+      </c>
+      <c r="AG39" s="33"/>
+      <c r="AH39" s="33"/>
+      <c r="AI39" s="33"/>
+      <c r="AJ39" s="33"/>
+      <c r="AK39" s="16"/>
+      <c r="AL39" s="16"/>
+      <c r="AM39" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="H34:L34"/>
-    <mergeCell ref="N34:R34"/>
-    <mergeCell ref="T34:X34"/>
-    <mergeCell ref="Z34:AD34"/>
-    <mergeCell ref="AF34:AJ34"/>
+    <mergeCell ref="AF39:AJ39"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="T2:AJ2"/>
     <mergeCell ref="B3:F3"/>
@@ -6572,6 +7480,11 @@
     <mergeCell ref="T3:X3"/>
     <mergeCell ref="Z3:AD3"/>
     <mergeCell ref="AF3:AJ3"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="H39:L39"/>
+    <mergeCell ref="N39:R39"/>
+    <mergeCell ref="T39:X39"/>
+    <mergeCell ref="Z39:AD39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -6581,27 +7494,27 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57A86273-0E84-8246-B3ED-A023C6721217}">
   <dimension ref="A1:M38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.1640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="4.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
       <c r="B2" s="34"/>
       <c r="C2" s="34"/>
@@ -6612,7 +7525,7 @@
       <c r="I2" s="34"/>
       <c r="J2" s="34"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="15"/>
       <c r="B3" s="35" t="s">
         <v>81</v>
@@ -6627,7 +7540,7 @@
       <c r="I3" s="35"/>
       <c r="J3" s="35"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="16"/>
       <c r="B4" s="17" t="s">
         <v>90</v>
@@ -6654,7 +7567,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>85</v>
       </c>
@@ -6667,7 +7580,7 @@
       <c r="I5" s="16"/>
       <c r="J5" s="16"/>
     </row>
-    <row r="6" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>96</v>
       </c>
@@ -6680,7 +7593,7 @@
       <c r="I6" s="18"/>
       <c r="J6" s="16"/>
     </row>
-    <row r="7" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>97</v>
       </c>
@@ -6693,7 +7606,7 @@
       <c r="I7" s="18"/>
       <c r="J7" s="16"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>86</v>
       </c>
@@ -6706,7 +7619,7 @@
       <c r="I8" s="16"/>
       <c r="J8" s="16"/>
     </row>
-    <row r="9" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>98</v>
       </c>
@@ -6719,7 +7632,7 @@
       <c r="I9" s="18"/>
       <c r="J9" s="16"/>
     </row>
-    <row r="10" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>99</v>
       </c>
@@ -6736,7 +7649,7 @@
       <c r="I10" s="18"/>
       <c r="J10" s="16"/>
     </row>
-    <row r="11" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>100</v>
       </c>
@@ -6753,7 +7666,7 @@
       <c r="I11" s="18"/>
       <c r="J11" s="16"/>
     </row>
-    <row r="12" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
         <v>101</v>
       </c>
@@ -6770,7 +7683,7 @@
       <c r="I12" s="18"/>
       <c r="J12" s="16"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>88</v>
       </c>
@@ -6787,7 +7700,7 @@
       <c r="I13" s="18"/>
       <c r="J13" s="16"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>87</v>
       </c>
@@ -6800,7 +7713,7 @@
       <c r="I14" s="16"/>
       <c r="J14" s="16"/>
     </row>
-    <row r="15" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>102</v>
       </c>
@@ -6817,7 +7730,7 @@
       <c r="I15" s="18"/>
       <c r="J15" s="16"/>
     </row>
-    <row r="16" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>103</v>
       </c>
@@ -6830,7 +7743,7 @@
       <c r="I16" s="18"/>
       <c r="J16" s="16"/>
     </row>
-    <row r="17" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>104</v>
       </c>
@@ -6843,7 +7756,7 @@
       <c r="I17" s="18"/>
       <c r="J17" s="16"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>107</v>
       </c>
@@ -6860,7 +7773,7 @@
       <c r="I18" s="18"/>
       <c r="J18" s="16"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>108</v>
       </c>
@@ -6877,7 +7790,7 @@
       <c r="I19" s="18"/>
       <c r="J19" s="16"/>
     </row>
-    <row r="20" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>105</v>
       </c>
@@ -6890,7 +7803,7 @@
       <c r="I20" s="18"/>
       <c r="J20" s="16"/>
     </row>
-    <row r="21" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>106</v>
       </c>
@@ -6903,7 +7816,7 @@
       <c r="I21" s="18"/>
       <c r="J21" s="16"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>110</v>
       </c>
@@ -6920,7 +7833,7 @@
       <c r="I22" s="18"/>
       <c r="J22" s="16"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>109</v>
       </c>
@@ -6937,7 +7850,7 @@
       <c r="I23" s="18"/>
       <c r="J23" s="16"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>111</v>
       </c>
@@ -6950,7 +7863,7 @@
       <c r="I24" s="18"/>
       <c r="J24" s="16"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>82</v>
       </c>
@@ -6963,7 +7876,7 @@
       <c r="I25" s="16"/>
       <c r="J25" s="16"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>84</v>
       </c>
@@ -6980,7 +7893,7 @@
       <c r="I26" s="18"/>
       <c r="J26" s="16"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
         <v>89</v>
       </c>
@@ -6997,7 +7910,7 @@
       <c r="I27" s="18"/>
       <c r="J27" s="16"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
         <v>93</v>
       </c>
@@ -7016,7 +7929,7 @@
       <c r="I28" s="18"/>
       <c r="J28" s="16"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>112</v>
       </c>
@@ -7029,7 +7942,7 @@
       <c r="I29" s="18"/>
       <c r="J29" s="16"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
         <v>83</v>
       </c>
@@ -7042,7 +7955,7 @@
       <c r="I30" s="16"/>
       <c r="J30" s="16"/>
     </row>
-    <row r="31" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>96</v>
       </c>
@@ -7061,7 +7974,7 @@
       <c r="I31" s="18"/>
       <c r="J31" s="16"/>
     </row>
-    <row r="32" spans="1:10" ht="17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
         <v>97</v>
       </c>
@@ -7080,7 +7993,7 @@
       <c r="I32" s="18"/>
       <c r="J32" s="16"/>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
         <v>84</v>
       </c>
@@ -7097,7 +8010,7 @@
       <c r="I33" s="18"/>
       <c r="J33" s="16"/>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
         <v>89</v>
       </c>
@@ -7114,7 +8027,7 @@
       <c r="I34" s="18"/>
       <c r="J34" s="16"/>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
         <v>93</v>
       </c>
@@ -7127,7 +8040,7 @@
       <c r="I35" s="18"/>
       <c r="J35" s="16"/>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
         <v>112</v>
       </c>
@@ -7138,7 +8051,7 @@
       <c r="H36" s="16"/>
       <c r="I36" s="18"/>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="20" t="s">
         <v>117</v>
       </c>
@@ -7155,7 +8068,7 @@
       <c r="L37" s="16"/>
       <c r="M37" s="16"/>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
         <v>118</v>
       </c>
@@ -7186,54 +8099,54 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{540507A6-720C-0B43-804E-087FEE710926}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" customWidth="1"/>
+    <col min="1" max="1" width="19.875" customWidth="1"/>
+    <col min="2" max="2" width="18.875" customWidth="1"/>
+    <col min="3" max="3" width="19.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="24"/>
     </row>
-    <row r="3" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="24"/>
     </row>
-    <row r="6" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="24"/>
     </row>
-    <row r="7" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="23" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B11" s="23" t="s">
         <v>129</v>
       </c>
@@ -7241,7 +8154,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>126</v>
       </c>
@@ -7252,7 +8165,7 @@
         <v>-1.4E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>127</v>
       </c>
@@ -7263,7 +8176,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>128</v>
       </c>
@@ -7274,7 +8187,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>133</v>
       </c>
@@ -7285,17 +8198,17 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="23" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B19" s="23" t="s">
         <v>129</v>
       </c>
@@ -7303,7 +8216,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>126</v>
       </c>
@@ -7314,7 +8227,7 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>127</v>
       </c>
@@ -7325,7 +8238,7 @@
         <v>-1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>128</v>
       </c>
@@ -7336,7 +8249,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>133</v>
       </c>
@@ -7347,7 +8260,7 @@
         <v>-1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E25" s="23" t="s">
         <v>132</v>
       </c>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nchaku\Documents\GitHub\pubertybrain\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmoffice-my.sharepoint.com/personal/abrieant_uvm_edu/Documents/OneDrive/Manuscripts/reg report DCN/pubertybrain/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0C5C2D-21F6-4142-814F-EFC173B4BD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="13_ncr:1_{DF0C5C2D-21F6-4142-814F-EFC173B4BD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A66E4D3C-8232-9C46-9AFD-9E69F4CA7021}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
+    <workbookView xWindow="-120" yWindow="500" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptive table" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="145">
   <si>
     <t>16.10 (2.98)</t>
   </si>
@@ -388,27 +388,6 @@
   </si>
   <si>
     <t>-</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>95%</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>CI</t>
-    </r>
   </si>
   <si>
     <r>
@@ -835,6 +814,15 @@
       </rPr>
       <t>with Tempo</t>
     </r>
+  </si>
+  <si>
+    <t>Model 3 - Boys</t>
+  </si>
+  <si>
+    <t>Model 3 - Girls</t>
+  </si>
+  <si>
+    <t>12.311      0.203</t>
   </si>
 </sst>
 </file>
@@ -957,7 +945,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -994,11 +982,114 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1046,20 +1137,34 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1641,20 +1746,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39987BE7-3659-524A-81AE-D479F97EF698}">
   <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="20.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="9"/>
       <c r="B2" s="10" t="s">
         <v>63</v>
@@ -1672,7 +1777,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="6"/>
       <c r="B3" s="11" t="s">
         <v>69</v>
@@ -1686,7 +1791,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>60</v>
       </c>
@@ -1696,7 +1801,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>61</v>
       </c>
@@ -1716,7 +1821,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>62</v>
       </c>
@@ -1736,7 +1841,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>58</v>
       </c>
@@ -1756,7 +1861,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>59</v>
       </c>
@@ -1766,7 +1871,7 @@
       <c r="E8" s="12"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>61</v>
       </c>
@@ -1786,7 +1891,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>66</v>
       </c>
@@ -1806,7 +1911,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>67</v>
       </c>
@@ -1826,7 +1931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>62</v>
       </c>
@@ -1846,7 +1951,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>68</v>
       </c>
@@ -1856,7 +1961,7 @@
       <c r="E13" s="12"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>73</v>
       </c>
@@ -1876,7 +1981,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>74</v>
       </c>
@@ -1896,7 +2001,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>75</v>
       </c>
@@ -1916,7 +2021,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>76</v>
       </c>
@@ -1934,7 +2039,7 @@
       </c>
       <c r="F17" s="19"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>71</v>
       </c>
@@ -1944,7 +2049,7 @@
       <c r="E18" s="12"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>61</v>
       </c>
@@ -1964,7 +2069,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>66</v>
       </c>
@@ -1984,7 +2089,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>67</v>
       </c>
@@ -2004,7 +2109,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>62</v>
       </c>
@@ -2024,7 +2129,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>72</v>
       </c>
@@ -2034,7 +2139,7 @@
       <c r="E23" s="12"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>61</v>
       </c>
@@ -2054,7 +2159,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>66</v>
       </c>
@@ -2074,7 +2179,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>67</v>
       </c>
@@ -2094,7 +2199,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>62</v>
       </c>
@@ -2114,7 +2219,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2122,7 +2227,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2138,11 +2243,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A749072B-F938-0F49-BE23-243603B2B3D0}">
   <dimension ref="M2"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -2154,7 +2259,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45875D41-9C56-AA4E-A18A-2D3A4CE169B3}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2164,7 +2269,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A5153E-6E5C-054A-8ACA-5118463B96C5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2174,142 +2279,142 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA86F85-A8D4-F648-84C3-730F1A42C846}">
   <dimension ref="A1:AM34"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="1.1640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.6640625" style="1" customWidth="1"/>
     <col min="11" max="11" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="1.125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="1.1640625" style="1" customWidth="1"/>
     <col min="14" max="14" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.6640625" style="1" customWidth="1"/>
     <col min="17" max="17" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="0.875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="0.83203125" style="1" customWidth="1"/>
     <col min="20" max="20" width="8.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="5.625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="6.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="5.6640625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="1" style="1" customWidth="1"/>
     <col min="26" max="26" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.6640625" style="1" customWidth="1"/>
     <col min="29" max="30" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="1.125" style="1" customWidth="1"/>
+    <col min="31" max="31" width="1.1640625" style="1" customWidth="1"/>
     <col min="32" max="32" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="5.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="5.625" style="1" customWidth="1"/>
-    <col min="36" max="36" width="6.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="5.6640625" style="1" customWidth="1"/>
+    <col min="36" max="36" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="31"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="31" t="s">
-        <v>115</v>
-      </c>
-      <c r="U2" s="31"/>
-      <c r="V2" s="31"/>
-      <c r="W2" s="31"/>
-      <c r="X2" s="31"/>
-      <c r="Y2" s="31"/>
-      <c r="Z2" s="31"/>
-      <c r="AA2" s="31"/>
-      <c r="AB2" s="31"/>
-      <c r="AC2" s="31"/>
-      <c r="AD2" s="31"/>
-      <c r="AE2" s="31"/>
-      <c r="AF2" s="31"/>
-      <c r="AG2" s="31"/>
-      <c r="AH2" s="31"/>
-      <c r="AI2" s="31"/>
-      <c r="AJ2" s="31"/>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
+      <c r="X2" s="32"/>
+      <c r="Y2" s="32"/>
+      <c r="Z2" s="32"/>
+      <c r="AA2" s="32"/>
+      <c r="AB2" s="32"/>
+      <c r="AC2" s="32"/>
+      <c r="AD2" s="32"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
+      <c r="AJ2" s="32"/>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A3" s="16"/>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
       <c r="G3" s="28"/>
-      <c r="H3" s="31" t="s">
+      <c r="H3" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
       <c r="M3" s="28"/>
-      <c r="N3" s="31" t="s">
+      <c r="N3" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-      <c r="T3" s="32" t="s">
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
+      <c r="R3" s="32"/>
+      <c r="T3" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="U3" s="32"/>
-      <c r="V3" s="32"/>
-      <c r="W3" s="32"/>
-      <c r="X3" s="32"/>
+      <c r="U3" s="33"/>
+      <c r="V3" s="33"/>
+      <c r="W3" s="33"/>
+      <c r="X3" s="33"/>
       <c r="Y3" s="28"/>
-      <c r="Z3" s="31" t="s">
+      <c r="Z3" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="AA3" s="31"/>
-      <c r="AB3" s="31"/>
-      <c r="AC3" s="31"/>
-      <c r="AD3" s="31"/>
+      <c r="AA3" s="32"/>
+      <c r="AB3" s="32"/>
+      <c r="AC3" s="32"/>
+      <c r="AD3" s="32"/>
       <c r="AE3" s="28"/>
-      <c r="AF3" s="31" t="s">
+      <c r="AF3" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="AG3" s="31"/>
-      <c r="AH3" s="31"/>
-      <c r="AI3" s="31"/>
-      <c r="AJ3" s="31"/>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AG3" s="32"/>
+      <c r="AH3" s="32"/>
+      <c r="AI3" s="32"/>
+      <c r="AJ3" s="32"/>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
       <c r="B4" s="29" t="s">
         <v>90</v>
@@ -2321,10 +2426,10 @@
         <v>92</v>
       </c>
       <c r="E4" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="F4" s="29" t="s">
         <v>135</v>
-      </c>
-      <c r="F4" s="29" t="s">
-        <v>136</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29" t="s">
@@ -2337,10 +2442,10 @@
         <v>92</v>
       </c>
       <c r="K4" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="L4" s="29" t="s">
         <v>135</v>
-      </c>
-      <c r="L4" s="29" t="s">
-        <v>136</v>
       </c>
       <c r="M4" s="29"/>
       <c r="N4" s="29" t="s">
@@ -2353,10 +2458,10 @@
         <v>92</v>
       </c>
       <c r="Q4" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="R4" s="29" t="s">
         <v>135</v>
-      </c>
-      <c r="R4" s="29" t="s">
-        <v>136</v>
       </c>
       <c r="S4" s="6"/>
       <c r="T4" s="29" t="s">
@@ -2369,10 +2474,10 @@
         <v>92</v>
       </c>
       <c r="W4" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="X4" s="29" t="s">
         <v>135</v>
-      </c>
-      <c r="X4" s="29" t="s">
-        <v>136</v>
       </c>
       <c r="Y4" s="17"/>
       <c r="Z4" s="29" t="s">
@@ -2385,10 +2490,10 @@
         <v>92</v>
       </c>
       <c r="AC4" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="AD4" s="29" t="s">
         <v>135</v>
-      </c>
-      <c r="AD4" s="29" t="s">
-        <v>136</v>
       </c>
       <c r="AE4" s="17"/>
       <c r="AF4" s="29" t="s">
@@ -2401,13 +2506,13 @@
         <v>92</v>
       </c>
       <c r="AI4" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="AJ4" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="AJ4" s="29" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
         <v>85</v>
       </c>
@@ -2446,9 +2551,9 @@
       <c r="AI5" s="16"/>
       <c r="AJ5" s="16"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B6" s="16">
         <v>12.162000000000001</v>
@@ -2545,9 +2650,9 @@
         <v>12.236000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B7" s="16">
         <v>-9.1289999999999996</v>
@@ -2644,7 +2749,7 @@
         <v>-7.7560000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A8" s="16"/>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -2681,7 +2786,7 @@
       <c r="AI8" s="18"/>
       <c r="AJ8" s="16"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A9" s="17" t="s">
         <v>86</v>
       </c>
@@ -2720,9 +2825,9 @@
       <c r="AI9" s="16"/>
       <c r="AJ9" s="16"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B10" s="16">
         <v>-0.312</v>
@@ -2819,9 +2924,9 @@
         <v>-0.24</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B11" s="16">
         <v>0.13200000000000001</v>
@@ -2918,9 +3023,9 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B12" s="16">
         <v>0.16300000000000001</v>
@@ -3017,9 +3122,9 @@
         <v>0.14899999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B13" s="16">
         <v>-5.5E-2</v>
@@ -3116,7 +3221,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A14" s="16" t="s">
         <v>88</v>
       </c>
@@ -3215,7 +3320,7 @@
         <v>0.28799999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A15" s="16"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -3252,7 +3357,7 @@
       <c r="AI15" s="18"/>
       <c r="AJ15" s="16"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
         <v>87</v>
       </c>
@@ -3291,9 +3396,9 @@
       <c r="AI16" s="16"/>
       <c r="AJ16" s="16"/>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B17" s="16">
         <v>0.34100000000000003</v>
@@ -3390,9 +3495,9 @@
         <v>0.443</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>94</v>
@@ -3489,9 +3594,9 @@
         <v>-0.10299999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>94</v>
@@ -3588,9 +3693,9 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B20" s="16" t="s">
         <v>94</v>
@@ -3687,9 +3792,9 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B21" s="16" t="s">
         <v>94</v>
@@ -3786,9 +3891,9 @@
         <v>-0.13600000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>94</v>
@@ -3883,9 +3988,9 @@
         <v>0.156</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B23" s="16" t="s">
         <v>94</v>
@@ -3980,9 +4085,9 @@
         <v>-1.6E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B24" s="16" t="s">
         <v>94</v>
@@ -4077,9 +4182,9 @@
         <v>0.112</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A25" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B25" s="16" t="s">
         <v>94</v>
@@ -4174,9 +4279,9 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>94</v>
@@ -4271,7 +4376,7 @@
         <v>-4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -4308,7 +4413,7 @@
       <c r="AI27" s="18"/>
       <c r="AJ27" s="16"/>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A28" s="17" t="s">
         <v>82</v>
       </c>
@@ -4347,7 +4452,7 @@
       <c r="AI28" s="16"/>
       <c r="AJ28" s="16"/>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A29" s="16" t="s">
         <v>84</v>
       </c>
@@ -4446,7 +4551,7 @@
         <v>14.164999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A30" s="16" t="s">
         <v>89</v>
       </c>
@@ -4545,7 +4650,7 @@
         <v>4.1660000000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A31" s="16" t="s">
         <v>93</v>
       </c>
@@ -4644,9 +4749,9 @@
         <v>1.0549999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A32" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B32" s="16" t="s">
         <v>94</v>
@@ -4741,9 +4846,9 @@
         <v>4.202</v>
       </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A33" s="20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -4784,69 +4889,63 @@
       <c r="AL33" s="16"/>
       <c r="AM33" s="16"/>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B34" s="33">
+        <v>117</v>
+      </c>
+      <c r="B34" s="31">
         <v>74058.118000000002</v>
       </c>
-      <c r="C34" s="33"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="33"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31"/>
       <c r="G34" s="27"/>
-      <c r="H34" s="33">
+      <c r="H34" s="31">
         <v>83016.937999999995</v>
       </c>
-      <c r="I34" s="33"/>
-      <c r="J34" s="33"/>
-      <c r="K34" s="33"/>
-      <c r="L34" s="33"/>
+      <c r="I34" s="31"/>
+      <c r="J34" s="31"/>
+      <c r="K34" s="31"/>
+      <c r="L34" s="31"/>
       <c r="M34" s="27"/>
-      <c r="N34" s="33">
+      <c r="N34" s="31">
         <v>94345.274999999994</v>
       </c>
-      <c r="O34" s="33"/>
-      <c r="P34" s="33"/>
-      <c r="Q34" s="33"/>
-      <c r="R34" s="33"/>
+      <c r="O34" s="31"/>
+      <c r="P34" s="31"/>
+      <c r="Q34" s="31"/>
+      <c r="R34" s="31"/>
       <c r="S34" s="15"/>
-      <c r="T34" s="33">
+      <c r="T34" s="31">
         <v>83167.763000000006</v>
       </c>
-      <c r="U34" s="33"/>
-      <c r="V34" s="33"/>
-      <c r="W34" s="33"/>
-      <c r="X34" s="33"/>
+      <c r="U34" s="31"/>
+      <c r="V34" s="31"/>
+      <c r="W34" s="31"/>
+      <c r="X34" s="31"/>
       <c r="Y34" s="27"/>
-      <c r="Z34" s="33">
+      <c r="Z34" s="31">
         <v>93083.505999999994</v>
       </c>
-      <c r="AA34" s="33"/>
-      <c r="AB34" s="33"/>
-      <c r="AC34" s="33"/>
-      <c r="AD34" s="33"/>
+      <c r="AA34" s="31"/>
+      <c r="AB34" s="31"/>
+      <c r="AC34" s="31"/>
+      <c r="AD34" s="31"/>
       <c r="AE34" s="27"/>
-      <c r="AF34" s="33">
+      <c r="AF34" s="31">
         <v>105770.462</v>
       </c>
-      <c r="AG34" s="33"/>
-      <c r="AH34" s="33"/>
-      <c r="AI34" s="33"/>
-      <c r="AJ34" s="33"/>
+      <c r="AG34" s="31"/>
+      <c r="AH34" s="31"/>
+      <c r="AI34" s="31"/>
+      <c r="AJ34" s="31"/>
       <c r="AK34" s="16"/>
       <c r="AL34" s="16"/>
       <c r="AM34" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="AF34:AJ34"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="H34:L34"/>
-    <mergeCell ref="T34:X34"/>
-    <mergeCell ref="N34:R34"/>
-    <mergeCell ref="Z34:AD34"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="H3:L3"/>
@@ -4855,6 +4954,12 @@
     <mergeCell ref="T3:X3"/>
     <mergeCell ref="Z3:AD3"/>
     <mergeCell ref="AF3:AJ3"/>
+    <mergeCell ref="AF34:AJ34"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="H34:L34"/>
+    <mergeCell ref="T34:X34"/>
+    <mergeCell ref="N34:R34"/>
+    <mergeCell ref="Z34:AD34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -4864,141 +4969,141 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CD5CF7F-81D6-D24D-8228-B4C578C35D65}">
   <dimension ref="A1:AM39"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" style="1" customWidth="1"/>
     <col min="5" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="1.1640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.6640625" style="1" customWidth="1"/>
     <col min="11" max="11" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="1.125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="1.1640625" style="1" customWidth="1"/>
     <col min="14" max="14" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.6640625" style="1" customWidth="1"/>
     <col min="17" max="17" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="0.875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="0.83203125" style="1" customWidth="1"/>
     <col min="20" max="20" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.6640625" style="1" customWidth="1"/>
     <col min="24" max="24" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="1" style="1" customWidth="1"/>
     <col min="26" max="26" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="30" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="1.125" style="1" customWidth="1"/>
+    <col min="31" max="31" width="1.1640625" style="1" customWidth="1"/>
     <col min="32" max="32" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="5.625" style="1" customWidth="1"/>
+    <col min="33" max="33" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.6640625" style="1" customWidth="1"/>
     <col min="35" max="36" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="31"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="31" t="s">
-        <v>115</v>
-      </c>
-      <c r="U2" s="31"/>
-      <c r="V2" s="31"/>
-      <c r="W2" s="31"/>
-      <c r="X2" s="31"/>
-      <c r="Y2" s="31"/>
-      <c r="Z2" s="31"/>
-      <c r="AA2" s="31"/>
-      <c r="AB2" s="31"/>
-      <c r="AC2" s="31"/>
-      <c r="AD2" s="31"/>
-      <c r="AE2" s="31"/>
-      <c r="AF2" s="31"/>
-      <c r="AG2" s="31"/>
-      <c r="AH2" s="31"/>
-      <c r="AI2" s="31"/>
-      <c r="AJ2" s="31"/>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
+      <c r="X2" s="32"/>
+      <c r="Y2" s="32"/>
+      <c r="Z2" s="32"/>
+      <c r="AA2" s="32"/>
+      <c r="AB2" s="32"/>
+      <c r="AC2" s="32"/>
+      <c r="AD2" s="32"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
+      <c r="AJ2" s="32"/>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A3" s="16"/>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
       <c r="G3" s="28"/>
-      <c r="H3" s="31" t="s">
+      <c r="H3" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
       <c r="M3" s="28"/>
-      <c r="N3" s="31" t="s">
+      <c r="N3" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="O3" s="31"/>
-      <c r="P3" s="31"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-      <c r="T3" s="32" t="s">
+      <c r="O3" s="32"/>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="32"/>
+      <c r="R3" s="32"/>
+      <c r="T3" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="U3" s="32"/>
-      <c r="V3" s="32"/>
-      <c r="W3" s="32"/>
-      <c r="X3" s="32"/>
+      <c r="U3" s="33"/>
+      <c r="V3" s="33"/>
+      <c r="W3" s="33"/>
+      <c r="X3" s="33"/>
       <c r="Y3" s="28"/>
-      <c r="Z3" s="31" t="s">
+      <c r="Z3" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="AA3" s="31"/>
-      <c r="AB3" s="31"/>
-      <c r="AC3" s="31"/>
-      <c r="AD3" s="31"/>
+      <c r="AA3" s="32"/>
+      <c r="AB3" s="32"/>
+      <c r="AC3" s="32"/>
+      <c r="AD3" s="32"/>
       <c r="AE3" s="28"/>
-      <c r="AF3" s="31" t="s">
+      <c r="AF3" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="AG3" s="31"/>
-      <c r="AH3" s="31"/>
-      <c r="AI3" s="31"/>
-      <c r="AJ3" s="31"/>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AG3" s="32"/>
+      <c r="AH3" s="32"/>
+      <c r="AI3" s="32"/>
+      <c r="AJ3" s="32"/>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
       <c r="B4" s="29" t="s">
         <v>90</v>
@@ -5010,10 +5115,10 @@
         <v>92</v>
       </c>
       <c r="E4" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="F4" s="29" t="s">
         <v>135</v>
-      </c>
-      <c r="F4" s="29" t="s">
-        <v>136</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29" t="s">
@@ -5026,10 +5131,10 @@
         <v>92</v>
       </c>
       <c r="K4" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="L4" s="29" t="s">
         <v>135</v>
-      </c>
-      <c r="L4" s="29" t="s">
-        <v>136</v>
       </c>
       <c r="M4" s="29"/>
       <c r="N4" s="29" t="s">
@@ -5042,10 +5147,10 @@
         <v>92</v>
       </c>
       <c r="Q4" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="R4" s="29" t="s">
         <v>135</v>
-      </c>
-      <c r="R4" s="29" t="s">
-        <v>136</v>
       </c>
       <c r="S4" s="6"/>
       <c r="T4" s="29" t="s">
@@ -5058,10 +5163,10 @@
         <v>92</v>
       </c>
       <c r="W4" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="X4" s="29" t="s">
         <v>135</v>
-      </c>
-      <c r="X4" s="29" t="s">
-        <v>136</v>
       </c>
       <c r="Y4" s="17"/>
       <c r="Z4" s="29" t="s">
@@ -5074,10 +5179,10 @@
         <v>92</v>
       </c>
       <c r="AC4" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="AD4" s="29" t="s">
         <v>135</v>
-      </c>
-      <c r="AD4" s="29" t="s">
-        <v>136</v>
       </c>
       <c r="AE4" s="17"/>
       <c r="AF4" s="29" t="s">
@@ -5090,13 +5195,13 @@
         <v>92</v>
       </c>
       <c r="AI4" s="29" t="s">
+        <v>134</v>
+      </c>
+      <c r="AJ4" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="AJ4" s="29" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
         <v>85</v>
       </c>
@@ -5135,9 +5240,9 @@
       <c r="AI5" s="16"/>
       <c r="AJ5" s="16"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B6" s="16">
         <v>13.944000000000001</v>
@@ -5214,9 +5319,9 @@
         <v>13.875999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B7" s="16">
         <v>-7.5229999999999997</v>
@@ -5293,9 +5398,9 @@
         <v>2.1219999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B8" s="16">
         <v>-0.253</v>
@@ -5342,7 +5447,7 @@
       <c r="AI8" s="16"/>
       <c r="AJ8" s="16"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A9" s="16"/>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
@@ -5379,7 +5484,7 @@
       <c r="AI9" s="18"/>
       <c r="AJ9" s="16"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A10" s="17" t="s">
         <v>86</v>
       </c>
@@ -5418,9 +5523,9 @@
       <c r="AI10" s="16"/>
       <c r="AJ10" s="16"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B11" s="16" t="s">
         <v>94</v>
@@ -5517,9 +5622,9 @@
         <v>0.40300000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B12" s="16">
         <v>0.11700000000000001</v>
@@ -5566,9 +5671,9 @@
       <c r="AI12" s="16"/>
       <c r="AJ12" s="16"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B13" s="16">
         <v>0.02</v>
@@ -5645,9 +5750,9 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B14" s="16">
         <v>6.9000000000000006E-2</v>
@@ -5724,9 +5829,9 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>94</v>
@@ -5793,9 +5898,9 @@
       <c r="AI15" s="16"/>
       <c r="AJ15" s="16"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>94</v>
@@ -5872,9 +5977,9 @@
         <v>0.22900000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B17" s="16">
         <v>-0.45300000000000001</v>
@@ -5921,7 +6026,7 @@
       <c r="AI17" s="16"/>
       <c r="AJ17" s="16"/>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
         <v>88</v>
       </c>
@@ -6000,7 +6105,7 @@
         <v>0.28799999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A19" s="16"/>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -6037,7 +6142,7 @@
       <c r="AI19" s="18"/>
       <c r="AJ19" s="16"/>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A20" s="17" t="s">
         <v>87</v>
       </c>
@@ -6076,9 +6181,9 @@
       <c r="AI20" s="16"/>
       <c r="AJ20" s="16"/>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B21" s="16">
         <v>-0.29099999999999998</v>
@@ -6125,9 +6230,9 @@
       <c r="AI21" s="16"/>
       <c r="AJ21" s="16"/>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>94</v>
@@ -6224,9 +6329,9 @@
         <v>0.14499999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B23" s="16" t="s">
         <v>94</v>
@@ -6303,9 +6408,9 @@
         <v>-9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B24" s="16" t="s">
         <v>94</v>
@@ -6382,9 +6487,9 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A25" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B25" s="16" t="s">
         <v>94</v>
@@ -6461,9 +6566,9 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>94</v>
@@ -6540,9 +6645,9 @@
         <v>-0.13600000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B27" s="16" t="s">
         <v>94</v>
@@ -6627,9 +6732,9 @@
         <v>0.17199999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B28" s="16" t="s">
         <v>94</v>
@@ -6714,9 +6819,9 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A29" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B29" s="16" t="s">
         <v>94</v>
@@ -6801,9 +6906,9 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A30" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B30" s="16" t="s">
         <v>94</v>
@@ -6888,9 +6993,9 @@
         <v>0.17499999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A31" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B31" s="16" t="s">
         <v>94</v>
@@ -6975,7 +7080,7 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A32" s="16"/>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
@@ -7012,7 +7117,7 @@
       <c r="AI32" s="18"/>
       <c r="AJ32" s="16"/>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A33" s="17" t="s">
         <v>82</v>
       </c>
@@ -7051,7 +7156,7 @@
       <c r="AI33" s="16"/>
       <c r="AJ33" s="16"/>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A34" s="16" t="s">
         <v>84</v>
       </c>
@@ -7130,7 +7235,7 @@
         <v>14.162000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A35" s="16" t="s">
         <v>89</v>
       </c>
@@ -7209,7 +7314,7 @@
         <v>4.1660000000000004</v>
       </c>
     </row>
-    <row r="36" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A36" s="16" t="s">
         <v>93</v>
       </c>
@@ -7288,9 +7393,9 @@
         <v>1.0549999999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A37" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B37" s="16" t="s">
         <v>94</v>
@@ -7375,9 +7480,9 @@
         <v>4.5090000000000003</v>
       </c>
     </row>
-    <row r="38" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A38" s="20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
@@ -7418,53 +7523,53 @@
       <c r="AL38" s="16"/>
       <c r="AM38" s="16"/>
     </row>
-    <row r="39" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A39" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B39" s="33">
+        <v>117</v>
+      </c>
+      <c r="B39" s="31">
         <v>34697.703999999998</v>
       </c>
-      <c r="C39" s="33"/>
-      <c r="D39" s="33"/>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
       <c r="G39" s="27"/>
-      <c r="H39" s="33"/>
-      <c r="I39" s="33"/>
-      <c r="J39" s="33"/>
-      <c r="K39" s="33"/>
-      <c r="L39" s="33"/>
+      <c r="H39" s="31"/>
+      <c r="I39" s="31"/>
+      <c r="J39" s="31"/>
+      <c r="K39" s="31"/>
+      <c r="L39" s="31"/>
       <c r="M39" s="27"/>
-      <c r="N39" s="33"/>
-      <c r="O39" s="33"/>
-      <c r="P39" s="33"/>
-      <c r="Q39" s="33"/>
-      <c r="R39" s="33"/>
+      <c r="N39" s="31"/>
+      <c r="O39" s="31"/>
+      <c r="P39" s="31"/>
+      <c r="Q39" s="31"/>
+      <c r="R39" s="31"/>
       <c r="S39" s="15"/>
-      <c r="T39" s="33">
+      <c r="T39" s="31">
         <v>37782.404000000002</v>
       </c>
-      <c r="U39" s="33"/>
-      <c r="V39" s="33"/>
-      <c r="W39" s="33"/>
-      <c r="X39" s="33"/>
+      <c r="U39" s="31"/>
+      <c r="V39" s="31"/>
+      <c r="W39" s="31"/>
+      <c r="X39" s="31"/>
       <c r="Y39" s="27"/>
-      <c r="Z39" s="33">
+      <c r="Z39" s="31">
         <v>47698.324999999997</v>
       </c>
-      <c r="AA39" s="33"/>
-      <c r="AB39" s="33"/>
-      <c r="AC39" s="33"/>
-      <c r="AD39" s="33"/>
+      <c r="AA39" s="31"/>
+      <c r="AB39" s="31"/>
+      <c r="AC39" s="31"/>
+      <c r="AD39" s="31"/>
       <c r="AE39" s="27"/>
-      <c r="AF39" s="33">
+      <c r="AF39" s="31">
         <v>60402.93</v>
       </c>
-      <c r="AG39" s="33"/>
-      <c r="AH39" s="33"/>
-      <c r="AI39" s="33"/>
-      <c r="AJ39" s="33"/>
+      <c r="AG39" s="31"/>
+      <c r="AH39" s="31"/>
+      <c r="AI39" s="31"/>
+      <c r="AJ39" s="31"/>
       <c r="AK39" s="16"/>
       <c r="AL39" s="16"/>
       <c r="AM39" s="16"/>
@@ -7493,604 +7598,601 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57A86273-0E84-8246-B3ED-A023C6721217}">
-  <dimension ref="A1:M38"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L38"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="11" style="1"/>
+    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.1640625" style="38" customWidth="1"/>
+    <col min="3" max="3" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5" style="35" customWidth="1"/>
+    <col min="7" max="7" width="11" style="1"/>
+    <col min="8" max="8" width="6.1640625" style="38" customWidth="1"/>
+    <col min="9" max="9" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.5" style="35" customWidth="1"/>
+    <col min="13" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="14"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="44"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="44"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="15"/>
+      <c r="B3" s="43" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="44"/>
+      <c r="H3" s="43" t="s">
+        <v>142</v>
+      </c>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="44"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="16"/>
+      <c r="B4" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" s="34" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="14"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="15"/>
-      <c r="B3" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="G3" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="16"/>
-      <c r="B4" s="17" t="s">
+      <c r="F4" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="H4" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="I4" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="J4" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="E4" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="J4" s="17" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="L4" s="34" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
       <c r="E5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
+      <c r="H5" s="39"/>
       <c r="I5" s="16"/>
       <c r="J5" s="16"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="16"/>
+    </row>
+    <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="16">
+        <v>0.17599999999999999</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="16"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="16"/>
+    </row>
+    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="16"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="18"/>
+      <c r="B7" s="39">
+        <v>-9.1010000000000009</v>
+      </c>
+      <c r="C7" s="16">
+        <v>0.74299999999999999</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>24</v>
+      </c>
       <c r="E7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="16"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H7" s="39"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="16"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="16"/>
+      <c r="B8" s="39"/>
       <c r="C8" s="16"/>
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
+      <c r="H8" s="39"/>
       <c r="I8" s="16"/>
       <c r="J8" s="16"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8" s="16"/>
+    </row>
+    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" s="39">
+        <v>-0.28799999999999998</v>
+      </c>
+      <c r="C9" s="16">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="16"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="16"/>
+    </row>
+    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="16"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B10" s="16">
-        <v>2.3919999999999999</v>
-      </c>
-      <c r="C10" s="16"/>
+      <c r="B10" s="39">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="C10" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
       <c r="D10" s="18">
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="E10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="16"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H10" s="39"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="16"/>
+    </row>
+    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B11" s="39">
+        <v>0.124</v>
+      </c>
+      <c r="C11" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="16"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="16"/>
+    </row>
+    <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+      <c r="A12" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="B11" s="16">
-        <v>0.76400000000000001</v>
-      </c>
-      <c r="C11" s="16"/>
-      <c r="D11" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="16"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="B12" s="25">
-        <v>-4.1000000000000002E-2</v>
-      </c>
-      <c r="C12" s="25"/>
+      <c r="B12" s="40">
+        <v>-3.2000000000000001E-2</v>
+      </c>
+      <c r="C12" s="25">
+        <v>3.9E-2</v>
+      </c>
       <c r="D12" s="26">
-        <v>0.40300000000000002</v>
+        <v>0.40699999999999997</v>
       </c>
       <c r="E12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="16"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H12" s="45"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="16"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="16">
-        <v>0.03</v>
-      </c>
+      <c r="B13" s="39"/>
       <c r="C13" s="16"/>
-      <c r="D13" s="18" t="s">
-        <v>24</v>
-      </c>
+      <c r="D13" s="18"/>
       <c r="E13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="16"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H13" s="39"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="16"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B14" s="16"/>
+      <c r="B14" s="39"/>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
+      <c r="H14" s="39"/>
       <c r="I14" s="16"/>
       <c r="J14" s="16"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K14" s="16"/>
+    </row>
+    <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="B15" s="16">
-        <v>3.1</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="B15" s="39"/>
       <c r="C15" s="16"/>
       <c r="D15" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E15" s="16"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="16"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="16"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H15" s="39"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="16"/>
+    </row>
+    <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="B16" s="16"/>
+        <v>102</v>
+      </c>
+      <c r="B16" s="39"/>
       <c r="C16" s="16"/>
       <c r="D16" s="18"/>
       <c r="E16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="16"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H16" s="39"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="16"/>
+    </row>
+    <row r="17" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="B17" s="16"/>
+        <v>103</v>
+      </c>
+      <c r="B17" s="39"/>
       <c r="C17" s="16"/>
       <c r="D17" s="18"/>
       <c r="E17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="16"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H17" s="39"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="16"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="B18" s="16">
-        <v>-7.8E-2</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="B18" s="39"/>
       <c r="C18" s="16"/>
       <c r="D18" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="16"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H18" s="39"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="16"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B19" s="16">
-        <v>-1.2E-2</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="B19" s="39"/>
       <c r="C19" s="16"/>
       <c r="D19" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="16"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H19" s="39"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="16"/>
+    </row>
+    <row r="20" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="B20" s="16"/>
+        <v>104</v>
+      </c>
+      <c r="B20" s="39"/>
       <c r="C20" s="16"/>
       <c r="D20" s="18"/>
       <c r="E20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="16"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H20" s="39"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="16"/>
+    </row>
+    <row r="21" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="B21" s="16"/>
+        <v>105</v>
+      </c>
+      <c r="B21" s="39"/>
       <c r="C21" s="16"/>
       <c r="D21" s="18"/>
       <c r="E21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="18"/>
-      <c r="J21" s="16"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H21" s="39"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="16"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B22" s="16">
-        <v>4.7E-2</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="B22" s="39"/>
       <c r="C22" s="16"/>
       <c r="D22" s="18">
         <v>0.51400000000000001</v>
       </c>
       <c r="E22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="16"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H22" s="39"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="16"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="B23" s="16">
-        <v>1.41</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="B23" s="39"/>
       <c r="C23" s="16"/>
       <c r="D23" s="18">
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="E23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="18"/>
-      <c r="J23" s="16"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H23" s="39"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="18"/>
+      <c r="K23" s="16"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="B24" s="16"/>
+        <v>110</v>
+      </c>
+      <c r="B24" s="39"/>
       <c r="C24" s="16"/>
       <c r="D24" s="18"/>
       <c r="E24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="18"/>
-      <c r="J24" s="16"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H24" s="39"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="18"/>
+      <c r="K24" s="16"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="B25" s="16"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
       <c r="E25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
+      <c r="H25" s="39"/>
       <c r="I25" s="16"/>
       <c r="J25" s="16"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K25" s="16"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="B26" s="16">
-        <v>12.433</v>
-      </c>
+      <c r="B26" s="39"/>
       <c r="C26" s="16"/>
       <c r="D26" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="18"/>
-      <c r="J26" s="16"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H26" s="39"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="18"/>
+      <c r="K26" s="16"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B27" s="16">
-        <v>0.60799999999999998</v>
-      </c>
+      <c r="B27" s="39"/>
       <c r="C27" s="16"/>
       <c r="D27" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="18"/>
-      <c r="J27" s="16"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H27" s="39"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="16"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B28" s="16">
-        <v>1.83</v>
-      </c>
-      <c r="C28" s="16">
-        <v>0.04</v>
-      </c>
+      <c r="B28" s="39"/>
+      <c r="C28" s="16"/>
       <c r="D28" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="18"/>
-      <c r="J28" s="16"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H28" s="39"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="16"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="B29" s="16"/>
+        <v>111</v>
+      </c>
+      <c r="B29" s="39"/>
       <c r="C29" s="16"/>
       <c r="D29" s="18"/>
       <c r="E29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="18"/>
-      <c r="J29" s="16"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H29" s="39"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="16"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="B30" s="16"/>
+      <c r="B30" s="39"/>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
+      <c r="H30" s="39"/>
       <c r="I30" s="16"/>
       <c r="J30" s="16"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K30" s="16"/>
+    </row>
+    <row r="31" spans="1:11" ht="17" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" s="39"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="16"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="16"/>
+      <c r="J31" s="18"/>
+      <c r="K31" s="16"/>
+    </row>
+    <row r="32" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+      <c r="A32" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B31" s="16">
-        <v>2199.7800000000002</v>
-      </c>
-      <c r="C31" s="16">
-        <v>74.569999999999993</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="18"/>
-      <c r="J31" s="16"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B32" s="16">
-        <v>93.71</v>
-      </c>
-      <c r="C32" s="16">
-        <v>14.08</v>
-      </c>
+      <c r="B32" s="39"/>
+      <c r="C32" s="16"/>
       <c r="D32" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E32" s="16"/>
-      <c r="G32" s="16"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="18"/>
-      <c r="J32" s="16"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H32" s="39"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="18"/>
+      <c r="K32" s="16"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="B33" s="16">
-        <v>0.93400000000000005</v>
-      </c>
+      <c r="B33" s="39"/>
       <c r="C33" s="16"/>
       <c r="D33" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="16"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H33" s="39"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="16"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B34" s="16">
-        <v>1.7000000000000001E-2</v>
-      </c>
+      <c r="B34" s="39"/>
       <c r="C34" s="16"/>
       <c r="D34" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="16"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H34" s="39"/>
+      <c r="I34" s="16"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="16"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B35" s="16"/>
+      <c r="B35" s="39"/>
       <c r="C35" s="16"/>
       <c r="D35" s="18"/>
       <c r="E35" s="16"/>
-      <c r="G35" s="16"/>
-      <c r="H35" s="16"/>
-      <c r="I35" s="18"/>
-      <c r="J35" s="16"/>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H35" s="39"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="16"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="B36" s="16"/>
+        <v>111</v>
+      </c>
+      <c r="B36" s="39"/>
       <c r="C36" s="16"/>
       <c r="D36" s="18"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="18"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H36" s="39"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="18"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="B37" s="14"/>
+        <v>116</v>
+      </c>
+      <c r="B37" s="41"/>
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
+      <c r="F37" s="36"/>
       <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
+      <c r="H37" s="41"/>
       <c r="I37" s="14"/>
       <c r="J37" s="14"/>
       <c r="K37" s="14"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L37" s="36"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="B38" s="15"/>
+        <v>117</v>
+      </c>
+      <c r="B38" s="42"/>
       <c r="C38" s="15"/>
       <c r="D38" s="15"/>
       <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
+      <c r="F38" s="37"/>
       <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
+      <c r="H38" s="42"/>
       <c r="I38" s="15"/>
       <c r="J38" s="15"/>
       <c r="K38" s="15"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
+      <c r="L38" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B2:F2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8099,64 +8201,64 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{540507A6-720C-0B43-804E-087FEE710926}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.875" customWidth="1"/>
-    <col min="2" max="2" width="18.875" customWidth="1"/>
-    <col min="3" max="3" width="19.125" customWidth="1"/>
+    <col min="1" max="1" width="19.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="23" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="24"/>
+    </row>
+    <row r="3" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="24" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="24" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="24"/>
+    </row>
+    <row r="6" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="24"/>
+    </row>
+    <row r="7" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="23" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24"/>
-    </row>
-    <row r="3" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
-    </row>
-    <row r="6" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-    </row>
-    <row r="7" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="23" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="24" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="24" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B11" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>126</v>
       </c>
       <c r="B12">
         <v>-3.4000000000000002E-2</v>
@@ -8165,9 +8267,9 @@
         <v>-1.4E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B13">
         <v>-2.4E-2</v>
@@ -8176,9 +8278,9 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B14">
         <v>-2.3E-2</v>
@@ -8187,9 +8289,9 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B15">
         <v>-2.5999999999999999E-2</v>
@@ -8198,27 +8300,27 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="23" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="24" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B19" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="C19" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="C19" s="23" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B20">
         <v>-3.1E-2</v>
@@ -8227,9 +8329,9 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B21">
         <v>-0.03</v>
@@ -8238,9 +8340,9 @@
         <v>-1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B22">
         <v>-0.113</v>
@@ -8249,9 +8351,9 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B23">
         <v>-3.3000000000000002E-2</v>
@@ -8260,9 +8362,9 @@
         <v>-1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E25" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmoffice-my.sharepoint.com/personal/abrieant_uvm_edu/Documents/OneDrive/Manuscripts/reg report DCN/pubertybrain/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="13_ncr:1_{DF0C5C2D-21F6-4142-814F-EFC173B4BD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A66E4D3C-8232-9C46-9AFD-9E69F4CA7021}"/>
+  <xr:revisionPtr revIDLastSave="127" documentId="13_ncr:1_{DF0C5C2D-21F6-4142-814F-EFC173B4BD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A3236C2-F16F-5D43-B246-97BCCB3236A0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="500" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="146">
   <si>
     <t>16.10 (2.98)</t>
   </si>
@@ -352,9 +352,6 @@
   </si>
   <si>
     <t>Means</t>
-  </si>
-  <si>
-    <t>Variances</t>
   </si>
   <si>
     <t xml:space="preserve">   Timing</t>
@@ -823,6 +820,33 @@
   </si>
   <si>
     <t>12.311      0.203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Timing with Tempo</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   Slope</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> with Tempo</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1089,7 +1113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1166,6 +1190,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2247,7 +2272,7 @@
   <sheetData>
     <row r="2" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2320,13 +2345,13 @@
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
       <c r="B2" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -2346,7 +2371,7 @@
       <c r="R2" s="32"/>
       <c r="S2" s="9"/>
       <c r="T2" s="32" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U2" s="32"/>
       <c r="V2" s="32"/>
@@ -2417,104 +2442,104 @@
     <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
       <c r="B4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="D4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="E4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="F4" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="F4" s="29" t="s">
-        <v>135</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="J4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="K4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="L4" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="L4" s="29" t="s">
-        <v>135</v>
       </c>
       <c r="M4" s="29"/>
       <c r="N4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="O4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="O4" s="29" t="s">
+      <c r="P4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="P4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="Q4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="R4" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="R4" s="29" t="s">
-        <v>135</v>
       </c>
       <c r="S4" s="6"/>
       <c r="T4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="U4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="U4" s="29" t="s">
+      <c r="V4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="V4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="W4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="X4" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="X4" s="29" t="s">
-        <v>135</v>
       </c>
       <c r="Y4" s="17"/>
       <c r="Z4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="AA4" s="29" t="s">
+      <c r="AB4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="AB4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="AC4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD4" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="AD4" s="29" t="s">
-        <v>135</v>
       </c>
       <c r="AE4" s="17"/>
       <c r="AF4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="AG4" s="29" t="s">
+      <c r="AH4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="AH4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="AI4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="AJ4" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="AJ4" s="29" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -2553,7 +2578,7 @@
     </row>
     <row r="6" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B6" s="16">
         <v>12.162000000000001</v>
@@ -2652,7 +2677,7 @@
     </row>
     <row r="7" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B7" s="16">
         <v>-9.1289999999999996</v>
@@ -2788,7 +2813,7 @@
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A9" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
@@ -2827,7 +2852,7 @@
     </row>
     <row r="10" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B10" s="16">
         <v>-0.312</v>
@@ -2926,7 +2951,7 @@
     </row>
     <row r="11" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B11" s="16">
         <v>0.13200000000000001</v>
@@ -3025,7 +3050,7 @@
     </row>
     <row r="12" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B12" s="16">
         <v>0.16300000000000001</v>
@@ -3124,7 +3149,7 @@
     </row>
     <row r="13" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B13" s="16">
         <v>-5.5E-2</v>
@@ -3223,7 +3248,7 @@
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A14" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B14" s="16">
         <v>0.318</v>
@@ -3359,7 +3384,7 @@
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -3398,7 +3423,7 @@
     </row>
     <row r="17" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B17" s="16">
         <v>0.34100000000000003</v>
@@ -3497,22 +3522,22 @@
     </row>
     <row r="18" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G18" s="21"/>
       <c r="H18" s="16">
@@ -3547,19 +3572,19 @@
         <v>-0.11</v>
       </c>
       <c r="T18" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U18" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V18" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W18" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X18" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y18" s="21"/>
       <c r="Z18" s="16">
@@ -3596,22 +3621,22 @@
     </row>
     <row r="19" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G19" s="21"/>
       <c r="H19" s="22">
@@ -3646,19 +3671,19 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="T19" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U19" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V19" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W19" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X19" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y19" s="21"/>
       <c r="Z19" s="16">
@@ -3695,22 +3720,22 @@
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G20" s="21"/>
       <c r="H20" s="16">
@@ -3745,19 +3770,19 @@
         <v>-0.15</v>
       </c>
       <c r="T20" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U20" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V20" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W20" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X20" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y20" s="21"/>
       <c r="Z20" s="16">
@@ -3794,22 +3819,22 @@
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G21" s="21"/>
       <c r="H21" s="16">
@@ -3844,19 +3869,19 @@
         <v>-0.183</v>
       </c>
       <c r="T21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W21" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X21" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y21" s="21"/>
       <c r="Z21" s="16">
@@ -3893,38 +3918,38 @@
     </row>
     <row r="22" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G22" s="21"/>
       <c r="H22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M22" s="16"/>
       <c r="N22" s="16">
@@ -3943,33 +3968,33 @@
         <v>0.21099999999999999</v>
       </c>
       <c r="T22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W22" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X22" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y22" s="21"/>
       <c r="Z22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC22" s="16"/>
       <c r="AD22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE22" s="16"/>
       <c r="AF22" s="16">
@@ -3990,38 +4015,38 @@
     </row>
     <row r="23" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G23" s="21"/>
       <c r="H23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M23" s="16"/>
       <c r="N23" s="16">
@@ -4040,33 +4065,33 @@
         <v>6.3E-2</v>
       </c>
       <c r="T23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W23" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X23" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y23" s="21"/>
       <c r="Z23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC23" s="16"/>
       <c r="AD23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE23" s="16"/>
       <c r="AF23" s="16">
@@ -4087,38 +4112,38 @@
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G24" s="21"/>
       <c r="H24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M24" s="16"/>
       <c r="N24" s="16">
@@ -4137,33 +4162,33 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="T24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W24" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X24" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y24" s="21"/>
       <c r="Z24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC24" s="16"/>
       <c r="AD24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE24" s="16"/>
       <c r="AF24" s="16">
@@ -4184,38 +4209,38 @@
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A25" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G25" s="21"/>
       <c r="H25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M25" s="16"/>
       <c r="N25" s="16">
@@ -4234,33 +4259,33 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="T25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W25" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X25" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y25" s="21"/>
       <c r="Z25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC25" s="16"/>
       <c r="AD25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE25" s="16"/>
       <c r="AF25" s="16">
@@ -4281,38 +4306,38 @@
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G26" s="21"/>
       <c r="H26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M26" s="16"/>
       <c r="N26" s="16">
@@ -4331,33 +4356,33 @@
         <v>-7.1999999999999995E-2</v>
       </c>
       <c r="T26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W26" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X26" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y26" s="21"/>
       <c r="Z26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC26" s="16"/>
       <c r="AD26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE26" s="16"/>
       <c r="AF26" s="16">
@@ -4454,7 +4479,7 @@
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A29" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B29" s="16">
         <v>10.965999999999999</v>
@@ -4553,7 +4578,7 @@
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B30" s="16">
         <v>3.7069999999999999</v>
@@ -4652,22 +4677,22 @@
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G31" s="21"/>
       <c r="H31" s="16">
@@ -4702,19 +4727,19 @@
         <v>1.0429999999999999</v>
       </c>
       <c r="T31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X31" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y31" s="21"/>
       <c r="Z31" s="16">
@@ -4751,36 +4776,36 @@
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A32" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G32" s="21"/>
       <c r="H32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K32" s="16"/>
       <c r="L32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M32" s="16"/>
       <c r="N32" s="16">
@@ -4799,35 +4824,35 @@
         <v>4.5410000000000004</v>
       </c>
       <c r="T32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W32" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X32" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y32" s="21"/>
       <c r="Z32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC32" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AD32" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE32" s="16"/>
       <c r="AF32" s="16">
@@ -4848,7 +4873,7 @@
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A33" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -4891,7 +4916,7 @@
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B34" s="31">
         <v>74058.118000000002</v>
@@ -5009,13 +5034,13 @@
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
       <c r="B2" s="32" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
@@ -5035,7 +5060,7 @@
       <c r="R2" s="32"/>
       <c r="S2" s="9"/>
       <c r="T2" s="32" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="U2" s="32"/>
       <c r="V2" s="32"/>
@@ -5106,104 +5131,104 @@
     <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
       <c r="B4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="D4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="E4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="F4" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="F4" s="29" t="s">
-        <v>135</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="J4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="K4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="L4" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="L4" s="29" t="s">
-        <v>135</v>
       </c>
       <c r="M4" s="29"/>
       <c r="N4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="O4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="O4" s="29" t="s">
+      <c r="P4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="P4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="Q4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="R4" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="R4" s="29" t="s">
-        <v>135</v>
       </c>
       <c r="S4" s="6"/>
       <c r="T4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="U4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="U4" s="29" t="s">
+      <c r="V4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="V4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="W4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="X4" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="X4" s="29" t="s">
-        <v>135</v>
       </c>
       <c r="Y4" s="17"/>
       <c r="Z4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="AA4" s="29" t="s">
+      <c r="AB4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="AB4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="AC4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD4" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="AD4" s="29" t="s">
-        <v>135</v>
       </c>
       <c r="AE4" s="17"/>
       <c r="AF4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="AG4" s="29" t="s">
+      <c r="AH4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="AH4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="AI4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="AJ4" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="AJ4" s="29" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -5242,7 +5267,7 @@
     </row>
     <row r="6" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B6" s="16">
         <v>13.944000000000001</v>
@@ -5321,7 +5346,7 @@
     </row>
     <row r="7" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B7" s="16">
         <v>-7.5229999999999997</v>
@@ -5400,7 +5425,7 @@
     </row>
     <row r="8" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B8" s="16">
         <v>-0.253</v>
@@ -5486,7 +5511,7 @@
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A10" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -5525,54 +5550,54 @@
     </row>
     <row r="11" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G11" s="16"/>
       <c r="H11" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J11" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M11" s="16"/>
       <c r="N11" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O11" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P11" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q11" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R11" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T11" s="16">
         <v>0.318</v>
@@ -5624,7 +5649,7 @@
     </row>
     <row r="12" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B12" s="16">
         <v>0.11700000000000001</v>
@@ -5673,7 +5698,7 @@
     </row>
     <row r="13" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B13" s="16">
         <v>0.02</v>
@@ -5752,7 +5777,7 @@
     </row>
     <row r="14" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B14" s="16">
         <v>6.9000000000000006E-2</v>
@@ -5831,54 +5856,54 @@
     </row>
     <row r="15" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G15" s="21"/>
       <c r="H15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K15" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M15" s="16"/>
       <c r="N15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q15" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R15" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T15" s="16"/>
       <c r="U15" s="16"/>
@@ -5900,22 +5925,22 @@
     </row>
     <row r="16" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G16" s="16"/>
       <c r="H16" s="16"/>
@@ -5979,7 +6004,7 @@
     </row>
     <row r="17" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B17" s="16">
         <v>-0.45300000000000001</v>
@@ -6028,7 +6053,7 @@
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B18" s="16">
         <v>0.318</v>
@@ -6144,7 +6169,7 @@
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A20" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
@@ -6183,7 +6208,7 @@
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B21" s="16">
         <v>-0.29099999999999998</v>
@@ -6232,54 +6257,54 @@
     </row>
     <row r="22" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G22" s="16"/>
       <c r="H22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K22" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L22" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M22" s="16"/>
       <c r="N22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q22" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R22" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T22" s="16">
         <v>8.5000000000000006E-2</v>
@@ -6331,22 +6356,22 @@
     </row>
     <row r="23" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G23" s="21"/>
       <c r="H23" s="16"/>
@@ -6361,19 +6386,19 @@
       <c r="Q23" s="16"/>
       <c r="R23" s="16"/>
       <c r="T23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W23" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X23" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y23" s="21"/>
       <c r="Z23" s="16">
@@ -6410,22 +6435,22 @@
     </row>
     <row r="24" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G24" s="21"/>
       <c r="H24" s="22"/>
@@ -6440,19 +6465,19 @@
       <c r="Q24" s="16"/>
       <c r="R24" s="16"/>
       <c r="T24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W24" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X24" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y24" s="21"/>
       <c r="Z24" s="16">
@@ -6489,22 +6514,22 @@
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A25" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G25" s="21"/>
       <c r="H25" s="16"/>
@@ -6519,19 +6544,19 @@
       <c r="Q25" s="16"/>
       <c r="R25" s="16"/>
       <c r="T25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W25" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X25" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y25" s="21"/>
       <c r="Z25" s="16">
@@ -6568,22 +6593,22 @@
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G26" s="21"/>
       <c r="H26" s="16"/>
@@ -6598,19 +6623,19 @@
       <c r="Q26" s="16"/>
       <c r="R26" s="16"/>
       <c r="T26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W26" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X26" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y26" s="21"/>
       <c r="Z26" s="16">
@@ -6647,38 +6672,38 @@
     </row>
     <row r="27" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G27" s="21"/>
       <c r="H27" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I27" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J27" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M27" s="16"/>
       <c r="N27" s="16"/>
@@ -6687,33 +6712,33 @@
       <c r="Q27" s="16"/>
       <c r="R27" s="16"/>
       <c r="T27" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U27" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V27" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W27" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X27" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y27" s="21"/>
       <c r="Z27" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA27" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB27" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC27" s="16"/>
       <c r="AD27" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE27" s="16"/>
       <c r="AF27" s="16">
@@ -6734,38 +6759,38 @@
     </row>
     <row r="28" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F28" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G28" s="21"/>
       <c r="H28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M28" s="16"/>
       <c r="N28" s="16"/>
@@ -6774,33 +6799,33 @@
       <c r="Q28" s="16"/>
       <c r="R28" s="16"/>
       <c r="T28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W28" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X28" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y28" s="21"/>
       <c r="Z28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC28" s="16"/>
       <c r="AD28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE28" s="16"/>
       <c r="AF28" s="16">
@@ -6821,38 +6846,38 @@
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A29" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F29" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G29" s="21"/>
       <c r="H29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M29" s="16"/>
       <c r="N29" s="16"/>
@@ -6861,33 +6886,33 @@
       <c r="Q29" s="16"/>
       <c r="R29" s="16"/>
       <c r="T29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W29" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X29" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y29" s="21"/>
       <c r="Z29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC29" s="16"/>
       <c r="AD29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE29" s="16"/>
       <c r="AF29" s="16">
@@ -6908,38 +6933,38 @@
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A30" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G30" s="21"/>
       <c r="H30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M30" s="16"/>
       <c r="N30" s="16"/>
@@ -6948,33 +6973,33 @@
       <c r="Q30" s="16"/>
       <c r="R30" s="16"/>
       <c r="T30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W30" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X30" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y30" s="21"/>
       <c r="Z30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC30" s="16"/>
       <c r="AD30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE30" s="16"/>
       <c r="AF30" s="16">
@@ -6995,38 +7020,38 @@
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A31" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G31" s="21"/>
       <c r="H31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M31" s="16"/>
       <c r="N31" s="16"/>
@@ -7035,33 +7060,33 @@
       <c r="Q31" s="16"/>
       <c r="R31" s="16"/>
       <c r="T31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W31" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X31" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y31" s="21"/>
       <c r="Z31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC31" s="16"/>
       <c r="AD31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE31" s="16"/>
       <c r="AF31" s="16">
@@ -7158,7 +7183,7 @@
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A34" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B34" s="16">
         <v>10.965</v>
@@ -7237,7 +7262,7 @@
     </row>
     <row r="35" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A35" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B35" s="16">
         <v>3.7109999999999999</v>
@@ -7316,22 +7341,22 @@
     </row>
     <row r="36" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A36" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F36" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G36" s="21"/>
       <c r="H36" s="16"/>
@@ -7346,19 +7371,19 @@
       <c r="Q36" s="16"/>
       <c r="R36" s="16"/>
       <c r="T36" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U36" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V36" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W36" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X36" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y36" s="21"/>
       <c r="Z36" s="16">
@@ -7395,36 +7420,36 @@
     </row>
     <row r="37" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A37" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E37" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F37" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G37" s="21"/>
       <c r="H37" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I37" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J37" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K37" s="16"/>
       <c r="L37" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M37" s="16"/>
       <c r="N37" s="16"/>
@@ -7433,35 +7458,35 @@
       <c r="Q37" s="16"/>
       <c r="R37" s="16"/>
       <c r="T37" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U37" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V37" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W37" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X37" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y37" s="21"/>
       <c r="Z37" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA37" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB37" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC37" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AD37" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE37" s="16"/>
       <c r="AF37" s="16">
@@ -7482,7 +7507,7 @@
     </row>
     <row r="38" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A38" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
@@ -7525,7 +7550,7 @@
     </row>
     <row r="39" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A39" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B39" s="31">
         <v>34697.703999999998</v>
@@ -7598,7 +7623,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57A86273-0E84-8246-B3ED-A023C6721217}">
-  <dimension ref="A1:L38"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -7606,7 +7631,7 @@
     <col min="3" max="3" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5" style="35" customWidth="1"/>
+    <col min="6" max="6" width="7.5" style="48" customWidth="1"/>
     <col min="7" max="7" width="11" style="1"/>
     <col min="8" max="8" width="6.1640625" style="38" customWidth="1"/>
     <col min="9" max="9" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
@@ -7618,7 +7643,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -7637,14 +7662,14 @@
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="15"/>
       <c r="B3" s="43" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C3" s="32"/>
       <c r="D3" s="32"/>
       <c r="E3" s="32"/>
       <c r="F3" s="44"/>
       <c r="H3" s="43" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I3" s="32"/>
       <c r="J3" s="32"/>
@@ -7654,39 +7679,39 @@
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="16"/>
       <c r="B4" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="D4" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="34" t="s">
-        <v>92</v>
-      </c>
       <c r="E4" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="F4" s="34" t="s">
         <v>134</v>
       </c>
-      <c r="F4" s="34" t="s">
-        <v>135</v>
-      </c>
       <c r="H4" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="34" t="s">
+      <c r="J4" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="34" t="s">
-        <v>92</v>
-      </c>
       <c r="K4" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="L4" s="34" t="s">
         <v>134</v>
-      </c>
-      <c r="L4" s="34" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5" s="16"/>
       <c r="H5" s="39"/>
@@ -7696,10 +7721,10 @@
     </row>
     <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B6" s="39" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C6" s="16">
         <v>0.17599999999999999</v>
@@ -7707,7 +7732,12 @@
       <c r="D6" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="16"/>
+      <c r="E6" s="16">
+        <v>11.912000000000001</v>
+      </c>
+      <c r="F6" s="48">
+        <v>12.709</v>
+      </c>
       <c r="H6" s="39"/>
       <c r="I6" s="16"/>
       <c r="J6" s="18"/>
@@ -7715,7 +7745,7 @@
     </row>
     <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B7" s="39">
         <v>-9.1010000000000009</v>
@@ -7726,7 +7756,12 @@
       <c r="D7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="16"/>
+      <c r="E7" s="16">
+        <v>-10.558</v>
+      </c>
+      <c r="F7" s="48">
+        <v>-7.6449999999999996</v>
+      </c>
       <c r="H7" s="39"/>
       <c r="I7" s="16"/>
       <c r="J7" s="18"/>
@@ -7734,7 +7769,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B8" s="39"/>
       <c r="C8" s="16"/>
@@ -7747,7 +7782,7 @@
     </row>
     <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B9" s="39">
         <v>-0.28799999999999998</v>
@@ -7766,7 +7801,7 @@
     </row>
     <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B10" s="39">
         <v>5.2999999999999999E-2</v>
@@ -7785,7 +7820,7 @@
     </row>
     <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B11" s="39">
         <v>0.124</v>
@@ -7804,7 +7839,7 @@
     </row>
     <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="46" t="s">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="B12" s="40">
         <v>-3.2000000000000001E-2</v>
@@ -7823,11 +7858,17 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="B13" s="39"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="18"/>
+        <v>144</v>
+      </c>
+      <c r="B13" s="39">
+        <v>0.24099999999999999</v>
+      </c>
+      <c r="C13" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>24</v>
+      </c>
       <c r="E13" s="16"/>
       <c r="H13" s="39"/>
       <c r="I13" s="16"/>
@@ -7836,7 +7877,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B14" s="39"/>
       <c r="C14" s="16"/>
@@ -7849,10 +7890,14 @@
     </row>
     <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="16"/>
+        <v>100</v>
+      </c>
+      <c r="B15" s="39">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="C15" s="16">
+        <v>4.1000000000000002E-2</v>
+      </c>
       <c r="D15" s="18" t="s">
         <v>24</v>
       </c>
@@ -7864,36 +7909,52 @@
     </row>
     <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="18"/>
+        <v>101</v>
+      </c>
+      <c r="B16" s="39">
+        <v>-0.14499999999999999</v>
+      </c>
+      <c r="C16" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>24</v>
+      </c>
       <c r="E16" s="16"/>
       <c r="H16" s="39"/>
       <c r="I16" s="16"/>
       <c r="J16" s="18"/>
       <c r="K16" s="16"/>
     </row>
-    <row r="17" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="18"/>
+        <v>102</v>
+      </c>
+      <c r="B17" s="39">
+        <v>-2.1999999999999999E-2</v>
+      </c>
+      <c r="C17" s="16">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D17" s="18">
+        <v>0.56699999999999995</v>
+      </c>
       <c r="E17" s="16"/>
       <c r="H17" s="39"/>
       <c r="I17" s="16"/>
       <c r="J17" s="18"/>
       <c r="K17" s="16"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="B18" s="39"/>
-      <c r="C18" s="16"/>
+        <v>105</v>
+      </c>
+      <c r="B18" s="39">
+        <v>-0.14399999999999999</v>
+      </c>
+      <c r="C18" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
       <c r="D18" s="18" t="s">
         <v>24</v>
       </c>
@@ -7903,12 +7964,16 @@
       <c r="J18" s="18"/>
       <c r="K18" s="16"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="B19" s="39"/>
-      <c r="C19" s="16"/>
+        <v>106</v>
+      </c>
+      <c r="B19" s="39">
+        <v>-0.16600000000000001</v>
+      </c>
+      <c r="C19" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
       <c r="D19" s="18" t="s">
         <v>24</v>
       </c>
@@ -7918,40 +7983,56 @@
       <c r="J19" s="18"/>
       <c r="K19" s="16"/>
     </row>
-    <row r="20" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="B20" s="39"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="18"/>
+        <v>103</v>
+      </c>
+      <c r="B20" s="39">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="C20" s="16">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>24</v>
+      </c>
       <c r="E20" s="16"/>
       <c r="H20" s="39"/>
       <c r="I20" s="16"/>
       <c r="J20" s="18"/>
       <c r="K20" s="16"/>
     </row>
-    <row r="21" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="18"/>
+        <v>104</v>
+      </c>
+      <c r="B21" s="39">
+        <v>1E-3</v>
+      </c>
+      <c r="C21" s="16">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="D21" s="18">
+        <v>0.98199999999999998</v>
+      </c>
       <c r="E21" s="16"/>
       <c r="H21" s="39"/>
       <c r="I21" s="16"/>
       <c r="J21" s="18"/>
       <c r="K21" s="16"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="16"/>
+        <v>108</v>
+      </c>
+      <c r="B22" s="39">
+        <v>1.6E-2</v>
+      </c>
+      <c r="C22" s="16">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="D22" s="18">
-        <v>0.51400000000000001</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="E22" s="16"/>
       <c r="H22" s="39"/>
@@ -7959,12 +8040,16 @@
       <c r="J22" s="18"/>
       <c r="K22" s="16"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B23" s="39"/>
-      <c r="C23" s="16"/>
+        <v>107</v>
+      </c>
+      <c r="B23" s="39">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="C23" s="16">
+        <v>2.3E-2</v>
+      </c>
       <c r="D23" s="18">
         <v>4.0000000000000001E-3</v>
       </c>
@@ -7974,20 +8059,26 @@
       <c r="J23" s="18"/>
       <c r="K23" s="16"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="18"/>
+        <v>109</v>
+      </c>
+      <c r="B24" s="39">
+        <v>-0.12</v>
+      </c>
+      <c r="C24" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>24</v>
+      </c>
       <c r="E24" s="16"/>
       <c r="H24" s="39"/>
       <c r="I24" s="16"/>
       <c r="J24" s="18"/>
       <c r="K24" s="16"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="17" t="s">
         <v>82</v>
       </c>
@@ -8000,12 +8091,16 @@
       <c r="J25" s="16"/>
       <c r="K25" s="16"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B26" s="39"/>
-      <c r="C26" s="16"/>
+        <v>83</v>
+      </c>
+      <c r="B26" s="39">
+        <v>12.734</v>
+      </c>
+      <c r="C26" s="16">
+        <v>0.17599999999999999</v>
+      </c>
       <c r="D26" s="18" t="s">
         <v>24</v>
       </c>
@@ -8015,12 +8110,16 @@
       <c r="J26" s="18"/>
       <c r="K26" s="16"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B27" s="39"/>
-      <c r="C27" s="16"/>
+        <v>88</v>
+      </c>
+      <c r="B27" s="39">
+        <v>4.5759999999999996</v>
+      </c>
+      <c r="C27" s="16">
+        <v>7.2999999999999995E-2</v>
+      </c>
       <c r="D27" s="18" t="s">
         <v>24</v>
       </c>
@@ -8030,12 +8129,16 @@
       <c r="J27" s="18"/>
       <c r="K27" s="16"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B28" s="39"/>
-      <c r="C28" s="16"/>
+        <v>92</v>
+      </c>
+      <c r="B28" s="39">
+        <v>1.012</v>
+      </c>
+      <c r="C28" s="16">
+        <v>1.7999999999999999E-2</v>
+      </c>
       <c r="D28" s="18" t="s">
         <v>24</v>
       </c>
@@ -8045,147 +8148,56 @@
       <c r="J28" s="18"/>
       <c r="K28" s="16"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="B29" s="39"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="18"/>
+        <v>110</v>
+      </c>
+      <c r="B29" s="39">
+        <v>4.0510000000000002</v>
+      </c>
+      <c r="C29" s="16">
+        <v>0.45200000000000001</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>24</v>
+      </c>
       <c r="E29" s="16"/>
       <c r="H29" s="39"/>
       <c r="I29" s="16"/>
       <c r="J29" s="18"/>
       <c r="K29" s="16"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A30" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="B30" s="39"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
-    </row>
-    <row r="31" spans="1:11" ht="17" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B31" s="39"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="16"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="18"/>
-      <c r="K31" s="16"/>
-    </row>
-    <row r="32" spans="1:11" ht="17" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B32" s="39"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="16"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="16"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B33" s="39"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="16"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="18"/>
-      <c r="K33" s="16"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B34" s="39"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="16"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="16"/>
-      <c r="J34" s="18"/>
-      <c r="K34" s="16"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A35" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B35" s="39"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="16"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="16"/>
-      <c r="J35" s="18"/>
-      <c r="K35" s="16"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A36" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="B36" s="39"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="18"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="18"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A37" s="20" t="s">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A30" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" s="41"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="36"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A31" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B37" s="41"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="41"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="36"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A38" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="B38" s="42"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="37"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="42"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="37"/>
+      <c r="B31" s="42"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -8210,7 +8222,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
@@ -8218,12 +8230,12 @@
     </row>
     <row r="3" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
@@ -8235,30 +8247,30 @@
     <row r="7" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B11" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="23" t="s">
         <v>128</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B12">
         <v>-3.4000000000000002E-2</v>
@@ -8269,7 +8281,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13">
         <v>-2.4E-2</v>
@@ -8280,7 +8292,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B14">
         <v>-2.3E-2</v>
@@ -8291,7 +8303,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B15">
         <v>-2.5999999999999999E-2</v>
@@ -8302,25 +8314,25 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B19" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" s="23" t="s">
         <v>128</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B20">
         <v>-3.1E-2</v>
@@ -8331,7 +8343,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B21">
         <v>-0.03</v>
@@ -8342,7 +8354,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B22">
         <v>-0.113</v>
@@ -8353,7 +8365,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B23">
         <v>-3.3000000000000002E-2</v>
@@ -8364,7 +8376,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E25" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmoffice-my.sharepoint.com/personal/abrieant_uvm_edu/Documents/OneDrive/Manuscripts/reg report DCN/pubertybrain/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nchaku\Documents\GitHub\pubertybrain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="13_ncr:1_{DF0C5C2D-21F6-4142-814F-EFC173B4BD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A66E4D3C-8232-9C46-9AFD-9E69F4CA7021}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F29979F-BB53-4166-B9B9-F89018F0CDEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="500" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptive table" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="147">
   <si>
     <t>16.10 (2.98)</t>
   </si>
@@ -823,6 +823,12 @@
   </si>
   <si>
     <t>12.311      0.203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ELA    on Quadratic Slope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   WM on Quadratic Slope</t>
   </si>
 </sst>
 </file>
@@ -1089,7 +1095,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1137,15 +1143,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1155,16 +1152,20 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1746,20 +1747,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39987BE7-3659-524A-81AE-D479F97EF698}">
   <dimension ref="A1:F29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="9"/>
       <c r="B2" s="10" t="s">
         <v>63</v>
@@ -1777,7 +1778,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="11" t="s">
         <v>69</v>
@@ -1791,7 +1792,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>60</v>
       </c>
@@ -1801,7 +1802,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>61</v>
       </c>
@@ -1821,7 +1822,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>62</v>
       </c>
@@ -1841,7 +1842,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>58</v>
       </c>
@@ -1861,7 +1862,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>59</v>
       </c>
@@ -1871,7 +1872,7 @@
       <c r="E8" s="12"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>61</v>
       </c>
@@ -1891,7 +1892,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>66</v>
       </c>
@@ -1911,7 +1912,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>67</v>
       </c>
@@ -1931,7 +1932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>62</v>
       </c>
@@ -1951,7 +1952,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>68</v>
       </c>
@@ -1961,7 +1962,7 @@
       <c r="E13" s="12"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>73</v>
       </c>
@@ -1981,7 +1982,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>74</v>
       </c>
@@ -2001,7 +2002,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>75</v>
       </c>
@@ -2021,7 +2022,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>76</v>
       </c>
@@ -2039,7 +2040,7 @@
       </c>
       <c r="F17" s="19"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>71</v>
       </c>
@@ -2049,7 +2050,7 @@
       <c r="E18" s="12"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>61</v>
       </c>
@@ -2069,7 +2070,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>66</v>
       </c>
@@ -2089,7 +2090,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>67</v>
       </c>
@@ -2109,7 +2110,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>62</v>
       </c>
@@ -2129,7 +2130,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>72</v>
       </c>
@@ -2139,7 +2140,7 @@
       <c r="E23" s="12"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>61</v>
       </c>
@@ -2159,7 +2160,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>66</v>
       </c>
@@ -2179,7 +2180,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>67</v>
       </c>
@@ -2199,7 +2200,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>62</v>
       </c>
@@ -2219,7 +2220,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2227,7 +2228,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2243,9 +2244,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A749072B-F938-0F49-BE23-243603B2B3D0}">
   <dimension ref="M2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="13:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M2" t="s">
         <v>112</v>
       </c>
@@ -2259,7 +2260,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45875D41-9C56-AA4E-A18A-2D3A4CE169B3}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2269,7 +2270,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A5153E-6E5C-054A-8ACA-5118463B96C5}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2279,142 +2280,142 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA86F85-A8D4-F648-84C3-730F1A42C846}">
   <dimension ref="A1:AM34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.1640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="1.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.625" style="1" customWidth="1"/>
     <col min="11" max="11" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="1.1640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="1.125" style="1" customWidth="1"/>
     <col min="14" max="14" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.6640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.625" style="1" customWidth="1"/>
     <col min="17" max="17" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="0.83203125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="0.875" style="1" customWidth="1"/>
     <col min="20" max="20" width="8.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="5.6640625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="5.625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="6.125" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="1" style="1" customWidth="1"/>
     <col min="26" max="26" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.6640625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.625" style="1" customWidth="1"/>
     <col min="29" max="30" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="1.1640625" style="1" customWidth="1"/>
+    <col min="31" max="31" width="1.125" style="1" customWidth="1"/>
     <col min="32" max="32" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="5.6640625" style="1" customWidth="1"/>
-    <col min="36" max="36" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="5.625" style="1" customWidth="1"/>
+    <col min="36" max="36" width="6.125" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="40"/>
       <c r="S2" s="9"/>
-      <c r="T2" s="32" t="s">
+      <c r="T2" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="32"/>
-      <c r="X2" s="32"/>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="32"/>
-      <c r="AA2" s="32"/>
-      <c r="AB2" s="32"/>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="U2" s="40"/>
+      <c r="V2" s="40"/>
+      <c r="W2" s="40"/>
+      <c r="X2" s="40"/>
+      <c r="Y2" s="40"/>
+      <c r="Z2" s="40"/>
+      <c r="AA2" s="40"/>
+      <c r="AB2" s="40"/>
+      <c r="AC2" s="40"/>
+      <c r="AD2" s="40"/>
+      <c r="AE2" s="40"/>
+      <c r="AF2" s="40"/>
+      <c r="AG2" s="40"/>
+      <c r="AH2" s="40"/>
+      <c r="AI2" s="40"/>
+      <c r="AJ2" s="40"/>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="16"/>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="28"/>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
       <c r="M3" s="28"/>
-      <c r="N3" s="32" t="s">
+      <c r="N3" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="32"/>
-      <c r="T3" s="33" t="s">
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="T3" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="U3" s="33"/>
-      <c r="V3" s="33"/>
-      <c r="W3" s="33"/>
-      <c r="X3" s="33"/>
+      <c r="U3" s="41"/>
+      <c r="V3" s="41"/>
+      <c r="W3" s="41"/>
+      <c r="X3" s="41"/>
       <c r="Y3" s="28"/>
-      <c r="Z3" s="32" t="s">
+      <c r="Z3" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="AA3" s="32"/>
-      <c r="AB3" s="32"/>
-      <c r="AC3" s="32"/>
-      <c r="AD3" s="32"/>
+      <c r="AA3" s="40"/>
+      <c r="AB3" s="40"/>
+      <c r="AC3" s="40"/>
+      <c r="AD3" s="40"/>
       <c r="AE3" s="28"/>
-      <c r="AF3" s="32" t="s">
+      <c r="AF3" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="AG3" s="32"/>
-      <c r="AH3" s="32"/>
-      <c r="AI3" s="32"/>
-      <c r="AJ3" s="32"/>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AG3" s="40"/>
+      <c r="AH3" s="40"/>
+      <c r="AI3" s="40"/>
+      <c r="AJ3" s="40"/>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="15"/>
       <c r="B4" s="29" t="s">
         <v>90</v>
@@ -2512,7 +2513,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>85</v>
       </c>
@@ -2551,7 +2552,7 @@
       <c r="AI5" s="16"/>
       <c r="AJ5" s="16"/>
     </row>
-    <row r="6" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>95</v>
       </c>
@@ -2650,7 +2651,7 @@
         <v>12.236000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>96</v>
       </c>
@@ -2749,7 +2750,7 @@
         <v>-7.7560000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -2786,7 +2787,7 @@
       <c r="AI8" s="18"/>
       <c r="AJ8" s="16"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>86</v>
       </c>
@@ -2825,7 +2826,7 @@
       <c r="AI9" s="16"/>
       <c r="AJ9" s="16"/>
     </row>
-    <row r="10" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>97</v>
       </c>
@@ -2924,7 +2925,7 @@
         <v>-0.24</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>98</v>
       </c>
@@ -3023,7 +3024,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>99</v>
       </c>
@@ -3122,7 +3123,7 @@
         <v>0.14899999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>100</v>
       </c>
@@ -3221,7 +3222,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>88</v>
       </c>
@@ -3320,7 +3321,7 @@
         <v>0.28799999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="16"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -3357,7 +3358,7 @@
       <c r="AI15" s="18"/>
       <c r="AJ15" s="16"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>87</v>
       </c>
@@ -3396,7 +3397,7 @@
       <c r="AI16" s="16"/>
       <c r="AJ16" s="16"/>
     </row>
-    <row r="17" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>101</v>
       </c>
@@ -3495,7 +3496,7 @@
         <v>0.443</v>
       </c>
     </row>
-    <row r="18" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>102</v>
       </c>
@@ -3594,7 +3595,7 @@
         <v>-0.10299999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>103</v>
       </c>
@@ -3693,7 +3694,7 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>106</v>
       </c>
@@ -3792,7 +3793,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>107</v>
       </c>
@@ -3891,7 +3892,7 @@
         <v>-0.13600000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>104</v>
       </c>
@@ -3988,7 +3989,7 @@
         <v>0.156</v>
       </c>
     </row>
-    <row r="23" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>105</v>
       </c>
@@ -4085,7 +4086,7 @@
         <v>-1.6E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>109</v>
       </c>
@@ -4182,7 +4183,7 @@
         <v>0.112</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>108</v>
       </c>
@@ -4279,7 +4280,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>110</v>
       </c>
@@ -4376,7 +4377,7 @@
         <v>-4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -4413,7 +4414,7 @@
       <c r="AI27" s="18"/>
       <c r="AJ27" s="16"/>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>82</v>
       </c>
@@ -4452,7 +4453,7 @@
       <c r="AI28" s="16"/>
       <c r="AJ28" s="16"/>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>84</v>
       </c>
@@ -4551,7 +4552,7 @@
         <v>14.164999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
         <v>89</v>
       </c>
@@ -4650,7 +4651,7 @@
         <v>4.1660000000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>93</v>
       </c>
@@ -4749,7 +4750,7 @@
         <v>1.0549999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
         <v>111</v>
       </c>
@@ -4846,7 +4847,7 @@
         <v>4.202</v>
       </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
         <v>116</v>
       </c>
@@ -4889,63 +4890,69 @@
       <c r="AL33" s="16"/>
       <c r="AM33" s="16"/>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="B34" s="31">
+      <c r="B34" s="42">
         <v>74058.118000000002</v>
       </c>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="31"/>
-      <c r="F34" s="31"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
       <c r="G34" s="27"/>
-      <c r="H34" s="31">
+      <c r="H34" s="42">
         <v>83016.937999999995</v>
       </c>
-      <c r="I34" s="31"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="31"/>
-      <c r="L34" s="31"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="42"/>
+      <c r="L34" s="42"/>
       <c r="M34" s="27"/>
-      <c r="N34" s="31">
+      <c r="N34" s="42">
         <v>94345.274999999994</v>
       </c>
-      <c r="O34" s="31"/>
-      <c r="P34" s="31"/>
-      <c r="Q34" s="31"/>
-      <c r="R34" s="31"/>
+      <c r="O34" s="42"/>
+      <c r="P34" s="42"/>
+      <c r="Q34" s="42"/>
+      <c r="R34" s="42"/>
       <c r="S34" s="15"/>
-      <c r="T34" s="31">
+      <c r="T34" s="42">
         <v>83167.763000000006</v>
       </c>
-      <c r="U34" s="31"/>
-      <c r="V34" s="31"/>
-      <c r="W34" s="31"/>
-      <c r="X34" s="31"/>
+      <c r="U34" s="42"/>
+      <c r="V34" s="42"/>
+      <c r="W34" s="42"/>
+      <c r="X34" s="42"/>
       <c r="Y34" s="27"/>
-      <c r="Z34" s="31">
+      <c r="Z34" s="42">
         <v>93083.505999999994</v>
       </c>
-      <c r="AA34" s="31"/>
-      <c r="AB34" s="31"/>
-      <c r="AC34" s="31"/>
-      <c r="AD34" s="31"/>
+      <c r="AA34" s="42"/>
+      <c r="AB34" s="42"/>
+      <c r="AC34" s="42"/>
+      <c r="AD34" s="42"/>
       <c r="AE34" s="27"/>
-      <c r="AF34" s="31">
+      <c r="AF34" s="42">
         <v>105770.462</v>
       </c>
-      <c r="AG34" s="31"/>
-      <c r="AH34" s="31"/>
-      <c r="AI34" s="31"/>
-      <c r="AJ34" s="31"/>
+      <c r="AG34" s="42"/>
+      <c r="AH34" s="42"/>
+      <c r="AI34" s="42"/>
+      <c r="AJ34" s="42"/>
       <c r="AK34" s="16"/>
       <c r="AL34" s="16"/>
       <c r="AM34" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="AF34:AJ34"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="H34:L34"/>
+    <mergeCell ref="T34:X34"/>
+    <mergeCell ref="N34:R34"/>
+    <mergeCell ref="Z34:AD34"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="H3:L3"/>
@@ -4954,12 +4961,6 @@
     <mergeCell ref="T3:X3"/>
     <mergeCell ref="Z3:AD3"/>
     <mergeCell ref="AF3:AJ3"/>
-    <mergeCell ref="AF34:AJ34"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="H34:L34"/>
-    <mergeCell ref="T34:X34"/>
-    <mergeCell ref="N34:R34"/>
-    <mergeCell ref="Z34:AD34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -4968,142 +4969,141 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CD5CF7F-81D6-D24D-8228-B4C578C35D65}">
-  <dimension ref="A1:AM39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AM41"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.625" style="1" customWidth="1"/>
     <col min="5" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.1640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="1.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.6640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="6.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="1.1640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.625" style="1" customWidth="1"/>
+    <col min="11" max="12" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="1.125" style="1" customWidth="1"/>
     <col min="14" max="14" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.6640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.625" style="1" customWidth="1"/>
     <col min="17" max="17" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="0.83203125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="0.875" style="1" customWidth="1"/>
     <col min="20" max="20" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.6640625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="5.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.625" style="1" customWidth="1"/>
     <col min="24" max="24" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="1" style="1" customWidth="1"/>
     <col min="26" max="26" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.625" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="30" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="1.1640625" style="1" customWidth="1"/>
+    <col min="31" max="31" width="1.125" style="1" customWidth="1"/>
     <col min="32" max="32" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="5.6640625" style="1" customWidth="1"/>
+    <col min="33" max="33" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.625" style="1" customWidth="1"/>
     <col min="35" max="36" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="32"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="40"/>
       <c r="S2" s="9"/>
-      <c r="T2" s="32" t="s">
+      <c r="T2" s="40" t="s">
         <v>114</v>
       </c>
-      <c r="U2" s="32"/>
-      <c r="V2" s="32"/>
-      <c r="W2" s="32"/>
-      <c r="X2" s="32"/>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="32"/>
-      <c r="AA2" s="32"/>
-      <c r="AB2" s="32"/>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="U2" s="40"/>
+      <c r="V2" s="40"/>
+      <c r="W2" s="40"/>
+      <c r="X2" s="40"/>
+      <c r="Y2" s="40"/>
+      <c r="Z2" s="40"/>
+      <c r="AA2" s="40"/>
+      <c r="AB2" s="40"/>
+      <c r="AC2" s="40"/>
+      <c r="AD2" s="40"/>
+      <c r="AE2" s="40"/>
+      <c r="AF2" s="40"/>
+      <c r="AG2" s="40"/>
+      <c r="AH2" s="40"/>
+      <c r="AI2" s="40"/>
+      <c r="AJ2" s="40"/>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="16"/>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
       <c r="G3" s="28"/>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
       <c r="M3" s="28"/>
-      <c r="N3" s="32" t="s">
+      <c r="N3" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="32"/>
-      <c r="T3" s="33" t="s">
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="T3" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="U3" s="33"/>
-      <c r="V3" s="33"/>
-      <c r="W3" s="33"/>
-      <c r="X3" s="33"/>
+      <c r="U3" s="41"/>
+      <c r="V3" s="41"/>
+      <c r="W3" s="41"/>
+      <c r="X3" s="41"/>
       <c r="Y3" s="28"/>
-      <c r="Z3" s="32" t="s">
+      <c r="Z3" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="AA3" s="32"/>
-      <c r="AB3" s="32"/>
-      <c r="AC3" s="32"/>
-      <c r="AD3" s="32"/>
+      <c r="AA3" s="40"/>
+      <c r="AB3" s="40"/>
+      <c r="AC3" s="40"/>
+      <c r="AD3" s="40"/>
       <c r="AE3" s="28"/>
-      <c r="AF3" s="32" t="s">
+      <c r="AF3" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="AG3" s="32"/>
-      <c r="AH3" s="32"/>
-      <c r="AI3" s="32"/>
-      <c r="AJ3" s="32"/>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AG3" s="40"/>
+      <c r="AH3" s="40"/>
+      <c r="AI3" s="40"/>
+      <c r="AJ3" s="40"/>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="15"/>
       <c r="B4" s="29" t="s">
         <v>90</v>
@@ -5201,7 +5201,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>85</v>
       </c>
@@ -5240,7 +5240,7 @@
       <c r="AI5" s="16"/>
       <c r="AJ5" s="16"/>
     </row>
-    <row r="6" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>95</v>
       </c>
@@ -5260,17 +5260,37 @@
         <v>14.35</v>
       </c>
       <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
+      <c r="H6" s="16">
+        <v>14.055</v>
+      </c>
+      <c r="I6" s="16">
+        <v>0.246</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="16">
+        <v>13.65</v>
+      </c>
+      <c r="L6" s="16">
+        <v>14.46</v>
+      </c>
       <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
+      <c r="N6" s="16">
+        <v>14.055</v>
+      </c>
+      <c r="O6" s="16">
+        <v>0.246</v>
+      </c>
+      <c r="P6" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>13.65</v>
+      </c>
+      <c r="R6" s="16">
+        <v>14.46</v>
+      </c>
       <c r="T6" s="16">
         <v>13.391</v>
       </c>
@@ -5319,37 +5339,57 @@
         <v>13.875999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="16">
-        <v>-7.5229999999999997</v>
-      </c>
-      <c r="C7" s="16">
-        <v>0.48599999999999999</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="16">
-        <v>-8.3209999999999997</v>
-      </c>
-      <c r="F7" s="16">
-        <v>-6.7240000000000002</v>
+      <c r="B7" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>94</v>
       </c>
       <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
+      <c r="H7" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K7" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="L7" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="M7" s="16"/>
-      <c r="N7" s="16"/>
-      <c r="O7" s="16"/>
-      <c r="P7" s="18"/>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="16"/>
+      <c r="N7" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="O7" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="P7" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q7" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="R7" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="T7" s="16">
         <v>1.222</v>
       </c>
@@ -5398,7 +5438,7 @@
         <v>2.1219999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>139</v>
       </c>
@@ -5418,36 +5458,86 @@
         <v>1.7789999999999999</v>
       </c>
       <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
+      <c r="H8" s="16">
+        <v>-8.5679999999999996</v>
+      </c>
+      <c r="I8" s="16">
+        <v>0.66800000000000004</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="16">
+        <v>-9.6669999999999998</v>
+      </c>
+      <c r="L8" s="16">
+        <v>-7.4690000000000003</v>
+      </c>
       <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="18"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="16"/>
-      <c r="T8" s="16"/>
-      <c r="U8" s="16"/>
-      <c r="V8" s="18"/>
-      <c r="W8" s="16"/>
-      <c r="X8" s="16"/>
+      <c r="N8" s="16">
+        <v>-8.5730000000000004</v>
+      </c>
+      <c r="O8" s="16">
+        <v>0.66800000000000004</v>
+      </c>
+      <c r="P8" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q8" s="16">
+        <v>-9.6720000000000006</v>
+      </c>
+      <c r="R8" s="16">
+        <v>-7.4729999999999999</v>
+      </c>
+      <c r="T8" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U8" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V8" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W8" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X8" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="Y8" s="16"/>
-      <c r="Z8" s="16"/>
-      <c r="AA8" s="16"/>
-      <c r="AB8" s="16"/>
-      <c r="AC8" s="16"/>
-      <c r="AD8" s="16"/>
+      <c r="Z8" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA8" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB8" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC8" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD8" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="AE8" s="16"/>
-      <c r="AF8" s="16"/>
-      <c r="AG8" s="16"/>
-      <c r="AH8" s="16"/>
-      <c r="AI8" s="16"/>
-      <c r="AJ8" s="16"/>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AF8" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AG8" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH8" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI8" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ8" s="21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="16"/>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
@@ -5484,7 +5574,7 @@
       <c r="AI9" s="18"/>
       <c r="AJ9" s="16"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>86</v>
       </c>
@@ -5523,7 +5613,7 @@
       <c r="AI10" s="16"/>
       <c r="AJ10" s="16"/>
     </row>
-    <row r="11" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>97</v>
       </c>
@@ -5622,7 +5712,7 @@
         <v>0.40300000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>138</v>
       </c>
@@ -5642,36 +5732,86 @@
         <v>0.21299999999999999</v>
       </c>
       <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
+      <c r="H12" s="16">
+        <v>0.111</v>
+      </c>
+      <c r="I12" s="16">
+        <v>0.06</v>
+      </c>
+      <c r="J12" s="16">
+        <v>6.3E-2</v>
+      </c>
+      <c r="K12" s="16">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="L12" s="16">
+        <v>0.20899999999999999</v>
+      </c>
       <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="18"/>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="16"/>
-      <c r="T12" s="16"/>
-      <c r="U12" s="16"/>
-      <c r="V12" s="18"/>
-      <c r="W12" s="16"/>
-      <c r="X12" s="16"/>
+      <c r="N12" s="16">
+        <v>0.111</v>
+      </c>
+      <c r="O12" s="16">
+        <v>0.06</v>
+      </c>
+      <c r="P12" s="16">
+        <v>6.3E-2</v>
+      </c>
+      <c r="Q12" s="16">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="R12" s="16">
+        <v>0.20899999999999999</v>
+      </c>
+      <c r="T12" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U12" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V12" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W12" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X12" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="Y12" s="16"/>
-      <c r="Z12" s="16"/>
-      <c r="AA12" s="16"/>
-      <c r="AB12" s="18"/>
-      <c r="AC12" s="16"/>
-      <c r="AD12" s="16"/>
+      <c r="Z12" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA12" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB12" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC12" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD12" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="AE12" s="16"/>
-      <c r="AF12" s="16"/>
-      <c r="AG12" s="16"/>
-      <c r="AH12" s="18"/>
-      <c r="AI12" s="16"/>
-      <c r="AJ12" s="16"/>
-    </row>
-    <row r="13" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+      <c r="AF12" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AG12" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH12" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI12" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ12" s="21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>98</v>
       </c>
@@ -5691,17 +5831,37 @@
         <v>5.6000000000000001E-2</v>
       </c>
       <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
+      <c r="H13" s="16">
+        <v>1.9E-2</v>
+      </c>
+      <c r="I13" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="J13" s="16">
+        <v>0.38100000000000001</v>
+      </c>
+      <c r="K13" s="16">
+        <v>-1.6E-2</v>
+      </c>
+      <c r="L13" s="16">
+        <v>5.3999999999999999E-2</v>
+      </c>
       <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="18"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="16"/>
+      <c r="N13" s="16">
+        <v>1.9E-2</v>
+      </c>
+      <c r="O13" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="P13" s="16">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="Q13" s="16">
+        <v>-1.6E-2</v>
+      </c>
+      <c r="R13" s="16">
+        <v>5.3999999999999999E-2</v>
+      </c>
       <c r="T13" s="16">
         <v>-0.01</v>
       </c>
@@ -5750,7 +5910,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>99</v>
       </c>
@@ -5770,17 +5930,37 @@
         <v>0.106</v>
       </c>
       <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
+      <c r="H14" s="16">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="I14" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="J14" s="16">
+        <v>2E-3</v>
+      </c>
+      <c r="K14" s="16">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="L14" s="16">
+        <v>0.105</v>
+      </c>
       <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
-      <c r="P14" s="18"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
+      <c r="N14" s="16">
+        <v>6.9000000000000006E-2</v>
+      </c>
+      <c r="O14" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="P14" s="16">
+        <v>2E-3</v>
+      </c>
+      <c r="Q14" s="16">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="R14" s="16">
+        <v>0.105</v>
+      </c>
       <c r="T14" s="16">
         <v>7.0999999999999994E-2</v>
       </c>
@@ -5829,7 +6009,7 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>140</v>
       </c>
@@ -5880,25 +6060,55 @@
       <c r="R15" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="T15" s="16"/>
-      <c r="U15" s="16"/>
-      <c r="V15" s="18"/>
-      <c r="W15" s="16"/>
-      <c r="X15" s="16"/>
+      <c r="T15" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U15" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V15" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W15" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X15" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="Y15" s="16"/>
-      <c r="Z15" s="16"/>
-      <c r="AA15" s="16"/>
-      <c r="AB15" s="16"/>
-      <c r="AC15" s="16"/>
-      <c r="AD15" s="16"/>
+      <c r="Z15" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA15" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB15" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC15" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD15" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="AE15" s="16"/>
-      <c r="AF15" s="16"/>
-      <c r="AG15" s="16"/>
-      <c r="AH15" s="16"/>
-      <c r="AI15" s="16"/>
-      <c r="AJ15" s="16"/>
-    </row>
-    <row r="16" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+      <c r="AF15" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AG15" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH15" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI15" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ15" s="21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>100</v>
       </c>
@@ -5918,17 +6128,37 @@
         <v>94</v>
       </c>
       <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
+      <c r="H16" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K16" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="L16" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="18"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
+      <c r="N16" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="O16" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="P16" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q16" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="R16" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="T16" s="16">
         <v>0.16800000000000001</v>
       </c>
@@ -5977,7 +6207,7 @@
         <v>0.22900000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>141</v>
       </c>
@@ -5997,36 +6227,86 @@
         <v>-0.22500000000000001</v>
       </c>
       <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
+      <c r="H17" s="16">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="I17" s="16">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="J17" s="16">
+        <v>4.7E-2</v>
+      </c>
+      <c r="K17" s="16">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="L17" s="16">
+        <v>0.154</v>
+      </c>
       <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="16"/>
-      <c r="P17" s="18"/>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="16"/>
-      <c r="T17" s="16"/>
-      <c r="U17" s="16"/>
-      <c r="V17" s="18"/>
-      <c r="W17" s="16"/>
-      <c r="X17" s="16"/>
+      <c r="N17" s="16">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="O17" s="16">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="P17" s="16">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="Q17" s="16">
+        <v>1.4E-2</v>
+      </c>
+      <c r="R17" s="16">
+        <v>0.153</v>
+      </c>
+      <c r="T17" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U17" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V17" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W17" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X17" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="Y17" s="16"/>
-      <c r="Z17" s="16"/>
-      <c r="AA17" s="16"/>
-      <c r="AB17" s="18"/>
-      <c r="AC17" s="16"/>
-      <c r="AD17" s="16"/>
+      <c r="Z17" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA17" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB17" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC17" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD17" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="AE17" s="16"/>
-      <c r="AF17" s="16"/>
-      <c r="AG17" s="16"/>
-      <c r="AH17" s="18"/>
-      <c r="AI17" s="16"/>
-      <c r="AJ17" s="16"/>
-    </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AF17" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AG17" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH17" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI17" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ17" s="21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>88</v>
       </c>
@@ -6046,17 +6326,37 @@
         <v>0.35099999999999998</v>
       </c>
       <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
+      <c r="H18" s="16">
+        <v>0.28899999999999998</v>
+      </c>
+      <c r="I18" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="J18" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="16">
+        <v>0.254</v>
+      </c>
+      <c r="L18" s="16">
+        <v>0.32300000000000001</v>
+      </c>
       <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="18"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="16"/>
+      <c r="N18" s="16">
+        <v>0.28899999999999998</v>
+      </c>
+      <c r="O18" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="P18" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q18" s="16">
+        <v>0.254</v>
+      </c>
+      <c r="R18" s="16">
+        <v>0.32300000000000001</v>
+      </c>
       <c r="T18" s="16">
         <v>0.248</v>
       </c>
@@ -6105,7 +6405,7 @@
         <v>0.28799999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="16"/>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -6142,7 +6442,7 @@
       <c r="AI19" s="18"/>
       <c r="AJ19" s="16"/>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>87</v>
       </c>
@@ -6181,155 +6481,205 @@
       <c r="AI20" s="16"/>
       <c r="AJ20" s="16"/>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K21" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="L21" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="M21" s="16"/>
+      <c r="N21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="O21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="P21" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q21" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="R21" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="T21" s="16">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="U21" s="16">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="V21" s="18">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="W21" s="16">
+        <v>2.4E-2</v>
+      </c>
+      <c r="X21" s="16">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="Y21" s="16"/>
+      <c r="Z21" s="16">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="AA21" s="16">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="AB21" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="AC21" s="16">
+        <v>2.4E-2</v>
+      </c>
+      <c r="AD21" s="16">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="AE21" s="16"/>
+      <c r="AF21" s="16">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="AG21" s="16">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="AH21" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="AI21" s="16">
+        <v>2.4E-2</v>
+      </c>
+      <c r="AJ21" s="16">
+        <v>0.14499999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B22" s="16">
         <v>-0.29099999999999998</v>
       </c>
-      <c r="C21" s="16">
+      <c r="C22" s="16">
         <v>0.106</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D22" s="16">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E22" s="16">
         <v>-0.46500000000000002</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F22" s="16">
         <v>-0.11700000000000001</v>
       </c>
-      <c r="G21" s="21"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="16"/>
-      <c r="O21" s="16"/>
-      <c r="P21" s="16"/>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="16"/>
-      <c r="T21" s="16"/>
-      <c r="U21" s="16"/>
-      <c r="V21" s="16"/>
-      <c r="W21" s="16"/>
-      <c r="X21" s="21"/>
-      <c r="Y21" s="21"/>
-      <c r="Z21" s="16"/>
-      <c r="AA21" s="16"/>
-      <c r="AB21" s="16"/>
-      <c r="AC21" s="16"/>
-      <c r="AD21" s="16"/>
-      <c r="AE21" s="16"/>
-      <c r="AF21" s="16"/>
-      <c r="AG21" s="16"/>
-      <c r="AH21" s="16"/>
-      <c r="AI21" s="16"/>
-      <c r="AJ21" s="16"/>
-    </row>
-    <row r="22" spans="1:36" ht="17" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E22" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="F22" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="J22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="K22" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="L22" s="21" t="s">
-        <v>94</v>
+      <c r="G22" s="21"/>
+      <c r="H22" s="16">
+        <v>0.505</v>
+      </c>
+      <c r="I22" s="16">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="J22" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K22" s="16">
+        <v>0.43099999999999999</v>
+      </c>
+      <c r="L22" s="16">
+        <v>0.57899999999999996</v>
       </c>
       <c r="M22" s="16"/>
-      <c r="N22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="O22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="P22" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q22" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="R22" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="T22" s="16">
-        <v>8.5000000000000006E-2</v>
-      </c>
-      <c r="U22" s="16">
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="V22" s="18">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="W22" s="16">
-        <v>2.4E-2</v>
-      </c>
-      <c r="X22" s="16">
-        <v>0.14499999999999999</v>
-      </c>
-      <c r="Y22" s="16"/>
-      <c r="Z22" s="16">
-        <v>8.4000000000000005E-2</v>
-      </c>
-      <c r="AA22" s="16">
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="AB22" s="16">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="AC22" s="16">
-        <v>2.4E-2</v>
-      </c>
-      <c r="AD22" s="16">
-        <v>0.14499999999999999</v>
+      <c r="N22" s="16">
+        <v>0.505</v>
+      </c>
+      <c r="O22" s="16">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="P22" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q22" s="16">
+        <v>0.43099999999999999</v>
+      </c>
+      <c r="R22" s="16">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="T22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W22" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X22" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y22" s="21"/>
+      <c r="Z22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC22" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD22" s="21" t="s">
+        <v>94</v>
       </c>
       <c r="AE22" s="16"/>
-      <c r="AF22" s="16">
-        <v>8.4000000000000005E-2</v>
-      </c>
-      <c r="AG22" s="16">
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="AH22" s="16">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="AI22" s="16">
-        <v>2.4E-2</v>
-      </c>
-      <c r="AJ22" s="16">
-        <v>0.14499999999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+      <c r="AF22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AG22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH22" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI22" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ22" s="21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>102</v>
       </c>
@@ -6349,17 +6699,37 @@
         <v>94</v>
       </c>
       <c r="G23" s="21"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
+      <c r="H23" s="16">
+        <v>-0.112</v>
+      </c>
+      <c r="I23" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="J23" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" s="16">
+        <v>-0.14799999999999999</v>
+      </c>
+      <c r="L23" s="16">
+        <v>-7.5999999999999998E-2</v>
+      </c>
       <c r="M23" s="16"/>
-      <c r="N23" s="16"/>
-      <c r="O23" s="16"/>
-      <c r="P23" s="18"/>
-      <c r="Q23" s="16"/>
-      <c r="R23" s="16"/>
+      <c r="N23" s="16">
+        <v>-0.112</v>
+      </c>
+      <c r="O23" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="P23" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q23" s="16">
+        <v>-0.14899999999999999</v>
+      </c>
+      <c r="R23" s="16">
+        <v>-7.5999999999999998E-2</v>
+      </c>
       <c r="T23" s="16" t="s">
         <v>94</v>
       </c>
@@ -6408,7 +6778,7 @@
         <v>-9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>103</v>
       </c>
@@ -6428,17 +6798,37 @@
         <v>94</v>
       </c>
       <c r="G24" s="21"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="16"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
+      <c r="H24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K24" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="L24" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="M24" s="16"/>
-      <c r="N24" s="16"/>
-      <c r="O24" s="16"/>
-      <c r="P24" s="18"/>
-      <c r="Q24" s="16"/>
-      <c r="R24" s="16"/>
+      <c r="N24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="O24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="P24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q24" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="R24" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="T24" s="16" t="s">
         <v>94</v>
       </c>
@@ -6487,116 +6877,137 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="H25" s="16">
+        <v>-8.8999999999999996E-2</v>
+      </c>
+      <c r="I25" s="16">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="J25" s="16">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="K25" s="16">
+        <v>0.43099999999999999</v>
+      </c>
+      <c r="L25" s="16">
+        <v>0.57899999999999996</v>
+      </c>
+      <c r="N25" s="16">
+        <v>-8.7999999999999995E-2</v>
+      </c>
+      <c r="O25" s="16">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="P25" s="16">
+        <v>1.2E-2</v>
+      </c>
+      <c r="Q25" s="16">
+        <v>-0.14599999999999999</v>
+      </c>
+      <c r="R25" s="16">
+        <v>-3.1E-2</v>
+      </c>
+      <c r="T25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W25" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X25" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC25" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD25" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AG25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH25" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI25" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ25" s="21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="B25" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E25" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="F25" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="G25" s="21"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="18"/>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="16"/>
-      <c r="O25" s="16"/>
-      <c r="P25" s="18"/>
-      <c r="Q25" s="16"/>
-      <c r="R25" s="16"/>
-      <c r="T25" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="U25" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="V25" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="W25" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="X25" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y25" s="21"/>
-      <c r="Z25" s="16">
-        <v>-2E-3</v>
-      </c>
-      <c r="AA25" s="16">
+      <c r="B26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G26" s="21"/>
+      <c r="H26" s="16">
+        <v>-0.185</v>
+      </c>
+      <c r="I26" s="16">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="AB25" s="16">
-        <v>0.92900000000000005</v>
-      </c>
-      <c r="AC25" s="16">
-        <v>-3.5999999999999997E-2</v>
-      </c>
-      <c r="AD25" s="16">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="AE25" s="16"/>
-      <c r="AF25" s="16">
-        <v>-3.0000000000000001E-3</v>
-      </c>
-      <c r="AG25" s="16">
+      <c r="J26" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K26" s="16">
+        <v>-0.22</v>
+      </c>
+      <c r="L26" s="16">
+        <v>-0.15</v>
+      </c>
+      <c r="M26" s="16"/>
+      <c r="N26" s="16">
+        <v>-0.185</v>
+      </c>
+      <c r="O26" s="16">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="AH25" s="16">
-        <v>0.90400000000000003</v>
-      </c>
-      <c r="AI25" s="16">
-        <v>-3.6999999999999998E-2</v>
-      </c>
-      <c r="AJ25" s="16">
-        <v>3.2000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A26" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E26" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="F26" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="G26" s="21"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="16"/>
-      <c r="O26" s="16"/>
-      <c r="P26" s="18"/>
-      <c r="Q26" s="16"/>
-      <c r="R26" s="16"/>
+      <c r="P26" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q26" s="16">
+        <v>-0.22</v>
+      </c>
+      <c r="R26" s="16">
+        <v>-0.15</v>
+      </c>
       <c r="T26" s="16" t="s">
         <v>94</v>
       </c>
@@ -6614,127 +7025,139 @@
       </c>
       <c r="Y26" s="21"/>
       <c r="Z26" s="16">
-        <v>-0.17</v>
+        <v>-2E-3</v>
       </c>
       <c r="AA26" s="16">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="AB26" s="18" t="s">
-        <v>24</v>
+      <c r="AB26" s="16">
+        <v>0.92900000000000005</v>
       </c>
       <c r="AC26" s="16">
-        <v>-0.20399999999999999</v>
+        <v>-3.5999999999999997E-2</v>
       </c>
       <c r="AD26" s="16">
-        <v>-0.13500000000000001</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="AE26" s="16"/>
       <c r="AF26" s="16">
-        <v>-0.17</v>
+        <v>-3.0000000000000001E-3</v>
       </c>
       <c r="AG26" s="16">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="AH26" s="18" t="s">
-        <v>24</v>
+      <c r="AH26" s="16">
+        <v>0.90400000000000003</v>
       </c>
       <c r="AI26" s="16">
+        <v>-3.6999999999999998E-2</v>
+      </c>
+      <c r="AJ26" s="16">
+        <v>3.2000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A27" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G27" s="21"/>
+      <c r="H27" s="16">
+        <v>-0.218</v>
+      </c>
+      <c r="I27" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="J27" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" s="16">
+        <v>-0.255</v>
+      </c>
+      <c r="L27" s="16">
+        <v>-0.182</v>
+      </c>
+      <c r="M27" s="16"/>
+      <c r="N27" s="16">
+        <v>-0.219</v>
+      </c>
+      <c r="O27" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="P27" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q27" s="16">
+        <v>-0.25600000000000001</v>
+      </c>
+      <c r="R27" s="16">
+        <v>-0.183</v>
+      </c>
+      <c r="T27" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U27" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V27" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W27" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X27" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y27" s="21"/>
+      <c r="Z27" s="16">
+        <v>-0.17</v>
+      </c>
+      <c r="AA27" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AB27" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC27" s="16">
         <v>-0.20399999999999999</v>
       </c>
-      <c r="AJ26" s="16">
-        <v>-0.13600000000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:36" ht="17" x14ac:dyDescent="0.25">
-      <c r="A27" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="F27" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="G27" s="21"/>
-      <c r="H27" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I27" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="J27" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="K27" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="L27" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="M27" s="16"/>
-      <c r="N27" s="16"/>
-      <c r="O27" s="16"/>
-      <c r="P27" s="18"/>
-      <c r="Q27" s="16"/>
-      <c r="R27" s="16"/>
-      <c r="T27" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="U27" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="V27" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="W27" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="X27" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y27" s="21"/>
-      <c r="Z27" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AA27" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AB27" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC27" s="16"/>
-      <c r="AD27" s="16" t="s">
-        <v>94</v>
+      <c r="AD27" s="16">
+        <v>-0.13500000000000001</v>
       </c>
       <c r="AE27" s="16"/>
       <c r="AF27" s="16">
-        <v>-3.7999999999999999E-2</v>
+        <v>-0.17</v>
       </c>
       <c r="AG27" s="16">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="AH27" s="16">
-        <v>0.39900000000000002</v>
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="AH27" s="18" t="s">
+        <v>24</v>
       </c>
       <c r="AI27" s="16">
-        <v>8.6999999999999994E-2</v>
+        <v>-0.20399999999999999</v>
       </c>
       <c r="AJ27" s="16">
-        <v>0.17199999999999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+        <v>-0.13600000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B28" s="16" t="s">
         <v>94</v>
@@ -6768,11 +7191,21 @@
         <v>94</v>
       </c>
       <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
-      <c r="O28" s="16"/>
-      <c r="P28" s="18"/>
-      <c r="Q28" s="16"/>
-      <c r="R28" s="16"/>
+      <c r="N28" s="16">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="O28" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="P28" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q28" s="16">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="R28" s="16">
+        <v>0.17399999999999999</v>
+      </c>
       <c r="T28" s="16" t="s">
         <v>94</v>
       </c>
@@ -6804,24 +7237,24 @@
       </c>
       <c r="AE28" s="16"/>
       <c r="AF28" s="16">
-        <v>0.129</v>
+        <v>-3.7999999999999999E-2</v>
       </c>
       <c r="AG28" s="16">
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="AH28" s="18" t="s">
-        <v>24</v>
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="AH28" s="16">
+        <v>0.39900000000000002</v>
       </c>
       <c r="AI28" s="16">
-        <v>-0.111</v>
+        <v>8.6999999999999994E-2</v>
       </c>
       <c r="AJ28" s="16">
-        <v>3.5999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
+        <v>0.17199999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B29" s="16" t="s">
         <v>94</v>
@@ -6855,11 +7288,21 @@
         <v>94</v>
       </c>
       <c r="M29" s="16"/>
-      <c r="N29" s="16"/>
-      <c r="O29" s="16"/>
-      <c r="P29" s="18"/>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="16"/>
+      <c r="N29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="O29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="P29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q29" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R29" s="16" t="s">
+        <v>94</v>
+      </c>
       <c r="T29" s="16" t="s">
         <v>94</v>
       </c>
@@ -6891,62 +7334,52 @@
       </c>
       <c r="AE29" s="16"/>
       <c r="AF29" s="16">
-        <v>4.2000000000000003E-2</v>
+        <v>0.129</v>
       </c>
       <c r="AG29" s="16">
-        <v>0.02</v>
-      </c>
-      <c r="AH29" s="16">
-        <v>3.5000000000000003E-2</v>
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="AH29" s="18" t="s">
+        <v>24</v>
       </c>
       <c r="AI29" s="16">
-        <v>8.9999999999999993E-3</v>
+        <v>-0.111</v>
       </c>
       <c r="AJ29" s="16">
-        <v>7.4999999999999997E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
+        <v>3.5999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E30" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="F30" s="21" t="s">
-        <v>94</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
       <c r="G30" s="21"/>
-      <c r="H30" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I30" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="J30" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="K30" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="L30" s="16" t="s">
-        <v>94</v>
-      </c>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="16"/>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
       <c r="M30" s="16"/>
-      <c r="N30" s="16"/>
-      <c r="O30" s="16"/>
-      <c r="P30" s="18"/>
-      <c r="Q30" s="16"/>
-      <c r="R30" s="16"/>
+      <c r="N30" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="O30" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="P30" s="16">
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="Q30" s="16">
+        <v>-3.3000000000000002E-2</v>
+      </c>
+      <c r="R30" s="16">
+        <v>0.13200000000000001</v>
+      </c>
       <c r="T30" s="16" t="s">
         <v>94</v>
       </c>
@@ -6972,30 +7405,32 @@
       <c r="AB30" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="AC30" s="16"/>
-      <c r="AD30" s="16" t="s">
+      <c r="AC30" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD30" s="21" t="s">
         <v>94</v>
       </c>
       <c r="AE30" s="16"/>
-      <c r="AF30" s="16">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="AG30" s="16">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="AH30" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="AI30" s="16">
-        <v>0.104</v>
-      </c>
-      <c r="AJ30" s="16">
-        <v>0.17499999999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AF30" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AG30" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AH30" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AI30" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ30" s="21" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B31" s="16" t="s">
         <v>94</v>
@@ -7029,11 +7464,21 @@
         <v>94</v>
       </c>
       <c r="M31" s="16"/>
-      <c r="N31" s="16"/>
-      <c r="O31" s="16"/>
-      <c r="P31" s="18"/>
-      <c r="Q31" s="16"/>
-      <c r="R31" s="16"/>
+      <c r="N31" s="16">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="O31" s="16">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="P31" s="16">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="Q31" s="16">
+        <v>-2.8000000000000001E-2</v>
+      </c>
+      <c r="R31" s="16">
+        <v>0.08</v>
+      </c>
       <c r="T31" s="16" t="s">
         <v>94</v>
       </c>
@@ -7065,518 +7510,786 @@
       </c>
       <c r="AE31" s="16"/>
       <c r="AF31" s="16">
-        <v>-8.4000000000000005E-2</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="AG31" s="16">
         <v>0.02</v>
       </c>
-      <c r="AH31" s="18" t="s">
-        <v>24</v>
+      <c r="AH31" s="16">
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="AI31" s="16">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="AJ31" s="16">
+        <v>7.4999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="A32" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G32" s="21"/>
+      <c r="H32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="M32" s="16"/>
+      <c r="N32" s="16">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="O32" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="P32" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q32" s="16">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="R32" s="16">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="T32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W32" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X32" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y32" s="21"/>
+      <c r="Z32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC32" s="16"/>
+      <c r="AD32" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE32" s="16"/>
+      <c r="AF32" s="16">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AG32" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="AH32" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI32" s="16">
+        <v>0.104</v>
+      </c>
+      <c r="AJ32" s="16">
+        <v>0.17499999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A33" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F33" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G33" s="21"/>
+      <c r="H33" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I33" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J33" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="M33" s="16"/>
+      <c r="N33" s="16">
+        <v>-0.108</v>
+      </c>
+      <c r="O33" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="P33" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q33" s="16">
+        <v>-0.14399999999999999</v>
+      </c>
+      <c r="R33" s="16">
+        <v>-7.1999999999999995E-2</v>
+      </c>
+      <c r="T33" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U33" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V33" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W33" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X33" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y33" s="21"/>
+      <c r="Z33" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA33" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB33" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC33" s="16"/>
+      <c r="AD33" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE33" s="16"/>
+      <c r="AF33" s="16">
+        <v>-8.4000000000000005E-2</v>
+      </c>
+      <c r="AG33" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="AH33" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI33" s="16">
         <v>-0.11700000000000001</v>
       </c>
-      <c r="AJ31" s="16">
+      <c r="AJ33" s="16">
         <v>-0.05</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A32" s="16"/>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="16"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="16"/>
-      <c r="O32" s="16"/>
-      <c r="P32" s="18"/>
-      <c r="Q32" s="18"/>
-      <c r="R32" s="16"/>
-      <c r="T32" s="16"/>
-      <c r="U32" s="16"/>
-      <c r="V32" s="16"/>
-      <c r="W32" s="16"/>
-      <c r="X32" s="21"/>
-      <c r="Y32" s="21"/>
-      <c r="Z32" s="16"/>
-      <c r="AA32" s="16"/>
-      <c r="AB32" s="16"/>
-      <c r="AC32" s="16"/>
-      <c r="AD32" s="16"/>
-      <c r="AE32" s="16"/>
-      <c r="AF32" s="16"/>
-      <c r="AG32" s="16"/>
-      <c r="AH32" s="18"/>
-      <c r="AI32" s="18"/>
-      <c r="AJ32" s="16"/>
-    </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A33" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="16"/>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="16"/>
-      <c r="O33" s="16"/>
-      <c r="P33" s="16"/>
-      <c r="Q33" s="16"/>
-      <c r="R33" s="16"/>
-      <c r="T33" s="16"/>
-      <c r="U33" s="16"/>
-      <c r="V33" s="16"/>
-      <c r="W33" s="16"/>
-      <c r="X33" s="21"/>
-      <c r="Y33" s="21"/>
-      <c r="Z33" s="16"/>
-      <c r="AA33" s="16"/>
-      <c r="AB33" s="16"/>
-      <c r="AC33" s="16"/>
-      <c r="AD33" s="16"/>
-      <c r="AE33" s="16"/>
-      <c r="AF33" s="16"/>
-      <c r="AG33" s="16"/>
-      <c r="AH33" s="16"/>
-      <c r="AI33" s="16"/>
-      <c r="AJ33" s="16"/>
-    </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A34" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B34" s="16">
-        <v>10.965</v>
-      </c>
-      <c r="C34" s="16">
-        <v>0.158</v>
-      </c>
-      <c r="D34" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="16">
-        <v>10.706</v>
-      </c>
-      <c r="F34" s="16">
-        <v>11.225</v>
-      </c>
-      <c r="G34" s="16"/>
+    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A34" s="16"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="21"/>
       <c r="H34" s="16"/>
       <c r="I34" s="16"/>
-      <c r="J34" s="18"/>
+      <c r="J34" s="16"/>
       <c r="K34" s="16"/>
       <c r="L34" s="16"/>
       <c r="M34" s="16"/>
       <c r="N34" s="16"/>
       <c r="O34" s="16"/>
       <c r="P34" s="18"/>
-      <c r="Q34" s="16"/>
+      <c r="Q34" s="18"/>
       <c r="R34" s="16"/>
-      <c r="T34" s="16">
-        <v>13.827</v>
-      </c>
-      <c r="U34" s="16">
-        <v>0.20100000000000001</v>
-      </c>
-      <c r="V34" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="W34" s="16">
-        <v>13.496</v>
-      </c>
-      <c r="X34" s="16">
-        <v>14.157999999999999</v>
-      </c>
-      <c r="Y34" s="16"/>
-      <c r="Z34" s="16">
-        <v>13.829000000000001</v>
-      </c>
-      <c r="AA34" s="16">
-        <v>0.20200000000000001</v>
-      </c>
-      <c r="AB34" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="AC34" s="16">
-        <v>13.496</v>
-      </c>
-      <c r="AD34" s="16">
-        <v>14.161</v>
-      </c>
+      <c r="T34" s="16"/>
+      <c r="U34" s="16"/>
+      <c r="V34" s="16"/>
+      <c r="W34" s="16"/>
+      <c r="X34" s="21"/>
+      <c r="Y34" s="21"/>
+      <c r="Z34" s="16"/>
+      <c r="AA34" s="16"/>
+      <c r="AB34" s="16"/>
+      <c r="AC34" s="16"/>
+      <c r="AD34" s="16"/>
       <c r="AE34" s="16"/>
-      <c r="AF34" s="16">
-        <v>13.829000000000001</v>
-      </c>
-      <c r="AG34" s="16">
-        <v>0.20200000000000001</v>
-      </c>
-      <c r="AH34" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="AI34" s="16">
-        <v>13.497</v>
-      </c>
-      <c r="AJ34" s="16">
-        <v>14.162000000000001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A35" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B35" s="16">
-        <v>3.7109999999999999</v>
-      </c>
-      <c r="C35" s="16">
-        <v>6.3E-2</v>
-      </c>
-      <c r="D35" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="16">
-        <v>3.6070000000000002</v>
-      </c>
-      <c r="F35" s="16">
-        <v>3.8149999999999999</v>
-      </c>
-      <c r="G35" s="16"/>
+      <c r="AF34" s="16"/>
+      <c r="AG34" s="16"/>
+      <c r="AH34" s="18"/>
+      <c r="AI34" s="18"/>
+      <c r="AJ34" s="16"/>
+    </row>
+    <row r="35" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A35" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
       <c r="H35" s="16"/>
       <c r="I35" s="16"/>
-      <c r="J35" s="18"/>
+      <c r="J35" s="16"/>
       <c r="K35" s="16"/>
       <c r="L35" s="16"/>
       <c r="M35" s="16"/>
       <c r="N35" s="16"/>
       <c r="O35" s="16"/>
-      <c r="P35" s="18"/>
+      <c r="P35" s="16"/>
       <c r="Q35" s="16"/>
       <c r="R35" s="16"/>
-      <c r="T35" s="16">
-        <v>3.8889999999999998</v>
-      </c>
-      <c r="U35" s="16">
-        <v>6.3E-2</v>
-      </c>
-      <c r="V35" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="W35" s="16">
-        <v>3.7839999999999998</v>
-      </c>
-      <c r="X35" s="16">
-        <v>3.9929999999999999</v>
-      </c>
-      <c r="Y35" s="16"/>
-      <c r="Z35" s="16">
-        <v>4.0620000000000003</v>
-      </c>
-      <c r="AA35" s="16">
-        <v>6.4000000000000001E-2</v>
-      </c>
-      <c r="AB35" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="AC35" s="16">
-        <v>3.9569999999999999</v>
-      </c>
-      <c r="AD35" s="16">
-        <v>4.1669999999999998</v>
-      </c>
+      <c r="T35" s="16"/>
+      <c r="U35" s="16"/>
+      <c r="V35" s="16"/>
+      <c r="W35" s="16"/>
+      <c r="X35" s="21"/>
+      <c r="Y35" s="21"/>
+      <c r="Z35" s="16"/>
+      <c r="AA35" s="16"/>
+      <c r="AB35" s="16"/>
+      <c r="AC35" s="16"/>
+      <c r="AD35" s="16"/>
       <c r="AE35" s="16"/>
-      <c r="AF35" s="16">
-        <v>4.0609999999999999</v>
-      </c>
-      <c r="AG35" s="16">
-        <v>6.4000000000000001E-2</v>
-      </c>
-      <c r="AH35" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="AI35" s="16">
-        <v>3.956</v>
-      </c>
-      <c r="AJ35" s="16">
-        <v>4.1660000000000004</v>
-      </c>
-    </row>
-    <row r="36" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="AF35" s="16"/>
+      <c r="AG35" s="16"/>
+      <c r="AH35" s="16"/>
+      <c r="AI35" s="16"/>
+      <c r="AJ35" s="16"/>
+    </row>
+    <row r="36" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C36" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D36" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E36" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="F36" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="G36" s="21"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="18"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
+        <v>84</v>
+      </c>
+      <c r="B36" s="16">
+        <v>10.965</v>
+      </c>
+      <c r="C36" s="16">
+        <v>0.158</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="16">
+        <v>10.706</v>
+      </c>
+      <c r="F36" s="16">
+        <v>11.225</v>
+      </c>
+      <c r="G36" s="16"/>
+      <c r="H36" s="16">
+        <v>11.154999999999999</v>
+      </c>
+      <c r="I36" s="16">
+        <v>0.158</v>
+      </c>
+      <c r="J36" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K36" s="16">
+        <v>10.895</v>
+      </c>
+      <c r="L36" s="16">
+        <v>11.414</v>
+      </c>
       <c r="M36" s="16"/>
-      <c r="N36" s="16"/>
-      <c r="O36" s="16"/>
-      <c r="P36" s="18"/>
-      <c r="Q36" s="16"/>
-      <c r="R36" s="16"/>
-      <c r="T36" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="U36" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="V36" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="W36" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="X36" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y36" s="21"/>
+      <c r="N36" s="16">
+        <v>11.154999999999999</v>
+      </c>
+      <c r="O36" s="16">
+        <v>0.158</v>
+      </c>
+      <c r="P36" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q36" s="16">
+        <v>10.895</v>
+      </c>
+      <c r="R36" s="16">
+        <v>11.414</v>
+      </c>
+      <c r="T36" s="16">
+        <v>13.827</v>
+      </c>
+      <c r="U36" s="16">
+        <v>0.20100000000000001</v>
+      </c>
+      <c r="V36" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="W36" s="16">
+        <v>13.496</v>
+      </c>
+      <c r="X36" s="16">
+        <v>14.157999999999999</v>
+      </c>
+      <c r="Y36" s="16"/>
       <c r="Z36" s="16">
-        <v>1.026</v>
+        <v>13.829000000000001</v>
       </c>
       <c r="AA36" s="16">
-        <v>1.7000000000000001E-2</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="AB36" s="18" t="s">
         <v>24</v>
       </c>
       <c r="AC36" s="16">
-        <v>0.998</v>
+        <v>13.496</v>
       </c>
       <c r="AD36" s="16">
-        <v>1.054</v>
+        <v>14.161</v>
       </c>
       <c r="AE36" s="16"/>
       <c r="AF36" s="16">
-        <v>1.0269999999999999</v>
+        <v>13.829000000000001</v>
       </c>
       <c r="AG36" s="16">
-        <v>1.7000000000000001E-2</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="AH36" s="18" t="s">
         <v>24</v>
       </c>
       <c r="AI36" s="16">
-        <v>0.999</v>
+        <v>13.497</v>
       </c>
       <c r="AJ36" s="16">
-        <v>1.0549999999999999</v>
-      </c>
-    </row>
-    <row r="37" spans="1:39" x14ac:dyDescent="0.2">
+        <v>14.162000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="B37" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E37" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="F37" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="G37" s="21"/>
-      <c r="H37" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I37" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="J37" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16" t="s">
-        <v>94</v>
+        <v>89</v>
+      </c>
+      <c r="B37" s="16">
+        <v>3.7109999999999999</v>
+      </c>
+      <c r="C37" s="16">
+        <v>6.3E-2</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="16">
+        <v>3.6070000000000002</v>
+      </c>
+      <c r="F37" s="16">
+        <v>3.8149999999999999</v>
+      </c>
+      <c r="G37" s="16"/>
+      <c r="H37" s="16">
+        <v>3.927</v>
+      </c>
+      <c r="I37" s="16">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="J37" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K37" s="16">
+        <v>3.82</v>
+      </c>
+      <c r="L37" s="16">
+        <v>4.0339999999999998</v>
       </c>
       <c r="M37" s="16"/>
-      <c r="N37" s="16"/>
-      <c r="O37" s="16"/>
-      <c r="P37" s="18"/>
-      <c r="Q37" s="16"/>
-      <c r="R37" s="16"/>
-      <c r="T37" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="U37" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="V37" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="W37" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="X37" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y37" s="21"/>
-      <c r="Z37" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AA37" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AB37" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC37" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="AD37" s="21" t="s">
-        <v>94</v>
+      <c r="N37" s="16">
+        <v>3.927</v>
+      </c>
+      <c r="O37" s="16">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P37" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q37" s="16">
+        <v>3.82</v>
+      </c>
+      <c r="R37" s="16">
+        <v>4.0339999999999998</v>
+      </c>
+      <c r="T37" s="16">
+        <v>3.8889999999999998</v>
+      </c>
+      <c r="U37" s="16">
+        <v>6.3E-2</v>
+      </c>
+      <c r="V37" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="W37" s="16">
+        <v>3.7839999999999998</v>
+      </c>
+      <c r="X37" s="16">
+        <v>3.9929999999999999</v>
+      </c>
+      <c r="Y37" s="16"/>
+      <c r="Z37" s="16">
+        <v>4.0620000000000003</v>
+      </c>
+      <c r="AA37" s="16">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="AB37" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC37" s="16">
+        <v>3.9569999999999999</v>
+      </c>
+      <c r="AD37" s="16">
+        <v>4.1669999999999998</v>
       </c>
       <c r="AE37" s="16"/>
       <c r="AF37" s="16">
+        <v>4.0609999999999999</v>
+      </c>
+      <c r="AG37" s="16">
+        <v>6.4000000000000001E-2</v>
+      </c>
+      <c r="AH37" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI37" s="16">
+        <v>3.956</v>
+      </c>
+      <c r="AJ37" s="16">
+        <v>4.1660000000000004</v>
+      </c>
+    </row>
+    <row r="38" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A38" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F38" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G38" s="21"/>
+      <c r="H38" s="16">
+        <v>1.014</v>
+      </c>
+      <c r="I38" s="16">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="J38" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K38" s="16">
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="L38" s="16">
+        <v>1.0429999999999999</v>
+      </c>
+      <c r="M38" s="16"/>
+      <c r="N38" s="16">
+        <v>1.014</v>
+      </c>
+      <c r="O38" s="16">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="P38" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q38" s="16">
+        <v>0.98499999999999999</v>
+      </c>
+      <c r="R38" s="16">
+        <v>1.0429999999999999</v>
+      </c>
+      <c r="T38" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U38" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V38" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W38" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="X38" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y38" s="21"/>
+      <c r="Z38" s="16">
+        <v>1.026</v>
+      </c>
+      <c r="AA38" s="16">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="AB38" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC38" s="16">
+        <v>0.998</v>
+      </c>
+      <c r="AD38" s="16">
+        <v>1.054</v>
+      </c>
+      <c r="AE38" s="16"/>
+      <c r="AF38" s="16">
+        <v>1.0269999999999999</v>
+      </c>
+      <c r="AG38" s="16">
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="AH38" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI38" s="16">
+        <v>0.999</v>
+      </c>
+      <c r="AJ38" s="16">
+        <v>1.0549999999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A39" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F39" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="G39" s="21"/>
+      <c r="H39" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I39" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="J39" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="K39" s="16"/>
+      <c r="L39" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="M39" s="16"/>
+      <c r="N39" s="16">
+        <v>4.2709999999999999</v>
+      </c>
+      <c r="O39" s="16">
+        <v>0.64900000000000002</v>
+      </c>
+      <c r="P39" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q39" s="16">
+        <v>3.2040000000000002</v>
+      </c>
+      <c r="R39" s="16">
+        <v>5.3380000000000001</v>
+      </c>
+      <c r="T39" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="U39" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="V39" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="W39" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="X39" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y39" s="21"/>
+      <c r="Z39" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA39" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AB39" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC39" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AD39" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE39" s="16"/>
+      <c r="AF39" s="16">
         <v>3.7440000000000002</v>
       </c>
-      <c r="AG37" s="16">
+      <c r="AG39" s="16">
         <v>0.46500000000000002</v>
       </c>
-      <c r="AH37" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="AI37" s="16">
+      <c r="AH39" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI39" s="16">
         <v>2.9790000000000001</v>
       </c>
-      <c r="AJ37" s="16">
+      <c r="AJ39" s="16">
         <v>4.5090000000000003</v>
       </c>
     </row>
-    <row r="38" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A38" s="20" t="s">
+    <row r="40" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A40" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
-      <c r="K38" s="14"/>
-      <c r="L38" s="14"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="14"/>
-      <c r="O38" s="14"/>
-      <c r="P38" s="14"/>
-      <c r="Q38" s="14"/>
-      <c r="R38" s="14"/>
-      <c r="S38" s="16"/>
-      <c r="T38" s="14"/>
-      <c r="U38" s="14"/>
-      <c r="V38" s="14"/>
-      <c r="W38" s="14"/>
-      <c r="X38" s="14"/>
-      <c r="Y38" s="16"/>
-      <c r="Z38" s="14"/>
-      <c r="AA38" s="14"/>
-      <c r="AB38" s="14"/>
-      <c r="AC38" s="14"/>
-      <c r="AD38" s="14"/>
-      <c r="AE38" s="16"/>
-      <c r="AF38" s="14"/>
-      <c r="AG38" s="14"/>
-      <c r="AH38" s="14"/>
-      <c r="AI38" s="14"/>
-      <c r="AJ38" s="14"/>
-      <c r="AK38" s="16"/>
-      <c r="AL38" s="16"/>
-      <c r="AM38" s="16"/>
-    </row>
-    <row r="39" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A39" s="15" t="s">
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="16"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="14"/>
+      <c r="K40" s="14"/>
+      <c r="L40" s="14"/>
+      <c r="M40" s="16"/>
+      <c r="N40" s="14"/>
+      <c r="O40" s="14"/>
+      <c r="P40" s="14"/>
+      <c r="Q40" s="14"/>
+      <c r="R40" s="14"/>
+      <c r="S40" s="16"/>
+      <c r="T40" s="14"/>
+      <c r="U40" s="14"/>
+      <c r="V40" s="14"/>
+      <c r="W40" s="14"/>
+      <c r="X40" s="14"/>
+      <c r="Y40" s="16"/>
+      <c r="Z40" s="14"/>
+      <c r="AA40" s="14"/>
+      <c r="AB40" s="14"/>
+      <c r="AC40" s="14"/>
+      <c r="AD40" s="14"/>
+      <c r="AE40" s="16"/>
+      <c r="AF40" s="14"/>
+      <c r="AG40" s="14"/>
+      <c r="AH40" s="14"/>
+      <c r="AI40" s="14"/>
+      <c r="AJ40" s="14"/>
+      <c r="AK40" s="16"/>
+      <c r="AL40" s="16"/>
+      <c r="AM40" s="16"/>
+    </row>
+    <row r="41" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A41" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="B39" s="31">
+      <c r="B41" s="42">
         <v>34697.703999999998</v>
       </c>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="31"/>
-      <c r="I39" s="31"/>
-      <c r="J39" s="31"/>
-      <c r="K39" s="31"/>
-      <c r="L39" s="31"/>
-      <c r="M39" s="27"/>
-      <c r="N39" s="31"/>
-      <c r="O39" s="31"/>
-      <c r="P39" s="31"/>
-      <c r="Q39" s="31"/>
-      <c r="R39" s="31"/>
-      <c r="S39" s="15"/>
-      <c r="T39" s="31">
+      <c r="C41" s="42"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="42"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="42">
+        <v>43730.449000000001</v>
+      </c>
+      <c r="I41" s="42"/>
+      <c r="J41" s="42"/>
+      <c r="K41" s="42"/>
+      <c r="L41" s="42"/>
+      <c r="M41" s="27"/>
+      <c r="N41" s="42">
+        <v>55075.362999999998</v>
+      </c>
+      <c r="O41" s="42"/>
+      <c r="P41" s="42"/>
+      <c r="Q41" s="42"/>
+      <c r="R41" s="42"/>
+      <c r="S41" s="15"/>
+      <c r="T41" s="42">
         <v>37782.404000000002</v>
       </c>
-      <c r="U39" s="31"/>
-      <c r="V39" s="31"/>
-      <c r="W39" s="31"/>
-      <c r="X39" s="31"/>
-      <c r="Y39" s="27"/>
-      <c r="Z39" s="31">
+      <c r="U41" s="42"/>
+      <c r="V41" s="42"/>
+      <c r="W41" s="42"/>
+      <c r="X41" s="42"/>
+      <c r="Y41" s="27"/>
+      <c r="Z41" s="42">
         <v>47698.324999999997</v>
       </c>
-      <c r="AA39" s="31"/>
-      <c r="AB39" s="31"/>
-      <c r="AC39" s="31"/>
-      <c r="AD39" s="31"/>
-      <c r="AE39" s="27"/>
-      <c r="AF39" s="31">
+      <c r="AA41" s="42"/>
+      <c r="AB41" s="42"/>
+      <c r="AC41" s="42"/>
+      <c r="AD41" s="42"/>
+      <c r="AE41" s="27"/>
+      <c r="AF41" s="42">
         <v>60402.93</v>
       </c>
-      <c r="AG39" s="31"/>
-      <c r="AH39" s="31"/>
-      <c r="AI39" s="31"/>
-      <c r="AJ39" s="31"/>
-      <c r="AK39" s="16"/>
-      <c r="AL39" s="16"/>
-      <c r="AM39" s="16"/>
+      <c r="AG41" s="42"/>
+      <c r="AH41" s="42"/>
+      <c r="AI41" s="42"/>
+      <c r="AJ41" s="42"/>
+      <c r="AK41" s="16"/>
+      <c r="AL41" s="16"/>
+      <c r="AM41" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="AF39:AJ39"/>
+    <mergeCell ref="AF41:AJ41"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="T2:AJ2"/>
     <mergeCell ref="B3:F3"/>
@@ -7585,11 +8298,11 @@
     <mergeCell ref="T3:X3"/>
     <mergeCell ref="Z3:AD3"/>
     <mergeCell ref="AF3:AJ3"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="H39:L39"/>
-    <mergeCell ref="N39:R39"/>
-    <mergeCell ref="T39:X39"/>
-    <mergeCell ref="Z39:AD39"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="H41:L41"/>
+    <mergeCell ref="N41:R41"/>
+    <mergeCell ref="T41:X41"/>
+    <mergeCell ref="Z41:AD41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -7599,106 +8312,106 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57A86273-0E84-8246-B3ED-A023C6721217}">
   <dimension ref="A1:L38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.1640625" style="38" customWidth="1"/>
-    <col min="3" max="3" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5" style="35" customWidth="1"/>
+    <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.125" style="35" customWidth="1"/>
+    <col min="3" max="3" width="4.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5" style="32" customWidth="1"/>
     <col min="7" max="7" width="11" style="1"/>
-    <col min="8" max="8" width="6.1640625" style="38" customWidth="1"/>
-    <col min="9" max="9" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.5" style="35" customWidth="1"/>
+    <col min="8" max="8" width="6.125" style="35" customWidth="1"/>
+    <col min="9" max="9" width="4.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.5" style="32" customWidth="1"/>
     <col min="13" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
       <c r="B2" s="43"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
       <c r="F2" s="44"/>
       <c r="H2" s="43"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
       <c r="L2" s="44"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="15"/>
       <c r="B3" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
       <c r="F3" s="44"/>
       <c r="H3" s="43" t="s">
         <v>142</v>
       </c>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
       <c r="L3" s="44"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="16"/>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E4" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="H4" s="34" t="s">
+      <c r="H4" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="34" t="s">
+      <c r="I4" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="34" t="s">
+      <c r="J4" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="K4" s="34" t="s">
+      <c r="K4" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="L4" s="34" t="s">
+      <c r="L4" s="31" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>85</v>
       </c>
       <c r="E5" s="16"/>
-      <c r="H5" s="39"/>
+      <c r="H5" s="36"/>
       <c r="I5" s="16"/>
       <c r="J5" s="16"/>
       <c r="K5" s="16"/>
     </row>
-    <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="36" t="s">
         <v>144</v>
       </c>
       <c r="C6" s="16">
@@ -7708,16 +8421,16 @@
         <v>24</v>
       </c>
       <c r="E6" s="16"/>
-      <c r="H6" s="39"/>
+      <c r="H6" s="36"/>
       <c r="I6" s="16"/>
       <c r="J6" s="18"/>
       <c r="K6" s="16"/>
     </row>
-    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="39">
+      <c r="B7" s="36">
         <v>-9.1010000000000009</v>
       </c>
       <c r="C7" s="16">
@@ -7727,29 +8440,29 @@
         <v>24</v>
       </c>
       <c r="E7" s="16"/>
-      <c r="H7" s="39"/>
+      <c r="H7" s="36"/>
       <c r="I7" s="16"/>
       <c r="J7" s="18"/>
       <c r="K7" s="16"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="39"/>
+      <c r="B8" s="36"/>
       <c r="C8" s="16"/>
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
-      <c r="H8" s="39"/>
+      <c r="H8" s="36"/>
       <c r="I8" s="16"/>
       <c r="J8" s="16"/>
       <c r="K8" s="16"/>
     </row>
-    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="B9" s="39">
+      <c r="B9" s="36">
         <v>-0.28799999999999998</v>
       </c>
       <c r="C9" s="16">
@@ -7759,16 +8472,16 @@
         <v>24</v>
       </c>
       <c r="E9" s="16"/>
-      <c r="H9" s="39"/>
+      <c r="H9" s="36"/>
       <c r="I9" s="16"/>
       <c r="J9" s="18"/>
       <c r="K9" s="16"/>
     </row>
-    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="B10" s="39">
+      <c r="B10" s="36">
         <v>5.2999999999999999E-2</v>
       </c>
       <c r="C10" s="16">
@@ -7778,16 +8491,16 @@
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="E10" s="16"/>
-      <c r="H10" s="39"/>
+      <c r="H10" s="36"/>
       <c r="I10" s="16"/>
       <c r="J10" s="18"/>
       <c r="K10" s="16"/>
     </row>
-    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="B11" s="39">
+      <c r="B11" s="36">
         <v>0.124</v>
       </c>
       <c r="C11" s="16">
@@ -7797,16 +8510,16 @@
         <v>24</v>
       </c>
       <c r="E11" s="16"/>
-      <c r="H11" s="39"/>
+      <c r="H11" s="36"/>
       <c r="I11" s="16"/>
       <c r="J11" s="18"/>
       <c r="K11" s="16"/>
     </row>
-    <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="40">
+      <c r="B12" s="37">
         <v>-3.2000000000000001E-2</v>
       </c>
       <c r="C12" s="25">
@@ -7816,376 +8529,376 @@
         <v>0.40699999999999997</v>
       </c>
       <c r="E12" s="16"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="47"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="18"/>
       <c r="K12" s="16"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="B13" s="39"/>
+      <c r="B13" s="36"/>
       <c r="C13" s="16"/>
       <c r="D13" s="18"/>
       <c r="E13" s="16"/>
-      <c r="H13" s="39"/>
+      <c r="H13" s="36"/>
       <c r="I13" s="16"/>
       <c r="J13" s="18"/>
       <c r="K13" s="16"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="B14" s="39"/>
+      <c r="B14" s="36"/>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16"/>
-      <c r="H14" s="39"/>
+      <c r="H14" s="36"/>
       <c r="I14" s="16"/>
       <c r="J14" s="16"/>
       <c r="K14" s="16"/>
     </row>
-    <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>101</v>
       </c>
-      <c r="B15" s="39"/>
+      <c r="B15" s="36"/>
       <c r="C15" s="16"/>
       <c r="D15" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E15" s="16"/>
-      <c r="H15" s="39"/>
+      <c r="H15" s="36"/>
       <c r="I15" s="16"/>
       <c r="J15" s="18"/>
       <c r="K15" s="16"/>
     </row>
-    <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="B16" s="39"/>
+      <c r="B16" s="36"/>
       <c r="C16" s="16"/>
       <c r="D16" s="18"/>
       <c r="E16" s="16"/>
-      <c r="H16" s="39"/>
+      <c r="H16" s="36"/>
       <c r="I16" s="16"/>
       <c r="J16" s="18"/>
       <c r="K16" s="16"/>
     </row>
-    <row r="17" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="B17" s="39"/>
+      <c r="B17" s="36"/>
       <c r="C17" s="16"/>
       <c r="D17" s="18"/>
       <c r="E17" s="16"/>
-      <c r="H17" s="39"/>
+      <c r="H17" s="36"/>
       <c r="I17" s="16"/>
       <c r="J17" s="18"/>
       <c r="K17" s="16"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="B18" s="39"/>
+      <c r="B18" s="36"/>
       <c r="C18" s="16"/>
       <c r="D18" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E18" s="16"/>
-      <c r="H18" s="39"/>
+      <c r="H18" s="36"/>
       <c r="I18" s="16"/>
       <c r="J18" s="18"/>
       <c r="K18" s="16"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="B19" s="39"/>
+      <c r="B19" s="36"/>
       <c r="C19" s="16"/>
       <c r="D19" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E19" s="16"/>
-      <c r="H19" s="39"/>
+      <c r="H19" s="36"/>
       <c r="I19" s="16"/>
       <c r="J19" s="18"/>
       <c r="K19" s="16"/>
     </row>
-    <row r="20" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="B20" s="39"/>
+      <c r="B20" s="36"/>
       <c r="C20" s="16"/>
       <c r="D20" s="18"/>
       <c r="E20" s="16"/>
-      <c r="H20" s="39"/>
+      <c r="H20" s="36"/>
       <c r="I20" s="16"/>
       <c r="J20" s="18"/>
       <c r="K20" s="16"/>
     </row>
-    <row r="21" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="B21" s="39"/>
+      <c r="B21" s="36"/>
       <c r="C21" s="16"/>
       <c r="D21" s="18"/>
       <c r="E21" s="16"/>
-      <c r="H21" s="39"/>
+      <c r="H21" s="36"/>
       <c r="I21" s="16"/>
       <c r="J21" s="18"/>
       <c r="K21" s="16"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="B22" s="39"/>
+      <c r="B22" s="36"/>
       <c r="C22" s="16"/>
       <c r="D22" s="18">
         <v>0.51400000000000001</v>
       </c>
       <c r="E22" s="16"/>
-      <c r="H22" s="39"/>
+      <c r="H22" s="36"/>
       <c r="I22" s="16"/>
       <c r="J22" s="18"/>
       <c r="K22" s="16"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="B23" s="39"/>
+      <c r="B23" s="36"/>
       <c r="C23" s="16"/>
       <c r="D23" s="18">
         <v>4.0000000000000001E-3</v>
       </c>
       <c r="E23" s="16"/>
-      <c r="H23" s="39"/>
+      <c r="H23" s="36"/>
       <c r="I23" s="16"/>
       <c r="J23" s="18"/>
       <c r="K23" s="16"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="B24" s="39"/>
+      <c r="B24" s="36"/>
       <c r="C24" s="16"/>
       <c r="D24" s="18"/>
       <c r="E24" s="16"/>
-      <c r="H24" s="39"/>
+      <c r="H24" s="36"/>
       <c r="I24" s="16"/>
       <c r="J24" s="18"/>
       <c r="K24" s="16"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="B25" s="39"/>
+      <c r="B25" s="36"/>
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
       <c r="E25" s="16"/>
-      <c r="H25" s="39"/>
+      <c r="H25" s="36"/>
       <c r="I25" s="16"/>
       <c r="J25" s="16"/>
       <c r="K25" s="16"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="B26" s="39"/>
+      <c r="B26" s="36"/>
       <c r="C26" s="16"/>
       <c r="D26" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E26" s="16"/>
-      <c r="H26" s="39"/>
+      <c r="H26" s="36"/>
       <c r="I26" s="16"/>
       <c r="J26" s="18"/>
       <c r="K26" s="16"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B27" s="39"/>
+      <c r="B27" s="36"/>
       <c r="C27" s="16"/>
       <c r="D27" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E27" s="16"/>
-      <c r="H27" s="39"/>
+      <c r="H27" s="36"/>
       <c r="I27" s="16"/>
       <c r="J27" s="18"/>
       <c r="K27" s="16"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B28" s="39"/>
+      <c r="B28" s="36"/>
       <c r="C28" s="16"/>
       <c r="D28" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E28" s="16"/>
-      <c r="H28" s="39"/>
+      <c r="H28" s="36"/>
       <c r="I28" s="16"/>
       <c r="J28" s="18"/>
       <c r="K28" s="16"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="B29" s="39"/>
+      <c r="B29" s="36"/>
       <c r="C29" s="16"/>
       <c r="D29" s="18"/>
       <c r="E29" s="16"/>
-      <c r="H29" s="39"/>
+      <c r="H29" s="36"/>
       <c r="I29" s="16"/>
       <c r="J29" s="18"/>
       <c r="K29" s="16"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="B30" s="39"/>
+      <c r="B30" s="36"/>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
-      <c r="H30" s="39"/>
+      <c r="H30" s="36"/>
       <c r="I30" s="16"/>
       <c r="J30" s="16"/>
       <c r="K30" s="16"/>
     </row>
-    <row r="31" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B31" s="39"/>
+      <c r="B31" s="36"/>
       <c r="C31" s="16"/>
       <c r="D31" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E31" s="16"/>
-      <c r="H31" s="39"/>
+      <c r="H31" s="36"/>
       <c r="I31" s="16"/>
       <c r="J31" s="18"/>
       <c r="K31" s="16"/>
     </row>
-    <row r="32" spans="1:11" ht="17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B32" s="39"/>
+      <c r="B32" s="36"/>
       <c r="C32" s="16"/>
       <c r="D32" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E32" s="16"/>
-      <c r="H32" s="39"/>
+      <c r="H32" s="36"/>
       <c r="I32" s="16"/>
       <c r="J32" s="18"/>
       <c r="K32" s="16"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="B33" s="39"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="16"/>
       <c r="D33" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E33" s="16"/>
-      <c r="H33" s="39"/>
+      <c r="H33" s="36"/>
       <c r="I33" s="16"/>
       <c r="J33" s="18"/>
       <c r="K33" s="16"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="B34" s="39"/>
+      <c r="B34" s="36"/>
       <c r="C34" s="16"/>
       <c r="D34" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E34" s="16"/>
-      <c r="H34" s="39"/>
+      <c r="H34" s="36"/>
       <c r="I34" s="16"/>
       <c r="J34" s="18"/>
       <c r="K34" s="16"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="B35" s="39"/>
+      <c r="B35" s="36"/>
       <c r="C35" s="16"/>
       <c r="D35" s="18"/>
       <c r="E35" s="16"/>
-      <c r="H35" s="39"/>
+      <c r="H35" s="36"/>
       <c r="I35" s="16"/>
       <c r="J35" s="18"/>
       <c r="K35" s="16"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="B36" s="39"/>
+      <c r="B36" s="36"/>
       <c r="C36" s="16"/>
       <c r="D36" s="18"/>
-      <c r="H36" s="39"/>
+      <c r="H36" s="36"/>
       <c r="I36" s="16"/>
       <c r="J36" s="18"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="20" t="s">
         <v>116</v>
       </c>
-      <c r="B37" s="41"/>
+      <c r="B37" s="38"/>
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
-      <c r="F37" s="36"/>
+      <c r="F37" s="33"/>
       <c r="G37" s="14"/>
-      <c r="H37" s="41"/>
+      <c r="H37" s="38"/>
       <c r="I37" s="14"/>
       <c r="J37" s="14"/>
       <c r="K37" s="14"/>
-      <c r="L37" s="36"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L37" s="33"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="B38" s="42"/>
+      <c r="B38" s="39"/>
       <c r="C38" s="15"/>
       <c r="D38" s="15"/>
       <c r="E38" s="15"/>
-      <c r="F38" s="37"/>
+      <c r="F38" s="34"/>
       <c r="G38" s="15"/>
-      <c r="H38" s="42"/>
+      <c r="H38" s="39"/>
       <c r="I38" s="15"/>
       <c r="J38" s="15"/>
       <c r="K38" s="15"/>
-      <c r="L38" s="37"/>
+      <c r="L38" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -8201,54 +8914,54 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{540507A6-720C-0B43-804E-087FEE710926}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" customWidth="1"/>
+    <col min="1" max="1" width="19.875" customWidth="1"/>
+    <col min="2" max="2" width="18.875" customWidth="1"/>
+    <col min="3" max="3" width="19.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="24"/>
     </row>
-    <row r="3" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="24"/>
     </row>
-    <row r="6" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="24"/>
     </row>
-    <row r="7" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="23" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B11" s="23" t="s">
         <v>128</v>
       </c>
@@ -8256,7 +8969,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>125</v>
       </c>
@@ -8267,7 +8980,7 @@
         <v>-1.4E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>126</v>
       </c>
@@ -8278,7 +8991,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>127</v>
       </c>
@@ -8289,7 +9002,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>132</v>
       </c>
@@ -8300,17 +9013,17 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="23" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B19" s="23" t="s">
         <v>128</v>
       </c>
@@ -8318,7 +9031,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>125</v>
       </c>
@@ -8329,7 +9042,7 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>126</v>
       </c>
@@ -8340,7 +9053,7 @@
         <v>-1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>127</v>
       </c>
@@ -8351,7 +9064,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>132</v>
       </c>
@@ -8362,7 +9075,7 @@
         <v>-1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E25" s="23" t="s">
         <v>131</v>
       </c>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nchaku\Documents\GitHub\pubertybrain\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmoffice-my.sharepoint.com/personal/abrieant_uvm_edu/Documents/OneDrive/Manuscripts/reg report DCN/pubertybrain/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F29979F-BB53-4166-B9B9-F89018F0CDEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{1F29979F-BB53-4166-B9B9-F89018F0CDEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51867643-3C5E-D94F-AF10-4EE9E35910E6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
+    <workbookView xWindow="-120" yWindow="500" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptive table" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="148">
   <si>
     <t>16.10 (2.98)</t>
   </si>
@@ -352,9 +352,6 @@
   </si>
   <si>
     <t>Means</t>
-  </si>
-  <si>
-    <t>Variances</t>
   </si>
   <si>
     <t xml:space="preserve">   Timing</t>
@@ -829,6 +826,33 @@
   </si>
   <si>
     <t xml:space="preserve">   WM on Quadratic Slope</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   Slope</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> with Tempo</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">   Timing with Tempo</t>
   </si>
 </sst>
 </file>
@@ -1095,7 +1119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1152,14 +1176,14 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1167,6 +1191,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1747,20 +1772,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39987BE7-3659-524A-81AE-D479F97EF698}">
   <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="20.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="9"/>
       <c r="B2" s="10" t="s">
         <v>63</v>
@@ -1778,7 +1803,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="6"/>
       <c r="B3" s="11" t="s">
         <v>69</v>
@@ -1792,7 +1817,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>60</v>
       </c>
@@ -1802,7 +1827,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>61</v>
       </c>
@@ -1822,7 +1847,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>62</v>
       </c>
@@ -1842,7 +1867,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>58</v>
       </c>
@@ -1862,7 +1887,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>59</v>
       </c>
@@ -1872,7 +1897,7 @@
       <c r="E8" s="12"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>61</v>
       </c>
@@ -1892,7 +1917,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>66</v>
       </c>
@@ -1912,7 +1937,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>67</v>
       </c>
@@ -1932,7 +1957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>62</v>
       </c>
@@ -1952,7 +1977,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>68</v>
       </c>
@@ -1962,7 +1987,7 @@
       <c r="E13" s="12"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>73</v>
       </c>
@@ -1982,7 +2007,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>74</v>
       </c>
@@ -2002,7 +2027,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>75</v>
       </c>
@@ -2022,7 +2047,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>76</v>
       </c>
@@ -2040,7 +2065,7 @@
       </c>
       <c r="F17" s="19"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>71</v>
       </c>
@@ -2050,7 +2075,7 @@
       <c r="E18" s="12"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>61</v>
       </c>
@@ -2070,7 +2095,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>66</v>
       </c>
@@ -2090,7 +2115,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>67</v>
       </c>
@@ -2110,7 +2135,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>62</v>
       </c>
@@ -2130,7 +2155,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>72</v>
       </c>
@@ -2140,7 +2165,7 @@
       <c r="E23" s="12"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>61</v>
       </c>
@@ -2160,7 +2185,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>66</v>
       </c>
@@ -2180,7 +2205,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>67</v>
       </c>
@@ -2200,7 +2225,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>62</v>
       </c>
@@ -2220,7 +2245,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2228,7 +2253,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2244,11 +2269,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A749072B-F938-0F49-BE23-243603B2B3D0}">
   <dimension ref="M2"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2260,7 +2285,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45875D41-9C56-AA4E-A18A-2D3A4CE169B3}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2270,7 +2295,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A5153E-6E5C-054A-8ACA-5118463B96C5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2280,242 +2305,242 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA86F85-A8D4-F648-84C3-730F1A42C846}">
   <dimension ref="A1:AM34"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="1.1640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.6640625" style="1" customWidth="1"/>
     <col min="11" max="11" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="1.125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="1.1640625" style="1" customWidth="1"/>
     <col min="14" max="14" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.6640625" style="1" customWidth="1"/>
     <col min="17" max="17" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="0.875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="0.83203125" style="1" customWidth="1"/>
     <col min="20" max="20" width="8.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="5.625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="6.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="5.6640625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="1" style="1" customWidth="1"/>
     <col min="26" max="26" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.6640625" style="1" customWidth="1"/>
     <col min="29" max="30" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="1.125" style="1" customWidth="1"/>
+    <col min="31" max="31" width="1.1640625" style="1" customWidth="1"/>
     <col min="32" max="32" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="5.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="5.625" style="1" customWidth="1"/>
-    <col min="36" max="36" width="6.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="5.6640625" style="1" customWidth="1"/>
+    <col min="36" max="36" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="41"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="40"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="40" t="s">
-        <v>114</v>
-      </c>
-      <c r="U2" s="40"/>
-      <c r="V2" s="40"/>
-      <c r="W2" s="40"/>
-      <c r="X2" s="40"/>
-      <c r="Y2" s="40"/>
-      <c r="Z2" s="40"/>
-      <c r="AA2" s="40"/>
-      <c r="AB2" s="40"/>
-      <c r="AC2" s="40"/>
-      <c r="AD2" s="40"/>
-      <c r="AE2" s="40"/>
-      <c r="AF2" s="40"/>
-      <c r="AG2" s="40"/>
-      <c r="AH2" s="40"/>
-      <c r="AI2" s="40"/>
-      <c r="AJ2" s="40"/>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="U2" s="41"/>
+      <c r="V2" s="41"/>
+      <c r="W2" s="41"/>
+      <c r="X2" s="41"/>
+      <c r="Y2" s="41"/>
+      <c r="Z2" s="41"/>
+      <c r="AA2" s="41"/>
+      <c r="AB2" s="41"/>
+      <c r="AC2" s="41"/>
+      <c r="AD2" s="41"/>
+      <c r="AE2" s="41"/>
+      <c r="AF2" s="41"/>
+      <c r="AG2" s="41"/>
+      <c r="AH2" s="41"/>
+      <c r="AI2" s="41"/>
+      <c r="AJ2" s="41"/>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A3" s="16"/>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
       <c r="G3" s="28"/>
-      <c r="H3" s="40" t="s">
+      <c r="H3" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
       <c r="M3" s="28"/>
-      <c r="N3" s="40" t="s">
+      <c r="N3" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="T3" s="41" t="s">
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="41"/>
+      <c r="T3" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="U3" s="41"/>
-      <c r="V3" s="41"/>
-      <c r="W3" s="41"/>
-      <c r="X3" s="41"/>
+      <c r="U3" s="42"/>
+      <c r="V3" s="42"/>
+      <c r="W3" s="42"/>
+      <c r="X3" s="42"/>
       <c r="Y3" s="28"/>
-      <c r="Z3" s="40" t="s">
+      <c r="Z3" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="AA3" s="40"/>
-      <c r="AB3" s="40"/>
-      <c r="AC3" s="40"/>
-      <c r="AD3" s="40"/>
+      <c r="AA3" s="41"/>
+      <c r="AB3" s="41"/>
+      <c r="AC3" s="41"/>
+      <c r="AD3" s="41"/>
       <c r="AE3" s="28"/>
-      <c r="AF3" s="40" t="s">
+      <c r="AF3" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="AG3" s="40"/>
-      <c r="AH3" s="40"/>
-      <c r="AI3" s="40"/>
-      <c r="AJ3" s="40"/>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AG3" s="41"/>
+      <c r="AH3" s="41"/>
+      <c r="AI3" s="41"/>
+      <c r="AJ3" s="41"/>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
       <c r="B4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="D4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="E4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="F4" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="F4" s="29" t="s">
-        <v>135</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="J4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="K4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="L4" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="L4" s="29" t="s">
-        <v>135</v>
       </c>
       <c r="M4" s="29"/>
       <c r="N4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="O4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="O4" s="29" t="s">
+      <c r="P4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="P4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="Q4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="R4" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="R4" s="29" t="s">
-        <v>135</v>
       </c>
       <c r="S4" s="6"/>
       <c r="T4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="U4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="U4" s="29" t="s">
+      <c r="V4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="V4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="W4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="X4" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="X4" s="29" t="s">
-        <v>135</v>
       </c>
       <c r="Y4" s="17"/>
       <c r="Z4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="AA4" s="29" t="s">
+      <c r="AB4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="AB4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="AC4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD4" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="AD4" s="29" t="s">
-        <v>135</v>
       </c>
       <c r="AE4" s="17"/>
       <c r="AF4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="AG4" s="29" t="s">
+      <c r="AH4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="AH4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="AI4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="AJ4" s="29" t="s">
         <v>134</v>
       </c>
-      <c r="AJ4" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -2552,9 +2577,9 @@
       <c r="AI5" s="16"/>
       <c r="AJ5" s="16"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B6" s="16">
         <v>12.162000000000001</v>
@@ -2651,9 +2676,9 @@
         <v>12.236000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B7" s="16">
         <v>-9.1289999999999996</v>
@@ -2750,7 +2775,7 @@
         <v>-7.7560000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A8" s="16"/>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -2787,9 +2812,9 @@
       <c r="AI8" s="18"/>
       <c r="AJ8" s="16"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A9" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
@@ -2826,9 +2851,9 @@
       <c r="AI9" s="16"/>
       <c r="AJ9" s="16"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B10" s="16">
         <v>-0.312</v>
@@ -2925,9 +2950,9 @@
         <v>-0.24</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B11" s="16">
         <v>0.13200000000000001</v>
@@ -3024,9 +3049,9 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B12" s="16">
         <v>0.16300000000000001</v>
@@ -3123,9 +3148,9 @@
         <v>0.14899999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B13" s="16">
         <v>-5.5E-2</v>
@@ -3222,9 +3247,9 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A14" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B14" s="16">
         <v>0.318</v>
@@ -3321,7 +3346,7 @@
         <v>0.28799999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A15" s="16"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -3358,9 +3383,9 @@
       <c r="AI15" s="18"/>
       <c r="AJ15" s="16"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -3397,9 +3422,9 @@
       <c r="AI16" s="16"/>
       <c r="AJ16" s="16"/>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B17" s="16">
         <v>0.34100000000000003</v>
@@ -3496,24 +3521,24 @@
         <v>0.443</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G18" s="21"/>
       <c r="H18" s="16">
@@ -3548,19 +3573,19 @@
         <v>-0.11</v>
       </c>
       <c r="T18" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U18" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V18" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W18" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X18" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y18" s="21"/>
       <c r="Z18" s="16">
@@ -3595,24 +3620,24 @@
         <v>-0.10299999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G19" s="21"/>
       <c r="H19" s="22">
@@ -3647,19 +3672,19 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="T19" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U19" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V19" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W19" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X19" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y19" s="21"/>
       <c r="Z19" s="16">
@@ -3694,24 +3719,24 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G20" s="21"/>
       <c r="H20" s="16">
@@ -3746,19 +3771,19 @@
         <v>-0.15</v>
       </c>
       <c r="T20" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U20" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V20" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W20" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X20" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y20" s="21"/>
       <c r="Z20" s="16">
@@ -3793,24 +3818,24 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G21" s="21"/>
       <c r="H21" s="16">
@@ -3845,19 +3870,19 @@
         <v>-0.183</v>
       </c>
       <c r="T21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W21" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X21" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y21" s="21"/>
       <c r="Z21" s="16">
@@ -3892,40 +3917,40 @@
         <v>-0.13600000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G22" s="21"/>
       <c r="H22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M22" s="16"/>
       <c r="N22" s="16">
@@ -3944,33 +3969,33 @@
         <v>0.21099999999999999</v>
       </c>
       <c r="T22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W22" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X22" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y22" s="21"/>
       <c r="Z22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC22" s="16"/>
       <c r="AD22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE22" s="16"/>
       <c r="AF22" s="16">
@@ -3989,40 +4014,40 @@
         <v>0.156</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G23" s="21"/>
       <c r="H23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M23" s="16"/>
       <c r="N23" s="16">
@@ -4041,33 +4066,33 @@
         <v>6.3E-2</v>
       </c>
       <c r="T23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W23" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X23" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y23" s="21"/>
       <c r="Z23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC23" s="16"/>
       <c r="AD23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE23" s="16"/>
       <c r="AF23" s="16">
@@ -4086,40 +4111,40 @@
         <v>-1.6E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G24" s="21"/>
       <c r="H24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M24" s="16"/>
       <c r="N24" s="16">
@@ -4138,33 +4163,33 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="T24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W24" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X24" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y24" s="21"/>
       <c r="Z24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC24" s="16"/>
       <c r="AD24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE24" s="16"/>
       <c r="AF24" s="16">
@@ -4183,40 +4208,40 @@
         <v>0.112</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A25" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G25" s="21"/>
       <c r="H25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M25" s="16"/>
       <c r="N25" s="16">
@@ -4235,33 +4260,33 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="T25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W25" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X25" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y25" s="21"/>
       <c r="Z25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC25" s="16"/>
       <c r="AD25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE25" s="16"/>
       <c r="AF25" s="16">
@@ -4280,40 +4305,40 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G26" s="21"/>
       <c r="H26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M26" s="16"/>
       <c r="N26" s="16">
@@ -4332,33 +4357,33 @@
         <v>-7.1999999999999995E-2</v>
       </c>
       <c r="T26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W26" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X26" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y26" s="21"/>
       <c r="Z26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC26" s="16"/>
       <c r="AD26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE26" s="16"/>
       <c r="AF26" s="16">
@@ -4377,7 +4402,7 @@
         <v>-4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -4414,7 +4439,7 @@
       <c r="AI27" s="18"/>
       <c r="AJ27" s="16"/>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A28" s="17" t="s">
         <v>82</v>
       </c>
@@ -4453,9 +4478,9 @@
       <c r="AI28" s="16"/>
       <c r="AJ28" s="16"/>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A29" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B29" s="16">
         <v>10.965999999999999</v>
@@ -4552,9 +4577,9 @@
         <v>14.164999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A30" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B30" s="16">
         <v>3.7069999999999999</v>
@@ -4651,24 +4676,24 @@
         <v>4.1660000000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G31" s="21"/>
       <c r="H31" s="16">
@@ -4703,19 +4728,19 @@
         <v>1.0429999999999999</v>
       </c>
       <c r="T31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X31" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y31" s="21"/>
       <c r="Z31" s="16">
@@ -4750,38 +4775,38 @@
         <v>1.0549999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A32" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G32" s="21"/>
       <c r="H32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K32" s="16"/>
       <c r="L32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M32" s="16"/>
       <c r="N32" s="16">
@@ -4800,35 +4825,35 @@
         <v>4.5410000000000004</v>
       </c>
       <c r="T32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W32" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X32" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y32" s="21"/>
       <c r="Z32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC32" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AD32" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE32" s="16"/>
       <c r="AF32" s="16">
@@ -4847,9 +4872,9 @@
         <v>4.202</v>
       </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A33" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -4890,69 +4915,63 @@
       <c r="AL33" s="16"/>
       <c r="AM33" s="16"/>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="B34" s="42">
+        <v>116</v>
+      </c>
+      <c r="B34" s="40">
         <v>74058.118000000002</v>
       </c>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
       <c r="G34" s="27"/>
-      <c r="H34" s="42">
+      <c r="H34" s="40">
         <v>83016.937999999995</v>
       </c>
-      <c r="I34" s="42"/>
-      <c r="J34" s="42"/>
-      <c r="K34" s="42"/>
-      <c r="L34" s="42"/>
+      <c r="I34" s="40"/>
+      <c r="J34" s="40"/>
+      <c r="K34" s="40"/>
+      <c r="L34" s="40"/>
       <c r="M34" s="27"/>
-      <c r="N34" s="42">
+      <c r="N34" s="40">
         <v>94345.274999999994</v>
       </c>
-      <c r="O34" s="42"/>
-      <c r="P34" s="42"/>
-      <c r="Q34" s="42"/>
-      <c r="R34" s="42"/>
+      <c r="O34" s="40"/>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="40"/>
       <c r="S34" s="15"/>
-      <c r="T34" s="42">
+      <c r="T34" s="40">
         <v>83167.763000000006</v>
       </c>
-      <c r="U34" s="42"/>
-      <c r="V34" s="42"/>
-      <c r="W34" s="42"/>
-      <c r="X34" s="42"/>
+      <c r="U34" s="40"/>
+      <c r="V34" s="40"/>
+      <c r="W34" s="40"/>
+      <c r="X34" s="40"/>
       <c r="Y34" s="27"/>
-      <c r="Z34" s="42">
+      <c r="Z34" s="40">
         <v>93083.505999999994</v>
       </c>
-      <c r="AA34" s="42"/>
-      <c r="AB34" s="42"/>
-      <c r="AC34" s="42"/>
-      <c r="AD34" s="42"/>
+      <c r="AA34" s="40"/>
+      <c r="AB34" s="40"/>
+      <c r="AC34" s="40"/>
+      <c r="AD34" s="40"/>
       <c r="AE34" s="27"/>
-      <c r="AF34" s="42">
+      <c r="AF34" s="40">
         <v>105770.462</v>
       </c>
-      <c r="AG34" s="42"/>
-      <c r="AH34" s="42"/>
-      <c r="AI34" s="42"/>
-      <c r="AJ34" s="42"/>
+      <c r="AG34" s="40"/>
+      <c r="AH34" s="40"/>
+      <c r="AI34" s="40"/>
+      <c r="AJ34" s="40"/>
       <c r="AK34" s="16"/>
       <c r="AL34" s="16"/>
       <c r="AM34" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="AF34:AJ34"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="H34:L34"/>
-    <mergeCell ref="T34:X34"/>
-    <mergeCell ref="N34:R34"/>
-    <mergeCell ref="Z34:AD34"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="H3:L3"/>
@@ -4961,6 +4980,12 @@
     <mergeCell ref="T3:X3"/>
     <mergeCell ref="Z3:AD3"/>
     <mergeCell ref="AF3:AJ3"/>
+    <mergeCell ref="AF34:AJ34"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="H34:L34"/>
+    <mergeCell ref="T34:X34"/>
+    <mergeCell ref="N34:R34"/>
+    <mergeCell ref="Z34:AD34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -4970,240 +4995,240 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CD5CF7F-81D6-D24D-8228-B4C578C35D65}">
   <dimension ref="A1:AM41"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" style="1" customWidth="1"/>
     <col min="5" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="1.1640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.6640625" style="1" customWidth="1"/>
     <col min="11" max="12" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="1.125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="1.1640625" style="1" customWidth="1"/>
     <col min="14" max="14" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.6640625" style="1" customWidth="1"/>
     <col min="17" max="17" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="0.875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="0.83203125" style="1" customWidth="1"/>
     <col min="20" max="20" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.6640625" style="1" customWidth="1"/>
     <col min="24" max="24" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="1" style="1" customWidth="1"/>
     <col min="26" max="26" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="30" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="1.125" style="1" customWidth="1"/>
+    <col min="31" max="31" width="1.1640625" style="1" customWidth="1"/>
     <col min="32" max="32" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="5.625" style="1" customWidth="1"/>
+    <col min="33" max="33" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.6640625" style="1" customWidth="1"/>
     <col min="35" max="36" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="41" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="41"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="40"/>
-      <c r="S2" s="9"/>
-      <c r="T2" s="40" t="s">
-        <v>114</v>
-      </c>
-      <c r="U2" s="40"/>
-      <c r="V2" s="40"/>
-      <c r="W2" s="40"/>
-      <c r="X2" s="40"/>
-      <c r="Y2" s="40"/>
-      <c r="Z2" s="40"/>
-      <c r="AA2" s="40"/>
-      <c r="AB2" s="40"/>
-      <c r="AC2" s="40"/>
-      <c r="AD2" s="40"/>
-      <c r="AE2" s="40"/>
-      <c r="AF2" s="40"/>
-      <c r="AG2" s="40"/>
-      <c r="AH2" s="40"/>
-      <c r="AI2" s="40"/>
-      <c r="AJ2" s="40"/>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="U2" s="41"/>
+      <c r="V2" s="41"/>
+      <c r="W2" s="41"/>
+      <c r="X2" s="41"/>
+      <c r="Y2" s="41"/>
+      <c r="Z2" s="41"/>
+      <c r="AA2" s="41"/>
+      <c r="AB2" s="41"/>
+      <c r="AC2" s="41"/>
+      <c r="AD2" s="41"/>
+      <c r="AE2" s="41"/>
+      <c r="AF2" s="41"/>
+      <c r="AG2" s="41"/>
+      <c r="AH2" s="41"/>
+      <c r="AI2" s="41"/>
+      <c r="AJ2" s="41"/>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A3" s="16"/>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
       <c r="G3" s="28"/>
-      <c r="H3" s="40" t="s">
+      <c r="H3" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
       <c r="M3" s="28"/>
-      <c r="N3" s="40" t="s">
+      <c r="N3" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="T3" s="41" t="s">
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="41"/>
+      <c r="T3" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="U3" s="41"/>
-      <c r="V3" s="41"/>
-      <c r="W3" s="41"/>
-      <c r="X3" s="41"/>
+      <c r="U3" s="42"/>
+      <c r="V3" s="42"/>
+      <c r="W3" s="42"/>
+      <c r="X3" s="42"/>
       <c r="Y3" s="28"/>
-      <c r="Z3" s="40" t="s">
+      <c r="Z3" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="AA3" s="40"/>
-      <c r="AB3" s="40"/>
-      <c r="AC3" s="40"/>
-      <c r="AD3" s="40"/>
+      <c r="AA3" s="41"/>
+      <c r="AB3" s="41"/>
+      <c r="AC3" s="41"/>
+      <c r="AD3" s="41"/>
       <c r="AE3" s="28"/>
-      <c r="AF3" s="40" t="s">
+      <c r="AF3" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="AG3" s="40"/>
-      <c r="AH3" s="40"/>
-      <c r="AI3" s="40"/>
-      <c r="AJ3" s="40"/>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AG3" s="41"/>
+      <c r="AH3" s="41"/>
+      <c r="AI3" s="41"/>
+      <c r="AJ3" s="41"/>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
       <c r="B4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="D4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="E4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="F4" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="F4" s="29" t="s">
-        <v>135</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="J4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="K4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="L4" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="L4" s="29" t="s">
-        <v>135</v>
       </c>
       <c r="M4" s="29"/>
       <c r="N4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="O4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="O4" s="29" t="s">
+      <c r="P4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="P4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="Q4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="R4" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="R4" s="29" t="s">
-        <v>135</v>
       </c>
       <c r="S4" s="6"/>
       <c r="T4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="U4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="U4" s="29" t="s">
+      <c r="V4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="V4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="W4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="X4" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="X4" s="29" t="s">
-        <v>135</v>
       </c>
       <c r="Y4" s="17"/>
       <c r="Z4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="AA4" s="29" t="s">
+      <c r="AB4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="AB4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="AC4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="AD4" s="29" t="s">
         <v>134</v>
-      </c>
-      <c r="AD4" s="29" t="s">
-        <v>135</v>
       </c>
       <c r="AE4" s="17"/>
       <c r="AF4" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="AG4" s="29" t="s">
+      <c r="AH4" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="AH4" s="29" t="s">
-        <v>92</v>
-      </c>
       <c r="AI4" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="AJ4" s="29" t="s">
         <v>134</v>
       </c>
-      <c r="AJ4" s="29" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -5240,9 +5265,9 @@
       <c r="AI5" s="16"/>
       <c r="AJ5" s="16"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B6" s="16">
         <v>13.944000000000001</v>
@@ -5339,56 +5364,56 @@
         <v>13.875999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J7" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K7" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M7" s="16"/>
       <c r="N7" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O7" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P7" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q7" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R7" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T7" s="16">
         <v>1.222</v>
@@ -5438,9 +5463,9 @@
         <v>2.1219999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B8" s="16">
         <v>-0.253</v>
@@ -5490,54 +5515,54 @@
         <v>-7.4729999999999999</v>
       </c>
       <c r="T8" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U8" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V8" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W8" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X8" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y8" s="16"/>
       <c r="Z8" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA8" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB8" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC8" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AD8" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE8" s="16"/>
       <c r="AF8" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG8" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH8" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI8" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AJ8" s="21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A9" s="16"/>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
@@ -5574,9 +5599,9 @@
       <c r="AI9" s="18"/>
       <c r="AJ9" s="16"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A10" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -5613,56 +5638,56 @@
       <c r="AI10" s="16"/>
       <c r="AJ10" s="16"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G11" s="16"/>
       <c r="H11" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J11" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M11" s="16"/>
       <c r="N11" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O11" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P11" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q11" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R11" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T11" s="16">
         <v>0.318</v>
@@ -5712,9 +5737,9 @@
         <v>0.40300000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B12" s="16">
         <v>0.11700000000000001</v>
@@ -5764,56 +5789,56 @@
         <v>0.20899999999999999</v>
       </c>
       <c r="T12" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U12" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V12" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W12" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X12" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y12" s="16"/>
       <c r="Z12" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA12" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB12" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC12" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AD12" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE12" s="16"/>
       <c r="AF12" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG12" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH12" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI12" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AJ12" s="21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B13" s="16">
         <v>0.02</v>
@@ -5910,9 +5935,9 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B14" s="16">
         <v>6.9000000000000006E-2</v>
@@ -6009,155 +6034,155 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G15" s="21"/>
       <c r="H15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K15" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M15" s="16"/>
       <c r="N15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q15" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R15" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W15" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X15" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y15" s="16"/>
       <c r="Z15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC15" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AD15" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE15" s="16"/>
       <c r="AF15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH15" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI15" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AJ15" s="21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G16" s="16"/>
       <c r="H16" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J16" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K16" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M16" s="16"/>
       <c r="N16" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O16" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P16" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q16" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R16" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T16" s="16">
         <v>0.16800000000000001</v>
@@ -6207,9 +6232,9 @@
         <v>0.22900000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B17" s="16">
         <v>-0.45300000000000001</v>
@@ -6259,56 +6284,56 @@
         <v>0.153</v>
       </c>
       <c r="T17" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U17" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V17" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W17" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X17" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y17" s="16"/>
       <c r="Z17" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA17" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB17" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC17" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AD17" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE17" s="16"/>
       <c r="AF17" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG17" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH17" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI17" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AJ17" s="21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B18" s="16">
         <v>0.318</v>
@@ -6405,7 +6430,7 @@
         <v>0.28799999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A19" s="16"/>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -6442,9 +6467,9 @@
       <c r="AI19" s="18"/>
       <c r="AJ19" s="16"/>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A20" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
@@ -6481,56 +6506,56 @@
       <c r="AI20" s="16"/>
       <c r="AJ20" s="16"/>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G21" s="16"/>
       <c r="H21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K21" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M21" s="16"/>
       <c r="N21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q21" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R21" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T21" s="16">
         <v>8.5000000000000006E-2</v>
@@ -6580,9 +6605,9 @@
         <v>0.14499999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B22" s="16">
         <v>-0.29099999999999998</v>
@@ -6632,71 +6657,71 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="T22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W22" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X22" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y22" s="21"/>
       <c r="Z22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC22" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AD22" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE22" s="16"/>
       <c r="AF22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH22" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI22" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AJ22" s="21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G23" s="21"/>
       <c r="H23" s="16">
@@ -6731,19 +6756,19 @@
         <v>-7.5999999999999998E-2</v>
       </c>
       <c r="T23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V23" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W23" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X23" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y23" s="21"/>
       <c r="Z23" s="16">
@@ -6778,71 +6803,71 @@
         <v>-9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G24" s="21"/>
       <c r="H24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K24" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L24" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M24" s="16"/>
       <c r="N24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q24" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R24" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V24" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W24" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X24" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y24" s="21"/>
       <c r="Z24" s="16">
@@ -6877,9 +6902,9 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H25" s="16">
         <v>-8.8999999999999996E-2</v>
@@ -6912,69 +6937,69 @@
         <v>-3.1E-2</v>
       </c>
       <c r="T25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W25" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X25" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Z25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC25" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AD25" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AF25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH25" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI25" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AJ25" s="21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G26" s="21"/>
       <c r="H26" s="16">
@@ -7009,19 +7034,19 @@
         <v>-0.15</v>
       </c>
       <c r="T26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V26" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W26" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X26" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y26" s="21"/>
       <c r="Z26" s="16">
@@ -7056,24 +7081,24 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G27" s="21"/>
       <c r="H27" s="16">
@@ -7108,19 +7133,19 @@
         <v>-0.183</v>
       </c>
       <c r="T27" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U27" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V27" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W27" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X27" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y27" s="21"/>
       <c r="Z27" s="16">
@@ -7155,40 +7180,40 @@
         <v>-0.13600000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F28" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G28" s="21"/>
       <c r="H28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M28" s="16"/>
       <c r="N28" s="16">
@@ -7207,33 +7232,33 @@
         <v>0.17399999999999999</v>
       </c>
       <c r="T28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W28" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X28" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y28" s="21"/>
       <c r="Z28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC28" s="16"/>
       <c r="AD28" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE28" s="16"/>
       <c r="AF28" s="16">
@@ -7252,85 +7277,85 @@
         <v>0.17199999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F29" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G29" s="21"/>
       <c r="H29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M29" s="16"/>
       <c r="N29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="R29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="T29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W29" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X29" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y29" s="21"/>
       <c r="Z29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC29" s="16"/>
       <c r="AD29" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE29" s="16"/>
       <c r="AF29" s="16">
@@ -7349,9 +7374,9 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A30" s="16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -7381,87 +7406,87 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="T30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W30" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X30" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y30" s="21"/>
       <c r="Z30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC30" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AD30" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE30" s="16"/>
       <c r="AF30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AG30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AH30" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AI30" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AJ30" s="21" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A31" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G31" s="21"/>
       <c r="H31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M31" s="16"/>
       <c r="N31" s="16">
@@ -7480,33 +7505,33 @@
         <v>0.08</v>
       </c>
       <c r="T31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W31" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X31" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y31" s="21"/>
       <c r="Z31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC31" s="16"/>
       <c r="AD31" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE31" s="16"/>
       <c r="AF31" s="16">
@@ -7525,40 +7550,40 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A32" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G32" s="21"/>
       <c r="H32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M32" s="16"/>
       <c r="N32" s="16">
@@ -7577,33 +7602,33 @@
         <v>0.13800000000000001</v>
       </c>
       <c r="T32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W32" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X32" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y32" s="21"/>
       <c r="Z32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC32" s="16"/>
       <c r="AD32" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE32" s="16"/>
       <c r="AF32" s="16">
@@ -7622,40 +7647,40 @@
         <v>0.17499999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A33" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F33" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G33" s="21"/>
       <c r="H33" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I33" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J33" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M33" s="16"/>
       <c r="N33" s="16">
@@ -7674,33 +7699,33 @@
         <v>-7.1999999999999995E-2</v>
       </c>
       <c r="T33" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U33" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V33" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W33" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X33" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y33" s="21"/>
       <c r="Z33" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA33" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB33" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC33" s="16"/>
       <c r="AD33" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE33" s="16"/>
       <c r="AF33" s="16">
@@ -7719,7 +7744,7 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A34" s="16"/>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
@@ -7756,7 +7781,7 @@
       <c r="AI34" s="18"/>
       <c r="AJ34" s="16"/>
     </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A35" s="17" t="s">
         <v>82</v>
       </c>
@@ -7795,9 +7820,9 @@
       <c r="AI35" s="16"/>
       <c r="AJ35" s="16"/>
     </row>
-    <row r="36" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A36" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B36" s="16">
         <v>10.965</v>
@@ -7894,9 +7919,9 @@
         <v>14.162000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A37" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B37" s="16">
         <v>3.7109999999999999</v>
@@ -7993,24 +8018,24 @@
         <v>4.1660000000000004</v>
       </c>
     </row>
-    <row r="38" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A38" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F38" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G38" s="21"/>
       <c r="H38" s="16">
@@ -8045,19 +8070,19 @@
         <v>1.0429999999999999</v>
       </c>
       <c r="T38" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U38" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V38" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W38" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X38" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y38" s="21"/>
       <c r="Z38" s="16">
@@ -8092,38 +8117,38 @@
         <v>1.0549999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A39" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F39" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G39" s="21"/>
       <c r="H39" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I39" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J39" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K39" s="16"/>
       <c r="L39" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M39" s="16"/>
       <c r="N39" s="16">
@@ -8142,35 +8167,35 @@
         <v>5.3380000000000001</v>
       </c>
       <c r="T39" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U39" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="V39" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W39" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="X39" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y39" s="21"/>
       <c r="Z39" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AA39" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AB39" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AC39" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AD39" s="21" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AE39" s="16"/>
       <c r="AF39" s="16">
@@ -8189,9 +8214,9 @@
         <v>4.5090000000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A40" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
@@ -8232,57 +8257,57 @@
       <c r="AL40" s="16"/>
       <c r="AM40" s="16"/>
     </row>
-    <row r="41" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A41" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="B41" s="42">
+        <v>116</v>
+      </c>
+      <c r="B41" s="40">
         <v>34697.703999999998</v>
       </c>
-      <c r="C41" s="42"/>
-      <c r="D41" s="42"/>
-      <c r="E41" s="42"/>
-      <c r="F41" s="42"/>
+      <c r="C41" s="40"/>
+      <c r="D41" s="40"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
       <c r="G41" s="27"/>
-      <c r="H41" s="42">
+      <c r="H41" s="40">
         <v>43730.449000000001</v>
       </c>
-      <c r="I41" s="42"/>
-      <c r="J41" s="42"/>
-      <c r="K41" s="42"/>
-      <c r="L41" s="42"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
       <c r="M41" s="27"/>
-      <c r="N41" s="42">
+      <c r="N41" s="40">
         <v>55075.362999999998</v>
       </c>
-      <c r="O41" s="42"/>
-      <c r="P41" s="42"/>
-      <c r="Q41" s="42"/>
-      <c r="R41" s="42"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="40"/>
       <c r="S41" s="15"/>
-      <c r="T41" s="42">
+      <c r="T41" s="40">
         <v>37782.404000000002</v>
       </c>
-      <c r="U41" s="42"/>
-      <c r="V41" s="42"/>
-      <c r="W41" s="42"/>
-      <c r="X41" s="42"/>
+      <c r="U41" s="40"/>
+      <c r="V41" s="40"/>
+      <c r="W41" s="40"/>
+      <c r="X41" s="40"/>
       <c r="Y41" s="27"/>
-      <c r="Z41" s="42">
+      <c r="Z41" s="40">
         <v>47698.324999999997</v>
       </c>
-      <c r="AA41" s="42"/>
-      <c r="AB41" s="42"/>
-      <c r="AC41" s="42"/>
-      <c r="AD41" s="42"/>
+      <c r="AA41" s="40"/>
+      <c r="AB41" s="40"/>
+      <c r="AC41" s="40"/>
+      <c r="AD41" s="40"/>
       <c r="AE41" s="27"/>
-      <c r="AF41" s="42">
+      <c r="AF41" s="40">
         <v>60402.93</v>
       </c>
-      <c r="AG41" s="42"/>
-      <c r="AH41" s="42"/>
-      <c r="AI41" s="42"/>
-      <c r="AJ41" s="42"/>
+      <c r="AG41" s="40"/>
+      <c r="AH41" s="40"/>
+      <c r="AI41" s="40"/>
+      <c r="AJ41" s="40"/>
       <c r="AK41" s="16"/>
       <c r="AL41" s="16"/>
       <c r="AM41" s="16"/>
@@ -8311,95 +8336,95 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57A86273-0E84-8246-B3ED-A023C6721217}">
-  <dimension ref="A1:L38"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.125" style="35" customWidth="1"/>
-    <col min="3" max="3" width="4.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5" style="32" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.1640625" style="35" customWidth="1"/>
+    <col min="3" max="3" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5" style="45" customWidth="1"/>
     <col min="7" max="7" width="11" style="1"/>
-    <col min="8" max="8" width="6.125" style="35" customWidth="1"/>
-    <col min="9" max="9" width="4.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.1640625" style="35" customWidth="1"/>
+    <col min="9" max="9" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.5" style="32" customWidth="1"/>
     <col min="13" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
       <c r="B2" s="43"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
       <c r="F2" s="44"/>
       <c r="H2" s="43"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
       <c r="L2" s="44"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="15"/>
       <c r="B3" s="43" t="s">
-        <v>143</v>
-      </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
+        <v>142</v>
+      </c>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
       <c r="F3" s="44"/>
       <c r="H3" s="43" t="s">
-        <v>142</v>
-      </c>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
+        <v>141</v>
+      </c>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
       <c r="L3" s="44"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="16"/>
       <c r="B4" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="D4" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="31" t="s">
-        <v>92</v>
-      </c>
       <c r="E4" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="F4" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="F4" s="31" t="s">
-        <v>135</v>
-      </c>
       <c r="H4" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="I4" s="31" t="s">
+      <c r="J4" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="31" t="s">
-        <v>92</v>
-      </c>
       <c r="K4" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="L4" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="L4" s="31" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5" s="16"/>
       <c r="H5" s="36"/>
@@ -8407,12 +8432,12 @@
       <c r="J5" s="16"/>
       <c r="K5" s="16"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C6" s="16">
         <v>0.17599999999999999</v>
@@ -8420,15 +8445,20 @@
       <c r="D6" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="16"/>
+      <c r="E6" s="16">
+        <v>11.912000000000001</v>
+      </c>
+      <c r="F6" s="45">
+        <v>12.709</v>
+      </c>
       <c r="H6" s="36"/>
       <c r="I6" s="16"/>
       <c r="J6" s="18"/>
       <c r="K6" s="16"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B7" s="36">
         <v>-9.1010000000000009</v>
@@ -8439,15 +8469,20 @@
       <c r="D7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="16"/>
+      <c r="E7" s="16">
+        <v>-10.558</v>
+      </c>
+      <c r="F7" s="45">
+        <v>-7.6449999999999996</v>
+      </c>
       <c r="H7" s="36"/>
       <c r="I7" s="16"/>
       <c r="J7" s="18"/>
       <c r="K7" s="16"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B8" s="36"/>
       <c r="C8" s="16"/>
@@ -8458,9 +8493,9 @@
       <c r="J8" s="16"/>
       <c r="K8" s="16"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B9" s="36">
         <v>-0.28799999999999998</v>
@@ -8477,9 +8512,9 @@
       <c r="J9" s="18"/>
       <c r="K9" s="16"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B10" s="36">
         <v>5.2999999999999999E-2</v>
@@ -8496,9 +8531,9 @@
       <c r="J10" s="18"/>
       <c r="K10" s="16"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B11" s="36">
         <v>0.124</v>
@@ -8515,9 +8550,9 @@
       <c r="J11" s="18"/>
       <c r="K11" s="16"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="B12" s="37">
         <v>-3.2000000000000001E-2</v>
@@ -8534,22 +8569,28 @@
       <c r="J12" s="18"/>
       <c r="K12" s="16"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="B13" s="36"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="18"/>
+        <v>147</v>
+      </c>
+      <c r="B13" s="36">
+        <v>0.24099999999999999</v>
+      </c>
+      <c r="C13" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>24</v>
+      </c>
       <c r="E13" s="16"/>
       <c r="H13" s="36"/>
       <c r="I13" s="16"/>
       <c r="J13" s="18"/>
       <c r="K13" s="16"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B14" s="36"/>
       <c r="C14" s="16"/>
@@ -8560,12 +8601,16 @@
       <c r="J14" s="16"/>
       <c r="K14" s="16"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="16"/>
+        <v>100</v>
+      </c>
+      <c r="B15" s="36">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="C15" s="16">
+        <v>4.1000000000000002E-2</v>
+      </c>
       <c r="D15" s="18" t="s">
         <v>24</v>
       </c>
@@ -8575,38 +8620,54 @@
       <c r="J15" s="18"/>
       <c r="K15" s="16"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="B16" s="36"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="18"/>
+        <v>101</v>
+      </c>
+      <c r="B16" s="36">
+        <v>-0.14499999999999999</v>
+      </c>
+      <c r="C16" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>24</v>
+      </c>
       <c r="E16" s="16"/>
       <c r="H16" s="36"/>
       <c r="I16" s="16"/>
       <c r="J16" s="18"/>
       <c r="K16" s="16"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="B17" s="36"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="18"/>
+        <v>102</v>
+      </c>
+      <c r="B17" s="36">
+        <v>-2.1999999999999999E-2</v>
+      </c>
+      <c r="C17" s="16">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D17" s="18">
+        <v>0.56699999999999995</v>
+      </c>
       <c r="E17" s="16"/>
       <c r="H17" s="36"/>
       <c r="I17" s="16"/>
       <c r="J17" s="18"/>
       <c r="K17" s="16"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="B18" s="36"/>
-      <c r="C18" s="16"/>
+        <v>105</v>
+      </c>
+      <c r="B18" s="36">
+        <v>-0.14399999999999999</v>
+      </c>
+      <c r="C18" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
       <c r="D18" s="18" t="s">
         <v>24</v>
       </c>
@@ -8616,12 +8677,16 @@
       <c r="J18" s="18"/>
       <c r="K18" s="16"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="B19" s="36"/>
-      <c r="C19" s="16"/>
+        <v>106</v>
+      </c>
+      <c r="B19" s="36">
+        <v>-0.16600000000000001</v>
+      </c>
+      <c r="C19" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
       <c r="D19" s="18" t="s">
         <v>24</v>
       </c>
@@ -8631,40 +8696,56 @@
       <c r="J19" s="18"/>
       <c r="K19" s="16"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="B20" s="36"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="18"/>
+        <v>103</v>
+      </c>
+      <c r="B20" s="36">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="C20" s="16">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>24</v>
+      </c>
       <c r="E20" s="16"/>
       <c r="H20" s="36"/>
       <c r="I20" s="16"/>
       <c r="J20" s="18"/>
       <c r="K20" s="16"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="B21" s="36"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="18"/>
+        <v>104</v>
+      </c>
+      <c r="B21" s="36">
+        <v>1E-3</v>
+      </c>
+      <c r="C21" s="16">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="D21" s="18">
+        <v>0.98199999999999998</v>
+      </c>
       <c r="E21" s="16"/>
       <c r="H21" s="36"/>
       <c r="I21" s="16"/>
       <c r="J21" s="18"/>
       <c r="K21" s="16"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="B22" s="36"/>
-      <c r="C22" s="16"/>
+        <v>108</v>
+      </c>
+      <c r="B22" s="36">
+        <v>1.6E-2</v>
+      </c>
+      <c r="C22" s="16">
+        <v>2.5000000000000001E-2</v>
+      </c>
       <c r="D22" s="18">
-        <v>0.51400000000000001</v>
+        <v>0.51500000000000001</v>
       </c>
       <c r="E22" s="16"/>
       <c r="H22" s="36"/>
@@ -8672,12 +8753,16 @@
       <c r="J22" s="18"/>
       <c r="K22" s="16"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B23" s="36"/>
-      <c r="C23" s="16"/>
+        <v>107</v>
+      </c>
+      <c r="B23" s="36">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="C23" s="16">
+        <v>2.3E-2</v>
+      </c>
       <c r="D23" s="18">
         <v>4.0000000000000001E-3</v>
       </c>
@@ -8687,20 +8772,26 @@
       <c r="J23" s="18"/>
       <c r="K23" s="16"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B24" s="36"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="18"/>
+        <v>109</v>
+      </c>
+      <c r="B24" s="36">
+        <v>-0.12</v>
+      </c>
+      <c r="C24" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>24</v>
+      </c>
       <c r="E24" s="16"/>
       <c r="H24" s="36"/>
       <c r="I24" s="16"/>
       <c r="J24" s="18"/>
       <c r="K24" s="16"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="17" t="s">
         <v>82</v>
       </c>
@@ -8713,12 +8804,16 @@
       <c r="J25" s="16"/>
       <c r="K25" s="16"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B26" s="36"/>
-      <c r="C26" s="16"/>
+        <v>83</v>
+      </c>
+      <c r="B26" s="36">
+        <v>12.734</v>
+      </c>
+      <c r="C26" s="16">
+        <v>0.17599999999999999</v>
+      </c>
       <c r="D26" s="18" t="s">
         <v>24</v>
       </c>
@@ -8728,12 +8823,16 @@
       <c r="J26" s="18"/>
       <c r="K26" s="16"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B27" s="36"/>
-      <c r="C27" s="16"/>
+        <v>88</v>
+      </c>
+      <c r="B27" s="36">
+        <v>4.5759999999999996</v>
+      </c>
+      <c r="C27" s="16">
+        <v>7.2999999999999995E-2</v>
+      </c>
       <c r="D27" s="18" t="s">
         <v>24</v>
       </c>
@@ -8743,12 +8842,16 @@
       <c r="J27" s="18"/>
       <c r="K27" s="16"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B28" s="36"/>
-      <c r="C28" s="16"/>
+        <v>92</v>
+      </c>
+      <c r="B28" s="36">
+        <v>1.012</v>
+      </c>
+      <c r="C28" s="16">
+        <v>1.7999999999999999E-2</v>
+      </c>
       <c r="D28" s="18" t="s">
         <v>24</v>
       </c>
@@ -8758,147 +8861,56 @@
       <c r="J28" s="18"/>
       <c r="K28" s="16"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="B29" s="36"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="18"/>
+        <v>110</v>
+      </c>
+      <c r="B29" s="36">
+        <v>4.0510000000000002</v>
+      </c>
+      <c r="C29" s="16">
+        <v>0.45200000000000001</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>24</v>
+      </c>
       <c r="E29" s="16"/>
       <c r="H29" s="36"/>
       <c r="I29" s="16"/>
       <c r="J29" s="18"/>
       <c r="K29" s="16"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="B30" s="36"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-      <c r="K30" s="16"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B31" s="36"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="16"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="18"/>
-      <c r="K31" s="16"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B32" s="36"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="16"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="18"/>
-      <c r="K32" s="16"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B33" s="36"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="16"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="18"/>
-      <c r="K33" s="16"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B34" s="36"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="16"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="16"/>
-      <c r="J34" s="18"/>
-      <c r="K34" s="16"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B35" s="36"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="16"/>
-      <c r="H35" s="36"/>
-      <c r="I35" s="16"/>
-      <c r="J35" s="18"/>
-      <c r="K35" s="16"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="B36" s="36"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="18"/>
-      <c r="H36" s="36"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="18"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="20" t="s">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A30" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" s="38"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="33"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A31" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B37" s="38"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="38"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="33"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="B38" s="39"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="39"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="15"/>
-      <c r="L38" s="34"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="39"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -8914,64 +8926,64 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{540507A6-720C-0B43-804E-087FEE710926}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.875" customWidth="1"/>
-    <col min="2" max="2" width="18.875" customWidth="1"/>
-    <col min="3" max="3" width="19.125" customWidth="1"/>
+    <col min="1" max="1" width="19.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="23" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="24"/>
+    </row>
+    <row r="3" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="24" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="24" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="24"/>
+    </row>
+    <row r="6" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="24"/>
+    </row>
+    <row r="7" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="23" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24"/>
-    </row>
-    <row r="3" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
-    </row>
-    <row r="6" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-    </row>
-    <row r="7" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="23" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="24" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="24" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B11" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
         <v>124</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>125</v>
       </c>
       <c r="B12">
         <v>-3.4000000000000002E-2</v>
@@ -8980,9 +8992,9 @@
         <v>-1.4E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B13">
         <v>-2.4E-2</v>
@@ -8991,9 +9003,9 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B14">
         <v>-2.3E-2</v>
@@ -9002,9 +9014,9 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B15">
         <v>-2.5999999999999999E-2</v>
@@ -9013,27 +9025,27 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="23" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="24" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B19" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="C19" s="23" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B20">
         <v>-3.1E-2</v>
@@ -9042,9 +9054,9 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B21">
         <v>-0.03</v>
@@ -9053,9 +9065,9 @@
         <v>-1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B22">
         <v>-0.113</v>
@@ -9064,9 +9076,9 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B23">
         <v>-3.3000000000000002E-2</v>
@@ -9075,9 +9087,9 @@
         <v>-1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E25" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmoffice-my.sharepoint.com/personal/abrieant_uvm_edu/Documents/OneDrive/Manuscripts/reg report DCN/pubertybrain/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nchaku\Documents\GitHub\pubertybrain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{1F29979F-BB53-4166-B9B9-F89018F0CDEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51867643-3C5E-D94F-AF10-4EE9E35910E6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69659088-394A-467C-AD8B-B0810D623CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="500" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptive table" sheetId="1" r:id="rId1"/>
@@ -1176,14 +1176,15 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1191,7 +1192,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1772,20 +1772,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39987BE7-3659-524A-81AE-D479F97EF698}">
   <dimension ref="A1:F29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="9"/>
       <c r="B2" s="10" t="s">
         <v>63</v>
@@ -1803,7 +1803,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="11" t="s">
         <v>69</v>
@@ -1817,7 +1817,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>60</v>
       </c>
@@ -1827,7 +1827,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>61</v>
       </c>
@@ -1847,7 +1847,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>62</v>
       </c>
@@ -1867,7 +1867,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>58</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>59</v>
       </c>
@@ -1897,7 +1897,7 @@
       <c r="E8" s="12"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>61</v>
       </c>
@@ -1917,7 +1917,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>66</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>67</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>62</v>
       </c>
@@ -1977,7 +1977,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>68</v>
       </c>
@@ -1987,7 +1987,7 @@
       <c r="E13" s="12"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>73</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>74</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>75</v>
       </c>
@@ -2047,7 +2047,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>76</v>
       </c>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="F17" s="19"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>71</v>
       </c>
@@ -2075,7 +2075,7 @@
       <c r="E18" s="12"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>61</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>66</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>67</v>
       </c>
@@ -2135,7 +2135,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>62</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>72</v>
       </c>
@@ -2165,7 +2165,7 @@
       <c r="E23" s="12"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>61</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>66</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>67</v>
       </c>
@@ -2225,7 +2225,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>62</v>
       </c>
@@ -2245,7 +2245,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2253,7 +2253,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2269,9 +2269,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A749072B-F938-0F49-BE23-243603B2B3D0}">
   <dimension ref="M2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="13:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M2" t="s">
         <v>111</v>
       </c>
@@ -2285,7 +2285,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45875D41-9C56-AA4E-A18A-2D3A4CE169B3}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2295,7 +2295,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A5153E-6E5C-054A-8ACA-5118463B96C5}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2305,51 +2305,51 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA86F85-A8D4-F648-84C3-730F1A42C846}">
   <dimension ref="A1:AM34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.1640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="1.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.625" style="1" customWidth="1"/>
     <col min="11" max="11" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="1.1640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="1.125" style="1" customWidth="1"/>
     <col min="14" max="14" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.6640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.625" style="1" customWidth="1"/>
     <col min="17" max="17" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="0.83203125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="0.875" style="1" customWidth="1"/>
     <col min="20" max="20" width="8.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="5.6640625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="5.625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="6.125" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="1" style="1" customWidth="1"/>
     <col min="26" max="26" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.6640625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.625" style="1" customWidth="1"/>
     <col min="29" max="30" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="1.1640625" style="1" customWidth="1"/>
+    <col min="31" max="31" width="1.125" style="1" customWidth="1"/>
     <col min="32" max="32" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="5.6640625" style="1" customWidth="1"/>
-    <col min="36" max="36" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="5.625" style="1" customWidth="1"/>
+    <col min="36" max="36" width="6.125" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
       <c r="B2" s="41" t="s">
         <v>112</v>
@@ -2391,7 +2391,7 @@
       <c r="AI2" s="41"/>
       <c r="AJ2" s="41"/>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="16"/>
       <c r="B3" s="41" t="s">
         <v>79</v>
@@ -2440,7 +2440,7 @@
       <c r="AI3" s="41"/>
       <c r="AJ3" s="41"/>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="15"/>
       <c r="B4" s="29" t="s">
         <v>89</v>
@@ -2538,7 +2538,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>84</v>
       </c>
@@ -2577,7 +2577,7 @@
       <c r="AI5" s="16"/>
       <c r="AJ5" s="16"/>
     </row>
-    <row r="6" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>94</v>
       </c>
@@ -2676,7 +2676,7 @@
         <v>12.236000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>95</v>
       </c>
@@ -2775,7 +2775,7 @@
         <v>-7.7560000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -2812,7 +2812,7 @@
       <c r="AI8" s="18"/>
       <c r="AJ8" s="16"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>85</v>
       </c>
@@ -2851,7 +2851,7 @@
       <c r="AI9" s="16"/>
       <c r="AJ9" s="16"/>
     </row>
-    <row r="10" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>96</v>
       </c>
@@ -2950,7 +2950,7 @@
         <v>-0.24</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>97</v>
       </c>
@@ -3049,7 +3049,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>98</v>
       </c>
@@ -3148,7 +3148,7 @@
         <v>0.14899999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>99</v>
       </c>
@@ -3247,7 +3247,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>87</v>
       </c>
@@ -3346,7 +3346,7 @@
         <v>0.28799999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="16"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -3383,7 +3383,7 @@
       <c r="AI15" s="18"/>
       <c r="AJ15" s="16"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>86</v>
       </c>
@@ -3422,7 +3422,7 @@
       <c r="AI16" s="16"/>
       <c r="AJ16" s="16"/>
     </row>
-    <row r="17" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>100</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>0.443</v>
       </c>
     </row>
-    <row r="18" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>101</v>
       </c>
@@ -3620,7 +3620,7 @@
         <v>-0.10299999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>102</v>
       </c>
@@ -3719,7 +3719,7 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>105</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>106</v>
       </c>
@@ -3917,7 +3917,7 @@
         <v>-0.13600000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>103</v>
       </c>
@@ -4014,7 +4014,7 @@
         <v>0.156</v>
       </c>
     </row>
-    <row r="23" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>104</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>-1.6E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>108</v>
       </c>
@@ -4208,7 +4208,7 @@
         <v>0.112</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>107</v>
       </c>
@@ -4305,7 +4305,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>109</v>
       </c>
@@ -4402,7 +4402,7 @@
         <v>-4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -4439,7 +4439,7 @@
       <c r="AI27" s="18"/>
       <c r="AJ27" s="16"/>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>82</v>
       </c>
@@ -4478,7 +4478,7 @@
       <c r="AI28" s="16"/>
       <c r="AJ28" s="16"/>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>83</v>
       </c>
@@ -4577,7 +4577,7 @@
         <v>14.164999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
         <v>88</v>
       </c>
@@ -4676,7 +4676,7 @@
         <v>4.1660000000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>92</v>
       </c>
@@ -4775,7 +4775,7 @@
         <v>1.0549999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
         <v>110</v>
       </c>
@@ -4872,7 +4872,7 @@
         <v>4.202</v>
       </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
         <v>115</v>
       </c>
@@ -4915,63 +4915,69 @@
       <c r="AL33" s="16"/>
       <c r="AM33" s="16"/>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B34" s="40">
+      <c r="B34" s="43">
         <v>74058.118000000002</v>
       </c>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
       <c r="G34" s="27"/>
-      <c r="H34" s="40">
+      <c r="H34" s="43">
         <v>83016.937999999995</v>
       </c>
-      <c r="I34" s="40"/>
-      <c r="J34" s="40"/>
-      <c r="K34" s="40"/>
-      <c r="L34" s="40"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="43"/>
+      <c r="L34" s="43"/>
       <c r="M34" s="27"/>
-      <c r="N34" s="40">
+      <c r="N34" s="43">
         <v>94345.274999999994</v>
       </c>
-      <c r="O34" s="40"/>
-      <c r="P34" s="40"/>
-      <c r="Q34" s="40"/>
-      <c r="R34" s="40"/>
+      <c r="O34" s="43"/>
+      <c r="P34" s="43"/>
+      <c r="Q34" s="43"/>
+      <c r="R34" s="43"/>
       <c r="S34" s="15"/>
-      <c r="T34" s="40">
+      <c r="T34" s="43">
         <v>83167.763000000006</v>
       </c>
-      <c r="U34" s="40"/>
-      <c r="V34" s="40"/>
-      <c r="W34" s="40"/>
-      <c r="X34" s="40"/>
+      <c r="U34" s="43"/>
+      <c r="V34" s="43"/>
+      <c r="W34" s="43"/>
+      <c r="X34" s="43"/>
       <c r="Y34" s="27"/>
-      <c r="Z34" s="40">
+      <c r="Z34" s="43">
         <v>93083.505999999994</v>
       </c>
-      <c r="AA34" s="40"/>
-      <c r="AB34" s="40"/>
-      <c r="AC34" s="40"/>
-      <c r="AD34" s="40"/>
+      <c r="AA34" s="43"/>
+      <c r="AB34" s="43"/>
+      <c r="AC34" s="43"/>
+      <c r="AD34" s="43"/>
       <c r="AE34" s="27"/>
-      <c r="AF34" s="40">
+      <c r="AF34" s="43">
         <v>105770.462</v>
       </c>
-      <c r="AG34" s="40"/>
-      <c r="AH34" s="40"/>
-      <c r="AI34" s="40"/>
-      <c r="AJ34" s="40"/>
+      <c r="AG34" s="43"/>
+      <c r="AH34" s="43"/>
+      <c r="AI34" s="43"/>
+      <c r="AJ34" s="43"/>
       <c r="AK34" s="16"/>
       <c r="AL34" s="16"/>
       <c r="AM34" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="AF34:AJ34"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="H34:L34"/>
+    <mergeCell ref="T34:X34"/>
+    <mergeCell ref="N34:R34"/>
+    <mergeCell ref="Z34:AD34"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="H3:L3"/>
@@ -4980,12 +4986,6 @@
     <mergeCell ref="T3:X3"/>
     <mergeCell ref="Z3:AD3"/>
     <mergeCell ref="AF3:AJ3"/>
-    <mergeCell ref="AF34:AJ34"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="H34:L34"/>
-    <mergeCell ref="T34:X34"/>
-    <mergeCell ref="N34:R34"/>
-    <mergeCell ref="Z34:AD34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -4995,49 +4995,49 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CD5CF7F-81D6-D24D-8228-B4C578C35D65}">
   <dimension ref="A1:AM41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.625" style="1" customWidth="1"/>
     <col min="5" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.1640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="1.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.625" style="1" customWidth="1"/>
     <col min="11" max="12" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="1.1640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="1.125" style="1" customWidth="1"/>
     <col min="14" max="14" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.6640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.625" style="1" customWidth="1"/>
     <col min="17" max="17" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="0.83203125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="0.875" style="1" customWidth="1"/>
     <col min="20" max="20" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.6640625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="5.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.625" style="1" customWidth="1"/>
     <col min="24" max="24" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="1" style="1" customWidth="1"/>
     <col min="26" max="26" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.625" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="30" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="1.1640625" style="1" customWidth="1"/>
+    <col min="31" max="31" width="1.125" style="1" customWidth="1"/>
     <col min="32" max="32" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="5.6640625" style="1" customWidth="1"/>
+    <col min="33" max="33" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.625" style="1" customWidth="1"/>
     <col min="35" max="36" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
       <c r="B2" s="41" t="s">
         <v>112</v>
@@ -5079,7 +5079,7 @@
       <c r="AI2" s="41"/>
       <c r="AJ2" s="41"/>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="16"/>
       <c r="B3" s="41" t="s">
         <v>79</v>
@@ -5128,7 +5128,7 @@
       <c r="AI3" s="41"/>
       <c r="AJ3" s="41"/>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="15"/>
       <c r="B4" s="29" t="s">
         <v>89</v>
@@ -5226,7 +5226,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>84</v>
       </c>
@@ -5265,7 +5265,7 @@
       <c r="AI5" s="16"/>
       <c r="AJ5" s="16"/>
     </row>
-    <row r="6" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>94</v>
       </c>
@@ -5364,7 +5364,7 @@
         <v>13.875999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>95</v>
       </c>
@@ -5463,7 +5463,7 @@
         <v>2.1219999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>138</v>
       </c>
@@ -5562,7 +5562,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="16"/>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
@@ -5599,7 +5599,7 @@
       <c r="AI9" s="18"/>
       <c r="AJ9" s="16"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>85</v>
       </c>
@@ -5638,7 +5638,7 @@
       <c r="AI10" s="16"/>
       <c r="AJ10" s="16"/>
     </row>
-    <row r="11" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>96</v>
       </c>
@@ -5737,7 +5737,7 @@
         <v>0.40300000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>137</v>
       </c>
@@ -5836,7 +5836,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>97</v>
       </c>
@@ -5935,7 +5935,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>98</v>
       </c>
@@ -6034,7 +6034,7 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>139</v>
       </c>
@@ -6133,7 +6133,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="16" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>99</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v>0.22900000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>140</v>
       </c>
@@ -6331,7 +6331,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>87</v>
       </c>
@@ -6430,7 +6430,7 @@
         <v>0.28799999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="16"/>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -6467,7 +6467,7 @@
       <c r="AI19" s="18"/>
       <c r="AJ19" s="16"/>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>86</v>
       </c>
@@ -6506,7 +6506,7 @@
       <c r="AI20" s="16"/>
       <c r="AJ20" s="16"/>
     </row>
-    <row r="21" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>100</v>
       </c>
@@ -6605,7 +6605,7 @@
         <v>0.14499999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>136</v>
       </c>
@@ -6704,7 +6704,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>101</v>
       </c>
@@ -6803,7 +6803,7 @@
         <v>-9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>102</v>
       </c>
@@ -6902,7 +6902,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>144</v>
       </c>
@@ -6982,7 +6982,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>105</v>
       </c>
@@ -7081,7 +7081,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
         <v>106</v>
       </c>
@@ -7180,7 +7180,7 @@
         <v>-0.13600000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
         <v>103</v>
       </c>
@@ -7277,7 +7277,7 @@
         <v>0.17199999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>104</v>
       </c>
@@ -7374,7 +7374,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
         <v>145</v>
       </c>
@@ -7453,7 +7453,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>108</v>
       </c>
@@ -7550,7 +7550,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
         <v>107</v>
       </c>
@@ -7647,7 +7647,7 @@
         <v>0.17499999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
         <v>109</v>
       </c>
@@ -7744,7 +7744,7 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A34" s="16"/>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
@@ -7781,7 +7781,7 @@
       <c r="AI34" s="18"/>
       <c r="AJ34" s="16"/>
     </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
         <v>82</v>
       </c>
@@ -7820,7 +7820,7 @@
       <c r="AI35" s="16"/>
       <c r="AJ35" s="16"/>
     </row>
-    <row r="36" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
         <v>83</v>
       </c>
@@ -7919,7 +7919,7 @@
         <v>14.162000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
         <v>88</v>
       </c>
@@ -8018,7 +8018,7 @@
         <v>4.1660000000000004</v>
       </c>
     </row>
-    <row r="38" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
         <v>92</v>
       </c>
@@ -8117,7 +8117,7 @@
         <v>1.0549999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
         <v>110</v>
       </c>
@@ -8214,7 +8214,7 @@
         <v>4.5090000000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A40" s="20" t="s">
         <v>115</v>
       </c>
@@ -8257,57 +8257,57 @@
       <c r="AL40" s="16"/>
       <c r="AM40" s="16"/>
     </row>
-    <row r="41" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B41" s="40">
+      <c r="B41" s="43">
         <v>34697.703999999998</v>
       </c>
-      <c r="C41" s="40"/>
-      <c r="D41" s="40"/>
-      <c r="E41" s="40"/>
-      <c r="F41" s="40"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="43"/>
       <c r="G41" s="27"/>
-      <c r="H41" s="40">
+      <c r="H41" s="43">
         <v>43730.449000000001</v>
       </c>
-      <c r="I41" s="40"/>
-      <c r="J41" s="40"/>
-      <c r="K41" s="40"/>
-      <c r="L41" s="40"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
+      <c r="L41" s="43"/>
       <c r="M41" s="27"/>
-      <c r="N41" s="40">
+      <c r="N41" s="43">
         <v>55075.362999999998</v>
       </c>
-      <c r="O41" s="40"/>
-      <c r="P41" s="40"/>
-      <c r="Q41" s="40"/>
-      <c r="R41" s="40"/>
+      <c r="O41" s="43"/>
+      <c r="P41" s="43"/>
+      <c r="Q41" s="43"/>
+      <c r="R41" s="43"/>
       <c r="S41" s="15"/>
-      <c r="T41" s="40">
+      <c r="T41" s="43">
         <v>37782.404000000002</v>
       </c>
-      <c r="U41" s="40"/>
-      <c r="V41" s="40"/>
-      <c r="W41" s="40"/>
-      <c r="X41" s="40"/>
+      <c r="U41" s="43"/>
+      <c r="V41" s="43"/>
+      <c r="W41" s="43"/>
+      <c r="X41" s="43"/>
       <c r="Y41" s="27"/>
-      <c r="Z41" s="40">
+      <c r="Z41" s="43">
         <v>47698.324999999997</v>
       </c>
-      <c r="AA41" s="40"/>
-      <c r="AB41" s="40"/>
-      <c r="AC41" s="40"/>
-      <c r="AD41" s="40"/>
+      <c r="AA41" s="43"/>
+      <c r="AB41" s="43"/>
+      <c r="AC41" s="43"/>
+      <c r="AD41" s="43"/>
       <c r="AE41" s="27"/>
-      <c r="AF41" s="40">
+      <c r="AF41" s="43">
         <v>60402.93</v>
       </c>
-      <c r="AG41" s="40"/>
-      <c r="AH41" s="40"/>
-      <c r="AI41" s="40"/>
-      <c r="AJ41" s="40"/>
+      <c r="AG41" s="43"/>
+      <c r="AH41" s="43"/>
+      <c r="AI41" s="43"/>
+      <c r="AJ41" s="43"/>
       <c r="AK41" s="16"/>
       <c r="AL41" s="16"/>
       <c r="AM41" s="16"/>
@@ -8337,59 +8337,59 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57A86273-0E84-8246-B3ED-A023C6721217}">
   <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.1640625" style="35" customWidth="1"/>
-    <col min="3" max="3" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5" style="45" customWidth="1"/>
+    <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.125" style="35" customWidth="1"/>
+    <col min="3" max="3" width="4.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5" style="40" customWidth="1"/>
     <col min="7" max="7" width="11" style="1"/>
-    <col min="8" max="8" width="6.1640625" style="35" customWidth="1"/>
-    <col min="9" max="9" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.125" style="35" customWidth="1"/>
+    <col min="9" max="9" width="4.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.5" style="32" customWidth="1"/>
     <col min="13" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
-      <c r="B2" s="43"/>
+      <c r="B2" s="44"/>
       <c r="C2" s="41"/>
       <c r="D2" s="41"/>
       <c r="E2" s="41"/>
-      <c r="F2" s="44"/>
-      <c r="H2" s="43"/>
+      <c r="F2" s="45"/>
+      <c r="H2" s="44"/>
       <c r="I2" s="41"/>
       <c r="J2" s="41"/>
       <c r="K2" s="41"/>
-      <c r="L2" s="44"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L2" s="45"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="15"/>
-      <c r="B3" s="43" t="s">
+      <c r="B3" s="44" t="s">
         <v>142</v>
       </c>
       <c r="C3" s="41"/>
       <c r="D3" s="41"/>
       <c r="E3" s="41"/>
-      <c r="F3" s="44"/>
-      <c r="H3" s="43" t="s">
+      <c r="F3" s="45"/>
+      <c r="H3" s="44" t="s">
         <v>141</v>
       </c>
       <c r="I3" s="41"/>
       <c r="J3" s="41"/>
       <c r="K3" s="41"/>
-      <c r="L3" s="44"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L3" s="45"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="16"/>
       <c r="B4" s="31" t="s">
         <v>89</v>
@@ -8422,7 +8422,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>84</v>
       </c>
@@ -8432,7 +8432,7 @@
       <c r="J5" s="16"/>
       <c r="K5" s="16"/>
     </row>
-    <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>94</v>
       </c>
@@ -8448,7 +8448,7 @@
       <c r="E6" s="16">
         <v>11.912000000000001</v>
       </c>
-      <c r="F6" s="45">
+      <c r="F6" s="40">
         <v>12.709</v>
       </c>
       <c r="H6" s="36"/>
@@ -8456,7 +8456,7 @@
       <c r="J6" s="18"/>
       <c r="K6" s="16"/>
     </row>
-    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>95</v>
       </c>
@@ -8472,7 +8472,7 @@
       <c r="E7" s="16">
         <v>-10.558</v>
       </c>
-      <c r="F7" s="45">
+      <c r="F7" s="40">
         <v>-7.6449999999999996</v>
       </c>
       <c r="H7" s="36"/>
@@ -8480,7 +8480,7 @@
       <c r="J7" s="18"/>
       <c r="K7" s="16"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>85</v>
       </c>
@@ -8493,7 +8493,7 @@
       <c r="J8" s="16"/>
       <c r="K8" s="16"/>
     </row>
-    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>96</v>
       </c>
@@ -8512,7 +8512,7 @@
       <c r="J9" s="18"/>
       <c r="K9" s="16"/>
     </row>
-    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>97</v>
       </c>
@@ -8531,7 +8531,7 @@
       <c r="J10" s="18"/>
       <c r="K10" s="16"/>
     </row>
-    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>98</v>
       </c>
@@ -8550,7 +8550,7 @@
       <c r="J11" s="18"/>
       <c r="K11" s="16"/>
     </row>
-    <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>146</v>
       </c>
@@ -8569,7 +8569,7 @@
       <c r="J12" s="18"/>
       <c r="K12" s="16"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>147</v>
       </c>
@@ -8588,7 +8588,7 @@
       <c r="J13" s="18"/>
       <c r="K13" s="16"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>86</v>
       </c>
@@ -8601,7 +8601,7 @@
       <c r="J14" s="16"/>
       <c r="K14" s="16"/>
     </row>
-    <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>100</v>
       </c>
@@ -8620,7 +8620,7 @@
       <c r="J15" s="18"/>
       <c r="K15" s="16"/>
     </row>
-    <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>101</v>
       </c>
@@ -8639,7 +8639,7 @@
       <c r="J16" s="18"/>
       <c r="K16" s="16"/>
     </row>
-    <row r="17" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>102</v>
       </c>
@@ -8658,7 +8658,7 @@
       <c r="J17" s="18"/>
       <c r="K17" s="16"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>105</v>
       </c>
@@ -8677,7 +8677,7 @@
       <c r="J18" s="18"/>
       <c r="K18" s="16"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>106</v>
       </c>
@@ -8696,7 +8696,7 @@
       <c r="J19" s="18"/>
       <c r="K19" s="16"/>
     </row>
-    <row r="20" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>103</v>
       </c>
@@ -8715,7 +8715,7 @@
       <c r="J20" s="18"/>
       <c r="K20" s="16"/>
     </row>
-    <row r="21" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>104</v>
       </c>
@@ -8734,7 +8734,7 @@
       <c r="J21" s="18"/>
       <c r="K21" s="16"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>108</v>
       </c>
@@ -8753,7 +8753,7 @@
       <c r="J22" s="18"/>
       <c r="K22" s="16"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>107</v>
       </c>
@@ -8772,7 +8772,7 @@
       <c r="J23" s="18"/>
       <c r="K23" s="16"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>109</v>
       </c>
@@ -8791,7 +8791,7 @@
       <c r="J24" s="18"/>
       <c r="K24" s="16"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>82</v>
       </c>
@@ -8804,7 +8804,7 @@
       <c r="J25" s="16"/>
       <c r="K25" s="16"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>83</v>
       </c>
@@ -8823,7 +8823,7 @@
       <c r="J26" s="18"/>
       <c r="K26" s="16"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="16" t="s">
         <v>88</v>
       </c>
@@ -8842,7 +8842,7 @@
       <c r="J27" s="18"/>
       <c r="K27" s="16"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
         <v>92</v>
       </c>
@@ -8861,7 +8861,7 @@
       <c r="J28" s="18"/>
       <c r="K28" s="16"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>110</v>
       </c>
@@ -8880,7 +8880,7 @@
       <c r="J29" s="18"/>
       <c r="K29" s="16"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="20" t="s">
         <v>115</v>
       </c>
@@ -8896,7 +8896,7 @@
       <c r="K30" s="14"/>
       <c r="L30" s="33"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
         <v>116</v>
       </c>
@@ -8926,54 +8926,54 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{540507A6-720C-0B43-804E-087FEE710926}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" customWidth="1"/>
+    <col min="1" max="1" width="19.875" customWidth="1"/>
+    <col min="2" max="2" width="18.875" customWidth="1"/>
+    <col min="3" max="3" width="19.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="24"/>
     </row>
-    <row r="3" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="24"/>
     </row>
-    <row r="6" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="24"/>
     </row>
-    <row r="7" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="23" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B11" s="23" t="s">
         <v>127</v>
       </c>
@@ -8981,7 +8981,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>124</v>
       </c>
@@ -8992,7 +8992,7 @@
         <v>-1.4E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>125</v>
       </c>
@@ -9003,7 +9003,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>126</v>
       </c>
@@ -9014,7 +9014,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>131</v>
       </c>
@@ -9025,17 +9025,17 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="23" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B19" s="23" t="s">
         <v>127</v>
       </c>
@@ -9043,7 +9043,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>124</v>
       </c>
@@ -9054,7 +9054,7 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>125</v>
       </c>
@@ -9065,7 +9065,7 @@
         <v>-1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>126</v>
       </c>
@@ -9076,7 +9076,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>131</v>
       </c>
@@ -9087,7 +9087,7 @@
         <v>-1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E25" s="23" t="s">
         <v>130</v>
       </c>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nchaku\Documents\GitHub\pubertybrain\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nchaku/Documents/GitHub/pubertybrain/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69659088-394A-467C-AD8B-B0810D623CC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBDCA32-700C-9942-8973-B738A2BA3D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
+    <workbookView xWindow="1440" yWindow="500" windowWidth="27360" windowHeight="16400" activeTab="7" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptive table" sheetId="1" r:id="rId1"/>
@@ -19,8 +19,9 @@
     <sheet name="Fig2 (Brain)" sheetId="4" r:id="rId4"/>
     <sheet name="CortModels" sheetId="6" r:id="rId5"/>
     <sheet name="SubCortModel" sheetId="10" r:id="rId6"/>
-    <sheet name="Youth report PDS" sheetId="9" r:id="rId7"/>
-    <sheet name="Indirect effects" sheetId="7" r:id="rId8"/>
+    <sheet name="Indirect effects" sheetId="7" r:id="rId7"/>
+    <sheet name="Sex Differences" sheetId="11" r:id="rId8"/>
+    <sheet name="Youth report PDS" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -1177,14 +1178,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1772,20 +1773,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39987BE7-3659-524A-81AE-D479F97EF698}">
   <dimension ref="A1:F29"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="20.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="9"/>
       <c r="B2" s="10" t="s">
         <v>63</v>
@@ -1803,7 +1804,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="6"/>
       <c r="B3" s="11" t="s">
         <v>69</v>
@@ -1817,7 +1818,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>60</v>
       </c>
@@ -1827,7 +1828,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>61</v>
       </c>
@@ -1847,7 +1848,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>62</v>
       </c>
@@ -1867,7 +1868,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>58</v>
       </c>
@@ -1887,7 +1888,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>59</v>
       </c>
@@ -1897,7 +1898,7 @@
       <c r="E8" s="12"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>61</v>
       </c>
@@ -1917,7 +1918,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>66</v>
       </c>
@@ -1937,7 +1938,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>67</v>
       </c>
@@ -1957,7 +1958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>62</v>
       </c>
@@ -1977,7 +1978,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>68</v>
       </c>
@@ -1987,7 +1988,7 @@
       <c r="E13" s="12"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>73</v>
       </c>
@@ -2007,7 +2008,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>74</v>
       </c>
@@ -2027,7 +2028,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>75</v>
       </c>
@@ -2047,7 +2048,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>76</v>
       </c>
@@ -2065,7 +2066,7 @@
       </c>
       <c r="F17" s="19"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>71</v>
       </c>
@@ -2075,7 +2076,7 @@
       <c r="E18" s="12"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>61</v>
       </c>
@@ -2095,7 +2096,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>66</v>
       </c>
@@ -2115,7 +2116,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>67</v>
       </c>
@@ -2135,7 +2136,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>62</v>
       </c>
@@ -2155,7 +2156,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="8" t="s">
         <v>72</v>
       </c>
@@ -2165,7 +2166,7 @@
       <c r="E23" s="12"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>61</v>
       </c>
@@ -2185,7 +2186,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>66</v>
       </c>
@@ -2205,7 +2206,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>67</v>
       </c>
@@ -2225,7 +2226,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="s">
         <v>62</v>
       </c>
@@ -2245,7 +2246,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A28" s="4"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2253,7 +2254,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2269,9 +2270,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A749072B-F938-0F49-BE23-243603B2B3D0}">
   <dimension ref="M2"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="13:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M2" t="s">
         <v>111</v>
       </c>
@@ -2285,7 +2286,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45875D41-9C56-AA4E-A18A-2D3A4CE169B3}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2295,7 +2296,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A5153E-6E5C-054A-8ACA-5118463B96C5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2305,142 +2306,142 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA86F85-A8D4-F648-84C3-730F1A42C846}">
   <dimension ref="A1:AM34"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="1.1640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.6640625" style="1" customWidth="1"/>
     <col min="11" max="11" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="1.125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="1.1640625" style="1" customWidth="1"/>
     <col min="14" max="14" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.6640625" style="1" customWidth="1"/>
     <col min="17" max="17" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="0.875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="0.83203125" style="1" customWidth="1"/>
     <col min="20" max="20" width="8.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="5.625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="6.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="5.6640625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="1" style="1" customWidth="1"/>
     <col min="26" max="26" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.6640625" style="1" customWidth="1"/>
     <col min="29" max="30" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="1.125" style="1" customWidth="1"/>
+    <col min="31" max="31" width="1.1640625" style="1" customWidth="1"/>
     <col min="32" max="32" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="5.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="5.625" style="1" customWidth="1"/>
-    <col min="36" max="36" width="6.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="5.6640625" style="1" customWidth="1"/>
+    <col min="36" max="36" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="42"/>
+      <c r="P2" s="42"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="42"/>
       <c r="S2" s="9"/>
-      <c r="T2" s="41" t="s">
+      <c r="T2" s="42" t="s">
         <v>113</v>
       </c>
-      <c r="U2" s="41"/>
-      <c r="V2" s="41"/>
-      <c r="W2" s="41"/>
-      <c r="X2" s="41"/>
-      <c r="Y2" s="41"/>
-      <c r="Z2" s="41"/>
-      <c r="AA2" s="41"/>
-      <c r="AB2" s="41"/>
-      <c r="AC2" s="41"/>
-      <c r="AD2" s="41"/>
-      <c r="AE2" s="41"/>
-      <c r="AF2" s="41"/>
-      <c r="AG2" s="41"/>
-      <c r="AH2" s="41"/>
-      <c r="AI2" s="41"/>
-      <c r="AJ2" s="41"/>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="U2" s="42"/>
+      <c r="V2" s="42"/>
+      <c r="W2" s="42"/>
+      <c r="X2" s="42"/>
+      <c r="Y2" s="42"/>
+      <c r="Z2" s="42"/>
+      <c r="AA2" s="42"/>
+      <c r="AB2" s="42"/>
+      <c r="AC2" s="42"/>
+      <c r="AD2" s="42"/>
+      <c r="AE2" s="42"/>
+      <c r="AF2" s="42"/>
+      <c r="AG2" s="42"/>
+      <c r="AH2" s="42"/>
+      <c r="AI2" s="42"/>
+      <c r="AJ2" s="42"/>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A3" s="16"/>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
       <c r="G3" s="28"/>
-      <c r="H3" s="41" t="s">
+      <c r="H3" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
       <c r="M3" s="28"/>
-      <c r="N3" s="41" t="s">
+      <c r="N3" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="41"/>
-      <c r="T3" s="42" t="s">
+      <c r="O3" s="42"/>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="42"/>
+      <c r="R3" s="42"/>
+      <c r="T3" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="U3" s="42"/>
-      <c r="V3" s="42"/>
-      <c r="W3" s="42"/>
-      <c r="X3" s="42"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="43"/>
+      <c r="W3" s="43"/>
+      <c r="X3" s="43"/>
       <c r="Y3" s="28"/>
-      <c r="Z3" s="41" t="s">
+      <c r="Z3" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="AA3" s="41"/>
-      <c r="AB3" s="41"/>
-      <c r="AC3" s="41"/>
-      <c r="AD3" s="41"/>
+      <c r="AA3" s="42"/>
+      <c r="AB3" s="42"/>
+      <c r="AC3" s="42"/>
+      <c r="AD3" s="42"/>
       <c r="AE3" s="28"/>
-      <c r="AF3" s="41" t="s">
+      <c r="AF3" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="AG3" s="41"/>
-      <c r="AH3" s="41"/>
-      <c r="AI3" s="41"/>
-      <c r="AJ3" s="41"/>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AG3" s="42"/>
+      <c r="AH3" s="42"/>
+      <c r="AI3" s="42"/>
+      <c r="AJ3" s="42"/>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
       <c r="B4" s="29" t="s">
         <v>89</v>
@@ -2538,7 +2539,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
         <v>84</v>
       </c>
@@ -2577,7 +2578,7 @@
       <c r="AI5" s="16"/>
       <c r="AJ5" s="16"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>94</v>
       </c>
@@ -2676,7 +2677,7 @@
         <v>12.236000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>95</v>
       </c>
@@ -2775,7 +2776,7 @@
         <v>-7.7560000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A8" s="16"/>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -2812,7 +2813,7 @@
       <c r="AI8" s="18"/>
       <c r="AJ8" s="16"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A9" s="17" t="s">
         <v>85</v>
       </c>
@@ -2851,7 +2852,7 @@
       <c r="AI9" s="16"/>
       <c r="AJ9" s="16"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>96</v>
       </c>
@@ -2950,7 +2951,7 @@
         <v>-0.24</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>97</v>
       </c>
@@ -3049,7 +3050,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>98</v>
       </c>
@@ -3148,7 +3149,7 @@
         <v>0.14899999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>99</v>
       </c>
@@ -3247,7 +3248,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A14" s="16" t="s">
         <v>87</v>
       </c>
@@ -3346,7 +3347,7 @@
         <v>0.28799999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A15" s="16"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -3383,7 +3384,7 @@
       <c r="AI15" s="18"/>
       <c r="AJ15" s="16"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
         <v>86</v>
       </c>
@@ -3422,7 +3423,7 @@
       <c r="AI16" s="16"/>
       <c r="AJ16" s="16"/>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>100</v>
       </c>
@@ -3521,7 +3522,7 @@
         <v>0.443</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>101</v>
       </c>
@@ -3620,7 +3621,7 @@
         <v>-0.10299999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>102</v>
       </c>
@@ -3719,7 +3720,7 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
         <v>105</v>
       </c>
@@ -3818,7 +3819,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
         <v>106</v>
       </c>
@@ -3917,7 +3918,7 @@
         <v>-0.13600000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>103</v>
       </c>
@@ -4014,7 +4015,7 @@
         <v>0.156</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>104</v>
       </c>
@@ -4111,7 +4112,7 @@
         <v>-1.6E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
         <v>108</v>
       </c>
@@ -4208,7 +4209,7 @@
         <v>0.112</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A25" s="16" t="s">
         <v>107</v>
       </c>
@@ -4305,7 +4306,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
         <v>109</v>
       </c>
@@ -4402,7 +4403,7 @@
         <v>-4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -4439,7 +4440,7 @@
       <c r="AI27" s="18"/>
       <c r="AJ27" s="16"/>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A28" s="17" t="s">
         <v>82</v>
       </c>
@@ -4478,7 +4479,7 @@
       <c r="AI28" s="16"/>
       <c r="AJ28" s="16"/>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A29" s="16" t="s">
         <v>83</v>
       </c>
@@ -4577,7 +4578,7 @@
         <v>14.164999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A30" s="16" t="s">
         <v>88</v>
       </c>
@@ -4676,7 +4677,7 @@
         <v>4.1660000000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A31" s="16" t="s">
         <v>92</v>
       </c>
@@ -4775,7 +4776,7 @@
         <v>1.0549999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A32" s="16" t="s">
         <v>110</v>
       </c>
@@ -4872,7 +4873,7 @@
         <v>4.202</v>
       </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A33" s="20" t="s">
         <v>115</v>
       </c>
@@ -4915,69 +4916,63 @@
       <c r="AL33" s="16"/>
       <c r="AM33" s="16"/>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B34" s="43">
+      <c r="B34" s="41">
         <v>74058.118000000002</v>
       </c>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
       <c r="G34" s="27"/>
-      <c r="H34" s="43">
+      <c r="H34" s="41">
         <v>83016.937999999995</v>
       </c>
-      <c r="I34" s="43"/>
-      <c r="J34" s="43"/>
-      <c r="K34" s="43"/>
-      <c r="L34" s="43"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="41"/>
+      <c r="K34" s="41"/>
+      <c r="L34" s="41"/>
       <c r="M34" s="27"/>
-      <c r="N34" s="43">
+      <c r="N34" s="41">
         <v>94345.274999999994</v>
       </c>
-      <c r="O34" s="43"/>
-      <c r="P34" s="43"/>
-      <c r="Q34" s="43"/>
-      <c r="R34" s="43"/>
+      <c r="O34" s="41"/>
+      <c r="P34" s="41"/>
+      <c r="Q34" s="41"/>
+      <c r="R34" s="41"/>
       <c r="S34" s="15"/>
-      <c r="T34" s="43">
+      <c r="T34" s="41">
         <v>83167.763000000006</v>
       </c>
-      <c r="U34" s="43"/>
-      <c r="V34" s="43"/>
-      <c r="W34" s="43"/>
-      <c r="X34" s="43"/>
+      <c r="U34" s="41"/>
+      <c r="V34" s="41"/>
+      <c r="W34" s="41"/>
+      <c r="X34" s="41"/>
       <c r="Y34" s="27"/>
-      <c r="Z34" s="43">
+      <c r="Z34" s="41">
         <v>93083.505999999994</v>
       </c>
-      <c r="AA34" s="43"/>
-      <c r="AB34" s="43"/>
-      <c r="AC34" s="43"/>
-      <c r="AD34" s="43"/>
+      <c r="AA34" s="41"/>
+      <c r="AB34" s="41"/>
+      <c r="AC34" s="41"/>
+      <c r="AD34" s="41"/>
       <c r="AE34" s="27"/>
-      <c r="AF34" s="43">
+      <c r="AF34" s="41">
         <v>105770.462</v>
       </c>
-      <c r="AG34" s="43"/>
-      <c r="AH34" s="43"/>
-      <c r="AI34" s="43"/>
-      <c r="AJ34" s="43"/>
+      <c r="AG34" s="41"/>
+      <c r="AH34" s="41"/>
+      <c r="AI34" s="41"/>
+      <c r="AJ34" s="41"/>
       <c r="AK34" s="16"/>
       <c r="AL34" s="16"/>
       <c r="AM34" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="AF34:AJ34"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="H34:L34"/>
-    <mergeCell ref="T34:X34"/>
-    <mergeCell ref="N34:R34"/>
-    <mergeCell ref="Z34:AD34"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="H3:L3"/>
@@ -4986,6 +4981,12 @@
     <mergeCell ref="T3:X3"/>
     <mergeCell ref="Z3:AD3"/>
     <mergeCell ref="AF3:AJ3"/>
+    <mergeCell ref="AF34:AJ34"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="H34:L34"/>
+    <mergeCell ref="T34:X34"/>
+    <mergeCell ref="N34:R34"/>
+    <mergeCell ref="Z34:AD34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -4995,140 +4996,140 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CD5CF7F-81D6-D24D-8228-B4C578C35D65}">
   <dimension ref="A1:AM41"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" style="1" customWidth="1"/>
     <col min="5" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="1.1640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.6640625" style="1" customWidth="1"/>
     <col min="11" max="12" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="1.125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="1.1640625" style="1" customWidth="1"/>
     <col min="14" max="14" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.6640625" style="1" customWidth="1"/>
     <col min="17" max="17" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="0.875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="0.83203125" style="1" customWidth="1"/>
     <col min="20" max="20" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.6640625" style="1" customWidth="1"/>
     <col min="24" max="24" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="1" style="1" customWidth="1"/>
     <col min="26" max="26" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="30" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="1.125" style="1" customWidth="1"/>
+    <col min="31" max="31" width="1.1640625" style="1" customWidth="1"/>
     <col min="32" max="32" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="5.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="5.625" style="1" customWidth="1"/>
+    <col min="33" max="33" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.6640625" style="1" customWidth="1"/>
     <col min="35" max="36" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="42"/>
+      <c r="P2" s="42"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="42"/>
       <c r="S2" s="9"/>
-      <c r="T2" s="41" t="s">
+      <c r="T2" s="42" t="s">
         <v>113</v>
       </c>
-      <c r="U2" s="41"/>
-      <c r="V2" s="41"/>
-      <c r="W2" s="41"/>
-      <c r="X2" s="41"/>
-      <c r="Y2" s="41"/>
-      <c r="Z2" s="41"/>
-      <c r="AA2" s="41"/>
-      <c r="AB2" s="41"/>
-      <c r="AC2" s="41"/>
-      <c r="AD2" s="41"/>
-      <c r="AE2" s="41"/>
-      <c r="AF2" s="41"/>
-      <c r="AG2" s="41"/>
-      <c r="AH2" s="41"/>
-      <c r="AI2" s="41"/>
-      <c r="AJ2" s="41"/>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="U2" s="42"/>
+      <c r="V2" s="42"/>
+      <c r="W2" s="42"/>
+      <c r="X2" s="42"/>
+      <c r="Y2" s="42"/>
+      <c r="Z2" s="42"/>
+      <c r="AA2" s="42"/>
+      <c r="AB2" s="42"/>
+      <c r="AC2" s="42"/>
+      <c r="AD2" s="42"/>
+      <c r="AE2" s="42"/>
+      <c r="AF2" s="42"/>
+      <c r="AG2" s="42"/>
+      <c r="AH2" s="42"/>
+      <c r="AI2" s="42"/>
+      <c r="AJ2" s="42"/>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A3" s="16"/>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
       <c r="G3" s="28"/>
-      <c r="H3" s="41" t="s">
+      <c r="H3" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
       <c r="M3" s="28"/>
-      <c r="N3" s="41" t="s">
+      <c r="N3" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="41"/>
-      <c r="T3" s="42" t="s">
+      <c r="O3" s="42"/>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="42"/>
+      <c r="R3" s="42"/>
+      <c r="T3" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="U3" s="42"/>
-      <c r="V3" s="42"/>
-      <c r="W3" s="42"/>
-      <c r="X3" s="42"/>
+      <c r="U3" s="43"/>
+      <c r="V3" s="43"/>
+      <c r="W3" s="43"/>
+      <c r="X3" s="43"/>
       <c r="Y3" s="28"/>
-      <c r="Z3" s="41" t="s">
+      <c r="Z3" s="42" t="s">
         <v>80</v>
       </c>
-      <c r="AA3" s="41"/>
-      <c r="AB3" s="41"/>
-      <c r="AC3" s="41"/>
-      <c r="AD3" s="41"/>
+      <c r="AA3" s="42"/>
+      <c r="AB3" s="42"/>
+      <c r="AC3" s="42"/>
+      <c r="AD3" s="42"/>
       <c r="AE3" s="28"/>
-      <c r="AF3" s="41" t="s">
+      <c r="AF3" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="AG3" s="41"/>
-      <c r="AH3" s="41"/>
-      <c r="AI3" s="41"/>
-      <c r="AJ3" s="41"/>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AG3" s="42"/>
+      <c r="AH3" s="42"/>
+      <c r="AI3" s="42"/>
+      <c r="AJ3" s="42"/>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
       <c r="B4" s="29" t="s">
         <v>89</v>
@@ -5226,7 +5227,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
         <v>84</v>
       </c>
@@ -5265,7 +5266,7 @@
       <c r="AI5" s="16"/>
       <c r="AJ5" s="16"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>94</v>
       </c>
@@ -5364,7 +5365,7 @@
         <v>13.875999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>95</v>
       </c>
@@ -5463,7 +5464,7 @@
         <v>2.1219999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>138</v>
       </c>
@@ -5562,7 +5563,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A9" s="16"/>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
@@ -5599,7 +5600,7 @@
       <c r="AI9" s="18"/>
       <c r="AJ9" s="16"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A10" s="17" t="s">
         <v>85</v>
       </c>
@@ -5638,7 +5639,7 @@
       <c r="AI10" s="16"/>
       <c r="AJ10" s="16"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>96</v>
       </c>
@@ -5737,7 +5738,7 @@
         <v>0.40300000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>137</v>
       </c>
@@ -5836,7 +5837,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>97</v>
       </c>
@@ -5935,7 +5936,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>98</v>
       </c>
@@ -6034,7 +6035,7 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>139</v>
       </c>
@@ -6133,7 +6134,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>99</v>
       </c>
@@ -6232,7 +6233,7 @@
         <v>0.22900000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>140</v>
       </c>
@@ -6331,7 +6332,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
         <v>87</v>
       </c>
@@ -6430,7 +6431,7 @@
         <v>0.28799999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A19" s="16"/>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -6467,7 +6468,7 @@
       <c r="AI19" s="18"/>
       <c r="AJ19" s="16"/>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A20" s="17" t="s">
         <v>86</v>
       </c>
@@ -6506,7 +6507,7 @@
       <c r="AI20" s="16"/>
       <c r="AJ20" s="16"/>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>100</v>
       </c>
@@ -6605,7 +6606,7 @@
         <v>0.14499999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
         <v>136</v>
       </c>
@@ -6704,7 +6705,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>101</v>
       </c>
@@ -6803,7 +6804,7 @@
         <v>-9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>102</v>
       </c>
@@ -6902,7 +6903,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="16" t="s">
         <v>144</v>
       </c>
@@ -6982,7 +6983,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
         <v>105</v>
       </c>
@@ -7081,7 +7082,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
         <v>106</v>
       </c>
@@ -7180,7 +7181,7 @@
         <v>-0.13600000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
         <v>103</v>
       </c>
@@ -7277,7 +7278,7 @@
         <v>0.17199999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>104</v>
       </c>
@@ -7374,7 +7375,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A30" s="16" t="s">
         <v>145</v>
       </c>
@@ -7453,7 +7454,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A31" s="16" t="s">
         <v>108</v>
       </c>
@@ -7550,7 +7551,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A32" s="16" t="s">
         <v>107</v>
       </c>
@@ -7647,7 +7648,7 @@
         <v>0.17499999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A33" s="16" t="s">
         <v>109</v>
       </c>
@@ -7744,7 +7745,7 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A34" s="16"/>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
@@ -7781,7 +7782,7 @@
       <c r="AI34" s="18"/>
       <c r="AJ34" s="16"/>
     </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A35" s="17" t="s">
         <v>82</v>
       </c>
@@ -7820,7 +7821,7 @@
       <c r="AI35" s="16"/>
       <c r="AJ35" s="16"/>
     </row>
-    <row r="36" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A36" s="16" t="s">
         <v>83</v>
       </c>
@@ -7919,7 +7920,7 @@
         <v>14.162000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A37" s="16" t="s">
         <v>88</v>
       </c>
@@ -8018,7 +8019,7 @@
         <v>4.1660000000000004</v>
       </c>
     </row>
-    <row r="38" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A38" s="16" t="s">
         <v>92</v>
       </c>
@@ -8117,7 +8118,7 @@
         <v>1.0549999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A39" s="16" t="s">
         <v>110</v>
       </c>
@@ -8214,7 +8215,7 @@
         <v>4.5090000000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A40" s="20" t="s">
         <v>115</v>
       </c>
@@ -8257,57 +8258,57 @@
       <c r="AL40" s="16"/>
       <c r="AM40" s="16"/>
     </row>
-    <row r="41" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A41" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B41" s="43">
+      <c r="B41" s="41">
         <v>34697.703999999998</v>
       </c>
-      <c r="C41" s="43"/>
-      <c r="D41" s="43"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="41"/>
       <c r="G41" s="27"/>
-      <c r="H41" s="43">
+      <c r="H41" s="41">
         <v>43730.449000000001</v>
       </c>
-      <c r="I41" s="43"/>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
-      <c r="L41" s="43"/>
+      <c r="I41" s="41"/>
+      <c r="J41" s="41"/>
+      <c r="K41" s="41"/>
+      <c r="L41" s="41"/>
       <c r="M41" s="27"/>
-      <c r="N41" s="43">
+      <c r="N41" s="41">
         <v>55075.362999999998</v>
       </c>
-      <c r="O41" s="43"/>
-      <c r="P41" s="43"/>
-      <c r="Q41" s="43"/>
-      <c r="R41" s="43"/>
+      <c r="O41" s="41"/>
+      <c r="P41" s="41"/>
+      <c r="Q41" s="41"/>
+      <c r="R41" s="41"/>
       <c r="S41" s="15"/>
-      <c r="T41" s="43">
+      <c r="T41" s="41">
         <v>37782.404000000002</v>
       </c>
-      <c r="U41" s="43"/>
-      <c r="V41" s="43"/>
-      <c r="W41" s="43"/>
-      <c r="X41" s="43"/>
+      <c r="U41" s="41"/>
+      <c r="V41" s="41"/>
+      <c r="W41" s="41"/>
+      <c r="X41" s="41"/>
       <c r="Y41" s="27"/>
-      <c r="Z41" s="43">
+      <c r="Z41" s="41">
         <v>47698.324999999997</v>
       </c>
-      <c r="AA41" s="43"/>
-      <c r="AB41" s="43"/>
-      <c r="AC41" s="43"/>
-      <c r="AD41" s="43"/>
+      <c r="AA41" s="41"/>
+      <c r="AB41" s="41"/>
+      <c r="AC41" s="41"/>
+      <c r="AD41" s="41"/>
       <c r="AE41" s="27"/>
-      <c r="AF41" s="43">
+      <c r="AF41" s="41">
         <v>60402.93</v>
       </c>
-      <c r="AG41" s="43"/>
-      <c r="AH41" s="43"/>
-      <c r="AI41" s="43"/>
-      <c r="AJ41" s="43"/>
+      <c r="AG41" s="41"/>
+      <c r="AH41" s="41"/>
+      <c r="AI41" s="41"/>
+      <c r="AJ41" s="41"/>
       <c r="AK41" s="16"/>
       <c r="AL41" s="16"/>
       <c r="AM41" s="16"/>
@@ -8335,61 +8336,244 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{540507A6-720C-0B43-804E-087FEE710926}">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="23" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="24"/>
+    </row>
+    <row r="3" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="24" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="24" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="24"/>
+    </row>
+    <row r="6" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="24"/>
+    </row>
+    <row r="7" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="23" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="24" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="24" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B11" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12">
+        <v>-3.4000000000000002E-2</v>
+      </c>
+      <c r="C12">
+        <v>-1.4E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>125</v>
+      </c>
+      <c r="B13">
+        <v>-2.4E-2</v>
+      </c>
+      <c r="C13">
+        <v>-8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14">
+        <v>-2.3E-2</v>
+      </c>
+      <c r="C14">
+        <v>-7.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>131</v>
+      </c>
+      <c r="B15">
+        <v>-2.5999999999999999E-2</v>
+      </c>
+      <c r="C15">
+        <v>-8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="23" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="24" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B19" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>124</v>
+      </c>
+      <c r="B20">
+        <v>-3.1E-2</v>
+      </c>
+      <c r="C20">
+        <v>-1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>125</v>
+      </c>
+      <c r="B21">
+        <v>-0.03</v>
+      </c>
+      <c r="C21">
+        <v>-1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22">
+        <v>-0.113</v>
+      </c>
+      <c r="C22">
+        <v>9.7000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23">
+        <v>-3.3000000000000002E-2</v>
+      </c>
+      <c r="C23">
+        <v>-1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E25" s="23" t="s">
+        <v>130</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A439B20-C024-854E-8504-DA6820AADA52}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57A86273-0E84-8246-B3ED-A023C6721217}">
   <dimension ref="A1:L31"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.125" style="35" customWidth="1"/>
-    <col min="3" max="3" width="4.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.1640625" style="35" customWidth="1"/>
+    <col min="3" max="3" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.5" style="40" customWidth="1"/>
     <col min="7" max="7" width="11" style="1"/>
-    <col min="8" max="8" width="6.125" style="35" customWidth="1"/>
-    <col min="9" max="9" width="4.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.1640625" style="35" customWidth="1"/>
+    <col min="9" max="9" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.5" style="32" customWidth="1"/>
     <col min="13" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
       <c r="B2" s="44"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
       <c r="F2" s="45"/>
       <c r="H2" s="44"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
       <c r="L2" s="45"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="15"/>
       <c r="B3" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
       <c r="F3" s="45"/>
       <c r="H3" s="44" t="s">
         <v>141</v>
       </c>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
       <c r="L3" s="45"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="16"/>
       <c r="B4" s="31" t="s">
         <v>89</v>
@@ -8422,7 +8606,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
         <v>84</v>
       </c>
@@ -8432,7 +8616,7 @@
       <c r="J5" s="16"/>
       <c r="K5" s="16"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>94</v>
       </c>
@@ -8456,7 +8640,7 @@
       <c r="J6" s="18"/>
       <c r="K6" s="16"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>95</v>
       </c>
@@ -8480,7 +8664,7 @@
       <c r="J7" s="18"/>
       <c r="K7" s="16"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
         <v>85</v>
       </c>
@@ -8493,7 +8677,7 @@
       <c r="J8" s="16"/>
       <c r="K8" s="16"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>96</v>
       </c>
@@ -8512,7 +8696,7 @@
       <c r="J9" s="18"/>
       <c r="K9" s="16"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>97</v>
       </c>
@@ -8531,7 +8715,7 @@
       <c r="J10" s="18"/>
       <c r="K10" s="16"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>98</v>
       </c>
@@ -8550,7 +8734,7 @@
       <c r="J11" s="18"/>
       <c r="K11" s="16"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>146</v>
       </c>
@@ -8569,7 +8753,7 @@
       <c r="J12" s="18"/>
       <c r="K12" s="16"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="16" t="s">
         <v>147</v>
       </c>
@@ -8588,7 +8772,7 @@
       <c r="J13" s="18"/>
       <c r="K13" s="16"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
         <v>86</v>
       </c>
@@ -8601,7 +8785,7 @@
       <c r="J14" s="16"/>
       <c r="K14" s="16"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>100</v>
       </c>
@@ -8620,7 +8804,7 @@
       <c r="J15" s="18"/>
       <c r="K15" s="16"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>101</v>
       </c>
@@ -8639,7 +8823,7 @@
       <c r="J16" s="18"/>
       <c r="K16" s="16"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>102</v>
       </c>
@@ -8658,7 +8842,7 @@
       <c r="J17" s="18"/>
       <c r="K17" s="16"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
         <v>105</v>
       </c>
@@ -8677,7 +8861,7 @@
       <c r="J18" s="18"/>
       <c r="K18" s="16"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
         <v>106</v>
       </c>
@@ -8696,7 +8880,7 @@
       <c r="J19" s="18"/>
       <c r="K19" s="16"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>103</v>
       </c>
@@ -8715,7 +8899,7 @@
       <c r="J20" s="18"/>
       <c r="K20" s="16"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>104</v>
       </c>
@@ -8734,7 +8918,7 @@
       <c r="J21" s="18"/>
       <c r="K21" s="16"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
         <v>108</v>
       </c>
@@ -8753,7 +8937,7 @@
       <c r="J22" s="18"/>
       <c r="K22" s="16"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="16" t="s">
         <v>107</v>
       </c>
@@ -8772,7 +8956,7 @@
       <c r="J23" s="18"/>
       <c r="K23" s="16"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
         <v>109</v>
       </c>
@@ -8791,7 +8975,7 @@
       <c r="J24" s="18"/>
       <c r="K24" s="16"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="17" t="s">
         <v>82</v>
       </c>
@@ -8804,7 +8988,7 @@
       <c r="J25" s="16"/>
       <c r="K25" s="16"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
         <v>83</v>
       </c>
@@ -8823,7 +9007,7 @@
       <c r="J26" s="18"/>
       <c r="K26" s="16"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
         <v>88</v>
       </c>
@@ -8842,7 +9026,7 @@
       <c r="J27" s="18"/>
       <c r="K27" s="16"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="16" t="s">
         <v>92</v>
       </c>
@@ -8861,7 +9045,7 @@
       <c r="J28" s="18"/>
       <c r="K28" s="16"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="16" t="s">
         <v>110</v>
       </c>
@@ -8880,7 +9064,7 @@
       <c r="J29" s="18"/>
       <c r="K29" s="16"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="20" t="s">
         <v>115</v>
       </c>
@@ -8896,7 +9080,7 @@
       <c r="K30" s="14"/>
       <c r="L30" s="33"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="15" t="s">
         <v>116</v>
       </c>
@@ -8921,178 +9105,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{540507A6-720C-0B43-804E-087FEE710926}">
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.875" customWidth="1"/>
-    <col min="2" max="2" width="18.875" customWidth="1"/>
-    <col min="3" max="3" width="19.125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="24"/>
-    </row>
-    <row r="3" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
-    </row>
-    <row r="6" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-    </row>
-    <row r="7" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="23" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>124</v>
-      </c>
-      <c r="B12">
-        <v>-3.4000000000000002E-2</v>
-      </c>
-      <c r="C12">
-        <v>-1.4E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>125</v>
-      </c>
-      <c r="B13">
-        <v>-2.4E-2</v>
-      </c>
-      <c r="C13">
-        <v>-8.0000000000000002E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>126</v>
-      </c>
-      <c r="B14">
-        <v>-2.3E-2</v>
-      </c>
-      <c r="C14">
-        <v>-7.0000000000000001E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>131</v>
-      </c>
-      <c r="B15">
-        <v>-2.5999999999999999E-2</v>
-      </c>
-      <c r="C15">
-        <v>-8.0000000000000002E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="23" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="24" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>124</v>
-      </c>
-      <c r="B20">
-        <v>-3.1E-2</v>
-      </c>
-      <c r="C20">
-        <v>-1.0999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>125</v>
-      </c>
-      <c r="B21">
-        <v>-0.03</v>
-      </c>
-      <c r="C21">
-        <v>-1.2999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>126</v>
-      </c>
-      <c r="B22">
-        <v>-0.113</v>
-      </c>
-      <c r="C22">
-        <v>9.7000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>131</v>
-      </c>
-      <c r="B23">
-        <v>-3.3000000000000002E-2</v>
-      </c>
-      <c r="C23">
-        <v>-1.4999999999999999E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E25" s="23" t="s">
-        <v>130</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nchaku/Documents/GitHub/pubertybrain/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmoffice-my.sharepoint.com/personal/abrieant_uvm_edu/Documents/OneDrive/Manuscripts/reg report DCN/pubertybrain/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBDCA32-700C-9942-8973-B738A2BA3D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{2DBDCA32-700C-9942-8973-B738A2BA3D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA8CBFAB-1504-2D4D-8A03-D773F8CDA273}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="500" windowWidth="27360" windowHeight="16400" activeTab="7" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
+    <workbookView xWindow="16120" yWindow="500" windowWidth="27740" windowHeight="16400" activeTab="8" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptive table" sheetId="1" r:id="rId1"/>
@@ -1178,14 +1178,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2352,94 +2352,94 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="41"/>
       <c r="S2" s="9"/>
-      <c r="T2" s="42" t="s">
+      <c r="T2" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="U2" s="42"/>
-      <c r="V2" s="42"/>
-      <c r="W2" s="42"/>
-      <c r="X2" s="42"/>
-      <c r="Y2" s="42"/>
-      <c r="Z2" s="42"/>
-      <c r="AA2" s="42"/>
-      <c r="AB2" s="42"/>
-      <c r="AC2" s="42"/>
-      <c r="AD2" s="42"/>
-      <c r="AE2" s="42"/>
-      <c r="AF2" s="42"/>
-      <c r="AG2" s="42"/>
-      <c r="AH2" s="42"/>
-      <c r="AI2" s="42"/>
-      <c r="AJ2" s="42"/>
+      <c r="U2" s="41"/>
+      <c r="V2" s="41"/>
+      <c r="W2" s="41"/>
+      <c r="X2" s="41"/>
+      <c r="Y2" s="41"/>
+      <c r="Z2" s="41"/>
+      <c r="AA2" s="41"/>
+      <c r="AB2" s="41"/>
+      <c r="AC2" s="41"/>
+      <c r="AD2" s="41"/>
+      <c r="AE2" s="41"/>
+      <c r="AF2" s="41"/>
+      <c r="AG2" s="41"/>
+      <c r="AH2" s="41"/>
+      <c r="AI2" s="41"/>
+      <c r="AJ2" s="41"/>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A3" s="16"/>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
       <c r="G3" s="28"/>
-      <c r="H3" s="42" t="s">
+      <c r="H3" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
       <c r="M3" s="28"/>
-      <c r="N3" s="42" t="s">
+      <c r="N3" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="O3" s="42"/>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="42"/>
-      <c r="R3" s="42"/>
-      <c r="T3" s="43" t="s">
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="41"/>
+      <c r="T3" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="U3" s="43"/>
-      <c r="V3" s="43"/>
-      <c r="W3" s="43"/>
-      <c r="X3" s="43"/>
+      <c r="U3" s="42"/>
+      <c r="V3" s="42"/>
+      <c r="W3" s="42"/>
+      <c r="X3" s="42"/>
       <c r="Y3" s="28"/>
-      <c r="Z3" s="42" t="s">
+      <c r="Z3" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="AA3" s="42"/>
-      <c r="AB3" s="42"/>
-      <c r="AC3" s="42"/>
-      <c r="AD3" s="42"/>
+      <c r="AA3" s="41"/>
+      <c r="AB3" s="41"/>
+      <c r="AC3" s="41"/>
+      <c r="AD3" s="41"/>
       <c r="AE3" s="28"/>
-      <c r="AF3" s="42" t="s">
+      <c r="AF3" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="AG3" s="42"/>
-      <c r="AH3" s="42"/>
-      <c r="AI3" s="42"/>
-      <c r="AJ3" s="42"/>
+      <c r="AG3" s="41"/>
+      <c r="AH3" s="41"/>
+      <c r="AI3" s="41"/>
+      <c r="AJ3" s="41"/>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
@@ -4920,59 +4920,65 @@
       <c r="A34" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B34" s="41">
+      <c r="B34" s="43">
         <v>74058.118000000002</v>
       </c>
-      <c r="C34" s="41"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="41"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
       <c r="G34" s="27"/>
-      <c r="H34" s="41">
+      <c r="H34" s="43">
         <v>83016.937999999995</v>
       </c>
-      <c r="I34" s="41"/>
-      <c r="J34" s="41"/>
-      <c r="K34" s="41"/>
-      <c r="L34" s="41"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="43"/>
+      <c r="L34" s="43"/>
       <c r="M34" s="27"/>
-      <c r="N34" s="41">
+      <c r="N34" s="43">
         <v>94345.274999999994</v>
       </c>
-      <c r="O34" s="41"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="41"/>
+      <c r="O34" s="43"/>
+      <c r="P34" s="43"/>
+      <c r="Q34" s="43"/>
+      <c r="R34" s="43"/>
       <c r="S34" s="15"/>
-      <c r="T34" s="41">
+      <c r="T34" s="43">
         <v>83167.763000000006</v>
       </c>
-      <c r="U34" s="41"/>
-      <c r="V34" s="41"/>
-      <c r="W34" s="41"/>
-      <c r="X34" s="41"/>
+      <c r="U34" s="43"/>
+      <c r="V34" s="43"/>
+      <c r="W34" s="43"/>
+      <c r="X34" s="43"/>
       <c r="Y34" s="27"/>
-      <c r="Z34" s="41">
+      <c r="Z34" s="43">
         <v>93083.505999999994</v>
       </c>
-      <c r="AA34" s="41"/>
-      <c r="AB34" s="41"/>
-      <c r="AC34" s="41"/>
-      <c r="AD34" s="41"/>
+      <c r="AA34" s="43"/>
+      <c r="AB34" s="43"/>
+      <c r="AC34" s="43"/>
+      <c r="AD34" s="43"/>
       <c r="AE34" s="27"/>
-      <c r="AF34" s="41">
+      <c r="AF34" s="43">
         <v>105770.462</v>
       </c>
-      <c r="AG34" s="41"/>
-      <c r="AH34" s="41"/>
-      <c r="AI34" s="41"/>
-      <c r="AJ34" s="41"/>
+      <c r="AG34" s="43"/>
+      <c r="AH34" s="43"/>
+      <c r="AI34" s="43"/>
+      <c r="AJ34" s="43"/>
       <c r="AK34" s="16"/>
       <c r="AL34" s="16"/>
       <c r="AM34" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="AF34:AJ34"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="H34:L34"/>
+    <mergeCell ref="T34:X34"/>
+    <mergeCell ref="N34:R34"/>
+    <mergeCell ref="Z34:AD34"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="H3:L3"/>
@@ -4981,12 +4987,6 @@
     <mergeCell ref="T3:X3"/>
     <mergeCell ref="Z3:AD3"/>
     <mergeCell ref="AF3:AJ3"/>
-    <mergeCell ref="AF34:AJ34"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="H34:L34"/>
-    <mergeCell ref="T34:X34"/>
-    <mergeCell ref="N34:R34"/>
-    <mergeCell ref="Z34:AD34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -5040,94 +5040,94 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="42"/>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="41"/>
       <c r="S2" s="9"/>
-      <c r="T2" s="42" t="s">
+      <c r="T2" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="U2" s="42"/>
-      <c r="V2" s="42"/>
-      <c r="W2" s="42"/>
-      <c r="X2" s="42"/>
-      <c r="Y2" s="42"/>
-      <c r="Z2" s="42"/>
-      <c r="AA2" s="42"/>
-      <c r="AB2" s="42"/>
-      <c r="AC2" s="42"/>
-      <c r="AD2" s="42"/>
-      <c r="AE2" s="42"/>
-      <c r="AF2" s="42"/>
-      <c r="AG2" s="42"/>
-      <c r="AH2" s="42"/>
-      <c r="AI2" s="42"/>
-      <c r="AJ2" s="42"/>
+      <c r="U2" s="41"/>
+      <c r="V2" s="41"/>
+      <c r="W2" s="41"/>
+      <c r="X2" s="41"/>
+      <c r="Y2" s="41"/>
+      <c r="Z2" s="41"/>
+      <c r="AA2" s="41"/>
+      <c r="AB2" s="41"/>
+      <c r="AC2" s="41"/>
+      <c r="AD2" s="41"/>
+      <c r="AE2" s="41"/>
+      <c r="AF2" s="41"/>
+      <c r="AG2" s="41"/>
+      <c r="AH2" s="41"/>
+      <c r="AI2" s="41"/>
+      <c r="AJ2" s="41"/>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A3" s="16"/>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="41" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
       <c r="G3" s="28"/>
-      <c r="H3" s="42" t="s">
+      <c r="H3" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
       <c r="M3" s="28"/>
-      <c r="N3" s="42" t="s">
+      <c r="N3" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="O3" s="42"/>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="42"/>
-      <c r="R3" s="42"/>
-      <c r="T3" s="43" t="s">
+      <c r="O3" s="41"/>
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="41"/>
+      <c r="T3" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="U3" s="43"/>
-      <c r="V3" s="43"/>
-      <c r="W3" s="43"/>
-      <c r="X3" s="43"/>
+      <c r="U3" s="42"/>
+      <c r="V3" s="42"/>
+      <c r="W3" s="42"/>
+      <c r="X3" s="42"/>
       <c r="Y3" s="28"/>
-      <c r="Z3" s="42" t="s">
+      <c r="Z3" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="AA3" s="42"/>
-      <c r="AB3" s="42"/>
-      <c r="AC3" s="42"/>
-      <c r="AD3" s="42"/>
+      <c r="AA3" s="41"/>
+      <c r="AB3" s="41"/>
+      <c r="AC3" s="41"/>
+      <c r="AD3" s="41"/>
       <c r="AE3" s="28"/>
-      <c r="AF3" s="42" t="s">
+      <c r="AF3" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="AG3" s="42"/>
-      <c r="AH3" s="42"/>
-      <c r="AI3" s="42"/>
-      <c r="AJ3" s="42"/>
+      <c r="AG3" s="41"/>
+      <c r="AH3" s="41"/>
+      <c r="AI3" s="41"/>
+      <c r="AJ3" s="41"/>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
@@ -8262,53 +8262,53 @@
       <c r="A41" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B41" s="41">
+      <c r="B41" s="43">
         <v>34697.703999999998</v>
       </c>
-      <c r="C41" s="41"/>
-      <c r="D41" s="41"/>
-      <c r="E41" s="41"/>
-      <c r="F41" s="41"/>
+      <c r="C41" s="43"/>
+      <c r="D41" s="43"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="43"/>
       <c r="G41" s="27"/>
-      <c r="H41" s="41">
+      <c r="H41" s="43">
         <v>43730.449000000001</v>
       </c>
-      <c r="I41" s="41"/>
-      <c r="J41" s="41"/>
-      <c r="K41" s="41"/>
-      <c r="L41" s="41"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="43"/>
+      <c r="L41" s="43"/>
       <c r="M41" s="27"/>
-      <c r="N41" s="41">
+      <c r="N41" s="43">
         <v>55075.362999999998</v>
       </c>
-      <c r="O41" s="41"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="41"/>
+      <c r="O41" s="43"/>
+      <c r="P41" s="43"/>
+      <c r="Q41" s="43"/>
+      <c r="R41" s="43"/>
       <c r="S41" s="15"/>
-      <c r="T41" s="41">
+      <c r="T41" s="43">
         <v>37782.404000000002</v>
       </c>
-      <c r="U41" s="41"/>
-      <c r="V41" s="41"/>
-      <c r="W41" s="41"/>
-      <c r="X41" s="41"/>
+      <c r="U41" s="43"/>
+      <c r="V41" s="43"/>
+      <c r="W41" s="43"/>
+      <c r="X41" s="43"/>
       <c r="Y41" s="27"/>
-      <c r="Z41" s="41">
+      <c r="Z41" s="43">
         <v>47698.324999999997</v>
       </c>
-      <c r="AA41" s="41"/>
-      <c r="AB41" s="41"/>
-      <c r="AC41" s="41"/>
-      <c r="AD41" s="41"/>
+      <c r="AA41" s="43"/>
+      <c r="AB41" s="43"/>
+      <c r="AC41" s="43"/>
+      <c r="AD41" s="43"/>
       <c r="AE41" s="27"/>
-      <c r="AF41" s="41">
+      <c r="AF41" s="43">
         <v>60402.93</v>
       </c>
-      <c r="AG41" s="41"/>
-      <c r="AH41" s="41"/>
-      <c r="AI41" s="41"/>
-      <c r="AJ41" s="41"/>
+      <c r="AG41" s="43"/>
+      <c r="AH41" s="43"/>
+      <c r="AI41" s="43"/>
+      <c r="AJ41" s="43"/>
       <c r="AK41" s="16"/>
       <c r="AL41" s="16"/>
       <c r="AM41" s="16"/>
@@ -8546,14 +8546,14 @@
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
       <c r="B2" s="44"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
       <c r="F2" s="45"/>
       <c r="H2" s="44"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
       <c r="L2" s="45"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
@@ -8561,16 +8561,16 @@
       <c r="B3" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
       <c r="F3" s="45"/>
       <c r="H3" s="44" t="s">
         <v>141</v>
       </c>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
       <c r="L3" s="45"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -8690,7 +8690,12 @@
       <c r="D9" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="16"/>
+      <c r="E9" s="16">
+        <v>-0.36399999999999999</v>
+      </c>
+      <c r="F9" s="40">
+        <v>-0.21199999999999999</v>
+      </c>
       <c r="H9" s="36"/>
       <c r="I9" s="16"/>
       <c r="J9" s="18"/>
@@ -8709,7 +8714,12 @@
       <c r="D10" s="18">
         <v>1.0999999999999999E-2</v>
       </c>
-      <c r="E10" s="16"/>
+      <c r="E10" s="16">
+        <v>1.2E-2</v>
+      </c>
+      <c r="F10" s="40">
+        <v>9.2999999999999999E-2</v>
+      </c>
       <c r="H10" s="36"/>
       <c r="I10" s="16"/>
       <c r="J10" s="18"/>
@@ -8728,7 +8738,12 @@
       <c r="D11" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="16"/>
+      <c r="E11" s="16">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="F11" s="40">
+        <v>0.16600000000000001</v>
+      </c>
       <c r="H11" s="36"/>
       <c r="I11" s="16"/>
       <c r="J11" s="18"/>
@@ -8747,7 +8762,12 @@
       <c r="D12" s="26">
         <v>0.40699999999999997</v>
       </c>
-      <c r="E12" s="16"/>
+      <c r="E12" s="16">
+        <v>-0.108</v>
+      </c>
+      <c r="F12" s="40">
+        <v>4.3999999999999997E-2</v>
+      </c>
       <c r="H12" s="36"/>
       <c r="I12" s="16"/>
       <c r="J12" s="18"/>
@@ -8766,7 +8786,12 @@
       <c r="D13" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="16"/>
+      <c r="E13" s="16">
+        <v>0.19700000000000001</v>
+      </c>
+      <c r="F13" s="40">
+        <v>0.28499999999999998</v>
+      </c>
       <c r="H13" s="36"/>
       <c r="I13" s="16"/>
       <c r="J13" s="18"/>
@@ -8798,7 +8823,12 @@
       <c r="D15" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="16"/>
+      <c r="E15" s="16">
+        <v>0.214</v>
+      </c>
+      <c r="F15" s="40">
+        <v>0.376</v>
+      </c>
       <c r="H15" s="36"/>
       <c r="I15" s="16"/>
       <c r="J15" s="18"/>
@@ -8817,7 +8847,12 @@
       <c r="D16" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="16"/>
+      <c r="E16" s="16">
+        <v>-0.187</v>
+      </c>
+      <c r="F16" s="40">
+        <v>-0.10299999999999999</v>
+      </c>
       <c r="H16" s="36"/>
       <c r="I16" s="16"/>
       <c r="J16" s="18"/>
@@ -8836,7 +8871,12 @@
       <c r="D17" s="18">
         <v>0.56699999999999995</v>
       </c>
-      <c r="E17" s="16"/>
+      <c r="E17" s="16">
+        <v>-9.8000000000000004E-2</v>
+      </c>
+      <c r="F17" s="40">
+        <v>5.3999999999999999E-2</v>
+      </c>
       <c r="H17" s="36"/>
       <c r="I17" s="16"/>
       <c r="J17" s="18"/>
@@ -8855,7 +8895,12 @@
       <c r="D18" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E18" s="16"/>
+      <c r="E18" s="16">
+        <v>-0.186</v>
+      </c>
+      <c r="F18" s="40">
+        <v>-0.10199999999999999</v>
+      </c>
       <c r="H18" s="36"/>
       <c r="I18" s="16"/>
       <c r="J18" s="18"/>
@@ -8874,7 +8919,12 @@
       <c r="D19" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="16"/>
+      <c r="E19" s="16">
+        <v>-0.20799999999999999</v>
+      </c>
+      <c r="F19" s="40">
+        <v>-0.124</v>
+      </c>
       <c r="H19" s="36"/>
       <c r="I19" s="16"/>
       <c r="J19" s="18"/>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmoffice-my.sharepoint.com/personal/abrieant_uvm_edu/Documents/OneDrive/Manuscripts/reg report DCN/pubertybrain/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{2DBDCA32-700C-9942-8973-B738A2BA3D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA8CBFAB-1504-2D4D-8A03-D773F8CDA273}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="13_ncr:1_{2DBDCA32-700C-9942-8973-B738A2BA3D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51F0BDD0-7196-8440-87E6-70DFE5126217}"/>
   <bookViews>
-    <workbookView xWindow="16120" yWindow="500" windowWidth="27740" windowHeight="16400" activeTab="8" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
+    <workbookView xWindow="6560" yWindow="500" windowWidth="37300" windowHeight="16400" activeTab="8" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptive table" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="157">
   <si>
     <t>16.10 (2.98)</t>
   </si>
@@ -854,6 +854,99 @@
   </si>
   <si>
     <t xml:space="preserve">   Timing with Tempo</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   ELA on Intercept</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   ELA on Slope</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">   ELA on Timing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   ELA on Tempo</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   Intercept</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> on WM</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   Slope</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> on WM</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">   ELA on WM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Timing on WM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Tempo on WM</t>
   </si>
 </sst>
 </file>
@@ -1120,7 +1213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1192,6 +1285,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8836,7 +8935,7 @@
     </row>
     <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="B16" s="36">
         <v>-0.14499999999999999</v>
@@ -8860,7 +8959,7 @@
     </row>
     <row r="17" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>102</v>
+        <v>149</v>
       </c>
       <c r="B17" s="36">
         <v>-2.1999999999999999E-2</v>
@@ -8884,7 +8983,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="B18" s="36">
         <v>-0.14399999999999999</v>
@@ -8908,7 +9007,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="B19" s="36">
         <v>-0.16600000000000001</v>
@@ -8932,7 +9031,7 @@
     </row>
     <row r="20" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="B20" s="36">
         <v>0.17899999999999999</v>
@@ -8943,7 +9042,12 @@
       <c r="D20" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="16"/>
+      <c r="E20" s="16">
+        <v>0.129</v>
+      </c>
+      <c r="F20" s="40">
+        <v>0.22900000000000001</v>
+      </c>
       <c r="H20" s="36"/>
       <c r="I20" s="16"/>
       <c r="J20" s="18"/>
@@ -8951,7 +9055,7 @@
     </row>
     <row r="21" spans="1:12" ht="17" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>104</v>
+        <v>153</v>
       </c>
       <c r="B21" s="36">
         <v>1E-3</v>
@@ -8962,7 +9066,12 @@
       <c r="D21" s="18">
         <v>0.98199999999999998</v>
       </c>
-      <c r="E21" s="16"/>
+      <c r="E21" s="16">
+        <v>-8.2000000000000003E-2</v>
+      </c>
+      <c r="F21" s="40">
+        <v>8.4000000000000005E-2</v>
+      </c>
       <c r="H21" s="36"/>
       <c r="I21" s="16"/>
       <c r="J21" s="18"/>
@@ -8970,7 +9079,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="B22" s="36">
         <v>1.6E-2</v>
@@ -8981,7 +9090,12 @@
       <c r="D22" s="18">
         <v>0.51500000000000001</v>
       </c>
-      <c r="E22" s="16"/>
+      <c r="E22" s="16">
+        <v>-3.2000000000000001E-2</v>
+      </c>
+      <c r="F22" s="40">
+        <v>6.5000000000000002E-2</v>
+      </c>
       <c r="H22" s="36"/>
       <c r="I22" s="16"/>
       <c r="J22" s="18"/>
@@ -8989,7 +9103,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="16" t="s">
-        <v>107</v>
+        <v>156</v>
       </c>
       <c r="B23" s="36">
         <v>6.5000000000000002E-2</v>
@@ -9000,7 +9114,12 @@
       <c r="D23" s="18">
         <v>4.0000000000000001E-3</v>
       </c>
-      <c r="E23" s="16"/>
+      <c r="E23" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="F23" s="40">
+        <v>0.11</v>
+      </c>
       <c r="H23" s="36"/>
       <c r="I23" s="16"/>
       <c r="J23" s="18"/>
@@ -9008,7 +9127,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
-        <v>109</v>
+        <v>154</v>
       </c>
       <c r="B24" s="36">
         <v>-0.12</v>
@@ -9019,7 +9138,12 @@
       <c r="D24" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E24" s="16"/>
+      <c r="E24" s="16">
+        <v>-0.16200000000000001</v>
+      </c>
+      <c r="F24" s="40">
+        <v>-7.6999999999999999E-2</v>
+      </c>
       <c r="H24" s="36"/>
       <c r="I24" s="16"/>
       <c r="J24" s="18"/>
@@ -9051,7 +9175,12 @@
       <c r="D26" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E26" s="16"/>
+      <c r="E26" s="16">
+        <v>12.388999999999999</v>
+      </c>
+      <c r="F26" s="40">
+        <v>13.079000000000001</v>
+      </c>
       <c r="H26" s="36"/>
       <c r="I26" s="16"/>
       <c r="J26" s="18"/>
@@ -9070,7 +9199,12 @@
       <c r="D27" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="16"/>
+      <c r="E27" s="16">
+        <v>4.4340000000000002</v>
+      </c>
+      <c r="F27" s="40">
+        <v>4.718</v>
+      </c>
       <c r="H27" s="36"/>
       <c r="I27" s="16"/>
       <c r="J27" s="18"/>
@@ -9089,7 +9223,12 @@
       <c r="D28" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="16"/>
+      <c r="E28" s="16">
+        <v>0.97799999999999998</v>
+      </c>
+      <c r="F28" s="40">
+        <v>1.0469999999999999</v>
+      </c>
       <c r="H28" s="36"/>
       <c r="I28" s="16"/>
       <c r="J28" s="18"/>
@@ -9108,7 +9247,12 @@
       <c r="D29" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E29" s="16"/>
+      <c r="E29" s="16">
+        <v>3.165</v>
+      </c>
+      <c r="F29" s="40">
+        <v>4.9379999999999997</v>
+      </c>
       <c r="H29" s="36"/>
       <c r="I29" s="16"/>
       <c r="J29" s="18"/>
@@ -9134,11 +9278,13 @@
       <c r="A31" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="B31" s="39"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="34"/>
+      <c r="B31" s="46">
+        <v>93579.540999999997</v>
+      </c>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="47"/>
       <c r="G31" s="15"/>
       <c r="H31" s="39"/>
       <c r="I31" s="15"/>
@@ -9147,11 +9293,12 @@
       <c r="L31" s="34"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B31:F31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmoffice-my.sharepoint.com/personal/abrieant_uvm_edu/Documents/OneDrive/Manuscripts/reg report DCN/pubertybrain/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="13_ncr:1_{2DBDCA32-700C-9942-8973-B738A2BA3D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51F0BDD0-7196-8440-87E6-70DFE5126217}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{2DBDCA32-700C-9942-8973-B738A2BA3D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0B398CC-9A7C-6F42-B28D-ECF982225E07}"/>
   <bookViews>
-    <workbookView xWindow="6560" yWindow="500" windowWidth="37300" windowHeight="16400" activeTab="8" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="43860" windowHeight="16400" activeTab="6" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptive table" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="Sex Differences" sheetId="11" r:id="rId8"/>
     <sheet name="Youth report PDS" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -953,7 +953,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1046,6 +1046,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1213,7 +1220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1292,6 +1299,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8577,13 +8585,13 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="A22" s="48" t="s">
         <v>126</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="48">
         <v>-0.113</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="48">
         <v>9.7000000000000003E-2</v>
       </c>
     </row>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmoffice-my.sharepoint.com/personal/abrieant_uvm_edu/Documents/OneDrive/Manuscripts/reg report DCN/pubertybrain/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{2DBDCA32-700C-9942-8973-B738A2BA3D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0B398CC-9A7C-6F42-B28D-ECF982225E07}"/>
+  <xr:revisionPtr revIDLastSave="436" documentId="13_ncr:1_{2DBDCA32-700C-9942-8973-B738A2BA3D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63DC9486-4C66-1646-B674-F3EAD1E5581C}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="43860" windowHeight="16400" activeTab="6" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
+    <workbookView xWindow="15860" yWindow="500" windowWidth="31800" windowHeight="17500" activeTab="8" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptive table" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Fig2 (Brain)" sheetId="4" r:id="rId4"/>
     <sheet name="CortModels" sheetId="6" r:id="rId5"/>
     <sheet name="SubCortModel" sheetId="10" r:id="rId6"/>
-    <sheet name="Indirect effects" sheetId="7" r:id="rId7"/>
+    <sheet name="Indirect effects" sheetId="7" state="hidden" r:id="rId7"/>
     <sheet name="Sex Differences" sheetId="11" r:id="rId8"/>
     <sheet name="Youth report PDS" sheetId="9" r:id="rId9"/>
   </sheets>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="192">
   <si>
     <t>16.10 (2.98)</t>
   </si>
@@ -371,9 +371,6 @@
   </si>
   <si>
     <t xml:space="preserve">   Tempo</t>
-  </si>
-  <si>
-    <t>B</t>
   </si>
   <si>
     <t>SE</t>
@@ -692,9 +689,6 @@
     <t>MALE - subcortical</t>
   </si>
   <si>
-    <t>Cortical volume by sex - YOUTH REPORT PDS</t>
-  </si>
-  <si>
     <t>LLCI</t>
   </si>
   <si>
@@ -820,9 +814,6 @@
     <t>Model 3 - Girls</t>
   </si>
   <si>
-    <t>12.311      0.203</t>
-  </si>
-  <si>
     <t xml:space="preserve">   ELA    on Quadratic Slope</t>
   </si>
   <si>
@@ -893,6 +884,45 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">   WM on Intercept</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   WM on Slope</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">   WM on Timing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   WM on Tempo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   WM on ELA</t>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">   Intercept</t>
     </r>
     <r>
@@ -948,12 +978,163 @@
   <si>
     <t xml:space="preserve">   Tempo on WM</t>
   </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>Estimate</t>
+  </si>
+  <si>
+    <t>Supplemental Table X. Estimates from sensitivity analyses with youth report of pubertal development</t>
+  </si>
+  <si>
+    <t>Models with cortical gray matter volume</t>
+  </si>
+  <si>
+    <t>Models with subcortical gray matter volume</t>
+  </si>
+  <si>
+    <t>Covariances</t>
+  </si>
+  <si>
+    <t>Interceptb with Slopeb</t>
+  </si>
+  <si>
+    <t>&lt; 0.001</t>
+  </si>
+  <si>
+    <t>Interceptb with Timing</t>
+  </si>
+  <si>
+    <t>Interceptb with Tempo</t>
+  </si>
+  <si>
+    <t>Slopeb with Tempo</t>
+  </si>
+  <si>
+    <t>Timing with Tempo</t>
+  </si>
+  <si>
+    <t>Timing on Slopeb</t>
+  </si>
+  <si>
+    <t>ELA on Interceptb</t>
+  </si>
+  <si>
+    <t>ELA on Slopeb</t>
+  </si>
+  <si>
+    <t>ELA on Timing</t>
+  </si>
+  <si>
+    <t>ELA on Tempo</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   Slope</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">b </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>with Quadratic Slope</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>b</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">   Slope</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">b </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>with Tempo</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">   ELA on Quadratic Slope</t>
+  </si>
+  <si>
+    <t>Row</t>
+  </si>
+  <si>
+    <t>–</t>
+  </si>
+  <si>
+    <t>Interceptb with Quadratic Slopeb</t>
+  </si>
+  <si>
+    <t>Slopeb with Quadratic Slopeb</t>
+  </si>
+  <si>
+    <t>Quadratic Slopeb with Tempo</t>
+  </si>
+  <si>
+    <t>Timing on Quadratic Slope</t>
+  </si>
+  <si>
+    <t>ELA on Quadratic Slope</t>
+  </si>
+  <si>
+    <t>WM on Interceptb</t>
+  </si>
+  <si>
+    <t>WM on Slopeb</t>
+  </si>
+  <si>
+    <t>WM on Quadratic Slope</t>
+  </si>
+  <si>
+    <t>WM on Timing</t>
+  </si>
+  <si>
+    <t>WM on Tempo</t>
+  </si>
+  <si>
+    <t>WM on ELA</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1055,6 +1236,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1076,7 +1272,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1204,23 +1400,47 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1287,10 +1507,13 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1300,6 +1523,37 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="11" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="11" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2381,7 +2635,7 @@
   <sheetData>
     <row r="2" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2416,19 +2670,19 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="1.1640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8" style="1" customWidth="1"/>
     <col min="9" max="9" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.6640625" style="1" customWidth="1"/>
     <col min="11" max="11" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="1.1640625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.5" style="1" customWidth="1"/>
     <col min="15" max="15" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="5.6640625" style="1" customWidth="1"/>
     <col min="17" max="17" width="6.5" style="1" bestFit="1" customWidth="1"/>
@@ -2439,12 +2693,12 @@
     <col min="22" max="23" width="5.6640625" style="1" customWidth="1"/>
     <col min="24" max="24" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="1" style="1" customWidth="1"/>
-    <col min="26" max="26" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="8.1640625" style="1" customWidth="1"/>
     <col min="27" max="27" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="5.6640625" style="1" customWidth="1"/>
     <col min="29" max="30" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="1.1640625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.33203125" style="1" customWidth="1"/>
     <col min="33" max="33" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="5.6640625" style="1" customWidth="1"/>
@@ -2454,13 +2708,13 @@
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
       <c r="B2" s="41" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C2" s="41"/>
       <c r="D2" s="41"/>
@@ -2480,7 +2734,7 @@
       <c r="R2" s="41"/>
       <c r="S2" s="9"/>
       <c r="T2" s="41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="U2" s="41"/>
       <c r="V2" s="41"/>
@@ -2551,99 +2805,99 @@
     <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
       <c r="B4" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="C4" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="D4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="D4" s="29" t="s">
-        <v>91</v>
-      </c>
       <c r="E4" s="29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="I4" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="J4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="J4" s="29" t="s">
-        <v>91</v>
-      </c>
       <c r="K4" s="29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L4" s="29" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="M4" s="29"/>
       <c r="N4" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="O4" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="O4" s="29" t="s">
+      <c r="P4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="P4" s="29" t="s">
-        <v>91</v>
-      </c>
       <c r="Q4" s="29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="R4" s="29" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="S4" s="6"/>
       <c r="T4" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="U4" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="U4" s="29" t="s">
+      <c r="V4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="V4" s="29" t="s">
-        <v>91</v>
-      </c>
       <c r="W4" s="29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="X4" s="29" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="Y4" s="17"/>
       <c r="Z4" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="AA4" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="AA4" s="29" t="s">
+      <c r="AB4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="AB4" s="29" t="s">
-        <v>91</v>
-      </c>
       <c r="AC4" s="29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AD4" s="29" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AE4" s="17"/>
       <c r="AF4" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="AG4" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="AG4" s="29" t="s">
+      <c r="AH4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="AH4" s="29" t="s">
-        <v>91</v>
-      </c>
       <c r="AI4" s="29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AJ4" s="29" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.2">
@@ -2687,7 +2941,7 @@
     </row>
     <row r="6" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B6" s="16">
         <v>12.162000000000001</v>
@@ -2786,7 +3040,7 @@
     </row>
     <row r="7" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B7" s="16">
         <v>-9.1289999999999996</v>
@@ -2961,7 +3215,7 @@
     </row>
     <row r="10" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B10" s="16">
         <v>-0.312</v>
@@ -3060,7 +3314,7 @@
     </row>
     <row r="11" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B11" s="16">
         <v>0.13200000000000001</v>
@@ -3159,7 +3413,7 @@
     </row>
     <row r="12" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B12" s="16">
         <v>0.16300000000000001</v>
@@ -3258,7 +3512,7 @@
     </row>
     <row r="13" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B13" s="16">
         <v>-5.5E-2</v>
@@ -3532,7 +3786,7 @@
     </row>
     <row r="17" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B17" s="16">
         <v>0.34100000000000003</v>
@@ -3631,22 +3885,22 @@
     </row>
     <row r="18" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G18" s="21"/>
       <c r="H18" s="16">
@@ -3681,19 +3935,19 @@
         <v>-0.11</v>
       </c>
       <c r="T18" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U18" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V18" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W18" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X18" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y18" s="21"/>
       <c r="Z18" s="16">
@@ -3730,22 +3984,22 @@
     </row>
     <row r="19" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G19" s="21"/>
       <c r="H19" s="22">
@@ -3780,19 +4034,19 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="T19" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U19" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V19" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W19" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X19" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y19" s="21"/>
       <c r="Z19" s="16">
@@ -3829,22 +4083,22 @@
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G20" s="21"/>
       <c r="H20" s="16">
@@ -3879,19 +4133,19 @@
         <v>-0.15</v>
       </c>
       <c r="T20" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U20" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V20" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W20" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X20" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y20" s="21"/>
       <c r="Z20" s="16">
@@ -3928,22 +4182,22 @@
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G21" s="21"/>
       <c r="H21" s="16">
@@ -3978,19 +4232,19 @@
         <v>-0.183</v>
       </c>
       <c r="T21" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U21" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V21" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W21" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X21" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y21" s="21"/>
       <c r="Z21" s="16">
@@ -4027,38 +4281,38 @@
     </row>
     <row r="22" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G22" s="21"/>
       <c r="H22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M22" s="16"/>
       <c r="N22" s="16">
@@ -4077,33 +4331,33 @@
         <v>0.21099999999999999</v>
       </c>
       <c r="T22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W22" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X22" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y22" s="21"/>
       <c r="Z22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AA22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AC22" s="16"/>
       <c r="AD22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE22" s="16"/>
       <c r="AF22" s="16">
@@ -4124,38 +4378,38 @@
     </row>
     <row r="23" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G23" s="21"/>
       <c r="H23" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J23" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M23" s="16"/>
       <c r="N23" s="16">
@@ -4174,33 +4428,33 @@
         <v>6.3E-2</v>
       </c>
       <c r="T23" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U23" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V23" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W23" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X23" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y23" s="21"/>
       <c r="Z23" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AA23" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB23" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AC23" s="16"/>
       <c r="AD23" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE23" s="16"/>
       <c r="AF23" s="16">
@@ -4221,38 +4475,38 @@
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G24" s="21"/>
       <c r="H24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M24" s="16"/>
       <c r="N24" s="16">
@@ -4271,33 +4525,33 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="T24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W24" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X24" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y24" s="21"/>
       <c r="Z24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AA24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AC24" s="16"/>
       <c r="AD24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE24" s="16"/>
       <c r="AF24" s="16">
@@ -4318,38 +4572,38 @@
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A25" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G25" s="21"/>
       <c r="H25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M25" s="16"/>
       <c r="N25" s="16">
@@ -4368,33 +4622,33 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="T25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W25" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X25" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y25" s="21"/>
       <c r="Z25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AA25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AC25" s="16"/>
       <c r="AD25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE25" s="16"/>
       <c r="AF25" s="16">
@@ -4415,38 +4669,38 @@
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G26" s="21"/>
       <c r="H26" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I26" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J26" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L26" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M26" s="16"/>
       <c r="N26" s="16">
@@ -4465,33 +4719,33 @@
         <v>-7.1999999999999995E-2</v>
       </c>
       <c r="T26" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U26" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V26" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W26" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X26" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y26" s="21"/>
       <c r="Z26" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AA26" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB26" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AC26" s="16"/>
       <c r="AD26" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE26" s="16"/>
       <c r="AF26" s="16">
@@ -4786,22 +5040,22 @@
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A31" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G31" s="21"/>
       <c r="H31" s="16">
@@ -4836,19 +5090,19 @@
         <v>1.0429999999999999</v>
       </c>
       <c r="T31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X31" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y31" s="21"/>
       <c r="Z31" s="16">
@@ -4885,36 +5139,36 @@
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A32" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G32" s="21"/>
       <c r="H32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K32" s="16"/>
       <c r="L32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M32" s="16"/>
       <c r="N32" s="16">
@@ -4933,35 +5187,35 @@
         <v>4.5410000000000004</v>
       </c>
       <c r="T32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W32" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X32" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y32" s="21"/>
       <c r="Z32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AA32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AC32" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AD32" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE32" s="16"/>
       <c r="AF32" s="16">
@@ -4982,7 +5236,7 @@
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A33" s="20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -5025,7 +5279,7 @@
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B34" s="43">
         <v>74058.118000000002</v>
@@ -5106,34 +5360,34 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5.6640625" style="1" customWidth="1"/>
     <col min="5" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="1.1640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.33203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.6640625" style="1" customWidth="1"/>
     <col min="11" max="12" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="1.1640625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.1640625" style="1" customWidth="1"/>
     <col min="15" max="15" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="5.6640625" style="1" customWidth="1"/>
     <col min="17" max="17" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="0.83203125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.33203125" style="1" customWidth="1"/>
     <col min="21" max="21" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="5.6640625" style="1" customWidth="1"/>
     <col min="24" max="24" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="1" style="1" customWidth="1"/>
-    <col min="26" max="26" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.33203125" style="1" customWidth="1"/>
     <col min="27" max="27" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="30" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="1.1640625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="6" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="9.1640625" style="1" customWidth="1"/>
     <col min="33" max="33" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="5.6640625" style="1" customWidth="1"/>
     <col min="35" max="36" width="6" style="1" bestFit="1" customWidth="1"/>
@@ -5142,13 +5396,13 @@
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
       <c r="B2" s="41" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C2" s="41"/>
       <c r="D2" s="41"/>
@@ -5168,7 +5422,7 @@
       <c r="R2" s="41"/>
       <c r="S2" s="9"/>
       <c r="T2" s="41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="U2" s="41"/>
       <c r="V2" s="41"/>
@@ -5239,99 +5493,99 @@
     <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
       <c r="B4" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="C4" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="D4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="D4" s="29" t="s">
-        <v>91</v>
-      </c>
       <c r="E4" s="29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="I4" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="J4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="J4" s="29" t="s">
-        <v>91</v>
-      </c>
       <c r="K4" s="29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L4" s="29" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="M4" s="29"/>
       <c r="N4" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="O4" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="O4" s="29" t="s">
+      <c r="P4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="P4" s="29" t="s">
-        <v>91</v>
-      </c>
       <c r="Q4" s="29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="R4" s="29" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="S4" s="6"/>
       <c r="T4" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="U4" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="U4" s="29" t="s">
+      <c r="V4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="V4" s="29" t="s">
-        <v>91</v>
-      </c>
       <c r="W4" s="29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="X4" s="29" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="Y4" s="17"/>
       <c r="Z4" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="AA4" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="AA4" s="29" t="s">
+      <c r="AB4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="AB4" s="29" t="s">
-        <v>91</v>
-      </c>
       <c r="AC4" s="29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AD4" s="29" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AE4" s="17"/>
       <c r="AF4" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="AG4" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="AG4" s="29" t="s">
+      <c r="AH4" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="AH4" s="29" t="s">
-        <v>91</v>
-      </c>
       <c r="AI4" s="29" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AJ4" s="29" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.2">
@@ -5375,7 +5629,7 @@
     </row>
     <row r="6" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B6" s="16">
         <v>13.944000000000001</v>
@@ -5474,54 +5728,54 @@
     </row>
     <row r="7" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J7" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K7" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L7" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M7" s="16"/>
       <c r="N7" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O7" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P7" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q7" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R7" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T7" s="16">
         <v>1.222</v>
@@ -5573,7 +5827,7 @@
     </row>
     <row r="8" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B8" s="16">
         <v>-0.253</v>
@@ -5623,51 +5877,51 @@
         <v>-7.4729999999999999</v>
       </c>
       <c r="T8" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U8" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V8" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W8" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X8" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y8" s="16"/>
       <c r="Z8" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AA8" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB8" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AC8" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AD8" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE8" s="16"/>
       <c r="AF8" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AG8" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AH8" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI8" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AJ8" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.2">
@@ -5748,54 +6002,54 @@
     </row>
     <row r="11" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G11" s="16"/>
       <c r="H11" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J11" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K11" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L11" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M11" s="16"/>
       <c r="N11" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O11" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P11" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q11" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R11" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T11" s="16">
         <v>0.318</v>
@@ -5847,7 +6101,7 @@
     </row>
     <row r="12" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B12" s="16">
         <v>0.11700000000000001</v>
@@ -5897,56 +6151,56 @@
         <v>0.20899999999999999</v>
       </c>
       <c r="T12" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U12" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V12" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W12" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X12" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y12" s="16"/>
       <c r="Z12" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AA12" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB12" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AC12" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AD12" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE12" s="16"/>
       <c r="AF12" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AG12" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AH12" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI12" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AJ12" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B13" s="16">
         <v>0.02</v>
@@ -6045,7 +6299,7 @@
     </row>
     <row r="14" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B14" s="16">
         <v>6.9000000000000006E-2</v>
@@ -6144,153 +6398,153 @@
     </row>
     <row r="15" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G15" s="21"/>
       <c r="H15" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K15" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L15" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M15" s="16"/>
       <c r="N15" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O15" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P15" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q15" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R15" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T15" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U15" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V15" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W15" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X15" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y15" s="16"/>
       <c r="Z15" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AA15" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB15" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AC15" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AD15" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE15" s="16"/>
       <c r="AF15" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AG15" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AH15" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI15" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AJ15" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G16" s="16"/>
       <c r="H16" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J16" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K16" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L16" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M16" s="16"/>
       <c r="N16" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O16" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P16" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q16" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R16" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T16" s="16">
         <v>0.16800000000000001</v>
@@ -6342,7 +6596,7 @@
     </row>
     <row r="17" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B17" s="16">
         <v>-0.45300000000000001</v>
@@ -6392,51 +6646,51 @@
         <v>0.153</v>
       </c>
       <c r="T17" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U17" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V17" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W17" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X17" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y17" s="16"/>
       <c r="Z17" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AA17" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB17" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AC17" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AD17" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE17" s="16"/>
       <c r="AF17" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AG17" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AH17" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI17" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AJ17" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.2">
@@ -6616,54 +6870,54 @@
     </row>
     <row r="21" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G21" s="16"/>
       <c r="H21" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J21" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K21" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L21" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M21" s="16"/>
       <c r="N21" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O21" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P21" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q21" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R21" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T21" s="16">
         <v>8.5000000000000006E-2</v>
@@ -6715,7 +6969,7 @@
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B22" s="16">
         <v>-0.29099999999999998</v>
@@ -6765,71 +7019,71 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="T22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W22" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X22" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y22" s="21"/>
       <c r="Z22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AA22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AC22" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AD22" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE22" s="16"/>
       <c r="AF22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AG22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AH22" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI22" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AJ22" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G23" s="21"/>
       <c r="H23" s="16">
@@ -6864,19 +7118,19 @@
         <v>-7.5999999999999998E-2</v>
       </c>
       <c r="T23" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U23" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V23" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W23" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X23" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y23" s="21"/>
       <c r="Z23" s="16">
@@ -6913,69 +7167,69 @@
     </row>
     <row r="24" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E24" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G24" s="21"/>
       <c r="H24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K24" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L24" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M24" s="16"/>
       <c r="N24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q24" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R24" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V24" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W24" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X24" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y24" s="21"/>
       <c r="Z24" s="16">
@@ -7012,7 +7266,7 @@
     </row>
     <row r="25" spans="1:36" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="16" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H25" s="16">
         <v>-8.8999999999999996E-2</v>
@@ -7045,69 +7299,69 @@
         <v>-3.1E-2</v>
       </c>
       <c r="T25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W25" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X25" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Z25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AA25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AC25" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AD25" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AF25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AG25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AH25" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI25" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AJ25" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G26" s="21"/>
       <c r="H26" s="16">
@@ -7142,19 +7396,19 @@
         <v>-0.15</v>
       </c>
       <c r="T26" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U26" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V26" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W26" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X26" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y26" s="21"/>
       <c r="Z26" s="16">
@@ -7191,22 +7445,22 @@
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G27" s="21"/>
       <c r="H27" s="16">
@@ -7241,19 +7495,19 @@
         <v>-0.183</v>
       </c>
       <c r="T27" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U27" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V27" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W27" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X27" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y27" s="21"/>
       <c r="Z27" s="16">
@@ -7290,38 +7544,38 @@
     </row>
     <row r="28" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A28" s="16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F28" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G28" s="21"/>
       <c r="H28" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I28" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J28" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M28" s="16"/>
       <c r="N28" s="16">
@@ -7340,33 +7594,33 @@
         <v>0.17399999999999999</v>
       </c>
       <c r="T28" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U28" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V28" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W28" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X28" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y28" s="21"/>
       <c r="Z28" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AA28" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB28" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AC28" s="16"/>
       <c r="AD28" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE28" s="16"/>
       <c r="AF28" s="16">
@@ -7387,83 +7641,83 @@
     </row>
     <row r="29" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F29" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G29" s="21"/>
       <c r="H29" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I29" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J29" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L29" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M29" s="16"/>
       <c r="N29" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="O29" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P29" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q29" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R29" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T29" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U29" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V29" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W29" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X29" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y29" s="21"/>
       <c r="Z29" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AA29" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB29" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AC29" s="16"/>
       <c r="AD29" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE29" s="16"/>
       <c r="AF29" s="16">
@@ -7484,7 +7738,7 @@
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A30" s="16" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -7514,87 +7768,87 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="T30" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U30" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V30" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W30" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X30" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y30" s="21"/>
       <c r="Z30" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AA30" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB30" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AC30" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AD30" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE30" s="16"/>
       <c r="AF30" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AG30" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AH30" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AI30" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AJ30" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A31" s="16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G31" s="21"/>
       <c r="H31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M31" s="16"/>
       <c r="N31" s="16">
@@ -7613,33 +7867,33 @@
         <v>0.08</v>
       </c>
       <c r="T31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W31" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X31" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y31" s="21"/>
       <c r="Z31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AA31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AC31" s="16"/>
       <c r="AD31" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE31" s="16"/>
       <c r="AF31" s="16">
@@ -7660,38 +7914,38 @@
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A32" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G32" s="21"/>
       <c r="H32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M32" s="16"/>
       <c r="N32" s="16">
@@ -7710,33 +7964,33 @@
         <v>0.13800000000000001</v>
       </c>
       <c r="T32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W32" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X32" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y32" s="21"/>
       <c r="Z32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AA32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AC32" s="16"/>
       <c r="AD32" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE32" s="16"/>
       <c r="AF32" s="16">
@@ -7757,38 +8011,38 @@
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A33" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F33" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G33" s="21"/>
       <c r="H33" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I33" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J33" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M33" s="16"/>
       <c r="N33" s="16">
@@ -7807,33 +8061,33 @@
         <v>-7.1999999999999995E-2</v>
       </c>
       <c r="T33" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U33" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V33" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W33" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X33" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y33" s="21"/>
       <c r="Z33" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AA33" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB33" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AC33" s="16"/>
       <c r="AD33" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE33" s="16"/>
       <c r="AF33" s="16">
@@ -8128,22 +8382,22 @@
     </row>
     <row r="38" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A38" s="16" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F38" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G38" s="21"/>
       <c r="H38" s="16">
@@ -8178,19 +8432,19 @@
         <v>1.0429999999999999</v>
       </c>
       <c r="T38" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U38" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V38" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W38" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X38" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y38" s="21"/>
       <c r="Z38" s="16">
@@ -8227,36 +8481,36 @@
     </row>
     <row r="39" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A39" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F39" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G39" s="21"/>
       <c r="H39" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I39" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J39" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K39" s="16"/>
       <c r="L39" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M39" s="16"/>
       <c r="N39" s="16">
@@ -8275,35 +8529,35 @@
         <v>5.3380000000000001</v>
       </c>
       <c r="T39" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U39" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="V39" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="W39" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="X39" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Y39" s="21"/>
       <c r="Z39" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AA39" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AB39" s="16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AC39" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AD39" s="21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AE39" s="16"/>
       <c r="AF39" s="16">
@@ -8324,7 +8578,7 @@
     </row>
     <row r="40" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A40" s="20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
@@ -8367,7 +8621,7 @@
     </row>
     <row r="41" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A41" s="15" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B41" s="43">
         <v>34697.703999999998</v>
@@ -8454,7 +8708,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
@@ -8462,12 +8716,12 @@
     </row>
     <row r="3" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
@@ -8479,30 +8733,30 @@
     <row r="7" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B11" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="23" t="s">
         <v>127</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B12">
         <v>-3.4000000000000002E-2</v>
@@ -8513,7 +8767,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B13">
         <v>-2.4E-2</v>
@@ -8524,7 +8778,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B14">
         <v>-2.3E-2</v>
@@ -8535,7 +8789,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B15">
         <v>-2.5999999999999999E-2</v>
@@ -8546,25 +8800,25 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B19" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="C19" s="23" t="s">
         <v>127</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B20">
         <v>-3.1E-2</v>
@@ -8575,7 +8829,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B21">
         <v>-0.03</v>
@@ -8585,19 +8839,19 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="48" t="s">
-        <v>126</v>
-      </c>
-      <c r="B22" s="48">
+      <c r="A22" s="49" t="s">
+        <v>125</v>
+      </c>
+      <c r="B22" s="49">
         <v>-0.113</v>
       </c>
-      <c r="C22" s="48">
+      <c r="C22" s="49">
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B23">
         <v>-3.3000000000000002E-2</v>
@@ -8608,7 +8862,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E25" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -8627,686 +8881,2882 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57A86273-0E84-8246-B3ED-A023C6721217}">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:AF59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.1640625" style="35" customWidth="1"/>
-    <col min="3" max="3" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" style="35" customWidth="1"/>
+    <col min="3" max="3" width="5.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.5" style="40" customWidth="1"/>
-    <col min="7" max="7" width="11" style="1"/>
-    <col min="8" max="8" width="6.1640625" style="35" customWidth="1"/>
-    <col min="9" max="9" width="4.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.83203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.1640625" style="35" customWidth="1"/>
+    <col min="9" max="9" width="5.6640625" style="1" customWidth="1"/>
     <col min="10" max="10" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.5" style="32" customWidth="1"/>
-    <col min="13" max="16384" width="11" style="1"/>
+    <col min="13" max="13" width="3.33203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="26.5" style="1" customWidth="1"/>
+    <col min="15" max="15" width="8" style="1" customWidth="1"/>
+    <col min="16" max="16" width="5.5" style="1" customWidth="1"/>
+    <col min="17" max="17" width="8" style="1" customWidth="1"/>
+    <col min="18" max="18" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.5" style="1" customWidth="1"/>
+    <col min="20" max="20" width="6.33203125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19" style="1" customWidth="1"/>
+    <col min="22" max="22" width="8.1640625" style="1" customWidth="1"/>
+    <col min="23" max="23" width="6.33203125" style="1" customWidth="1"/>
+    <col min="24" max="24" width="7.6640625" style="1" customWidth="1"/>
+    <col min="25" max="25" width="7" style="1" customWidth="1"/>
+    <col min="26" max="26" width="7.83203125" style="1" customWidth="1"/>
+    <col min="27" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+      <c r="N1" s="35"/>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
-      <c r="B2" s="44"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="45"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="45"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B2" s="53" t="s">
+        <v>162</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="53" t="s">
+        <v>163</v>
+      </c>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
+      <c r="R2" s="53"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="53"/>
+      <c r="U2" s="53"/>
+      <c r="V2" s="53"/>
+      <c r="W2" s="53"/>
+      <c r="X2" s="53"/>
+      <c r="Y2" s="53"/>
+      <c r="Z2" s="53"/>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3" s="15"/>
       <c r="B3" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="45"/>
+        <v>140</v>
+      </c>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="46"/>
       <c r="H3" s="44" t="s">
-        <v>141</v>
-      </c>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="45"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+        <v>139</v>
+      </c>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="46"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="P3" s="45"/>
+      <c r="Q3" s="45"/>
+      <c r="R3" s="45"/>
+      <c r="S3" s="46"/>
+      <c r="T3" s="60"/>
+      <c r="U3" s="61"/>
+      <c r="V3" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="W3" s="45"/>
+      <c r="X3" s="45"/>
+      <c r="Y3" s="45"/>
+      <c r="Z3" s="46"/>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4" s="16"/>
       <c r="B4" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="C4" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="D4" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="D4" s="31" t="s">
-        <v>91</v>
-      </c>
       <c r="E4" s="31" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H4" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="I4" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="I4" s="31" t="s">
+      <c r="J4" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="J4" s="31" t="s">
-        <v>91</v>
-      </c>
       <c r="K4" s="31" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L4" s="31" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+        <v>132</v>
+      </c>
+      <c r="N4" s="38"/>
+      <c r="O4" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="P4" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q4" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="R4" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="S4" s="62" t="s">
+        <v>132</v>
+      </c>
+      <c r="T4" s="64"/>
+      <c r="U4" s="34"/>
+      <c r="V4" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="W4" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="X4" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y4" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="Z4" s="31" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
-        <v>84</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="B5" s="36"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
       <c r="E5" s="16"/>
+      <c r="G5" s="16"/>
       <c r="H5" s="36"/>
       <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
+      <c r="J5" s="18"/>
       <c r="K5" s="16"/>
-    </row>
-    <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+      <c r="L5" s="40"/>
+      <c r="N5" s="54" t="s">
+        <v>85</v>
+      </c>
+      <c r="O5" s="38"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="55"/>
+      <c r="T5" s="65"/>
+      <c r="U5" s="63" t="s">
+        <v>85</v>
+      </c>
+      <c r="V5" s="36"/>
+      <c r="W5" s="16"/>
+      <c r="X5" s="18"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="40"/>
+      <c r="AA5" s="50"/>
+      <c r="AB5"/>
+      <c r="AC5"/>
+      <c r="AD5"/>
+      <c r="AE5"/>
+      <c r="AF5"/>
+    </row>
+    <row r="6" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="B6" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="36">
+        <v>-0.28799999999999998</v>
+      </c>
+      <c r="C6" s="16">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="16">
+        <v>-0.36399999999999999</v>
+      </c>
+      <c r="F6" s="40">
+        <v>-0.21199999999999999</v>
+      </c>
+      <c r="G6" s="16"/>
+      <c r="H6" s="36">
+        <v>-0.28199999999999997</v>
+      </c>
+      <c r="I6" s="16">
+        <v>0.04</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="16">
+        <v>-0.36199999999999999</v>
+      </c>
+      <c r="L6" s="40">
+        <v>-0.20300000000000001</v>
+      </c>
+      <c r="N6" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="O6" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="P6" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q6" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="R6" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="S6" s="70" t="s">
+        <v>92</v>
+      </c>
+      <c r="T6" s="55"/>
+      <c r="U6" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="V6" s="36">
+        <v>0.32200000000000001</v>
+      </c>
+      <c r="W6" s="16">
+        <v>0.05</v>
+      </c>
+      <c r="X6" s="67" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y6" s="16">
+        <v>0.224</v>
+      </c>
+      <c r="Z6" s="16">
+        <v>0.42</v>
+      </c>
+      <c r="AA6" s="51"/>
+      <c r="AB6"/>
+      <c r="AC6"/>
+      <c r="AD6"/>
+      <c r="AE6"/>
+      <c r="AF6"/>
+    </row>
+    <row r="7" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="36">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="C7" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="D7" s="18">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="E7" s="16">
+        <v>1.2E-2</v>
+      </c>
+      <c r="F7" s="40">
+        <v>9.2999999999999999E-2</v>
+      </c>
+      <c r="G7" s="16"/>
+      <c r="H7" s="36">
+        <v>-7.0000000000000001E-3</v>
+      </c>
+      <c r="I7" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="J7" s="18">
+        <v>0.74199999999999999</v>
+      </c>
+      <c r="K7" s="16">
+        <v>-4.8000000000000001E-2</v>
+      </c>
+      <c r="L7" s="40">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="N7" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="O7" s="36">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="P7" s="16">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="Q7" s="67">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="R7" s="16">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="S7" s="40">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="T7" s="55"/>
+      <c r="U7" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="V7" s="36">
+        <v>-0.05</v>
+      </c>
+      <c r="W7" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="X7" s="67">
+        <v>1.6E-2</v>
+      </c>
+      <c r="Y7" s="16">
+        <v>-9.0999999999999998E-2</v>
+      </c>
+      <c r="Z7" s="16">
+        <v>-8.9999999999999993E-3</v>
+      </c>
+      <c r="AA7" s="51"/>
+      <c r="AB7"/>
+      <c r="AC7"/>
+      <c r="AD7"/>
+      <c r="AE7"/>
+      <c r="AF7"/>
+    </row>
+    <row r="8" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" s="36">
+        <v>0.124</v>
+      </c>
+      <c r="C8" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="16">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="F8" s="40">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="G8" s="16"/>
+      <c r="H8" s="36">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="I8" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="16">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="L8" s="40">
+        <v>0.129</v>
+      </c>
+      <c r="N8" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="O8" s="36">
+        <v>-8.0000000000000002E-3</v>
+      </c>
+      <c r="P8" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="Q8" s="67">
+        <v>0.71599999999999997</v>
+      </c>
+      <c r="R8" s="16">
+        <v>-4.8000000000000001E-2</v>
+      </c>
+      <c r="S8" s="40">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="T8" s="55"/>
+      <c r="U8" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="V8" s="36">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="W8" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="X8" s="67" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y8" s="16">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="Z8" s="16">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="AA8" s="51"/>
+      <c r="AB8"/>
+      <c r="AC8"/>
+      <c r="AD8"/>
+      <c r="AE8"/>
+      <c r="AF8"/>
+    </row>
+    <row r="9" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="C6" s="16">
-        <v>0.17599999999999999</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="16">
-        <v>11.912000000000001</v>
-      </c>
-      <c r="F6" s="40">
-        <v>12.709</v>
-      </c>
-      <c r="H6" s="36"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="16"/>
-    </row>
-    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B7" s="36">
-        <v>-9.1010000000000009</v>
-      </c>
-      <c r="C7" s="16">
-        <v>0.74299999999999999</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="16">
-        <v>-10.558</v>
-      </c>
-      <c r="F7" s="40">
-        <v>-7.6449999999999996</v>
-      </c>
-      <c r="H7" s="36"/>
-      <c r="I7" s="16"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="16"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-    </row>
-    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B9" s="36">
-        <v>-0.28799999999999998</v>
-      </c>
-      <c r="C9" s="16">
+      <c r="B9" s="37">
+        <v>-3.2000000000000001E-2</v>
+      </c>
+      <c r="C9" s="25">
         <v>3.9E-2</v>
       </c>
-      <c r="D9" s="16" t="s">
-        <v>24</v>
+      <c r="D9" s="26">
+        <v>0.40699999999999997</v>
       </c>
       <c r="E9" s="16">
-        <v>-0.36399999999999999</v>
+        <v>-0.108</v>
       </c>
       <c r="F9" s="40">
-        <v>-0.21199999999999999</v>
-      </c>
-      <c r="H9" s="36"/>
-      <c r="I9" s="16"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="16"/>
-    </row>
-    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="G9" s="16"/>
+      <c r="H9" s="36">
+        <v>-9.6000000000000002E-2</v>
+      </c>
+      <c r="I9" s="16">
+        <v>3.9E-2</v>
+      </c>
+      <c r="J9" s="18">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="K9" s="16">
+        <v>-0.17299999999999999</v>
+      </c>
+      <c r="L9" s="40">
+        <v>-1.7999999999999999E-2</v>
+      </c>
+      <c r="N9" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="O9" s="36">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="P9" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="Q9" s="67" t="s">
+        <v>24</v>
+      </c>
+      <c r="R9" s="16">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="S9" s="40">
+        <v>0.115</v>
+      </c>
+      <c r="T9" s="55"/>
+      <c r="U9" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="V9" s="36">
+        <v>0.115</v>
+      </c>
+      <c r="W9" s="16">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="X9" s="67">
+        <v>1E-3</v>
+      </c>
+      <c r="Y9" s="16">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="Z9" s="16">
+        <v>0.185</v>
+      </c>
+      <c r="AA9" s="51"/>
+      <c r="AB9"/>
+      <c r="AC9"/>
+      <c r="AD9"/>
+      <c r="AE9"/>
+      <c r="AF9"/>
+    </row>
+    <row r="10" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>97</v>
+        <v>144</v>
       </c>
       <c r="B10" s="36">
-        <v>5.2999999999999999E-2</v>
+        <v>0.24099999999999999</v>
       </c>
       <c r="C10" s="16">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="D10" s="18">
-        <v>1.0999999999999999E-2</v>
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>24</v>
       </c>
       <c r="E10" s="16">
-        <v>1.2E-2</v>
+        <v>0.19700000000000001</v>
       </c>
       <c r="F10" s="40">
-        <v>9.2999999999999999E-2</v>
-      </c>
-      <c r="H10" s="36"/>
-      <c r="I10" s="16"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="16"/>
-    </row>
-    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B11" s="36">
-        <v>0.124</v>
-      </c>
-      <c r="C11" s="16">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="16">
-        <v>8.3000000000000004E-2</v>
-      </c>
-      <c r="F11" s="40">
-        <v>0.16600000000000001</v>
-      </c>
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="G10" s="16"/>
+      <c r="H10" s="36">
+        <v>0.04</v>
+      </c>
+      <c r="I10" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="J10" s="18">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="K10" s="16">
+        <v>1E-3</v>
+      </c>
+      <c r="L10" s="40">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="N10" s="36" t="s">
+        <v>176</v>
+      </c>
+      <c r="O10" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="P10" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q10" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="R10" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="S10" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="T10" s="55"/>
+      <c r="U10" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="V10" s="36">
+        <v>0.04</v>
+      </c>
+      <c r="W10" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="X10" s="67">
+        <v>4.7E-2</v>
+      </c>
+      <c r="Y10" s="16">
+        <v>1E-3</v>
+      </c>
+      <c r="Z10" s="16">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="AA10" s="51"/>
+      <c r="AB10"/>
+      <c r="AC10"/>
+      <c r="AD10"/>
+      <c r="AE10"/>
+      <c r="AF10"/>
+    </row>
+    <row r="11" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" s="36"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="G11" s="16"/>
       <c r="H11" s="36"/>
       <c r="I11" s="16"/>
-      <c r="J11" s="18"/>
+      <c r="J11" s="16"/>
       <c r="K11" s="16"/>
-    </row>
-    <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+      <c r="L11" s="40"/>
+      <c r="N11" s="36" t="s">
+        <v>177</v>
+      </c>
+      <c r="O11" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="P11" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q11" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="R11" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="S11" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="T11" s="55"/>
+      <c r="U11" s="54" t="s">
+        <v>86</v>
+      </c>
+      <c r="V11" s="36"/>
+      <c r="W11" s="16"/>
+      <c r="X11" s="67"/>
+      <c r="Y11" s="16"/>
+      <c r="Z11" s="16"/>
+      <c r="AA11" s="57"/>
+      <c r="AB11"/>
+      <c r="AC11"/>
+      <c r="AD11"/>
+      <c r="AE11"/>
+      <c r="AF11"/>
+    </row>
+    <row r="12" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="B12" s="37">
-        <v>-3.2000000000000001E-2</v>
-      </c>
-      <c r="C12" s="25">
-        <v>3.9E-2</v>
-      </c>
-      <c r="D12" s="26">
-        <v>0.40699999999999997</v>
+        <v>99</v>
+      </c>
+      <c r="B12" s="36">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="C12" s="16">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>24</v>
       </c>
       <c r="E12" s="16">
-        <v>-0.108</v>
+        <v>0.214</v>
       </c>
       <c r="F12" s="40">
-        <v>4.3999999999999997E-2</v>
-      </c>
-      <c r="H12" s="36"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="16"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+        <v>0.376</v>
+      </c>
+      <c r="G12" s="16"/>
+      <c r="H12" s="36">
+        <v>0.40100000000000002</v>
+      </c>
+      <c r="I12" s="16">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="16">
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="L12" s="40">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="N12" s="36" t="s">
+        <v>138</v>
+      </c>
+      <c r="O12" s="36">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="P12" s="16">
+        <v>0.04</v>
+      </c>
+      <c r="Q12" s="67">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="R12" s="16">
+        <v>1E-3</v>
+      </c>
+      <c r="S12" s="40">
+        <v>0.157</v>
+      </c>
+      <c r="T12" s="55"/>
+      <c r="U12" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="V12" s="36">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="W12" s="16">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="X12" s="67">
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="Y12" s="16">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="Z12" s="16">
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="AA12" s="51"/>
+      <c r="AB12"/>
+      <c r="AC12"/>
+      <c r="AD12"/>
+      <c r="AE12"/>
+      <c r="AF12"/>
+    </row>
+    <row r="13" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B13" s="36">
-        <v>0.24099999999999999</v>
+        <v>-0.14499999999999999</v>
       </c>
       <c r="C13" s="16">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E13" s="16">
+        <v>-0.187</v>
+      </c>
+      <c r="F13" s="40">
+        <v>-0.10299999999999999</v>
+      </c>
+      <c r="G13" s="16"/>
+      <c r="H13" s="36">
+        <v>-0.13700000000000001</v>
+      </c>
+      <c r="I13" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="16">
+        <v>-0.17899999999999999</v>
+      </c>
+      <c r="L13" s="40">
+        <v>-9.5000000000000001E-2</v>
+      </c>
+      <c r="N13" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="O13" s="36">
+        <v>0.24099999999999999</v>
+      </c>
+      <c r="P13" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="Q13" s="67" t="s">
+        <v>24</v>
+      </c>
+      <c r="R13" s="16">
         <v>0.19700000000000001</v>
       </c>
-      <c r="F13" s="40">
-        <v>0.28499999999999998</v>
-      </c>
-      <c r="H13" s="36"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="16"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="17" t="s">
+      <c r="S13" s="40">
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="T13" s="55"/>
+      <c r="U13" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="V13" s="36">
+        <v>-0.13100000000000001</v>
+      </c>
+      <c r="W13" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="X13" s="67" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y13" s="16">
+        <v>-0.17299999999999999</v>
+      </c>
+      <c r="Z13" s="16">
+        <v>-8.8999999999999996E-2</v>
+      </c>
+      <c r="AA13" s="51"/>
+      <c r="AB13"/>
+      <c r="AC13"/>
+      <c r="AD13"/>
+      <c r="AE13"/>
+      <c r="AF13"/>
+    </row>
+    <row r="14" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="B14" s="36">
+        <v>-2.1999999999999999E-2</v>
+      </c>
+      <c r="C14" s="16">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D14" s="18">
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="E14" s="16">
+        <v>-9.8000000000000004E-2</v>
+      </c>
+      <c r="F14" s="40">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="G14" s="16"/>
+      <c r="H14" s="36">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="I14" s="16">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="J14" s="18">
+        <v>0.42299999999999999</v>
+      </c>
+      <c r="K14" s="16">
+        <v>-4.7E-2</v>
+      </c>
+      <c r="L14" s="40">
+        <v>0.112</v>
+      </c>
+      <c r="N14" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
-      <c r="K14" s="16"/>
-    </row>
-    <row r="15" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+      <c r="O14" s="36"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="18"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="40"/>
+      <c r="T14" s="55"/>
+      <c r="U14" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="V14" s="36">
+        <v>-6.0000000000000001E-3</v>
+      </c>
+      <c r="W14" s="16">
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="X14" s="67">
+        <v>0.871</v>
+      </c>
+      <c r="Y14" s="16">
+        <v>-7.8E-2</v>
+      </c>
+      <c r="Z14" s="16">
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="AA14" s="51"/>
+      <c r="AB14"/>
+      <c r="AC14"/>
+      <c r="AD14"/>
+      <c r="AE14"/>
+      <c r="AF14"/>
+    </row>
+    <row r="15" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="B15" s="36">
-        <v>0.29499999999999998</v>
+        <v>-0.14399999999999999</v>
       </c>
       <c r="C15" s="16">
-        <v>4.1000000000000002E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E15" s="16">
-        <v>0.214</v>
+        <v>-0.186</v>
       </c>
       <c r="F15" s="40">
-        <v>0.376</v>
-      </c>
-      <c r="H15" s="36"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="16"/>
-    </row>
-    <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.25">
+        <v>-0.10199999999999999</v>
+      </c>
+      <c r="G15" s="16"/>
+      <c r="H15" s="36">
+        <v>-3.5999999999999997E-2</v>
+      </c>
+      <c r="I15" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="J15" s="18">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="K15" s="16">
+        <v>-7.6999999999999999E-2</v>
+      </c>
+      <c r="L15" s="40">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="M15"/>
+      <c r="N15" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="O15" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="P15" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q15" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="R15" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="S15" s="70" t="s">
+        <v>92</v>
+      </c>
+      <c r="T15" s="55"/>
+      <c r="U15" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="V15" s="36">
+        <v>-3.5999999999999997E-2</v>
+      </c>
+      <c r="W15" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="X15" s="67">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="Y15" s="16">
+        <v>-7.5999999999999998E-2</v>
+      </c>
+      <c r="Z15" s="16">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AA15" s="51"/>
+      <c r="AB15"/>
+      <c r="AC15"/>
+      <c r="AD15"/>
+      <c r="AE15"/>
+      <c r="AF15"/>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A16" s="16" t="s">
         <v>148</v>
       </c>
       <c r="B16" s="36">
-        <v>-0.14499999999999999</v>
+        <v>-0.16600000000000001</v>
       </c>
       <c r="C16" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="16">
+        <v>-0.20799999999999999</v>
+      </c>
+      <c r="F16" s="40">
+        <v>-0.124</v>
+      </c>
+      <c r="G16" s="16"/>
+      <c r="H16" s="36">
+        <v>-0.159</v>
+      </c>
+      <c r="I16" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="J16" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" s="16">
+        <v>-0.19700000000000001</v>
+      </c>
+      <c r="L16" s="40">
+        <v>-0.12</v>
+      </c>
+      <c r="M16"/>
+      <c r="N16" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="O16" s="36">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="P16" s="16">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="Q16" s="67" t="s">
+        <v>24</v>
+      </c>
+      <c r="R16" s="16">
+        <v>0.312</v>
+      </c>
+      <c r="S16" s="40">
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="T16" s="55"/>
+      <c r="U16" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="V16" s="36">
+        <v>-0.159</v>
+      </c>
+      <c r="W16" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="X16" s="67" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y16" s="16">
+        <v>-0.19800000000000001</v>
+      </c>
+      <c r="Z16" s="16">
+        <v>-0.121</v>
+      </c>
+      <c r="AA16" s="51"/>
+      <c r="AB16"/>
+      <c r="AC16"/>
+      <c r="AD16"/>
+      <c r="AE16"/>
+      <c r="AF16"/>
+    </row>
+    <row r="17" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="B17" s="36">
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="C17" s="16">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="16">
+        <v>0.129</v>
+      </c>
+      <c r="F17" s="40">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="G17" s="16"/>
+      <c r="H17" s="36">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="I17" s="16">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="D16" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="16">
-        <v>-0.187</v>
-      </c>
-      <c r="F16" s="40">
+      <c r="J17" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="16">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="L17" s="40">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="M17"/>
+      <c r="N17" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="O17" s="36">
+        <v>-0.112</v>
+      </c>
+      <c r="P17" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="Q17" s="67" t="s">
+        <v>24</v>
+      </c>
+      <c r="R17" s="16">
+        <v>-0.155</v>
+      </c>
+      <c r="S17" s="40">
+        <v>-6.9000000000000006E-2</v>
+      </c>
+      <c r="T17" s="55"/>
+      <c r="U17" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="V17" s="36">
+        <v>0.123</v>
+      </c>
+      <c r="W17" s="16">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="X17" s="67" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y17" s="16">
+        <v>7.1999999999999995E-2</v>
+      </c>
+      <c r="Z17" s="16">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="AA17" s="51"/>
+      <c r="AB17"/>
+      <c r="AC17"/>
+      <c r="AD17"/>
+      <c r="AE17"/>
+      <c r="AF17"/>
+    </row>
+    <row r="18" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+      <c r="A18" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="B18" s="36">
+        <v>1E-3</v>
+      </c>
+      <c r="C18" s="16">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="D18" s="18">
+        <v>0.98199999999999998</v>
+      </c>
+      <c r="E18" s="16">
+        <v>-8.2000000000000003E-2</v>
+      </c>
+      <c r="F18" s="40">
+        <v>8.4000000000000005E-2</v>
+      </c>
+      <c r="G18" s="16"/>
+      <c r="H18" s="36">
+        <v>-6.4000000000000001E-2</v>
+      </c>
+      <c r="I18" s="16">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="J18" s="18">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="K18" s="16">
+        <v>-0.151</v>
+      </c>
+      <c r="L18" s="40">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="M18"/>
+      <c r="N18" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="O18" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="P18" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q18" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="R18" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="S18" s="70" t="s">
+        <v>92</v>
+      </c>
+      <c r="T18" s="55"/>
+      <c r="U18" s="36" t="s">
+        <v>155</v>
+      </c>
+      <c r="V18" s="36">
+        <v>-2.7E-2</v>
+      </c>
+      <c r="W18" s="16">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="X18" s="67">
+        <v>0.53600000000000003</v>
+      </c>
+      <c r="Y18" s="16">
+        <v>-0.114</v>
+      </c>
+      <c r="Z18" s="16">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="AA18" s="51"/>
+      <c r="AB18"/>
+      <c r="AC18"/>
+      <c r="AD18"/>
+      <c r="AE18"/>
+      <c r="AF18"/>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A19" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="B19" s="36">
+        <v>1.6E-2</v>
+      </c>
+      <c r="C19" s="16">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="D19" s="18">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="E19" s="16">
+        <v>-3.2000000000000001E-2</v>
+      </c>
+      <c r="F19" s="40">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="G19" s="16"/>
+      <c r="H19" s="36">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="I19" s="16">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="J19" s="18">
+        <v>0.1</v>
+      </c>
+      <c r="K19" s="16">
+        <v>-8.9999999999999993E-3</v>
+      </c>
+      <c r="L19" s="40">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="M19"/>
+      <c r="N19" s="36" t="s">
+        <v>178</v>
+      </c>
+      <c r="O19" s="36">
+        <v>-0.13100000000000001</v>
+      </c>
+      <c r="P19" s="16">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="Q19" s="67" t="s">
+        <v>24</v>
+      </c>
+      <c r="R19" s="16">
+        <v>-0.2</v>
+      </c>
+      <c r="S19" s="40">
+        <v>-6.2E-2</v>
+      </c>
+      <c r="T19" s="55"/>
+      <c r="U19" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="V19" s="36">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="W19" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="X19" s="67">
+        <v>0.216</v>
+      </c>
+      <c r="Y19" s="16">
+        <v>-1.4999999999999999E-2</v>
+      </c>
+      <c r="Z19" s="16">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="AA19" s="51"/>
+      <c r="AB19"/>
+      <c r="AC19"/>
+      <c r="AD19"/>
+      <c r="AE19"/>
+      <c r="AF19"/>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A20" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="B20" s="36">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="C20" s="16">
+        <v>2.3E-2</v>
+      </c>
+      <c r="D20" s="18">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="E20" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="F20" s="40">
+        <v>0.11</v>
+      </c>
+      <c r="G20" s="16"/>
+      <c r="H20" s="36">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="I20" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="J20" s="18">
+        <v>0.1</v>
+      </c>
+      <c r="K20" s="16">
+        <v>0.105</v>
+      </c>
+      <c r="L20" s="40">
+        <v>0.186</v>
+      </c>
+      <c r="N20" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="O20" s="36">
+        <v>-0.14399999999999999</v>
+      </c>
+      <c r="P20" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="Q20" s="67" t="s">
+        <v>24</v>
+      </c>
+      <c r="R20" s="16">
+        <v>-0.186</v>
+      </c>
+      <c r="S20" s="40">
         <v>-0.10299999999999999</v>
       </c>
-      <c r="H16" s="36"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="16"/>
-    </row>
-    <row r="17" spans="1:12" ht="17" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
+      <c r="T20" s="55"/>
+      <c r="U20" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="V20" s="36">
+        <v>0.156</v>
+      </c>
+      <c r="W20" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="X20" s="67" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y20" s="16">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="Z20" s="16">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="AA20" s="51"/>
+      <c r="AB20"/>
+      <c r="AC20"/>
+      <c r="AD20"/>
+      <c r="AE20"/>
+      <c r="AF20"/>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A21" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B21" s="36">
+        <v>-0.12</v>
+      </c>
+      <c r="C21" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="16">
+        <v>-0.16200000000000001</v>
+      </c>
+      <c r="F21" s="40">
+        <v>-7.6999999999999999E-2</v>
+      </c>
+      <c r="G21" s="16"/>
+      <c r="H21" s="36">
+        <v>-7.9000000000000001E-2</v>
+      </c>
+      <c r="I21" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K21" s="16">
+        <v>-0.11899999999999999</v>
+      </c>
+      <c r="L21" s="40">
+        <v>-3.9E-2</v>
+      </c>
+      <c r="N21" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="O21" s="36">
+        <v>-0.16600000000000001</v>
+      </c>
+      <c r="P21" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="Q21" s="67" t="s">
+        <v>24</v>
+      </c>
+      <c r="R21" s="16">
+        <v>-0.20799999999999999</v>
+      </c>
+      <c r="S21" s="40">
+        <v>-0.124</v>
+      </c>
+      <c r="T21" s="55"/>
+      <c r="U21" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="V21" s="36">
+        <v>-8.2000000000000003E-2</v>
+      </c>
+      <c r="W21" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="X21" s="67" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y21" s="16">
+        <v>-0.122</v>
+      </c>
+      <c r="Z21" s="16">
+        <v>-4.2999999999999997E-2</v>
+      </c>
+      <c r="AA21" s="51"/>
+      <c r="AB21"/>
+      <c r="AC21"/>
+      <c r="AD21"/>
+      <c r="AE21"/>
+      <c r="AF21"/>
+    </row>
+    <row r="22" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+      <c r="A22" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" s="38"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="52"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="33"/>
+      <c r="N22" s="36" t="s">
         <v>149</v>
       </c>
-      <c r="B17" s="36">
-        <v>-2.1999999999999999E-2</v>
-      </c>
-      <c r="C17" s="16">
-        <v>3.9E-2</v>
-      </c>
-      <c r="D17" s="18">
-        <v>0.56699999999999995</v>
-      </c>
-      <c r="E17" s="16">
-        <v>-9.8000000000000004E-2</v>
-      </c>
-      <c r="F17" s="40">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="H17" s="36"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="16"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="16" t="s">
+      <c r="O22" s="36">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="P22" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="Q22" s="67" t="s">
+        <v>24</v>
+      </c>
+      <c r="R22" s="16">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="S22" s="40">
+        <v>0.183</v>
+      </c>
+      <c r="T22" s="55"/>
+      <c r="U22" s="66" t="s">
+        <v>114</v>
+      </c>
+      <c r="V22" s="38"/>
+      <c r="W22" s="14"/>
+      <c r="X22" s="52"/>
+      <c r="Y22" s="14"/>
+      <c r="Z22" s="33"/>
+      <c r="AA22" s="50"/>
+      <c r="AB22"/>
+      <c r="AC22"/>
+      <c r="AD22"/>
+      <c r="AE22"/>
+      <c r="AF22"/>
+    </row>
+    <row r="23" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+      <c r="A23" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" s="47">
+        <v>93579.540999999997</v>
+      </c>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="47">
+        <v>104772.751</v>
+      </c>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="48"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="36" t="s">
         <v>150</v>
       </c>
-      <c r="B18" s="36">
+      <c r="O23" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="P23" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q23" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="R23" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="S23" s="70" t="s">
+        <v>92</v>
+      </c>
+      <c r="T23" s="59"/>
+      <c r="U23" s="58" t="s">
+        <v>115</v>
+      </c>
+      <c r="V23" s="47">
+        <v>59389.061000000002</v>
+      </c>
+      <c r="W23" s="43"/>
+      <c r="X23" s="43"/>
+      <c r="Y23" s="43"/>
+      <c r="Z23" s="48"/>
+      <c r="AA23"/>
+      <c r="AB23"/>
+      <c r="AC23"/>
+      <c r="AD23"/>
+      <c r="AE23"/>
+      <c r="AF23"/>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A24" s="56"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="56"/>
+      <c r="D24" s="56"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="56"/>
+      <c r="J24" s="56"/>
+      <c r="K24" s="56"/>
+      <c r="L24" s="56"/>
+      <c r="M24" s="56"/>
+      <c r="N24" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="O24" s="36">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="P24" s="16">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="Q24" s="67">
+        <v>0.125</v>
+      </c>
+      <c r="R24" s="16">
+        <v>-0.02</v>
+      </c>
+      <c r="S24" s="40">
+        <v>0.161</v>
+      </c>
+      <c r="T24" s="56"/>
+      <c r="U24" s="56"/>
+      <c r="V24" s="56"/>
+      <c r="W24" s="56"/>
+      <c r="X24" s="56"/>
+      <c r="Y24" s="56"/>
+      <c r="Z24" s="56"/>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A25" s="56"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="56"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="56"/>
+      <c r="K25" s="56"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="56"/>
+      <c r="N25" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="O25" s="36">
+        <v>-1E-3</v>
+      </c>
+      <c r="P25" s="16">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Q25" s="67">
+        <v>0.96799999999999997</v>
+      </c>
+      <c r="R25" s="16">
+        <v>-5.7000000000000002E-2</v>
+      </c>
+      <c r="S25" s="40">
+        <v>5.5E-2</v>
+      </c>
+      <c r="T25" s="56"/>
+      <c r="U25" s="56"/>
+      <c r="V25" s="56"/>
+      <c r="W25" s="56"/>
+      <c r="X25" s="56"/>
+      <c r="Y25" s="56"/>
+      <c r="Z25" s="56"/>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A26" s="56"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="56"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="56"/>
+      <c r="H26" s="56"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="56"/>
+      <c r="K26" s="56"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="56"/>
+      <c r="N26" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="O26" s="36">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="P26" s="16">
+        <v>2.3E-2</v>
+      </c>
+      <c r="Q26" s="67">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="R26" s="16">
+        <v>2.3E-2</v>
+      </c>
+      <c r="S26" s="40">
+        <v>0.114</v>
+      </c>
+      <c r="T26" s="56"/>
+      <c r="U26" s="56"/>
+      <c r="V26" s="56"/>
+      <c r="W26" s="56"/>
+      <c r="X26" s="56"/>
+      <c r="Y26" s="56"/>
+      <c r="Z26" s="56"/>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A27" s="56"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="56"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="56"/>
+      <c r="H27" s="56"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="56"/>
+      <c r="K27" s="56"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="56"/>
+      <c r="N27" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="O27" s="39">
+        <v>-0.11799999999999999</v>
+      </c>
+      <c r="P27" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="Q27" s="67" t="s">
+        <v>24</v>
+      </c>
+      <c r="R27" s="16">
+        <v>-0.16200000000000001</v>
+      </c>
+      <c r="S27" s="34">
+        <v>-7.3999999999999996E-2</v>
+      </c>
+      <c r="T27" s="56"/>
+      <c r="U27" s="56"/>
+      <c r="V27" s="56"/>
+      <c r="W27" s="56"/>
+      <c r="X27" s="56"/>
+      <c r="Y27" s="56"/>
+      <c r="Z27" s="56"/>
+    </row>
+    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A28" s="56"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="56"/>
+      <c r="E28" s="56"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="56"/>
+      <c r="H28" s="56"/>
+      <c r="I28" s="56"/>
+      <c r="J28" s="56"/>
+      <c r="K28" s="56"/>
+      <c r="L28" s="56"/>
+      <c r="M28" s="56"/>
+      <c r="N28" s="66" t="s">
+        <v>114</v>
+      </c>
+      <c r="O28" s="38"/>
+      <c r="P28" s="14"/>
+      <c r="Q28" s="52"/>
+      <c r="R28" s="14"/>
+      <c r="S28" s="33"/>
+      <c r="T28" s="56"/>
+      <c r="U28" s="56"/>
+      <c r="V28" s="56"/>
+      <c r="W28" s="56"/>
+      <c r="X28" s="56"/>
+      <c r="Y28" s="56"/>
+      <c r="Z28" s="56"/>
+    </row>
+    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A29" s="56"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="56"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="56"/>
+      <c r="F29" s="55"/>
+      <c r="G29" s="56"/>
+      <c r="H29" s="56"/>
+      <c r="I29" s="56"/>
+      <c r="J29" s="56"/>
+      <c r="K29" s="56"/>
+      <c r="L29" s="56"/>
+      <c r="M29" s="56"/>
+      <c r="N29" s="58" t="s">
+        <v>115</v>
+      </c>
+      <c r="O29" s="47">
+        <v>54236.89</v>
+      </c>
+      <c r="P29" s="43"/>
+      <c r="Q29" s="43"/>
+      <c r="R29" s="43"/>
+      <c r="S29" s="48"/>
+      <c r="T29" s="56"/>
+      <c r="U29" s="56"/>
+      <c r="V29" s="56"/>
+      <c r="W29" s="56"/>
+      <c r="X29" s="56"/>
+      <c r="Y29" s="56"/>
+      <c r="Z29" s="56"/>
+    </row>
+    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A30" s="56"/>
+      <c r="B30" s="56"/>
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="55"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="56"/>
+      <c r="J30" s="56"/>
+      <c r="K30" s="56"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="56"/>
+      <c r="N30" s="56"/>
+      <c r="O30" s="56"/>
+      <c r="P30" s="56"/>
+      <c r="Q30" s="56"/>
+      <c r="R30" s="56"/>
+      <c r="S30" s="56"/>
+      <c r="T30" s="56"/>
+      <c r="U30" s="56"/>
+      <c r="V30" s="56"/>
+      <c r="W30" s="56"/>
+      <c r="X30" s="56"/>
+      <c r="Y30" s="56"/>
+      <c r="Z30" s="56"/>
+    </row>
+    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A31" s="56"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="56"/>
+      <c r="D31" s="56"/>
+      <c r="E31" s="56"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="56"/>
+      <c r="H31" s="56"/>
+      <c r="I31" s="56"/>
+      <c r="J31" s="56"/>
+      <c r="K31" s="56"/>
+      <c r="L31" s="56"/>
+      <c r="M31" s="56"/>
+      <c r="N31" s="56"/>
+      <c r="O31" s="56"/>
+      <c r="P31" s="56"/>
+      <c r="Q31" s="56"/>
+      <c r="R31" s="56"/>
+      <c r="S31" s="56"/>
+      <c r="T31" s="56"/>
+      <c r="U31" s="56"/>
+      <c r="V31" s="56"/>
+      <c r="W31" s="56"/>
+      <c r="X31" s="56"/>
+      <c r="Y31" s="56"/>
+      <c r="Z31" s="56"/>
+    </row>
+    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A32" s="56"/>
+      <c r="B32" s="56"/>
+      <c r="C32" s="56"/>
+      <c r="D32" s="56"/>
+      <c r="E32" s="56"/>
+      <c r="F32" s="55"/>
+      <c r="G32" s="56"/>
+      <c r="H32" s="56"/>
+      <c r="I32" s="56"/>
+      <c r="J32" s="56"/>
+      <c r="K32" s="56"/>
+      <c r="L32" s="56"/>
+      <c r="M32" s="56"/>
+      <c r="N32" s="56"/>
+      <c r="O32" s="56"/>
+      <c r="P32" s="56"/>
+      <c r="Q32" s="56"/>
+      <c r="R32" s="56"/>
+      <c r="S32" s="56"/>
+      <c r="T32" s="56"/>
+      <c r="U32" s="56"/>
+      <c r="V32" s="56"/>
+      <c r="W32" s="56"/>
+      <c r="X32" s="56"/>
+      <c r="Y32" s="56"/>
+      <c r="Z32" s="56"/>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A33" s="56"/>
+      <c r="B33" s="56"/>
+      <c r="C33" s="56"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="56"/>
+      <c r="H33" s="56"/>
+      <c r="I33" s="56"/>
+      <c r="J33" s="56"/>
+      <c r="K33" s="56"/>
+      <c r="L33" s="56"/>
+      <c r="M33" s="56"/>
+      <c r="N33" s="56"/>
+      <c r="O33" s="56"/>
+      <c r="P33" s="56"/>
+      <c r="Q33" s="56"/>
+      <c r="R33" s="56"/>
+      <c r="S33" s="56"/>
+      <c r="T33" s="56"/>
+      <c r="U33" s="56"/>
+      <c r="V33" s="56"/>
+      <c r="W33" s="56"/>
+      <c r="X33" s="56"/>
+      <c r="Y33" s="56"/>
+      <c r="Z33" s="56"/>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A34" s="56"/>
+      <c r="B34" s="56"/>
+      <c r="C34" s="56"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="56"/>
+      <c r="F34" s="55"/>
+      <c r="G34" s="56"/>
+      <c r="H34" s="56"/>
+      <c r="I34" s="56"/>
+      <c r="J34" s="56"/>
+      <c r="K34" s="56"/>
+      <c r="L34" s="56"/>
+      <c r="M34" s="56"/>
+      <c r="N34" s="50" t="s">
+        <v>179</v>
+      </c>
+      <c r="O34" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="P34" s="50" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q34" s="50" t="s">
+        <v>159</v>
+      </c>
+      <c r="R34" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="S34" s="50" t="s">
+        <v>132</v>
+      </c>
+      <c r="T34" s="56"/>
+      <c r="U34" s="56"/>
+      <c r="V34" s="56"/>
+      <c r="W34" s="56"/>
+      <c r="X34" s="56"/>
+      <c r="Y34" s="56"/>
+      <c r="Z34" s="56"/>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A35" s="56"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="56"/>
+      <c r="D35" s="56"/>
+      <c r="E35" s="56"/>
+      <c r="F35" s="55"/>
+      <c r="G35" s="56"/>
+      <c r="H35" s="56"/>
+      <c r="I35" s="56"/>
+      <c r="J35" s="56"/>
+      <c r="K35" s="56"/>
+      <c r="L35" s="56"/>
+      <c r="M35" s="56"/>
+      <c r="N35" s="50" t="s">
+        <v>164</v>
+      </c>
+      <c r="O35"/>
+      <c r="P35"/>
+      <c r="Q35"/>
+      <c r="R35"/>
+      <c r="S35"/>
+      <c r="T35" s="56"/>
+      <c r="U35" s="56"/>
+      <c r="V35" s="56"/>
+      <c r="W35" s="56"/>
+      <c r="X35" s="56"/>
+      <c r="Y35" s="56"/>
+      <c r="Z35" s="56"/>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A36" s="56"/>
+      <c r="B36" s="56"/>
+      <c r="C36" s="56"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="56"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="56"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="56"/>
+      <c r="J36" s="56"/>
+      <c r="K36" s="56"/>
+      <c r="L36" s="56"/>
+      <c r="M36" s="56"/>
+      <c r="N36" t="s">
+        <v>165</v>
+      </c>
+      <c r="O36">
+        <v>999</v>
+      </c>
+      <c r="P36">
+        <v>999</v>
+      </c>
+      <c r="Q36">
+        <v>999</v>
+      </c>
+      <c r="R36" t="s">
+        <v>180</v>
+      </c>
+      <c r="S36" t="s">
+        <v>180</v>
+      </c>
+      <c r="T36" s="56"/>
+      <c r="U36" s="56"/>
+      <c r="V36" s="56"/>
+      <c r="W36" s="56"/>
+      <c r="X36" s="56"/>
+      <c r="Y36" s="56"/>
+      <c r="Z36" s="56"/>
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A37" s="56"/>
+      <c r="B37" s="56"/>
+      <c r="C37" s="56"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="56"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="56"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="56"/>
+      <c r="J37" s="56"/>
+      <c r="K37" s="56"/>
+      <c r="L37" s="56"/>
+      <c r="M37" s="56"/>
+      <c r="N37" t="s">
+        <v>181</v>
+      </c>
+      <c r="O37">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="P37">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="Q37">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="R37">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="S37">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="T37" s="56"/>
+      <c r="U37" s="56"/>
+      <c r="V37" s="56"/>
+      <c r="W37" s="56"/>
+      <c r="X37" s="56"/>
+      <c r="Y37" s="56"/>
+      <c r="Z37" s="56"/>
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A38" s="56"/>
+      <c r="B38" s="56"/>
+      <c r="C38" s="56"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="56"/>
+      <c r="H38" s="56"/>
+      <c r="I38" s="56"/>
+      <c r="J38" s="56"/>
+      <c r="K38" s="56"/>
+      <c r="L38" s="56"/>
+      <c r="M38" s="56"/>
+      <c r="N38" t="s">
+        <v>167</v>
+      </c>
+      <c r="O38">
+        <v>0.01</v>
+      </c>
+      <c r="P38">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>24</v>
+      </c>
+      <c r="R38">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="S38">
+        <v>1.6E-2</v>
+      </c>
+      <c r="T38" s="56"/>
+      <c r="U38" s="56"/>
+      <c r="V38" s="56"/>
+      <c r="W38" s="56"/>
+      <c r="X38" s="56"/>
+      <c r="Y38" s="56"/>
+      <c r="Z38" s="56"/>
+    </row>
+    <row r="39" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A39" s="56"/>
+      <c r="B39" s="56"/>
+      <c r="C39" s="56"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="56"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="56"/>
+      <c r="H39" s="56"/>
+      <c r="I39" s="56"/>
+      <c r="J39" s="56"/>
+      <c r="K39" s="56"/>
+      <c r="L39" s="56"/>
+      <c r="M39" s="56"/>
+      <c r="N39" t="s">
+        <v>168</v>
+      </c>
+      <c r="O39">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="P39">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>24</v>
+      </c>
+      <c r="R39">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="S39">
+        <v>0.115</v>
+      </c>
+      <c r="T39" s="56"/>
+      <c r="U39" s="56"/>
+      <c r="V39" s="56"/>
+      <c r="W39" s="56"/>
+      <c r="X39" s="56"/>
+      <c r="Y39" s="56"/>
+      <c r="Z39" s="56"/>
+    </row>
+    <row r="40" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A40" s="56"/>
+      <c r="B40" s="56"/>
+      <c r="C40" s="56"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="56"/>
+      <c r="J40" s="56"/>
+      <c r="K40" s="56"/>
+      <c r="L40" s="56"/>
+      <c r="M40" s="56"/>
+      <c r="N40" t="s">
+        <v>182</v>
+      </c>
+      <c r="O40">
+        <v>999</v>
+      </c>
+      <c r="P40">
+        <v>999</v>
+      </c>
+      <c r="Q40">
+        <v>999</v>
+      </c>
+      <c r="R40" t="s">
+        <v>180</v>
+      </c>
+      <c r="S40" t="s">
+        <v>180</v>
+      </c>
+      <c r="T40" s="56"/>
+      <c r="U40" s="56"/>
+      <c r="V40" s="56"/>
+      <c r="W40" s="56"/>
+      <c r="X40" s="56"/>
+      <c r="Y40" s="56"/>
+      <c r="Z40" s="56"/>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A41" s="56"/>
+      <c r="B41" s="56"/>
+      <c r="C41" s="56"/>
+      <c r="D41" s="56"/>
+      <c r="E41" s="56"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="56"/>
+      <c r="H41" s="56"/>
+      <c r="I41" s="56"/>
+      <c r="J41" s="56"/>
+      <c r="K41" s="56"/>
+      <c r="L41" s="56"/>
+      <c r="M41" s="56"/>
+      <c r="N41" t="s">
+        <v>169</v>
+      </c>
+      <c r="O41">
+        <v>999</v>
+      </c>
+      <c r="P41">
+        <v>999</v>
+      </c>
+      <c r="Q41">
+        <v>999</v>
+      </c>
+      <c r="R41" t="s">
+        <v>180</v>
+      </c>
+      <c r="S41" t="s">
+        <v>180</v>
+      </c>
+      <c r="T41" s="56"/>
+      <c r="U41" s="56"/>
+      <c r="V41" s="56"/>
+      <c r="W41" s="56"/>
+      <c r="X41" s="56"/>
+      <c r="Y41" s="56"/>
+      <c r="Z41" s="56"/>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A42" s="56"/>
+      <c r="B42" s="56"/>
+      <c r="C42" s="56"/>
+      <c r="D42" s="56"/>
+      <c r="E42" s="56"/>
+      <c r="F42" s="55"/>
+      <c r="G42" s="56"/>
+      <c r="H42" s="56"/>
+      <c r="I42" s="56"/>
+      <c r="J42" s="56"/>
+      <c r="K42" s="56"/>
+      <c r="L42" s="56"/>
+      <c r="M42" s="56"/>
+      <c r="N42" t="s">
+        <v>183</v>
+      </c>
+      <c r="O42">
+        <v>0.01</v>
+      </c>
+      <c r="P42">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="Q42">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0.02</v>
+      </c>
+      <c r="T42" s="56"/>
+      <c r="U42" s="56"/>
+      <c r="V42" s="56"/>
+      <c r="W42" s="56"/>
+      <c r="X42" s="56"/>
+      <c r="Y42" s="56"/>
+      <c r="Z42" s="56"/>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A43" s="56"/>
+      <c r="B43" s="56"/>
+      <c r="C43" s="56"/>
+      <c r="D43" s="56"/>
+      <c r="E43" s="56"/>
+      <c r="F43" s="55"/>
+      <c r="G43" s="56"/>
+      <c r="H43" s="56"/>
+      <c r="I43" s="56"/>
+      <c r="J43" s="56"/>
+      <c r="K43" s="56"/>
+      <c r="L43" s="56"/>
+      <c r="M43" s="56"/>
+      <c r="N43" t="s">
+        <v>170</v>
+      </c>
+      <c r="O43">
+        <v>0.03</v>
+      </c>
+      <c r="P43">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>24</v>
+      </c>
+      <c r="R43">
+        <v>2.4E-2</v>
+      </c>
+      <c r="S43">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="T43" s="56"/>
+      <c r="U43" s="56"/>
+      <c r="V43" s="56"/>
+      <c r="W43" s="56"/>
+      <c r="X43" s="56"/>
+      <c r="Y43" s="56"/>
+      <c r="Z43" s="56"/>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A44" s="56"/>
+      <c r="B44" s="56"/>
+      <c r="C44" s="56"/>
+      <c r="D44" s="56"/>
+      <c r="E44" s="56"/>
+      <c r="F44" s="55"/>
+      <c r="G44" s="56"/>
+      <c r="H44" s="56"/>
+      <c r="I44" s="56"/>
+      <c r="J44" s="56"/>
+      <c r="K44" s="56"/>
+      <c r="L44" s="56"/>
+      <c r="M44" s="56"/>
+      <c r="N44" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="O44"/>
+      <c r="P44"/>
+      <c r="Q44"/>
+      <c r="R44"/>
+      <c r="S44"/>
+      <c r="T44" s="56"/>
+      <c r="U44" s="56"/>
+      <c r="V44" s="56"/>
+      <c r="W44" s="56"/>
+      <c r="X44" s="56"/>
+      <c r="Y44" s="56"/>
+      <c r="Z44" s="56"/>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A45" s="56"/>
+      <c r="B45" s="56"/>
+      <c r="C45" s="56"/>
+      <c r="D45" s="56"/>
+      <c r="E45" s="56"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="56"/>
+      <c r="H45" s="56"/>
+      <c r="I45" s="56"/>
+      <c r="J45" s="56"/>
+      <c r="K45" s="56"/>
+      <c r="L45" s="56"/>
+      <c r="M45" s="56"/>
+      <c r="N45" t="s">
+        <v>171</v>
+      </c>
+      <c r="O45">
+        <v>999</v>
+      </c>
+      <c r="P45">
+        <v>999</v>
+      </c>
+      <c r="Q45">
+        <v>999</v>
+      </c>
+      <c r="R45" t="s">
+        <v>180</v>
+      </c>
+      <c r="S45" t="s">
+        <v>180</v>
+      </c>
+      <c r="T45" s="56"/>
+      <c r="U45" s="56"/>
+      <c r="V45" s="56"/>
+      <c r="W45" s="56"/>
+      <c r="X45" s="56"/>
+      <c r="Y45" s="56"/>
+      <c r="Z45" s="56"/>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A46" s="56"/>
+      <c r="B46" s="56"/>
+      <c r="C46" s="56"/>
+      <c r="D46" s="56"/>
+      <c r="E46" s="56"/>
+      <c r="F46" s="55"/>
+      <c r="G46" s="56"/>
+      <c r="H46" s="56"/>
+      <c r="I46" s="56"/>
+      <c r="J46" s="56"/>
+      <c r="K46" s="56"/>
+      <c r="L46" s="56"/>
+      <c r="M46" s="56"/>
+      <c r="N46" t="s">
+        <v>184</v>
+      </c>
+      <c r="O46">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="P46">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>24</v>
+      </c>
+      <c r="R46">
+        <v>0.312</v>
+      </c>
+      <c r="S46">
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="T46" s="56"/>
+      <c r="U46" s="56"/>
+      <c r="V46" s="56"/>
+      <c r="W46" s="56"/>
+      <c r="X46" s="56"/>
+      <c r="Y46" s="56"/>
+      <c r="Z46" s="56"/>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A47" s="56"/>
+      <c r="B47" s="56"/>
+      <c r="C47" s="56"/>
+      <c r="D47" s="56"/>
+      <c r="E47" s="56"/>
+      <c r="F47" s="55"/>
+      <c r="G47" s="56"/>
+      <c r="H47" s="56"/>
+      <c r="I47" s="56"/>
+      <c r="J47" s="56"/>
+      <c r="K47" s="56"/>
+      <c r="L47" s="56"/>
+      <c r="M47" s="56"/>
+      <c r="N47" t="s">
+        <v>172</v>
+      </c>
+      <c r="O47">
+        <v>-0.112</v>
+      </c>
+      <c r="P47">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>24</v>
+      </c>
+      <c r="R47">
+        <v>-0.156</v>
+      </c>
+      <c r="S47">
+        <v>-6.8000000000000005E-2</v>
+      </c>
+      <c r="T47" s="56"/>
+      <c r="U47" s="56"/>
+      <c r="V47" s="56"/>
+      <c r="W47" s="56"/>
+      <c r="X47" s="56"/>
+      <c r="Y47" s="56"/>
+      <c r="Z47" s="56"/>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A48" s="56"/>
+      <c r="B48" s="56"/>
+      <c r="C48" s="56"/>
+      <c r="D48" s="56"/>
+      <c r="E48" s="56"/>
+      <c r="F48" s="55"/>
+      <c r="G48" s="56"/>
+      <c r="H48" s="56"/>
+      <c r="I48" s="56"/>
+      <c r="J48" s="56"/>
+      <c r="K48" s="56"/>
+      <c r="L48" s="56"/>
+      <c r="M48" s="56"/>
+      <c r="N48" t="s">
+        <v>173</v>
+      </c>
+      <c r="O48">
+        <v>999</v>
+      </c>
+      <c r="P48">
+        <v>999</v>
+      </c>
+      <c r="Q48"/>
+      <c r="R48"/>
+      <c r="S48"/>
+      <c r="T48" s="56"/>
+      <c r="U48" s="56"/>
+      <c r="V48" s="56"/>
+      <c r="W48" s="56"/>
+      <c r="X48" s="56"/>
+      <c r="Y48" s="56"/>
+      <c r="Z48" s="56"/>
+    </row>
+    <row r="49" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A49" s="56"/>
+      <c r="B49" s="56"/>
+      <c r="C49" s="56"/>
+      <c r="D49" s="56"/>
+      <c r="E49" s="56"/>
+      <c r="F49" s="55"/>
+      <c r="G49" s="56"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="56"/>
+      <c r="J49" s="56"/>
+      <c r="K49" s="56"/>
+      <c r="L49" s="56"/>
+      <c r="M49" s="56"/>
+      <c r="N49" t="s">
+        <v>185</v>
+      </c>
+      <c r="O49">
+        <v>-0.13100000000000001</v>
+      </c>
+      <c r="P49">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>24</v>
+      </c>
+      <c r="R49">
+        <v>-0.19900000000000001</v>
+      </c>
+      <c r="S49">
+        <v>-6.3E-2</v>
+      </c>
+      <c r="T49" s="56"/>
+      <c r="U49" s="56"/>
+      <c r="V49" s="56"/>
+      <c r="W49" s="56"/>
+      <c r="X49" s="56"/>
+      <c r="Y49" s="56"/>
+      <c r="Z49" s="56"/>
+    </row>
+    <row r="50" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A50" s="56"/>
+      <c r="B50" s="56"/>
+      <c r="C50" s="56"/>
+      <c r="D50" s="56"/>
+      <c r="E50" s="56"/>
+      <c r="F50" s="55"/>
+      <c r="G50" s="56"/>
+      <c r="H50" s="56"/>
+      <c r="I50" s="56"/>
+      <c r="J50" s="56"/>
+      <c r="K50" s="56"/>
+      <c r="L50" s="56"/>
+      <c r="M50" s="56"/>
+      <c r="N50" t="s">
+        <v>174</v>
+      </c>
+      <c r="O50">
         <v>-0.14399999999999999</v>
       </c>
-      <c r="C18" s="16">
+      <c r="P50">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="D18" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="16">
+      <c r="Q50" t="s">
+        <v>24</v>
+      </c>
+      <c r="R50">
         <v>-0.186</v>
       </c>
-      <c r="F18" s="40">
+      <c r="S50">
         <v>-0.10199999999999999</v>
       </c>
-      <c r="H18" s="36"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="16"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="B19" s="36">
+      <c r="T50" s="56"/>
+      <c r="U50" s="56"/>
+      <c r="V50" s="56"/>
+      <c r="W50" s="56"/>
+      <c r="X50" s="56"/>
+      <c r="Y50" s="56"/>
+      <c r="Z50" s="56"/>
+    </row>
+    <row r="51" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A51" s="56"/>
+      <c r="B51" s="56"/>
+      <c r="C51" s="56"/>
+      <c r="D51" s="56"/>
+      <c r="E51" s="56"/>
+      <c r="F51" s="55"/>
+      <c r="G51" s="56"/>
+      <c r="H51" s="56"/>
+      <c r="I51" s="56"/>
+      <c r="J51" s="56"/>
+      <c r="K51" s="56"/>
+      <c r="L51" s="56"/>
+      <c r="M51" s="56"/>
+      <c r="N51" t="s">
+        <v>175</v>
+      </c>
+      <c r="O51">
         <v>-0.16600000000000001</v>
       </c>
-      <c r="C19" s="16">
+      <c r="P51">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="D19" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="16">
+      <c r="Q51" t="s">
+        <v>24</v>
+      </c>
+      <c r="R51">
         <v>-0.20799999999999999</v>
       </c>
-      <c r="F19" s="40">
+      <c r="S51">
         <v>-0.124</v>
       </c>
-      <c r="H19" s="36"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="16"/>
-    </row>
-    <row r="20" spans="1:12" ht="17" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="B20" s="36">
-        <v>0.17899999999999999</v>
-      </c>
-      <c r="C20" s="16">
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="16">
-        <v>0.129</v>
-      </c>
-      <c r="F20" s="40">
-        <v>0.22900000000000001</v>
-      </c>
-      <c r="H20" s="36"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="16"/>
-    </row>
-    <row r="21" spans="1:12" ht="17" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="B21" s="36">
-        <v>1E-3</v>
-      </c>
-      <c r="C21" s="16">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="D21" s="18">
-        <v>0.98199999999999998</v>
-      </c>
-      <c r="E21" s="16">
-        <v>-8.2000000000000003E-2</v>
-      </c>
-      <c r="F21" s="40">
-        <v>8.4000000000000005E-2</v>
-      </c>
-      <c r="H21" s="36"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="18"/>
-      <c r="K21" s="16"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="B22" s="36">
-        <v>1.6E-2</v>
-      </c>
-      <c r="C22" s="16">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="D22" s="18">
-        <v>0.51500000000000001</v>
-      </c>
-      <c r="E22" s="16">
-        <v>-3.2000000000000001E-2</v>
-      </c>
-      <c r="F22" s="40">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="H22" s="36"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="18"/>
-      <c r="K22" s="16"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="B23" s="36">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="C23" s="16">
+      <c r="T51" s="56"/>
+      <c r="U51" s="56"/>
+      <c r="V51" s="56"/>
+      <c r="W51" s="56"/>
+      <c r="X51" s="56"/>
+      <c r="Y51" s="56"/>
+      <c r="Z51" s="56"/>
+    </row>
+    <row r="52" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A52" s="56"/>
+      <c r="B52" s="56"/>
+      <c r="C52" s="56"/>
+      <c r="D52" s="56"/>
+      <c r="E52" s="56"/>
+      <c r="F52" s="55"/>
+      <c r="G52" s="56"/>
+      <c r="H52" s="56"/>
+      <c r="I52" s="56"/>
+      <c r="J52" s="56"/>
+      <c r="K52" s="56"/>
+      <c r="L52" s="56"/>
+      <c r="M52" s="56"/>
+      <c r="N52" t="s">
+        <v>186</v>
+      </c>
+      <c r="O52">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="P52">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>24</v>
+      </c>
+      <c r="R52">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="S52">
+        <v>0.183</v>
+      </c>
+      <c r="T52" s="56"/>
+      <c r="U52" s="56"/>
+      <c r="V52" s="56"/>
+      <c r="W52" s="56"/>
+      <c r="X52" s="56"/>
+      <c r="Y52" s="56"/>
+      <c r="Z52" s="56"/>
+    </row>
+    <row r="53" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A53" s="56"/>
+      <c r="B53" s="56"/>
+      <c r="C53" s="56"/>
+      <c r="D53" s="56"/>
+      <c r="E53" s="56"/>
+      <c r="F53" s="55"/>
+      <c r="G53" s="56"/>
+      <c r="H53" s="56"/>
+      <c r="I53" s="56"/>
+      <c r="J53" s="56"/>
+      <c r="K53" s="56"/>
+      <c r="L53" s="56"/>
+      <c r="M53" s="56"/>
+      <c r="N53" t="s">
+        <v>187</v>
+      </c>
+      <c r="O53">
+        <v>999</v>
+      </c>
+      <c r="P53">
+        <v>999</v>
+      </c>
+      <c r="Q53">
+        <v>999</v>
+      </c>
+      <c r="R53" t="s">
+        <v>180</v>
+      </c>
+      <c r="S53" t="s">
+        <v>180</v>
+      </c>
+      <c r="T53" s="56"/>
+      <c r="U53" s="56"/>
+      <c r="V53" s="56"/>
+      <c r="W53" s="56"/>
+      <c r="X53" s="56"/>
+      <c r="Y53" s="56"/>
+      <c r="Z53" s="56"/>
+    </row>
+    <row r="54" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A54" s="56"/>
+      <c r="B54" s="56"/>
+      <c r="C54" s="56"/>
+      <c r="D54" s="56"/>
+      <c r="E54" s="56"/>
+      <c r="F54" s="55"/>
+      <c r="G54" s="56"/>
+      <c r="H54" s="56"/>
+      <c r="I54" s="56"/>
+      <c r="J54" s="56"/>
+      <c r="K54" s="56"/>
+      <c r="L54" s="56"/>
+      <c r="M54" s="56"/>
+      <c r="N54" t="s">
+        <v>188</v>
+      </c>
+      <c r="O54">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="P54">
+        <v>4.5999999999999999E-2</v>
+      </c>
+      <c r="Q54">
+        <v>0.125</v>
+      </c>
+      <c r="R54">
+        <v>-1.9E-2</v>
+      </c>
+      <c r="S54">
+        <v>0.161</v>
+      </c>
+      <c r="T54" s="56"/>
+      <c r="U54" s="56"/>
+      <c r="V54" s="56"/>
+      <c r="W54" s="56"/>
+      <c r="X54" s="56"/>
+      <c r="Y54" s="56"/>
+      <c r="Z54" s="56"/>
+    </row>
+    <row r="55" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A55" s="56"/>
+      <c r="B55" s="56"/>
+      <c r="C55" s="56"/>
+      <c r="D55" s="56"/>
+      <c r="E55" s="56"/>
+      <c r="F55" s="55"/>
+      <c r="G55" s="56"/>
+      <c r="H55" s="56"/>
+      <c r="I55" s="56"/>
+      <c r="J55" s="56"/>
+      <c r="K55" s="56"/>
+      <c r="L55" s="56"/>
+      <c r="M55" s="56"/>
+      <c r="N55" t="s">
+        <v>189</v>
+      </c>
+      <c r="O55">
+        <v>-1E-3</v>
+      </c>
+      <c r="P55">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Q55">
+        <v>0.96799999999999997</v>
+      </c>
+      <c r="R55">
+        <v>-5.7000000000000002E-2</v>
+      </c>
+      <c r="S55">
+        <v>5.5E-2</v>
+      </c>
+      <c r="T55" s="56"/>
+      <c r="U55" s="56"/>
+      <c r="V55" s="56"/>
+      <c r="W55" s="56"/>
+      <c r="X55" s="56"/>
+      <c r="Y55" s="56"/>
+      <c r="Z55" s="56"/>
+    </row>
+    <row r="56" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A56" s="56"/>
+      <c r="B56" s="56"/>
+      <c r="C56" s="56"/>
+      <c r="D56" s="56"/>
+      <c r="E56" s="56"/>
+      <c r="F56" s="55"/>
+      <c r="G56" s="56"/>
+      <c r="H56" s="56"/>
+      <c r="I56" s="56"/>
+      <c r="J56" s="56"/>
+      <c r="K56" s="56"/>
+      <c r="L56" s="56"/>
+      <c r="M56" s="56"/>
+      <c r="N56" t="s">
+        <v>190</v>
+      </c>
+      <c r="O56">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="P56">
         <v>2.3E-2</v>
       </c>
-      <c r="D23" s="18">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="E23" s="16">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="F23" s="40">
-        <v>0.11</v>
-      </c>
-      <c r="H23" s="36"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="18"/>
-      <c r="K23" s="16"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="B24" s="36">
-        <v>-0.12</v>
-      </c>
-      <c r="C24" s="16">
+      <c r="Q56">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="R56">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="D24" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="16">
+      <c r="S56">
+        <v>0.114</v>
+      </c>
+      <c r="T56" s="56"/>
+      <c r="U56" s="56"/>
+      <c r="V56" s="56"/>
+      <c r="W56" s="56"/>
+      <c r="X56" s="56"/>
+      <c r="Y56" s="56"/>
+      <c r="Z56" s="56"/>
+    </row>
+    <row r="57" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A57" s="56"/>
+      <c r="B57" s="56"/>
+      <c r="C57" s="56"/>
+      <c r="D57" s="56"/>
+      <c r="E57" s="56"/>
+      <c r="F57" s="55"/>
+      <c r="G57" s="56"/>
+      <c r="H57" s="56"/>
+      <c r="I57" s="56"/>
+      <c r="J57" s="56"/>
+      <c r="K57" s="56"/>
+      <c r="L57" s="56"/>
+      <c r="M57" s="56"/>
+      <c r="N57" t="s">
+        <v>191</v>
+      </c>
+      <c r="O57">
+        <v>-0.11799999999999999</v>
+      </c>
+      <c r="P57">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>24</v>
+      </c>
+      <c r="R57">
         <v>-0.16200000000000001</v>
       </c>
-      <c r="F24" s="40">
-        <v>-7.6999999999999999E-2</v>
-      </c>
-      <c r="H24" s="36"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="18"/>
-      <c r="K24" s="16"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="B25" s="36"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="16"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="B26" s="36">
-        <v>12.734</v>
-      </c>
-      <c r="C26" s="16">
-        <v>0.17599999999999999</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="16">
-        <v>12.388999999999999</v>
-      </c>
-      <c r="F26" s="40">
-        <v>13.079000000000001</v>
-      </c>
-      <c r="H26" s="36"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="18"/>
-      <c r="K26" s="16"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="B27" s="36">
-        <v>4.5759999999999996</v>
-      </c>
-      <c r="C27" s="16">
-        <v>7.2999999999999995E-2</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="16">
-        <v>4.4340000000000002</v>
-      </c>
-      <c r="F27" s="40">
-        <v>4.718</v>
-      </c>
-      <c r="H27" s="36"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="18"/>
-      <c r="K27" s="16"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="B28" s="36">
-        <v>1.012</v>
-      </c>
-      <c r="C28" s="16">
-        <v>1.7999999999999999E-2</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="16">
-        <v>0.97799999999999998</v>
-      </c>
-      <c r="F28" s="40">
-        <v>1.0469999999999999</v>
-      </c>
-      <c r="H28" s="36"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="18"/>
-      <c r="K28" s="16"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="B29" s="36">
-        <v>4.0510000000000002</v>
-      </c>
-      <c r="C29" s="16">
-        <v>0.45200000000000001</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" s="16">
-        <v>3.165</v>
-      </c>
-      <c r="F29" s="40">
-        <v>4.9379999999999997</v>
-      </c>
-      <c r="H29" s="36"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="18"/>
-      <c r="K29" s="16"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="B30" s="38"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="33"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="B31" s="46">
-        <v>93579.540999999997</v>
-      </c>
-      <c r="C31" s="43"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="34"/>
+      <c r="S57">
+        <v>-7.3999999999999996E-2</v>
+      </c>
+      <c r="T57" s="56"/>
+      <c r="U57" s="56"/>
+      <c r="V57" s="56"/>
+      <c r="W57" s="56"/>
+      <c r="X57" s="56"/>
+      <c r="Y57" s="56"/>
+      <c r="Z57" s="56"/>
+    </row>
+    <row r="58" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A58" s="56"/>
+      <c r="B58" s="56"/>
+      <c r="C58" s="56"/>
+      <c r="D58" s="56"/>
+      <c r="E58" s="56"/>
+      <c r="F58" s="55"/>
+      <c r="G58" s="56"/>
+      <c r="H58" s="56"/>
+      <c r="I58" s="56"/>
+      <c r="J58" s="56"/>
+      <c r="K58" s="56"/>
+      <c r="L58" s="56"/>
+      <c r="M58" s="56"/>
+      <c r="N58" s="56"/>
+      <c r="O58" s="56"/>
+      <c r="P58" s="56"/>
+      <c r="Q58" s="56"/>
+      <c r="R58" s="56"/>
+      <c r="S58" s="56"/>
+      <c r="T58" s="56"/>
+      <c r="U58" s="56"/>
+      <c r="V58" s="56"/>
+      <c r="W58" s="56"/>
+      <c r="X58" s="56"/>
+      <c r="Y58" s="56"/>
+      <c r="Z58" s="56"/>
+    </row>
+    <row r="59" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A59" s="56"/>
+      <c r="B59" s="56"/>
+      <c r="C59" s="56"/>
+      <c r="D59" s="56"/>
+      <c r="E59" s="56"/>
+      <c r="F59" s="55"/>
+      <c r="G59" s="56"/>
+      <c r="H59" s="56"/>
+      <c r="I59" s="56"/>
+      <c r="J59" s="56"/>
+      <c r="K59" s="56"/>
+      <c r="L59" s="56"/>
+      <c r="M59" s="56"/>
+      <c r="N59" s="56"/>
+      <c r="O59" s="56"/>
+      <c r="P59" s="56"/>
+      <c r="Q59" s="56"/>
+      <c r="R59" s="56"/>
+      <c r="S59" s="56"/>
+      <c r="T59" s="56"/>
+      <c r="U59" s="56"/>
+      <c r="V59" s="56"/>
+      <c r="W59" s="56"/>
+      <c r="X59" s="56"/>
+      <c r="Y59" s="56"/>
+      <c r="Z59" s="56"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="H2:L2"/>
+  <mergeCells count="10">
+    <mergeCell ref="O29:S29"/>
+    <mergeCell ref="O2:Z2"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="V3:Z3"/>
+    <mergeCell ref="V23:Z23"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="H23:L23"/>
+    <mergeCell ref="B2:L2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmoffice-my.sharepoint.com/personal/abrieant_uvm_edu/Documents/OneDrive/Manuscripts/reg report DCN/pubertybrain/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="436" documentId="13_ncr:1_{2DBDCA32-700C-9942-8973-B738A2BA3D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63DC9486-4C66-1646-B674-F3EAD1E5581C}"/>
+  <xr:revisionPtr revIDLastSave="460" documentId="13_ncr:1_{2DBDCA32-700C-9942-8973-B738A2BA3D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C60FEBB-D1DE-6E46-974E-69E73352881B}"/>
   <bookViews>
-    <workbookView xWindow="15860" yWindow="500" windowWidth="31800" windowHeight="17500" activeTab="8" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="8" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptive table" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="163">
   <si>
     <t>16.10 (2.98)</t>
   </si>
@@ -884,45 +884,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">   WM on Intercept</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>b</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">   WM on Slope</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>b</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">   WM on Timing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   WM on Tempo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   WM on ELA</t>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">   Intercept</t>
     </r>
     <r>
@@ -979,9 +940,6 @@
     <t xml:space="preserve">   Tempo on WM</t>
   </si>
   <si>
-    <t>p</t>
-  </si>
-  <si>
     <t>Estimate</t>
   </si>
   <si>
@@ -994,40 +952,7 @@
     <t>Models with subcortical gray matter volume</t>
   </si>
   <si>
-    <t>Covariances</t>
-  </si>
-  <si>
-    <t>Interceptb with Slopeb</t>
-  </si>
-  <si>
     <t>&lt; 0.001</t>
-  </si>
-  <si>
-    <t>Interceptb with Timing</t>
-  </si>
-  <si>
-    <t>Interceptb with Tempo</t>
-  </si>
-  <si>
-    <t>Slopeb with Tempo</t>
-  </si>
-  <si>
-    <t>Timing with Tempo</t>
-  </si>
-  <si>
-    <t>Timing on Slopeb</t>
-  </si>
-  <si>
-    <t>ELA on Interceptb</t>
-  </si>
-  <si>
-    <t>ELA on Slopeb</t>
-  </si>
-  <si>
-    <t>ELA on Timing</t>
-  </si>
-  <si>
-    <t>ELA on Tempo</t>
   </si>
   <si>
     <r>
@@ -1091,43 +1016,7 @@
     <t xml:space="preserve">   ELA on Quadratic Slope</t>
   </si>
   <si>
-    <t>Row</t>
-  </si>
-  <si>
-    <t>–</t>
-  </si>
-  <si>
-    <t>Interceptb with Quadratic Slopeb</t>
-  </si>
-  <si>
-    <t>Slopeb with Quadratic Slopeb</t>
-  </si>
-  <si>
-    <t>Quadratic Slopeb with Tempo</t>
-  </si>
-  <si>
-    <t>Timing on Quadratic Slope</t>
-  </si>
-  <si>
-    <t>ELA on Quadratic Slope</t>
-  </si>
-  <si>
-    <t>WM on Interceptb</t>
-  </si>
-  <si>
-    <t>WM on Slopeb</t>
-  </si>
-  <si>
-    <t>WM on Quadratic Slope</t>
-  </si>
-  <si>
-    <t>WM on Timing</t>
-  </si>
-  <si>
-    <t>WM on Tempo</t>
-  </si>
-  <si>
-    <t>WM on ELA</t>
+    <t xml:space="preserve">   Quadratic Slope on WM</t>
   </si>
 </sst>
 </file>
@@ -1252,7 +1141,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1262,12 +1151,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1476,10 +1359,6 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1494,7 +1373,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1528,13 +1406,15 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1554,6 +1434,9 @@
     </xf>
     <xf numFmtId="11" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2713,190 +2596,190 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="38"/>
+      <c r="R2" s="38"/>
       <c r="S2" s="9"/>
-      <c r="T2" s="41" t="s">
+      <c r="T2" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="U2" s="41"/>
-      <c r="V2" s="41"/>
-      <c r="W2" s="41"/>
-      <c r="X2" s="41"/>
-      <c r="Y2" s="41"/>
-      <c r="Z2" s="41"/>
-      <c r="AA2" s="41"/>
-      <c r="AB2" s="41"/>
-      <c r="AC2" s="41"/>
-      <c r="AD2" s="41"/>
-      <c r="AE2" s="41"/>
-      <c r="AF2" s="41"/>
-      <c r="AG2" s="41"/>
-      <c r="AH2" s="41"/>
-      <c r="AI2" s="41"/>
-      <c r="AJ2" s="41"/>
+      <c r="U2" s="38"/>
+      <c r="V2" s="38"/>
+      <c r="W2" s="38"/>
+      <c r="X2" s="38"/>
+      <c r="Y2" s="38"/>
+      <c r="Z2" s="38"/>
+      <c r="AA2" s="38"/>
+      <c r="AB2" s="38"/>
+      <c r="AC2" s="38"/>
+      <c r="AD2" s="38"/>
+      <c r="AE2" s="38"/>
+      <c r="AF2" s="38"/>
+      <c r="AG2" s="38"/>
+      <c r="AH2" s="38"/>
+      <c r="AI2" s="38"/>
+      <c r="AJ2" s="38"/>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A3" s="16"/>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="41" t="s">
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="41" t="s">
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="41"/>
-      <c r="T3" s="42" t="s">
+      <c r="O3" s="38"/>
+      <c r="P3" s="38"/>
+      <c r="Q3" s="38"/>
+      <c r="R3" s="38"/>
+      <c r="T3" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="U3" s="42"/>
-      <c r="V3" s="42"/>
-      <c r="W3" s="42"/>
-      <c r="X3" s="42"/>
-      <c r="Y3" s="28"/>
-      <c r="Z3" s="41" t="s">
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="39"/>
+      <c r="Y3" s="26"/>
+      <c r="Z3" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="AA3" s="41"/>
-      <c r="AB3" s="41"/>
-      <c r="AC3" s="41"/>
-      <c r="AD3" s="41"/>
-      <c r="AE3" s="28"/>
-      <c r="AF3" s="41" t="s">
+      <c r="AA3" s="38"/>
+      <c r="AB3" s="38"/>
+      <c r="AC3" s="38"/>
+      <c r="AD3" s="38"/>
+      <c r="AE3" s="26"/>
+      <c r="AF3" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="AG3" s="41"/>
-      <c r="AH3" s="41"/>
-      <c r="AI3" s="41"/>
-      <c r="AJ3" s="41"/>
+      <c r="AG3" s="38"/>
+      <c r="AH3" s="38"/>
+      <c r="AI3" s="38"/>
+      <c r="AJ3" s="38"/>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
-      <c r="B4" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="C4" s="29" t="s">
+      <c r="B4" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="27" t="s">
         <v>132</v>
       </c>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="I4" s="29" t="s">
+      <c r="G4" s="27"/>
+      <c r="H4" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="I4" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="J4" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="L4" s="29" t="s">
+      <c r="L4" s="27" t="s">
         <v>132</v>
       </c>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="O4" s="29" t="s">
+      <c r="M4" s="27"/>
+      <c r="N4" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="O4" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="P4" s="29" t="s">
+      <c r="P4" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="Q4" s="29" t="s">
+      <c r="Q4" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="R4" s="29" t="s">
+      <c r="R4" s="27" t="s">
         <v>132</v>
       </c>
       <c r="S4" s="6"/>
-      <c r="T4" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="U4" s="29" t="s">
+      <c r="T4" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="U4" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="V4" s="29" t="s">
+      <c r="V4" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="W4" s="29" t="s">
+      <c r="W4" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="X4" s="29" t="s">
+      <c r="X4" s="27" t="s">
         <v>132</v>
       </c>
       <c r="Y4" s="17"/>
-      <c r="Z4" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="AA4" s="29" t="s">
+      <c r="Z4" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="AA4" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="AB4" s="29" t="s">
+      <c r="AB4" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="AC4" s="29" t="s">
+      <c r="AC4" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="AD4" s="29" t="s">
+      <c r="AD4" s="27" t="s">
         <v>132</v>
       </c>
       <c r="AE4" s="17"/>
-      <c r="AF4" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="AG4" s="29" t="s">
+      <c r="AF4" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="AG4" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="AH4" s="29" t="s">
+      <c r="AH4" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="AI4" s="29" t="s">
+      <c r="AI4" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="AJ4" s="29" t="s">
+      <c r="AJ4" s="27" t="s">
         <v>132</v>
       </c>
     </row>
@@ -3885,7 +3768,7 @@
     </row>
     <row r="18" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>92</v>
@@ -3984,7 +3867,7 @@
     </row>
     <row r="19" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>101</v>
+        <v>146</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>92</v>
@@ -4077,13 +3960,13 @@
       <c r="AI19" s="16">
         <v>-4.2999999999999997E-2</v>
       </c>
-      <c r="AJ19" s="30">
+      <c r="AJ19" s="28">
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="B20" s="16" t="s">
         <v>92</v>
@@ -4182,7 +4065,7 @@
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="B21" s="16" t="s">
         <v>92</v>
@@ -4281,7 +4164,7 @@
     </row>
     <row r="22" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>102</v>
+        <v>149</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>92</v>
@@ -4378,7 +4261,7 @@
     </row>
     <row r="23" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>103</v>
+        <v>150</v>
       </c>
       <c r="B23" s="16" t="s">
         <v>92</v>
@@ -4475,7 +4358,7 @@
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="B24" s="16" t="s">
         <v>92</v>
@@ -4572,7 +4455,7 @@
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A25" s="16" t="s">
-        <v>106</v>
+        <v>153</v>
       </c>
       <c r="B25" s="16" t="s">
         <v>92</v>
@@ -4669,7 +4552,7 @@
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
-        <v>108</v>
+        <v>151</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>92</v>
@@ -5281,53 +5164,53 @@
       <c r="A34" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="B34" s="43">
+      <c r="B34" s="40">
         <v>74058.118000000002</v>
       </c>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="43">
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="40">
         <v>83016.937999999995</v>
       </c>
-      <c r="I34" s="43"/>
-      <c r="J34" s="43"/>
-      <c r="K34" s="43"/>
-      <c r="L34" s="43"/>
-      <c r="M34" s="27"/>
-      <c r="N34" s="43">
+      <c r="I34" s="40"/>
+      <c r="J34" s="40"/>
+      <c r="K34" s="40"/>
+      <c r="L34" s="40"/>
+      <c r="M34" s="25"/>
+      <c r="N34" s="40">
         <v>94345.274999999994</v>
       </c>
-      <c r="O34" s="43"/>
-      <c r="P34" s="43"/>
-      <c r="Q34" s="43"/>
-      <c r="R34" s="43"/>
+      <c r="O34" s="40"/>
+      <c r="P34" s="40"/>
+      <c r="Q34" s="40"/>
+      <c r="R34" s="40"/>
       <c r="S34" s="15"/>
-      <c r="T34" s="43">
+      <c r="T34" s="40">
         <v>83167.763000000006</v>
       </c>
-      <c r="U34" s="43"/>
-      <c r="V34" s="43"/>
-      <c r="W34" s="43"/>
-      <c r="X34" s="43"/>
-      <c r="Y34" s="27"/>
-      <c r="Z34" s="43">
+      <c r="U34" s="40"/>
+      <c r="V34" s="40"/>
+      <c r="W34" s="40"/>
+      <c r="X34" s="40"/>
+      <c r="Y34" s="25"/>
+      <c r="Z34" s="40">
         <v>93083.505999999994</v>
       </c>
-      <c r="AA34" s="43"/>
-      <c r="AB34" s="43"/>
-      <c r="AC34" s="43"/>
-      <c r="AD34" s="43"/>
-      <c r="AE34" s="27"/>
-      <c r="AF34" s="43">
+      <c r="AA34" s="40"/>
+      <c r="AB34" s="40"/>
+      <c r="AC34" s="40"/>
+      <c r="AD34" s="40"/>
+      <c r="AE34" s="25"/>
+      <c r="AF34" s="40">
         <v>105770.462</v>
       </c>
-      <c r="AG34" s="43"/>
-      <c r="AH34" s="43"/>
-      <c r="AI34" s="43"/>
-      <c r="AJ34" s="43"/>
+      <c r="AG34" s="40"/>
+      <c r="AH34" s="40"/>
+      <c r="AI34" s="40"/>
+      <c r="AJ34" s="40"/>
       <c r="AK34" s="16"/>
       <c r="AL34" s="16"/>
       <c r="AM34" s="16"/>
@@ -5401,190 +5284,190 @@
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="38"/>
+      <c r="R2" s="38"/>
       <c r="S2" s="9"/>
-      <c r="T2" s="41" t="s">
+      <c r="T2" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="U2" s="41"/>
-      <c r="V2" s="41"/>
-      <c r="W2" s="41"/>
-      <c r="X2" s="41"/>
-      <c r="Y2" s="41"/>
-      <c r="Z2" s="41"/>
-      <c r="AA2" s="41"/>
-      <c r="AB2" s="41"/>
-      <c r="AC2" s="41"/>
-      <c r="AD2" s="41"/>
-      <c r="AE2" s="41"/>
-      <c r="AF2" s="41"/>
-      <c r="AG2" s="41"/>
-      <c r="AH2" s="41"/>
-      <c r="AI2" s="41"/>
-      <c r="AJ2" s="41"/>
+      <c r="U2" s="38"/>
+      <c r="V2" s="38"/>
+      <c r="W2" s="38"/>
+      <c r="X2" s="38"/>
+      <c r="Y2" s="38"/>
+      <c r="Z2" s="38"/>
+      <c r="AA2" s="38"/>
+      <c r="AB2" s="38"/>
+      <c r="AC2" s="38"/>
+      <c r="AD2" s="38"/>
+      <c r="AE2" s="38"/>
+      <c r="AF2" s="38"/>
+      <c r="AG2" s="38"/>
+      <c r="AH2" s="38"/>
+      <c r="AI2" s="38"/>
+      <c r="AJ2" s="38"/>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A3" s="16"/>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="41" t="s">
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="41" t="s">
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="41"/>
-      <c r="T3" s="42" t="s">
+      <c r="O3" s="38"/>
+      <c r="P3" s="38"/>
+      <c r="Q3" s="38"/>
+      <c r="R3" s="38"/>
+      <c r="T3" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="U3" s="42"/>
-      <c r="V3" s="42"/>
-      <c r="W3" s="42"/>
-      <c r="X3" s="42"/>
-      <c r="Y3" s="28"/>
-      <c r="Z3" s="41" t="s">
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="39"/>
+      <c r="Y3" s="26"/>
+      <c r="Z3" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="AA3" s="41"/>
-      <c r="AB3" s="41"/>
-      <c r="AC3" s="41"/>
-      <c r="AD3" s="41"/>
-      <c r="AE3" s="28"/>
-      <c r="AF3" s="41" t="s">
+      <c r="AA3" s="38"/>
+      <c r="AB3" s="38"/>
+      <c r="AC3" s="38"/>
+      <c r="AD3" s="38"/>
+      <c r="AE3" s="26"/>
+      <c r="AF3" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="AG3" s="41"/>
-      <c r="AH3" s="41"/>
-      <c r="AI3" s="41"/>
-      <c r="AJ3" s="41"/>
+      <c r="AG3" s="38"/>
+      <c r="AH3" s="38"/>
+      <c r="AI3" s="38"/>
+      <c r="AJ3" s="38"/>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
-      <c r="B4" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="C4" s="29" t="s">
+      <c r="B4" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="27" t="s">
         <v>132</v>
       </c>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="I4" s="29" t="s">
+      <c r="G4" s="27"/>
+      <c r="H4" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="I4" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="J4" s="29" t="s">
+      <c r="J4" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="L4" s="29" t="s">
+      <c r="L4" s="27" t="s">
         <v>132</v>
       </c>
-      <c r="M4" s="29"/>
-      <c r="N4" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="O4" s="29" t="s">
+      <c r="M4" s="27"/>
+      <c r="N4" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="O4" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="P4" s="29" t="s">
+      <c r="P4" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="Q4" s="29" t="s">
+      <c r="Q4" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="R4" s="29" t="s">
+      <c r="R4" s="27" t="s">
         <v>132</v>
       </c>
       <c r="S4" s="6"/>
-      <c r="T4" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="U4" s="29" t="s">
+      <c r="T4" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="U4" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="V4" s="29" t="s">
+      <c r="V4" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="W4" s="29" t="s">
+      <c r="W4" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="X4" s="29" t="s">
+      <c r="X4" s="27" t="s">
         <v>132</v>
       </c>
       <c r="Y4" s="17"/>
-      <c r="Z4" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="AA4" s="29" t="s">
+      <c r="Z4" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="AA4" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="AB4" s="29" t="s">
+      <c r="AB4" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="AC4" s="29" t="s">
+      <c r="AC4" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="AD4" s="29" t="s">
+      <c r="AD4" s="27" t="s">
         <v>132</v>
       </c>
       <c r="AE4" s="17"/>
-      <c r="AF4" s="29" t="s">
-        <v>160</v>
-      </c>
-      <c r="AG4" s="29" t="s">
+      <c r="AF4" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="AG4" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="AH4" s="29" t="s">
+      <c r="AH4" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="AI4" s="29" t="s">
+      <c r="AI4" s="27" t="s">
         <v>131</v>
       </c>
-      <c r="AJ4" s="29" t="s">
+      <c r="AJ4" s="27" t="s">
         <v>132</v>
       </c>
     </row>
@@ -8623,53 +8506,53 @@
       <c r="A41" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="B41" s="43">
+      <c r="B41" s="40">
         <v>34697.703999999998</v>
       </c>
-      <c r="C41" s="43"/>
-      <c r="D41" s="43"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="43">
+      <c r="C41" s="40"/>
+      <c r="D41" s="40"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="40"/>
+      <c r="G41" s="25"/>
+      <c r="H41" s="40">
         <v>43730.449000000001</v>
       </c>
-      <c r="I41" s="43"/>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
-      <c r="L41" s="43"/>
-      <c r="M41" s="27"/>
-      <c r="N41" s="43">
+      <c r="I41" s="40"/>
+      <c r="J41" s="40"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40"/>
+      <c r="M41" s="25"/>
+      <c r="N41" s="40">
         <v>55075.362999999998</v>
       </c>
-      <c r="O41" s="43"/>
-      <c r="P41" s="43"/>
-      <c r="Q41" s="43"/>
-      <c r="R41" s="43"/>
+      <c r="O41" s="40"/>
+      <c r="P41" s="40"/>
+      <c r="Q41" s="40"/>
+      <c r="R41" s="40"/>
       <c r="S41" s="15"/>
-      <c r="T41" s="43">
+      <c r="T41" s="40">
         <v>37782.404000000002</v>
       </c>
-      <c r="U41" s="43"/>
-      <c r="V41" s="43"/>
-      <c r="W41" s="43"/>
-      <c r="X41" s="43"/>
-      <c r="Y41" s="27"/>
-      <c r="Z41" s="43">
+      <c r="U41" s="40"/>
+      <c r="V41" s="40"/>
+      <c r="W41" s="40"/>
+      <c r="X41" s="40"/>
+      <c r="Y41" s="25"/>
+      <c r="Z41" s="40">
         <v>47698.324999999997</v>
       </c>
-      <c r="AA41" s="43"/>
-      <c r="AB41" s="43"/>
-      <c r="AC41" s="43"/>
-      <c r="AD41" s="43"/>
-      <c r="AE41" s="27"/>
-      <c r="AF41" s="43">
+      <c r="AA41" s="40"/>
+      <c r="AB41" s="40"/>
+      <c r="AC41" s="40"/>
+      <c r="AD41" s="40"/>
+      <c r="AE41" s="25"/>
+      <c r="AF41" s="40">
         <v>60402.93</v>
       </c>
-      <c r="AG41" s="43"/>
-      <c r="AH41" s="43"/>
-      <c r="AI41" s="43"/>
-      <c r="AJ41" s="43"/>
+      <c r="AG41" s="40"/>
+      <c r="AH41" s="40"/>
+      <c r="AI41" s="40"/>
+      <c r="AJ41" s="40"/>
       <c r="AK41" s="16"/>
       <c r="AL41" s="16"/>
       <c r="AM41" s="16"/>
@@ -8839,13 +8722,13 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="49" t="s">
+      <c r="A22" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="B22" s="49">
+      <c r="B22" s="46">
         <v>-0.113</v>
       </c>
-      <c r="C22" s="49">
+      <c r="C22" s="46">
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
@@ -8881,21 +8764,21 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57A86273-0E84-8246-B3ED-A023C6721217}">
-  <dimension ref="A1:AF59"/>
+  <dimension ref="A1:AF61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8" style="35" customWidth="1"/>
+    <col min="2" max="2" width="8" style="33" customWidth="1"/>
     <col min="3" max="3" width="5.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5" style="40" customWidth="1"/>
+    <col min="6" max="6" width="7.5" style="37" customWidth="1"/>
     <col min="7" max="7" width="6.83203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.1640625" style="35" customWidth="1"/>
+    <col min="8" max="8" width="8.1640625" style="33" customWidth="1"/>
     <col min="9" max="9" width="5.6640625" style="1" customWidth="1"/>
     <col min="10" max="10" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.5" style="32" customWidth="1"/>
+    <col min="12" max="12" width="7.5" style="30" customWidth="1"/>
     <col min="13" max="13" width="3.33203125" style="1" customWidth="1"/>
     <col min="14" max="14" width="26.5" style="1" customWidth="1"/>
     <col min="15" max="15" width="8" style="1" customWidth="1"/>
@@ -8915,331 +8798,231 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="N1" s="35"/>
+        <v>155</v>
+      </c>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A2" s="14"/>
-      <c r="B2" s="53" t="s">
-        <v>162</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="53" t="s">
-        <v>163</v>
-      </c>
-      <c r="P2" s="53"/>
-      <c r="Q2" s="53"/>
-      <c r="R2" s="53"/>
-      <c r="S2" s="53"/>
-      <c r="T2" s="53"/>
-      <c r="U2" s="53"/>
-      <c r="V2" s="53"/>
-      <c r="W2" s="53"/>
-      <c r="X2" s="53"/>
-      <c r="Y2" s="53"/>
-      <c r="Z2" s="53"/>
+      <c r="A2" s="52"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="52"/>
+      <c r="U2" s="52"/>
+      <c r="V2" s="52"/>
+      <c r="W2" s="52"/>
+      <c r="X2" s="52"/>
+      <c r="Y2" s="52"/>
+      <c r="Z2" s="52"/>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A3" s="15"/>
-      <c r="B3" s="44" t="s">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A4" s="51"/>
+      <c r="B4" s="70" t="s">
+        <v>156</v>
+      </c>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
+      <c r="G4" s="70"/>
+      <c r="H4" s="70"/>
+      <c r="I4" s="70"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="70"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="70" t="s">
+        <v>157</v>
+      </c>
+      <c r="P4" s="70"/>
+      <c r="Q4" s="70"/>
+      <c r="R4" s="70"/>
+      <c r="S4" s="70"/>
+      <c r="T4" s="70"/>
+      <c r="U4" s="70"/>
+      <c r="V4" s="70"/>
+      <c r="W4" s="70"/>
+      <c r="X4" s="70"/>
+      <c r="Y4" s="70"/>
+      <c r="Z4" s="70"/>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A5" s="15"/>
+      <c r="B5" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="46"/>
-      <c r="H3" s="44" t="s">
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="43"/>
+      <c r="H5" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="46"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="44" t="s">
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="43"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="41" t="s">
         <v>140</v>
       </c>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="45"/>
-      <c r="S3" s="46"/>
-      <c r="T3" s="60"/>
-      <c r="U3" s="61"/>
-      <c r="V3" s="44" t="s">
+      <c r="P5" s="42"/>
+      <c r="Q5" s="42"/>
+      <c r="R5" s="42"/>
+      <c r="S5" s="43"/>
+      <c r="T5" s="59"/>
+      <c r="U5" s="60"/>
+      <c r="V5" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="W3" s="45"/>
-      <c r="X3" s="45"/>
-      <c r="Y3" s="45"/>
-      <c r="Z3" s="46"/>
-    </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A4" s="16"/>
-      <c r="B4" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="C4" s="31" t="s">
+      <c r="W5" s="42"/>
+      <c r="X5" s="42"/>
+      <c r="Y5" s="42"/>
+      <c r="Z5" s="43"/>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A6" s="16"/>
+      <c r="B6" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="D4" s="31" t="s">
+      <c r="D6" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E6" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F6" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="H4" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="I4" s="31" t="s">
+      <c r="H6" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="I6" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="J4" s="31" t="s">
+      <c r="J6" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="K4" s="31" t="s">
+      <c r="K6" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="L4" s="31" t="s">
+      <c r="L6" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="N4" s="38"/>
-      <c r="O4" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="P4" s="31" t="s">
+      <c r="N6" s="35"/>
+      <c r="O6" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="P6" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="Q4" s="31" t="s">
+      <c r="Q6" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="R4" s="31" t="s">
+      <c r="R6" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="S4" s="62" t="s">
+      <c r="S6" s="61" t="s">
         <v>132</v>
       </c>
-      <c r="T4" s="64"/>
-      <c r="U4" s="34"/>
-      <c r="V4" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="W4" s="31" t="s">
+      <c r="T6" s="63"/>
+      <c r="U6" s="32"/>
+      <c r="V6" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="W6" s="29" t="s">
         <v>89</v>
       </c>
-      <c r="X4" s="31" t="s">
+      <c r="X6" s="29" t="s">
         <v>90</v>
       </c>
-      <c r="Y4" s="31" t="s">
+      <c r="Y6" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="Z4" s="31" t="s">
+      <c r="Z6" s="29" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A5" s="17" t="s">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A7" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="40"/>
-      <c r="N5" s="54" t="s">
+      <c r="B7" s="34"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="16"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="37"/>
+      <c r="N7" s="50" t="s">
         <v>85</v>
       </c>
-      <c r="O5" s="38"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="16"/>
-      <c r="S5" s="55"/>
-      <c r="T5" s="65"/>
-      <c r="U5" s="63" t="s">
+      <c r="O7" s="35"/>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="66"/>
+      <c r="R7" s="16"/>
+      <c r="S7" s="51"/>
+      <c r="T7" s="64"/>
+      <c r="U7" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="V5" s="36"/>
-      <c r="W5" s="16"/>
-      <c r="X5" s="18"/>
-      <c r="Y5" s="16"/>
-      <c r="Z5" s="40"/>
-      <c r="AA5" s="50"/>
-      <c r="AB5"/>
-      <c r="AC5"/>
-      <c r="AD5"/>
-      <c r="AE5"/>
-      <c r="AF5"/>
-    </row>
-    <row r="6" spans="1:32" ht="17" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B6" s="36">
-        <v>-0.28799999999999998</v>
-      </c>
-      <c r="C6" s="16">
-        <v>3.9E-2</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="16">
-        <v>-0.36399999999999999</v>
-      </c>
-      <c r="F6" s="40">
-        <v>-0.21199999999999999</v>
-      </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="36">
-        <v>-0.28199999999999997</v>
-      </c>
-      <c r="I6" s="16">
-        <v>0.04</v>
-      </c>
-      <c r="J6" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="K6" s="16">
-        <v>-0.36199999999999999</v>
-      </c>
-      <c r="L6" s="40">
-        <v>-0.20300000000000001</v>
-      </c>
-      <c r="N6" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="O6" s="69" t="s">
-        <v>92</v>
-      </c>
-      <c r="P6" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q6" s="68" t="s">
-        <v>92</v>
-      </c>
-      <c r="R6" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="S6" s="70" t="s">
-        <v>92</v>
-      </c>
-      <c r="T6" s="55"/>
-      <c r="U6" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="V6" s="36">
-        <v>0.32200000000000001</v>
-      </c>
-      <c r="W6" s="16">
-        <v>0.05</v>
-      </c>
-      <c r="X6" s="67" t="s">
-        <v>166</v>
-      </c>
-      <c r="Y6" s="16">
-        <v>0.224</v>
-      </c>
-      <c r="Z6" s="16">
-        <v>0.42</v>
-      </c>
-      <c r="AA6" s="51"/>
-      <c r="AB6"/>
-      <c r="AC6"/>
-      <c r="AD6"/>
-      <c r="AE6"/>
-      <c r="AF6"/>
-    </row>
-    <row r="7" spans="1:32" ht="17" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B7" s="36">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="C7" s="16">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="D7" s="18">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="E7" s="16">
-        <v>1.2E-2</v>
-      </c>
-      <c r="F7" s="40">
-        <v>9.2999999999999999E-2</v>
-      </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="36">
-        <v>-7.0000000000000001E-3</v>
-      </c>
-      <c r="I7" s="16">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="J7" s="18">
-        <v>0.74199999999999999</v>
-      </c>
-      <c r="K7" s="16">
-        <v>-4.8000000000000001E-2</v>
-      </c>
-      <c r="L7" s="40">
-        <v>3.4000000000000002E-2</v>
-      </c>
-      <c r="N7" s="36" t="s">
-        <v>135</v>
-      </c>
-      <c r="O7" s="36">
-        <v>0.11600000000000001</v>
-      </c>
-      <c r="P7" s="16">
-        <v>5.7000000000000002E-2</v>
-      </c>
-      <c r="Q7" s="67">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="R7" s="16">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="S7" s="40">
-        <v>0.22900000000000001</v>
-      </c>
-      <c r="T7" s="55"/>
-      <c r="U7" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="V7" s="36">
-        <v>-0.05</v>
-      </c>
-      <c r="W7" s="16">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="X7" s="67">
-        <v>1.6E-2</v>
-      </c>
-      <c r="Y7" s="16">
-        <v>-9.0999999999999998E-2</v>
-      </c>
-      <c r="Z7" s="16">
-        <v>-8.9999999999999993E-3</v>
-      </c>
-      <c r="AA7" s="51"/>
+      <c r="V7" s="34"/>
+      <c r="W7" s="16"/>
+      <c r="X7" s="18"/>
+      <c r="Y7" s="16"/>
+      <c r="Z7" s="37"/>
+      <c r="AA7" s="47"/>
       <c r="AB7"/>
       <c r="AC7"/>
       <c r="AD7"/>
@@ -9248,77 +9031,77 @@
     </row>
     <row r="8" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="B8" s="36">
-        <v>0.124</v>
+        <v>95</v>
+      </c>
+      <c r="B8" s="34">
+        <v>-0.28799999999999998</v>
       </c>
       <c r="C8" s="16">
-        <v>2.1000000000000001E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="D8" s="16" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="16">
-        <v>8.3000000000000004E-2</v>
-      </c>
-      <c r="F8" s="40">
-        <v>0.16600000000000001</v>
+        <v>-0.36399999999999999</v>
+      </c>
+      <c r="F8" s="37">
+        <v>-0.21199999999999999</v>
       </c>
       <c r="G8" s="16"/>
-      <c r="H8" s="36">
-        <v>8.6999999999999994E-2</v>
+      <c r="H8" s="34">
+        <v>-0.28199999999999997</v>
       </c>
       <c r="I8" s="16">
-        <v>2.1000000000000001E-2</v>
+        <v>0.04</v>
       </c>
       <c r="J8" s="18" t="s">
         <v>24</v>
       </c>
       <c r="K8" s="16">
-        <v>4.5999999999999999E-2</v>
-      </c>
-      <c r="L8" s="40">
-        <v>0.129</v>
-      </c>
-      <c r="N8" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="O8" s="36">
-        <v>-8.0000000000000002E-3</v>
-      </c>
-      <c r="P8" s="16">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="Q8" s="67">
-        <v>0.71599999999999997</v>
-      </c>
-      <c r="R8" s="16">
-        <v>-4.8000000000000001E-2</v>
-      </c>
-      <c r="S8" s="40">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="T8" s="55"/>
-      <c r="U8" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="V8" s="36">
-        <v>7.4999999999999997E-2</v>
+        <v>-0.36199999999999999</v>
+      </c>
+      <c r="L8" s="37">
+        <v>-0.20300000000000001</v>
+      </c>
+      <c r="N8" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="O8" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="P8" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q8" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="R8" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="S8" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="T8" s="51"/>
+      <c r="U8" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="V8" s="34">
+        <v>0.32200000000000001</v>
       </c>
       <c r="W8" s="16">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="X8" s="67" t="s">
-        <v>166</v>
+        <v>0.05</v>
+      </c>
+      <c r="X8" s="66" t="s">
+        <v>158</v>
       </c>
       <c r="Y8" s="16">
-        <v>3.4000000000000002E-2</v>
+        <v>0.224</v>
       </c>
       <c r="Z8" s="16">
-        <v>0.11600000000000001</v>
-      </c>
-      <c r="AA8" s="51"/>
+        <v>0.42</v>
+      </c>
+      <c r="AA8" s="48"/>
       <c r="AB8"/>
       <c r="AC8"/>
       <c r="AD8"/>
@@ -9327,77 +9110,77 @@
     </row>
     <row r="9" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="B9" s="37">
-        <v>-3.2000000000000001E-2</v>
-      </c>
-      <c r="C9" s="25">
-        <v>3.9E-2</v>
-      </c>
-      <c r="D9" s="26">
-        <v>0.40699999999999997</v>
+        <v>96</v>
+      </c>
+      <c r="B9" s="34">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="C9" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="D9" s="18">
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="E9" s="16">
-        <v>-0.108</v>
-      </c>
-      <c r="F9" s="40">
-        <v>4.3999999999999997E-2</v>
+        <v>1.2E-2</v>
+      </c>
+      <c r="F9" s="37">
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="G9" s="16"/>
-      <c r="H9" s="36">
-        <v>-9.6000000000000002E-2</v>
+      <c r="H9" s="34">
+        <v>-7.0000000000000001E-3</v>
       </c>
       <c r="I9" s="16">
-        <v>3.9E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="J9" s="18">
-        <v>1.4999999999999999E-2</v>
+        <v>0.74199999999999999</v>
       </c>
       <c r="K9" s="16">
-        <v>-0.17299999999999999</v>
-      </c>
-      <c r="L9" s="40">
-        <v>-1.7999999999999999E-2</v>
-      </c>
-      <c r="N9" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="O9" s="36">
-        <v>7.3999999999999996E-2</v>
+        <v>-4.8000000000000001E-2</v>
+      </c>
+      <c r="L9" s="37">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="N9" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="O9" s="34">
+        <v>0.11600000000000001</v>
       </c>
       <c r="P9" s="16">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="Q9" s="66">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="R9" s="16">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="S9" s="37">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="T9" s="51"/>
+      <c r="U9" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="V9" s="34">
+        <v>-0.05</v>
+      </c>
+      <c r="W9" s="16">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="Q9" s="67" t="s">
-        <v>24</v>
-      </c>
-      <c r="R9" s="16">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="S9" s="40">
-        <v>0.115</v>
-      </c>
-      <c r="T9" s="55"/>
-      <c r="U9" s="36" t="s">
-        <v>143</v>
-      </c>
-      <c r="V9" s="36">
-        <v>0.115</v>
-      </c>
-      <c r="W9" s="16">
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="X9" s="67">
-        <v>1E-3</v>
+      <c r="X9" s="66">
+        <v>1.6E-2</v>
       </c>
       <c r="Y9" s="16">
-        <v>4.4999999999999998E-2</v>
+        <v>-9.0999999999999998E-2</v>
       </c>
       <c r="Z9" s="16">
-        <v>0.185</v>
-      </c>
-      <c r="AA9" s="51"/>
+        <v>-8.9999999999999993E-3</v>
+      </c>
+      <c r="AA9" s="48"/>
       <c r="AB9"/>
       <c r="AC9"/>
       <c r="AD9"/>
@@ -9406,77 +9189,77 @@
     </row>
     <row r="10" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="B10" s="36">
-        <v>0.24099999999999999</v>
+        <v>97</v>
+      </c>
+      <c r="B10" s="34">
+        <v>0.124</v>
       </c>
       <c r="C10" s="16">
-        <v>2.1999999999999999E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="D10" s="16" t="s">
         <v>24</v>
       </c>
       <c r="E10" s="16">
-        <v>0.19700000000000001</v>
-      </c>
-      <c r="F10" s="40">
-        <v>0.28499999999999998</v>
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="F10" s="37">
+        <v>0.16600000000000001</v>
       </c>
       <c r="G10" s="16"/>
-      <c r="H10" s="36">
-        <v>0.04</v>
+      <c r="H10" s="34">
+        <v>8.6999999999999994E-2</v>
       </c>
       <c r="I10" s="16">
-        <v>0.02</v>
-      </c>
-      <c r="J10" s="18">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="16">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="K10" s="16">
-        <v>1E-3</v>
-      </c>
-      <c r="L10" s="40">
-        <v>7.9000000000000001E-2</v>
-      </c>
-      <c r="N10" s="36" t="s">
-        <v>176</v>
-      </c>
-      <c r="O10" s="69" t="s">
-        <v>92</v>
-      </c>
-      <c r="P10" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q10" s="68" t="s">
-        <v>92</v>
-      </c>
-      <c r="R10" s="68" t="s">
-        <v>92</v>
-      </c>
-      <c r="S10" s="68" t="s">
-        <v>92</v>
-      </c>
-      <c r="T10" s="55"/>
-      <c r="U10" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="V10" s="36">
-        <v>0.04</v>
+      <c r="L10" s="37">
+        <v>0.129</v>
+      </c>
+      <c r="N10" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="O10" s="34">
+        <v>-8.0000000000000002E-3</v>
+      </c>
+      <c r="P10" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="Q10" s="66">
+        <v>0.71599999999999997</v>
+      </c>
+      <c r="R10" s="16">
+        <v>-4.8000000000000001E-2</v>
+      </c>
+      <c r="S10" s="37">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="T10" s="51"/>
+      <c r="U10" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="V10" s="34">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="W10" s="16">
-        <v>0.02</v>
-      </c>
-      <c r="X10" s="67">
-        <v>4.7E-2</v>
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="X10" s="66" t="s">
+        <v>158</v>
       </c>
       <c r="Y10" s="16">
-        <v>1E-3</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="Z10" s="16">
-        <v>7.9000000000000001E-2</v>
-      </c>
-      <c r="AA10" s="51"/>
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="AA10" s="48"/>
       <c r="AB10"/>
       <c r="AC10"/>
       <c r="AD10"/>
@@ -9484,47 +9267,78 @@
       <c r="AF10"/>
     </row>
     <row r="11" spans="1:32" ht="17" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="B11" s="36"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
+      <c r="A11" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="54">
+        <v>-3.2000000000000001E-2</v>
+      </c>
+      <c r="C11" s="55">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D11" s="56">
+        <v>0.40699999999999997</v>
+      </c>
+      <c r="E11" s="16">
+        <v>-0.108</v>
+      </c>
+      <c r="F11" s="37">
+        <v>4.3999999999999997E-2</v>
+      </c>
       <c r="G11" s="16"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="40"/>
-      <c r="N11" s="36" t="s">
-        <v>177</v>
-      </c>
-      <c r="O11" s="69" t="s">
-        <v>92</v>
-      </c>
-      <c r="P11" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q11" s="68" t="s">
-        <v>92</v>
-      </c>
-      <c r="R11" s="68" t="s">
-        <v>92</v>
-      </c>
-      <c r="S11" s="68" t="s">
-        <v>92</v>
-      </c>
-      <c r="T11" s="55"/>
-      <c r="U11" s="54" t="s">
-        <v>86</v>
-      </c>
-      <c r="V11" s="36"/>
-      <c r="W11" s="16"/>
-      <c r="X11" s="67"/>
-      <c r="Y11" s="16"/>
-      <c r="Z11" s="16"/>
-      <c r="AA11" s="57"/>
+      <c r="H11" s="34">
+        <v>-9.6000000000000002E-2</v>
+      </c>
+      <c r="I11" s="16">
+        <v>3.9E-2</v>
+      </c>
+      <c r="J11" s="18">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="K11" s="16">
+        <v>-0.17299999999999999</v>
+      </c>
+      <c r="L11" s="37">
+        <v>-1.7999999999999999E-2</v>
+      </c>
+      <c r="N11" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="O11" s="34">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="P11" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="Q11" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="R11" s="16">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="S11" s="37">
+        <v>0.115</v>
+      </c>
+      <c r="T11" s="51"/>
+      <c r="U11" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="V11" s="34">
+        <v>0.115</v>
+      </c>
+      <c r="W11" s="16">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="X11" s="66">
+        <v>1E-3</v>
+      </c>
+      <c r="Y11" s="16">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="Z11" s="16">
+        <v>0.185</v>
+      </c>
+      <c r="AA11" s="48"/>
       <c r="AB11"/>
       <c r="AC11"/>
       <c r="AD11"/>
@@ -9533,77 +9347,77 @@
     </row>
     <row r="12" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="B12" s="36">
-        <v>0.29499999999999998</v>
+        <v>144</v>
+      </c>
+      <c r="B12" s="34">
+        <v>0.24099999999999999</v>
       </c>
       <c r="C12" s="16">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="D12" s="18" t="s">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="D12" s="16" t="s">
         <v>24</v>
       </c>
       <c r="E12" s="16">
-        <v>0.214</v>
-      </c>
-      <c r="F12" s="40">
-        <v>0.376</v>
+        <v>0.19700000000000001</v>
+      </c>
+      <c r="F12" s="37">
+        <v>0.28499999999999998</v>
       </c>
       <c r="G12" s="16"/>
-      <c r="H12" s="36">
-        <v>0.40100000000000002</v>
+      <c r="H12" s="34">
+        <v>0.04</v>
       </c>
       <c r="I12" s="16">
-        <v>3.7999999999999999E-2</v>
-      </c>
-      <c r="J12" s="18" t="s">
-        <v>24</v>
+        <v>0.02</v>
+      </c>
+      <c r="J12" s="18">
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="K12" s="16">
-        <v>0.32700000000000001</v>
-      </c>
-      <c r="L12" s="40">
-        <v>0.47499999999999998</v>
-      </c>
-      <c r="N12" s="36" t="s">
-        <v>138</v>
-      </c>
-      <c r="O12" s="36">
+        <v>1E-3</v>
+      </c>
+      <c r="L12" s="37">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="P12" s="16">
+      <c r="N12" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="O12" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="P12" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q12" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="R12" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="S12" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="T12" s="51"/>
+      <c r="U12" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="V12" s="34">
         <v>0.04</v>
       </c>
-      <c r="Q12" s="67">
-        <v>4.8000000000000001E-2</v>
-      </c>
-      <c r="R12" s="16">
+      <c r="W12" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="X12" s="66">
+        <v>4.7E-2</v>
+      </c>
+      <c r="Y12" s="16">
         <v>1E-3</v>
       </c>
-      <c r="S12" s="40">
-        <v>0.157</v>
-      </c>
-      <c r="T12" s="55"/>
-      <c r="U12" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="V12" s="36">
-        <v>7.3999999999999996E-2</v>
-      </c>
-      <c r="W12" s="16">
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="X12" s="67">
-        <v>3.7999999999999999E-2</v>
-      </c>
-      <c r="Y12" s="16">
-        <v>4.0000000000000001E-3</v>
-      </c>
       <c r="Z12" s="16">
-        <v>0.14299999999999999</v>
-      </c>
-      <c r="AA12" s="51"/>
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="AA12" s="48"/>
       <c r="AB12"/>
       <c r="AC12"/>
       <c r="AD12"/>
@@ -9611,78 +9425,47 @@
       <c r="AF12"/>
     </row>
     <row r="13" spans="1:32" ht="17" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="B13" s="36">
-        <v>-0.14499999999999999</v>
-      </c>
-      <c r="C13" s="16">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E13" s="16">
-        <v>-0.187</v>
-      </c>
-      <c r="F13" s="40">
-        <v>-0.10299999999999999</v>
-      </c>
+      <c r="A13" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" s="34"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
       <c r="G13" s="16"/>
-      <c r="H13" s="36">
-        <v>-0.13700000000000001</v>
-      </c>
-      <c r="I13" s="16">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="K13" s="16">
-        <v>-0.17899999999999999</v>
-      </c>
-      <c r="L13" s="40">
-        <v>-9.5000000000000001E-2</v>
-      </c>
-      <c r="N13" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="O13" s="36">
-        <v>0.24099999999999999</v>
-      </c>
-      <c r="P13" s="16">
-        <v>2.1999999999999999E-2</v>
+      <c r="H13" s="34"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="37"/>
+      <c r="N13" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="O13" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="P13" s="21" t="s">
+        <v>92</v>
       </c>
       <c r="Q13" s="67" t="s">
-        <v>24</v>
-      </c>
-      <c r="R13" s="16">
-        <v>0.19700000000000001</v>
-      </c>
-      <c r="S13" s="40">
-        <v>0.28399999999999997</v>
-      </c>
-      <c r="T13" s="55"/>
-      <c r="U13" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="V13" s="36">
-        <v>-0.13100000000000001</v>
-      </c>
-      <c r="W13" s="16">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="X13" s="67" t="s">
-        <v>166</v>
-      </c>
-      <c r="Y13" s="16">
-        <v>-0.17299999999999999</v>
-      </c>
-      <c r="Z13" s="16">
-        <v>-8.8999999999999996E-2</v>
-      </c>
-      <c r="AA13" s="51"/>
+        <v>92</v>
+      </c>
+      <c r="R13" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="S13" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="T13" s="51"/>
+      <c r="U13" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="V13" s="34"/>
+      <c r="W13" s="16"/>
+      <c r="X13" s="66"/>
+      <c r="Y13" s="16"/>
+      <c r="Z13" s="16"/>
+      <c r="AA13" s="53"/>
       <c r="AB13"/>
       <c r="AC13"/>
       <c r="AD13"/>
@@ -9691,67 +9474,77 @@
     </row>
     <row r="14" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="B14" s="36">
-        <v>-2.1999999999999999E-2</v>
+        <v>99</v>
+      </c>
+      <c r="B14" s="34">
+        <v>0.29499999999999998</v>
       </c>
       <c r="C14" s="16">
-        <v>3.9E-2</v>
-      </c>
-      <c r="D14" s="18">
-        <v>0.56699999999999995</v>
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>24</v>
       </c>
       <c r="E14" s="16">
-        <v>-9.8000000000000004E-2</v>
-      </c>
-      <c r="F14" s="40">
-        <v>5.3999999999999999E-2</v>
+        <v>0.214</v>
+      </c>
+      <c r="F14" s="37">
+        <v>0.376</v>
       </c>
       <c r="G14" s="16"/>
-      <c r="H14" s="36">
-        <v>3.2000000000000001E-2</v>
+      <c r="H14" s="34">
+        <v>0.40100000000000002</v>
       </c>
       <c r="I14" s="16">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="J14" s="18">
-        <v>0.42299999999999999</v>
+        <v>3.7999999999999999E-2</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>24</v>
       </c>
       <c r="K14" s="16">
-        <v>-4.7E-2</v>
-      </c>
-      <c r="L14" s="40">
-        <v>0.112</v>
-      </c>
-      <c r="N14" s="54" t="s">
-        <v>86</v>
-      </c>
-      <c r="O14" s="36"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="18"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="40"/>
-      <c r="T14" s="55"/>
-      <c r="U14" s="36" t="s">
-        <v>146</v>
-      </c>
-      <c r="V14" s="36">
-        <v>-6.0000000000000001E-3</v>
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="L14" s="37">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="N14" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="O14" s="34">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="P14" s="16">
+        <v>0.04</v>
+      </c>
+      <c r="Q14" s="66">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="R14" s="16">
+        <v>1E-3</v>
+      </c>
+      <c r="S14" s="37">
+        <v>0.157</v>
+      </c>
+      <c r="T14" s="51"/>
+      <c r="U14" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="V14" s="34">
+        <v>7.3999999999999996E-2</v>
       </c>
       <c r="W14" s="16">
-        <v>3.6999999999999998E-2</v>
-      </c>
-      <c r="X14" s="67">
-        <v>0.871</v>
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="X14" s="66">
+        <v>3.7999999999999999E-2</v>
       </c>
       <c r="Y14" s="16">
-        <v>-7.8E-2</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="Z14" s="16">
-        <v>6.6000000000000003E-2</v>
-      </c>
-      <c r="AA14" s="51"/>
+        <v>0.14299999999999999</v>
+      </c>
+      <c r="AA14" s="48"/>
       <c r="AB14"/>
       <c r="AC14"/>
       <c r="AD14"/>
@@ -9760,158 +9553,146 @@
     </row>
     <row r="15" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="B15" s="36">
-        <v>-0.14399999999999999</v>
+        <v>145</v>
+      </c>
+      <c r="B15" s="34">
+        <v>-0.14499999999999999</v>
       </c>
       <c r="C15" s="16">
-        <v>2.1000000000000001E-2</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E15" s="16">
-        <v>-0.186</v>
-      </c>
-      <c r="F15" s="40">
-        <v>-0.10199999999999999</v>
+        <v>-0.187</v>
+      </c>
+      <c r="F15" s="37">
+        <v>-0.10299999999999999</v>
       </c>
       <c r="G15" s="16"/>
-      <c r="H15" s="36">
-        <v>-3.5999999999999997E-2</v>
+      <c r="H15" s="34">
+        <v>-0.13700000000000001</v>
       </c>
       <c r="I15" s="16">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="J15" s="18">
-        <v>7.9000000000000001E-2</v>
+      <c r="J15" s="18" t="s">
+        <v>24</v>
       </c>
       <c r="K15" s="16">
-        <v>-7.6999999999999999E-2</v>
-      </c>
-      <c r="L15" s="40">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="M15"/>
-      <c r="N15" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="O15" s="69" t="s">
-        <v>92</v>
-      </c>
-      <c r="P15" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q15" s="68" t="s">
-        <v>92</v>
-      </c>
-      <c r="R15" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="S15" s="70" t="s">
-        <v>92</v>
-      </c>
-      <c r="T15" s="55"/>
-      <c r="U15" s="36" t="s">
-        <v>147</v>
-      </c>
-      <c r="V15" s="36">
-        <v>-3.5999999999999997E-2</v>
+        <v>-0.17899999999999999</v>
+      </c>
+      <c r="L15" s="37">
+        <v>-9.5000000000000001E-2</v>
+      </c>
+      <c r="N15" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="O15" s="34">
+        <v>0.24099999999999999</v>
+      </c>
+      <c r="P15" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="Q15" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="R15" s="16">
+        <v>0.19700000000000001</v>
+      </c>
+      <c r="S15" s="37">
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="T15" s="51"/>
+      <c r="U15" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="V15" s="34">
+        <v>-0.13100000000000001</v>
       </c>
       <c r="W15" s="16">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="X15" s="67">
-        <v>8.2000000000000003E-2</v>
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="X15" s="66" t="s">
+        <v>158</v>
       </c>
       <c r="Y15" s="16">
-        <v>-7.5999999999999998E-2</v>
+        <v>-0.17299999999999999</v>
       </c>
       <c r="Z15" s="16">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="AA15" s="51"/>
+        <v>-8.8999999999999996E-2</v>
+      </c>
+      <c r="AA15" s="48"/>
       <c r="AB15"/>
       <c r="AC15"/>
       <c r="AD15"/>
       <c r="AE15"/>
       <c r="AF15"/>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="B16" s="36">
-        <v>-0.16600000000000001</v>
+        <v>146</v>
+      </c>
+      <c r="B16" s="34">
+        <v>-2.1999999999999999E-2</v>
       </c>
       <c r="C16" s="16">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>24</v>
+        <v>3.9E-2</v>
+      </c>
+      <c r="D16" s="18">
+        <v>0.56699999999999995</v>
       </c>
       <c r="E16" s="16">
-        <v>-0.20799999999999999</v>
-      </c>
-      <c r="F16" s="40">
-        <v>-0.124</v>
+        <v>-9.8000000000000004E-2</v>
+      </c>
+      <c r="F16" s="37">
+        <v>5.3999999999999999E-2</v>
       </c>
       <c r="G16" s="16"/>
-      <c r="H16" s="36">
-        <v>-0.159</v>
+      <c r="H16" s="34">
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="I16" s="16">
-        <v>0.02</v>
-      </c>
-      <c r="J16" s="18" t="s">
-        <v>24</v>
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="J16" s="18">
+        <v>0.42299999999999999</v>
       </c>
       <c r="K16" s="16">
-        <v>-0.19700000000000001</v>
-      </c>
-      <c r="L16" s="40">
-        <v>-0.12</v>
-      </c>
-      <c r="M16"/>
-      <c r="N16" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="O16" s="36">
-        <v>0.39500000000000002</v>
-      </c>
-      <c r="P16" s="16">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="Q16" s="67" t="s">
-        <v>24</v>
-      </c>
-      <c r="R16" s="16">
-        <v>0.312</v>
-      </c>
-      <c r="S16" s="40">
-        <v>0.47799999999999998</v>
-      </c>
-      <c r="T16" s="55"/>
-      <c r="U16" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="V16" s="36">
-        <v>-0.159</v>
+        <v>-4.7E-2</v>
+      </c>
+      <c r="L16" s="37">
+        <v>0.112</v>
+      </c>
+      <c r="N16" s="50" t="s">
+        <v>86</v>
+      </c>
+      <c r="O16" s="34"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="18"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="37"/>
+      <c r="T16" s="51"/>
+      <c r="U16" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="V16" s="34">
+        <v>-6.0000000000000001E-3</v>
       </c>
       <c r="W16" s="16">
-        <v>0.02</v>
-      </c>
-      <c r="X16" s="67" t="s">
-        <v>166</v>
+        <v>3.6999999999999998E-2</v>
+      </c>
+      <c r="X16" s="66">
+        <v>0.871</v>
       </c>
       <c r="Y16" s="16">
-        <v>-0.19800000000000001</v>
+        <v>-7.8E-2</v>
       </c>
       <c r="Z16" s="16">
-        <v>-0.121</v>
-      </c>
-      <c r="AA16" s="51"/>
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="AA16" s="48"/>
       <c r="AB16"/>
       <c r="AC16"/>
       <c r="AD16"/>
@@ -9920,317 +9701,318 @@
     </row>
     <row r="17" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="B17" s="36">
-        <v>0.17899999999999999</v>
+        <v>147</v>
+      </c>
+      <c r="B17" s="34">
+        <v>-0.14399999999999999</v>
       </c>
       <c r="C17" s="16">
-        <v>2.5999999999999999E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="D17" s="18" t="s">
         <v>24</v>
       </c>
       <c r="E17" s="16">
-        <v>0.129</v>
-      </c>
-      <c r="F17" s="40">
-        <v>0.22900000000000001</v>
+        <v>-0.186</v>
+      </c>
+      <c r="F17" s="37">
+        <v>-0.10199999999999999</v>
       </c>
       <c r="G17" s="16"/>
-      <c r="H17" s="36">
-        <v>0.13100000000000001</v>
+      <c r="H17" s="34">
+        <v>-3.5999999999999997E-2</v>
       </c>
       <c r="I17" s="16">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="J17" s="18" t="s">
-        <v>24</v>
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="J17" s="18">
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="K17" s="16">
-        <v>8.6999999999999994E-2</v>
-      </c>
-      <c r="L17" s="40">
-        <v>0.17499999999999999</v>
+        <v>-7.6999999999999999E-2</v>
+      </c>
+      <c r="L17" s="37">
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="M17"/>
-      <c r="N17" s="36" t="s">
-        <v>145</v>
-      </c>
-      <c r="O17" s="36">
-        <v>-0.112</v>
-      </c>
-      <c r="P17" s="16">
-        <v>2.1999999999999999E-2</v>
+      <c r="N17" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="O17" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="P17" s="21" t="s">
+        <v>92</v>
       </c>
       <c r="Q17" s="67" t="s">
-        <v>24</v>
-      </c>
-      <c r="R17" s="16">
-        <v>-0.155</v>
-      </c>
-      <c r="S17" s="40">
-        <v>-6.9000000000000006E-2</v>
-      </c>
-      <c r="T17" s="55"/>
-      <c r="U17" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="V17" s="36">
-        <v>0.123</v>
+        <v>92</v>
+      </c>
+      <c r="R17" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="S17" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="T17" s="51"/>
+      <c r="U17" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="V17" s="34">
+        <v>-3.5999999999999997E-2</v>
       </c>
       <c r="W17" s="16">
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="X17" s="67" t="s">
-        <v>166</v>
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="X17" s="66">
+        <v>8.2000000000000003E-2</v>
       </c>
       <c r="Y17" s="16">
-        <v>7.1999999999999995E-2</v>
+        <v>-7.5999999999999998E-2</v>
       </c>
       <c r="Z17" s="16">
-        <v>0.17399999999999999</v>
-      </c>
-      <c r="AA17" s="51"/>
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="AA17" s="48"/>
       <c r="AB17"/>
       <c r="AC17"/>
       <c r="AD17"/>
       <c r="AE17"/>
       <c r="AF17"/>
     </row>
-    <row r="18" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="B18" s="36">
-        <v>1E-3</v>
+        <v>148</v>
+      </c>
+      <c r="B18" s="34">
+        <v>-0.16600000000000001</v>
       </c>
       <c r="C18" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="16">
+        <v>-0.20799999999999999</v>
+      </c>
+      <c r="F18" s="37">
+        <v>-0.124</v>
+      </c>
+      <c r="G18" s="16"/>
+      <c r="H18" s="34">
+        <v>-0.159</v>
+      </c>
+      <c r="I18" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="J18" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="16">
+        <v>-0.19700000000000001</v>
+      </c>
+      <c r="L18" s="37">
+        <v>-0.12</v>
+      </c>
+      <c r="M18"/>
+      <c r="N18" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="O18" s="34">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="P18" s="16">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="D18" s="18">
-        <v>0.98199999999999998</v>
-      </c>
-      <c r="E18" s="16">
-        <v>-8.2000000000000003E-2</v>
-      </c>
-      <c r="F18" s="40">
-        <v>8.4000000000000005E-2</v>
-      </c>
-      <c r="G18" s="16"/>
-      <c r="H18" s="36">
-        <v>-6.4000000000000001E-2</v>
-      </c>
-      <c r="I18" s="16">
-        <v>4.3999999999999997E-2</v>
-      </c>
-      <c r="J18" s="18">
-        <v>0.14499999999999999</v>
-      </c>
-      <c r="K18" s="16">
-        <v>-0.151</v>
-      </c>
-      <c r="L18" s="40">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="M18"/>
-      <c r="N18" s="36" t="s">
-        <v>146</v>
-      </c>
-      <c r="O18" s="69" t="s">
-        <v>92</v>
-      </c>
-      <c r="P18" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q18" s="68" t="s">
-        <v>92</v>
-      </c>
-      <c r="R18" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="S18" s="70" t="s">
-        <v>92</v>
-      </c>
-      <c r="T18" s="55"/>
-      <c r="U18" s="36" t="s">
-        <v>155</v>
-      </c>
-      <c r="V18" s="36">
-        <v>-2.7E-2</v>
+      <c r="Q18" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="R18" s="16">
+        <v>0.312</v>
+      </c>
+      <c r="S18" s="37">
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="T18" s="51"/>
+      <c r="U18" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="V18" s="34">
+        <v>-0.159</v>
       </c>
       <c r="W18" s="16">
-        <v>4.3999999999999997E-2</v>
-      </c>
-      <c r="X18" s="67">
-        <v>0.53600000000000003</v>
+        <v>0.02</v>
+      </c>
+      <c r="X18" s="66" t="s">
+        <v>158</v>
       </c>
       <c r="Y18" s="16">
-        <v>-0.114</v>
+        <v>-0.19800000000000001</v>
       </c>
       <c r="Z18" s="16">
-        <v>5.8999999999999997E-2</v>
-      </c>
-      <c r="AA18" s="51"/>
+        <v>-0.121</v>
+      </c>
+      <c r="AA18" s="48"/>
       <c r="AB18"/>
       <c r="AC18"/>
       <c r="AD18"/>
       <c r="AE18"/>
       <c r="AF18"/>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="B19" s="36">
-        <v>1.6E-2</v>
+        <v>149</v>
+      </c>
+      <c r="B19" s="34">
+        <v>0.17899999999999999</v>
       </c>
       <c r="C19" s="16">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="D19" s="18">
-        <v>0.51500000000000001</v>
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>24</v>
       </c>
       <c r="E19" s="16">
-        <v>-3.2000000000000001E-2</v>
-      </c>
-      <c r="F19" s="40">
-        <v>6.5000000000000002E-2</v>
+        <v>0.129</v>
+      </c>
+      <c r="F19" s="37">
+        <v>0.22900000000000001</v>
       </c>
       <c r="G19" s="16"/>
-      <c r="H19" s="36">
-        <v>4.4999999999999998E-2</v>
+      <c r="H19" s="34">
+        <v>0.13100000000000001</v>
       </c>
       <c r="I19" s="16">
-        <v>2.8000000000000001E-2</v>
-      </c>
-      <c r="J19" s="18">
-        <v>0.1</v>
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="J19" s="18" t="s">
+        <v>24</v>
       </c>
       <c r="K19" s="16">
-        <v>-8.9999999999999993E-3</v>
-      </c>
-      <c r="L19" s="40">
-        <v>9.9000000000000005E-2</v>
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="L19" s="37">
+        <v>0.17499999999999999</v>
       </c>
       <c r="M19"/>
-      <c r="N19" s="36" t="s">
-        <v>178</v>
-      </c>
-      <c r="O19" s="36">
-        <v>-0.13100000000000001</v>
+      <c r="N19" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="O19" s="34">
+        <v>-0.112</v>
       </c>
       <c r="P19" s="16">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="Q19" s="67" t="s">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="Q19" s="66" t="s">
         <v>24</v>
       </c>
       <c r="R19" s="16">
-        <v>-0.2</v>
-      </c>
-      <c r="S19" s="40">
-        <v>-6.2E-2</v>
-      </c>
-      <c r="T19" s="55"/>
-      <c r="U19" s="36" t="s">
-        <v>157</v>
-      </c>
-      <c r="V19" s="36">
+        <v>-0.155</v>
+      </c>
+      <c r="S19" s="37">
+        <v>-6.9000000000000006E-2</v>
+      </c>
+      <c r="T19" s="51"/>
+      <c r="U19" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="V19" s="34">
+        <v>0.123</v>
+      </c>
+      <c r="W19" s="16">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="W19" s="16">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="X19" s="67">
-        <v>0.216</v>
+      <c r="X19" s="66" t="s">
+        <v>158</v>
       </c>
       <c r="Y19" s="16">
-        <v>-1.4999999999999999E-2</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="Z19" s="16">
-        <v>6.8000000000000005E-2</v>
-      </c>
-      <c r="AA19" s="51"/>
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="AA19" s="48"/>
       <c r="AB19"/>
       <c r="AC19"/>
       <c r="AD19"/>
       <c r="AE19"/>
       <c r="AF19"/>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="B20" s="36">
-        <v>6.5000000000000002E-2</v>
+        <v>150</v>
+      </c>
+      <c r="B20" s="34">
+        <v>1E-3</v>
       </c>
       <c r="C20" s="16">
-        <v>2.3E-2</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="D20" s="18">
-        <v>4.0000000000000001E-3</v>
+        <v>0.98199999999999998</v>
       </c>
       <c r="E20" s="16">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="F20" s="40">
-        <v>0.11</v>
+        <v>-8.2000000000000003E-2</v>
+      </c>
+      <c r="F20" s="37">
+        <v>8.4000000000000005E-2</v>
       </c>
       <c r="G20" s="16"/>
-      <c r="H20" s="36">
+      <c r="H20" s="34">
+        <v>-6.4000000000000001E-2</v>
+      </c>
+      <c r="I20" s="16">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="J20" s="18">
         <v>0.14499999999999999</v>
       </c>
-      <c r="I20" s="16">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="J20" s="18">
-        <v>0.1</v>
-      </c>
       <c r="K20" s="16">
-        <v>0.105</v>
-      </c>
-      <c r="L20" s="40">
-        <v>0.186</v>
-      </c>
-      <c r="N20" s="36" t="s">
-        <v>147</v>
-      </c>
-      <c r="O20" s="36">
-        <v>-0.14399999999999999</v>
-      </c>
-      <c r="P20" s="16">
-        <v>2.1000000000000001E-2</v>
+        <v>-0.151</v>
+      </c>
+      <c r="L20" s="37">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="M20"/>
+      <c r="N20" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="O20" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="P20" s="21" t="s">
+        <v>92</v>
       </c>
       <c r="Q20" s="67" t="s">
-        <v>24</v>
-      </c>
-      <c r="R20" s="16">
-        <v>-0.186</v>
-      </c>
-      <c r="S20" s="40">
-        <v>-0.10299999999999999</v>
-      </c>
-      <c r="T20" s="55"/>
-      <c r="U20" s="36" t="s">
-        <v>158</v>
-      </c>
-      <c r="V20" s="36">
-        <v>0.156</v>
+        <v>92</v>
+      </c>
+      <c r="R20" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="S20" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="T20" s="51"/>
+      <c r="U20" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="V20" s="34">
+        <v>-2.7E-2</v>
       </c>
       <c r="W20" s="16">
-        <v>0.02</v>
-      </c>
-      <c r="X20" s="67" t="s">
-        <v>166</v>
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="X20" s="66">
+        <v>0.53600000000000003</v>
       </c>
       <c r="Y20" s="16">
-        <v>0.11600000000000001</v>
+        <v>-0.114</v>
       </c>
       <c r="Z20" s="16">
-        <v>0.19600000000000001</v>
-      </c>
-      <c r="AA20" s="51"/>
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="AA20" s="48"/>
       <c r="AB20"/>
       <c r="AC20"/>
       <c r="AD20"/>
@@ -10239,1524 +10021,1421 @@
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="B21" s="36">
-        <v>-0.12</v>
+        <v>152</v>
+      </c>
+      <c r="B21" s="34">
+        <v>1.6E-2</v>
       </c>
       <c r="C21" s="16">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>24</v>
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="D21" s="18">
+        <v>0.51500000000000001</v>
       </c>
       <c r="E21" s="16">
-        <v>-0.16200000000000001</v>
-      </c>
-      <c r="F21" s="40">
-        <v>-7.6999999999999999E-2</v>
+        <v>-3.2000000000000001E-2</v>
+      </c>
+      <c r="F21" s="37">
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="G21" s="16"/>
-      <c r="H21" s="36">
-        <v>-7.9000000000000001E-2</v>
+      <c r="H21" s="34">
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="I21" s="16">
-        <v>0.02</v>
-      </c>
-      <c r="J21" s="18" t="s">
-        <v>24</v>
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="J21" s="18">
+        <v>0.1</v>
       </c>
       <c r="K21" s="16">
-        <v>-0.11899999999999999</v>
-      </c>
-      <c r="L21" s="40">
-        <v>-3.9E-2</v>
-      </c>
-      <c r="N21" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="O21" s="36">
-        <v>-0.16600000000000001</v>
+        <v>-8.9999999999999993E-3</v>
+      </c>
+      <c r="L21" s="37">
+        <v>9.9000000000000005E-2</v>
+      </c>
+      <c r="M21"/>
+      <c r="N21" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="O21" s="34">
+        <v>-0.13100000000000001</v>
       </c>
       <c r="P21" s="16">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="Q21" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="R21" s="16">
+        <v>-0.2</v>
+      </c>
+      <c r="S21" s="37">
+        <v>-6.2E-2</v>
+      </c>
+      <c r="T21" s="51"/>
+      <c r="U21" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="V21" s="34">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="W21" s="16">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="Q21" s="67" t="s">
-        <v>24</v>
-      </c>
-      <c r="R21" s="16">
-        <v>-0.20799999999999999</v>
-      </c>
-      <c r="S21" s="40">
-        <v>-0.124</v>
-      </c>
-      <c r="T21" s="55"/>
-      <c r="U21" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="V21" s="36">
-        <v>-8.2000000000000003E-2</v>
-      </c>
-      <c r="W21" s="16">
-        <v>0.02</v>
-      </c>
-      <c r="X21" s="67" t="s">
-        <v>166</v>
+      <c r="X21" s="66">
+        <v>0.216</v>
       </c>
       <c r="Y21" s="16">
-        <v>-0.122</v>
+        <v>-1.4999999999999999E-2</v>
       </c>
       <c r="Z21" s="16">
-        <v>-4.2999999999999997E-2</v>
-      </c>
-      <c r="AA21" s="51"/>
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="AA21" s="48"/>
       <c r="AB21"/>
       <c r="AC21"/>
       <c r="AD21"/>
       <c r="AE21"/>
       <c r="AF21"/>
     </row>
-    <row r="22" spans="1:32" ht="17" x14ac:dyDescent="0.25">
-      <c r="A22" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="B22" s="38"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="52"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="33"/>
-      <c r="N22" s="36" t="s">
-        <v>149</v>
-      </c>
-      <c r="O22" s="36">
-        <v>0.13900000000000001</v>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A22" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="B22" s="34">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="C22" s="16">
+        <v>2.3E-2</v>
+      </c>
+      <c r="D22" s="18">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="E22" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="F22" s="37">
+        <v>0.11</v>
+      </c>
+      <c r="G22" s="16"/>
+      <c r="H22" s="34">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="I22" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="J22" s="18">
+        <v>0.1</v>
+      </c>
+      <c r="K22" s="16">
+        <v>0.105</v>
+      </c>
+      <c r="L22" s="37">
+        <v>0.186</v>
+      </c>
+      <c r="N22" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="O22" s="34">
+        <v>-0.14399999999999999</v>
       </c>
       <c r="P22" s="16">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="Q22" s="67" t="s">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="Q22" s="66" t="s">
         <v>24</v>
       </c>
       <c r="R22" s="16">
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="S22" s="40">
-        <v>0.183</v>
-      </c>
-      <c r="T22" s="55"/>
-      <c r="U22" s="66" t="s">
-        <v>114</v>
-      </c>
-      <c r="V22" s="38"/>
-      <c r="W22" s="14"/>
-      <c r="X22" s="52"/>
-      <c r="Y22" s="14"/>
-      <c r="Z22" s="33"/>
-      <c r="AA22" s="50"/>
+        <v>-0.186</v>
+      </c>
+      <c r="S22" s="37">
+        <v>-0.10299999999999999</v>
+      </c>
+      <c r="T22" s="51"/>
+      <c r="U22" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="V22" s="34">
+        <v>0.156</v>
+      </c>
+      <c r="W22" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="X22" s="66" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y22" s="16">
+        <v>0.11600000000000001</v>
+      </c>
+      <c r="Z22" s="16">
+        <v>0.19600000000000001</v>
+      </c>
+      <c r="AA22" s="48"/>
       <c r="AB22"/>
       <c r="AC22"/>
       <c r="AD22"/>
       <c r="AE22"/>
       <c r="AF22"/>
     </row>
-    <row r="23" spans="1:32" ht="17" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="B23" s="47">
-        <v>93579.540999999997</v>
-      </c>
-      <c r="C23" s="43"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="47">
-        <v>104772.751</v>
-      </c>
-      <c r="I23" s="43"/>
-      <c r="J23" s="43"/>
-      <c r="K23" s="43"/>
-      <c r="L23" s="48"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="O23" s="69" t="s">
-        <v>92</v>
-      </c>
-      <c r="P23" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q23" s="68" t="s">
-        <v>92</v>
-      </c>
-      <c r="R23" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="S23" s="70" t="s">
-        <v>92</v>
-      </c>
-      <c r="T23" s="59"/>
-      <c r="U23" s="58" t="s">
-        <v>115</v>
-      </c>
-      <c r="V23" s="47">
-        <v>59389.061000000002</v>
-      </c>
-      <c r="W23" s="43"/>
-      <c r="X23" s="43"/>
-      <c r="Y23" s="43"/>
-      <c r="Z23" s="48"/>
-      <c r="AA23"/>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A23" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B23" s="34">
+        <v>-0.12</v>
+      </c>
+      <c r="C23" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" s="16">
+        <v>-0.16200000000000001</v>
+      </c>
+      <c r="F23" s="37">
+        <v>-7.6999999999999999E-2</v>
+      </c>
+      <c r="G23" s="16"/>
+      <c r="H23" s="34">
+        <v>-7.9000000000000001E-2</v>
+      </c>
+      <c r="I23" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="J23" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" s="16">
+        <v>-0.11899999999999999</v>
+      </c>
+      <c r="L23" s="37">
+        <v>-3.9E-2</v>
+      </c>
+      <c r="N23" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="O23" s="34">
+        <v>-0.16600000000000001</v>
+      </c>
+      <c r="P23" s="16">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="Q23" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="R23" s="16">
+        <v>-0.20799999999999999</v>
+      </c>
+      <c r="S23" s="37">
+        <v>-0.124</v>
+      </c>
+      <c r="T23" s="51"/>
+      <c r="U23" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="V23" s="34">
+        <v>-8.2000000000000003E-2</v>
+      </c>
+      <c r="W23" s="16">
+        <v>0.02</v>
+      </c>
+      <c r="X23" s="66" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y23" s="16">
+        <v>-0.122</v>
+      </c>
+      <c r="Z23" s="16">
+        <v>-4.2999999999999997E-2</v>
+      </c>
+      <c r="AA23" s="48"/>
       <c r="AB23"/>
       <c r="AC23"/>
       <c r="AD23"/>
       <c r="AE23"/>
       <c r="AF23"/>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A24" s="56"/>
-      <c r="B24" s="56"/>
-      <c r="C24" s="56"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="56"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="56"/>
-      <c r="I24" s="56"/>
-      <c r="J24" s="56"/>
-      <c r="K24" s="56"/>
-      <c r="L24" s="56"/>
-      <c r="M24" s="56"/>
-      <c r="N24" s="36" t="s">
-        <v>142</v>
-      </c>
-      <c r="O24" s="36">
+    <row r="24" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+      <c r="A24" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" s="35"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="49"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="31"/>
+      <c r="N24" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="O24" s="34">
+        <v>0.13900000000000001</v>
+      </c>
+      <c r="P24" s="16">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="Q24" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="R24" s="16">
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="S24" s="37">
+        <v>0.183</v>
+      </c>
+      <c r="T24" s="51"/>
+      <c r="U24" s="65" t="s">
+        <v>114</v>
+      </c>
+      <c r="V24" s="35"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="49"/>
+      <c r="Y24" s="14"/>
+      <c r="Z24" s="31"/>
+      <c r="AA24" s="47"/>
+      <c r="AB24"/>
+      <c r="AC24"/>
+      <c r="AD24"/>
+      <c r="AE24"/>
+      <c r="AF24"/>
+    </row>
+    <row r="25" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" s="44">
+        <v>93579.540999999997</v>
+      </c>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="44">
+        <v>104772.751</v>
+      </c>
+      <c r="I25" s="40"/>
+      <c r="J25" s="40"/>
+      <c r="K25" s="40"/>
+      <c r="L25" s="45"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="O25" s="68" t="s">
+        <v>92</v>
+      </c>
+      <c r="P25" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q25" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="R25" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="S25" s="69" t="s">
+        <v>92</v>
+      </c>
+      <c r="T25" s="58"/>
+      <c r="U25" s="57" t="s">
+        <v>115</v>
+      </c>
+      <c r="V25" s="44">
+        <v>59389.061000000002</v>
+      </c>
+      <c r="W25" s="40"/>
+      <c r="X25" s="40"/>
+      <c r="Y25" s="40"/>
+      <c r="Z25" s="45"/>
+      <c r="AA25"/>
+      <c r="AB25"/>
+      <c r="AC25"/>
+      <c r="AD25"/>
+      <c r="AE25"/>
+      <c r="AF25"/>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A26" s="52"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="51"/>
+      <c r="G26" s="52"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="52"/>
+      <c r="J26" s="52"/>
+      <c r="K26" s="52"/>
+      <c r="L26" s="52"/>
+      <c r="M26" s="52"/>
+      <c r="N26" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="O26" s="34">
         <v>7.0999999999999994E-2</v>
       </c>
-      <c r="P24" s="16">
+      <c r="P26" s="16">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="Q24" s="67">
+      <c r="Q26" s="66">
         <v>0.125</v>
       </c>
-      <c r="R24" s="16">
+      <c r="R26" s="16">
         <v>-0.02</v>
       </c>
-      <c r="S24" s="40">
+      <c r="S26" s="37">
         <v>0.161</v>
       </c>
-      <c r="T24" s="56"/>
-      <c r="U24" s="56"/>
-      <c r="V24" s="56"/>
-      <c r="W24" s="56"/>
-      <c r="X24" s="56"/>
-      <c r="Y24" s="56"/>
-      <c r="Z24" s="56"/>
-    </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A25" s="56"/>
-      <c r="B25" s="56"/>
-      <c r="C25" s="56"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="56"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="56"/>
-      <c r="J25" s="56"/>
-      <c r="K25" s="56"/>
-      <c r="L25" s="56"/>
-      <c r="M25" s="56"/>
-      <c r="N25" s="36" t="s">
+      <c r="T26" s="52"/>
+      <c r="U26" s="52"/>
+      <c r="V26" s="52"/>
+      <c r="W26" s="52"/>
+      <c r="X26" s="52"/>
+      <c r="Y26" s="52"/>
+      <c r="Z26" s="52"/>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A27" s="52"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="52"/>
+      <c r="K27" s="52"/>
+      <c r="L27" s="52"/>
+      <c r="M27" s="52"/>
+      <c r="N27" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="O27" s="34">
+        <v>-1E-3</v>
+      </c>
+      <c r="P27" s="16">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="Q27" s="66">
+        <v>0.96799999999999997</v>
+      </c>
+      <c r="R27" s="16">
+        <v>-5.7000000000000002E-2</v>
+      </c>
+      <c r="S27" s="37">
+        <v>5.5E-2</v>
+      </c>
+      <c r="T27" s="52"/>
+      <c r="U27" s="52"/>
+      <c r="V27" s="52"/>
+      <c r="W27" s="52"/>
+      <c r="X27" s="52"/>
+      <c r="Y27" s="52"/>
+      <c r="Z27" s="52"/>
+    </row>
+    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A28" s="52"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="52"/>
+      <c r="D28" s="52"/>
+      <c r="E28" s="52"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="52"/>
+      <c r="H28" s="52"/>
+      <c r="I28" s="52"/>
+      <c r="J28" s="52"/>
+      <c r="K28" s="52"/>
+      <c r="L28" s="52"/>
+      <c r="M28" s="52"/>
+      <c r="N28" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="O28" s="34">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="P28" s="16">
+        <v>2.3E-2</v>
+      </c>
+      <c r="Q28" s="66">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="R28" s="16">
+        <v>2.3E-2</v>
+      </c>
+      <c r="S28" s="37">
+        <v>0.113</v>
+      </c>
+      <c r="T28" s="52"/>
+      <c r="U28" s="52"/>
+      <c r="V28" s="52"/>
+      <c r="W28" s="52"/>
+      <c r="X28" s="52"/>
+      <c r="Y28" s="52"/>
+      <c r="Z28" s="52"/>
+    </row>
+    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A29" s="52"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="51"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="52"/>
+      <c r="J29" s="52"/>
+      <c r="K29" s="52"/>
+      <c r="L29" s="52"/>
+      <c r="M29" s="52"/>
+      <c r="N29" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="O25" s="36">
-        <v>-1E-3</v>
-      </c>
-      <c r="P25" s="16">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="Q25" s="67">
-        <v>0.96799999999999997</v>
-      </c>
-      <c r="R25" s="16">
-        <v>-5.7000000000000002E-2</v>
-      </c>
-      <c r="S25" s="40">
-        <v>5.5E-2</v>
-      </c>
-      <c r="T25" s="56"/>
-      <c r="U25" s="56"/>
-      <c r="V25" s="56"/>
-      <c r="W25" s="56"/>
-      <c r="X25" s="56"/>
-      <c r="Y25" s="56"/>
-      <c r="Z25" s="56"/>
-    </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A26" s="56"/>
-      <c r="B26" s="56"/>
-      <c r="C26" s="56"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="56"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="56"/>
-      <c r="K26" s="56"/>
-      <c r="L26" s="56"/>
-      <c r="M26" s="56"/>
-      <c r="N26" s="36" t="s">
-        <v>152</v>
-      </c>
-      <c r="O26" s="36">
-        <v>6.8000000000000005E-2</v>
-      </c>
-      <c r="P26" s="16">
-        <v>2.3E-2</v>
-      </c>
-      <c r="Q26" s="67">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="R26" s="16">
-        <v>2.3E-2</v>
-      </c>
-      <c r="S26" s="40">
-        <v>0.114</v>
-      </c>
-      <c r="T26" s="56"/>
-      <c r="U26" s="56"/>
-      <c r="V26" s="56"/>
-      <c r="W26" s="56"/>
-      <c r="X26" s="56"/>
-      <c r="Y26" s="56"/>
-      <c r="Z26" s="56"/>
-    </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A27" s="56"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="56"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="55"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="56"/>
-      <c r="K27" s="56"/>
-      <c r="L27" s="56"/>
-      <c r="M27" s="56"/>
-      <c r="N27" s="39" t="s">
-        <v>153</v>
-      </c>
-      <c r="O27" s="39">
+      <c r="O29" s="36">
         <v>-0.11799999999999999</v>
       </c>
-      <c r="P27" s="16">
+      <c r="P29" s="16">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="Q27" s="67" t="s">
-        <v>24</v>
-      </c>
-      <c r="R27" s="16">
-        <v>-0.16200000000000001</v>
-      </c>
-      <c r="S27" s="34">
-        <v>-7.3999999999999996E-2</v>
-      </c>
-      <c r="T27" s="56"/>
-      <c r="U27" s="56"/>
-      <c r="V27" s="56"/>
-      <c r="W27" s="56"/>
-      <c r="X27" s="56"/>
-      <c r="Y27" s="56"/>
-      <c r="Z27" s="56"/>
-    </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A28" s="56"/>
-      <c r="B28" s="56"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="56"/>
-      <c r="K28" s="56"/>
-      <c r="L28" s="56"/>
-      <c r="M28" s="56"/>
-      <c r="N28" s="66" t="s">
+      <c r="Q29" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="R29" s="16">
+        <v>-0.161</v>
+      </c>
+      <c r="S29" s="32">
+        <v>-7.4999999999999997E-2</v>
+      </c>
+      <c r="T29" s="52"/>
+      <c r="U29" s="52"/>
+      <c r="V29" s="52"/>
+      <c r="W29" s="52"/>
+      <c r="X29" s="52"/>
+      <c r="Y29" s="52"/>
+      <c r="Z29" s="52"/>
+    </row>
+    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A30" s="52"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="51"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="52"/>
+      <c r="L30" s="52"/>
+      <c r="M30" s="52"/>
+      <c r="N30" s="65" t="s">
         <v>114</v>
       </c>
-      <c r="O28" s="38"/>
-      <c r="P28" s="14"/>
-      <c r="Q28" s="52"/>
-      <c r="R28" s="14"/>
-      <c r="S28" s="33"/>
-      <c r="T28" s="56"/>
-      <c r="U28" s="56"/>
-      <c r="V28" s="56"/>
-      <c r="W28" s="56"/>
-      <c r="X28" s="56"/>
-      <c r="Y28" s="56"/>
-      <c r="Z28" s="56"/>
-    </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A29" s="56"/>
-      <c r="B29" s="56"/>
-      <c r="C29" s="56"/>
-      <c r="D29" s="56"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="55"/>
-      <c r="G29" s="56"/>
-      <c r="H29" s="56"/>
-      <c r="I29" s="56"/>
-      <c r="J29" s="56"/>
-      <c r="K29" s="56"/>
-      <c r="L29" s="56"/>
-      <c r="M29" s="56"/>
-      <c r="N29" s="58" t="s">
+      <c r="O30" s="35"/>
+      <c r="P30" s="14"/>
+      <c r="Q30" s="49"/>
+      <c r="R30" s="14"/>
+      <c r="S30" s="31"/>
+      <c r="T30" s="52"/>
+      <c r="U30" s="52"/>
+      <c r="V30" s="52"/>
+      <c r="W30" s="52"/>
+      <c r="X30" s="52"/>
+      <c r="Y30" s="52"/>
+      <c r="Z30" s="52"/>
+    </row>
+    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A31" s="52"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="51"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="52"/>
+      <c r="K31" s="52"/>
+      <c r="L31" s="52"/>
+      <c r="M31" s="52"/>
+      <c r="N31" s="57" t="s">
         <v>115</v>
       </c>
-      <c r="O29" s="47">
+      <c r="O31" s="44">
         <v>54236.89</v>
       </c>
-      <c r="P29" s="43"/>
-      <c r="Q29" s="43"/>
-      <c r="R29" s="43"/>
-      <c r="S29" s="48"/>
-      <c r="T29" s="56"/>
-      <c r="U29" s="56"/>
-      <c r="V29" s="56"/>
-      <c r="W29" s="56"/>
-      <c r="X29" s="56"/>
-      <c r="Y29" s="56"/>
-      <c r="Z29" s="56"/>
-    </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A30" s="56"/>
-      <c r="B30" s="56"/>
-      <c r="C30" s="56"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="55"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="56"/>
-      <c r="J30" s="56"/>
-      <c r="K30" s="56"/>
-      <c r="L30" s="56"/>
-      <c r="M30" s="56"/>
-      <c r="N30" s="56"/>
-      <c r="O30" s="56"/>
-      <c r="P30" s="56"/>
-      <c r="Q30" s="56"/>
-      <c r="R30" s="56"/>
-      <c r="S30" s="56"/>
-      <c r="T30" s="56"/>
-      <c r="U30" s="56"/>
-      <c r="V30" s="56"/>
-      <c r="W30" s="56"/>
-      <c r="X30" s="56"/>
-      <c r="Y30" s="56"/>
-      <c r="Z30" s="56"/>
-    </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A31" s="56"/>
-      <c r="B31" s="56"/>
-      <c r="C31" s="56"/>
-      <c r="D31" s="56"/>
-      <c r="E31" s="56"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="56"/>
-      <c r="H31" s="56"/>
-      <c r="I31" s="56"/>
-      <c r="J31" s="56"/>
-      <c r="K31" s="56"/>
-      <c r="L31" s="56"/>
-      <c r="M31" s="56"/>
-      <c r="N31" s="56"/>
-      <c r="O31" s="56"/>
-      <c r="P31" s="56"/>
-      <c r="Q31" s="56"/>
-      <c r="R31" s="56"/>
-      <c r="S31" s="56"/>
-      <c r="T31" s="56"/>
-      <c r="U31" s="56"/>
-      <c r="V31" s="56"/>
-      <c r="W31" s="56"/>
-      <c r="X31" s="56"/>
-      <c r="Y31" s="56"/>
-      <c r="Z31" s="56"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="40"/>
+      <c r="S31" s="45"/>
+      <c r="T31" s="52"/>
+      <c r="U31" s="52"/>
+      <c r="V31" s="52"/>
+      <c r="W31" s="52"/>
+      <c r="X31" s="52"/>
+      <c r="Y31" s="52"/>
+      <c r="Z31" s="52"/>
     </row>
     <row r="32" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A32" s="56"/>
-      <c r="B32" s="56"/>
-      <c r="C32" s="56"/>
-      <c r="D32" s="56"/>
-      <c r="E32" s="56"/>
-      <c r="F32" s="55"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="56"/>
-      <c r="I32" s="56"/>
-      <c r="J32" s="56"/>
-      <c r="K32" s="56"/>
-      <c r="L32" s="56"/>
-      <c r="M32" s="56"/>
-      <c r="N32" s="56"/>
-      <c r="O32" s="56"/>
-      <c r="P32" s="56"/>
-      <c r="Q32" s="56"/>
-      <c r="R32" s="56"/>
-      <c r="S32" s="56"/>
-      <c r="T32" s="56"/>
-      <c r="U32" s="56"/>
-      <c r="V32" s="56"/>
-      <c r="W32" s="56"/>
-      <c r="X32" s="56"/>
-      <c r="Y32" s="56"/>
-      <c r="Z32" s="56"/>
+      <c r="A32" s="52"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="51"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="52"/>
+      <c r="K32" s="52"/>
+      <c r="L32" s="52"/>
+      <c r="M32" s="52"/>
+      <c r="N32" s="52"/>
+      <c r="O32" s="52"/>
+      <c r="P32" s="52"/>
+      <c r="Q32" s="52"/>
+      <c r="R32" s="52"/>
+      <c r="S32" s="52"/>
+      <c r="T32" s="52"/>
+      <c r="U32" s="52"/>
+      <c r="V32" s="52"/>
+      <c r="W32" s="52"/>
+      <c r="X32" s="52"/>
+      <c r="Y32" s="52"/>
+      <c r="Z32" s="52"/>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A33" s="56"/>
-      <c r="B33" s="56"/>
-      <c r="C33" s="56"/>
-      <c r="D33" s="56"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="55"/>
-      <c r="G33" s="56"/>
-      <c r="H33" s="56"/>
-      <c r="I33" s="56"/>
-      <c r="J33" s="56"/>
-      <c r="K33" s="56"/>
-      <c r="L33" s="56"/>
-      <c r="M33" s="56"/>
-      <c r="N33" s="56"/>
-      <c r="O33" s="56"/>
-      <c r="P33" s="56"/>
-      <c r="Q33" s="56"/>
-      <c r="R33" s="56"/>
-      <c r="S33" s="56"/>
-      <c r="T33" s="56"/>
-      <c r="U33" s="56"/>
-      <c r="V33" s="56"/>
-      <c r="W33" s="56"/>
-      <c r="X33" s="56"/>
-      <c r="Y33" s="56"/>
-      <c r="Z33" s="56"/>
+      <c r="A33" s="52"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="52"/>
+      <c r="I33" s="52"/>
+      <c r="J33" s="52"/>
+      <c r="K33" s="52"/>
+      <c r="L33" s="52"/>
+      <c r="M33" s="52"/>
+      <c r="N33" s="52"/>
+      <c r="O33" s="52"/>
+      <c r="P33" s="52"/>
+      <c r="Q33" s="52"/>
+      <c r="R33" s="52"/>
+      <c r="S33" s="52"/>
+      <c r="T33" s="52"/>
+      <c r="U33" s="52"/>
+      <c r="V33" s="52"/>
+      <c r="W33" s="52"/>
+      <c r="X33" s="52"/>
+      <c r="Y33" s="52"/>
+      <c r="Z33" s="52"/>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A34" s="56"/>
-      <c r="B34" s="56"/>
-      <c r="C34" s="56"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="55"/>
-      <c r="G34" s="56"/>
-      <c r="H34" s="56"/>
-      <c r="I34" s="56"/>
-      <c r="J34" s="56"/>
-      <c r="K34" s="56"/>
-      <c r="L34" s="56"/>
-      <c r="M34" s="56"/>
-      <c r="N34" s="50" t="s">
-        <v>179</v>
-      </c>
-      <c r="O34" s="50" t="s">
-        <v>160</v>
-      </c>
-      <c r="P34" s="50" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q34" s="50" t="s">
-        <v>159</v>
-      </c>
-      <c r="R34" s="50" t="s">
-        <v>131</v>
-      </c>
-      <c r="S34" s="50" t="s">
-        <v>132</v>
-      </c>
-      <c r="T34" s="56"/>
-      <c r="U34" s="56"/>
-      <c r="V34" s="56"/>
-      <c r="W34" s="56"/>
-      <c r="X34" s="56"/>
-      <c r="Y34" s="56"/>
-      <c r="Z34" s="56"/>
+      <c r="A34" s="52"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="51"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="52"/>
+      <c r="K34" s="52"/>
+      <c r="L34" s="52"/>
+      <c r="M34" s="52"/>
+      <c r="N34" s="52"/>
+      <c r="O34" s="52"/>
+      <c r="P34" s="52"/>
+      <c r="Q34" s="52"/>
+      <c r="R34" s="52"/>
+      <c r="S34" s="52"/>
+      <c r="T34" s="52"/>
+      <c r="U34" s="52"/>
+      <c r="V34" s="52"/>
+      <c r="W34" s="52"/>
+      <c r="X34" s="52"/>
+      <c r="Y34" s="52"/>
+      <c r="Z34" s="52"/>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A35" s="56"/>
-      <c r="B35" s="56"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
-      <c r="F35" s="55"/>
-      <c r="G35" s="56"/>
-      <c r="H35" s="56"/>
-      <c r="I35" s="56"/>
-      <c r="J35" s="56"/>
-      <c r="K35" s="56"/>
-      <c r="L35" s="56"/>
-      <c r="M35" s="56"/>
-      <c r="N35" s="50" t="s">
-        <v>164</v>
-      </c>
-      <c r="O35"/>
-      <c r="P35"/>
-      <c r="Q35"/>
-      <c r="R35"/>
-      <c r="S35"/>
-      <c r="T35" s="56"/>
-      <c r="U35" s="56"/>
-      <c r="V35" s="56"/>
-      <c r="W35" s="56"/>
-      <c r="X35" s="56"/>
-      <c r="Y35" s="56"/>
-      <c r="Z35" s="56"/>
+      <c r="A35" s="52"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="51"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="52"/>
+      <c r="K35" s="52"/>
+      <c r="L35" s="52"/>
+      <c r="M35" s="52"/>
+      <c r="N35" s="52"/>
+      <c r="O35" s="52"/>
+      <c r="P35" s="52"/>
+      <c r="Q35" s="52"/>
+      <c r="R35" s="52"/>
+      <c r="S35" s="52"/>
+      <c r="T35" s="52"/>
+      <c r="U35" s="52"/>
+      <c r="V35" s="52"/>
+      <c r="W35" s="52"/>
+      <c r="X35" s="52"/>
+      <c r="Y35" s="52"/>
+      <c r="Z35" s="52"/>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A36" s="56"/>
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="E36" s="56"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="56"/>
-      <c r="H36" s="56"/>
-      <c r="I36" s="56"/>
-      <c r="J36" s="56"/>
-      <c r="K36" s="56"/>
-      <c r="L36" s="56"/>
-      <c r="M36" s="56"/>
-      <c r="N36" t="s">
-        <v>165</v>
-      </c>
-      <c r="O36">
-        <v>999</v>
-      </c>
-      <c r="P36">
-        <v>999</v>
-      </c>
-      <c r="Q36">
-        <v>999</v>
-      </c>
-      <c r="R36" t="s">
-        <v>180</v>
-      </c>
-      <c r="S36" t="s">
-        <v>180</v>
-      </c>
-      <c r="T36" s="56"/>
-      <c r="U36" s="56"/>
-      <c r="V36" s="56"/>
-      <c r="W36" s="56"/>
-      <c r="X36" s="56"/>
-      <c r="Y36" s="56"/>
-      <c r="Z36" s="56"/>
+      <c r="A36" s="52"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="52"/>
+      <c r="J36" s="52"/>
+      <c r="K36" s="52"/>
+      <c r="L36" s="52"/>
+      <c r="M36" s="52"/>
+      <c r="N36" s="47"/>
+      <c r="O36" s="47"/>
+      <c r="P36" s="47"/>
+      <c r="Q36" s="47"/>
+      <c r="R36" s="47"/>
+      <c r="S36" s="47"/>
+      <c r="T36" s="52"/>
+      <c r="U36" s="52"/>
+      <c r="V36" s="52"/>
+      <c r="W36" s="52"/>
+      <c r="X36" s="52"/>
+      <c r="Y36" s="52"/>
+      <c r="Z36" s="52"/>
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A37" s="56"/>
-      <c r="B37" s="56"/>
-      <c r="C37" s="56"/>
-      <c r="D37" s="56"/>
-      <c r="E37" s="56"/>
-      <c r="F37" s="55"/>
-      <c r="G37" s="56"/>
-      <c r="H37" s="56"/>
-      <c r="I37" s="56"/>
-      <c r="J37" s="56"/>
-      <c r="K37" s="56"/>
-      <c r="L37" s="56"/>
-      <c r="M37" s="56"/>
-      <c r="N37" t="s">
-        <v>181</v>
-      </c>
-      <c r="O37">
-        <v>0.11600000000000001</v>
-      </c>
-      <c r="P37">
-        <v>5.7000000000000002E-2</v>
-      </c>
-      <c r="Q37">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="R37">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="S37">
-        <v>0.22800000000000001</v>
-      </c>
-      <c r="T37" s="56"/>
-      <c r="U37" s="56"/>
-      <c r="V37" s="56"/>
-      <c r="W37" s="56"/>
-      <c r="X37" s="56"/>
-      <c r="Y37" s="56"/>
-      <c r="Z37" s="56"/>
+      <c r="A37" s="52"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="51"/>
+      <c r="G37" s="52"/>
+      <c r="H37" s="52"/>
+      <c r="I37" s="52"/>
+      <c r="J37" s="52"/>
+      <c r="K37" s="52"/>
+      <c r="L37" s="52"/>
+      <c r="M37" s="52"/>
+      <c r="N37" s="47"/>
+      <c r="O37"/>
+      <c r="P37"/>
+      <c r="Q37"/>
+      <c r="R37"/>
+      <c r="S37"/>
+      <c r="T37" s="52"/>
+      <c r="U37" s="52"/>
+      <c r="V37" s="52"/>
+      <c r="W37" s="52"/>
+      <c r="X37" s="52"/>
+      <c r="Y37" s="52"/>
+      <c r="Z37" s="52"/>
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A38" s="56"/>
-      <c r="B38" s="56"/>
-      <c r="C38" s="56"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="55"/>
-      <c r="G38" s="56"/>
-      <c r="H38" s="56"/>
-      <c r="I38" s="56"/>
-      <c r="J38" s="56"/>
-      <c r="K38" s="56"/>
-      <c r="L38" s="56"/>
-      <c r="M38" s="56"/>
-      <c r="N38" t="s">
-        <v>167</v>
-      </c>
-      <c r="O38">
-        <v>0.01</v>
-      </c>
-      <c r="P38">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>24</v>
-      </c>
-      <c r="R38">
-        <v>4.0000000000000001E-3</v>
-      </c>
-      <c r="S38">
-        <v>1.6E-2</v>
-      </c>
-      <c r="T38" s="56"/>
-      <c r="U38" s="56"/>
-      <c r="V38" s="56"/>
-      <c r="W38" s="56"/>
-      <c r="X38" s="56"/>
-      <c r="Y38" s="56"/>
-      <c r="Z38" s="56"/>
+      <c r="A38" s="52"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="51"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="52"/>
+      <c r="L38" s="52"/>
+      <c r="M38" s="52"/>
+      <c r="N38"/>
+      <c r="O38"/>
+      <c r="P38"/>
+      <c r="Q38"/>
+      <c r="R38"/>
+      <c r="S38"/>
+      <c r="T38" s="52"/>
+      <c r="U38" s="52"/>
+      <c r="V38" s="52"/>
+      <c r="W38" s="52"/>
+      <c r="X38" s="52"/>
+      <c r="Y38" s="52"/>
+      <c r="Z38" s="52"/>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A39" s="56"/>
-      <c r="B39" s="56"/>
-      <c r="C39" s="56"/>
-      <c r="D39" s="56"/>
-      <c r="E39" s="56"/>
-      <c r="F39" s="55"/>
-      <c r="G39" s="56"/>
-      <c r="H39" s="56"/>
-      <c r="I39" s="56"/>
-      <c r="J39" s="56"/>
-      <c r="K39" s="56"/>
-      <c r="L39" s="56"/>
-      <c r="M39" s="56"/>
-      <c r="N39" t="s">
-        <v>168</v>
-      </c>
-      <c r="O39">
-        <v>7.3999999999999996E-2</v>
-      </c>
-      <c r="P39">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>24</v>
-      </c>
-      <c r="R39">
-        <v>3.3000000000000002E-2</v>
-      </c>
-      <c r="S39">
-        <v>0.115</v>
-      </c>
-      <c r="T39" s="56"/>
-      <c r="U39" s="56"/>
-      <c r="V39" s="56"/>
-      <c r="W39" s="56"/>
-      <c r="X39" s="56"/>
-      <c r="Y39" s="56"/>
-      <c r="Z39" s="56"/>
+      <c r="A39" s="52"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="51"/>
+      <c r="G39" s="52"/>
+      <c r="H39" s="52"/>
+      <c r="I39" s="52"/>
+      <c r="J39" s="52"/>
+      <c r="K39" s="52"/>
+      <c r="L39" s="52"/>
+      <c r="M39" s="52"/>
+      <c r="N39"/>
+      <c r="O39"/>
+      <c r="P39"/>
+      <c r="Q39"/>
+      <c r="R39"/>
+      <c r="S39"/>
+      <c r="T39" s="52"/>
+      <c r="U39" s="52"/>
+      <c r="V39" s="52"/>
+      <c r="W39" s="52"/>
+      <c r="X39" s="52"/>
+      <c r="Y39" s="52"/>
+      <c r="Z39" s="52"/>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A40" s="56"/>
-      <c r="B40" s="56"/>
-      <c r="C40" s="56"/>
-      <c r="D40" s="56"/>
-      <c r="E40" s="56"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="56"/>
-      <c r="H40" s="56"/>
-      <c r="I40" s="56"/>
-      <c r="J40" s="56"/>
-      <c r="K40" s="56"/>
-      <c r="L40" s="56"/>
-      <c r="M40" s="56"/>
-      <c r="N40" t="s">
-        <v>182</v>
-      </c>
-      <c r="O40">
-        <v>999</v>
-      </c>
-      <c r="P40">
-        <v>999</v>
-      </c>
-      <c r="Q40">
-        <v>999</v>
-      </c>
-      <c r="R40" t="s">
-        <v>180</v>
-      </c>
-      <c r="S40" t="s">
-        <v>180</v>
-      </c>
-      <c r="T40" s="56"/>
-      <c r="U40" s="56"/>
-      <c r="V40" s="56"/>
-      <c r="W40" s="56"/>
-      <c r="X40" s="56"/>
-      <c r="Y40" s="56"/>
-      <c r="Z40" s="56"/>
+      <c r="A40" s="52"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="51"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="52"/>
+      <c r="J40" s="52"/>
+      <c r="K40" s="52"/>
+      <c r="L40" s="52"/>
+      <c r="M40" s="52"/>
+      <c r="N40"/>
+      <c r="O40"/>
+      <c r="P40"/>
+      <c r="Q40"/>
+      <c r="R40"/>
+      <c r="S40"/>
+      <c r="T40" s="52"/>
+      <c r="U40" s="52"/>
+      <c r="V40" s="52"/>
+      <c r="W40" s="52"/>
+      <c r="X40" s="52"/>
+      <c r="Y40" s="52"/>
+      <c r="Z40" s="52"/>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A41" s="56"/>
-      <c r="B41" s="56"/>
-      <c r="C41" s="56"/>
-      <c r="D41" s="56"/>
-      <c r="E41" s="56"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="56"/>
-      <c r="H41" s="56"/>
-      <c r="I41" s="56"/>
-      <c r="J41" s="56"/>
-      <c r="K41" s="56"/>
-      <c r="L41" s="56"/>
-      <c r="M41" s="56"/>
-      <c r="N41" t="s">
-        <v>169</v>
-      </c>
-      <c r="O41">
-        <v>999</v>
-      </c>
-      <c r="P41">
-        <v>999</v>
-      </c>
-      <c r="Q41">
-        <v>999</v>
-      </c>
-      <c r="R41" t="s">
-        <v>180</v>
-      </c>
-      <c r="S41" t="s">
-        <v>180</v>
-      </c>
-      <c r="T41" s="56"/>
-      <c r="U41" s="56"/>
-      <c r="V41" s="56"/>
-      <c r="W41" s="56"/>
-      <c r="X41" s="56"/>
-      <c r="Y41" s="56"/>
-      <c r="Z41" s="56"/>
+      <c r="A41" s="52"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="52"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="52"/>
+      <c r="F41" s="51"/>
+      <c r="G41" s="52"/>
+      <c r="H41" s="52"/>
+      <c r="I41" s="52"/>
+      <c r="J41" s="52"/>
+      <c r="K41" s="52"/>
+      <c r="L41" s="52"/>
+      <c r="M41" s="52"/>
+      <c r="N41"/>
+      <c r="O41"/>
+      <c r="P41"/>
+      <c r="Q41"/>
+      <c r="R41"/>
+      <c r="S41"/>
+      <c r="T41" s="52"/>
+      <c r="U41" s="52"/>
+      <c r="V41" s="52"/>
+      <c r="W41" s="52"/>
+      <c r="X41" s="52"/>
+      <c r="Y41" s="52"/>
+      <c r="Z41" s="52"/>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A42" s="56"/>
-      <c r="B42" s="56"/>
-      <c r="C42" s="56"/>
-      <c r="D42" s="56"/>
-      <c r="E42" s="56"/>
-      <c r="F42" s="55"/>
-      <c r="G42" s="56"/>
-      <c r="H42" s="56"/>
-      <c r="I42" s="56"/>
-      <c r="J42" s="56"/>
-      <c r="K42" s="56"/>
-      <c r="L42" s="56"/>
-      <c r="M42" s="56"/>
-      <c r="N42" t="s">
-        <v>183</v>
-      </c>
-      <c r="O42">
-        <v>0.01</v>
-      </c>
-      <c r="P42">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="Q42">
-        <v>4.8000000000000001E-2</v>
-      </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42">
-        <v>0.02</v>
-      </c>
-      <c r="T42" s="56"/>
-      <c r="U42" s="56"/>
-      <c r="V42" s="56"/>
-      <c r="W42" s="56"/>
-      <c r="X42" s="56"/>
-      <c r="Y42" s="56"/>
-      <c r="Z42" s="56"/>
+      <c r="A42" s="52"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="51"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="52"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="52"/>
+      <c r="K42" s="52"/>
+      <c r="L42" s="52"/>
+      <c r="M42" s="52"/>
+      <c r="N42"/>
+      <c r="O42"/>
+      <c r="P42"/>
+      <c r="Q42"/>
+      <c r="R42"/>
+      <c r="S42"/>
+      <c r="T42" s="52"/>
+      <c r="U42" s="52"/>
+      <c r="V42" s="52"/>
+      <c r="W42" s="52"/>
+      <c r="X42" s="52"/>
+      <c r="Y42" s="52"/>
+      <c r="Z42" s="52"/>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A43" s="56"/>
-      <c r="B43" s="56"/>
-      <c r="C43" s="56"/>
-      <c r="D43" s="56"/>
-      <c r="E43" s="56"/>
-      <c r="F43" s="55"/>
-      <c r="G43" s="56"/>
-      <c r="H43" s="56"/>
-      <c r="I43" s="56"/>
-      <c r="J43" s="56"/>
-      <c r="K43" s="56"/>
-      <c r="L43" s="56"/>
-      <c r="M43" s="56"/>
-      <c r="N43" t="s">
-        <v>170</v>
-      </c>
-      <c r="O43">
-        <v>0.03</v>
-      </c>
-      <c r="P43">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>24</v>
-      </c>
-      <c r="R43">
-        <v>2.4E-2</v>
-      </c>
-      <c r="S43">
-        <v>3.5999999999999997E-2</v>
-      </c>
-      <c r="T43" s="56"/>
-      <c r="U43" s="56"/>
-      <c r="V43" s="56"/>
-      <c r="W43" s="56"/>
-      <c r="X43" s="56"/>
-      <c r="Y43" s="56"/>
-      <c r="Z43" s="56"/>
+      <c r="A43" s="52"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="51"/>
+      <c r="G43" s="52"/>
+      <c r="H43" s="52"/>
+      <c r="I43" s="52"/>
+      <c r="J43" s="52"/>
+      <c r="K43" s="52"/>
+      <c r="L43" s="52"/>
+      <c r="M43" s="52"/>
+      <c r="N43"/>
+      <c r="O43"/>
+      <c r="P43"/>
+      <c r="Q43"/>
+      <c r="R43"/>
+      <c r="S43"/>
+      <c r="T43" s="52"/>
+      <c r="U43" s="52"/>
+      <c r="V43" s="52"/>
+      <c r="W43" s="52"/>
+      <c r="X43" s="52"/>
+      <c r="Y43" s="52"/>
+      <c r="Z43" s="52"/>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A44" s="56"/>
-      <c r="B44" s="56"/>
-      <c r="C44" s="56"/>
-      <c r="D44" s="56"/>
-      <c r="E44" s="56"/>
-      <c r="F44" s="55"/>
-      <c r="G44" s="56"/>
-      <c r="H44" s="56"/>
-      <c r="I44" s="56"/>
-      <c r="J44" s="56"/>
-      <c r="K44" s="56"/>
-      <c r="L44" s="56"/>
-      <c r="M44" s="56"/>
-      <c r="N44" s="50" t="s">
-        <v>86</v>
-      </c>
+      <c r="A44" s="52"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="52"/>
+      <c r="D44" s="52"/>
+      <c r="E44" s="52"/>
+      <c r="F44" s="51"/>
+      <c r="G44" s="52"/>
+      <c r="H44" s="52"/>
+      <c r="I44" s="52"/>
+      <c r="J44" s="52"/>
+      <c r="K44" s="52"/>
+      <c r="L44" s="52"/>
+      <c r="M44" s="52"/>
+      <c r="N44"/>
       <c r="O44"/>
       <c r="P44"/>
       <c r="Q44"/>
       <c r="R44"/>
       <c r="S44"/>
-      <c r="T44" s="56"/>
-      <c r="U44" s="56"/>
-      <c r="V44" s="56"/>
-      <c r="W44" s="56"/>
-      <c r="X44" s="56"/>
-      <c r="Y44" s="56"/>
-      <c r="Z44" s="56"/>
+      <c r="T44" s="52"/>
+      <c r="U44" s="52"/>
+      <c r="V44" s="52"/>
+      <c r="W44" s="52"/>
+      <c r="X44" s="52"/>
+      <c r="Y44" s="52"/>
+      <c r="Z44" s="52"/>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A45" s="56"/>
-      <c r="B45" s="56"/>
-      <c r="C45" s="56"/>
-      <c r="D45" s="56"/>
-      <c r="E45" s="56"/>
-      <c r="F45" s="55"/>
-      <c r="G45" s="56"/>
-      <c r="H45" s="56"/>
-      <c r="I45" s="56"/>
-      <c r="J45" s="56"/>
-      <c r="K45" s="56"/>
-      <c r="L45" s="56"/>
-      <c r="M45" s="56"/>
-      <c r="N45" t="s">
-        <v>171</v>
-      </c>
-      <c r="O45">
-        <v>999</v>
-      </c>
-      <c r="P45">
-        <v>999</v>
-      </c>
-      <c r="Q45">
-        <v>999</v>
-      </c>
-      <c r="R45" t="s">
-        <v>180</v>
-      </c>
-      <c r="S45" t="s">
-        <v>180</v>
-      </c>
-      <c r="T45" s="56"/>
-      <c r="U45" s="56"/>
-      <c r="V45" s="56"/>
-      <c r="W45" s="56"/>
-      <c r="X45" s="56"/>
-      <c r="Y45" s="56"/>
-      <c r="Z45" s="56"/>
+      <c r="A45" s="52"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="52"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="52"/>
+      <c r="H45" s="52"/>
+      <c r="I45" s="52"/>
+      <c r="J45" s="52"/>
+      <c r="K45" s="52"/>
+      <c r="L45" s="52"/>
+      <c r="M45" s="52"/>
+      <c r="N45"/>
+      <c r="O45"/>
+      <c r="P45"/>
+      <c r="Q45"/>
+      <c r="R45"/>
+      <c r="S45"/>
+      <c r="T45" s="52"/>
+      <c r="U45" s="52"/>
+      <c r="V45" s="52"/>
+      <c r="W45" s="52"/>
+      <c r="X45" s="52"/>
+      <c r="Y45" s="52"/>
+      <c r="Z45" s="52"/>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A46" s="56"/>
-      <c r="B46" s="56"/>
-      <c r="C46" s="56"/>
-      <c r="D46" s="56"/>
-      <c r="E46" s="56"/>
-      <c r="F46" s="55"/>
-      <c r="G46" s="56"/>
-      <c r="H46" s="56"/>
-      <c r="I46" s="56"/>
-      <c r="J46" s="56"/>
-      <c r="K46" s="56"/>
-      <c r="L46" s="56"/>
-      <c r="M46" s="56"/>
-      <c r="N46" t="s">
-        <v>184</v>
-      </c>
-      <c r="O46">
-        <v>0.39500000000000002</v>
-      </c>
-      <c r="P46">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>24</v>
-      </c>
-      <c r="R46">
-        <v>0.312</v>
-      </c>
-      <c r="S46">
-        <v>0.47799999999999998</v>
-      </c>
-      <c r="T46" s="56"/>
-      <c r="U46" s="56"/>
-      <c r="V46" s="56"/>
-      <c r="W46" s="56"/>
-      <c r="X46" s="56"/>
-      <c r="Y46" s="56"/>
-      <c r="Z46" s="56"/>
+      <c r="A46" s="52"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="51"/>
+      <c r="G46" s="52"/>
+      <c r="H46" s="52"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="52"/>
+      <c r="K46" s="52"/>
+      <c r="L46" s="52"/>
+      <c r="M46" s="52"/>
+      <c r="N46" s="47"/>
+      <c r="O46"/>
+      <c r="P46"/>
+      <c r="Q46"/>
+      <c r="R46"/>
+      <c r="S46"/>
+      <c r="T46" s="52"/>
+      <c r="U46" s="52"/>
+      <c r="V46" s="52"/>
+      <c r="W46" s="52"/>
+      <c r="X46" s="52"/>
+      <c r="Y46" s="52"/>
+      <c r="Z46" s="52"/>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A47" s="56"/>
-      <c r="B47" s="56"/>
-      <c r="C47" s="56"/>
-      <c r="D47" s="56"/>
-      <c r="E47" s="56"/>
-      <c r="F47" s="55"/>
-      <c r="G47" s="56"/>
-      <c r="H47" s="56"/>
-      <c r="I47" s="56"/>
-      <c r="J47" s="56"/>
-      <c r="K47" s="56"/>
-      <c r="L47" s="56"/>
-      <c r="M47" s="56"/>
-      <c r="N47" t="s">
-        <v>172</v>
-      </c>
-      <c r="O47">
-        <v>-0.112</v>
-      </c>
-      <c r="P47">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>24</v>
-      </c>
-      <c r="R47">
-        <v>-0.156</v>
-      </c>
-      <c r="S47">
-        <v>-6.8000000000000005E-2</v>
-      </c>
-      <c r="T47" s="56"/>
-      <c r="U47" s="56"/>
-      <c r="V47" s="56"/>
-      <c r="W47" s="56"/>
-      <c r="X47" s="56"/>
-      <c r="Y47" s="56"/>
-      <c r="Z47" s="56"/>
+      <c r="A47" s="52"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="51"/>
+      <c r="G47" s="52"/>
+      <c r="H47" s="52"/>
+      <c r="I47" s="52"/>
+      <c r="J47" s="52"/>
+      <c r="K47" s="52"/>
+      <c r="L47" s="52"/>
+      <c r="M47" s="52"/>
+      <c r="N47"/>
+      <c r="O47"/>
+      <c r="P47"/>
+      <c r="Q47"/>
+      <c r="R47"/>
+      <c r="S47"/>
+      <c r="T47" s="52"/>
+      <c r="U47" s="52"/>
+      <c r="V47" s="52"/>
+      <c r="W47" s="52"/>
+      <c r="X47" s="52"/>
+      <c r="Y47" s="52"/>
+      <c r="Z47" s="52"/>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A48" s="56"/>
-      <c r="B48" s="56"/>
-      <c r="C48" s="56"/>
-      <c r="D48" s="56"/>
-      <c r="E48" s="56"/>
-      <c r="F48" s="55"/>
-      <c r="G48" s="56"/>
-      <c r="H48" s="56"/>
-      <c r="I48" s="56"/>
-      <c r="J48" s="56"/>
-      <c r="K48" s="56"/>
-      <c r="L48" s="56"/>
-      <c r="M48" s="56"/>
-      <c r="N48" t="s">
-        <v>173</v>
-      </c>
-      <c r="O48">
-        <v>999</v>
-      </c>
-      <c r="P48">
-        <v>999</v>
-      </c>
+      <c r="A48" s="52"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="51"/>
+      <c r="G48" s="52"/>
+      <c r="H48" s="52"/>
+      <c r="I48" s="52"/>
+      <c r="J48" s="52"/>
+      <c r="K48" s="52"/>
+      <c r="L48" s="52"/>
+      <c r="M48" s="52"/>
+      <c r="N48"/>
+      <c r="O48"/>
+      <c r="P48"/>
       <c r="Q48"/>
       <c r="R48"/>
       <c r="S48"/>
-      <c r="T48" s="56"/>
-      <c r="U48" s="56"/>
-      <c r="V48" s="56"/>
-      <c r="W48" s="56"/>
-      <c r="X48" s="56"/>
-      <c r="Y48" s="56"/>
-      <c r="Z48" s="56"/>
+      <c r="T48" s="52"/>
+      <c r="U48" s="52"/>
+      <c r="V48" s="52"/>
+      <c r="W48" s="52"/>
+      <c r="X48" s="52"/>
+      <c r="Y48" s="52"/>
+      <c r="Z48" s="52"/>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A49" s="56"/>
-      <c r="B49" s="56"/>
-      <c r="C49" s="56"/>
-      <c r="D49" s="56"/>
-      <c r="E49" s="56"/>
-      <c r="F49" s="55"/>
-      <c r="G49" s="56"/>
-      <c r="H49" s="56"/>
-      <c r="I49" s="56"/>
-      <c r="J49" s="56"/>
-      <c r="K49" s="56"/>
-      <c r="L49" s="56"/>
-      <c r="M49" s="56"/>
-      <c r="N49" t="s">
-        <v>185</v>
-      </c>
-      <c r="O49">
-        <v>-0.13100000000000001</v>
-      </c>
-      <c r="P49">
-        <v>3.5000000000000003E-2</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>24</v>
-      </c>
-      <c r="R49">
-        <v>-0.19900000000000001</v>
-      </c>
-      <c r="S49">
-        <v>-6.3E-2</v>
-      </c>
-      <c r="T49" s="56"/>
-      <c r="U49" s="56"/>
-      <c r="V49" s="56"/>
-      <c r="W49" s="56"/>
-      <c r="X49" s="56"/>
-      <c r="Y49" s="56"/>
-      <c r="Z49" s="56"/>
+      <c r="A49" s="52"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="51"/>
+      <c r="G49" s="52"/>
+      <c r="H49" s="52"/>
+      <c r="I49" s="52"/>
+      <c r="J49" s="52"/>
+      <c r="K49" s="52"/>
+      <c r="L49" s="52"/>
+      <c r="M49" s="52"/>
+      <c r="N49"/>
+      <c r="O49"/>
+      <c r="P49"/>
+      <c r="Q49"/>
+      <c r="R49"/>
+      <c r="S49"/>
+      <c r="T49" s="52"/>
+      <c r="U49" s="52"/>
+      <c r="V49" s="52"/>
+      <c r="W49" s="52"/>
+      <c r="X49" s="52"/>
+      <c r="Y49" s="52"/>
+      <c r="Z49" s="52"/>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A50" s="56"/>
-      <c r="B50" s="56"/>
-      <c r="C50" s="56"/>
-      <c r="D50" s="56"/>
-      <c r="E50" s="56"/>
-      <c r="F50" s="55"/>
-      <c r="G50" s="56"/>
-      <c r="H50" s="56"/>
-      <c r="I50" s="56"/>
-      <c r="J50" s="56"/>
-      <c r="K50" s="56"/>
-      <c r="L50" s="56"/>
-      <c r="M50" s="56"/>
-      <c r="N50" t="s">
-        <v>174</v>
-      </c>
-      <c r="O50">
-        <v>-0.14399999999999999</v>
-      </c>
-      <c r="P50">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>24</v>
-      </c>
-      <c r="R50">
-        <v>-0.186</v>
-      </c>
-      <c r="S50">
-        <v>-0.10199999999999999</v>
-      </c>
-      <c r="T50" s="56"/>
-      <c r="U50" s="56"/>
-      <c r="V50" s="56"/>
-      <c r="W50" s="56"/>
-      <c r="X50" s="56"/>
-      <c r="Y50" s="56"/>
-      <c r="Z50" s="56"/>
+      <c r="A50" s="52"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="52"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="51"/>
+      <c r="G50" s="52"/>
+      <c r="H50" s="52"/>
+      <c r="I50" s="52"/>
+      <c r="J50" s="52"/>
+      <c r="K50" s="52"/>
+      <c r="L50" s="52"/>
+      <c r="M50" s="52"/>
+      <c r="N50"/>
+      <c r="O50"/>
+      <c r="P50"/>
+      <c r="Q50"/>
+      <c r="R50"/>
+      <c r="S50"/>
+      <c r="T50" s="52"/>
+      <c r="U50" s="52"/>
+      <c r="V50" s="52"/>
+      <c r="W50" s="52"/>
+      <c r="X50" s="52"/>
+      <c r="Y50" s="52"/>
+      <c r="Z50" s="52"/>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A51" s="56"/>
-      <c r="B51" s="56"/>
-      <c r="C51" s="56"/>
-      <c r="D51" s="56"/>
-      <c r="E51" s="56"/>
-      <c r="F51" s="55"/>
-      <c r="G51" s="56"/>
-      <c r="H51" s="56"/>
-      <c r="I51" s="56"/>
-      <c r="J51" s="56"/>
-      <c r="K51" s="56"/>
-      <c r="L51" s="56"/>
-      <c r="M51" s="56"/>
-      <c r="N51" t="s">
-        <v>175</v>
-      </c>
-      <c r="O51">
-        <v>-0.16600000000000001</v>
-      </c>
-      <c r="P51">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>24</v>
-      </c>
-      <c r="R51">
-        <v>-0.20799999999999999</v>
-      </c>
-      <c r="S51">
-        <v>-0.124</v>
-      </c>
-      <c r="T51" s="56"/>
-      <c r="U51" s="56"/>
-      <c r="V51" s="56"/>
-      <c r="W51" s="56"/>
-      <c r="X51" s="56"/>
-      <c r="Y51" s="56"/>
-      <c r="Z51" s="56"/>
+      <c r="A51" s="52"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="52"/>
+      <c r="D51" s="52"/>
+      <c r="E51" s="52"/>
+      <c r="F51" s="51"/>
+      <c r="G51" s="52"/>
+      <c r="H51" s="52"/>
+      <c r="I51" s="52"/>
+      <c r="J51" s="52"/>
+      <c r="K51" s="52"/>
+      <c r="L51" s="52"/>
+      <c r="M51" s="52"/>
+      <c r="N51"/>
+      <c r="O51"/>
+      <c r="P51"/>
+      <c r="Q51"/>
+      <c r="R51"/>
+      <c r="S51"/>
+      <c r="T51" s="52"/>
+      <c r="U51" s="52"/>
+      <c r="V51" s="52"/>
+      <c r="W51" s="52"/>
+      <c r="X51" s="52"/>
+      <c r="Y51" s="52"/>
+      <c r="Z51" s="52"/>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A52" s="56"/>
-      <c r="B52" s="56"/>
-      <c r="C52" s="56"/>
-      <c r="D52" s="56"/>
-      <c r="E52" s="56"/>
-      <c r="F52" s="55"/>
-      <c r="G52" s="56"/>
-      <c r="H52" s="56"/>
-      <c r="I52" s="56"/>
-      <c r="J52" s="56"/>
-      <c r="K52" s="56"/>
-      <c r="L52" s="56"/>
-      <c r="M52" s="56"/>
-      <c r="N52" t="s">
-        <v>186</v>
-      </c>
-      <c r="O52">
-        <v>0.13900000000000001</v>
-      </c>
-      <c r="P52">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>24</v>
-      </c>
-      <c r="R52">
-        <v>9.5000000000000001E-2</v>
-      </c>
-      <c r="S52">
-        <v>0.183</v>
-      </c>
-      <c r="T52" s="56"/>
-      <c r="U52" s="56"/>
-      <c r="V52" s="56"/>
-      <c r="W52" s="56"/>
-      <c r="X52" s="56"/>
-      <c r="Y52" s="56"/>
-      <c r="Z52" s="56"/>
+      <c r="A52" s="52"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="52"/>
+      <c r="D52" s="52"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="51"/>
+      <c r="G52" s="52"/>
+      <c r="H52" s="52"/>
+      <c r="I52" s="52"/>
+      <c r="J52" s="52"/>
+      <c r="K52" s="52"/>
+      <c r="L52" s="52"/>
+      <c r="M52" s="52"/>
+      <c r="N52"/>
+      <c r="O52"/>
+      <c r="P52"/>
+      <c r="Q52"/>
+      <c r="R52"/>
+      <c r="S52"/>
+      <c r="T52" s="52"/>
+      <c r="U52" s="52"/>
+      <c r="V52" s="52"/>
+      <c r="W52" s="52"/>
+      <c r="X52" s="52"/>
+      <c r="Y52" s="52"/>
+      <c r="Z52" s="52"/>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A53" s="56"/>
-      <c r="B53" s="56"/>
-      <c r="C53" s="56"/>
-      <c r="D53" s="56"/>
-      <c r="E53" s="56"/>
-      <c r="F53" s="55"/>
-      <c r="G53" s="56"/>
-      <c r="H53" s="56"/>
-      <c r="I53" s="56"/>
-      <c r="J53" s="56"/>
-      <c r="K53" s="56"/>
-      <c r="L53" s="56"/>
-      <c r="M53" s="56"/>
-      <c r="N53" t="s">
-        <v>187</v>
-      </c>
-      <c r="O53">
-        <v>999</v>
-      </c>
-      <c r="P53">
-        <v>999</v>
-      </c>
-      <c r="Q53">
-        <v>999</v>
-      </c>
-      <c r="R53" t="s">
-        <v>180</v>
-      </c>
-      <c r="S53" t="s">
-        <v>180</v>
-      </c>
-      <c r="T53" s="56"/>
-      <c r="U53" s="56"/>
-      <c r="V53" s="56"/>
-      <c r="W53" s="56"/>
-      <c r="X53" s="56"/>
-      <c r="Y53" s="56"/>
-      <c r="Z53" s="56"/>
+      <c r="A53" s="52"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="52"/>
+      <c r="D53" s="52"/>
+      <c r="E53" s="52"/>
+      <c r="F53" s="51"/>
+      <c r="G53" s="52"/>
+      <c r="H53" s="52"/>
+      <c r="I53" s="52"/>
+      <c r="J53" s="52"/>
+      <c r="K53" s="52"/>
+      <c r="L53" s="52"/>
+      <c r="M53" s="52"/>
+      <c r="N53"/>
+      <c r="O53"/>
+      <c r="P53"/>
+      <c r="Q53"/>
+      <c r="R53"/>
+      <c r="S53"/>
+      <c r="T53" s="52"/>
+      <c r="U53" s="52"/>
+      <c r="V53" s="52"/>
+      <c r="W53" s="52"/>
+      <c r="X53" s="52"/>
+      <c r="Y53" s="52"/>
+      <c r="Z53" s="52"/>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A54" s="56"/>
-      <c r="B54" s="56"/>
-      <c r="C54" s="56"/>
-      <c r="D54" s="56"/>
-      <c r="E54" s="56"/>
-      <c r="F54" s="55"/>
-      <c r="G54" s="56"/>
-      <c r="H54" s="56"/>
-      <c r="I54" s="56"/>
-      <c r="J54" s="56"/>
-      <c r="K54" s="56"/>
-      <c r="L54" s="56"/>
-      <c r="M54" s="56"/>
-      <c r="N54" t="s">
-        <v>188</v>
-      </c>
-      <c r="O54">
-        <v>7.0999999999999994E-2</v>
-      </c>
-      <c r="P54">
-        <v>4.5999999999999999E-2</v>
-      </c>
-      <c r="Q54">
-        <v>0.125</v>
-      </c>
-      <c r="R54">
-        <v>-1.9E-2</v>
-      </c>
-      <c r="S54">
-        <v>0.161</v>
-      </c>
-      <c r="T54" s="56"/>
-      <c r="U54" s="56"/>
-      <c r="V54" s="56"/>
-      <c r="W54" s="56"/>
-      <c r="X54" s="56"/>
-      <c r="Y54" s="56"/>
-      <c r="Z54" s="56"/>
+      <c r="A54" s="52"/>
+      <c r="B54" s="52"/>
+      <c r="C54" s="52"/>
+      <c r="D54" s="52"/>
+      <c r="E54" s="52"/>
+      <c r="F54" s="51"/>
+      <c r="G54" s="52"/>
+      <c r="H54" s="52"/>
+      <c r="I54" s="52"/>
+      <c r="J54" s="52"/>
+      <c r="K54" s="52"/>
+      <c r="L54" s="52"/>
+      <c r="M54" s="52"/>
+      <c r="N54"/>
+      <c r="O54"/>
+      <c r="P54"/>
+      <c r="Q54"/>
+      <c r="R54"/>
+      <c r="S54"/>
+      <c r="T54" s="52"/>
+      <c r="U54" s="52"/>
+      <c r="V54" s="52"/>
+      <c r="W54" s="52"/>
+      <c r="X54" s="52"/>
+      <c r="Y54" s="52"/>
+      <c r="Z54" s="52"/>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A55" s="56"/>
-      <c r="B55" s="56"/>
-      <c r="C55" s="56"/>
-      <c r="D55" s="56"/>
-      <c r="E55" s="56"/>
-      <c r="F55" s="55"/>
-      <c r="G55" s="56"/>
-      <c r="H55" s="56"/>
-      <c r="I55" s="56"/>
-      <c r="J55" s="56"/>
-      <c r="K55" s="56"/>
-      <c r="L55" s="56"/>
-      <c r="M55" s="56"/>
-      <c r="N55" t="s">
-        <v>189</v>
-      </c>
-      <c r="O55">
-        <v>-1E-3</v>
-      </c>
-      <c r="P55">
-        <v>2.9000000000000001E-2</v>
-      </c>
-      <c r="Q55">
-        <v>0.96799999999999997</v>
-      </c>
-      <c r="R55">
-        <v>-5.7000000000000002E-2</v>
-      </c>
-      <c r="S55">
-        <v>5.5E-2</v>
-      </c>
-      <c r="T55" s="56"/>
-      <c r="U55" s="56"/>
-      <c r="V55" s="56"/>
-      <c r="W55" s="56"/>
-      <c r="X55" s="56"/>
-      <c r="Y55" s="56"/>
-      <c r="Z55" s="56"/>
+      <c r="A55" s="52"/>
+      <c r="B55" s="52"/>
+      <c r="C55" s="52"/>
+      <c r="D55" s="52"/>
+      <c r="E55" s="52"/>
+      <c r="F55" s="51"/>
+      <c r="G55" s="52"/>
+      <c r="H55" s="52"/>
+      <c r="I55" s="52"/>
+      <c r="J55" s="52"/>
+      <c r="K55" s="52"/>
+      <c r="L55" s="52"/>
+      <c r="M55" s="52"/>
+      <c r="N55"/>
+      <c r="O55"/>
+      <c r="P55"/>
+      <c r="Q55"/>
+      <c r="R55"/>
+      <c r="S55"/>
+      <c r="T55" s="52"/>
+      <c r="U55" s="52"/>
+      <c r="V55" s="52"/>
+      <c r="W55" s="52"/>
+      <c r="X55" s="52"/>
+      <c r="Y55" s="52"/>
+      <c r="Z55" s="52"/>
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A56" s="56"/>
-      <c r="B56" s="56"/>
-      <c r="C56" s="56"/>
-      <c r="D56" s="56"/>
-      <c r="E56" s="56"/>
-      <c r="F56" s="55"/>
-      <c r="G56" s="56"/>
-      <c r="H56" s="56"/>
-      <c r="I56" s="56"/>
-      <c r="J56" s="56"/>
-      <c r="K56" s="56"/>
-      <c r="L56" s="56"/>
-      <c r="M56" s="56"/>
-      <c r="N56" t="s">
-        <v>190</v>
-      </c>
-      <c r="O56">
-        <v>6.8000000000000005E-2</v>
-      </c>
-      <c r="P56">
-        <v>2.3E-2</v>
-      </c>
-      <c r="Q56">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="R56">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="S56">
-        <v>0.114</v>
-      </c>
-      <c r="T56" s="56"/>
-      <c r="U56" s="56"/>
-      <c r="V56" s="56"/>
-      <c r="W56" s="56"/>
-      <c r="X56" s="56"/>
-      <c r="Y56" s="56"/>
-      <c r="Z56" s="56"/>
+      <c r="A56" s="52"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="52"/>
+      <c r="D56" s="52"/>
+      <c r="E56" s="52"/>
+      <c r="F56" s="51"/>
+      <c r="G56" s="52"/>
+      <c r="H56" s="52"/>
+      <c r="I56" s="52"/>
+      <c r="J56" s="52"/>
+      <c r="K56" s="52"/>
+      <c r="L56" s="52"/>
+      <c r="M56" s="52"/>
+      <c r="N56"/>
+      <c r="O56"/>
+      <c r="P56"/>
+      <c r="Q56"/>
+      <c r="R56"/>
+      <c r="S56"/>
+      <c r="T56" s="52"/>
+      <c r="U56" s="52"/>
+      <c r="V56" s="52"/>
+      <c r="W56" s="52"/>
+      <c r="X56" s="52"/>
+      <c r="Y56" s="52"/>
+      <c r="Z56" s="52"/>
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A57" s="56"/>
-      <c r="B57" s="56"/>
-      <c r="C57" s="56"/>
-      <c r="D57" s="56"/>
-      <c r="E57" s="56"/>
-      <c r="F57" s="55"/>
-      <c r="G57" s="56"/>
-      <c r="H57" s="56"/>
-      <c r="I57" s="56"/>
-      <c r="J57" s="56"/>
-      <c r="K57" s="56"/>
-      <c r="L57" s="56"/>
-      <c r="M57" s="56"/>
-      <c r="N57" t="s">
-        <v>191</v>
-      </c>
-      <c r="O57">
-        <v>-0.11799999999999999</v>
-      </c>
-      <c r="P57">
-        <v>2.1999999999999999E-2</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>24</v>
-      </c>
-      <c r="R57">
-        <v>-0.16200000000000001</v>
-      </c>
-      <c r="S57">
-        <v>-7.3999999999999996E-2</v>
-      </c>
-      <c r="T57" s="56"/>
-      <c r="U57" s="56"/>
-      <c r="V57" s="56"/>
-      <c r="W57" s="56"/>
-      <c r="X57" s="56"/>
-      <c r="Y57" s="56"/>
-      <c r="Z57" s="56"/>
+      <c r="A57" s="52"/>
+      <c r="B57" s="52"/>
+      <c r="C57" s="52"/>
+      <c r="D57" s="52"/>
+      <c r="E57" s="52"/>
+      <c r="F57" s="51"/>
+      <c r="G57" s="52"/>
+      <c r="H57" s="52"/>
+      <c r="I57" s="52"/>
+      <c r="J57" s="52"/>
+      <c r="K57" s="52"/>
+      <c r="L57" s="52"/>
+      <c r="M57" s="52"/>
+      <c r="N57"/>
+      <c r="O57"/>
+      <c r="P57"/>
+      <c r="Q57"/>
+      <c r="R57"/>
+      <c r="S57"/>
+      <c r="T57" s="52"/>
+      <c r="U57" s="52"/>
+      <c r="V57" s="52"/>
+      <c r="W57" s="52"/>
+      <c r="X57" s="52"/>
+      <c r="Y57" s="52"/>
+      <c r="Z57" s="52"/>
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A58" s="56"/>
-      <c r="B58" s="56"/>
-      <c r="C58" s="56"/>
-      <c r="D58" s="56"/>
-      <c r="E58" s="56"/>
-      <c r="F58" s="55"/>
-      <c r="G58" s="56"/>
-      <c r="H58" s="56"/>
-      <c r="I58" s="56"/>
-      <c r="J58" s="56"/>
-      <c r="K58" s="56"/>
-      <c r="L58" s="56"/>
-      <c r="M58" s="56"/>
-      <c r="N58" s="56"/>
-      <c r="O58" s="56"/>
-      <c r="P58" s="56"/>
-      <c r="Q58" s="56"/>
-      <c r="R58" s="56"/>
-      <c r="S58" s="56"/>
-      <c r="T58" s="56"/>
-      <c r="U58" s="56"/>
-      <c r="V58" s="56"/>
-      <c r="W58" s="56"/>
-      <c r="X58" s="56"/>
-      <c r="Y58" s="56"/>
-      <c r="Z58" s="56"/>
+      <c r="A58" s="52"/>
+      <c r="B58" s="52"/>
+      <c r="C58" s="52"/>
+      <c r="D58" s="52"/>
+      <c r="E58" s="52"/>
+      <c r="F58" s="51"/>
+      <c r="G58" s="52"/>
+      <c r="H58" s="52"/>
+      <c r="I58" s="52"/>
+      <c r="J58" s="52"/>
+      <c r="K58" s="52"/>
+      <c r="L58" s="52"/>
+      <c r="M58" s="52"/>
+      <c r="N58"/>
+      <c r="O58"/>
+      <c r="P58"/>
+      <c r="Q58"/>
+      <c r="R58"/>
+      <c r="S58"/>
+      <c r="T58" s="52"/>
+      <c r="U58" s="52"/>
+      <c r="V58" s="52"/>
+      <c r="W58" s="52"/>
+      <c r="X58" s="52"/>
+      <c r="Y58" s="52"/>
+      <c r="Z58" s="52"/>
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A59" s="56"/>
-      <c r="B59" s="56"/>
-      <c r="C59" s="56"/>
-      <c r="D59" s="56"/>
-      <c r="E59" s="56"/>
-      <c r="F59" s="55"/>
-      <c r="G59" s="56"/>
-      <c r="H59" s="56"/>
-      <c r="I59" s="56"/>
-      <c r="J59" s="56"/>
-      <c r="K59" s="56"/>
-      <c r="L59" s="56"/>
-      <c r="M59" s="56"/>
-      <c r="N59" s="56"/>
-      <c r="O59" s="56"/>
-      <c r="P59" s="56"/>
-      <c r="Q59" s="56"/>
-      <c r="R59" s="56"/>
-      <c r="S59" s="56"/>
-      <c r="T59" s="56"/>
-      <c r="U59" s="56"/>
-      <c r="V59" s="56"/>
-      <c r="W59" s="56"/>
-      <c r="X59" s="56"/>
-      <c r="Y59" s="56"/>
-      <c r="Z59" s="56"/>
+      <c r="A59" s="52"/>
+      <c r="B59" s="52"/>
+      <c r="C59" s="52"/>
+      <c r="D59" s="52"/>
+      <c r="E59" s="52"/>
+      <c r="F59" s="51"/>
+      <c r="G59" s="52"/>
+      <c r="H59" s="52"/>
+      <c r="I59" s="52"/>
+      <c r="J59" s="52"/>
+      <c r="K59" s="52"/>
+      <c r="L59" s="52"/>
+      <c r="M59" s="52"/>
+      <c r="N59"/>
+      <c r="O59"/>
+      <c r="P59"/>
+      <c r="Q59"/>
+      <c r="R59"/>
+      <c r="S59"/>
+      <c r="T59" s="52"/>
+      <c r="U59" s="52"/>
+      <c r="V59" s="52"/>
+      <c r="W59" s="52"/>
+      <c r="X59" s="52"/>
+      <c r="Y59" s="52"/>
+      <c r="Z59" s="52"/>
+    </row>
+    <row r="60" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A60" s="52"/>
+      <c r="B60" s="52"/>
+      <c r="C60" s="52"/>
+      <c r="D60" s="52"/>
+      <c r="E60" s="52"/>
+      <c r="F60" s="51"/>
+      <c r="G60" s="52"/>
+      <c r="H60" s="52"/>
+      <c r="I60" s="52"/>
+      <c r="J60" s="52"/>
+      <c r="K60" s="52"/>
+      <c r="L60" s="52"/>
+      <c r="M60" s="52"/>
+      <c r="N60" s="52"/>
+      <c r="O60" s="52"/>
+      <c r="P60" s="52"/>
+      <c r="Q60" s="52"/>
+      <c r="R60" s="52"/>
+      <c r="S60" s="52"/>
+      <c r="T60" s="52"/>
+      <c r="U60" s="52"/>
+      <c r="V60" s="52"/>
+      <c r="W60" s="52"/>
+      <c r="X60" s="52"/>
+      <c r="Y60" s="52"/>
+      <c r="Z60" s="52"/>
+    </row>
+    <row r="61" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A61" s="52"/>
+      <c r="B61" s="52"/>
+      <c r="C61" s="52"/>
+      <c r="D61" s="52"/>
+      <c r="E61" s="52"/>
+      <c r="F61" s="51"/>
+      <c r="G61" s="52"/>
+      <c r="H61" s="52"/>
+      <c r="I61" s="52"/>
+      <c r="J61" s="52"/>
+      <c r="K61" s="52"/>
+      <c r="L61" s="52"/>
+      <c r="M61" s="52"/>
+      <c r="N61" s="52"/>
+      <c r="O61" s="52"/>
+      <c r="P61" s="52"/>
+      <c r="Q61" s="52"/>
+      <c r="R61" s="52"/>
+      <c r="S61" s="52"/>
+      <c r="T61" s="52"/>
+      <c r="U61" s="52"/>
+      <c r="V61" s="52"/>
+      <c r="W61" s="52"/>
+      <c r="X61" s="52"/>
+      <c r="Y61" s="52"/>
+      <c r="Z61" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="O29:S29"/>
-    <mergeCell ref="O2:Z2"/>
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="V3:Z3"/>
-    <mergeCell ref="V23:Z23"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="H23:L23"/>
-    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="O31:S31"/>
+    <mergeCell ref="O4:Z4"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="V5:Z5"/>
+    <mergeCell ref="V25:Z25"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="H25:L25"/>
+    <mergeCell ref="B4:L4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmoffice-my.sharepoint.com/personal/abrieant_uvm_edu/Documents/OneDrive/Manuscripts/reg report DCN/pubertybrain/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="460" documentId="13_ncr:1_{2DBDCA32-700C-9942-8973-B738A2BA3D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C60FEBB-D1DE-6E46-974E-69E73352881B}"/>
+  <xr:revisionPtr revIDLastSave="463" documentId="13_ncr:1_{2DBDCA32-700C-9942-8973-B738A2BA3D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3006A2E2-BCBE-BA42-AFF3-BF55CEAF5BF6}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="8" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="5" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptive table" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="152">
   <si>
     <t>16.10 (2.98)</t>
   </si>
@@ -536,81 +536,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">   ELA    on Intercept</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>b</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">   ELA    on Slope</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>b</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">   WM    on Intercept</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>b</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">   WM    on Slope</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="subscript"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>b</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">   ELA    on Timing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   ELA    on Tempo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   WM    on Tempo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   WM    on Timing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   WM    on ELA</t>
-  </si>
-  <si>
     <t xml:space="preserve">   WM</t>
   </si>
   <si>
@@ -812,12 +737,6 @@
   </si>
   <si>
     <t>Model 3 - Girls</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   ELA    on Quadratic Slope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   WM on Quadratic Slope</t>
   </si>
   <si>
     <r>
@@ -2518,7 +2437,7 @@
   <sheetData>
     <row r="2" spans="13:13" x14ac:dyDescent="0.2">
       <c r="M2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -2591,13 +2510,13 @@
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
       <c r="B2" s="38" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C2" s="38"/>
       <c r="D2" s="38"/>
@@ -2617,7 +2536,7 @@
       <c r="R2" s="38"/>
       <c r="S2" s="9"/>
       <c r="T2" s="38" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="U2" s="38"/>
       <c r="V2" s="38"/>
@@ -2688,7 +2607,7 @@
     <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
       <c r="B4" s="27" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>89</v>
@@ -2697,14 +2616,14 @@
         <v>90</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="G4" s="27"/>
       <c r="H4" s="27" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="I4" s="27" t="s">
         <v>89</v>
@@ -2713,14 +2632,14 @@
         <v>90</v>
       </c>
       <c r="K4" s="27" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="L4" s="27" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="M4" s="27"/>
       <c r="N4" s="27" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="O4" s="27" t="s">
         <v>89</v>
@@ -2729,14 +2648,14 @@
         <v>90</v>
       </c>
       <c r="Q4" s="27" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="R4" s="27" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="S4" s="6"/>
       <c r="T4" s="27" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="U4" s="27" t="s">
         <v>89</v>
@@ -2745,14 +2664,14 @@
         <v>90</v>
       </c>
       <c r="W4" s="27" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="X4" s="27" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="Y4" s="17"/>
       <c r="Z4" s="27" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="AA4" s="27" t="s">
         <v>89</v>
@@ -2761,14 +2680,14 @@
         <v>90</v>
       </c>
       <c r="AC4" s="27" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="AD4" s="27" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="AE4" s="17"/>
       <c r="AF4" s="27" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="AG4" s="27" t="s">
         <v>89</v>
@@ -2777,10 +2696,10 @@
         <v>90</v>
       </c>
       <c r="AI4" s="27" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="AJ4" s="27" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.2">
@@ -3768,7 +3687,7 @@
     </row>
     <row r="18" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>92</v>
@@ -3867,7 +3786,7 @@
     </row>
     <row r="19" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>92</v>
@@ -3966,7 +3885,7 @@
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="B20" s="16" t="s">
         <v>92</v>
@@ -4065,7 +3984,7 @@
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="B21" s="16" t="s">
         <v>92</v>
@@ -4164,7 +4083,7 @@
     </row>
     <row r="22" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>92</v>
@@ -4261,7 +4180,7 @@
     </row>
     <row r="23" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="B23" s="16" t="s">
         <v>92</v>
@@ -4358,7 +4277,7 @@
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B24" s="16" t="s">
         <v>92</v>
@@ -4455,7 +4374,7 @@
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A25" s="16" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="B25" s="16" t="s">
         <v>92</v>
@@ -4552,7 +4471,7 @@
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>92</v>
@@ -5022,7 +4941,7 @@
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A32" s="16" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B32" s="16" t="s">
         <v>92</v>
@@ -5119,7 +5038,7 @@
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A33" s="20" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
@@ -5162,7 +5081,7 @@
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B34" s="40">
         <v>74058.118000000002</v>
@@ -5279,13 +5198,13 @@
   <sheetData>
     <row r="1" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
       <c r="B2" s="38" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C2" s="38"/>
       <c r="D2" s="38"/>
@@ -5305,7 +5224,7 @@
       <c r="R2" s="38"/>
       <c r="S2" s="9"/>
       <c r="T2" s="38" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="U2" s="38"/>
       <c r="V2" s="38"/>
@@ -5376,7 +5295,7 @@
     <row r="4" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A4" s="15"/>
       <c r="B4" s="27" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>89</v>
@@ -5385,14 +5304,14 @@
         <v>90</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="G4" s="27"/>
       <c r="H4" s="27" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="I4" s="27" t="s">
         <v>89</v>
@@ -5401,14 +5320,14 @@
         <v>90</v>
       </c>
       <c r="K4" s="27" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="L4" s="27" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="M4" s="27"/>
       <c r="N4" s="27" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="O4" s="27" t="s">
         <v>89</v>
@@ -5417,14 +5336,14 @@
         <v>90</v>
       </c>
       <c r="Q4" s="27" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="R4" s="27" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="S4" s="6"/>
       <c r="T4" s="27" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="U4" s="27" t="s">
         <v>89</v>
@@ -5433,14 +5352,14 @@
         <v>90</v>
       </c>
       <c r="W4" s="27" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="X4" s="27" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="Y4" s="17"/>
       <c r="Z4" s="27" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="AA4" s="27" t="s">
         <v>89</v>
@@ -5449,14 +5368,14 @@
         <v>90</v>
       </c>
       <c r="AC4" s="27" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="AD4" s="27" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="AE4" s="17"/>
       <c r="AF4" s="27" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="AG4" s="27" t="s">
         <v>89</v>
@@ -5465,10 +5384,10 @@
         <v>90</v>
       </c>
       <c r="AI4" s="27" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="AJ4" s="27" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.2">
@@ -5710,7 +5629,7 @@
     </row>
     <row r="8" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="B8" s="16">
         <v>-0.253</v>
@@ -5984,7 +5903,7 @@
     </row>
     <row r="12" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="B12" s="16">
         <v>0.11700000000000001</v>
@@ -6281,7 +6200,7 @@
     </row>
     <row r="15" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="B15" s="16" t="s">
         <v>92</v>
@@ -6479,7 +6398,7 @@
     </row>
     <row r="17" spans="1:36" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B17" s="16">
         <v>-0.45300000000000001</v>
@@ -6752,7 +6671,7 @@
       <c r="AJ20" s="16"/>
     </row>
     <row r="21" spans="1:36" ht="17" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="34" t="s">
         <v>99</v>
       </c>
       <c r="B21" s="16" t="s">
@@ -6851,8 +6770,8 @@
       </c>
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A22" s="16" t="s">
-        <v>134</v>
+      <c r="A22" s="34" t="s">
+        <v>125</v>
       </c>
       <c r="B22" s="16">
         <v>-0.29099999999999998</v>
@@ -6950,8 +6869,8 @@
       </c>
     </row>
     <row r="23" spans="1:36" ht="17" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
-        <v>100</v>
+      <c r="A23" s="34" t="s">
+        <v>134</v>
       </c>
       <c r="B23" s="16" t="s">
         <v>92</v>
@@ -7049,8 +6968,8 @@
       </c>
     </row>
     <row r="24" spans="1:36" ht="17" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
-        <v>101</v>
+      <c r="A24" s="34" t="s">
+        <v>135</v>
       </c>
       <c r="B24" s="16" t="s">
         <v>92</v>
@@ -7148,8 +7067,8 @@
       </c>
     </row>
     <row r="25" spans="1:36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="16" t="s">
-        <v>141</v>
+      <c r="A25" s="34" t="s">
+        <v>150</v>
       </c>
       <c r="H25" s="16">
         <v>-8.8999999999999996E-2</v>
@@ -7228,8 +7147,8 @@
       </c>
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A26" s="16" t="s">
-        <v>104</v>
+      <c r="A26" s="34" t="s">
+        <v>136</v>
       </c>
       <c r="B26" s="16" t="s">
         <v>92</v>
@@ -7327,8 +7246,8 @@
       </c>
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A27" s="16" t="s">
-        <v>105</v>
+      <c r="A27" s="34" t="s">
+        <v>137</v>
       </c>
       <c r="B27" s="16" t="s">
         <v>92</v>
@@ -7426,8 +7345,8 @@
       </c>
     </row>
     <row r="28" spans="1:36" ht="17" x14ac:dyDescent="0.25">
-      <c r="A28" s="16" t="s">
-        <v>102</v>
+      <c r="A28" s="34" t="s">
+        <v>138</v>
       </c>
       <c r="B28" s="16" t="s">
         <v>92</v>
@@ -7523,8 +7442,8 @@
       </c>
     </row>
     <row r="29" spans="1:36" ht="17" x14ac:dyDescent="0.25">
-      <c r="A29" s="16" t="s">
-        <v>103</v>
+      <c r="A29" s="34" t="s">
+        <v>139</v>
       </c>
       <c r="B29" s="16" t="s">
         <v>92</v>
@@ -7620,8 +7539,8 @@
       </c>
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A30" s="16" t="s">
-        <v>142</v>
+      <c r="A30" s="34" t="s">
+        <v>151</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -7699,8 +7618,8 @@
       </c>
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A31" s="16" t="s">
-        <v>107</v>
+      <c r="A31" s="34" t="s">
+        <v>141</v>
       </c>
       <c r="B31" s="16" t="s">
         <v>92</v>
@@ -7796,8 +7715,8 @@
       </c>
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.2">
-      <c r="A32" s="16" t="s">
-        <v>106</v>
+      <c r="A32" s="34" t="s">
+        <v>142</v>
       </c>
       <c r="B32" s="16" t="s">
         <v>92</v>
@@ -7893,8 +7812,8 @@
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A33" s="16" t="s">
-        <v>108</v>
+      <c r="A33" s="36" t="s">
+        <v>140</v>
       </c>
       <c r="B33" s="16" t="s">
         <v>92</v>
@@ -8364,7 +8283,7 @@
     </row>
     <row r="39" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A39" s="16" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="B39" s="16" t="s">
         <v>92</v>
@@ -8461,7 +8380,7 @@
     </row>
     <row r="40" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A40" s="20" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B40" s="14"/>
       <c r="C40" s="14"/>
@@ -8504,7 +8423,7 @@
     </row>
     <row r="41" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A41" s="15" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B41" s="40">
         <v>34697.703999999998</v>
@@ -8591,7 +8510,7 @@
   <sheetData>
     <row r="1" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="23" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
@@ -8599,12 +8518,12 @@
     </row>
     <row r="3" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="24" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="24" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
@@ -8616,30 +8535,30 @@
     <row r="7" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="23" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="24" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="24" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B11" s="23" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="B12">
         <v>-3.4000000000000002E-2</v>
@@ -8650,7 +8569,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="B13">
         <v>-2.4E-2</v>
@@ -8661,7 +8580,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B14">
         <v>-2.3E-2</v>
@@ -8672,7 +8591,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B15">
         <v>-2.5999999999999999E-2</v>
@@ -8683,25 +8602,25 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="23" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="24" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B19" s="23" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="B20">
         <v>-3.1E-2</v>
@@ -8712,7 +8631,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="B21">
         <v>-0.03</v>
@@ -8723,7 +8642,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="46" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="B22" s="46">
         <v>-0.113</v>
@@ -8734,7 +8653,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="B23">
         <v>-3.3000000000000002E-2</v>
@@ -8745,7 +8664,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E25" s="23" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -8798,7 +8717,7 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="L1" s="52"/>
       <c r="M1" s="52"/>
@@ -8863,7 +8782,7 @@
     <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4" s="51"/>
       <c r="B4" s="70" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="C4" s="70"/>
       <c r="D4" s="70"/>
@@ -8877,7 +8796,7 @@
       <c r="L4" s="70"/>
       <c r="N4" s="34"/>
       <c r="O4" s="70" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="P4" s="70"/>
       <c r="Q4" s="70"/>
@@ -8894,14 +8813,14 @@
     <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="15"/>
       <c r="B5" s="41" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C5" s="42"/>
       <c r="D5" s="42"/>
       <c r="E5" s="42"/>
       <c r="F5" s="43"/>
       <c r="H5" s="41" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="I5" s="42"/>
       <c r="J5" s="42"/>
@@ -8909,7 +8828,7 @@
       <c r="L5" s="43"/>
       <c r="N5" s="36"/>
       <c r="O5" s="41" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="P5" s="42"/>
       <c r="Q5" s="42"/>
@@ -8918,7 +8837,7 @@
       <c r="T5" s="59"/>
       <c r="U5" s="60"/>
       <c r="V5" s="41" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="W5" s="42"/>
       <c r="X5" s="42"/>
@@ -8928,7 +8847,7 @@
     <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A6" s="16"/>
       <c r="B6" s="29" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="C6" s="29" t="s">
         <v>89</v>
@@ -8937,13 +8856,13 @@
         <v>90</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="I6" s="29" t="s">
         <v>89</v>
@@ -8952,14 +8871,14 @@
         <v>90</v>
       </c>
       <c r="K6" s="29" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="N6" s="35"/>
       <c r="O6" s="29" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="P6" s="29" t="s">
         <v>89</v>
@@ -8968,15 +8887,15 @@
         <v>90</v>
       </c>
       <c r="R6" s="29" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="S6" s="61" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="T6" s="63"/>
       <c r="U6" s="32"/>
       <c r="V6" s="29" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="W6" s="29" t="s">
         <v>89</v>
@@ -8985,10 +8904,10 @@
         <v>90</v>
       </c>
       <c r="Y6" s="29" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="Z6" s="29" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.2">
@@ -9093,7 +9012,7 @@
         <v>0.05</v>
       </c>
       <c r="X8" s="66" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="Y8" s="16">
         <v>0.224</v>
@@ -9144,7 +9063,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="N9" s="34" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="O9" s="34">
         <v>0.11600000000000001</v>
@@ -9251,7 +9170,7 @@
         <v>2.1000000000000001E-2</v>
       </c>
       <c r="X10" s="66" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="Y10" s="16">
         <v>3.4000000000000002E-2</v>
@@ -9268,7 +9187,7 @@
     </row>
     <row r="11" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="B11" s="54">
         <v>-3.2000000000000001E-2</v>
@@ -9321,7 +9240,7 @@
       </c>
       <c r="T11" s="51"/>
       <c r="U11" s="34" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="V11" s="34">
         <v>0.115</v>
@@ -9347,7 +9266,7 @@
     </row>
     <row r="12" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="B12" s="34">
         <v>0.24099999999999999</v>
@@ -9381,7 +9300,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
       <c r="N12" s="34" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="O12" s="68" t="s">
         <v>92</v>
@@ -9400,7 +9319,7 @@
       </c>
       <c r="T12" s="51"/>
       <c r="U12" s="34" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="V12" s="34">
         <v>0.04</v>
@@ -9439,7 +9358,7 @@
       <c r="K13" s="16"/>
       <c r="L13" s="37"/>
       <c r="N13" s="34" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="O13" s="68" t="s">
         <v>92</v>
@@ -9508,7 +9427,7 @@
         <v>0.47499999999999998</v>
       </c>
       <c r="N14" s="34" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="O14" s="34">
         <v>7.9000000000000001E-2</v>
@@ -9553,7 +9472,7 @@
     </row>
     <row r="15" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="B15" s="34">
         <v>-0.14499999999999999</v>
@@ -9587,7 +9506,7 @@
         <v>-9.5000000000000001E-2</v>
       </c>
       <c r="N15" s="34" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="O15" s="34">
         <v>0.24099999999999999</v>
@@ -9606,7 +9525,7 @@
       </c>
       <c r="T15" s="51"/>
       <c r="U15" s="34" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="V15" s="34">
         <v>-0.13100000000000001</v>
@@ -9615,7 +9534,7 @@
         <v>2.1999999999999999E-2</v>
       </c>
       <c r="X15" s="66" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="Y15" s="16">
         <v>-0.17299999999999999</v>
@@ -9632,7 +9551,7 @@
     </row>
     <row r="16" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="B16" s="34">
         <v>-2.1999999999999999E-2</v>
@@ -9675,7 +9594,7 @@
       <c r="S16" s="37"/>
       <c r="T16" s="51"/>
       <c r="U16" s="34" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="V16" s="34">
         <v>-6.0000000000000001E-3</v>
@@ -9701,7 +9620,7 @@
     </row>
     <row r="17" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="B17" s="34">
         <v>-0.14399999999999999</v>
@@ -9755,7 +9674,7 @@
       </c>
       <c r="T17" s="51"/>
       <c r="U17" s="34" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="V17" s="34">
         <v>-3.5999999999999997E-2</v>
@@ -9781,7 +9700,7 @@
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="B18" s="34">
         <v>-0.16600000000000001</v>
@@ -9816,7 +9735,7 @@
       </c>
       <c r="M18"/>
       <c r="N18" s="34" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="O18" s="34">
         <v>0.39500000000000002</v>
@@ -9835,7 +9754,7 @@
       </c>
       <c r="T18" s="51"/>
       <c r="U18" s="34" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="V18" s="34">
         <v>-0.159</v>
@@ -9844,7 +9763,7 @@
         <v>0.02</v>
       </c>
       <c r="X18" s="66" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="Y18" s="16">
         <v>-0.19800000000000001</v>
@@ -9861,7 +9780,7 @@
     </row>
     <row r="19" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="B19" s="34">
         <v>0.17899999999999999</v>
@@ -9896,7 +9815,7 @@
       </c>
       <c r="M19"/>
       <c r="N19" s="34" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="O19" s="34">
         <v>-0.112</v>
@@ -9915,7 +9834,7 @@
       </c>
       <c r="T19" s="51"/>
       <c r="U19" s="34" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="V19" s="34">
         <v>0.123</v>
@@ -9924,7 +9843,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
       <c r="X19" s="66" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="Y19" s="16">
         <v>7.1999999999999995E-2</v>
@@ -9941,7 +9860,7 @@
     </row>
     <row r="20" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="B20" s="34">
         <v>1E-3</v>
@@ -9976,7 +9895,7 @@
       </c>
       <c r="M20"/>
       <c r="N20" s="34" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="O20" s="68" t="s">
         <v>92</v>
@@ -9995,7 +9914,7 @@
       </c>
       <c r="T20" s="51"/>
       <c r="U20" s="34" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="V20" s="34">
         <v>-2.7E-2</v>
@@ -10021,7 +9940,7 @@
     </row>
     <row r="21" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B21" s="34">
         <v>1.6E-2</v>
@@ -10056,7 +9975,7 @@
       </c>
       <c r="M21"/>
       <c r="N21" s="34" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="O21" s="34">
         <v>-0.13100000000000001</v>
@@ -10075,7 +9994,7 @@
       </c>
       <c r="T21" s="51"/>
       <c r="U21" s="34" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="V21" s="34">
         <v>2.5999999999999999E-2</v>
@@ -10101,7 +10020,7 @@
     </row>
     <row r="22" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="B22" s="34">
         <v>6.5000000000000002E-2</v>
@@ -10135,7 +10054,7 @@
         <v>0.186</v>
       </c>
       <c r="N22" s="34" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="O22" s="34">
         <v>-0.14399999999999999</v>
@@ -10154,7 +10073,7 @@
       </c>
       <c r="T22" s="51"/>
       <c r="U22" s="34" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="V22" s="34">
         <v>0.156</v>
@@ -10163,7 +10082,7 @@
         <v>0.02</v>
       </c>
       <c r="X22" s="66" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="Y22" s="16">
         <v>0.11600000000000001</v>
@@ -10180,7 +10099,7 @@
     </row>
     <row r="23" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A23" s="16" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B23" s="34">
         <v>-0.12</v>
@@ -10214,7 +10133,7 @@
         <v>-3.9E-2</v>
       </c>
       <c r="N23" s="34" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="O23" s="34">
         <v>-0.16600000000000001</v>
@@ -10233,7 +10152,7 @@
       </c>
       <c r="T23" s="51"/>
       <c r="U23" s="34" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="V23" s="34">
         <v>-8.2000000000000003E-2</v>
@@ -10242,7 +10161,7 @@
         <v>0.02</v>
       </c>
       <c r="X23" s="66" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="Y23" s="16">
         <v>-0.122</v>
@@ -10259,7 +10178,7 @@
     </row>
     <row r="24" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B24" s="35"/>
       <c r="C24" s="14"/>
@@ -10273,7 +10192,7 @@
       <c r="K24" s="14"/>
       <c r="L24" s="31"/>
       <c r="N24" s="34" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="O24" s="34">
         <v>0.13900000000000001</v>
@@ -10292,7 +10211,7 @@
       </c>
       <c r="T24" s="51"/>
       <c r="U24" s="65" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="V24" s="35"/>
       <c r="W24" s="14"/>
@@ -10308,7 +10227,7 @@
     </row>
     <row r="25" spans="1:32" ht="17" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="B25" s="44">
         <v>93579.540999999997</v>
@@ -10327,7 +10246,7 @@
       <c r="L25" s="45"/>
       <c r="M25" s="6"/>
       <c r="N25" s="34" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="O25" s="68" t="s">
         <v>92</v>
@@ -10346,7 +10265,7 @@
       </c>
       <c r="T25" s="58"/>
       <c r="U25" s="57" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="V25" s="44">
         <v>59389.061000000002</v>
@@ -10377,7 +10296,7 @@
       <c r="L26" s="52"/>
       <c r="M26" s="52"/>
       <c r="N26" s="34" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="O26" s="34">
         <v>7.0999999999999994E-2</v>
@@ -10417,7 +10336,7 @@
       <c r="L27" s="52"/>
       <c r="M27" s="52"/>
       <c r="N27" s="34" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="O27" s="34">
         <v>-1E-3</v>
@@ -10457,7 +10376,7 @@
       <c r="L28" s="52"/>
       <c r="M28" s="52"/>
       <c r="N28" s="34" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="O28" s="34">
         <v>6.8000000000000005E-2</v>
@@ -10497,7 +10416,7 @@
       <c r="L29" s="52"/>
       <c r="M29" s="52"/>
       <c r="N29" s="36" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="O29" s="36">
         <v>-0.11799999999999999</v>
@@ -10537,7 +10456,7 @@
       <c r="L30" s="52"/>
       <c r="M30" s="52"/>
       <c r="N30" s="65" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="O30" s="35"/>
       <c r="P30" s="14"/>
@@ -10567,7 +10486,7 @@
       <c r="L31" s="52"/>
       <c r="M31" s="52"/>
       <c r="N31" s="57" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="O31" s="44">
         <v>54236.89</v>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmoffice-my.sharepoint.com/personal/abrieant_uvm_edu/Documents/OneDrive/Manuscripts/reg report DCN/pubertybrain/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="463" documentId="13_ncr:1_{2DBDCA32-700C-9942-8973-B738A2BA3D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3006A2E2-BCBE-BA42-AFF3-BF55CEAF5BF6}"/>
+  <xr:revisionPtr revIDLastSave="474" documentId="13_ncr:1_{2DBDCA32-700C-9942-8973-B738A2BA3D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3271789-288D-674D-ACDF-1738A1CB7C8D}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="5" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="9" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptive table" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="Indirect effects" sheetId="7" state="hidden" r:id="rId7"/>
     <sheet name="Sex Differences" sheetId="11" r:id="rId8"/>
     <sheet name="Youth report PDS" sheetId="9" r:id="rId9"/>
+    <sheet name="GMV model fits" sheetId="12" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="153">
   <si>
     <t>16.10 (2.98)</t>
   </si>
@@ -936,6 +937,9 @@
   </si>
   <si>
     <t xml:space="preserve">   Quadratic Slope on WM</t>
+  </si>
+  <si>
+    <t>In progress</t>
   </si>
 </sst>
 </file>
@@ -1242,7 +1246,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1356,6 +1360,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1607,6 +1612,99 @@
         <a:xfrm>
           <a:off x="38100" y="85724"/>
           <a:ext cx="6527800" cy="5616575"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>57292</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F72092C-FF29-F788-5A1D-5FDD2A02F217}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7772400" cy="4527692"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>184292</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6A73A67-A359-FF60-ECB0-C2A53BB4D3D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="4800600"/>
+          <a:ext cx="7772400" cy="4527692"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2430,13 +2528,26 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82037491-20BB-9544-BB4E-D07D863BBAA7}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A749072B-F938-0F49-BE23-243603B2B3D0}">
   <dimension ref="M2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="13" max="13" width="23.5" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="13:13" x14ac:dyDescent="0.2">
-      <c r="M2" t="s">
+      <c r="M2" s="71" t="s">
         <v>101</v>
       </c>
     </row>
@@ -8676,7 +8787,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A439B20-C024-854E-8504-DA6820AADA52}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Tables.xlsx
+++ b/Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uvmoffice-my.sharepoint.com/personal/abrieant_uvm_edu/Documents/OneDrive/Manuscripts/reg report DCN/pubertybrain/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nchaku\Documents\GitHub\pubertybrain\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="474" documentId="13_ncr:1_{2DBDCA32-700C-9942-8973-B738A2BA3D07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3271789-288D-674D-ACDF-1738A1CB7C8D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B8BA9C8-0A57-410A-899C-E6EE4A34A372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="9" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="7" xr2:uid="{E0F15479-AA73-0644-8B08-3949D67CD8FE}"/>
   </bookViews>
   <sheets>
     <sheet name="Descriptive table" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="159">
   <si>
     <t>16.10 (2.98)</t>
   </si>
@@ -939,13 +939,52 @@
     <t xml:space="preserve">   Quadratic Slope on WM</t>
   </si>
   <si>
-    <t>In progress</t>
+    <t>Females</t>
+  </si>
+  <si>
+    <t>Males</t>
+  </si>
+  <si>
+    <t>Cortical models</t>
+  </si>
+  <si>
+    <t>Subcortical models</t>
+  </si>
+  <si>
+    <t>z-test</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> value</t>
+    </r>
+  </si>
+  <si>
+    <t>z test</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="167" formatCode="0.000"/>
+  </numFmts>
   <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1246,7 +1285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1299,30 +1338,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
@@ -1330,22 +1345,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1357,10 +1360,53 @@
     </xf>
     <xf numFmtId="11" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2034,20 +2080,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39987BE7-3659-524A-81AE-D479F97EF698}">
   <dimension ref="A1:F29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="9"/>
       <c r="B2" s="10" t="s">
         <v>63</v>
@@ -2065,7 +2111,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="11" t="s">
         <v>69</v>
@@ -2079,7 +2125,7 @@
       <c r="E3" s="11"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>60</v>
       </c>
@@ -2089,7 +2135,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>61</v>
       </c>
@@ -2109,7 +2155,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>62</v>
       </c>
@@ -2129,7 +2175,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>58</v>
       </c>
@@ -2149,7 +2195,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>59</v>
       </c>
@@ -2159,7 +2205,7 @@
       <c r="E8" s="12"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>61</v>
       </c>
@@ -2179,7 +2225,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>66</v>
       </c>
@@ -2199,7 +2245,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>67</v>
       </c>
@@ -2219,7 +2265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>62</v>
       </c>
@@ -2239,7 +2285,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>68</v>
       </c>
@@ -2249,7 +2295,7 @@
       <c r="E13" s="12"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>73</v>
       </c>
@@ -2269,7 +2315,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>74</v>
       </c>
@@ -2289,7 +2335,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>75</v>
       </c>
@@ -2309,7 +2355,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>76</v>
       </c>
@@ -2327,7 +2373,7 @@
       </c>
       <c r="F17" s="19"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>71</v>
       </c>
@@ -2337,7 +2383,7 @@
       <c r="E18" s="12"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>61</v>
       </c>
@@ -2357,7 +2403,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>66</v>
       </c>
@@ -2377,7 +2423,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>67</v>
       </c>
@@ -2397,7 +2443,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>62</v>
       </c>
@@ -2417,7 +2463,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>72</v>
       </c>
@@ -2427,7 +2473,7 @@
       <c r="E23" s="12"/>
       <c r="F23" s="1"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>61</v>
       </c>
@@ -2447,7 +2493,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>66</v>
       </c>
@@ -2467,7 +2513,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>67</v>
       </c>
@@ -2487,7 +2533,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>62</v>
       </c>
@@ -2507,7 +2553,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2515,7 +2561,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A29" s="4"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2531,7 +2577,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82037491-20BB-9544-BB4E-D07D863BBAA7}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2541,13 +2587,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A749072B-F938-0F49-BE23-243603B2B3D0}">
   <dimension ref="M2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="13" max="13" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="13:13" x14ac:dyDescent="0.2">
-      <c r="M2" s="71" t="s">
+    <row r="2" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M2" s="54" t="s">
         <v>101</v>
       </c>
     </row>
@@ -2560,7 +2606,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45875D41-9C56-AA4E-A18A-2D3A4CE169B3}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2570,7 +2616,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2A5153E-6E5C-054A-8ACA-5118463B96C5}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -2580,142 +2626,142 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA86F85-A8D4-F648-84C3-730F1A42C846}">
   <dimension ref="A1:AM34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.1640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="1.125" style="1" customWidth="1"/>
     <col min="8" max="8" width="8" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.625" style="1" customWidth="1"/>
     <col min="11" max="11" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="1.1640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="1.125" style="1" customWidth="1"/>
     <col min="14" max="14" width="8.5" style="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.6640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.625" style="1" customWidth="1"/>
     <col min="17" max="17" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="0.83203125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="0.875" style="1" customWidth="1"/>
     <col min="20" max="20" width="8.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="5.6640625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="5.625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="6.125" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="1" style="1" customWidth="1"/>
-    <col min="26" max="26" width="8.1640625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.6640625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="8.125" style="1" customWidth="1"/>
+    <col min="27" max="27" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.625" style="1" customWidth="1"/>
     <col min="29" max="30" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="1.1640625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="9.33203125" style="1" customWidth="1"/>
-    <col min="33" max="33" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="5.6640625" style="1" customWidth="1"/>
-    <col min="36" max="36" width="6.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="1.125" style="1" customWidth="1"/>
+    <col min="32" max="32" width="9.375" style="1" customWidth="1"/>
+    <col min="33" max="33" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="5.625" style="1" customWidth="1"/>
+    <col min="36" max="36" width="6.125" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="56"/>
       <c r="S2" s="9"/>
-      <c r="T2" s="38" t="s">
+      <c r="T2" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="U2" s="38"/>
-      <c r="V2" s="38"/>
-      <c r="W2" s="38"/>
-      <c r="X2" s="38"/>
-      <c r="Y2" s="38"/>
-      <c r="Z2" s="38"/>
-      <c r="AA2" s="38"/>
-      <c r="AB2" s="38"/>
-      <c r="AC2" s="38"/>
-      <c r="AD2" s="38"/>
-      <c r="AE2" s="38"/>
-      <c r="AF2" s="38"/>
-      <c r="AG2" s="38"/>
-      <c r="AH2" s="38"/>
-      <c r="AI2" s="38"/>
-      <c r="AJ2" s="38"/>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="U2" s="56"/>
+      <c r="V2" s="56"/>
+      <c r="W2" s="56"/>
+      <c r="X2" s="56"/>
+      <c r="Y2" s="56"/>
+      <c r="Z2" s="56"/>
+      <c r="AA2" s="56"/>
+      <c r="AB2" s="56"/>
+      <c r="AC2" s="56"/>
+      <c r="AD2" s="56"/>
+      <c r="AE2" s="56"/>
+      <c r="AF2" s="56"/>
+      <c r="AG2" s="56"/>
+      <c r="AH2" s="56"/>
+      <c r="AI2" s="56"/>
+      <c r="AJ2" s="56"/>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="16"/>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
       <c r="G3" s="26"/>
-      <c r="H3" s="38" t="s">
+      <c r="H3" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
       <c r="M3" s="26"/>
-      <c r="N3" s="38" t="s">
+      <c r="N3" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
-      <c r="T3" s="39" t="s">
+      <c r="O3" s="56"/>
+      <c r="P3" s="56"/>
+      <c r="Q3" s="56"/>
+      <c r="R3" s="56"/>
+      <c r="T3" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="39"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="57"/>
+      <c r="W3" s="57"/>
+      <c r="X3" s="57"/>
       <c r="Y3" s="26"/>
-      <c r="Z3" s="38" t="s">
+      <c r="Z3" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="AA3" s="38"/>
-      <c r="AB3" s="38"/>
-      <c r="AC3" s="38"/>
-      <c r="AD3" s="38"/>
+      <c r="AA3" s="56"/>
+      <c r="AB3" s="56"/>
+      <c r="AC3" s="56"/>
+      <c r="AD3" s="56"/>
       <c r="AE3" s="26"/>
-      <c r="AF3" s="38" t="s">
+      <c r="AF3" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="AG3" s="38"/>
-      <c r="AH3" s="38"/>
-      <c r="AI3" s="38"/>
-      <c r="AJ3" s="38"/>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AG3" s="56"/>
+      <c r="AH3" s="56"/>
+      <c r="AI3" s="56"/>
+      <c r="AJ3" s="56"/>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="15"/>
       <c r="B4" s="27" t="s">
         <v>143</v>
@@ -2813,7 +2859,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>84</v>
       </c>
@@ -2852,7 +2898,7 @@
       <c r="AI5" s="16"/>
       <c r="AJ5" s="16"/>
     </row>
-    <row r="6" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>93</v>
       </c>
@@ -2951,7 +2997,7 @@
         <v>12.236000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>94</v>
       </c>
@@ -3050,7 +3096,7 @@
         <v>-7.7560000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="16"/>
       <c r="C8" s="16"/>
@@ -3087,7 +3133,7 @@
       <c r="AI8" s="18"/>
       <c r="AJ8" s="16"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>85</v>
       </c>
@@ -3126,7 +3172,7 @@
       <c r="AI9" s="16"/>
       <c r="AJ9" s="16"/>
     </row>
-    <row r="10" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>95</v>
       </c>
@@ -3225,7 +3271,7 @@
         <v>-0.24</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>96</v>
       </c>
@@ -3324,7 +3370,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>97</v>
       </c>
@@ -3423,7 +3469,7 @@
         <v>0.14899999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>98</v>
       </c>
@@ -3522,7 +3568,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>87</v>
       </c>
@@ -3621,7 +3667,7 @@
         <v>0.28799999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="16"/>
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
@@ -3658,7 +3704,7 @@
       <c r="AI15" s="18"/>
       <c r="AJ15" s="16"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>86</v>
       </c>
@@ -3697,7 +3743,7 @@
       <c r="AI16" s="16"/>
       <c r="AJ16" s="16"/>
     </row>
-    <row r="17" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>99</v>
       </c>
@@ -3796,7 +3842,7 @@
         <v>0.443</v>
       </c>
     </row>
-    <row r="18" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>134</v>
       </c>
@@ -3895,7 +3941,7 @@
         <v>-0.10299999999999999</v>
       </c>
     </row>
-    <row r="19" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>135</v>
       </c>
@@ -3994,7 +4040,7 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>136</v>
       </c>
@@ -4093,7 +4139,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>137</v>
       </c>
@@ -4192,7 +4238,7 @@
         <v>-0.13600000000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>138</v>
       </c>
@@ -4289,7 +4335,7 @@
         <v>0.156</v>
       </c>
     </row>
-    <row r="23" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>139</v>
       </c>
@@ -4386,7 +4432,7 @@
         <v>-1.6E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="16" t="s">
         <v>141</v>
       </c>
@@ -4483,7 +4529,7 @@
         <v>0.112</v>
       </c>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="16" t="s">
         <v>142</v>
       </c>
@@ -4580,7 +4626,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
         <v>140</v>
       </c>
@@ -4677,7 +4723,7 @@
         <v>-4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="16"/>
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
@@ -4714,7 +4760,7 @@
       <c r="AI27" s="18"/>
       <c r="AJ27" s="16"/>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>82</v>
       </c>
@@ -4753,7 +4799,7 @@
       <c r="AI28" s="16"/>
       <c r="AJ28" s="16"/>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="16" t="s">
         <v>83</v>
       </c>
@@ -4852,7 +4898,7 @@
         <v>14.164999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="16" t="s">
         <v>88</v>
       </c>
@@ -4951,7 +4997,7 @@
         <v>4.1660000000000004</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="16" t="s">
         <v>91</v>
       </c>
@@ -5050,7 +5096,7 @@
         <v>1.0549999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
         <v>100</v>
       </c>
@@ -5147,7 +5193,7 @@
         <v>4.202</v>
       </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A33" s="20" t="s">
         <v>105</v>
       </c>
@@ -5190,69 +5236,63 @@
       <c r="AL33" s="16"/>
       <c r="AM33" s="16"/>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="B34" s="40">
+      <c r="B34" s="55">
         <v>74058.118000000002</v>
       </c>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
+      <c r="C34" s="55"/>
+      <c r="D34" s="55"/>
+      <c r="E34" s="55"/>
+      <c r="F34" s="55"/>
       <c r="G34" s="25"/>
-      <c r="H34" s="40">
+      <c r="H34" s="55">
         <v>83016.937999999995</v>
       </c>
-      <c r="I34" s="40"/>
-      <c r="J34" s="40"/>
-      <c r="K34" s="40"/>
-      <c r="L34" s="40"/>
+      <c r="I34" s="55"/>
+      <c r="J34" s="55"/>
+      <c r="K34" s="55"/>
+      <c r="L34" s="55"/>
       <c r="M34" s="25"/>
-      <c r="N34" s="40">
+      <c r="N34" s="55">
         <v>94345.274999999994</v>
       </c>
-      <c r="O34" s="40"/>
-      <c r="P34" s="40"/>
-      <c r="Q34" s="40"/>
-      <c r="R34" s="40"/>
+      <c r="O34" s="55"/>
+      <c r="P34" s="55"/>
+      <c r="Q34" s="55"/>
+      <c r="R34" s="55"/>
       <c r="S34" s="15"/>
-      <c r="T34" s="40">
+      <c r="T34" s="55">
         <v>83167.763000000006</v>
       </c>
-      <c r="U34" s="40"/>
-      <c r="V34" s="40"/>
-      <c r="W34" s="40"/>
-      <c r="X34" s="40"/>
+      <c r="U34" s="55"/>
+      <c r="V34" s="55"/>
+      <c r="W34" s="55"/>
+      <c r="X34" s="55"/>
       <c r="Y34" s="25"/>
-      <c r="Z34" s="40">
+      <c r="Z34" s="55">
         <v>93083.505999999994</v>
       </c>
-      <c r="AA34" s="40"/>
-      <c r="AB34" s="40"/>
-      <c r="AC34" s="40"/>
-      <c r="AD34" s="40"/>
+      <c r="AA34" s="55"/>
+      <c r="AB34" s="55"/>
+      <c r="AC34" s="55"/>
+      <c r="AD34" s="55"/>
       <c r="AE34" s="25"/>
-      <c r="AF34" s="40">
+      <c r="AF34" s="55">
         <v>105770.462</v>
       </c>
-      <c r="AG34" s="40"/>
-      <c r="AH34" s="40"/>
-      <c r="AI34" s="40"/>
-      <c r="AJ34" s="40"/>
+      <c r="AG34" s="55"/>
+      <c r="AH34" s="55"/>
+      <c r="AI34" s="55"/>
+      <c r="AJ34" s="55"/>
       <c r="AK34" s="16"/>
       <c r="AL34" s="16"/>
       <c r="AM34" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="AF34:AJ34"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="H34:L34"/>
-    <mergeCell ref="T34:X34"/>
-    <mergeCell ref="N34:R34"/>
-    <mergeCell ref="Z34:AD34"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B2:R2"/>
     <mergeCell ref="H3:L3"/>
@@ -5261,6 +5301,12 @@
     <mergeCell ref="T3:X3"/>
     <mergeCell ref="Z3:AD3"/>
     <mergeCell ref="AF3:AJ3"/>
+    <mergeCell ref="AF34:AJ34"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="H34:L34"/>
+    <mergeCell ref="T34:X34"/>
+    <mergeCell ref="N34:R34"/>
+    <mergeCell ref="Z34:AD34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -5270,140 +5316,140 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CD5CF7F-81D6-D24D-8228-B4C578C35D65}">
   <dimension ref="A1:AM41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="7.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.625" style="1" customWidth="1"/>
     <col min="5" max="6" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="1.1640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="1.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.625" style="1" customWidth="1"/>
     <col min="11" max="12" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="1.1640625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="9.1640625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.6640625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="1.125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="9.125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.625" style="1" customWidth="1"/>
     <col min="17" max="17" width="6.5" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="0.83203125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="9.33203125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.6640625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="0.875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="9.375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="5.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.625" style="1" customWidth="1"/>
     <col min="24" max="24" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="1" style="1" customWidth="1"/>
-    <col min="26" max="26" width="9.33203125" style="1" customWidth="1"/>
-    <col min="27" max="27" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.375" style="1" customWidth="1"/>
+    <col min="27" max="27" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="5.625" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="30" width="6" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="1.1640625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="9.1640625" style="1" customWidth="1"/>
-    <col min="33" max="33" width="5.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="5.6640625" style="1" customWidth="1"/>
+    <col min="31" max="31" width="1.125" style="1" customWidth="1"/>
+    <col min="32" max="32" width="9.125" style="1" customWidth="1"/>
+    <col min="33" max="33" width="5.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.625" style="1" customWidth="1"/>
     <col min="35" max="36" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="56" t="s">
         <v>102</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="56"/>
       <c r="S2" s="9"/>
-      <c r="T2" s="38" t="s">
+      <c r="T2" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="U2" s="38"/>
-      <c r="V2" s="38"/>
-      <c r="W2" s="38"/>
-      <c r="X2" s="38"/>
-      <c r="Y2" s="38"/>
-      <c r="Z2" s="38"/>
-      <c r="AA2" s="38"/>
-      <c r="AB2" s="38"/>
-      <c r="AC2" s="38"/>
-      <c r="AD2" s="38"/>
-      <c r="AE2" s="38"/>
-      <c r="AF2" s="38"/>
-      <c r="AG2" s="38"/>
-      <c r="AH2" s="38"/>
-      <c r="AI2" s="38"/>
-      <c r="AJ2" s="38"/>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="U2" s="56"/>
+      <c r="V2" s="56"/>
+      <c r="W2" s="56"/>
+      <c r="X2" s="56"/>
+      <c r="Y2" s="56"/>
+      <c r="Z2" s="56"/>
+      <c r="AA2" s="56"/>
+      <c r="AB2" s="56"/>
+      <c r="AC2" s="56"/>
+      <c r="AD2" s="56"/>
+      <c r="AE2" s="56"/>
+      <c r="AF2" s="56"/>
+      <c r="AG2" s="56"/>
+      <c r="AH2" s="56"/>
+      <c r="AI2" s="56"/>
+      <c r="AJ2" s="56"/>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" s="16"/>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="56" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
       <c r="G3" s="26"/>
-      <c r="H3" s="38" t="s">
+      <c r="H3" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="56"/>
+      <c r="L3" s="56"/>
       <c r="M3" s="26"/>
-      <c r="N3" s="38" t="s">
+      <c r="N3" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
-      <c r="T3" s="39" t="s">
+      <c r="O3" s="56"/>
+      <c r="P3" s="56"/>
+      <c r="Q3" s="56"/>
+      <c r="R3" s="56"/>
+      <c r="T3" s="57" t="s">
         <v>79</v>
       </c>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="39"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="57"/>
+      <c r="W3" s="57"/>
+      <c r="X3" s="57"/>
       <c r="Y3" s="26"/>
-      <c r="Z3" s="38" t="s">
+      <c r="Z3" s="56" t="s">
         <v>80</v>
       </c>
-      <c r="AA3" s="38"/>
-      <c r="AB3" s="38"/>
-      <c r="AC3" s="38"/>
-      <c r="AD3" s="38"/>
+      <c r="AA3" s="56"/>
+      <c r="AB3" s="56"/>
+      <c r="AC3" s="56"/>
+      <c r="AD3" s="56"/>
       <c r="AE3" s="26"/>
-      <c r="AF3" s="38" t="s">
+      <c r="AF3" s="56" t="s">
         <v>81</v>
       </c>
-      <c r="AG3" s="38"/>
-      <c r="AH3" s="38"/>
-      <c r="AI3" s="38"/>
-      <c r="AJ3" s="38"/>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.2">
+      <c r="AG3" s="56"/>
+      <c r="AH3" s="56"/>
+      <c r="AI3" s="56"/>
+      <c r="AJ3" s="56"/>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" s="15"/>
       <c r="B4" s="27" t="s">
         <v>143</v>
@@ -5501,7 +5547,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>84</v>
       </c>
@@ -5540,7 +5586,7 @@
       <c r="AI5" s="16"/>
       <c r="AJ5" s="16"/>
     </row>
-    <row r="6" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
         <v>93</v>
       </c>
@@ -5639,7 +5685,7 @@
         <v>13.875999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
         <v>94</v>
       </c>
@@ -5738,7 +5784,7 @@
         <v>2.1219999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>127</v>
       </c>
@@ -5837,7 +5883,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A9" s="16"/>
       <c r="B9" s="16"/>
       <c r="C9" s="16"/>
@@ -5874,7 +5920,7 @@
       <c r="AI9" s="18"/>
       <c r="AJ9" s="16"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>85</v>
       </c>
@@ -5913,7 +5959,7 @@
       <c r="AI10" s="16"/>
       <c r="AJ10" s="16"/>
     </row>
-    <row r="11" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>95</v>
       </c>
@@ -6012,7 +6058,7 @@
         <v>0.40300000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>126</v>
       </c>
@@ -6111,7 +6157,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
         <v>96</v>
       </c>
@@ -6210,7 +6256,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>97</v>
       </c>
@@ -6309,7 +6355,7 @@
         <v>8.5999999999999993E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>128</v>
       </c>
@@ -6408,7 +6454,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="16" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>98</v>
       </c>
@@ -6507,7 +6553,7 @@
         <v>0.22900000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>129</v>
       </c>
@@ -6606,7 +6652,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>87</v>
       </c>
@@ -6705,7 +6751,7 @@
         <v>0.28799999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="16"/>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -6742,7 +6788,7 @@
       <c r="AI19" s="18"/>
       <c r="AJ19" s="16"/>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="s">
         <v>86</v>
       </c>
@@ -6781,7 +6827,7 @@
       <c r="AI20" s="16"/>
       <c r="AJ20" s="16"/>
     </row>
-    <row r="21" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
         <v>99</v>
       </c>
@@ -6880,7 +6926,7 @@
         <v>0.14499999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="34" t="s">
         <v>125</v>
       </c>
@@ -6979,7 +7025,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="34" t="s">
         <v>134</v>
       </c>
@@ -7078,7 +7124,7 @@
         <v>-9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="34" t="s">
         <v>135</v>
       </c>
@@ -7177,7 +7223,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:36" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
         <v>150</v>
       </c>
@@ -7257,7 +7303,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="34" t="s">
         <v>136</v>
       </c>
@@ -7356,7 +7402,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="34" t="s">
         <v>137</v>
       </c>
@@ -7455,7 +7501,7 @@
         <v>-0.13600000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="34" t="s">
         <v>138</v>
       </c>
@@ -7552,7 +7598,7 @@
         <v>0.17199999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:36" ht="17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="34" t="s">
         <v>139</v>
       </c>
@@ -7649,7 +7695,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="34" t="s">
         <v>151</v>
       </c>
@@ -7728,7 +7774,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="34" t="s">
         <v>141</v>
       </c>
@@ -7825,7 +7871,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" s="34" t="s">
         <v>142</v>
       </c>
@@ -7922,8 +7968,8 @@
         <v>0.17499999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A33" s="36" t="s">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A33" s="65" t="s">
         <v>140</v>
       </c>
       <c r="B33" s="16" t="s">
@@ -8019,7 +8065,7 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A34" s="16"/>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
@@ -8056,7 +8102,7 @@
       <c r="AI34" s="18"/>
       <c r="AJ34" s="16"/>
     </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
         <v>82</v>
       </c>
@@ -8095,7 +8141,7 @@
       <c r="AI35" s="16"/>
       <c r="AJ35" s="16"/>
     </row>
-    <row r="36" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
         <v>83</v>
       </c>
@@ -8194,7 +8240,7 @@
         <v>14.162000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
         <v>88</v>
       </c>
@@ -8293,7 +8339,7 @@
         <v>4.1660000000000004</v>
       </c>
     </row>
-    <row r="38" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
         <v>91</v>
       </c>
@@ -8392,7 +8438,7 @@
         <v>1.0549999999999999</v>
       </c>
     </row>
-    <row r="39" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
         <v>100</v>
       </c>
@@ -8489,7 +8535,7 @@
         <v>4.5090000000000003</v>
       </c>
     </row>
-    <row r="40" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A40" s="20" t="s">
         <v>105</v>
       </c>
@@ -8532,57 +8578,57 @@
       <c r="AL40" s="16"/>
       <c r="AM40" s="16"/>
     </row>
-    <row r="41" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="B41" s="40">
+      <c r="B41" s="55">
         <v>34697.703999999998</v>
       </c>
-      <c r="C41" s="40"/>
-      <c r="D41" s="40"/>
-      <c r="E41" s="40"/>
-      <c r="F41" s="40"/>
+      <c r="C41" s="55"/>
+      <c r="D41" s="55"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
       <c r="G41" s="25"/>
-      <c r="H41" s="40">
+      <c r="H41" s="55">
         <v>43730.449000000001</v>
       </c>
-      <c r="I41" s="40"/>
-      <c r="J41" s="40"/>
-      <c r="K41" s="40"/>
-      <c r="L41" s="40"/>
+      <c r="I41" s="55"/>
+      <c r="J41" s="55"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="55"/>
       <c r="M41" s="25"/>
-      <c r="N41" s="40">
+      <c r="N41" s="55">
         <v>55075.362999999998</v>
       </c>
-      <c r="O41" s="40"/>
-      <c r="P41" s="40"/>
-      <c r="Q41" s="40"/>
-      <c r="R41" s="40"/>
+      <c r="O41" s="55"/>
+      <c r="P41" s="55"/>
+      <c r="Q41" s="55"/>
+      <c r="R41" s="55"/>
       <c r="S41" s="15"/>
-      <c r="T41" s="40">
+      <c r="T41" s="55">
         <v>37782.404000000002</v>
       </c>
-      <c r="U41" s="40"/>
-      <c r="V41" s="40"/>
-      <c r="W41" s="40"/>
-      <c r="X41" s="40"/>
+      <c r="U41" s="55"/>
+      <c r="V41" s="55"/>
+      <c r="W41" s="55"/>
+      <c r="X41" s="55"/>
       <c r="Y41" s="25"/>
-      <c r="Z41" s="40">
+      <c r="Z41" s="55">
         <v>47698.324999999997</v>
       </c>
-      <c r="AA41" s="40"/>
-      <c r="AB41" s="40"/>
-      <c r="AC41" s="40"/>
-      <c r="AD41" s="40"/>
+      <c r="AA41" s="55"/>
+      <c r="AB41" s="55"/>
+      <c r="AC41" s="55"/>
+      <c r="AD41" s="55"/>
       <c r="AE41" s="25"/>
-      <c r="AF41" s="40">
+      <c r="AF41" s="55">
         <v>60402.93</v>
       </c>
-      <c r="AG41" s="40"/>
-      <c r="AH41" s="40"/>
-      <c r="AI41" s="40"/>
-      <c r="AJ41" s="40"/>
+      <c r="AG41" s="55"/>
+      <c r="AH41" s="55"/>
+      <c r="AI41" s="55"/>
+      <c r="AJ41" s="55"/>
       <c r="AK41" s="16"/>
       <c r="AL41" s="16"/>
       <c r="AM41" s="16"/>
@@ -8612,54 +8658,54 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{540507A6-720C-0B43-804E-087FEE710926}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="19.1640625" customWidth="1"/>
+    <col min="1" max="1" width="19.875" customWidth="1"/>
+    <col min="2" max="2" width="18.875" customWidth="1"/>
+    <col min="3" max="3" width="19.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="24"/>
     </row>
-    <row r="3" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="24"/>
     </row>
-    <row r="6" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="24"/>
     </row>
-    <row r="7" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:3" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="23" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B11" s="23" t="s">
         <v>117</v>
       </c>
@@ -8667,7 +8713,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>114</v>
       </c>
@@ -8678,7 +8724,7 @@
         <v>-1.4E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>115</v>
       </c>
@@ -8689,7 +8735,7 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>116</v>
       </c>
@@ -8700,7 +8746,7 @@
         <v>-7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>121</v>
       </c>
@@ -8711,17 +8757,17 @@
         <v>-8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="23" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B19" s="23" t="s">
         <v>117</v>
       </c>
@@ -8729,7 +8775,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>114</v>
       </c>
@@ -8740,7 +8786,7 @@
         <v>-1.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>115</v>
       </c>
@@ -8751,18 +8797,18 @@
         <v>-1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="46" t="s">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="38" t="s">
         <v>116</v>
       </c>
-      <c r="B22" s="46">
+      <c r="B22" s="38">
         <v>-0.113</v>
       </c>
-      <c r="C22" s="46">
+      <c r="C22" s="38">
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>121</v>
       </c>
@@ -8773,7 +8819,7 @@
         <v>-1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E25" s="23" t="s">
         <v>120</v>
       </c>
@@ -8785,15 +8831,1223 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A439B20-C024-854E-8504-DA6820AADA52}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:T71"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="0.875" customWidth="1"/>
+    <col min="5" max="5" width="6.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="0.875" customWidth="1"/>
+    <col min="8" max="8" width="4.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="1.25" customWidth="1"/>
+    <col min="11" max="11" width="6.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="0.875" customWidth="1"/>
+    <col min="14" max="14" width="6.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="0.875" customWidth="1"/>
+    <col min="17" max="17" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B1" s="62" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="62"/>
+      <c r="G1" s="62"/>
+      <c r="H1" s="62"/>
+      <c r="I1" s="62"/>
+      <c r="K1" s="62" t="s">
+        <v>155</v>
+      </c>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
+      <c r="P1" s="62"/>
+      <c r="Q1" s="62"/>
+      <c r="R1" s="62"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="16"/>
+      <c r="B2" s="67" t="s">
         <v>152</v>
       </c>
+      <c r="C2" s="67"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="67" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2" s="67"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="73" t="s">
+        <v>158</v>
+      </c>
+      <c r="I2" s="67"/>
+      <c r="K2" s="67" t="s">
+        <v>152</v>
+      </c>
+      <c r="L2" s="67"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="67" t="s">
+        <v>153</v>
+      </c>
+      <c r="O2" s="67"/>
+      <c r="P2" s="68"/>
+      <c r="Q2" s="73" t="s">
+        <v>158</v>
+      </c>
+      <c r="R2" s="67"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" s="16"/>
+      <c r="E3" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3" s="65"/>
+      <c r="H3" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="M3" s="16"/>
+      <c r="N3" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="O3" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="P3" s="65"/>
+      <c r="Q3" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="R3" s="15" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="16">
+        <v>583.58000000000004</v>
+      </c>
+      <c r="C4" s="16">
+        <v>1.5069999999999999</v>
+      </c>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16">
+        <v>628.20799999999997</v>
+      </c>
+      <c r="F4" s="16">
+        <v>1.613</v>
+      </c>
+      <c r="G4" s="16"/>
+      <c r="H4" s="69">
+        <f>(E4-B4)/SQRT(C4^2+F4^2)</f>
+        <v>20.217028765672296</v>
+      </c>
+      <c r="I4" s="71">
+        <f>2*(1-_xlfn.NORM.S.DIST(ABS((E4-B4)/SQRT(F4^2+C4^2)),TRUE))</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="69"/>
+      <c r="R4" s="71"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="16">
+        <v>-94.037999999999997</v>
+      </c>
+      <c r="C5" s="16">
+        <v>4.6189999999999998</v>
+      </c>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16">
+        <v>-97.516999999999996</v>
+      </c>
+      <c r="F5" s="16">
+        <v>5.6059999999999999</v>
+      </c>
+      <c r="G5" s="16"/>
+      <c r="H5" s="69">
+        <f>(E5-B5)/SQRT(C5^2+F5^2)</f>
+        <v>-0.4789521973518257</v>
+      </c>
+      <c r="I5" s="71">
+        <f>2*(1-_xlfn.NORM.S.DIST(ABS((E5-B5)/SQRT(F5^2+C5^2)),TRUE))</f>
+        <v>0.63197263613839638</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="L5" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="69"/>
+      <c r="R5" s="71"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="I6" s="71" t="s">
+        <v>92</v>
+      </c>
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="O6" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16"/>
+      <c r="R6" s="71"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="H7" s="16"/>
+      <c r="I7" s="71"/>
+      <c r="Q7" s="16"/>
+      <c r="R7" s="71"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="71"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="71"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B9" s="16">
+        <v>-143.018</v>
+      </c>
+      <c r="C9" s="16">
+        <v>19.260000000000002</v>
+      </c>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16">
+        <v>-163.089</v>
+      </c>
+      <c r="F9" s="16">
+        <v>23.18</v>
+      </c>
+      <c r="G9" s="16"/>
+      <c r="H9" s="69">
+        <f t="shared" ref="H9:H37" si="0">(E9-B9)/SQRT(C9^2+F9^2)</f>
+        <v>-0.66598418602211018</v>
+      </c>
+      <c r="I9" s="71">
+        <f t="shared" ref="I9:I37" si="1">2*(1-_xlfn.NORM.S.DIST(ABS((E9-B9)/SQRT(F9^2+C9^2)),TRUE))</f>
+        <v>0.50542120843141158</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="69"/>
+      <c r="R9" s="71"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="71"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="O10" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16"/>
+      <c r="R10" s="71"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B11" s="16">
+        <v>5.476</v>
+      </c>
+      <c r="C11" s="16">
+        <v>1.054</v>
+      </c>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16">
+        <v>2.9449999999999998</v>
+      </c>
+      <c r="F11" s="16">
+        <v>1.117</v>
+      </c>
+      <c r="G11" s="16"/>
+      <c r="H11" s="69">
+        <f t="shared" si="0"/>
+        <v>-1.6480278164792663</v>
+      </c>
+      <c r="I11" s="71">
+        <f t="shared" si="1"/>
+        <v>9.9346963219966389E-2</v>
+      </c>
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16"/>
+      <c r="P11" s="16"/>
+      <c r="Q11" s="69"/>
+      <c r="R11" s="71"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="16">
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="C12" s="16">
+        <v>0.14899999999999999</v>
+      </c>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16">
+        <v>0.71199999999999997</v>
+      </c>
+      <c r="F12" s="16">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="G12" s="16"/>
+      <c r="H12" s="69">
+        <f t="shared" si="0"/>
+        <v>-1.0735963465802587</v>
+      </c>
+      <c r="I12" s="71">
+        <f t="shared" si="1"/>
+        <v>0.28300363576262133</v>
+      </c>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="69"/>
+      <c r="R12" s="71"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="71"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="71"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" s="16">
+        <v>-7.8E-2</v>
+      </c>
+      <c r="C14" s="16">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16">
+        <v>-3.4000000000000002E-2</v>
+      </c>
+      <c r="F14" s="16">
+        <v>4.7E-2</v>
+      </c>
+      <c r="G14" s="16"/>
+      <c r="H14" s="69">
+        <f t="shared" si="0"/>
+        <v>0.61461866027722878</v>
+      </c>
+      <c r="I14" s="71">
+        <f t="shared" si="1"/>
+        <v>0.53880658814494398</v>
+      </c>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="69"/>
+      <c r="R14" s="71"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="G15" s="16"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="71"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="R15" s="71"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="16">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="C16" s="16">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16">
+        <v>3.1E-2</v>
+      </c>
+      <c r="F16" s="16">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="G16" s="16"/>
+      <c r="H16" s="69">
+        <f>(E16-B16)/SQRT(C16^2+F16^2)</f>
+        <v>-3.2998316455372216</v>
+      </c>
+      <c r="I16" s="71">
+        <f t="shared" si="1"/>
+        <v>9.6742845024766488E-4</v>
+      </c>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="69"/>
+      <c r="R16" s="71"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="71"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="71"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="71"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="71"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B19" s="16">
+        <v>3.2040000000000002</v>
+      </c>
+      <c r="C19" s="16">
+        <v>0.379</v>
+      </c>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16">
+        <v>4.17</v>
+      </c>
+      <c r="F19" s="16">
+        <v>0.39700000000000002</v>
+      </c>
+      <c r="G19" s="16"/>
+      <c r="H19" s="69">
+        <f t="shared" si="0"/>
+        <v>1.7600037721574058</v>
+      </c>
+      <c r="I19" s="71">
+        <f t="shared" si="1"/>
+        <v>7.8407166997530142E-2</v>
+      </c>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="69"/>
+      <c r="R19" s="71"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="I20" s="71" t="s">
+        <v>92</v>
+      </c>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="71"/>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="B21" s="16">
+        <v>-3.8210000000000002</v>
+      </c>
+      <c r="C21" s="16">
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16">
+        <v>-4.1269999999999998</v>
+      </c>
+      <c r="F21" s="16">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="G21" s="16"/>
+      <c r="H21" s="69">
+        <f t="shared" si="0"/>
+        <v>-0.35714486154069242</v>
+      </c>
+      <c r="I21" s="71">
+        <f t="shared" si="1"/>
+        <v>0.7209833614345651</v>
+      </c>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="16"/>
+      <c r="O21" s="16"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="69"/>
+      <c r="R21" s="71"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B22" s="16">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="C22" s="16">
+        <v>0.222</v>
+      </c>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16">
+        <v>0.151</v>
+      </c>
+      <c r="F22" s="16">
+        <v>0.252</v>
+      </c>
+      <c r="G22" s="16"/>
+      <c r="H22" s="69">
+        <f t="shared" si="0"/>
+        <v>0.41091087812397076</v>
+      </c>
+      <c r="I22" s="71">
+        <f t="shared" si="1"/>
+        <v>0.68113788560684063</v>
+      </c>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="16"/>
+      <c r="O22" s="16"/>
+      <c r="P22" s="16"/>
+      <c r="Q22" s="69"/>
+      <c r="R22" s="71"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="I23" s="71" t="s">
+        <v>92</v>
+      </c>
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
+      <c r="M23" s="16"/>
+      <c r="N23" s="16"/>
+      <c r="O23" s="16"/>
+      <c r="P23" s="16"/>
+      <c r="Q23" s="16"/>
+      <c r="R23" s="71"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" s="16">
+        <v>-0.112</v>
+      </c>
+      <c r="C24" s="16">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16">
+        <v>-2E-3</v>
+      </c>
+      <c r="F24" s="16">
+        <v>1.2E-2</v>
+      </c>
+      <c r="G24" s="16"/>
+      <c r="H24" s="69">
+        <f t="shared" si="0"/>
+        <v>6.2175676083864371</v>
+      </c>
+      <c r="I24" s="71">
+        <f t="shared" si="1"/>
+        <v>5.0492054981532419E-10</v>
+      </c>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="16"/>
+      <c r="N24" s="16"/>
+      <c r="O24" s="16"/>
+      <c r="P24" s="16"/>
+      <c r="Q24" s="69"/>
+      <c r="R24" s="71"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="B25" s="16">
+        <v>-1.7999999999999999E-2</v>
+      </c>
+      <c r="C25" s="16">
+        <v>2E-3</v>
+      </c>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16">
+        <v>-1.2E-2</v>
+      </c>
+      <c r="F25" s="16">
+        <v>1E-3</v>
+      </c>
+      <c r="G25" s="16"/>
+      <c r="H25" s="69">
+        <f t="shared" si="0"/>
+        <v>2.6832815729997472</v>
+      </c>
+      <c r="I25" s="71">
+        <f t="shared" si="1"/>
+        <v>7.2903580915355537E-3</v>
+      </c>
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
+      <c r="M25" s="16"/>
+      <c r="N25" s="16"/>
+      <c r="O25" s="16"/>
+      <c r="P25" s="16"/>
+      <c r="Q25" s="69"/>
+      <c r="R25" s="71"/>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="B26" s="16">
+        <v>0.01</v>
+      </c>
+      <c r="C26" s="16">
+        <v>2E-3</v>
+      </c>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="F26" s="16">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="G26" s="16"/>
+      <c r="H26" s="69">
+        <f t="shared" si="0"/>
+        <v>2.4537178936808859</v>
+      </c>
+      <c r="I26" s="71">
+        <f t="shared" si="1"/>
+        <v>1.4138785229651951E-2</v>
+      </c>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
+      <c r="N26" s="16"/>
+      <c r="O26" s="16"/>
+      <c r="P26" s="16"/>
+      <c r="Q26" s="69"/>
+      <c r="R26" s="71"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B27" s="16">
+        <v>-2E-3</v>
+      </c>
+      <c r="C27" s="16">
+        <v>1.2E-2</v>
+      </c>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16">
+        <v>3.0750000000000002</v>
+      </c>
+      <c r="F27" s="16">
+        <v>0.53200000000000003</v>
+      </c>
+      <c r="G27" s="16"/>
+      <c r="H27" s="69">
+        <f t="shared" si="0"/>
+        <v>5.7823637668592012</v>
+      </c>
+      <c r="I27" s="71">
+        <f t="shared" si="1"/>
+        <v>7.3658215082872402E-9</v>
+      </c>
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="16"/>
+      <c r="N27" s="16"/>
+      <c r="O27" s="16"/>
+      <c r="P27" s="16"/>
+      <c r="Q27" s="69"/>
+      <c r="R27" s="71"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="I28" s="71" t="s">
+        <v>92</v>
+      </c>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
+      <c r="O28" s="16"/>
+      <c r="P28" s="16"/>
+      <c r="Q28" s="16"/>
+      <c r="R28" s="71"/>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="B29" s="16">
+        <v>0.105</v>
+      </c>
+      <c r="C29" s="16">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16">
+        <v>7.0000000000000001E-3</v>
+      </c>
+      <c r="F29" s="16">
+        <v>1E-3</v>
+      </c>
+      <c r="G29" s="16"/>
+      <c r="H29" s="69">
+        <f t="shared" si="0"/>
+        <v>-1.3801448049627287</v>
+      </c>
+      <c r="I29" s="71">
+        <f>2*(1-_xlfn.NORM.S.DIST(ABS((E29-B29)/SQRT(F29^2+C29^2)),TRUE))</f>
+        <v>0.16754206433275831</v>
+      </c>
+      <c r="K29" s="16"/>
+      <c r="L29" s="16"/>
+      <c r="M29" s="16"/>
+      <c r="N29" s="16"/>
+      <c r="O29" s="16"/>
+      <c r="P29" s="16"/>
+      <c r="Q29" s="69"/>
+      <c r="R29" s="71"/>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="B30" s="16">
+        <v>1.841</v>
+      </c>
+      <c r="C30" s="16">
+        <v>0.41799999999999998</v>
+      </c>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16">
+        <v>-2.4E-2</v>
+      </c>
+      <c r="F30" s="16">
+        <v>1.2E-2</v>
+      </c>
+      <c r="G30" s="16"/>
+      <c r="H30" s="69">
+        <f t="shared" si="0"/>
+        <v>-4.4598850439046966</v>
+      </c>
+      <c r="I30" s="71">
+        <f t="shared" si="1"/>
+        <v>8.2003625045956596E-6</v>
+      </c>
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+      <c r="M30" s="16"/>
+      <c r="N30" s="16"/>
+      <c r="O30" s="16"/>
+      <c r="P30" s="16"/>
+      <c r="Q30" s="69"/>
+      <c r="R30" s="71"/>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="B31" s="16">
+        <v>-0.17100000000000001</v>
+      </c>
+      <c r="C31" s="16">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="F31" s="16">
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="G31" s="16"/>
+      <c r="H31" s="69">
+        <f t="shared" si="0"/>
+        <v>0.63530459447531529</v>
+      </c>
+      <c r="I31" s="71">
+        <f t="shared" si="1"/>
+        <v>0.5252297776626822</v>
+      </c>
+      <c r="K31" s="16"/>
+      <c r="L31" s="16"/>
+      <c r="M31" s="16"/>
+      <c r="N31" s="16"/>
+      <c r="O31" s="16"/>
+      <c r="P31" s="16"/>
+      <c r="Q31" s="69"/>
+      <c r="R31" s="71"/>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="16"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="71"/>
+      <c r="K32" s="16"/>
+      <c r="L32" s="16"/>
+      <c r="M32" s="16"/>
+      <c r="N32" s="16"/>
+      <c r="O32" s="16"/>
+      <c r="P32" s="16"/>
+      <c r="Q32" s="16"/>
+      <c r="R32" s="71"/>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="71"/>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
+      <c r="M33" s="16"/>
+      <c r="N33" s="16"/>
+      <c r="O33" s="16"/>
+      <c r="P33" s="16"/>
+      <c r="Q33" s="16"/>
+      <c r="R33" s="71"/>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" s="16">
+        <v>12.225</v>
+      </c>
+      <c r="C34" s="16">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16">
+        <v>14.064</v>
+      </c>
+      <c r="F34" s="16">
+        <v>3.1E-2</v>
+      </c>
+      <c r="G34" s="16"/>
+      <c r="H34" s="69">
+        <f t="shared" si="0"/>
+        <v>39.332961809669918</v>
+      </c>
+      <c r="I34" s="71">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
+      <c r="M34" s="16"/>
+      <c r="N34" s="16"/>
+      <c r="O34" s="16"/>
+      <c r="P34" s="16"/>
+      <c r="Q34" s="69"/>
+      <c r="R34" s="71"/>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B35" s="16">
+        <v>0.58499999999999996</v>
+      </c>
+      <c r="C35" s="16">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16">
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="F35" s="16">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="G35" s="16"/>
+      <c r="H35" s="69">
+        <f t="shared" si="0"/>
+        <v>-14.680333617528966</v>
+      </c>
+      <c r="I35" s="71">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
+      <c r="M35" s="16"/>
+      <c r="N35" s="16"/>
+      <c r="O35" s="16"/>
+      <c r="P35" s="16"/>
+      <c r="Q35" s="69"/>
+      <c r="R35" s="71"/>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" s="65" t="s">
+        <v>91</v>
+      </c>
+      <c r="B36" s="65">
+        <v>1.8320000000000001</v>
+      </c>
+      <c r="C36" s="65">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="D36" s="65"/>
+      <c r="E36" s="65">
+        <v>1.8180000000000001</v>
+      </c>
+      <c r="F36" s="65">
+        <v>3.9E-2</v>
+      </c>
+      <c r="G36" s="65"/>
+      <c r="H36" s="74">
+        <f t="shared" si="0"/>
+        <v>-0.24426449720876661</v>
+      </c>
+      <c r="I36" s="75">
+        <f t="shared" si="1"/>
+        <v>0.80702597789458186</v>
+      </c>
+      <c r="J36" s="66"/>
+      <c r="K36" s="65"/>
+      <c r="L36" s="65"/>
+      <c r="M36" s="65"/>
+      <c r="N36" s="65"/>
+      <c r="O36" s="65"/>
+      <c r="P36" s="65"/>
+      <c r="Q36" s="74"/>
+      <c r="R36" s="75"/>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B37" s="15">
+        <v>10.971</v>
+      </c>
+      <c r="C37" s="15">
+        <v>1.2090000000000001</v>
+      </c>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15">
+        <v>10.044</v>
+      </c>
+      <c r="F37" s="15">
+        <v>1.397</v>
+      </c>
+      <c r="G37" s="15"/>
+      <c r="H37" s="70">
+        <f t="shared" si="0"/>
+        <v>-0.5017566533064739</v>
+      </c>
+      <c r="I37" s="72">
+        <f t="shared" si="1"/>
+        <v>0.61583870769501337</v>
+      </c>
+      <c r="J37" s="76"/>
+      <c r="K37" s="15"/>
+      <c r="L37" s="15"/>
+      <c r="M37" s="15"/>
+      <c r="N37" s="15"/>
+      <c r="O37" s="15"/>
+      <c r="P37" s="15"/>
+      <c r="Q37" s="70"/>
+      <c r="R37" s="72"/>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="K38" s="16"/>
+    </row>
+    <row r="71" spans="20:20" x14ac:dyDescent="0.25">
+      <c r="T71" s="64"/>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="K1:R1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="B1:I1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8801,74 +10055,50 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57A86273-0E84-8246-B3ED-A023C6721217}">
   <dimension ref="A1:AF61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8" style="33" customWidth="1"/>
     <col min="3" max="3" width="5.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.5" style="37" customWidth="1"/>
-    <col min="7" max="7" width="6.83203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.1640625" style="33" customWidth="1"/>
-    <col min="9" max="9" width="5.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.125" style="33" customWidth="1"/>
+    <col min="9" max="9" width="5.625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="5.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="5.875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.5" style="30" customWidth="1"/>
-    <col min="13" max="13" width="3.33203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="3.375" style="1" customWidth="1"/>
     <col min="14" max="14" width="26.5" style="1" customWidth="1"/>
     <col min="15" max="15" width="8" style="1" customWidth="1"/>
     <col min="16" max="16" width="5.5" style="1" customWidth="1"/>
     <col min="17" max="17" width="8" style="1" customWidth="1"/>
-    <col min="18" max="18" width="5.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.875" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7.5" style="1" customWidth="1"/>
-    <col min="20" max="20" width="6.33203125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="6.375" style="1" customWidth="1"/>
     <col min="21" max="21" width="19" style="1" customWidth="1"/>
-    <col min="22" max="22" width="8.1640625" style="1" customWidth="1"/>
-    <col min="23" max="23" width="6.33203125" style="1" customWidth="1"/>
-    <col min="24" max="24" width="7.6640625" style="1" customWidth="1"/>
+    <col min="22" max="22" width="8.125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="6.375" style="1" customWidth="1"/>
+    <col min="24" max="24" width="7.625" style="1" customWidth="1"/>
     <col min="25" max="25" width="7" style="1" customWidth="1"/>
-    <col min="26" max="26" width="7.83203125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="7.875" style="1" customWidth="1"/>
     <col min="27" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A2" s="52"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52"/>
-      <c r="O2" s="52"/>
-      <c r="P2" s="52"/>
-      <c r="Q2" s="52"/>
-      <c r="R2" s="52"/>
-      <c r="S2" s="52"/>
-      <c r="T2" s="52"/>
-      <c r="U2" s="52"/>
-      <c r="V2" s="52"/>
-      <c r="W2" s="52"/>
-      <c r="X2" s="52"/>
-      <c r="Y2" s="52"/>
-      <c r="Z2" s="52"/>
-    </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="L1" s="1"/>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="B2" s="1"/>
+      <c r="F2" s="16"/>
+      <c r="H2" s="1"/>
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -8896,72 +10126,72 @@
       <c r="Y3" s="6"/>
       <c r="Z3" s="6"/>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A4" s="51"/>
-      <c r="B4" s="70" t="s">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A4" s="16"/>
+      <c r="B4" s="60" t="s">
         <v>145</v>
       </c>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="70"/>
-      <c r="K4" s="70"/>
-      <c r="L4" s="70"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="60"/>
       <c r="N4" s="34"/>
-      <c r="O4" s="70" t="s">
+      <c r="O4" s="60" t="s">
         <v>146</v>
       </c>
-      <c r="P4" s="70"/>
-      <c r="Q4" s="70"/>
-      <c r="R4" s="70"/>
-      <c r="S4" s="70"/>
-      <c r="T4" s="70"/>
-      <c r="U4" s="70"/>
-      <c r="V4" s="70"/>
-      <c r="W4" s="70"/>
-      <c r="X4" s="70"/>
-      <c r="Y4" s="70"/>
-      <c r="Z4" s="70"/>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="P4" s="60"/>
+      <c r="Q4" s="60"/>
+      <c r="R4" s="60"/>
+      <c r="S4" s="60"/>
+      <c r="T4" s="60"/>
+      <c r="U4" s="60"/>
+      <c r="V4" s="60"/>
+      <c r="W4" s="60"/>
+      <c r="X4" s="60"/>
+      <c r="Y4" s="60"/>
+      <c r="Z4" s="60"/>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="15"/>
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="61" t="s">
         <v>131</v>
       </c>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="43"/>
-      <c r="H5" s="41" t="s">
+      <c r="C5" s="62"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="63"/>
+      <c r="H5" s="61" t="s">
         <v>130</v>
       </c>
-      <c r="I5" s="42"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="43"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="62"/>
+      <c r="K5" s="62"/>
+      <c r="L5" s="63"/>
       <c r="N5" s="36"/>
-      <c r="O5" s="41" t="s">
+      <c r="O5" s="61" t="s">
         <v>131</v>
       </c>
-      <c r="P5" s="42"/>
-      <c r="Q5" s="42"/>
-      <c r="R5" s="42"/>
-      <c r="S5" s="43"/>
-      <c r="T5" s="59"/>
-      <c r="U5" s="60"/>
-      <c r="V5" s="41" t="s">
+      <c r="P5" s="62"/>
+      <c r="Q5" s="62"/>
+      <c r="R5" s="62"/>
+      <c r="S5" s="63"/>
+      <c r="T5" s="26"/>
+      <c r="U5" s="45"/>
+      <c r="V5" s="61" t="s">
         <v>130</v>
       </c>
-      <c r="W5" s="42"/>
-      <c r="X5" s="42"/>
-      <c r="Y5" s="42"/>
-      <c r="Z5" s="43"/>
-    </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="W5" s="62"/>
+      <c r="X5" s="62"/>
+      <c r="Y5" s="62"/>
+      <c r="Z5" s="63"/>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="16"/>
       <c r="B6" s="29" t="s">
         <v>143</v>
@@ -9006,10 +10236,10 @@
       <c r="R6" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="S6" s="61" t="s">
+      <c r="S6" s="46" t="s">
         <v>123</v>
       </c>
-      <c r="T6" s="63"/>
+      <c r="T6" s="47"/>
       <c r="U6" s="32"/>
       <c r="V6" s="29" t="s">
         <v>143</v>
@@ -9027,7 +10257,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>85</v>
       </c>
@@ -9041,16 +10271,16 @@
       <c r="J7" s="18"/>
       <c r="K7" s="16"/>
       <c r="L7" s="37"/>
-      <c r="N7" s="50" t="s">
+      <c r="N7" s="42" t="s">
         <v>85</v>
       </c>
       <c r="O7" s="35"/>
       <c r="P7" s="16"/>
-      <c r="Q7" s="66"/>
+      <c r="Q7" s="50"/>
       <c r="R7" s="16"/>
-      <c r="S7" s="51"/>
-      <c r="T7" s="64"/>
-      <c r="U7" s="62" t="s">
+      <c r="S7" s="16"/>
+      <c r="T7" s="48"/>
+      <c r="U7" s="17" t="s">
         <v>85</v>
       </c>
       <c r="V7" s="34"/>
@@ -9058,14 +10288,14 @@
       <c r="X7" s="18"/>
       <c r="Y7" s="16"/>
       <c r="Z7" s="37"/>
-      <c r="AA7" s="47"/>
+      <c r="AA7" s="39"/>
       <c r="AB7"/>
       <c r="AC7"/>
       <c r="AD7"/>
       <c r="AE7"/>
       <c r="AF7"/>
     </row>
-    <row r="8" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="16" t="s">
         <v>95</v>
       </c>
@@ -9103,22 +10333,22 @@
       <c r="N8" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="O8" s="68" t="s">
+      <c r="O8" s="52" t="s">
         <v>92</v>
       </c>
       <c r="P8" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="Q8" s="67" t="s">
+      <c r="Q8" s="51" t="s">
         <v>92</v>
       </c>
       <c r="R8" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="S8" s="69" t="s">
-        <v>92</v>
-      </c>
-      <c r="T8" s="51"/>
+      <c r="S8" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="T8" s="16"/>
       <c r="U8" s="34" t="s">
         <v>95</v>
       </c>
@@ -9128,7 +10358,7 @@
       <c r="W8" s="16">
         <v>0.05</v>
       </c>
-      <c r="X8" s="66" t="s">
+      <c r="X8" s="50" t="s">
         <v>147</v>
       </c>
       <c r="Y8" s="16">
@@ -9137,14 +10367,14 @@
       <c r="Z8" s="16">
         <v>0.42</v>
       </c>
-      <c r="AA8" s="48"/>
+      <c r="AA8" s="40"/>
       <c r="AB8"/>
       <c r="AC8"/>
       <c r="AD8"/>
       <c r="AE8"/>
       <c r="AF8"/>
     </row>
-    <row r="9" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
         <v>96</v>
       </c>
@@ -9188,7 +10418,7 @@
       <c r="P9" s="16">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="Q9" s="66">
+      <c r="Q9" s="50">
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="R9" s="16">
@@ -9197,7 +10427,7 @@
       <c r="S9" s="37">
         <v>0.22900000000000001</v>
       </c>
-      <c r="T9" s="51"/>
+      <c r="T9" s="16"/>
       <c r="U9" s="34" t="s">
         <v>96</v>
       </c>
@@ -9207,7 +10437,7 @@
       <c r="W9" s="16">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="X9" s="66">
+      <c r="X9" s="50">
         <v>1.6E-2</v>
       </c>
       <c r="Y9" s="16">
@@ -9216,14 +10446,14 @@
       <c r="Z9" s="16">
         <v>-8.9999999999999993E-3</v>
       </c>
-      <c r="AA9" s="48"/>
+      <c r="AA9" s="40"/>
       <c r="AB9"/>
       <c r="AC9"/>
       <c r="AD9"/>
       <c r="AE9"/>
       <c r="AF9"/>
     </row>
-    <row r="10" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="16" t="s">
         <v>97</v>
       </c>
@@ -9267,7 +10497,7 @@
       <c r="P10" s="16">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="Q10" s="66">
+      <c r="Q10" s="50">
         <v>0.71599999999999997</v>
       </c>
       <c r="R10" s="16">
@@ -9276,7 +10506,7 @@
       <c r="S10" s="37">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="T10" s="51"/>
+      <c r="T10" s="16"/>
       <c r="U10" s="34" t="s">
         <v>97</v>
       </c>
@@ -9286,7 +10516,7 @@
       <c r="W10" s="16">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="X10" s="66" t="s">
+      <c r="X10" s="50" t="s">
         <v>147</v>
       </c>
       <c r="Y10" s="16">
@@ -9295,24 +10525,24 @@
       <c r="Z10" s="16">
         <v>0.11600000000000001</v>
       </c>
-      <c r="AA10" s="48"/>
+      <c r="AA10" s="40"/>
       <c r="AB10"/>
       <c r="AC10"/>
       <c r="AD10"/>
       <c r="AE10"/>
       <c r="AF10"/>
     </row>
-    <row r="11" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="B11" s="54">
+      <c r="B11" s="34">
         <v>-3.2000000000000001E-2</v>
       </c>
-      <c r="C11" s="55">
+      <c r="C11" s="16">
         <v>3.9E-2</v>
       </c>
-      <c r="D11" s="56">
+      <c r="D11" s="18">
         <v>0.40699999999999997</v>
       </c>
       <c r="E11" s="16">
@@ -9346,7 +10576,7 @@
       <c r="P11" s="16">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="Q11" s="66" t="s">
+      <c r="Q11" s="50" t="s">
         <v>24</v>
       </c>
       <c r="R11" s="16">
@@ -9355,7 +10585,7 @@
       <c r="S11" s="37">
         <v>0.115</v>
       </c>
-      <c r="T11" s="51"/>
+      <c r="T11" s="16"/>
       <c r="U11" s="34" t="s">
         <v>132</v>
       </c>
@@ -9365,7 +10595,7 @@
       <c r="W11" s="16">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="X11" s="66">
+      <c r="X11" s="50">
         <v>1E-3</v>
       </c>
       <c r="Y11" s="16">
@@ -9374,14 +10604,14 @@
       <c r="Z11" s="16">
         <v>0.185</v>
       </c>
-      <c r="AA11" s="48"/>
+      <c r="AA11" s="40"/>
       <c r="AB11"/>
       <c r="AC11"/>
       <c r="AD11"/>
       <c r="AE11"/>
       <c r="AF11"/>
     </row>
-    <row r="12" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
         <v>133</v>
       </c>
@@ -9419,22 +10649,22 @@
       <c r="N12" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="O12" s="68" t="s">
+      <c r="O12" s="52" t="s">
         <v>92</v>
       </c>
       <c r="P12" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="Q12" s="67" t="s">
-        <v>92</v>
-      </c>
-      <c r="R12" s="67" t="s">
-        <v>92</v>
-      </c>
-      <c r="S12" s="67" t="s">
-        <v>92</v>
-      </c>
-      <c r="T12" s="51"/>
+      <c r="Q12" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="R12" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="S12" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="T12" s="16"/>
       <c r="U12" s="34" t="s">
         <v>133</v>
       </c>
@@ -9444,7 +10674,7 @@
       <c r="W12" s="16">
         <v>0.02</v>
       </c>
-      <c r="X12" s="66">
+      <c r="X12" s="50">
         <v>4.7E-2</v>
       </c>
       <c r="Y12" s="16">
@@ -9453,14 +10683,14 @@
       <c r="Z12" s="16">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="AA12" s="48"/>
+      <c r="AA12" s="40"/>
       <c r="AB12"/>
       <c r="AC12"/>
       <c r="AD12"/>
       <c r="AE12"/>
       <c r="AF12"/>
     </row>
-    <row r="13" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>86</v>
       </c>
@@ -9477,38 +10707,38 @@
       <c r="N13" s="34" t="s">
         <v>149</v>
       </c>
-      <c r="O13" s="68" t="s">
+      <c r="O13" s="52" t="s">
         <v>92</v>
       </c>
       <c r="P13" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="Q13" s="67" t="s">
-        <v>92</v>
-      </c>
-      <c r="R13" s="67" t="s">
-        <v>92</v>
-      </c>
-      <c r="S13" s="67" t="s">
-        <v>92</v>
-      </c>
-      <c r="T13" s="51"/>
-      <c r="U13" s="50" t="s">
+      <c r="Q13" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="R13" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="S13" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="T13" s="16"/>
+      <c r="U13" s="42" t="s">
         <v>86</v>
       </c>
       <c r="V13" s="34"/>
       <c r="W13" s="16"/>
-      <c r="X13" s="66"/>
+      <c r="X13" s="50"/>
       <c r="Y13" s="16"/>
       <c r="Z13" s="16"/>
-      <c r="AA13" s="53"/>
+      <c r="AA13" s="43"/>
       <c r="AB13"/>
       <c r="AC13"/>
       <c r="AD13"/>
       <c r="AE13"/>
       <c r="AF13"/>
     </row>
-    <row r="14" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
         <v>99</v>
       </c>
@@ -9552,7 +10782,7 @@
       <c r="P14" s="16">
         <v>0.04</v>
       </c>
-      <c r="Q14" s="66">
+      <c r="Q14" s="50">
         <v>4.8000000000000001E-2</v>
       </c>
       <c r="R14" s="16">
@@ -9561,7 +10791,7 @@
       <c r="S14" s="37">
         <v>0.157</v>
       </c>
-      <c r="T14" s="51"/>
+      <c r="T14" s="16"/>
       <c r="U14" s="34" t="s">
         <v>99</v>
       </c>
@@ -9571,7 +10801,7 @@
       <c r="W14" s="16">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="X14" s="66">
+      <c r="X14" s="50">
         <v>3.7999999999999999E-2</v>
       </c>
       <c r="Y14" s="16">
@@ -9580,14 +10810,14 @@
       <c r="Z14" s="16">
         <v>0.14299999999999999</v>
       </c>
-      <c r="AA14" s="48"/>
+      <c r="AA14" s="40"/>
       <c r="AB14"/>
       <c r="AC14"/>
       <c r="AD14"/>
       <c r="AE14"/>
       <c r="AF14"/>
     </row>
-    <row r="15" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
         <v>134</v>
       </c>
@@ -9631,7 +10861,7 @@
       <c r="P15" s="16">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="Q15" s="66" t="s">
+      <c r="Q15" s="50" t="s">
         <v>24</v>
       </c>
       <c r="R15" s="16">
@@ -9640,7 +10870,7 @@
       <c r="S15" s="37">
         <v>0.28399999999999997</v>
       </c>
-      <c r="T15" s="51"/>
+      <c r="T15" s="16"/>
       <c r="U15" s="34" t="s">
         <v>134</v>
       </c>
@@ -9650,7 +10880,7 @@
       <c r="W15" s="16">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="X15" s="66" t="s">
+      <c r="X15" s="50" t="s">
         <v>147</v>
       </c>
       <c r="Y15" s="16">
@@ -9659,14 +10889,14 @@
       <c r="Z15" s="16">
         <v>-8.8999999999999996E-2</v>
       </c>
-      <c r="AA15" s="48"/>
+      <c r="AA15" s="40"/>
       <c r="AB15"/>
       <c r="AC15"/>
       <c r="AD15"/>
       <c r="AE15"/>
       <c r="AF15"/>
     </row>
-    <row r="16" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="16" t="s">
         <v>135</v>
       </c>
@@ -9701,7 +10931,7 @@
       <c r="L16" s="37">
         <v>0.112</v>
       </c>
-      <c r="N16" s="50" t="s">
+      <c r="N16" s="42" t="s">
         <v>86</v>
       </c>
       <c r="O16" s="34"/>
@@ -9709,7 +10939,7 @@
       <c r="Q16" s="18"/>
       <c r="R16" s="16"/>
       <c r="S16" s="37"/>
-      <c r="T16" s="51"/>
+      <c r="T16" s="16"/>
       <c r="U16" s="34" t="s">
         <v>135</v>
       </c>
@@ -9719,7 +10949,7 @@
       <c r="W16" s="16">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="X16" s="66">
+      <c r="X16" s="50">
         <v>0.871</v>
       </c>
       <c r="Y16" s="16">
@@ -9728,14 +10958,14 @@
       <c r="Z16" s="16">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="AA16" s="48"/>
+      <c r="AA16" s="40"/>
       <c r="AB16"/>
       <c r="AC16"/>
       <c r="AD16"/>
       <c r="AE16"/>
       <c r="AF16"/>
     </row>
-    <row r="17" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
         <v>136</v>
       </c>
@@ -9774,22 +11004,22 @@
       <c r="N17" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="O17" s="68" t="s">
+      <c r="O17" s="52" t="s">
         <v>92</v>
       </c>
       <c r="P17" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="Q17" s="67" t="s">
+      <c r="Q17" s="51" t="s">
         <v>92</v>
       </c>
       <c r="R17" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="S17" s="69" t="s">
-        <v>92</v>
-      </c>
-      <c r="T17" s="51"/>
+      <c r="S17" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="T17" s="16"/>
       <c r="U17" s="34" t="s">
         <v>136</v>
       </c>
@@ -9799,7 +11029,7 @@
       <c r="W17" s="16">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="X17" s="66">
+      <c r="X17" s="50">
         <v>8.2000000000000003E-2</v>
       </c>
       <c r="Y17" s="16">
@@ -9808,14 +11038,14 @@
       <c r="Z17" s="16">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="AA17" s="48"/>
+      <c r="AA17" s="40"/>
       <c r="AB17"/>
       <c r="AC17"/>
       <c r="AD17"/>
       <c r="AE17"/>
       <c r="AF17"/>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="16" t="s">
         <v>137</v>
       </c>
@@ -9860,7 +11090,7 @@
       <c r="P18" s="16">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="Q18" s="66" t="s">
+      <c r="Q18" s="50" t="s">
         <v>24</v>
       </c>
       <c r="R18" s="16">
@@ -9869,7 +11099,7 @@
       <c r="S18" s="37">
         <v>0.47799999999999998</v>
       </c>
-      <c r="T18" s="51"/>
+      <c r="T18" s="16"/>
       <c r="U18" s="34" t="s">
         <v>137</v>
       </c>
@@ -9879,7 +11109,7 @@
       <c r="W18" s="16">
         <v>0.02</v>
       </c>
-      <c r="X18" s="66" t="s">
+      <c r="X18" s="50" t="s">
         <v>147</v>
       </c>
       <c r="Y18" s="16">
@@ -9888,14 +11118,14 @@
       <c r="Z18" s="16">
         <v>-0.121</v>
       </c>
-      <c r="AA18" s="48"/>
+      <c r="AA18" s="40"/>
       <c r="AB18"/>
       <c r="AC18"/>
       <c r="AD18"/>
       <c r="AE18"/>
       <c r="AF18"/>
     </row>
-    <row r="19" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A19" s="16" t="s">
         <v>138</v>
       </c>
@@ -9940,7 +11170,7 @@
       <c r="P19" s="16">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="Q19" s="66" t="s">
+      <c r="Q19" s="50" t="s">
         <v>24</v>
       </c>
       <c r="R19" s="16">
@@ -9949,7 +11179,7 @@
       <c r="S19" s="37">
         <v>-6.9000000000000006E-2</v>
       </c>
-      <c r="T19" s="51"/>
+      <c r="T19" s="16"/>
       <c r="U19" s="34" t="s">
         <v>138</v>
       </c>
@@ -9959,7 +11189,7 @@
       <c r="W19" s="16">
         <v>2.5999999999999999E-2</v>
       </c>
-      <c r="X19" s="66" t="s">
+      <c r="X19" s="50" t="s">
         <v>147</v>
       </c>
       <c r="Y19" s="16">
@@ -9968,14 +11198,14 @@
       <c r="Z19" s="16">
         <v>0.17399999999999999</v>
       </c>
-      <c r="AA19" s="48"/>
+      <c r="AA19" s="40"/>
       <c r="AB19"/>
       <c r="AC19"/>
       <c r="AD19"/>
       <c r="AE19"/>
       <c r="AF19"/>
     </row>
-    <row r="20" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
         <v>139</v>
       </c>
@@ -10014,22 +11244,22 @@
       <c r="N20" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="O20" s="68" t="s">
+      <c r="O20" s="52" t="s">
         <v>92</v>
       </c>
       <c r="P20" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="Q20" s="67" t="s">
+      <c r="Q20" s="51" t="s">
         <v>92</v>
       </c>
       <c r="R20" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="S20" s="69" t="s">
-        <v>92</v>
-      </c>
-      <c r="T20" s="51"/>
+      <c r="S20" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="T20" s="16"/>
       <c r="U20" s="34" t="s">
         <v>139</v>
       </c>
@@ -10039,7 +11269,7 @@
       <c r="W20" s="16">
         <v>4.3999999999999997E-2</v>
       </c>
-      <c r="X20" s="66">
+      <c r="X20" s="50">
         <v>0.53600000000000003</v>
       </c>
       <c r="Y20" s="16">
@@ -10048,14 +11278,14 @@
       <c r="Z20" s="16">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="AA20" s="48"/>
+      <c r="AA20" s="40"/>
       <c r="AB20"/>
       <c r="AC20"/>
       <c r="AD20"/>
       <c r="AE20"/>
       <c r="AF20"/>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="16" t="s">
         <v>141</v>
       </c>
@@ -10100,7 +11330,7 @@
       <c r="P21" s="16">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="Q21" s="66" t="s">
+      <c r="Q21" s="50" t="s">
         <v>24</v>
       </c>
       <c r="R21" s="16">
@@ -10109,7 +11339,7 @@
       <c r="S21" s="37">
         <v>-6.2E-2</v>
       </c>
-      <c r="T21" s="51"/>
+      <c r="T21" s="16"/>
       <c r="U21" s="34" t="s">
         <v>141</v>
       </c>
@@ -10119,7 +11349,7 @@
       <c r="W21" s="16">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="X21" s="66">
+      <c r="X21" s="50">
         <v>0.216</v>
       </c>
       <c r="Y21" s="16">
@@ -10128,14 +11358,14 @@
       <c r="Z21" s="16">
         <v>6.8000000000000005E-2</v>
       </c>
-      <c r="AA21" s="48"/>
+      <c r="AA21" s="40"/>
       <c r="AB21"/>
       <c r="AC21"/>
       <c r="AD21"/>
       <c r="AE21"/>
       <c r="AF21"/>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
         <v>142</v>
       </c>
@@ -10179,7 +11409,7 @@
       <c r="P22" s="16">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="Q22" s="66" t="s">
+      <c r="Q22" s="50" t="s">
         <v>24</v>
       </c>
       <c r="R22" s="16">
@@ -10188,7 +11418,7 @@
       <c r="S22" s="37">
         <v>-0.10299999999999999</v>
       </c>
-      <c r="T22" s="51"/>
+      <c r="T22" s="16"/>
       <c r="U22" s="34" t="s">
         <v>142</v>
       </c>
@@ -10198,7 +11428,7 @@
       <c r="W22" s="16">
         <v>0.02</v>
       </c>
-      <c r="X22" s="66" t="s">
+      <c r="X22" s="50" t="s">
         <v>147</v>
       </c>
       <c r="Y22" s="16">
@@ -10207,14 +11437,14 @@
       <c r="Z22" s="16">
         <v>0.19600000000000001</v>
       </c>
-      <c r="AA22" s="48"/>
+      <c r="AA22" s="40"/>
       <c r="AB22"/>
       <c r="AC22"/>
       <c r="AD22"/>
       <c r="AE22"/>
       <c r="AF22"/>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="16" t="s">
         <v>140</v>
       </c>
@@ -10258,7 +11488,7 @@
       <c r="P23" s="16">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="Q23" s="66" t="s">
+      <c r="Q23" s="50" t="s">
         <v>24</v>
       </c>
       <c r="R23" s="16">
@@ -10267,7 +11497,7 @@
       <c r="S23" s="37">
         <v>-0.124</v>
       </c>
-      <c r="T23" s="51"/>
+      <c r="T23" s="16"/>
       <c r="U23" s="34" t="s">
         <v>140</v>
       </c>
@@ -10277,7 +11507,7 @@
       <c r="W23" s="16">
         <v>0.02</v>
       </c>
-      <c r="X23" s="66" t="s">
+      <c r="X23" s="50" t="s">
         <v>147</v>
       </c>
       <c r="Y23" s="16">
@@ -10286,14 +11516,14 @@
       <c r="Z23" s="16">
         <v>-4.2999999999999997E-2</v>
       </c>
-      <c r="AA23" s="48"/>
+      <c r="AA23" s="40"/>
       <c r="AB23"/>
       <c r="AC23"/>
       <c r="AD23"/>
       <c r="AE23"/>
       <c r="AF23"/>
     </row>
-    <row r="24" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" s="20" t="s">
         <v>105</v>
       </c>
@@ -10305,7 +11535,7 @@
       <c r="G24" s="14"/>
       <c r="H24" s="35"/>
       <c r="I24" s="14"/>
-      <c r="J24" s="49"/>
+      <c r="J24" s="41"/>
       <c r="K24" s="14"/>
       <c r="L24" s="31"/>
       <c r="N24" s="34" t="s">
@@ -10317,7 +11547,7 @@
       <c r="P24" s="16">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="Q24" s="66" t="s">
+      <c r="Q24" s="50" t="s">
         <v>24</v>
       </c>
       <c r="R24" s="16">
@@ -10326,71 +11556,71 @@
       <c r="S24" s="37">
         <v>0.183</v>
       </c>
-      <c r="T24" s="51"/>
-      <c r="U24" s="65" t="s">
+      <c r="T24" s="16"/>
+      <c r="U24" s="49" t="s">
         <v>105</v>
       </c>
       <c r="V24" s="35"/>
       <c r="W24" s="14"/>
-      <c r="X24" s="49"/>
+      <c r="X24" s="41"/>
       <c r="Y24" s="14"/>
       <c r="Z24" s="31"/>
-      <c r="AA24" s="47"/>
+      <c r="AA24" s="39"/>
       <c r="AB24"/>
       <c r="AC24"/>
       <c r="AD24"/>
       <c r="AE24"/>
       <c r="AF24"/>
     </row>
-    <row r="25" spans="1:32" ht="17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="B25" s="44">
+      <c r="B25" s="58">
         <v>93579.540999999997</v>
       </c>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="40"/>
-      <c r="F25" s="45"/>
+      <c r="C25" s="55"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="59"/>
       <c r="G25" s="15"/>
-      <c r="H25" s="44">
+      <c r="H25" s="58">
         <v>104772.751</v>
       </c>
-      <c r="I25" s="40"/>
-      <c r="J25" s="40"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="45"/>
+      <c r="I25" s="55"/>
+      <c r="J25" s="55"/>
+      <c r="K25" s="55"/>
+      <c r="L25" s="59"/>
       <c r="M25" s="6"/>
       <c r="N25" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="O25" s="68" t="s">
+      <c r="O25" s="52" t="s">
         <v>92</v>
       </c>
       <c r="P25" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="Q25" s="67" t="s">
+      <c r="Q25" s="51" t="s">
         <v>92</v>
       </c>
       <c r="R25" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="S25" s="69" t="s">
-        <v>92</v>
-      </c>
-      <c r="T25" s="58"/>
-      <c r="U25" s="57" t="s">
+      <c r="S25" s="53" t="s">
+        <v>92</v>
+      </c>
+      <c r="T25" s="16"/>
+      <c r="U25" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="V25" s="44">
+      <c r="V25" s="58">
         <v>59389.061000000002</v>
       </c>
-      <c r="W25" s="40"/>
-      <c r="X25" s="40"/>
-      <c r="Y25" s="40"/>
-      <c r="Z25" s="45"/>
+      <c r="W25" s="55"/>
+      <c r="X25" s="55"/>
+      <c r="Y25" s="55"/>
+      <c r="Z25" s="59"/>
       <c r="AA25"/>
       <c r="AB25"/>
       <c r="AC25"/>
@@ -10398,20 +11628,11 @@
       <c r="AE25"/>
       <c r="AF25"/>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A26" s="52"/>
-      <c r="B26" s="52"/>
-      <c r="C26" s="52"/>
-      <c r="D26" s="52"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="51"/>
-      <c r="G26" s="52"/>
-      <c r="H26" s="52"/>
-      <c r="I26" s="52"/>
-      <c r="J26" s="52"/>
-      <c r="K26" s="52"/>
-      <c r="L26" s="52"/>
-      <c r="M26" s="52"/>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="B26" s="1"/>
+      <c r="F26" s="16"/>
+      <c r="H26" s="1"/>
+      <c r="L26" s="1"/>
       <c r="N26" s="34" t="s">
         <v>151</v>
       </c>
@@ -10421,7 +11642,7 @@
       <c r="P26" s="16">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="Q26" s="66">
+      <c r="Q26" s="50">
         <v>0.125</v>
       </c>
       <c r="R26" s="16">
@@ -10430,28 +11651,12 @@
       <c r="S26" s="37">
         <v>0.161</v>
       </c>
-      <c r="T26" s="52"/>
-      <c r="U26" s="52"/>
-      <c r="V26" s="52"/>
-      <c r="W26" s="52"/>
-      <c r="X26" s="52"/>
-      <c r="Y26" s="52"/>
-      <c r="Z26" s="52"/>
-    </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A27" s="52"/>
-      <c r="B27" s="52"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="51"/>
-      <c r="G27" s="52"/>
-      <c r="H27" s="52"/>
-      <c r="I27" s="52"/>
-      <c r="J27" s="52"/>
-      <c r="K27" s="52"/>
-      <c r="L27" s="52"/>
-      <c r="M27" s="52"/>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="B27" s="1"/>
+      <c r="F27" s="16"/>
+      <c r="H27" s="1"/>
+      <c r="L27" s="1"/>
       <c r="N27" s="34" t="s">
         <v>141</v>
       </c>
@@ -10461,7 +11666,7 @@
       <c r="P27" s="16">
         <v>2.9000000000000001E-2</v>
       </c>
-      <c r="Q27" s="66">
+      <c r="Q27" s="50">
         <v>0.96799999999999997</v>
       </c>
       <c r="R27" s="16">
@@ -10470,28 +11675,12 @@
       <c r="S27" s="37">
         <v>5.5E-2</v>
       </c>
-      <c r="T27" s="52"/>
-      <c r="U27" s="52"/>
-      <c r="V27" s="52"/>
-      <c r="W27" s="52"/>
-      <c r="X27" s="52"/>
-      <c r="Y27" s="52"/>
-      <c r="Z27" s="52"/>
-    </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A28" s="52"/>
-      <c r="B28" s="52"/>
-      <c r="C28" s="52"/>
-      <c r="D28" s="52"/>
-      <c r="E28" s="52"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="52"/>
-      <c r="H28" s="52"/>
-      <c r="I28" s="52"/>
-      <c r="J28" s="52"/>
-      <c r="K28" s="52"/>
-      <c r="L28" s="52"/>
-      <c r="M28" s="52"/>
+    </row>
+    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="B28" s="1"/>
+      <c r="F28" s="16"/>
+      <c r="H28" s="1"/>
+      <c r="L28" s="1"/>
       <c r="N28" s="34" t="s">
         <v>142</v>
       </c>
@@ -10501,7 +11690,7 @@
       <c r="P28" s="16">
         <v>2.3E-2</v>
       </c>
-      <c r="Q28" s="66">
+      <c r="Q28" s="50">
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="R28" s="16">
@@ -10510,28 +11699,12 @@
       <c r="S28" s="37">
         <v>0.113</v>
       </c>
-      <c r="T28" s="52"/>
-      <c r="U28" s="52"/>
-      <c r="V28" s="52"/>
-      <c r="W28" s="52"/>
-      <c r="X28" s="52"/>
-      <c r="Y28" s="52"/>
-      <c r="Z28" s="52"/>
-    </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A29" s="52"/>
-      <c r="B29" s="52"/>
-      <c r="C29" s="52"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="52"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="52"/>
-      <c r="H29" s="52"/>
-      <c r="I29" s="52"/>
-      <c r="J29" s="52"/>
-      <c r="K29" s="52"/>
-      <c r="L29" s="52"/>
-      <c r="M29" s="52"/>
+    </row>
+    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="B29" s="1"/>
+      <c r="F29" s="16"/>
+      <c r="H29" s="1"/>
+      <c r="L29" s="1"/>
       <c r="N29" s="36" t="s">
         <v>140</v>
       </c>
@@ -10541,7 +11714,7 @@
       <c r="P29" s="16">
         <v>2.1999999999999999E-2</v>
       </c>
-      <c r="Q29" s="66" t="s">
+      <c r="Q29" s="50" t="s">
         <v>24</v>
       </c>
       <c r="R29" s="16">
@@ -10550,928 +11723,373 @@
       <c r="S29" s="32">
         <v>-7.4999999999999997E-2</v>
       </c>
-      <c r="T29" s="52"/>
-      <c r="U29" s="52"/>
-      <c r="V29" s="52"/>
-      <c r="W29" s="52"/>
-      <c r="X29" s="52"/>
-      <c r="Y29" s="52"/>
-      <c r="Z29" s="52"/>
-    </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A30" s="52"/>
-      <c r="B30" s="52"/>
-      <c r="C30" s="52"/>
-      <c r="D30" s="52"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="51"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="52"/>
-      <c r="K30" s="52"/>
-      <c r="L30" s="52"/>
-      <c r="M30" s="52"/>
-      <c r="N30" s="65" t="s">
+    </row>
+    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="B30" s="1"/>
+      <c r="F30" s="16"/>
+      <c r="H30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="N30" s="49" t="s">
         <v>105</v>
       </c>
       <c r="O30" s="35"/>
       <c r="P30" s="14"/>
-      <c r="Q30" s="49"/>
+      <c r="Q30" s="41"/>
       <c r="R30" s="14"/>
       <c r="S30" s="31"/>
-      <c r="T30" s="52"/>
-      <c r="U30" s="52"/>
-      <c r="V30" s="52"/>
-      <c r="W30" s="52"/>
-      <c r="X30" s="52"/>
-      <c r="Y30" s="52"/>
-      <c r="Z30" s="52"/>
-    </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A31" s="52"/>
-      <c r="B31" s="52"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="51"/>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="52"/>
-      <c r="K31" s="52"/>
-      <c r="L31" s="52"/>
-      <c r="M31" s="52"/>
-      <c r="N31" s="57" t="s">
+    </row>
+    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="B31" s="1"/>
+      <c r="F31" s="16"/>
+      <c r="H31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="N31" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="O31" s="44">
+      <c r="O31" s="58">
         <v>54236.89</v>
       </c>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="40"/>
-      <c r="S31" s="45"/>
-      <c r="T31" s="52"/>
-      <c r="U31" s="52"/>
-      <c r="V31" s="52"/>
-      <c r="W31" s="52"/>
-      <c r="X31" s="52"/>
-      <c r="Y31" s="52"/>
-      <c r="Z31" s="52"/>
-    </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A32" s="52"/>
-      <c r="B32" s="52"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="51"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
-      <c r="K32" s="52"/>
-      <c r="L32" s="52"/>
-      <c r="M32" s="52"/>
-      <c r="N32" s="52"/>
-      <c r="O32" s="52"/>
-      <c r="P32" s="52"/>
-      <c r="Q32" s="52"/>
-      <c r="R32" s="52"/>
-      <c r="S32" s="52"/>
-      <c r="T32" s="52"/>
-      <c r="U32" s="52"/>
-      <c r="V32" s="52"/>
-      <c r="W32" s="52"/>
-      <c r="X32" s="52"/>
-      <c r="Y32" s="52"/>
-      <c r="Z32" s="52"/>
-    </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A33" s="52"/>
-      <c r="B33" s="52"/>
-      <c r="C33" s="52"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="51"/>
-      <c r="G33" s="52"/>
-      <c r="H33" s="52"/>
-      <c r="I33" s="52"/>
-      <c r="J33" s="52"/>
-      <c r="K33" s="52"/>
-      <c r="L33" s="52"/>
-      <c r="M33" s="52"/>
-      <c r="N33" s="52"/>
-      <c r="O33" s="52"/>
-      <c r="P33" s="52"/>
-      <c r="Q33" s="52"/>
-      <c r="R33" s="52"/>
-      <c r="S33" s="52"/>
-      <c r="T33" s="52"/>
-      <c r="U33" s="52"/>
-      <c r="V33" s="52"/>
-      <c r="W33" s="52"/>
-      <c r="X33" s="52"/>
-      <c r="Y33" s="52"/>
-      <c r="Z33" s="52"/>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A34" s="52"/>
-      <c r="B34" s="52"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="51"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="52"/>
-      <c r="J34" s="52"/>
-      <c r="K34" s="52"/>
-      <c r="L34" s="52"/>
-      <c r="M34" s="52"/>
-      <c r="N34" s="52"/>
-      <c r="O34" s="52"/>
-      <c r="P34" s="52"/>
-      <c r="Q34" s="52"/>
-      <c r="R34" s="52"/>
-      <c r="S34" s="52"/>
-      <c r="T34" s="52"/>
-      <c r="U34" s="52"/>
-      <c r="V34" s="52"/>
-      <c r="W34" s="52"/>
-      <c r="X34" s="52"/>
-      <c r="Y34" s="52"/>
-      <c r="Z34" s="52"/>
-    </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A35" s="52"/>
-      <c r="B35" s="52"/>
-      <c r="C35" s="52"/>
-      <c r="D35" s="52"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="52"/>
-      <c r="H35" s="52"/>
-      <c r="I35" s="52"/>
-      <c r="J35" s="52"/>
-      <c r="K35" s="52"/>
-      <c r="L35" s="52"/>
-      <c r="M35" s="52"/>
-      <c r="N35" s="52"/>
-      <c r="O35" s="52"/>
-      <c r="P35" s="52"/>
-      <c r="Q35" s="52"/>
-      <c r="R35" s="52"/>
-      <c r="S35" s="52"/>
-      <c r="T35" s="52"/>
-      <c r="U35" s="52"/>
-      <c r="V35" s="52"/>
-      <c r="W35" s="52"/>
-      <c r="X35" s="52"/>
-      <c r="Y35" s="52"/>
-      <c r="Z35" s="52"/>
-    </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A36" s="52"/>
-      <c r="B36" s="52"/>
-      <c r="C36" s="52"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="52"/>
-      <c r="H36" s="52"/>
-      <c r="I36" s="52"/>
-      <c r="J36" s="52"/>
-      <c r="K36" s="52"/>
-      <c r="L36" s="52"/>
-      <c r="M36" s="52"/>
-      <c r="N36" s="47"/>
-      <c r="O36" s="47"/>
-      <c r="P36" s="47"/>
-      <c r="Q36" s="47"/>
-      <c r="R36" s="47"/>
-      <c r="S36" s="47"/>
-      <c r="T36" s="52"/>
-      <c r="U36" s="52"/>
-      <c r="V36" s="52"/>
-      <c r="W36" s="52"/>
-      <c r="X36" s="52"/>
-      <c r="Y36" s="52"/>
-      <c r="Z36" s="52"/>
-    </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A37" s="52"/>
-      <c r="B37" s="52"/>
-      <c r="C37" s="52"/>
-      <c r="D37" s="52"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="51"/>
-      <c r="G37" s="52"/>
-      <c r="H37" s="52"/>
-      <c r="I37" s="52"/>
-      <c r="J37" s="52"/>
-      <c r="K37" s="52"/>
-      <c r="L37" s="52"/>
-      <c r="M37" s="52"/>
-      <c r="N37" s="47"/>
+      <c r="P31" s="55"/>
+      <c r="Q31" s="55"/>
+      <c r="R31" s="55"/>
+      <c r="S31" s="59"/>
+    </row>
+    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="B32" s="1"/>
+      <c r="F32" s="16"/>
+      <c r="H32" s="1"/>
+      <c r="L32" s="1"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B33" s="1"/>
+      <c r="F33" s="16"/>
+      <c r="H33" s="1"/>
+      <c r="L33" s="1"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B34" s="1"/>
+      <c r="F34" s="16"/>
+      <c r="H34" s="1"/>
+      <c r="L34" s="1"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B35" s="1"/>
+      <c r="F35" s="16"/>
+      <c r="H35" s="1"/>
+      <c r="L35" s="1"/>
+    </row>
+    <row r="36" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B36" s="1"/>
+      <c r="F36" s="16"/>
+      <c r="H36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="N36" s="39"/>
+      <c r="O36" s="39"/>
+      <c r="P36" s="39"/>
+      <c r="Q36" s="39"/>
+      <c r="R36" s="39"/>
+      <c r="S36" s="39"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="B37" s="1"/>
+      <c r="F37" s